--- a/team_stats_2026.xlsx
+++ b/team_stats_2026.xlsx
@@ -546,31 +546,31 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G2" t="n">
-        <v>2166.7</v>
+        <v>2170.1</v>
       </c>
       <c r="H2" t="n">
-        <v>3.9474</v>
+        <v>3.9737</v>
       </c>
       <c r="I2" t="n">
-        <v>122.78</v>
+        <v>123.79</v>
       </c>
       <c r="J2" t="n">
-        <v>92.67</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>30.11</v>
+        <v>30.64</v>
       </c>
       <c r="L2" t="n">
-        <v>0.279</v>
+        <v>0.2823</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1537</v>
+        <v>0.1519</v>
       </c>
       <c r="N2" t="n">
-        <v>25</v>
+        <v>28.2</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -591,7 +591,7 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>1691.3</v>
+        <v>1690.2</v>
       </c>
     </row>
     <row r="3">
@@ -688,31 +688,31 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G4" t="n">
-        <v>2035.8</v>
+        <v>2030.1</v>
       </c>
       <c r="H4" t="n">
-        <v>3.5611</v>
+        <v>3.0314</v>
       </c>
       <c r="I4" t="n">
-        <v>119.51</v>
+        <v>118.09</v>
       </c>
       <c r="J4" t="n">
-        <v>96.20999999999999</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>23.3</v>
+        <v>21.66</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3131</v>
+        <v>0.3174</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1465</v>
+        <v>0.1477</v>
       </c>
       <c r="N4" t="n">
-        <v>3.6</v>
+        <v>-3.2</v>
       </c>
       <c r="O4" t="n">
         <v>7</v>
@@ -733,7 +733,7 @@
         <v>10</v>
       </c>
       <c r="U4" t="n">
-        <v>1671.8</v>
+        <v>1692.3</v>
       </c>
     </row>
     <row r="5">
@@ -830,31 +830,31 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G6" t="n">
-        <v>1909.3</v>
+        <v>1912.8</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.9652</v>
+        <v>-1.7463</v>
       </c>
       <c r="I6" t="n">
-        <v>116.77</v>
+        <v>117.37</v>
       </c>
       <c r="J6" t="n">
-        <v>101.52</v>
+        <v>101.08</v>
       </c>
       <c r="K6" t="n">
-        <v>15.26</v>
+        <v>16.3</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3579</v>
+        <v>0.3535</v>
       </c>
       <c r="M6" t="n">
-        <v>0.169</v>
+        <v>0.1667</v>
       </c>
       <c r="N6" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="O6" t="n">
         <v>18</v>
@@ -875,7 +875,7 @@
         <v>20</v>
       </c>
       <c r="U6" t="n">
-        <v>1704.1</v>
+        <v>1692.2</v>
       </c>
     </row>
     <row r="7">
@@ -901,31 +901,31 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G7" t="n">
-        <v>1826.1</v>
+        <v>1830.2</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.8169</v>
+        <v>-3.7351</v>
       </c>
       <c r="I7" t="n">
-        <v>119.14</v>
+        <v>119.03</v>
       </c>
       <c r="J7" t="n">
-        <v>100.72</v>
+        <v>100.17</v>
       </c>
       <c r="K7" t="n">
-        <v>18.42</v>
+        <v>18.86</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2919</v>
+        <v>0.29</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1608</v>
+        <v>0.1596</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="O7" t="n">
         <v>19</v>
@@ -946,7 +946,7 @@
         <v>17</v>
       </c>
       <c r="U7" t="n">
-        <v>1680.4</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="8">
@@ -1185,31 +1185,31 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G11" t="n">
-        <v>1798.4</v>
+        <v>1824.2</v>
       </c>
       <c r="H11" t="n">
-        <v>6.9484</v>
+        <v>6.8019</v>
       </c>
       <c r="I11" t="n">
-        <v>110.3</v>
+        <v>110.58</v>
       </c>
       <c r="J11" t="n">
-        <v>101.19</v>
+        <v>101.35</v>
       </c>
       <c r="K11" t="n">
-        <v>9.109999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3139</v>
+        <v>0.3181</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1514</v>
+        <v>0.1536</v>
       </c>
       <c r="N11" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="O11" t="n">
         <v>49</v>
@@ -1230,7 +1230,7 @@
         <v>45</v>
       </c>
       <c r="U11" t="n">
-        <v>1659.6</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="12">
@@ -1469,31 +1469,31 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G15" t="n">
-        <v>1680.5</v>
+        <v>1685.2</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9785</v>
+        <v>1.8461</v>
       </c>
       <c r="I15" t="n">
-        <v>115.5</v>
+        <v>115.35</v>
       </c>
       <c r="J15" t="n">
-        <v>103.4</v>
+        <v>102.31</v>
       </c>
       <c r="K15" t="n">
-        <v>12.1</v>
+        <v>13.04</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3187</v>
+        <v>0.3159</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1387</v>
+        <v>0.1414</v>
       </c>
       <c r="N15" t="n">
-        <v>7.8</v>
+        <v>10.8</v>
       </c>
       <c r="O15" t="n">
         <v>104</v>
@@ -1514,7 +1514,7 @@
         <v>93</v>
       </c>
       <c r="U15" t="n">
-        <v>1429.3</v>
+        <v>1429.5</v>
       </c>
     </row>
     <row r="16">
@@ -1824,31 +1824,31 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G20" t="n">
-        <v>1991</v>
+        <v>1993.6</v>
       </c>
       <c r="H20" t="n">
-        <v>4.005</v>
+        <v>4.3059</v>
       </c>
       <c r="I20" t="n">
-        <v>120.45</v>
+        <v>121.4</v>
       </c>
       <c r="J20" t="n">
-        <v>98.51000000000001</v>
+        <v>98.63</v>
       </c>
       <c r="K20" t="n">
-        <v>21.94</v>
+        <v>22.77</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3301</v>
+        <v>0.3333</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1588</v>
+        <v>0.1547</v>
       </c>
       <c r="N20" t="n">
-        <v>17.8</v>
+        <v>22.8</v>
       </c>
       <c r="O20" t="n">
         <v>4</v>
@@ -1869,7 +1869,7 @@
         <v>4</v>
       </c>
       <c r="U20" t="n">
-        <v>1706.1</v>
+        <v>1699.9</v>
       </c>
     </row>
     <row r="21">
@@ -1966,31 +1966,31 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G22" t="n">
-        <v>2060.2</v>
+        <v>2034.5</v>
       </c>
       <c r="H22" t="n">
-        <v>11.6236</v>
+        <v>11.3167</v>
       </c>
       <c r="I22" t="n">
-        <v>119.2</v>
+        <v>118.24</v>
       </c>
       <c r="J22" t="n">
-        <v>105.14</v>
+        <v>105.38</v>
       </c>
       <c r="K22" t="n">
-        <v>14.06</v>
+        <v>12.86</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2931</v>
+        <v>0.2929</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1537</v>
+        <v>0.1562</v>
       </c>
       <c r="N22" t="n">
-        <v>9.4</v>
+        <v>7.2</v>
       </c>
       <c r="O22" t="n">
         <v>13</v>
@@ -2011,7 +2011,7 @@
         <v>13</v>
       </c>
       <c r="U22" t="n">
-        <v>1755.9</v>
+        <v>1753.9</v>
       </c>
     </row>
     <row r="23">
@@ -2108,31 +2108,31 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G24" t="n">
-        <v>1922.8</v>
+        <v>1901.3</v>
       </c>
       <c r="H24" t="n">
-        <v>3.4567</v>
+        <v>2.827</v>
       </c>
       <c r="I24" t="n">
-        <v>118.43</v>
+        <v>117.49</v>
       </c>
       <c r="J24" t="n">
-        <v>105.6</v>
+        <v>106.29</v>
       </c>
       <c r="K24" t="n">
-        <v>12.83</v>
+        <v>11.21</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2952</v>
+        <v>0.2953</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1442</v>
+        <v>0.1466</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.8</v>
+        <v>-8</v>
       </c>
       <c r="O24" t="n">
         <v>23</v>
@@ -2153,7 +2153,7 @@
         <v>23</v>
       </c>
       <c r="U24" t="n">
-        <v>1711.8</v>
+        <v>1712.1</v>
       </c>
     </row>
     <row r="25">
@@ -2179,31 +2179,31 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G25" t="n">
-        <v>1885.3</v>
+        <v>1864.3</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.313</v>
+        <v>-0.3251</v>
       </c>
       <c r="I25" t="n">
-        <v>120.72</v>
+        <v>119.66</v>
       </c>
       <c r="J25" t="n">
-        <v>102.92</v>
+        <v>104.27</v>
       </c>
       <c r="K25" t="n">
-        <v>17.79</v>
+        <v>15.38</v>
       </c>
       <c r="L25" t="n">
-        <v>0.3024</v>
+        <v>0.3059</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1489</v>
+        <v>0.1487</v>
       </c>
       <c r="N25" t="n">
-        <v>5.6</v>
+        <v>-4.6</v>
       </c>
       <c r="O25" t="n">
         <v>26</v>
@@ -2224,7 +2224,7 @@
         <v>26</v>
       </c>
       <c r="U25" t="n">
-        <v>1591.1</v>
+        <v>1591.6</v>
       </c>
     </row>
     <row r="26">
@@ -2253,7 +2253,7 @@
         <v>117</v>
       </c>
       <c r="G26" t="n">
-        <v>1761</v>
+        <v>1757.4</v>
       </c>
       <c r="H26" t="n">
         <v>13.1837</v>
@@ -2321,31 +2321,31 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G27" t="n">
-        <v>1795.5</v>
+        <v>1810.7</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.7475000000000001</v>
+        <v>-0.8284</v>
       </c>
       <c r="I27" t="n">
-        <v>120.49</v>
+        <v>120.8</v>
       </c>
       <c r="J27" t="n">
-        <v>105.83</v>
+        <v>106.43</v>
       </c>
       <c r="K27" t="n">
-        <v>14.66</v>
+        <v>14.38</v>
       </c>
       <c r="L27" t="n">
-        <v>0.3208</v>
+        <v>0.3238</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1349</v>
+        <v>0.1381</v>
       </c>
       <c r="N27" t="n">
-        <v>2.8</v>
+        <v>8</v>
       </c>
       <c r="O27" t="n">
         <v>33</v>
@@ -2366,7 +2366,7 @@
         <v>31</v>
       </c>
       <c r="U27" t="n">
-        <v>1628.9</v>
+        <v>1647.3</v>
       </c>
     </row>
     <row r="28">
@@ -2392,31 +2392,31 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G28" t="n">
-        <v>1821.3</v>
+        <v>1842</v>
       </c>
       <c r="H28" t="n">
-        <v>2.4427</v>
+        <v>2.4672</v>
       </c>
       <c r="I28" t="n">
-        <v>116.64</v>
+        <v>116.51</v>
       </c>
       <c r="J28" t="n">
-        <v>108.06</v>
+        <v>106.69</v>
       </c>
       <c r="K28" t="n">
-        <v>8.59</v>
+        <v>9.82</v>
       </c>
       <c r="L28" t="n">
-        <v>0.2987</v>
+        <v>0.2986</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1299</v>
+        <v>0.1302</v>
       </c>
       <c r="N28" t="n">
-        <v>-7.6</v>
+        <v>2.4</v>
       </c>
       <c r="O28" t="n">
         <v>41</v>
@@ -2437,7 +2437,7 @@
         <v>39</v>
       </c>
       <c r="U28" t="n">
-        <v>1672.3</v>
+        <v>1687.7</v>
       </c>
     </row>
     <row r="29">
@@ -2463,31 +2463,31 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G29" t="n">
-        <v>1786.5</v>
+        <v>1836.9</v>
       </c>
       <c r="H29" t="n">
-        <v>4.8041</v>
+        <v>4.4256</v>
       </c>
       <c r="I29" t="n">
-        <v>117.75</v>
+        <v>118.62</v>
       </c>
       <c r="J29" t="n">
-        <v>106.35</v>
+        <v>106.73</v>
       </c>
       <c r="K29" t="n">
-        <v>11.4</v>
+        <v>11.89</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3057</v>
+        <v>0.3028</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1422</v>
+        <v>0.1406</v>
       </c>
       <c r="N29" t="n">
-        <v>-5.4</v>
+        <v>-0.6</v>
       </c>
       <c r="O29" t="n">
         <v>38</v>
@@ -2508,7 +2508,7 @@
         <v>43</v>
       </c>
       <c r="U29" t="n">
-        <v>1644.3</v>
+        <v>1655.1</v>
       </c>
     </row>
     <row r="30">
@@ -2605,31 +2605,31 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G31" t="n">
-        <v>1561</v>
+        <v>1563.2</v>
       </c>
       <c r="H31" t="n">
-        <v>3.2801</v>
+        <v>3.2331</v>
       </c>
       <c r="I31" t="n">
-        <v>113.06</v>
+        <v>113.58</v>
       </c>
       <c r="J31" t="n">
-        <v>98.08</v>
+        <v>98.86</v>
       </c>
       <c r="K31" t="n">
-        <v>14.97</v>
+        <v>14.72</v>
       </c>
       <c r="L31" t="n">
-        <v>0.3122</v>
+        <v>0.311</v>
       </c>
       <c r="M31" t="n">
-        <v>0.1337</v>
+        <v>0.1336</v>
       </c>
       <c r="N31" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="O31" t="n">
         <v>88</v>
@@ -2650,7 +2650,7 @@
         <v>85</v>
       </c>
       <c r="U31" t="n">
-        <v>1384.3</v>
+        <v>1382.6</v>
       </c>
     </row>
     <row r="32">
@@ -2889,31 +2889,31 @@
         <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G35" t="n">
-        <v>1392.4</v>
+        <v>1390.3</v>
       </c>
       <c r="H35" t="n">
-        <v>1.0385</v>
+        <v>1.1323</v>
       </c>
       <c r="I35" t="n">
-        <v>111.17</v>
+        <v>111.8</v>
       </c>
       <c r="J35" t="n">
-        <v>102.98</v>
+        <v>101.74</v>
       </c>
       <c r="K35" t="n">
-        <v>8.19</v>
+        <v>10.06</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2107</v>
+        <v>0.2176</v>
       </c>
       <c r="M35" t="n">
-        <v>0.1343</v>
+        <v>0.1378</v>
       </c>
       <c r="N35" t="n">
-        <v>15</v>
+        <v>18.4</v>
       </c>
       <c r="O35" t="n">
         <v>221</v>
@@ -2934,7 +2934,7 @@
         <v>223</v>
       </c>
       <c r="U35" t="n">
-        <v>1370.8</v>
+        <v>1368.2</v>
       </c>
     </row>
     <row r="36">
@@ -3102,31 +3102,31 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G38" t="n">
-        <v>2024.8</v>
+        <v>1990.6</v>
       </c>
       <c r="H38" t="n">
-        <v>12.1666</v>
+        <v>11.3442</v>
       </c>
       <c r="I38" t="n">
-        <v>116.39</v>
+        <v>115.07</v>
       </c>
       <c r="J38" t="n">
-        <v>96.90000000000001</v>
+        <v>98.04000000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>19.5</v>
+        <v>17.03</v>
       </c>
       <c r="L38" t="n">
-        <v>0.2407</v>
+        <v>0.2419</v>
       </c>
       <c r="M38" t="n">
-        <v>0.1368</v>
+        <v>0.1401</v>
       </c>
       <c r="N38" t="n">
-        <v>13</v>
+        <v>5.2</v>
       </c>
       <c r="O38" t="n">
         <v>11</v>
@@ -3147,7 +3147,7 @@
         <v>12</v>
       </c>
       <c r="U38" t="n">
-        <v>1652</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="39">
@@ -3173,31 +3173,31 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G39" t="n">
-        <v>1947.8</v>
+        <v>1951.2</v>
       </c>
       <c r="H39" t="n">
-        <v>14.5268</v>
+        <v>13.9718</v>
       </c>
       <c r="I39" t="n">
-        <v>118.75</v>
+        <v>118.9</v>
       </c>
       <c r="J39" t="n">
-        <v>99.73</v>
+        <v>99.7</v>
       </c>
       <c r="K39" t="n">
-        <v>19.02</v>
+        <v>19.2</v>
       </c>
       <c r="L39" t="n">
-        <v>0.3173</v>
+        <v>0.3157</v>
       </c>
       <c r="M39" t="n">
         <v>0.1519</v>
       </c>
       <c r="N39" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="O39" t="n">
         <v>17</v>
@@ -3218,7 +3218,7 @@
         <v>14</v>
       </c>
       <c r="U39" t="n">
-        <v>1641</v>
+        <v>1635.2</v>
       </c>
     </row>
     <row r="40">
@@ -3244,31 +3244,31 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G40" t="n">
-        <v>1914.8</v>
+        <v>1921</v>
       </c>
       <c r="H40" t="n">
-        <v>2.5315</v>
+        <v>1.9274</v>
       </c>
       <c r="I40" t="n">
-        <v>121.92</v>
+        <v>121.87</v>
       </c>
       <c r="J40" t="n">
-        <v>105.39</v>
+        <v>105.42</v>
       </c>
       <c r="K40" t="n">
-        <v>16.53</v>
+        <v>16.45</v>
       </c>
       <c r="L40" t="n">
-        <v>0.2752</v>
+        <v>0.2854</v>
       </c>
       <c r="M40" t="n">
-        <v>0.1255</v>
+        <v>0.1247</v>
       </c>
       <c r="N40" t="n">
-        <v>0.4</v>
+        <v>-1.6</v>
       </c>
       <c r="O40" t="n">
         <v>14</v>
@@ -3289,7 +3289,7 @@
         <v>18</v>
       </c>
       <c r="U40" t="n">
-        <v>1688.9</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="41">
@@ -3315,31 +3315,31 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G41" t="n">
         <v>1921.2</v>
       </c>
       <c r="H41" t="n">
-        <v>2.539</v>
+        <v>2.4067</v>
       </c>
       <c r="I41" t="n">
-        <v>116.62</v>
+        <v>115.82</v>
       </c>
       <c r="J41" t="n">
-        <v>103.11</v>
+        <v>102.6</v>
       </c>
       <c r="K41" t="n">
-        <v>13.51</v>
+        <v>13.22</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2711</v>
+        <v>0.2692</v>
       </c>
       <c r="M41" t="n">
-        <v>0.1371</v>
+        <v>0.1364</v>
       </c>
       <c r="N41" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="O41" t="n">
         <v>28</v>
@@ -3360,7 +3360,7 @@
         <v>25</v>
       </c>
       <c r="U41" t="n">
-        <v>1647.2</v>
+        <v>1655.5</v>
       </c>
     </row>
     <row r="42">
@@ -3457,28 +3457,28 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G43" t="n">
-        <v>1823</v>
+        <v>1839.8</v>
       </c>
       <c r="H43" t="n">
-        <v>8.086399999999999</v>
+        <v>7.5365</v>
       </c>
       <c r="I43" t="n">
-        <v>115.8</v>
+        <v>115.83</v>
       </c>
       <c r="J43" t="n">
-        <v>109.86</v>
+        <v>110.45</v>
       </c>
       <c r="K43" t="n">
-        <v>5.94</v>
+        <v>5.38</v>
       </c>
       <c r="L43" t="n">
-        <v>0.3088</v>
+        <v>0.3093</v>
       </c>
       <c r="M43" t="n">
-        <v>0.1558</v>
+        <v>0.1541</v>
       </c>
       <c r="N43" t="n">
         <v>3.6</v>
@@ -3502,7 +3502,7 @@
         <v>46</v>
       </c>
       <c r="U43" t="n">
-        <v>1687.1</v>
+        <v>1687.9</v>
       </c>
     </row>
     <row r="44">
@@ -3528,31 +3528,31 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G44" t="n">
-        <v>1754.7</v>
+        <v>1751.4</v>
       </c>
       <c r="H44" t="n">
-        <v>8.5853</v>
+        <v>8.2582</v>
       </c>
       <c r="I44" t="n">
-        <v>119.4</v>
+        <v>118.51</v>
       </c>
       <c r="J44" t="n">
-        <v>106.58</v>
+        <v>107.99</v>
       </c>
       <c r="K44" t="n">
-        <v>12.82</v>
+        <v>10.52</v>
       </c>
       <c r="L44" t="n">
-        <v>0.2754</v>
+        <v>0.2827</v>
       </c>
       <c r="M44" t="n">
-        <v>0.1284</v>
+        <v>0.1274</v>
       </c>
       <c r="N44" t="n">
-        <v>-10.6</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="O44" t="n">
         <v>31</v>
@@ -3573,7 +3573,7 @@
         <v>29</v>
       </c>
       <c r="U44" t="n">
-        <v>1655.5</v>
+        <v>1678.8</v>
       </c>
     </row>
     <row r="45">
@@ -3602,7 +3602,7 @@
         <v>117</v>
       </c>
       <c r="G45" t="n">
-        <v>1818.7</v>
+        <v>1785.1</v>
       </c>
       <c r="H45" t="n">
         <v>2.0552</v>
@@ -4025,31 +4025,31 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G51" t="n">
-        <v>1449.7</v>
+        <v>1458.6</v>
       </c>
       <c r="H51" t="n">
-        <v>2.2967</v>
+        <v>2.1359</v>
       </c>
       <c r="I51" t="n">
-        <v>104.35</v>
+        <v>105.36</v>
       </c>
       <c r="J51" t="n">
-        <v>101.66</v>
+        <v>101.08</v>
       </c>
       <c r="K51" t="n">
-        <v>2.69</v>
+        <v>4.28</v>
       </c>
       <c r="L51" t="n">
-        <v>0.2629</v>
+        <v>0.2592</v>
       </c>
       <c r="M51" t="n">
-        <v>0.1739</v>
+        <v>0.1706</v>
       </c>
       <c r="N51" t="n">
-        <v>-7</v>
+        <v>0.2</v>
       </c>
       <c r="O51" t="n">
         <v>159</v>
@@ -4070,7 +4070,7 @@
         <v>151</v>
       </c>
       <c r="U51" t="n">
-        <v>1420</v>
+        <v>1417.2</v>
       </c>
     </row>
     <row r="52">
@@ -4096,31 +4096,31 @@
         <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G52" t="n">
-        <v>1405.9</v>
+        <v>1405</v>
       </c>
       <c r="H52" t="n">
-        <v>3.6589</v>
+        <v>3.4361</v>
       </c>
       <c r="I52" t="n">
-        <v>107.64</v>
+        <v>108.68</v>
       </c>
       <c r="J52" t="n">
-        <v>97.78</v>
+        <v>98.20999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>9.859999999999999</v>
+        <v>10.47</v>
       </c>
       <c r="L52" t="n">
-        <v>0.3171</v>
+        <v>0.3193</v>
       </c>
       <c r="M52" t="n">
-        <v>0.1839</v>
+        <v>0.1857</v>
       </c>
       <c r="N52" t="n">
-        <v>22</v>
+        <v>27.2</v>
       </c>
       <c r="O52" t="n">
         <v>199</v>
@@ -4141,7 +4141,7 @@
         <v>202</v>
       </c>
       <c r="U52" t="n">
-        <v>1387.3</v>
+        <v>1378.5</v>
       </c>
     </row>
     <row r="53">
@@ -4238,31 +4238,31 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G54" t="n">
-        <v>2237.1</v>
+        <v>2242.8</v>
       </c>
       <c r="H54" t="n">
-        <v>9.117900000000001</v>
+        <v>8.6394</v>
       </c>
       <c r="I54" t="n">
-        <v>121.31</v>
+        <v>120.84</v>
       </c>
       <c r="J54" t="n">
-        <v>95.70999999999999</v>
+        <v>95.38</v>
       </c>
       <c r="K54" t="n">
-        <v>25.61</v>
+        <v>25.46</v>
       </c>
       <c r="L54" t="n">
-        <v>0.2966</v>
+        <v>0.2935</v>
       </c>
       <c r="M54" t="n">
-        <v>0.1491</v>
+        <v>0.1524</v>
       </c>
       <c r="N54" t="n">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -4283,7 +4283,7 @@
         <v>3</v>
       </c>
       <c r="U54" t="n">
-        <v>1737.1</v>
+        <v>1747.2</v>
       </c>
     </row>
     <row r="55">
@@ -4309,31 +4309,31 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G55" t="n">
-        <v>1994.4</v>
+        <v>1996.4</v>
       </c>
       <c r="H55" t="n">
-        <v>9.371</v>
+        <v>8.884600000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>125.48</v>
+        <v>125.29</v>
       </c>
       <c r="J55" t="n">
-        <v>103.59</v>
+        <v>102.13</v>
       </c>
       <c r="K55" t="n">
-        <v>21.89</v>
+        <v>23.17</v>
       </c>
       <c r="L55" t="n">
-        <v>0.3241</v>
+        <v>0.3216</v>
       </c>
       <c r="M55" t="n">
-        <v>0.1319</v>
+        <v>0.1296</v>
       </c>
       <c r="N55" t="n">
-        <v>7.8</v>
+        <v>13.4</v>
       </c>
       <c r="O55" t="n">
         <v>5</v>
@@ -4354,7 +4354,7 @@
         <v>5</v>
       </c>
       <c r="U55" t="n">
-        <v>1721.9</v>
+        <v>1710.4</v>
       </c>
     </row>
     <row r="56">
@@ -4380,31 +4380,31 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G56" t="n">
-        <v>1997.6</v>
+        <v>1972.3</v>
       </c>
       <c r="H56" t="n">
-        <v>11.7834</v>
+        <v>11.3738</v>
       </c>
       <c r="I56" t="n">
-        <v>111.06</v>
+        <v>110.16</v>
       </c>
       <c r="J56" t="n">
-        <v>100.88</v>
+        <v>100.46</v>
       </c>
       <c r="K56" t="n">
-        <v>10.18</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L56" t="n">
-        <v>0.2424</v>
+        <v>0.2509</v>
       </c>
       <c r="M56" t="n">
-        <v>0.1489</v>
+        <v>0.1535</v>
       </c>
       <c r="N56" t="n">
-        <v>-6.4</v>
+        <v>-4.8</v>
       </c>
       <c r="O56" t="n">
         <v>16</v>
@@ -4425,7 +4425,7 @@
         <v>15</v>
       </c>
       <c r="U56" t="n">
-        <v>1790.5</v>
+        <v>1777.3</v>
       </c>
     </row>
     <row r="57">
@@ -4451,31 +4451,31 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G57" t="n">
-        <v>1987.5</v>
+        <v>1966.5</v>
       </c>
       <c r="H57" t="n">
-        <v>-1.936</v>
+        <v>-1.6248</v>
       </c>
       <c r="I57" t="n">
-        <v>121.38</v>
+        <v>121.39</v>
       </c>
       <c r="J57" t="n">
-        <v>109.56</v>
+        <v>110.58</v>
       </c>
       <c r="K57" t="n">
-        <v>11.82</v>
+        <v>10.81</v>
       </c>
       <c r="L57" t="n">
-        <v>0.2753</v>
+        <v>0.279</v>
       </c>
       <c r="M57" t="n">
         <v>0.1296</v>
       </c>
       <c r="N57" t="n">
-        <v>10</v>
+        <v>5.2</v>
       </c>
       <c r="O57" t="n">
         <v>15</v>
@@ -4496,7 +4496,7 @@
         <v>16</v>
       </c>
       <c r="U57" t="n">
-        <v>1770.3</v>
+        <v>1769.4</v>
       </c>
     </row>
     <row r="58">
@@ -4522,31 +4522,31 @@
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G58" t="n">
-        <v>1953.4</v>
+        <v>1955.3</v>
       </c>
       <c r="H58" t="n">
-        <v>4.6322</v>
+        <v>4.7636</v>
       </c>
       <c r="I58" t="n">
-        <v>114.23</v>
+        <v>113.73</v>
       </c>
       <c r="J58" t="n">
-        <v>98.26000000000001</v>
+        <v>98.58</v>
       </c>
       <c r="K58" t="n">
-        <v>15.97</v>
+        <v>15.15</v>
       </c>
       <c r="L58" t="n">
-        <v>0.3231</v>
+        <v>0.3268</v>
       </c>
       <c r="M58" t="n">
-        <v>0.1412</v>
+        <v>0.1411</v>
       </c>
       <c r="N58" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="O58" t="n">
         <v>21</v>
@@ -4567,7 +4567,7 @@
         <v>22</v>
       </c>
       <c r="U58" t="n">
-        <v>1685</v>
+        <v>1677.8</v>
       </c>
     </row>
     <row r="59">
@@ -4593,31 +4593,31 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G59" t="n">
-        <v>1910.2</v>
+        <v>1893.4</v>
       </c>
       <c r="H59" t="n">
-        <v>6.1328</v>
+        <v>6.006</v>
       </c>
       <c r="I59" t="n">
-        <v>117.29</v>
+        <v>116.85</v>
       </c>
       <c r="J59" t="n">
-        <v>104.88</v>
+        <v>105.78</v>
       </c>
       <c r="K59" t="n">
-        <v>12.41</v>
+        <v>11.07</v>
       </c>
       <c r="L59" t="n">
-        <v>0.3083</v>
+        <v>0.3101</v>
       </c>
       <c r="M59" t="n">
-        <v>0.1456</v>
+        <v>0.1466</v>
       </c>
       <c r="N59" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="O59" t="n">
         <v>25</v>
@@ -4638,7 +4638,7 @@
         <v>27</v>
       </c>
       <c r="U59" t="n">
-        <v>1715.2</v>
+        <v>1717.2</v>
       </c>
     </row>
     <row r="60">
@@ -4735,31 +4735,31 @@
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G61" t="n">
-        <v>1850</v>
+        <v>1839.7</v>
       </c>
       <c r="H61" t="n">
-        <v>3.4896</v>
+        <v>3.0742</v>
       </c>
       <c r="I61" t="n">
-        <v>113.1</v>
+        <v>112.26</v>
       </c>
       <c r="J61" t="n">
-        <v>99.94</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="K61" t="n">
-        <v>13.16</v>
+        <v>12.36</v>
       </c>
       <c r="L61" t="n">
-        <v>0.2428</v>
+        <v>0.2417</v>
       </c>
       <c r="M61" t="n">
-        <v>0.1391</v>
+        <v>0.1398</v>
       </c>
       <c r="N61" t="n">
-        <v>-6.2</v>
+        <v>-5</v>
       </c>
       <c r="O61" t="n">
         <v>36</v>
@@ -4780,7 +4780,7 @@
         <v>35</v>
       </c>
       <c r="U61" t="n">
-        <v>1642.5</v>
+        <v>1652.1</v>
       </c>
     </row>
     <row r="62">
@@ -4806,31 +4806,31 @@
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G62" t="n">
-        <v>1783.2</v>
+        <v>1768.2</v>
       </c>
       <c r="H62" t="n">
-        <v>-3.3477</v>
+        <v>-2.8893</v>
       </c>
       <c r="I62" t="n">
-        <v>116.22</v>
+        <v>115.23</v>
       </c>
       <c r="J62" t="n">
-        <v>108.21</v>
+        <v>109.22</v>
       </c>
       <c r="K62" t="n">
-        <v>8.01</v>
+        <v>6.01</v>
       </c>
       <c r="L62" t="n">
-        <v>0.2999</v>
+        <v>0.3029</v>
       </c>
       <c r="M62" t="n">
-        <v>0.1675</v>
+        <v>0.1713</v>
       </c>
       <c r="N62" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O62" t="n">
         <v>47</v>
@@ -4851,7 +4851,7 @@
         <v>53</v>
       </c>
       <c r="U62" t="n">
-        <v>1636.2</v>
+        <v>1637.7</v>
       </c>
     </row>
     <row r="63">
@@ -4948,31 +4948,31 @@
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G64" t="n">
-        <v>1773.3</v>
+        <v>1772.7</v>
       </c>
       <c r="H64" t="n">
-        <v>10.2962</v>
+        <v>9.988799999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>120.46</v>
+        <v>120.02</v>
       </c>
       <c r="J64" t="n">
-        <v>103.82</v>
+        <v>103.88</v>
       </c>
       <c r="K64" t="n">
-        <v>16.64</v>
+        <v>16.14</v>
       </c>
       <c r="L64" t="n">
         <v>0.2071</v>
       </c>
       <c r="M64" t="n">
-        <v>0.1391</v>
+        <v>0.1427</v>
       </c>
       <c r="N64" t="n">
-        <v>10.2</v>
+        <v>7.4</v>
       </c>
       <c r="O64" t="n">
         <v>87</v>
@@ -4993,7 +4993,7 @@
         <v>52</v>
       </c>
       <c r="U64" t="n">
-        <v>1410.4</v>
+        <v>1413.1</v>
       </c>
     </row>
     <row r="65">

--- a/team_stats_2026.xlsx
+++ b/team_stats_2026.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,107 +429,107 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Is_FirstFour</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>

--- a/team_stats_2026.xlsx
+++ b/team_stats_2026.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,107 +417,107 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Is_FirstFour</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -984,31 +972,31 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G8" t="n">
-        <v>1813.5</v>
+        <v>1820.1</v>
       </c>
       <c r="H8" t="n">
-        <v>6.893</v>
+        <v>6.5295</v>
       </c>
       <c r="I8" t="n">
-        <v>114.62</v>
+        <v>114.74</v>
       </c>
       <c r="J8" t="n">
-        <v>105.11</v>
+        <v>103.88</v>
       </c>
       <c r="K8" t="n">
-        <v>9.51</v>
+        <v>10.87</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3173</v>
+        <v>0.3148</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1412</v>
+        <v>0.141</v>
       </c>
       <c r="N8" t="n">
-        <v>-3.8</v>
+        <v>-2.2</v>
       </c>
       <c r="O8" t="n">
         <v>34</v>
@@ -1029,7 +1017,7 @@
         <v>33</v>
       </c>
       <c r="U8" t="n">
-        <v>1649.2</v>
+        <v>1643.5</v>
       </c>
     </row>
     <row r="9">
@@ -1055,31 +1043,31 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G9" t="n">
-        <v>1828.2</v>
+        <v>1825.9</v>
       </c>
       <c r="H9" t="n">
-        <v>11.0707</v>
+        <v>10.4518</v>
       </c>
       <c r="I9" t="n">
-        <v>121.57</v>
+        <v>122</v>
       </c>
       <c r="J9" t="n">
-        <v>96.51000000000001</v>
+        <v>96.95</v>
       </c>
       <c r="K9" t="n">
-        <v>25.06</v>
+        <v>25.05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2343</v>
+        <v>0.2326</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1691</v>
+        <v>0.167</v>
       </c>
       <c r="N9" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="O9" t="n">
         <v>27</v>
@@ -1100,7 +1088,7 @@
         <v>24</v>
       </c>
       <c r="U9" t="n">
-        <v>1506.9</v>
+        <v>1501.8</v>
       </c>
     </row>
     <row r="10">
@@ -1129,7 +1117,7 @@
         <v>117</v>
       </c>
       <c r="G10" t="n">
-        <v>1821.4</v>
+        <v>1855.3</v>
       </c>
       <c r="H10" t="n">
         <v>4.8208</v>
@@ -1339,31 +1327,31 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G13" t="n">
-        <v>1782.1</v>
+        <v>1787.4</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1828</v>
+        <v>1.3307</v>
       </c>
       <c r="I13" t="n">
-        <v>117.32</v>
+        <v>118.28</v>
       </c>
       <c r="J13" t="n">
-        <v>108.16</v>
+        <v>107.42</v>
       </c>
       <c r="K13" t="n">
-        <v>9.16</v>
+        <v>10.87</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2601</v>
+        <v>0.255</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1481</v>
+        <v>0.1501</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4</v>
+        <v>6.8</v>
       </c>
       <c r="O13" t="n">
         <v>35</v>
@@ -1384,7 +1372,7 @@
         <v>34</v>
       </c>
       <c r="U13" t="n">
-        <v>1704.7</v>
+        <v>1694.2</v>
       </c>
     </row>
     <row r="14">
@@ -1623,31 +1611,31 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G17" t="n">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="H17" t="n">
-        <v>2.7724</v>
+        <v>2.7542</v>
       </c>
       <c r="I17" t="n">
-        <v>115.19</v>
+        <v>115.65</v>
       </c>
       <c r="J17" t="n">
-        <v>110.17</v>
+        <v>109.07</v>
       </c>
       <c r="K17" t="n">
-        <v>5.01</v>
+        <v>6.58</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3011</v>
+        <v>0.2992</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1585</v>
+        <v>0.158</v>
       </c>
       <c r="N17" t="n">
-        <v>3.2</v>
+        <v>6.6</v>
       </c>
       <c r="O17" t="n">
         <v>153</v>
@@ -1668,7 +1656,7 @@
         <v>140</v>
       </c>
       <c r="U17" t="n">
-        <v>1438.5</v>
+        <v>1435.2</v>
       </c>
     </row>
     <row r="18">
@@ -1907,31 +1895,31 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G21" t="n">
-        <v>1972.2</v>
+        <v>1976</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3222</v>
+        <v>0.8268</v>
       </c>
       <c r="I21" t="n">
-        <v>124.01</v>
+        <v>123.88</v>
       </c>
       <c r="J21" t="n">
-        <v>105.95</v>
+        <v>105.93</v>
       </c>
       <c r="K21" t="n">
-        <v>18.06</v>
+        <v>17.95</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2978</v>
+        <v>0.2977</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1321</v>
+        <v>0.1374</v>
       </c>
       <c r="N21" t="n">
-        <v>5.8</v>
+        <v>2.4</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
@@ -1952,7 +1940,7 @@
         <v>9</v>
       </c>
       <c r="U21" t="n">
-        <v>1747.3</v>
+        <v>1740.2</v>
       </c>
     </row>
     <row r="22">
@@ -2049,31 +2037,31 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G23" t="n">
-        <v>1925.2</v>
+        <v>1932.7</v>
       </c>
       <c r="H23" t="n">
-        <v>7.1116</v>
+        <v>6.7834</v>
       </c>
       <c r="I23" t="n">
-        <v>122.37</v>
+        <v>123.18</v>
       </c>
       <c r="J23" t="n">
-        <v>109.06</v>
+        <v>108.72</v>
       </c>
       <c r="K23" t="n">
-        <v>13.31</v>
+        <v>14.46</v>
       </c>
       <c r="L23" t="n">
-        <v>0.3062</v>
+        <v>0.2975</v>
       </c>
       <c r="M23" t="n">
-        <v>0.119</v>
+        <v>0.1194</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O23" t="n">
         <v>20</v>
@@ -2094,7 +2082,7 @@
         <v>19</v>
       </c>
       <c r="U23" t="n">
-        <v>1726.1</v>
+        <v>1725.9</v>
       </c>
     </row>
     <row r="24">
@@ -2262,31 +2250,31 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G26" t="n">
-        <v>1757.4</v>
+        <v>1773.8</v>
       </c>
       <c r="H26" t="n">
-        <v>13.1837</v>
+        <v>12.7945</v>
       </c>
       <c r="I26" t="n">
-        <v>117.38</v>
+        <v>117.09</v>
       </c>
       <c r="J26" t="n">
-        <v>99.64</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>17.74</v>
+        <v>17.19</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3063</v>
+        <v>0.3061</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1591</v>
+        <v>0.1624</v>
       </c>
       <c r="N26" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="O26" t="n">
         <v>32</v>
@@ -2307,7 +2295,7 @@
         <v>30</v>
       </c>
       <c r="U26" t="n">
-        <v>1596.7</v>
+        <v>1607.1</v>
       </c>
     </row>
     <row r="27">
@@ -2830,31 +2818,31 @@
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G34" t="n">
-        <v>1413.1</v>
+        <v>1414.1</v>
       </c>
       <c r="H34" t="n">
-        <v>2.527</v>
+        <v>2.4721</v>
       </c>
       <c r="I34" t="n">
-        <v>108.42</v>
+        <v>109.35</v>
       </c>
       <c r="J34" t="n">
-        <v>103.89</v>
+        <v>104.93</v>
       </c>
       <c r="K34" t="n">
-        <v>4.53</v>
+        <v>4.42</v>
       </c>
       <c r="L34" t="n">
-        <v>0.3154</v>
+        <v>0.32</v>
       </c>
       <c r="M34" t="n">
-        <v>0.1883</v>
+        <v>0.1885</v>
       </c>
       <c r="N34" t="n">
-        <v>8.6</v>
+        <v>5.8</v>
       </c>
       <c r="O34" t="n">
         <v>210</v>
@@ -2875,7 +2863,7 @@
         <v>195</v>
       </c>
       <c r="U34" t="n">
-        <v>1384.3</v>
+        <v>1378.7</v>
       </c>
     </row>
     <row r="35">
@@ -3043,31 +3031,31 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G37" t="n">
-        <v>2083.1</v>
+        <v>2085.1</v>
       </c>
       <c r="H37" t="n">
-        <v>3.0302</v>
+        <v>2.67</v>
       </c>
       <c r="I37" t="n">
-        <v>118.12</v>
+        <v>117.81</v>
       </c>
       <c r="J37" t="n">
-        <v>94.48</v>
+        <v>94.78</v>
       </c>
       <c r="K37" t="n">
-        <v>23.64</v>
+        <v>23.03</v>
       </c>
       <c r="L37" t="n">
-        <v>0.3382</v>
+        <v>0.3414</v>
       </c>
       <c r="M37" t="n">
-        <v>0.1188</v>
+        <v>0.1193</v>
       </c>
       <c r="N37" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="O37" t="n">
         <v>6</v>
@@ -3088,7 +3076,7 @@
         <v>7</v>
       </c>
       <c r="U37" t="n">
-        <v>1703.5</v>
+        <v>1703.4</v>
       </c>
     </row>
     <row r="38">
@@ -3398,31 +3386,31 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G42" t="n">
-        <v>1833.6</v>
+        <v>1837.7</v>
       </c>
       <c r="H42" t="n">
-        <v>0.5562</v>
+        <v>0.7673</v>
       </c>
       <c r="I42" t="n">
-        <v>117.74</v>
+        <v>118.38</v>
       </c>
       <c r="J42" t="n">
-        <v>107.72</v>
+        <v>106.47</v>
       </c>
       <c r="K42" t="n">
-        <v>10.02</v>
+        <v>11.91</v>
       </c>
       <c r="L42" t="n">
-        <v>0.2772</v>
+        <v>0.2733</v>
       </c>
       <c r="M42" t="n">
-        <v>0.1264</v>
+        <v>0.1236</v>
       </c>
       <c r="N42" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="O42" t="n">
         <v>30</v>
@@ -3443,7 +3431,7 @@
         <v>32</v>
       </c>
       <c r="U42" t="n">
-        <v>1689.3</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="43">
@@ -3611,31 +3599,31 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G45" t="n">
-        <v>1785.1</v>
+        <v>1777.5</v>
       </c>
       <c r="H45" t="n">
-        <v>2.0552</v>
+        <v>2.2904</v>
       </c>
       <c r="I45" t="n">
-        <v>121.1</v>
+        <v>120.67</v>
       </c>
       <c r="J45" t="n">
-        <v>110.26</v>
+        <v>111.46</v>
       </c>
       <c r="K45" t="n">
-        <v>10.85</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>0.3116</v>
+        <v>0.3123</v>
       </c>
       <c r="M45" t="n">
-        <v>0.1505</v>
+        <v>0.1488</v>
       </c>
       <c r="N45" t="n">
-        <v>0.4</v>
+        <v>-7</v>
       </c>
       <c r="O45" t="n">
         <v>29</v>
@@ -3656,7 +3644,7 @@
         <v>37</v>
       </c>
       <c r="U45" t="n">
-        <v>1691.9</v>
+        <v>1700.7</v>
       </c>
     </row>
     <row r="46">
@@ -3682,31 +3670,31 @@
         <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G46" t="n">
-        <v>1847</v>
+        <v>1825.3</v>
       </c>
       <c r="H46" t="n">
-        <v>4.3818</v>
+        <v>4.1386</v>
       </c>
       <c r="I46" t="n">
-        <v>114.73</v>
+        <v>114.16</v>
       </c>
       <c r="J46" t="n">
-        <v>100.98</v>
+        <v>101.47</v>
       </c>
       <c r="K46" t="n">
-        <v>13.75</v>
+        <v>12.7</v>
       </c>
       <c r="L46" t="n">
-        <v>0.2694</v>
+        <v>0.2721</v>
       </c>
       <c r="M46" t="n">
-        <v>0.143</v>
+        <v>0.1448</v>
       </c>
       <c r="N46" t="n">
-        <v>8.6</v>
+        <v>5.8</v>
       </c>
       <c r="O46" t="n">
         <v>46</v>
@@ -3727,7 +3715,7 @@
         <v>42</v>
       </c>
       <c r="U46" t="n">
-        <v>1589.8</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="47">
@@ -3753,31 +3741,31 @@
         <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G47" t="n">
-        <v>1746.4</v>
+        <v>1752.7</v>
       </c>
       <c r="H47" t="n">
-        <v>-2.8012</v>
+        <v>-2.7312</v>
       </c>
       <c r="I47" t="n">
-        <v>115.78</v>
+        <v>116.39</v>
       </c>
       <c r="J47" t="n">
-        <v>107.65</v>
+        <v>106.14</v>
       </c>
       <c r="K47" t="n">
-        <v>8.130000000000001</v>
+        <v>10.26</v>
       </c>
       <c r="L47" t="n">
-        <v>0.237</v>
+        <v>0.234</v>
       </c>
       <c r="M47" t="n">
-        <v>0.1402</v>
+        <v>0.1415</v>
       </c>
       <c r="N47" t="n">
-        <v>-9.6</v>
+        <v>-7.2</v>
       </c>
       <c r="O47" t="n">
         <v>43</v>
@@ -3798,7 +3786,7 @@
         <v>41</v>
       </c>
       <c r="U47" t="n">
-        <v>1703.1</v>
+        <v>1695.9</v>
       </c>
     </row>
     <row r="48">
@@ -4889,31 +4877,31 @@
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G63" t="n">
-        <v>1770.1</v>
+        <v>1753.7</v>
       </c>
       <c r="H63" t="n">
-        <v>1.6059</v>
+        <v>1.2979</v>
       </c>
       <c r="I63" t="n">
-        <v>119.38</v>
+        <v>118.53</v>
       </c>
       <c r="J63" t="n">
-        <v>110.1</v>
+        <v>109.67</v>
       </c>
       <c r="K63" t="n">
-        <v>9.279999999999999</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>0.3004</v>
+        <v>0.3029</v>
       </c>
       <c r="M63" t="n">
-        <v>0.1491</v>
+        <v>0.1516</v>
       </c>
       <c r="N63" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="O63" t="n">
         <v>39</v>
@@ -4934,7 +4922,7 @@
         <v>36</v>
       </c>
       <c r="U63" t="n">
-        <v>1642.4</v>
+        <v>1646.7</v>
       </c>
     </row>
     <row r="64">

--- a/team_stats_2026.xlsx
+++ b/team_stats_2026.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,107 +429,107 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Is_FirstFour</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -972,31 +984,31 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G8" t="n">
-        <v>1820.1</v>
+        <v>1813.5</v>
       </c>
       <c r="H8" t="n">
-        <v>6.5295</v>
+        <v>6.893</v>
       </c>
       <c r="I8" t="n">
-        <v>114.74</v>
+        <v>114.62</v>
       </c>
       <c r="J8" t="n">
-        <v>103.88</v>
+        <v>105.11</v>
       </c>
       <c r="K8" t="n">
-        <v>10.87</v>
+        <v>9.51</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3148</v>
+        <v>0.3173</v>
       </c>
       <c r="M8" t="n">
-        <v>0.141</v>
+        <v>0.1412</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.2</v>
+        <v>-3.8</v>
       </c>
       <c r="O8" t="n">
         <v>34</v>
@@ -1017,7 +1029,7 @@
         <v>33</v>
       </c>
       <c r="U8" t="n">
-        <v>1643.5</v>
+        <v>1649.2</v>
       </c>
     </row>
     <row r="9">
@@ -1043,31 +1055,31 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G9" t="n">
-        <v>1825.9</v>
+        <v>1828.2</v>
       </c>
       <c r="H9" t="n">
-        <v>10.4518</v>
+        <v>11.0707</v>
       </c>
       <c r="I9" t="n">
-        <v>122</v>
+        <v>121.57</v>
       </c>
       <c r="J9" t="n">
-        <v>96.95</v>
+        <v>96.51000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>25.05</v>
+        <v>25.06</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2326</v>
+        <v>0.2343</v>
       </c>
       <c r="M9" t="n">
-        <v>0.167</v>
+        <v>0.1691</v>
       </c>
       <c r="N9" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="O9" t="n">
         <v>27</v>
@@ -1088,7 +1100,7 @@
         <v>24</v>
       </c>
       <c r="U9" t="n">
-        <v>1501.8</v>
+        <v>1506.9</v>
       </c>
     </row>
     <row r="10">
@@ -1117,7 +1129,7 @@
         <v>117</v>
       </c>
       <c r="G10" t="n">
-        <v>1855.3</v>
+        <v>1821.4</v>
       </c>
       <c r="H10" t="n">
         <v>4.8208</v>
@@ -1327,31 +1339,31 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G13" t="n">
-        <v>1787.4</v>
+        <v>1782.1</v>
       </c>
       <c r="H13" t="n">
-        <v>1.3307</v>
+        <v>1.1828</v>
       </c>
       <c r="I13" t="n">
-        <v>118.28</v>
+        <v>117.32</v>
       </c>
       <c r="J13" t="n">
-        <v>107.42</v>
+        <v>108.16</v>
       </c>
       <c r="K13" t="n">
-        <v>10.87</v>
+        <v>9.16</v>
       </c>
       <c r="L13" t="n">
-        <v>0.255</v>
+        <v>0.2601</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1501</v>
+        <v>0.1481</v>
       </c>
       <c r="N13" t="n">
-        <v>6.8</v>
+        <v>-0.4</v>
       </c>
       <c r="O13" t="n">
         <v>35</v>
@@ -1372,7 +1384,7 @@
         <v>34</v>
       </c>
       <c r="U13" t="n">
-        <v>1694.2</v>
+        <v>1704.7</v>
       </c>
     </row>
     <row r="14">
@@ -1611,31 +1623,31 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G17" t="n">
-        <v>1464</v>
+        <v>1462</v>
       </c>
       <c r="H17" t="n">
-        <v>2.7542</v>
+        <v>2.7724</v>
       </c>
       <c r="I17" t="n">
-        <v>115.65</v>
+        <v>115.19</v>
       </c>
       <c r="J17" t="n">
-        <v>109.07</v>
+        <v>110.17</v>
       </c>
       <c r="K17" t="n">
-        <v>6.58</v>
+        <v>5.01</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2992</v>
+        <v>0.3011</v>
       </c>
       <c r="M17" t="n">
-        <v>0.158</v>
+        <v>0.1585</v>
       </c>
       <c r="N17" t="n">
-        <v>6.6</v>
+        <v>3.2</v>
       </c>
       <c r="O17" t="n">
         <v>153</v>
@@ -1656,7 +1668,7 @@
         <v>140</v>
       </c>
       <c r="U17" t="n">
-        <v>1435.2</v>
+        <v>1438.5</v>
       </c>
     </row>
     <row r="18">
@@ -1895,31 +1907,31 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G21" t="n">
-        <v>1976</v>
+        <v>1972.2</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8268</v>
+        <v>1.3222</v>
       </c>
       <c r="I21" t="n">
-        <v>123.88</v>
+        <v>124.01</v>
       </c>
       <c r="J21" t="n">
-        <v>105.93</v>
+        <v>105.95</v>
       </c>
       <c r="K21" t="n">
-        <v>17.95</v>
+        <v>18.06</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2977</v>
+        <v>0.2978</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1374</v>
+        <v>0.1321</v>
       </c>
       <c r="N21" t="n">
-        <v>2.4</v>
+        <v>5.8</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
@@ -1940,7 +1952,7 @@
         <v>9</v>
       </c>
       <c r="U21" t="n">
-        <v>1740.2</v>
+        <v>1747.3</v>
       </c>
     </row>
     <row r="22">
@@ -2037,31 +2049,31 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G23" t="n">
-        <v>1932.7</v>
+        <v>1925.2</v>
       </c>
       <c r="H23" t="n">
-        <v>6.7834</v>
+        <v>7.1116</v>
       </c>
       <c r="I23" t="n">
-        <v>123.18</v>
+        <v>122.37</v>
       </c>
       <c r="J23" t="n">
-        <v>108.72</v>
+        <v>109.06</v>
       </c>
       <c r="K23" t="n">
-        <v>14.46</v>
+        <v>13.31</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2975</v>
+        <v>0.3062</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1194</v>
+        <v>0.119</v>
       </c>
       <c r="N23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>20</v>
@@ -2082,7 +2094,7 @@
         <v>19</v>
       </c>
       <c r="U23" t="n">
-        <v>1725.9</v>
+        <v>1726.1</v>
       </c>
     </row>
     <row r="24">
@@ -2250,31 +2262,31 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G26" t="n">
-        <v>1773.8</v>
+        <v>1757.4</v>
       </c>
       <c r="H26" t="n">
-        <v>12.7945</v>
+        <v>13.1837</v>
       </c>
       <c r="I26" t="n">
-        <v>117.09</v>
+        <v>117.38</v>
       </c>
       <c r="J26" t="n">
-        <v>99.90000000000001</v>
+        <v>99.64</v>
       </c>
       <c r="K26" t="n">
-        <v>17.19</v>
+        <v>17.74</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3061</v>
+        <v>0.3063</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1624</v>
+        <v>0.1591</v>
       </c>
       <c r="N26" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="O26" t="n">
         <v>32</v>
@@ -2295,7 +2307,7 @@
         <v>30</v>
       </c>
       <c r="U26" t="n">
-        <v>1607.1</v>
+        <v>1596.7</v>
       </c>
     </row>
     <row r="27">
@@ -2818,31 +2830,31 @@
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G34" t="n">
-        <v>1414.1</v>
+        <v>1413.1</v>
       </c>
       <c r="H34" t="n">
-        <v>2.4721</v>
+        <v>2.527</v>
       </c>
       <c r="I34" t="n">
-        <v>109.35</v>
+        <v>108.42</v>
       </c>
       <c r="J34" t="n">
-        <v>104.93</v>
+        <v>103.89</v>
       </c>
       <c r="K34" t="n">
-        <v>4.42</v>
+        <v>4.53</v>
       </c>
       <c r="L34" t="n">
-        <v>0.32</v>
+        <v>0.3154</v>
       </c>
       <c r="M34" t="n">
-        <v>0.1885</v>
+        <v>0.1883</v>
       </c>
       <c r="N34" t="n">
-        <v>5.8</v>
+        <v>8.6</v>
       </c>
       <c r="O34" t="n">
         <v>210</v>
@@ -2863,7 +2875,7 @@
         <v>195</v>
       </c>
       <c r="U34" t="n">
-        <v>1378.7</v>
+        <v>1384.3</v>
       </c>
     </row>
     <row r="35">
@@ -3031,31 +3043,31 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G37" t="n">
-        <v>2085.1</v>
+        <v>2083.1</v>
       </c>
       <c r="H37" t="n">
-        <v>2.67</v>
+        <v>3.0302</v>
       </c>
       <c r="I37" t="n">
-        <v>117.81</v>
+        <v>118.12</v>
       </c>
       <c r="J37" t="n">
-        <v>94.78</v>
+        <v>94.48</v>
       </c>
       <c r="K37" t="n">
-        <v>23.03</v>
+        <v>23.64</v>
       </c>
       <c r="L37" t="n">
-        <v>0.3414</v>
+        <v>0.3382</v>
       </c>
       <c r="M37" t="n">
-        <v>0.1193</v>
+        <v>0.1188</v>
       </c>
       <c r="N37" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O37" t="n">
         <v>6</v>
@@ -3076,7 +3088,7 @@
         <v>7</v>
       </c>
       <c r="U37" t="n">
-        <v>1703.4</v>
+        <v>1703.5</v>
       </c>
     </row>
     <row r="38">
@@ -3386,31 +3398,31 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G42" t="n">
-        <v>1837.7</v>
+        <v>1833.6</v>
       </c>
       <c r="H42" t="n">
-        <v>0.7673</v>
+        <v>0.5562</v>
       </c>
       <c r="I42" t="n">
-        <v>118.38</v>
+        <v>117.74</v>
       </c>
       <c r="J42" t="n">
-        <v>106.47</v>
+        <v>107.72</v>
       </c>
       <c r="K42" t="n">
-        <v>11.91</v>
+        <v>10.02</v>
       </c>
       <c r="L42" t="n">
-        <v>0.2733</v>
+        <v>0.2772</v>
       </c>
       <c r="M42" t="n">
-        <v>0.1236</v>
+        <v>0.1264</v>
       </c>
       <c r="N42" t="n">
-        <v>6.4</v>
+        <v>4</v>
       </c>
       <c r="O42" t="n">
         <v>30</v>
@@ -3431,7 +3443,7 @@
         <v>32</v>
       </c>
       <c r="U42" t="n">
-        <v>1686</v>
+        <v>1689.3</v>
       </c>
     </row>
     <row r="43">
@@ -3599,31 +3611,31 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G45" t="n">
-        <v>1777.5</v>
+        <v>1785.1</v>
       </c>
       <c r="H45" t="n">
-        <v>2.2904</v>
+        <v>2.0552</v>
       </c>
       <c r="I45" t="n">
-        <v>120.67</v>
+        <v>121.1</v>
       </c>
       <c r="J45" t="n">
-        <v>111.46</v>
+        <v>110.26</v>
       </c>
       <c r="K45" t="n">
-        <v>9.210000000000001</v>
+        <v>10.85</v>
       </c>
       <c r="L45" t="n">
-        <v>0.3123</v>
+        <v>0.3116</v>
       </c>
       <c r="M45" t="n">
-        <v>0.1488</v>
+        <v>0.1505</v>
       </c>
       <c r="N45" t="n">
-        <v>-7</v>
+        <v>0.4</v>
       </c>
       <c r="O45" t="n">
         <v>29</v>
@@ -3644,7 +3656,7 @@
         <v>37</v>
       </c>
       <c r="U45" t="n">
-        <v>1700.7</v>
+        <v>1691.9</v>
       </c>
     </row>
     <row r="46">
@@ -3670,31 +3682,31 @@
         <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G46" t="n">
-        <v>1825.3</v>
+        <v>1847</v>
       </c>
       <c r="H46" t="n">
-        <v>4.1386</v>
+        <v>4.3818</v>
       </c>
       <c r="I46" t="n">
-        <v>114.16</v>
+        <v>114.73</v>
       </c>
       <c r="J46" t="n">
-        <v>101.47</v>
+        <v>100.98</v>
       </c>
       <c r="K46" t="n">
-        <v>12.7</v>
+        <v>13.75</v>
       </c>
       <c r="L46" t="n">
-        <v>0.2721</v>
+        <v>0.2694</v>
       </c>
       <c r="M46" t="n">
-        <v>0.1448</v>
+        <v>0.143</v>
       </c>
       <c r="N46" t="n">
-        <v>5.8</v>
+        <v>8.6</v>
       </c>
       <c r="O46" t="n">
         <v>46</v>
@@ -3715,7 +3727,7 @@
         <v>42</v>
       </c>
       <c r="U46" t="n">
-        <v>1590</v>
+        <v>1589.8</v>
       </c>
     </row>
     <row r="47">
@@ -3741,31 +3753,31 @@
         <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G47" t="n">
-        <v>1752.7</v>
+        <v>1746.4</v>
       </c>
       <c r="H47" t="n">
-        <v>-2.7312</v>
+        <v>-2.8012</v>
       </c>
       <c r="I47" t="n">
-        <v>116.39</v>
+        <v>115.78</v>
       </c>
       <c r="J47" t="n">
-        <v>106.14</v>
+        <v>107.65</v>
       </c>
       <c r="K47" t="n">
-        <v>10.26</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>0.234</v>
+        <v>0.237</v>
       </c>
       <c r="M47" t="n">
-        <v>0.1415</v>
+        <v>0.1402</v>
       </c>
       <c r="N47" t="n">
-        <v>-7.2</v>
+        <v>-9.6</v>
       </c>
       <c r="O47" t="n">
         <v>43</v>
@@ -3786,7 +3798,7 @@
         <v>41</v>
       </c>
       <c r="U47" t="n">
-        <v>1695.9</v>
+        <v>1703.1</v>
       </c>
     </row>
     <row r="48">
@@ -4877,31 +4889,31 @@
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G63" t="n">
-        <v>1753.7</v>
+        <v>1770.1</v>
       </c>
       <c r="H63" t="n">
-        <v>1.2979</v>
+        <v>1.6059</v>
       </c>
       <c r="I63" t="n">
-        <v>118.53</v>
+        <v>119.38</v>
       </c>
       <c r="J63" t="n">
-        <v>109.67</v>
+        <v>110.1</v>
       </c>
       <c r="K63" t="n">
-        <v>8.859999999999999</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>0.3029</v>
+        <v>0.3004</v>
       </c>
       <c r="M63" t="n">
-        <v>0.1516</v>
+        <v>0.1491</v>
       </c>
       <c r="N63" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="O63" t="n">
         <v>39</v>
@@ -4922,7 +4934,7 @@
         <v>36</v>
       </c>
       <c r="U63" t="n">
-        <v>1646.7</v>
+        <v>1642.4</v>
       </c>
     </row>
     <row r="64">

--- a/team_stats_2026.xlsx
+++ b/team_stats_2026.xlsx
@@ -617,31 +617,31 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G3" t="n">
-        <v>2050.3</v>
+        <v>2051.5</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5431</v>
+        <v>0.5706</v>
       </c>
       <c r="I3" t="n">
-        <v>116.95</v>
+        <v>117.41</v>
       </c>
       <c r="J3" t="n">
-        <v>98.98</v>
+        <v>100.06</v>
       </c>
       <c r="K3" t="n">
-        <v>17.97</v>
+        <v>17.36</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2979</v>
+        <v>0.2989</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1625</v>
+        <v>0.165</v>
       </c>
       <c r="N3" t="n">
-        <v>4.6</v>
+        <v>9.6</v>
       </c>
       <c r="O3" t="n">
         <v>9</v>
@@ -662,7 +662,7 @@
         <v>11</v>
       </c>
       <c r="U3" t="n">
-        <v>1712.3</v>
+        <v>1704.4</v>
       </c>
     </row>
     <row r="4">
@@ -738,11 +738,11 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1211</v>
+        <v>1104</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gonzaga</t>
+          <t>Alabama</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -759,61 +759,61 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G5" t="n">
-        <v>2055.1</v>
+        <v>1966.5</v>
       </c>
       <c r="H5" t="n">
-        <v>6.9647</v>
+        <v>-1.6248</v>
       </c>
       <c r="I5" t="n">
-        <v>120.35</v>
+        <v>121.39</v>
       </c>
       <c r="J5" t="n">
-        <v>93.25</v>
+        <v>110.58</v>
       </c>
       <c r="K5" t="n">
-        <v>27.1</v>
+        <v>10.81</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2992</v>
+        <v>0.279</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1329</v>
+        <v>0.1296</v>
       </c>
       <c r="N5" t="n">
-        <v>13.6</v>
+        <v>5.2</v>
       </c>
       <c r="O5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="P5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q5" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="R5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T5" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="U5" t="n">
-        <v>1597.1</v>
+        <v>1769.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1397</v>
+        <v>1385</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>St John's</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -833,58 +833,58 @@
         <v>120</v>
       </c>
       <c r="G6" t="n">
-        <v>1912.8</v>
+        <v>1955.3</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.7463</v>
+        <v>4.7636</v>
       </c>
       <c r="I6" t="n">
-        <v>117.37</v>
+        <v>113.73</v>
       </c>
       <c r="J6" t="n">
-        <v>101.08</v>
+        <v>98.58</v>
       </c>
       <c r="K6" t="n">
-        <v>16.3</v>
+        <v>15.15</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3535</v>
+        <v>0.3268</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1667</v>
+        <v>0.1411</v>
       </c>
       <c r="N6" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="O6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="P6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="R6" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="S6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="T6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="U6" t="n">
-        <v>1692.2</v>
+        <v>1677.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1257</v>
+        <v>1246</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Louisville</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -904,58 +904,58 @@
         <v>120</v>
       </c>
       <c r="G7" t="n">
-        <v>1830.2</v>
+        <v>1893.4</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.7351</v>
+        <v>6.006</v>
       </c>
       <c r="I7" t="n">
-        <v>119.03</v>
+        <v>116.85</v>
       </c>
       <c r="J7" t="n">
-        <v>100.17</v>
+        <v>105.78</v>
       </c>
       <c r="K7" t="n">
-        <v>18.86</v>
+        <v>11.07</v>
       </c>
       <c r="L7" t="n">
-        <v>0.29</v>
+        <v>0.3101</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1596</v>
+        <v>0.1466</v>
       </c>
       <c r="N7" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="O7" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="P7" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>23</v>
+      </c>
+      <c r="R7" t="n">
         <v>27</v>
       </c>
-      <c r="Q7" t="n">
-        <v>14</v>
-      </c>
-      <c r="R7" t="n">
-        <v>21</v>
-      </c>
       <c r="S7" t="n">
+        <v>33</v>
+      </c>
+      <c r="T7" t="n">
         <v>27</v>
       </c>
-      <c r="T7" t="n">
-        <v>17</v>
-      </c>
       <c r="U7" t="n">
-        <v>1675</v>
+        <v>1717.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1437</v>
+        <v>1274</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Villanova</t>
+          <t>Miami FL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -975,58 +975,58 @@
         <v>121</v>
       </c>
       <c r="G8" t="n">
-        <v>1820.1</v>
+        <v>1773.8</v>
       </c>
       <c r="H8" t="n">
-        <v>6.5295</v>
+        <v>12.7945</v>
       </c>
       <c r="I8" t="n">
-        <v>114.74</v>
+        <v>117.09</v>
       </c>
       <c r="J8" t="n">
-        <v>103.88</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>10.87</v>
+        <v>17.19</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3148</v>
+        <v>0.3061</v>
       </c>
       <c r="M8" t="n">
-        <v>0.141</v>
+        <v>0.1624</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.2</v>
+        <v>7.6</v>
       </c>
       <c r="O8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P8" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q8" t="n">
         <v>26</v>
       </c>
-      <c r="Q8" t="n">
-        <v>41</v>
-      </c>
       <c r="R8" t="n">
+        <v>32</v>
+      </c>
+      <c r="S8" t="n">
         <v>30</v>
       </c>
-      <c r="S8" t="n">
-        <v>25</v>
-      </c>
       <c r="T8" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="U8" t="n">
-        <v>1643.5</v>
+        <v>1607.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1387</v>
+        <v>1429</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>St Louis</t>
+          <t>Utah St</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1043,61 +1043,61 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G9" t="n">
-        <v>1825.9</v>
+        <v>1864.3</v>
       </c>
       <c r="H9" t="n">
-        <v>10.4518</v>
+        <v>-0.3251</v>
       </c>
       <c r="I9" t="n">
-        <v>122</v>
+        <v>119.66</v>
       </c>
       <c r="J9" t="n">
-        <v>96.95</v>
+        <v>104.27</v>
       </c>
       <c r="K9" t="n">
-        <v>25.05</v>
+        <v>15.38</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2326</v>
+        <v>0.3059</v>
       </c>
       <c r="M9" t="n">
-        <v>0.167</v>
+        <v>0.1487</v>
       </c>
       <c r="N9" t="n">
-        <v>4.4</v>
+        <v>-4.6</v>
       </c>
       <c r="O9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P9" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="Q9" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="R9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="S9" t="n">
+        <v>29</v>
+      </c>
+      <c r="T9" t="n">
         <v>26</v>
       </c>
-      <c r="T9" t="n">
-        <v>24</v>
-      </c>
       <c r="U9" t="n">
-        <v>1501.8</v>
+        <v>1591.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1234</v>
+        <v>1417</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Iowa</t>
+          <t>UCLA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1114,61 +1114,61 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G10" t="n">
-        <v>1855.3</v>
+        <v>1842</v>
       </c>
       <c r="H10" t="n">
-        <v>4.8208</v>
+        <v>2.4672</v>
       </c>
       <c r="I10" t="n">
-        <v>119.88</v>
+        <v>116.51</v>
       </c>
       <c r="J10" t="n">
-        <v>103.67</v>
+        <v>106.69</v>
       </c>
       <c r="K10" t="n">
-        <v>16.21</v>
+        <v>9.82</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2891</v>
+        <v>0.2986</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1416</v>
+        <v>0.1302</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.8</v>
+        <v>2.4</v>
       </c>
       <c r="O10" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="P10" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="Q10" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="R10" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="S10" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="T10" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="U10" t="n">
-        <v>1682.5</v>
+        <v>1687.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1395</v>
+        <v>1281</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TCU</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1188,58 +1188,58 @@
         <v>120</v>
       </c>
       <c r="G11" t="n">
-        <v>1824.2</v>
+        <v>1768.2</v>
       </c>
       <c r="H11" t="n">
-        <v>6.8019</v>
+        <v>-2.8893</v>
       </c>
       <c r="I11" t="n">
-        <v>110.58</v>
+        <v>115.23</v>
       </c>
       <c r="J11" t="n">
-        <v>101.35</v>
+        <v>109.22</v>
       </c>
       <c r="K11" t="n">
-        <v>9.23</v>
+        <v>6.01</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3181</v>
+        <v>0.3029</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1536</v>
+        <v>0.1713</v>
       </c>
       <c r="N11" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="P11" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="Q11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R11" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S11" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="T11" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="U11" t="n">
-        <v>1678</v>
+        <v>1637.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1365</v>
+        <v>1374</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>SMU</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1256,61 +1256,61 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G12" t="n">
-        <v>1765.3</v>
+        <v>1753.7</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5462</v>
+        <v>1.2979</v>
       </c>
       <c r="I12" t="n">
-        <v>117.4</v>
+        <v>118.53</v>
       </c>
       <c r="J12" t="n">
-        <v>102.2</v>
+        <v>109.67</v>
       </c>
       <c r="K12" t="n">
-        <v>15.2</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3448</v>
+        <v>0.3029</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1494</v>
+        <v>0.1516</v>
       </c>
       <c r="N12" t="n">
-        <v>5.4</v>
+        <v>0.4</v>
       </c>
       <c r="O12" t="n">
+        <v>39</v>
+      </c>
+      <c r="P12" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q12" t="n">
         <v>37</v>
       </c>
-      <c r="P12" t="n">
-        <v>43</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>45</v>
-      </c>
       <c r="R12" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S12" t="n">
+        <v>38</v>
+      </c>
+      <c r="T12" t="n">
         <v>36</v>
       </c>
-      <c r="T12" t="n">
-        <v>40</v>
-      </c>
       <c r="U12" t="n">
-        <v>1571</v>
+        <v>1646.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1326</v>
+        <v>1231</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ohio St</t>
+          <t>Indiana</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1330,58 +1330,58 @@
         <v>121</v>
       </c>
       <c r="G13" t="n">
-        <v>1787.4</v>
+        <v>1752.7</v>
       </c>
       <c r="H13" t="n">
-        <v>1.3307</v>
+        <v>-2.7312</v>
       </c>
       <c r="I13" t="n">
-        <v>118.28</v>
+        <v>116.39</v>
       </c>
       <c r="J13" t="n">
-        <v>107.42</v>
+        <v>106.14</v>
       </c>
       <c r="K13" t="n">
-        <v>10.87</v>
+        <v>10.26</v>
       </c>
       <c r="L13" t="n">
-        <v>0.255</v>
+        <v>0.234</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1501</v>
+        <v>0.1415</v>
       </c>
       <c r="N13" t="n">
-        <v>6.8</v>
+        <v>-7.2</v>
       </c>
       <c r="O13" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="P13" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="Q13" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="R13" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="S13" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="T13" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="U13" t="n">
-        <v>1694.2</v>
+        <v>1695.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1463</v>
+        <v>1125</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Yale</t>
+          <t>Belmont</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1398,52 +1398,52 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G14" t="n">
-        <v>1725.3</v>
+        <v>1753.8</v>
       </c>
       <c r="H14" t="n">
-        <v>1.115</v>
+        <v>5.6074</v>
       </c>
       <c r="I14" t="n">
-        <v>120.83</v>
+        <v>118.84</v>
       </c>
       <c r="J14" t="n">
-        <v>108.5</v>
+        <v>104.39</v>
       </c>
       <c r="K14" t="n">
-        <v>12.33</v>
+        <v>14.44</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2837</v>
+        <v>0.2389</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1401</v>
+        <v>0.1756</v>
       </c>
       <c r="N14" t="n">
-        <v>4.2</v>
+        <v>13.2</v>
       </c>
       <c r="O14" t="n">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="P14" t="n">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="Q14" t="n">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="R14" t="n">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="S14" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="T14" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="U14" t="n">
-        <v>1460.6</v>
+        <v>1487.2</v>
       </c>
     </row>
     <row r="15">
@@ -1519,11 +1519,11 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1295</v>
+        <v>1407</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>N Dakota St</t>
+          <t>Troy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1540,52 +1540,52 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G16" t="n">
-        <v>1588.9</v>
+        <v>1596.8</v>
       </c>
       <c r="H16" t="n">
-        <v>4.0163</v>
+        <v>1.2901</v>
       </c>
       <c r="I16" t="n">
-        <v>114.83</v>
+        <v>112.11</v>
       </c>
       <c r="J16" t="n">
-        <v>103.4</v>
+        <v>106.85</v>
       </c>
       <c r="K16" t="n">
-        <v>11.43</v>
+        <v>5.26</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3086</v>
+        <v>0.3162</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1517</v>
+        <v>0.1601</v>
       </c>
       <c r="N16" t="n">
-        <v>14.4</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="P16" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="Q16" t="n">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="R16" t="n">
+        <v>139</v>
+      </c>
+      <c r="S16" t="n">
         <v>128</v>
       </c>
-      <c r="S16" t="n">
-        <v>94</v>
-      </c>
       <c r="T16" t="n">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="U16" t="n">
-        <v>1418.9</v>
+        <v>1465.3</v>
       </c>
     </row>
     <row r="17">
@@ -1945,11 +1945,11 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1403</v>
+        <v>1438</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Texas Tech</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>120</v>
       </c>
       <c r="G22" t="n">
-        <v>2034.5</v>
+        <v>1951.2</v>
       </c>
       <c r="H22" t="n">
-        <v>11.3167</v>
+        <v>13.9718</v>
       </c>
       <c r="I22" t="n">
-        <v>118.24</v>
+        <v>118.9</v>
       </c>
       <c r="J22" t="n">
-        <v>105.38</v>
+        <v>99.7</v>
       </c>
       <c r="K22" t="n">
-        <v>12.86</v>
+        <v>19.2</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2929</v>
+        <v>0.3157</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1562</v>
+        <v>0.1519</v>
       </c>
       <c r="N22" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="O22" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="P22" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>15</v>
+      </c>
+      <c r="R22" t="n">
+        <v>18</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="n">
         <v>14</v>
       </c>
-      <c r="Q22" t="n">
-        <v>11</v>
-      </c>
-      <c r="R22" t="n">
-        <v>11</v>
-      </c>
-      <c r="S22" t="n">
-        <v>15</v>
-      </c>
-      <c r="T22" t="n">
-        <v>13</v>
-      </c>
       <c r="U22" t="n">
-        <v>1753.9</v>
+        <v>1635.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1116</v>
+        <v>1397</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2037,61 +2037,61 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G23" t="n">
-        <v>1932.7</v>
+        <v>1912.8</v>
       </c>
       <c r="H23" t="n">
-        <v>6.7834</v>
+        <v>-1.7463</v>
       </c>
       <c r="I23" t="n">
-        <v>123.18</v>
+        <v>117.37</v>
       </c>
       <c r="J23" t="n">
-        <v>108.72</v>
+        <v>101.08</v>
       </c>
       <c r="K23" t="n">
-        <v>14.46</v>
+        <v>16.3</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2975</v>
+        <v>0.3535</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1194</v>
+        <v>0.1667</v>
       </c>
       <c r="N23" t="n">
-        <v>1.4</v>
+        <v>8</v>
       </c>
       <c r="O23" t="n">
+        <v>18</v>
+      </c>
+      <c r="P23" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q23" t="n">
         <v>20</v>
       </c>
-      <c r="P23" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
+        <v>20</v>
+      </c>
+      <c r="S23" t="n">
         <v>24</v>
       </c>
-      <c r="R23" t="n">
-        <v>19</v>
-      </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>20</v>
       </c>
-      <c r="T23" t="n">
-        <v>19</v>
-      </c>
       <c r="U23" t="n">
-        <v>1725.9</v>
+        <v>1692.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1140</v>
+        <v>1257</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BYU</t>
+          <t>Louisville</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2111,58 +2111,58 @@
         <v>120</v>
       </c>
       <c r="G24" t="n">
-        <v>1901.3</v>
+        <v>1830.2</v>
       </c>
       <c r="H24" t="n">
-        <v>2.827</v>
+        <v>-3.7351</v>
       </c>
       <c r="I24" t="n">
-        <v>117.49</v>
+        <v>119.03</v>
       </c>
       <c r="J24" t="n">
-        <v>106.29</v>
+        <v>100.17</v>
       </c>
       <c r="K24" t="n">
-        <v>11.21</v>
+        <v>18.86</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2953</v>
+        <v>0.29</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1466</v>
+        <v>0.1596</v>
       </c>
       <c r="N24" t="n">
-        <v>-8</v>
+        <v>2.8</v>
       </c>
       <c r="O24" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="P24" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Q24" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="R24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="S24" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="T24" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="U24" t="n">
-        <v>1712.1</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1429</v>
+        <v>1437</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Utah St</t>
+          <t>Villanova</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2179,61 +2179,61 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G25" t="n">
-        <v>1864.3</v>
+        <v>1820.1</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.3251</v>
+        <v>6.5295</v>
       </c>
       <c r="I25" t="n">
-        <v>119.66</v>
+        <v>114.74</v>
       </c>
       <c r="J25" t="n">
-        <v>104.27</v>
+        <v>103.88</v>
       </c>
       <c r="K25" t="n">
-        <v>15.38</v>
+        <v>10.87</v>
       </c>
       <c r="L25" t="n">
-        <v>0.3059</v>
+        <v>0.3148</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1487</v>
+        <v>0.141</v>
       </c>
       <c r="N25" t="n">
-        <v>-4.6</v>
+        <v>-2.2</v>
       </c>
       <c r="O25" t="n">
+        <v>34</v>
+      </c>
+      <c r="P25" t="n">
         <v>26</v>
       </c>
-      <c r="P25" t="n">
-        <v>32</v>
-      </c>
       <c r="Q25" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="R25" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S25" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="T25" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="U25" t="n">
-        <v>1591.6</v>
+        <v>1643.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1274</v>
+        <v>1387</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Miami FL</t>
+          <t>St Louis</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2253,58 +2253,58 @@
         <v>121</v>
       </c>
       <c r="G26" t="n">
-        <v>1773.8</v>
+        <v>1825.9</v>
       </c>
       <c r="H26" t="n">
-        <v>12.7945</v>
+        <v>10.4518</v>
       </c>
       <c r="I26" t="n">
-        <v>117.09</v>
+        <v>122</v>
       </c>
       <c r="J26" t="n">
-        <v>99.90000000000001</v>
+        <v>96.95</v>
       </c>
       <c r="K26" t="n">
-        <v>17.19</v>
+        <v>25.05</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3061</v>
+        <v>0.2326</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1624</v>
+        <v>0.167</v>
       </c>
       <c r="N26" t="n">
-        <v>7.6</v>
+        <v>4.4</v>
       </c>
       <c r="O26" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P26" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Q26" t="n">
+        <v>25</v>
+      </c>
+      <c r="R26" t="n">
+        <v>24</v>
+      </c>
+      <c r="S26" t="n">
         <v>26</v>
       </c>
-      <c r="R26" t="n">
-        <v>32</v>
-      </c>
-      <c r="S26" t="n">
-        <v>30</v>
-      </c>
       <c r="T26" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="U26" t="n">
-        <v>1607.1</v>
+        <v>1501.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1208</v>
+        <v>1234</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Iowa</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2321,61 +2321,61 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G27" t="n">
-        <v>1810.7</v>
+        <v>1849.8</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.8284</v>
+        <v>4.4435</v>
       </c>
       <c r="I27" t="n">
-        <v>120.8</v>
+        <v>119.28</v>
       </c>
       <c r="J27" t="n">
-        <v>106.43</v>
+        <v>103.76</v>
       </c>
       <c r="K27" t="n">
-        <v>14.38</v>
+        <v>15.52</v>
       </c>
       <c r="L27" t="n">
-        <v>0.3238</v>
+        <v>0.2925</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1381</v>
+        <v>0.1388</v>
       </c>
       <c r="N27" t="n">
-        <v>8</v>
+        <v>0.8</v>
       </c>
       <c r="O27" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="P27" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>32</v>
+      </c>
+      <c r="R27" t="n">
+        <v>29</v>
+      </c>
+      <c r="S27" t="n">
         <v>31</v>
       </c>
-      <c r="Q27" t="n">
-        <v>30</v>
-      </c>
-      <c r="R27" t="n">
-        <v>31</v>
-      </c>
-      <c r="S27" t="n">
-        <v>39</v>
-      </c>
       <c r="T27" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="U27" t="n">
-        <v>1647.3</v>
+        <v>1706.7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1417</v>
+        <v>1401</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>UCLA</t>
+          <t>Texas A&amp;M</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2395,58 +2395,58 @@
         <v>120</v>
       </c>
       <c r="G28" t="n">
-        <v>1842</v>
+        <v>1836.9</v>
       </c>
       <c r="H28" t="n">
-        <v>2.4672</v>
+        <v>4.4256</v>
       </c>
       <c r="I28" t="n">
-        <v>116.51</v>
+        <v>118.62</v>
       </c>
       <c r="J28" t="n">
-        <v>106.69</v>
+        <v>106.73</v>
       </c>
       <c r="K28" t="n">
-        <v>9.82</v>
+        <v>11.89</v>
       </c>
       <c r="L28" t="n">
-        <v>0.2986</v>
+        <v>0.3028</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1302</v>
+        <v>0.1406</v>
       </c>
       <c r="N28" t="n">
-        <v>2.4</v>
+        <v>-0.6</v>
       </c>
       <c r="O28" t="n">
+        <v>38</v>
+      </c>
+      <c r="P28" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>36</v>
+      </c>
+      <c r="R28" t="n">
+        <v>39</v>
+      </c>
+      <c r="S28" t="n">
         <v>41</v>
       </c>
-      <c r="P28" t="n">
-        <v>36</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>39</v>
-      </c>
-      <c r="R28" t="n">
-        <v>40</v>
-      </c>
-      <c r="S28" t="n">
-        <v>35</v>
-      </c>
       <c r="T28" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="U28" t="n">
-        <v>1687.7</v>
+        <v>1655.1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1401</v>
+        <v>1365</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Texas A&amp;M</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2456,68 +2456,68 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>11a</t>
         </is>
       </c>
       <c r="E29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G29" t="n">
-        <v>1836.9</v>
+        <v>1765.3</v>
       </c>
       <c r="H29" t="n">
-        <v>4.4256</v>
+        <v>-0.5462</v>
       </c>
       <c r="I29" t="n">
-        <v>118.62</v>
+        <v>117.4</v>
       </c>
       <c r="J29" t="n">
-        <v>106.73</v>
+        <v>102.2</v>
       </c>
       <c r="K29" t="n">
-        <v>11.89</v>
+        <v>15.2</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3028</v>
+        <v>0.3448</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1406</v>
+        <v>0.1494</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.6</v>
+        <v>5.4</v>
       </c>
       <c r="O29" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P29" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="Q29" t="n">
+        <v>45</v>
+      </c>
+      <c r="R29" t="n">
+        <v>37</v>
+      </c>
+      <c r="S29" t="n">
         <v>36</v>
       </c>
-      <c r="R29" t="n">
-        <v>39</v>
-      </c>
-      <c r="S29" t="n">
-        <v>41</v>
-      </c>
       <c r="T29" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="U29" t="n">
-        <v>1655.1</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1378</v>
+        <v>1307</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>South Florida</t>
+          <t>New Mexico</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2527,68 +2527,68 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11b</t>
         </is>
       </c>
       <c r="E30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G30" t="n">
-        <v>1711.9</v>
+        <v>1825.3</v>
       </c>
       <c r="H30" t="n">
-        <v>9.663</v>
+        <v>4.1386</v>
       </c>
       <c r="I30" t="n">
-        <v>115.41</v>
+        <v>114.16</v>
       </c>
       <c r="J30" t="n">
-        <v>101.54</v>
+        <v>101.47</v>
       </c>
       <c r="K30" t="n">
-        <v>13.87</v>
+        <v>12.7</v>
       </c>
       <c r="L30" t="n">
-        <v>0.3355</v>
+        <v>0.2721</v>
       </c>
       <c r="M30" t="n">
-        <v>0.1477</v>
+        <v>0.1448</v>
       </c>
       <c r="N30" t="n">
-        <v>15.6</v>
+        <v>5.8</v>
       </c>
       <c r="O30" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="P30" t="n">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="Q30" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="R30" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="S30" t="n">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="T30" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="U30" t="n">
-        <v>1559.6</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1372</v>
+        <v>1251</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SF Austin</t>
+          <t>Liberty</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2598,68 +2598,68 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E31" t="b">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G31" t="n">
-        <v>1563.2</v>
+        <v>1732.5</v>
       </c>
       <c r="H31" t="n">
-        <v>3.2331</v>
+        <v>3.2122</v>
       </c>
       <c r="I31" t="n">
-        <v>113.58</v>
+        <v>117.41</v>
       </c>
       <c r="J31" t="n">
-        <v>98.86</v>
+        <v>110.66</v>
       </c>
       <c r="K31" t="n">
-        <v>14.72</v>
+        <v>6.75</v>
       </c>
       <c r="L31" t="n">
-        <v>0.311</v>
+        <v>0.1701</v>
       </c>
       <c r="M31" t="n">
-        <v>0.1336</v>
+        <v>0.1316</v>
       </c>
       <c r="N31" t="n">
-        <v>7.6</v>
+        <v>-6.2</v>
       </c>
       <c r="O31" t="n">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="P31" t="n">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="Q31" t="n">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="R31" t="n">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="S31" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="T31" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="U31" t="n">
-        <v>1382.6</v>
+        <v>1483.4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1407</v>
+        <v>1465</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Troy</t>
+          <t>Cal Baptist</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2669,68 +2669,68 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E32" t="b">
         <v>0</v>
       </c>
       <c r="F32" t="n">
+        <v>122</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1592.1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.4758</v>
+      </c>
+      <c r="I32" t="n">
+        <v>107.02</v>
+      </c>
+      <c r="J32" t="n">
+        <v>98.72</v>
+      </c>
+      <c r="K32" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.1721</v>
+      </c>
+      <c r="N32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="O32" t="n">
+        <v>119</v>
+      </c>
+      <c r="P32" t="n">
         <v>116</v>
       </c>
-      <c r="G32" t="n">
-        <v>1596.8</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1.2901</v>
-      </c>
-      <c r="I32" t="n">
-        <v>112.11</v>
-      </c>
-      <c r="J32" t="n">
-        <v>106.85</v>
-      </c>
-      <c r="K32" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0.3162</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0.1601</v>
-      </c>
-      <c r="N32" t="n">
-        <v>4</v>
-      </c>
-      <c r="O32" t="n">
-        <v>156</v>
-      </c>
-      <c r="P32" t="n">
-        <v>133</v>
-      </c>
       <c r="Q32" t="n">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="R32" t="n">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="S32" t="n">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="T32" t="n">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="U32" t="n">
-        <v>1465.3</v>
+        <v>1460.6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1467</v>
+        <v>1295</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Merrimack</t>
+          <t>N Dakota St</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2740,68 +2740,68 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E33" t="b">
         <v>0</v>
       </c>
       <c r="F33" t="n">
+        <v>122</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1589.9</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3.844</v>
+      </c>
+      <c r="I33" t="n">
+        <v>114.57</v>
+      </c>
+      <c r="J33" t="n">
+        <v>103.26</v>
+      </c>
+      <c r="K33" t="n">
+        <v>11.31</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.3149</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.1499</v>
+      </c>
+      <c r="N33" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="O33" t="n">
         <v>118</v>
       </c>
-      <c r="G33" t="n">
-        <v>1512.4</v>
-      </c>
-      <c r="H33" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="I33" t="n">
-        <v>107.55</v>
-      </c>
-      <c r="J33" t="n">
-        <v>104.05</v>
-      </c>
-      <c r="K33" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0.2641</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="N33" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O33" t="n">
-        <v>172</v>
-      </c>
       <c r="P33" t="n">
-        <v>172</v>
+        <v>121</v>
       </c>
       <c r="Q33" t="n">
-        <v>192</v>
+        <v>155</v>
       </c>
       <c r="R33" t="n">
-        <v>158</v>
+        <v>128</v>
       </c>
       <c r="S33" t="n">
-        <v>119</v>
+        <v>94</v>
       </c>
       <c r="T33" t="n">
-        <v>185</v>
+        <v>117</v>
       </c>
       <c r="U33" t="n">
-        <v>1452.7</v>
+        <v>1412.7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1254</v>
+        <v>1467</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LIU Brooklyn</t>
+          <t>Merrimack</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2811,68 +2811,68 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>16a</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G34" t="n">
-        <v>1414.1</v>
+        <v>1512.4</v>
       </c>
       <c r="H34" t="n">
-        <v>2.4721</v>
+        <v>3.91</v>
       </c>
       <c r="I34" t="n">
-        <v>109.35</v>
+        <v>107.55</v>
       </c>
       <c r="J34" t="n">
-        <v>104.93</v>
+        <v>104.05</v>
       </c>
       <c r="K34" t="n">
-        <v>4.42</v>
+        <v>3.5</v>
       </c>
       <c r="L34" t="n">
-        <v>0.32</v>
+        <v>0.2641</v>
       </c>
       <c r="M34" t="n">
-        <v>0.1885</v>
+        <v>0.144</v>
       </c>
       <c r="N34" t="n">
-        <v>5.8</v>
+        <v>3.6</v>
       </c>
       <c r="O34" t="n">
-        <v>210</v>
+        <v>172</v>
       </c>
       <c r="P34" t="n">
-        <v>228</v>
+        <v>172</v>
       </c>
       <c r="Q34" t="n">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="R34" t="n">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="S34" t="n">
-        <v>173</v>
+        <v>119</v>
       </c>
       <c r="T34" t="n">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="U34" t="n">
-        <v>1378.7</v>
+        <v>1452.7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1420</v>
+        <v>1398</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>UMBC</t>
+          <t>Tennessee St</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2882,139 +2882,139 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>16b</t>
+          <t>16a</t>
         </is>
       </c>
       <c r="E35" t="b">
         <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G35" t="n">
-        <v>1390.3</v>
+        <v>1459.3</v>
       </c>
       <c r="H35" t="n">
-        <v>1.1323</v>
+        <v>3.6053</v>
       </c>
       <c r="I35" t="n">
-        <v>111.8</v>
+        <v>108.6</v>
       </c>
       <c r="J35" t="n">
-        <v>101.74</v>
+        <v>103.65</v>
       </c>
       <c r="K35" t="n">
-        <v>10.06</v>
+        <v>4.95</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2176</v>
+        <v>0.3274</v>
       </c>
       <c r="M35" t="n">
-        <v>0.1378</v>
+        <v>0.1566</v>
       </c>
       <c r="N35" t="n">
-        <v>18.4</v>
+        <v>12.2</v>
       </c>
       <c r="O35" t="n">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="P35" t="n">
-        <v>238</v>
+        <v>199</v>
       </c>
       <c r="Q35" t="n">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="R35" t="n">
-        <v>206</v>
+        <v>182</v>
       </c>
       <c r="S35" t="n">
-        <v>221</v>
+        <v>184</v>
       </c>
       <c r="T35" t="n">
-        <v>223</v>
+        <v>191</v>
       </c>
       <c r="U35" t="n">
-        <v>1368.2</v>
+        <v>1406.8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1276</v>
+        <v>1254</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>LIU Brooklyn</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>16b</t>
         </is>
       </c>
       <c r="E36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="G36" t="n">
-        <v>2167</v>
+        <v>1414.1</v>
       </c>
       <c r="H36" t="n">
-        <v>8.613799999999999</v>
+        <v>2.4721</v>
       </c>
       <c r="I36" t="n">
-        <v>122.15</v>
+        <v>109.35</v>
       </c>
       <c r="J36" t="n">
-        <v>94.92</v>
+        <v>104.93</v>
       </c>
       <c r="K36" t="n">
-        <v>27.23</v>
+        <v>4.42</v>
       </c>
       <c r="L36" t="n">
-        <v>0.2673</v>
+        <v>0.32</v>
       </c>
       <c r="M36" t="n">
-        <v>0.1627</v>
+        <v>0.1885</v>
       </c>
       <c r="N36" t="n">
-        <v>12</v>
+        <v>5.8</v>
       </c>
       <c r="O36" t="n">
-        <v>2</v>
+        <v>210</v>
       </c>
       <c r="P36" t="n">
-        <v>3</v>
+        <v>228</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>211</v>
       </c>
       <c r="R36" t="n">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>173</v>
       </c>
       <c r="T36" t="n">
-        <v>2</v>
+        <v>195</v>
       </c>
       <c r="U36" t="n">
-        <v>1754.5</v>
+        <v>1378.7</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1222</v>
+        <v>1276</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3024,68 +3024,68 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="E37" t="b">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G37" t="n">
-        <v>2085.1</v>
+        <v>2172.4</v>
       </c>
       <c r="H37" t="n">
-        <v>2.67</v>
+        <v>8.183400000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>117.81</v>
+        <v>121.54</v>
       </c>
       <c r="J37" t="n">
-        <v>94.78</v>
+        <v>95.23</v>
       </c>
       <c r="K37" t="n">
-        <v>23.03</v>
+        <v>26.31</v>
       </c>
       <c r="L37" t="n">
-        <v>0.3414</v>
+        <v>0.2642</v>
       </c>
       <c r="M37" t="n">
-        <v>0.1193</v>
+        <v>0.1678</v>
       </c>
       <c r="N37" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="O37" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P37" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T37" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U37" t="n">
-        <v>1703.4</v>
+        <v>1756.1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1304</v>
+        <v>1222</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nebraska</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3095,68 +3095,68 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="E38" t="b">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G38" t="n">
-        <v>1990.6</v>
+        <v>2085.1</v>
       </c>
       <c r="H38" t="n">
-        <v>11.3442</v>
+        <v>2.67</v>
       </c>
       <c r="I38" t="n">
-        <v>115.07</v>
+        <v>117.81</v>
       </c>
       <c r="J38" t="n">
-        <v>98.04000000000001</v>
+        <v>94.78</v>
       </c>
       <c r="K38" t="n">
-        <v>17.03</v>
+        <v>23.03</v>
       </c>
       <c r="L38" t="n">
-        <v>0.2419</v>
+        <v>0.3414</v>
       </c>
       <c r="M38" t="n">
-        <v>0.1401</v>
+        <v>0.1193</v>
       </c>
       <c r="N38" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="O38" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="P38" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="Q38" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="R38" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T38" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="U38" t="n">
-        <v>1658</v>
+        <v>1703.4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1438</v>
+        <v>1304</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>Nebraska</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="E39" t="b">
@@ -3176,58 +3176,58 @@
         <v>120</v>
       </c>
       <c r="G39" t="n">
-        <v>1951.2</v>
+        <v>1990.6</v>
       </c>
       <c r="H39" t="n">
-        <v>13.9718</v>
+        <v>11.3442</v>
       </c>
       <c r="I39" t="n">
-        <v>118.9</v>
+        <v>115.07</v>
       </c>
       <c r="J39" t="n">
-        <v>99.7</v>
+        <v>98.04000000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>19.2</v>
+        <v>17.03</v>
       </c>
       <c r="L39" t="n">
-        <v>0.3157</v>
+        <v>0.2419</v>
       </c>
       <c r="M39" t="n">
-        <v>0.1519</v>
+        <v>0.1401</v>
       </c>
       <c r="N39" t="n">
-        <v>7.4</v>
+        <v>5.2</v>
       </c>
       <c r="O39" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="P39" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="Q39" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="R39" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T39" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="U39" t="n">
-        <v>1635.2</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1435</v>
+        <v>1242</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Vanderbilt</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>04</t>
         </is>
       </c>
       <c r="E40" t="b">
@@ -3247,58 +3247,58 @@
         <v>120</v>
       </c>
       <c r="G40" t="n">
-        <v>1921</v>
+        <v>1972.3</v>
       </c>
       <c r="H40" t="n">
-        <v>1.9274</v>
+        <v>11.3738</v>
       </c>
       <c r="I40" t="n">
-        <v>121.87</v>
+        <v>110.16</v>
       </c>
       <c r="J40" t="n">
-        <v>105.42</v>
+        <v>100.46</v>
       </c>
       <c r="K40" t="n">
-        <v>16.45</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L40" t="n">
-        <v>0.2854</v>
+        <v>0.2509</v>
       </c>
       <c r="M40" t="n">
-        <v>0.1247</v>
+        <v>0.1535</v>
       </c>
       <c r="N40" t="n">
-        <v>-1.6</v>
+        <v>-4.8</v>
       </c>
       <c r="O40" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="P40" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Q40" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R40" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S40" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="T40" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="U40" t="n">
-        <v>1684</v>
+        <v>1777.3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1314</v>
+        <v>1116</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3308,68 +3308,68 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>05</t>
         </is>
       </c>
       <c r="E41" t="b">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G41" t="n">
-        <v>1921.2</v>
+        <v>1932.7</v>
       </c>
       <c r="H41" t="n">
-        <v>2.4067</v>
+        <v>6.7834</v>
       </c>
       <c r="I41" t="n">
-        <v>115.82</v>
+        <v>123.18</v>
       </c>
       <c r="J41" t="n">
-        <v>102.6</v>
+        <v>108.72</v>
       </c>
       <c r="K41" t="n">
-        <v>13.22</v>
+        <v>14.46</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2692</v>
+        <v>0.2975</v>
       </c>
       <c r="M41" t="n">
-        <v>0.1364</v>
+        <v>0.1194</v>
       </c>
       <c r="N41" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="O41" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="P41" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Q41" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R41" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="S41" t="n">
+        <v>20</v>
+      </c>
+      <c r="T41" t="n">
         <v>19</v>
       </c>
-      <c r="T41" t="n">
-        <v>25</v>
-      </c>
       <c r="U41" t="n">
-        <v>1655.5</v>
+        <v>1725.9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1458</v>
+        <v>1435</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Vanderbilt</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3379,68 +3379,68 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>06</t>
         </is>
       </c>
       <c r="E42" t="b">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G42" t="n">
-        <v>1837.7</v>
+        <v>1921</v>
       </c>
       <c r="H42" t="n">
-        <v>0.7673</v>
+        <v>1.9274</v>
       </c>
       <c r="I42" t="n">
-        <v>118.38</v>
+        <v>121.87</v>
       </c>
       <c r="J42" t="n">
-        <v>106.47</v>
+        <v>105.42</v>
       </c>
       <c r="K42" t="n">
-        <v>11.91</v>
+        <v>16.45</v>
       </c>
       <c r="L42" t="n">
-        <v>0.2733</v>
+        <v>0.2854</v>
       </c>
       <c r="M42" t="n">
-        <v>0.1236</v>
+        <v>0.1247</v>
       </c>
       <c r="N42" t="n">
-        <v>6.4</v>
+        <v>-1.6</v>
       </c>
       <c r="O42" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="P42" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="Q42" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="R42" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="S42" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="T42" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="U42" t="n">
-        <v>1686</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1416</v>
+        <v>1388</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>UCF</t>
+          <t>St Mary's CA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3450,68 +3450,68 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>07</t>
         </is>
       </c>
       <c r="E43" t="b">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G43" t="n">
-        <v>1839.8</v>
+        <v>1877.4</v>
       </c>
       <c r="H43" t="n">
-        <v>7.5365</v>
+        <v>-0.2467</v>
       </c>
       <c r="I43" t="n">
-        <v>115.83</v>
+        <v>118.87</v>
       </c>
       <c r="J43" t="n">
-        <v>110.45</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>5.38</v>
+        <v>20.05</v>
       </c>
       <c r="L43" t="n">
-        <v>0.3093</v>
+        <v>0.2966</v>
       </c>
       <c r="M43" t="n">
-        <v>0.1541</v>
+        <v>0.1557</v>
       </c>
       <c r="N43" t="n">
-        <v>3.6</v>
+        <v>11.8</v>
       </c>
       <c r="O43" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="P43" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="Q43" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="R43" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="S43" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="T43" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="U43" t="n">
-        <v>1687.9</v>
+        <v>1595.8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1301</v>
+        <v>1155</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NC State</t>
+          <t>Clemson</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3521,68 +3521,68 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>08</t>
         </is>
       </c>
       <c r="E44" t="b">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G44" t="n">
-        <v>1751.4</v>
+        <v>1839.7</v>
       </c>
       <c r="H44" t="n">
-        <v>8.2582</v>
+        <v>3.0742</v>
       </c>
       <c r="I44" t="n">
-        <v>118.51</v>
+        <v>112.26</v>
       </c>
       <c r="J44" t="n">
-        <v>107.99</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>10.52</v>
+        <v>12.36</v>
       </c>
       <c r="L44" t="n">
-        <v>0.2827</v>
+        <v>0.2417</v>
       </c>
       <c r="M44" t="n">
-        <v>0.1274</v>
+        <v>0.1398</v>
       </c>
       <c r="N44" t="n">
-        <v>-8.199999999999999</v>
+        <v>-5</v>
       </c>
       <c r="O44" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="P44" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="Q44" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="R44" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S44" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="T44" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="U44" t="n">
-        <v>1678.8</v>
+        <v>1652.1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1400</v>
+        <v>1416</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>UCF</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3592,68 +3592,68 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>09</t>
         </is>
       </c>
       <c r="E45" t="b">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G45" t="n">
-        <v>1777.5</v>
+        <v>1839.8</v>
       </c>
       <c r="H45" t="n">
-        <v>2.2904</v>
+        <v>7.5365</v>
       </c>
       <c r="I45" t="n">
-        <v>120.67</v>
+        <v>115.83</v>
       </c>
       <c r="J45" t="n">
-        <v>111.46</v>
+        <v>110.45</v>
       </c>
       <c r="K45" t="n">
-        <v>9.210000000000001</v>
+        <v>5.38</v>
       </c>
       <c r="L45" t="n">
-        <v>0.3123</v>
+        <v>0.3093</v>
       </c>
       <c r="M45" t="n">
-        <v>0.1488</v>
+        <v>0.1541</v>
       </c>
       <c r="N45" t="n">
-        <v>-7</v>
+        <v>3.6</v>
       </c>
       <c r="O45" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="P45" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="Q45" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="R45" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="S45" t="n">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="T45" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="U45" t="n">
-        <v>1700.7</v>
+        <v>1687.9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1307</v>
+        <v>1326</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>New Mexico</t>
+          <t>Ohio St</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3663,68 +3663,68 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>11a</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
         <v>121</v>
       </c>
       <c r="G46" t="n">
-        <v>1825.3</v>
+        <v>1787.4</v>
       </c>
       <c r="H46" t="n">
-        <v>4.1386</v>
+        <v>1.3307</v>
       </c>
       <c r="I46" t="n">
-        <v>114.16</v>
+        <v>118.28</v>
       </c>
       <c r="J46" t="n">
-        <v>101.47</v>
+        <v>107.42</v>
       </c>
       <c r="K46" t="n">
-        <v>12.7</v>
+        <v>10.87</v>
       </c>
       <c r="L46" t="n">
-        <v>0.2721</v>
+        <v>0.255</v>
       </c>
       <c r="M46" t="n">
-        <v>0.1448</v>
+        <v>0.1501</v>
       </c>
       <c r="N46" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="O46" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="P46" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="Q46" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="R46" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="S46" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="T46" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="U46" t="n">
-        <v>1590</v>
+        <v>1694.2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1231</v>
+        <v>1275</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Indiana</t>
+          <t>Miami OH</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3734,68 +3734,68 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>11b</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G47" t="n">
-        <v>1752.7</v>
+        <v>1772.7</v>
       </c>
       <c r="H47" t="n">
-        <v>-2.7312</v>
+        <v>9.988799999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>116.39</v>
+        <v>120.02</v>
       </c>
       <c r="J47" t="n">
-        <v>106.14</v>
+        <v>103.88</v>
       </c>
       <c r="K47" t="n">
-        <v>10.26</v>
+        <v>16.14</v>
       </c>
       <c r="L47" t="n">
-        <v>0.234</v>
+        <v>0.2071</v>
       </c>
       <c r="M47" t="n">
-        <v>0.1415</v>
+        <v>0.1427</v>
       </c>
       <c r="N47" t="n">
-        <v>-7.2</v>
+        <v>7.4</v>
       </c>
       <c r="O47" t="n">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="P47" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="Q47" t="n">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="R47" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="S47" t="n">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="T47" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="U47" t="n">
-        <v>1695.9</v>
+        <v>1413.1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1251</v>
+        <v>1378</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Liberty</t>
+          <t>South Florida</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3812,61 +3812,61 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G48" t="n">
-        <v>1748.8</v>
+        <v>1713.4</v>
       </c>
       <c r="H48" t="n">
-        <v>3.3725</v>
+        <v>9.475099999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>117.36</v>
+        <v>115.67</v>
       </c>
       <c r="J48" t="n">
-        <v>109.9</v>
+        <v>102.39</v>
       </c>
       <c r="K48" t="n">
-        <v>7.45</v>
+        <v>13.28</v>
       </c>
       <c r="L48" t="n">
-        <v>0.1613</v>
+        <v>0.336</v>
       </c>
       <c r="M48" t="n">
-        <v>0.1322</v>
+        <v>0.1478</v>
       </c>
       <c r="N48" t="n">
-        <v>-3.4</v>
+        <v>15.4</v>
       </c>
       <c r="O48" t="n">
-        <v>111</v>
+        <v>52</v>
       </c>
       <c r="P48" t="n">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="Q48" t="n">
-        <v>111</v>
+        <v>55</v>
       </c>
       <c r="R48" t="n">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="S48" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T48" t="n">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="U48" t="n">
-        <v>1483.1</v>
+        <v>1560.8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1465</v>
+        <v>1219</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Cal Baptist</t>
+          <t>High Point</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3883,61 +3883,61 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G49" t="n">
-        <v>1593.4</v>
+        <v>1623.3</v>
       </c>
       <c r="H49" t="n">
-        <v>1.4565</v>
+        <v>-1.5579</v>
       </c>
       <c r="I49" t="n">
-        <v>106.65</v>
+        <v>121.64</v>
       </c>
       <c r="J49" t="n">
-        <v>100.29</v>
+        <v>100.61</v>
       </c>
       <c r="K49" t="n">
-        <v>6.36</v>
+        <v>21.04</v>
       </c>
       <c r="L49" t="n">
-        <v>0.3373</v>
+        <v>0.3121</v>
       </c>
       <c r="M49" t="n">
-        <v>0.1707</v>
+        <v>0.1266</v>
       </c>
       <c r="N49" t="n">
-        <v>4</v>
+        <v>16.8</v>
       </c>
       <c r="O49" t="n">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="P49" t="n">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="Q49" t="n">
-        <v>130</v>
+        <v>92</v>
       </c>
       <c r="R49" t="n">
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="S49" t="n">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="T49" t="n">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="U49" t="n">
-        <v>1462</v>
+        <v>1381.5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1414</v>
+        <v>1298</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>UC Irvine</t>
+          <t>Navy</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3954,61 +3954,61 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G50" t="n">
-        <v>1609.5</v>
+        <v>1430.5</v>
       </c>
       <c r="H50" t="n">
-        <v>2.2816</v>
+        <v>3.2584</v>
       </c>
       <c r="I50" t="n">
-        <v>102.13</v>
+        <v>113.28</v>
       </c>
       <c r="J50" t="n">
-        <v>95.97</v>
+        <v>98.59</v>
       </c>
       <c r="K50" t="n">
-        <v>6.16</v>
+        <v>14.69</v>
       </c>
       <c r="L50" t="n">
-        <v>0.2694</v>
+        <v>0.2673</v>
       </c>
       <c r="M50" t="n">
-        <v>0.1701</v>
+        <v>0.1673</v>
       </c>
       <c r="N50" t="n">
-        <v>7</v>
+        <v>17.8</v>
       </c>
       <c r="O50" t="n">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="P50" t="n">
-        <v>122</v>
+        <v>164</v>
       </c>
       <c r="Q50" t="n">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="R50" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="S50" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="T50" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="U50" t="n">
-        <v>1474.6</v>
+        <v>1375.7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1340</v>
+        <v>1190</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Portland St</t>
+          <t>ETSU</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4025,52 +4025,52 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G51" t="n">
-        <v>1458.6</v>
+        <v>1515</v>
       </c>
       <c r="H51" t="n">
-        <v>2.1359</v>
+        <v>0.5934</v>
       </c>
       <c r="I51" t="n">
-        <v>105.36</v>
+        <v>116.43</v>
       </c>
       <c r="J51" t="n">
-        <v>101.08</v>
+        <v>105.39</v>
       </c>
       <c r="K51" t="n">
-        <v>4.28</v>
+        <v>11.04</v>
       </c>
       <c r="L51" t="n">
-        <v>0.2592</v>
+        <v>0.2692</v>
       </c>
       <c r="M51" t="n">
-        <v>0.1706</v>
+        <v>0.1444</v>
       </c>
       <c r="N51" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="O51" t="n">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="P51" t="n">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="Q51" t="n">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="R51" t="n">
-        <v>167</v>
+        <v>136</v>
       </c>
       <c r="S51" t="n">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="T51" t="n">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="U51" t="n">
-        <v>1417.2</v>
+        <v>1424.7</v>
       </c>
     </row>
     <row r="52">
@@ -4096,31 +4096,31 @@
         <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G52" t="n">
-        <v>1405</v>
+        <v>1410.9</v>
       </c>
       <c r="H52" t="n">
-        <v>3.4361</v>
+        <v>3.2396</v>
       </c>
       <c r="I52" t="n">
-        <v>108.68</v>
+        <v>109.08</v>
       </c>
       <c r="J52" t="n">
-        <v>98.20999999999999</v>
+        <v>98.81</v>
       </c>
       <c r="K52" t="n">
-        <v>10.47</v>
+        <v>10.27</v>
       </c>
       <c r="L52" t="n">
-        <v>0.3193</v>
+        <v>0.3126</v>
       </c>
       <c r="M52" t="n">
-        <v>0.1857</v>
+        <v>0.1855</v>
       </c>
       <c r="N52" t="n">
-        <v>27.2</v>
+        <v>23.6</v>
       </c>
       <c r="O52" t="n">
         <v>199</v>
@@ -4141,7 +4141,7 @@
         <v>202</v>
       </c>
       <c r="U52" t="n">
-        <v>1378.5</v>
+        <v>1380.9</v>
       </c>
     </row>
     <row r="53">
@@ -4167,31 +4167,31 @@
         <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G53" t="n">
-        <v>1378.8</v>
+        <v>1375.9</v>
       </c>
       <c r="H53" t="n">
-        <v>0.8435</v>
+        <v>0.9186</v>
       </c>
       <c r="I53" t="n">
-        <v>105.06</v>
+        <v>104.96</v>
       </c>
       <c r="J53" t="n">
-        <v>108.63</v>
+        <v>108.7</v>
       </c>
       <c r="K53" t="n">
-        <v>-3.58</v>
+        <v>-3.74</v>
       </c>
       <c r="L53" t="n">
-        <v>0.2799</v>
+        <v>0.2778</v>
       </c>
       <c r="M53" t="n">
-        <v>0.1853</v>
+        <v>0.1862</v>
       </c>
       <c r="N53" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O53" t="n">
         <v>233</v>
@@ -4212,7 +4212,7 @@
         <v>246</v>
       </c>
       <c r="U53" t="n">
-        <v>1441.9</v>
+        <v>1436.2</v>
       </c>
     </row>
     <row r="54">
@@ -4359,11 +4359,11 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1242</v>
+        <v>1211</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Gonzaga</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4380,61 +4380,61 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G56" t="n">
-        <v>1972.3</v>
+        <v>2055.1</v>
       </c>
       <c r="H56" t="n">
-        <v>11.3738</v>
+        <v>6.9647</v>
       </c>
       <c r="I56" t="n">
-        <v>110.16</v>
+        <v>120.35</v>
       </c>
       <c r="J56" t="n">
-        <v>100.46</v>
+        <v>93.25</v>
       </c>
       <c r="K56" t="n">
-        <v>9.699999999999999</v>
+        <v>27.1</v>
       </c>
       <c r="L56" t="n">
-        <v>0.2509</v>
+        <v>0.2992</v>
       </c>
       <c r="M56" t="n">
-        <v>0.1535</v>
+        <v>0.1329</v>
       </c>
       <c r="N56" t="n">
-        <v>-4.8</v>
+        <v>13.6</v>
       </c>
       <c r="O56" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P56" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Q56" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="R56" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="S56" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T56" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="U56" t="n">
-        <v>1777.3</v>
+        <v>1597.1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1104</v>
+        <v>1403</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Alabama</t>
+          <t>Texas Tech</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4454,58 +4454,58 @@
         <v>120</v>
       </c>
       <c r="G57" t="n">
-        <v>1966.5</v>
+        <v>2034.5</v>
       </c>
       <c r="H57" t="n">
-        <v>-1.6248</v>
+        <v>11.3167</v>
       </c>
       <c r="I57" t="n">
-        <v>121.39</v>
+        <v>118.24</v>
       </c>
       <c r="J57" t="n">
-        <v>110.58</v>
+        <v>105.38</v>
       </c>
       <c r="K57" t="n">
-        <v>10.81</v>
+        <v>12.86</v>
       </c>
       <c r="L57" t="n">
-        <v>0.279</v>
+        <v>0.2929</v>
       </c>
       <c r="M57" t="n">
-        <v>0.1296</v>
+        <v>0.1562</v>
       </c>
       <c r="N57" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="O57" t="n">
+        <v>13</v>
+      </c>
+      <c r="P57" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>11</v>
+      </c>
+      <c r="R57" t="n">
+        <v>11</v>
+      </c>
+      <c r="S57" t="n">
         <v>15</v>
       </c>
-      <c r="P57" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q57" t="n">
+      <c r="T57" t="n">
         <v>13</v>
       </c>
-      <c r="R57" t="n">
-        <v>14</v>
-      </c>
-      <c r="S57" t="n">
-        <v>16</v>
-      </c>
-      <c r="T57" t="n">
-        <v>16</v>
-      </c>
       <c r="U57" t="n">
-        <v>1769.4</v>
+        <v>1753.9</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1385</v>
+        <v>1314</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>St John's</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4525,58 +4525,58 @@
         <v>120</v>
       </c>
       <c r="G58" t="n">
-        <v>1955.3</v>
+        <v>1921.2</v>
       </c>
       <c r="H58" t="n">
-        <v>4.7636</v>
+        <v>2.4067</v>
       </c>
       <c r="I58" t="n">
-        <v>113.73</v>
+        <v>115.82</v>
       </c>
       <c r="J58" t="n">
-        <v>98.58</v>
+        <v>102.6</v>
       </c>
       <c r="K58" t="n">
-        <v>15.15</v>
+        <v>13.22</v>
       </c>
       <c r="L58" t="n">
-        <v>0.3268</v>
+        <v>0.2692</v>
       </c>
       <c r="M58" t="n">
-        <v>0.1411</v>
+        <v>0.1364</v>
       </c>
       <c r="N58" t="n">
-        <v>7.6</v>
+        <v>0.6</v>
       </c>
       <c r="O58" t="n">
+        <v>28</v>
+      </c>
+      <c r="P58" t="n">
         <v>21</v>
       </c>
-      <c r="P58" t="n">
-        <v>17</v>
-      </c>
       <c r="Q58" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="R58" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="S58" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="T58" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="U58" t="n">
-        <v>1677.8</v>
+        <v>1655.5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1246</v>
+        <v>1458</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4593,61 +4593,61 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G59" t="n">
-        <v>1893.4</v>
+        <v>1837.7</v>
       </c>
       <c r="H59" t="n">
-        <v>6.006</v>
+        <v>0.7673</v>
       </c>
       <c r="I59" t="n">
-        <v>116.85</v>
+        <v>118.38</v>
       </c>
       <c r="J59" t="n">
-        <v>105.78</v>
+        <v>106.47</v>
       </c>
       <c r="K59" t="n">
-        <v>11.07</v>
+        <v>11.91</v>
       </c>
       <c r="L59" t="n">
-        <v>0.3101</v>
+        <v>0.2733</v>
       </c>
       <c r="M59" t="n">
-        <v>0.1466</v>
+        <v>0.1236</v>
       </c>
       <c r="N59" t="n">
-        <v>0.6</v>
+        <v>6.4</v>
       </c>
       <c r="O59" t="n">
+        <v>30</v>
+      </c>
+      <c r="P59" t="n">
         <v>25</v>
       </c>
-      <c r="P59" t="n">
-        <v>22</v>
-      </c>
       <c r="Q59" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="R59" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S59" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T59" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="U59" t="n">
-        <v>1717.2</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1388</v>
+        <v>1140</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>St Mary's CA</t>
+          <t>BYU</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4664,61 +4664,61 @@
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G60" t="n">
-        <v>1877.4</v>
+        <v>1901.3</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.2467</v>
+        <v>2.827</v>
       </c>
       <c r="I60" t="n">
-        <v>118.87</v>
+        <v>117.49</v>
       </c>
       <c r="J60" t="n">
-        <v>98.81999999999999</v>
+        <v>106.29</v>
       </c>
       <c r="K60" t="n">
-        <v>20.05</v>
+        <v>11.21</v>
       </c>
       <c r="L60" t="n">
-        <v>0.2966</v>
+        <v>0.2953</v>
       </c>
       <c r="M60" t="n">
-        <v>0.1557</v>
+        <v>0.1466</v>
       </c>
       <c r="N60" t="n">
-        <v>11.8</v>
+        <v>-8</v>
       </c>
       <c r="O60" t="n">
+        <v>23</v>
+      </c>
+      <c r="P60" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q60" t="n">
         <v>22</v>
       </c>
-      <c r="P60" t="n">
+      <c r="R60" t="n">
+        <v>22</v>
+      </c>
+      <c r="S60" t="n">
+        <v>21</v>
+      </c>
+      <c r="T60" t="n">
         <v>23</v>
       </c>
-      <c r="Q60" t="n">
-        <v>27</v>
-      </c>
-      <c r="R60" t="n">
-        <v>23</v>
-      </c>
-      <c r="S60" t="n">
-        <v>23</v>
-      </c>
-      <c r="T60" t="n">
-        <v>21</v>
-      </c>
       <c r="U60" t="n">
-        <v>1595.8</v>
+        <v>1712.1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1155</v>
+        <v>1208</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Clemson</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4738,58 +4738,58 @@
         <v>120</v>
       </c>
       <c r="G61" t="n">
-        <v>1839.7</v>
+        <v>1810.7</v>
       </c>
       <c r="H61" t="n">
-        <v>3.0742</v>
+        <v>-0.8284</v>
       </c>
       <c r="I61" t="n">
-        <v>112.26</v>
+        <v>120.8</v>
       </c>
       <c r="J61" t="n">
-        <v>99.90000000000001</v>
+        <v>106.43</v>
       </c>
       <c r="K61" t="n">
-        <v>12.36</v>
+        <v>14.38</v>
       </c>
       <c r="L61" t="n">
-        <v>0.2417</v>
+        <v>0.3238</v>
       </c>
       <c r="M61" t="n">
-        <v>0.1398</v>
+        <v>0.1381</v>
       </c>
       <c r="N61" t="n">
-        <v>-5</v>
+        <v>8</v>
       </c>
       <c r="O61" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P61" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q61" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R61" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="S61" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="T61" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="U61" t="n">
-        <v>1652.1</v>
+        <v>1647.3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1281</v>
+        <v>1301</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>NC State</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4806,61 +4806,61 @@
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G62" t="n">
-        <v>1768.2</v>
+        <v>1751.4</v>
       </c>
       <c r="H62" t="n">
-        <v>-2.8893</v>
+        <v>8.2582</v>
       </c>
       <c r="I62" t="n">
-        <v>115.23</v>
+        <v>118.51</v>
       </c>
       <c r="J62" t="n">
-        <v>109.22</v>
+        <v>107.99</v>
       </c>
       <c r="K62" t="n">
-        <v>6.01</v>
+        <v>10.52</v>
       </c>
       <c r="L62" t="n">
-        <v>0.3029</v>
+        <v>0.2827</v>
       </c>
       <c r="M62" t="n">
-        <v>0.1713</v>
+        <v>0.1274</v>
       </c>
       <c r="N62" t="n">
-        <v>1</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="O62" t="n">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="P62" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="Q62" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="R62" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="S62" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="T62" t="n">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="U62" t="n">
-        <v>1637.7</v>
+        <v>1678.8</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1374</v>
+        <v>1395</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SMU</t>
+          <t>TCU</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4877,61 +4877,61 @@
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G63" t="n">
-        <v>1753.7</v>
+        <v>1824.2</v>
       </c>
       <c r="H63" t="n">
-        <v>1.2979</v>
+        <v>6.8019</v>
       </c>
       <c r="I63" t="n">
-        <v>118.53</v>
+        <v>110.58</v>
       </c>
       <c r="J63" t="n">
-        <v>109.67</v>
+        <v>101.35</v>
       </c>
       <c r="K63" t="n">
-        <v>8.859999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="L63" t="n">
-        <v>0.3029</v>
+        <v>0.3181</v>
       </c>
       <c r="M63" t="n">
-        <v>0.1516</v>
+        <v>0.1536</v>
       </c>
       <c r="N63" t="n">
-        <v>0.4</v>
+        <v>4.8</v>
       </c>
       <c r="O63" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="P63" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>46</v>
+      </c>
+      <c r="R63" t="n">
+        <v>49</v>
+      </c>
+      <c r="S63" t="n">
+        <v>47</v>
+      </c>
+      <c r="T63" t="n">
         <v>45</v>
       </c>
-      <c r="Q63" t="n">
-        <v>37</v>
-      </c>
-      <c r="R63" t="n">
-        <v>36</v>
-      </c>
-      <c r="S63" t="n">
-        <v>38</v>
-      </c>
-      <c r="T63" t="n">
-        <v>36</v>
-      </c>
       <c r="U63" t="n">
-        <v>1646.7</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1275</v>
+        <v>1400</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Miami OH</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4948,61 +4948,61 @@
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G64" t="n">
-        <v>1772.7</v>
+        <v>1777.5</v>
       </c>
       <c r="H64" t="n">
-        <v>9.988799999999999</v>
+        <v>2.2904</v>
       </c>
       <c r="I64" t="n">
-        <v>120.02</v>
+        <v>120.67</v>
       </c>
       <c r="J64" t="n">
-        <v>103.88</v>
+        <v>111.46</v>
       </c>
       <c r="K64" t="n">
-        <v>16.14</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="L64" t="n">
-        <v>0.2071</v>
+        <v>0.3123</v>
       </c>
       <c r="M64" t="n">
-        <v>0.1427</v>
+        <v>0.1488</v>
       </c>
       <c r="N64" t="n">
-        <v>7.4</v>
+        <v>-7</v>
       </c>
       <c r="O64" t="n">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="P64" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="Q64" t="n">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="R64" t="n">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="S64" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="T64" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="U64" t="n">
-        <v>1413.1</v>
+        <v>1700.7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1125</v>
+        <v>1463</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Belmont</t>
+          <t>Yale</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5019,61 +5019,61 @@
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G65" t="n">
-        <v>1753.8</v>
+        <v>1725.3</v>
       </c>
       <c r="H65" t="n">
-        <v>5.6074</v>
+        <v>1.115</v>
       </c>
       <c r="I65" t="n">
-        <v>118.84</v>
+        <v>120.83</v>
       </c>
       <c r="J65" t="n">
-        <v>104.39</v>
+        <v>108.5</v>
       </c>
       <c r="K65" t="n">
-        <v>14.44</v>
+        <v>12.33</v>
       </c>
       <c r="L65" t="n">
-        <v>0.2389</v>
+        <v>0.2837</v>
       </c>
       <c r="M65" t="n">
-        <v>0.1756</v>
+        <v>0.1401</v>
       </c>
       <c r="N65" t="n">
-        <v>13.2</v>
+        <v>4.2</v>
       </c>
       <c r="O65" t="n">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="P65" t="n">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="Q65" t="n">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="R65" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="S65" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="T65" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="U65" t="n">
-        <v>1487.2</v>
+        <v>1460.6</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1219</v>
+        <v>1372</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>High Point</t>
+          <t>SF Austin</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5090,61 +5090,61 @@
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G66" t="n">
-        <v>1623.3</v>
+        <v>1563.2</v>
       </c>
       <c r="H66" t="n">
-        <v>-1.5579</v>
+        <v>3.2331</v>
       </c>
       <c r="I66" t="n">
-        <v>121.64</v>
+        <v>113.58</v>
       </c>
       <c r="J66" t="n">
-        <v>100.61</v>
+        <v>98.86</v>
       </c>
       <c r="K66" t="n">
-        <v>21.04</v>
+        <v>14.72</v>
       </c>
       <c r="L66" t="n">
-        <v>0.3121</v>
+        <v>0.311</v>
       </c>
       <c r="M66" t="n">
-        <v>0.1266</v>
+        <v>0.1336</v>
       </c>
       <c r="N66" t="n">
-        <v>16.8</v>
+        <v>7.6</v>
       </c>
       <c r="O66" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="P66" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="Q66" t="n">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="R66" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="S66" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="T66" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="U66" t="n">
-        <v>1381.5</v>
+        <v>1382.6</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1298</v>
+        <v>1414</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Navy</t>
+          <t>UC Irvine</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5161,61 +5161,61 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G67" t="n">
-        <v>1429.1</v>
+        <v>1611.8</v>
       </c>
       <c r="H67" t="n">
-        <v>3.2768</v>
+        <v>2.2597</v>
       </c>
       <c r="I67" t="n">
-        <v>113.21</v>
+        <v>103.83</v>
       </c>
       <c r="J67" t="n">
-        <v>98.06999999999999</v>
+        <v>96.66</v>
       </c>
       <c r="K67" t="n">
-        <v>15.13</v>
+        <v>7.18</v>
       </c>
       <c r="L67" t="n">
-        <v>0.2695</v>
+        <v>0.2682</v>
       </c>
       <c r="M67" t="n">
-        <v>0.1651</v>
+        <v>0.1661</v>
       </c>
       <c r="N67" t="n">
-        <v>17.6</v>
+        <v>7.2</v>
       </c>
       <c r="O67" t="n">
-        <v>136</v>
+        <v>109</v>
       </c>
       <c r="P67" t="n">
-        <v>164</v>
+        <v>122</v>
       </c>
       <c r="Q67" t="n">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="R67" t="n">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="S67" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="T67" t="n">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="U67" t="n">
-        <v>1379.6</v>
+        <v>1470.9</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1190</v>
+        <v>1340</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ETSU</t>
+          <t>Portland St</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5232,61 +5232,61 @@
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G68" t="n">
-        <v>1515</v>
+        <v>1458.6</v>
       </c>
       <c r="H68" t="n">
-        <v>0.5934</v>
+        <v>2.1359</v>
       </c>
       <c r="I68" t="n">
-        <v>116.43</v>
+        <v>105.36</v>
       </c>
       <c r="J68" t="n">
-        <v>105.39</v>
+        <v>101.08</v>
       </c>
       <c r="K68" t="n">
-        <v>11.04</v>
+        <v>4.28</v>
       </c>
       <c r="L68" t="n">
-        <v>0.2692</v>
+        <v>0.2592</v>
       </c>
       <c r="M68" t="n">
-        <v>0.1444</v>
+        <v>0.1706</v>
       </c>
       <c r="N68" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="O68" t="n">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="P68" t="n">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="Q68" t="n">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="R68" t="n">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="S68" t="n">
+        <v>124</v>
+      </c>
+      <c r="T68" t="n">
         <v>151</v>
       </c>
-      <c r="T68" t="n">
-        <v>128</v>
-      </c>
       <c r="U68" t="n">
-        <v>1424.7</v>
+        <v>1417.2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1398</v>
+        <v>1420</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tennessee St</t>
+          <t>UMBC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5303,52 +5303,52 @@
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G69" t="n">
-        <v>1459.3</v>
+        <v>1390.3</v>
       </c>
       <c r="H69" t="n">
-        <v>3.6053</v>
+        <v>1.1323</v>
       </c>
       <c r="I69" t="n">
-        <v>108.6</v>
+        <v>111.8</v>
       </c>
       <c r="J69" t="n">
-        <v>103.65</v>
+        <v>101.74</v>
       </c>
       <c r="K69" t="n">
-        <v>4.95</v>
+        <v>10.06</v>
       </c>
       <c r="L69" t="n">
-        <v>0.3274</v>
+        <v>0.2176</v>
       </c>
       <c r="M69" t="n">
-        <v>0.1566</v>
+        <v>0.1378</v>
       </c>
       <c r="N69" t="n">
-        <v>12.2</v>
+        <v>18.4</v>
       </c>
       <c r="O69" t="n">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="P69" t="n">
-        <v>199</v>
+        <v>238</v>
       </c>
       <c r="Q69" t="n">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="R69" t="n">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="S69" t="n">
-        <v>184</v>
+        <v>221</v>
       </c>
       <c r="T69" t="n">
-        <v>191</v>
+        <v>223</v>
       </c>
       <c r="U69" t="n">
-        <v>1406.8</v>
+        <v>1368.2</v>
       </c>
     </row>
   </sheetData>

--- a/team_stats_2026.xlsx
+++ b/team_stats_2026.xlsx
@@ -1377,11 +1377,11 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1125</v>
+        <v>1227</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Belmont</t>
+          <t>IL Chicago</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1401,49 +1401,49 @@
         <v>118</v>
       </c>
       <c r="G14" t="n">
-        <v>1753.8</v>
+        <v>1521.6</v>
       </c>
       <c r="H14" t="n">
-        <v>5.6074</v>
+        <v>1.8755</v>
       </c>
       <c r="I14" t="n">
-        <v>118.84</v>
+        <v>107.6</v>
       </c>
       <c r="J14" t="n">
-        <v>104.39</v>
+        <v>103.45</v>
       </c>
       <c r="K14" t="n">
-        <v>14.44</v>
+        <v>4.15</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2389</v>
+        <v>0.3478</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1756</v>
+        <v>0.1686</v>
       </c>
       <c r="N14" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="O14" t="n">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="P14" t="n">
-        <v>61</v>
+        <v>139</v>
       </c>
       <c r="Q14" t="n">
-        <v>67</v>
+        <v>129</v>
       </c>
       <c r="R14" t="n">
-        <v>53</v>
+        <v>117</v>
       </c>
       <c r="S14" t="n">
-        <v>42</v>
+        <v>133</v>
       </c>
       <c r="T14" t="n">
-        <v>55</v>
+        <v>116</v>
       </c>
       <c r="U14" t="n">
-        <v>1487.2</v>
+        <v>1504.2</v>
       </c>
     </row>
     <row r="15">

--- a/team_stats_2026.xlsx
+++ b/team_stats_2026.xlsx
@@ -1377,11 +1377,11 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1227</v>
+        <v>1463</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IL Chicago</t>
+          <t>Yale</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1398,52 +1398,52 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G14" t="n">
-        <v>1521.6</v>
+        <v>1725.3</v>
       </c>
       <c r="H14" t="n">
-        <v>1.8755</v>
+        <v>1.115</v>
       </c>
       <c r="I14" t="n">
-        <v>107.6</v>
+        <v>120.83</v>
       </c>
       <c r="J14" t="n">
-        <v>103.45</v>
+        <v>108.5</v>
       </c>
       <c r="K14" t="n">
-        <v>4.15</v>
+        <v>12.33</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3478</v>
+        <v>0.2837</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1686</v>
+        <v>0.1401</v>
       </c>
       <c r="N14" t="n">
-        <v>10.4</v>
+        <v>4.2</v>
       </c>
       <c r="O14" t="n">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="P14" t="n">
-        <v>139</v>
+        <v>89</v>
       </c>
       <c r="Q14" t="n">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="R14" t="n">
-        <v>117</v>
+        <v>73</v>
       </c>
       <c r="S14" t="n">
-        <v>133</v>
+        <v>54</v>
       </c>
       <c r="T14" t="n">
-        <v>116</v>
+        <v>66</v>
       </c>
       <c r="U14" t="n">
-        <v>1504.2</v>
+        <v>1460.6</v>
       </c>
     </row>
     <row r="15">
@@ -2584,11 +2584,11 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1251</v>
+        <v>1372</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Liberty</t>
+          <t>SF Austin</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2605,61 +2605,61 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G31" t="n">
-        <v>1732.5</v>
+        <v>1563.2</v>
       </c>
       <c r="H31" t="n">
-        <v>3.2122</v>
+        <v>3.2331</v>
       </c>
       <c r="I31" t="n">
-        <v>117.41</v>
+        <v>113.58</v>
       </c>
       <c r="J31" t="n">
-        <v>110.66</v>
+        <v>98.86</v>
       </c>
       <c r="K31" t="n">
-        <v>6.75</v>
+        <v>14.72</v>
       </c>
       <c r="L31" t="n">
-        <v>0.1701</v>
+        <v>0.311</v>
       </c>
       <c r="M31" t="n">
-        <v>0.1316</v>
+        <v>0.1336</v>
       </c>
       <c r="N31" t="n">
-        <v>-6.2</v>
+        <v>7.6</v>
       </c>
       <c r="O31" t="n">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="P31" t="n">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="Q31" t="n">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="R31" t="n">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="S31" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="T31" t="n">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="U31" t="n">
-        <v>1483.4</v>
+        <v>1382.6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1465</v>
+        <v>1295</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cal Baptist</t>
+          <t>N Dakota St</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2679,58 +2679,58 @@
         <v>122</v>
       </c>
       <c r="G32" t="n">
-        <v>1592.1</v>
+        <v>1589.9</v>
       </c>
       <c r="H32" t="n">
-        <v>1.4758</v>
+        <v>3.844</v>
       </c>
       <c r="I32" t="n">
-        <v>107.02</v>
+        <v>114.57</v>
       </c>
       <c r="J32" t="n">
-        <v>98.72</v>
+        <v>103.26</v>
       </c>
       <c r="K32" t="n">
-        <v>8.300000000000001</v>
+        <v>11.31</v>
       </c>
       <c r="L32" t="n">
-        <v>0.3312</v>
+        <v>0.3149</v>
       </c>
       <c r="M32" t="n">
-        <v>0.1721</v>
+        <v>0.1499</v>
       </c>
       <c r="N32" t="n">
-        <v>8.4</v>
+        <v>13.2</v>
       </c>
       <c r="O32" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P32" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="Q32" t="n">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="R32" t="n">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="S32" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="T32" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="U32" t="n">
-        <v>1460.6</v>
+        <v>1412.7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1295</v>
+        <v>1133</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>N Dakota St</t>
+          <t>Bradley</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2747,52 +2747,52 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="G33" t="n">
-        <v>1589.9</v>
+        <v>1625.8</v>
       </c>
       <c r="H33" t="n">
-        <v>3.844</v>
+        <v>1.4157</v>
       </c>
       <c r="I33" t="n">
-        <v>114.57</v>
+        <v>111.03</v>
       </c>
       <c r="J33" t="n">
-        <v>103.26</v>
+        <v>106.13</v>
       </c>
       <c r="K33" t="n">
-        <v>11.31</v>
+        <v>4.91</v>
       </c>
       <c r="L33" t="n">
-        <v>0.3149</v>
+        <v>0.2732</v>
       </c>
       <c r="M33" t="n">
-        <v>0.1499</v>
+        <v>0.1331</v>
       </c>
       <c r="N33" t="n">
-        <v>13.2</v>
+        <v>3.8</v>
       </c>
       <c r="O33" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="P33" t="n">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="Q33" t="n">
-        <v>155</v>
+        <v>109</v>
       </c>
       <c r="R33" t="n">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="S33" t="n">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="T33" t="n">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="U33" t="n">
-        <v>1412.7</v>
+        <v>1527.8</v>
       </c>
     </row>
     <row r="34">
@@ -3862,11 +3862,11 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1219</v>
+        <v>1251</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>High Point</t>
+          <t>Liberty</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3883,52 +3883,52 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="G49" t="n">
-        <v>1623.3</v>
+        <v>1732.5</v>
       </c>
       <c r="H49" t="n">
-        <v>-1.5579</v>
+        <v>3.2122</v>
       </c>
       <c r="I49" t="n">
-        <v>121.64</v>
+        <v>117.41</v>
       </c>
       <c r="J49" t="n">
-        <v>100.61</v>
+        <v>110.66</v>
       </c>
       <c r="K49" t="n">
-        <v>21.04</v>
+        <v>6.75</v>
       </c>
       <c r="L49" t="n">
-        <v>0.3121</v>
+        <v>0.1701</v>
       </c>
       <c r="M49" t="n">
-        <v>0.1266</v>
+        <v>0.1316</v>
       </c>
       <c r="N49" t="n">
-        <v>16.8</v>
+        <v>-6.2</v>
       </c>
       <c r="O49" t="n">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="P49" t="n">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="Q49" t="n">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="R49" t="n">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="S49" t="n">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="T49" t="n">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="U49" t="n">
-        <v>1381.5</v>
+        <v>1483.4</v>
       </c>
     </row>
     <row r="50">
@@ -4998,11 +4998,11 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1463</v>
+        <v>1219</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Yale</t>
+          <t>High Point</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5019,61 +5019,61 @@
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G65" t="n">
-        <v>1725.3</v>
+        <v>1623.3</v>
       </c>
       <c r="H65" t="n">
-        <v>1.115</v>
+        <v>-1.5579</v>
       </c>
       <c r="I65" t="n">
-        <v>120.83</v>
+        <v>121.64</v>
       </c>
       <c r="J65" t="n">
-        <v>108.5</v>
+        <v>100.61</v>
       </c>
       <c r="K65" t="n">
-        <v>12.33</v>
+        <v>21.04</v>
       </c>
       <c r="L65" t="n">
-        <v>0.2837</v>
+        <v>0.3121</v>
       </c>
       <c r="M65" t="n">
-        <v>0.1401</v>
+        <v>0.1266</v>
       </c>
       <c r="N65" t="n">
-        <v>4.2</v>
+        <v>16.8</v>
       </c>
       <c r="O65" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="P65" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="Q65" t="n">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="R65" t="n">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="S65" t="n">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="T65" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="U65" t="n">
-        <v>1460.6</v>
+        <v>1381.5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1372</v>
+        <v>1465</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SF Austin</t>
+          <t>Cal Baptist</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5090,52 +5090,52 @@
         <v>0</v>
       </c>
       <c r="F66" t="n">
+        <v>122</v>
+      </c>
+      <c r="G66" t="n">
+        <v>1592.1</v>
+      </c>
+      <c r="H66" t="n">
+        <v>1.4758</v>
+      </c>
+      <c r="I66" t="n">
+        <v>107.02</v>
+      </c>
+      <c r="J66" t="n">
+        <v>98.72</v>
+      </c>
+      <c r="K66" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.1721</v>
+      </c>
+      <c r="N66" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="O66" t="n">
         <v>119</v>
       </c>
-      <c r="G66" t="n">
-        <v>1563.2</v>
-      </c>
-      <c r="H66" t="n">
-        <v>3.2331</v>
-      </c>
-      <c r="I66" t="n">
-        <v>113.58</v>
-      </c>
-      <c r="J66" t="n">
-        <v>98.86</v>
-      </c>
-      <c r="K66" t="n">
-        <v>14.72</v>
-      </c>
-      <c r="L66" t="n">
-        <v>0.311</v>
-      </c>
-      <c r="M66" t="n">
-        <v>0.1336</v>
-      </c>
-      <c r="N66" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="O66" t="n">
-        <v>88</v>
-      </c>
       <c r="P66" t="n">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="Q66" t="n">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="R66" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="S66" t="n">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="T66" t="n">
-        <v>85</v>
+        <v>111</v>
       </c>
       <c r="U66" t="n">
-        <v>1382.6</v>
+        <v>1460.6</v>
       </c>
     </row>
     <row r="67">

--- a/team_stats_2026.xlsx
+++ b/team_stats_2026.xlsx
@@ -549,10 +549,10 @@
         <v>119</v>
       </c>
       <c r="G2" t="n">
-        <v>2170.1</v>
+        <v>2179.5</v>
       </c>
       <c r="H2" t="n">
-        <v>3.9737</v>
+        <v>3.6659</v>
       </c>
       <c r="I2" t="n">
         <v>123.79</v>
@@ -591,7 +591,7 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>1690.2</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="3">
@@ -620,10 +620,10 @@
         <v>122</v>
       </c>
       <c r="G3" t="n">
-        <v>2051.5</v>
+        <v>2057.8</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5706</v>
+        <v>0.2001</v>
       </c>
       <c r="I3" t="n">
         <v>117.41</v>
@@ -662,7 +662,7 @@
         <v>11</v>
       </c>
       <c r="U3" t="n">
-        <v>1704.4</v>
+        <v>1707.1</v>
       </c>
     </row>
     <row r="4">
@@ -691,10 +691,10 @@
         <v>119</v>
       </c>
       <c r="G4" t="n">
-        <v>2030.1</v>
+        <v>2024.5</v>
       </c>
       <c r="H4" t="n">
-        <v>3.0314</v>
+        <v>3.6605</v>
       </c>
       <c r="I4" t="n">
         <v>118.09</v>
@@ -733,7 +733,7 @@
         <v>10</v>
       </c>
       <c r="U4" t="n">
-        <v>1692.3</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="5">
@@ -762,10 +762,10 @@
         <v>120</v>
       </c>
       <c r="G5" t="n">
-        <v>1966.5</v>
+        <v>1967.1</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.6248</v>
+        <v>-1.6145</v>
       </c>
       <c r="I5" t="n">
         <v>121.39</v>
@@ -836,7 +836,7 @@
         <v>1955.3</v>
       </c>
       <c r="H6" t="n">
-        <v>4.7636</v>
+        <v>5.539</v>
       </c>
       <c r="I6" t="n">
         <v>113.73</v>
@@ -875,7 +875,7 @@
         <v>22</v>
       </c>
       <c r="U6" t="n">
-        <v>1677.8</v>
+        <v>1679.7</v>
       </c>
     </row>
     <row r="7">
@@ -904,10 +904,10 @@
         <v>120</v>
       </c>
       <c r="G7" t="n">
-        <v>1893.4</v>
+        <v>1894.4</v>
       </c>
       <c r="H7" t="n">
-        <v>6.006</v>
+        <v>5.7232</v>
       </c>
       <c r="I7" t="n">
         <v>116.85</v>
@@ -975,10 +975,10 @@
         <v>121</v>
       </c>
       <c r="G8" t="n">
-        <v>1773.8</v>
+        <v>1775.8</v>
       </c>
       <c r="H8" t="n">
-        <v>12.7945</v>
+        <v>12.7773</v>
       </c>
       <c r="I8" t="n">
         <v>117.09</v>
@@ -1017,7 +1017,7 @@
         <v>30</v>
       </c>
       <c r="U8" t="n">
-        <v>1607.1</v>
+        <v>1609.3</v>
       </c>
     </row>
     <row r="9">
@@ -1046,10 +1046,10 @@
         <v>120</v>
       </c>
       <c r="G9" t="n">
-        <v>1864.3</v>
+        <v>1858.4</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3251</v>
+        <v>0.4232</v>
       </c>
       <c r="I9" t="n">
         <v>119.66</v>
@@ -1088,7 +1088,7 @@
         <v>26</v>
       </c>
       <c r="U9" t="n">
-        <v>1591.6</v>
+        <v>1589.9</v>
       </c>
     </row>
     <row r="10">
@@ -1117,10 +1117,10 @@
         <v>120</v>
       </c>
       <c r="G10" t="n">
-        <v>1842</v>
+        <v>1845.8</v>
       </c>
       <c r="H10" t="n">
-        <v>2.4672</v>
+        <v>2.0997</v>
       </c>
       <c r="I10" t="n">
         <v>116.51</v>
@@ -1159,7 +1159,7 @@
         <v>39</v>
       </c>
       <c r="U10" t="n">
-        <v>1687.7</v>
+        <v>1689.8</v>
       </c>
     </row>
     <row r="11">
@@ -1188,10 +1188,10 @@
         <v>120</v>
       </c>
       <c r="G11" t="n">
-        <v>1768.2</v>
+        <v>1767.4</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.8893</v>
+        <v>-2.184</v>
       </c>
       <c r="I11" t="n">
         <v>115.23</v>
@@ -1230,7 +1230,7 @@
         <v>53</v>
       </c>
       <c r="U11" t="n">
-        <v>1637.7</v>
+        <v>1638.6</v>
       </c>
     </row>
     <row r="12">
@@ -1259,10 +1259,10 @@
         <v>121</v>
       </c>
       <c r="G12" t="n">
-        <v>1753.7</v>
+        <v>1752.7</v>
       </c>
       <c r="H12" t="n">
-        <v>1.2979</v>
+        <v>1.268</v>
       </c>
       <c r="I12" t="n">
         <v>118.53</v>
@@ -1301,7 +1301,7 @@
         <v>36</v>
       </c>
       <c r="U12" t="n">
-        <v>1646.7</v>
+        <v>1646.2</v>
       </c>
     </row>
     <row r="13">
@@ -1330,10 +1330,10 @@
         <v>121</v>
       </c>
       <c r="G13" t="n">
-        <v>1752.7</v>
+        <v>1752.6</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.7312</v>
+        <v>-2.4765</v>
       </c>
       <c r="I13" t="n">
         <v>116.39</v>
@@ -1372,7 +1372,7 @@
         <v>41</v>
       </c>
       <c r="U13" t="n">
-        <v>1695.9</v>
+        <v>1696.5</v>
       </c>
     </row>
     <row r="14">
@@ -1401,10 +1401,10 @@
         <v>117</v>
       </c>
       <c r="G14" t="n">
-        <v>1725.3</v>
+        <v>1722.6</v>
       </c>
       <c r="H14" t="n">
-        <v>1.115</v>
+        <v>1.2386</v>
       </c>
       <c r="I14" t="n">
         <v>120.83</v>
@@ -1443,7 +1443,7 @@
         <v>66</v>
       </c>
       <c r="U14" t="n">
-        <v>1460.6</v>
+        <v>1460.4</v>
       </c>
     </row>
     <row r="15">
@@ -1472,10 +1472,10 @@
         <v>120</v>
       </c>
       <c r="G15" t="n">
-        <v>1685.2</v>
+        <v>1681</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8461</v>
+        <v>2.0383</v>
       </c>
       <c r="I15" t="n">
         <v>115.35</v>
@@ -1514,7 +1514,7 @@
         <v>93</v>
       </c>
       <c r="U15" t="n">
-        <v>1429.5</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="16">
@@ -1543,10 +1543,10 @@
         <v>116</v>
       </c>
       <c r="G16" t="n">
-        <v>1596.8</v>
+        <v>1593.7</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2901</v>
+        <v>1.3343</v>
       </c>
       <c r="I16" t="n">
         <v>112.11</v>
@@ -1585,7 +1585,7 @@
         <v>138</v>
       </c>
       <c r="U16" t="n">
-        <v>1465.3</v>
+        <v>1464.1</v>
       </c>
     </row>
     <row r="17">
@@ -1614,10 +1614,10 @@
         <v>121</v>
       </c>
       <c r="G17" t="n">
-        <v>1464</v>
+        <v>1464.5</v>
       </c>
       <c r="H17" t="n">
-        <v>2.7542</v>
+        <v>2.7711</v>
       </c>
       <c r="I17" t="n">
         <v>115.65</v>
@@ -1656,7 +1656,7 @@
         <v>140</v>
       </c>
       <c r="U17" t="n">
-        <v>1435.2</v>
+        <v>1435.1</v>
       </c>
     </row>
     <row r="18">
@@ -1688,7 +1688,7 @@
         <v>1365</v>
       </c>
       <c r="H18" t="n">
-        <v>3.1006</v>
+        <v>3.0881</v>
       </c>
       <c r="I18" t="n">
         <v>111.58</v>
@@ -1727,7 +1727,7 @@
         <v>164</v>
       </c>
       <c r="U18" t="n">
-        <v>1443.1</v>
+        <v>1443.7</v>
       </c>
     </row>
     <row r="19">
@@ -1756,10 +1756,10 @@
         <v>117</v>
       </c>
       <c r="G19" t="n">
-        <v>2083.8</v>
+        <v>2092.8</v>
       </c>
       <c r="H19" t="n">
-        <v>9.8756</v>
+        <v>9.4907</v>
       </c>
       <c r="I19" t="n">
         <v>117.38</v>
@@ -1798,7 +1798,7 @@
         <v>8</v>
       </c>
       <c r="U19" t="n">
-        <v>1664.7</v>
+        <v>1667.4</v>
       </c>
     </row>
     <row r="20">
@@ -1827,10 +1827,10 @@
         <v>120</v>
       </c>
       <c r="G20" t="n">
-        <v>1993.6</v>
+        <v>2002.2</v>
       </c>
       <c r="H20" t="n">
-        <v>4.3059</v>
+        <v>2.5717</v>
       </c>
       <c r="I20" t="n">
         <v>121.4</v>
@@ -1869,7 +1869,7 @@
         <v>4</v>
       </c>
       <c r="U20" t="n">
-        <v>1699.9</v>
+        <v>1700.4</v>
       </c>
     </row>
     <row r="21">
@@ -1898,10 +1898,10 @@
         <v>121</v>
       </c>
       <c r="G21" t="n">
-        <v>1976</v>
+        <v>1978.1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8268</v>
+        <v>0.7736</v>
       </c>
       <c r="I21" t="n">
         <v>123.88</v>
@@ -1940,7 +1940,7 @@
         <v>9</v>
       </c>
       <c r="U21" t="n">
-        <v>1740.2</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="22">
@@ -1969,10 +1969,10 @@
         <v>120</v>
       </c>
       <c r="G22" t="n">
-        <v>1951.2</v>
+        <v>1951.6</v>
       </c>
       <c r="H22" t="n">
-        <v>13.9718</v>
+        <v>14.014</v>
       </c>
       <c r="I22" t="n">
         <v>118.9</v>
@@ -2011,7 +2011,7 @@
         <v>14</v>
       </c>
       <c r="U22" t="n">
-        <v>1635.2</v>
+        <v>1635.8</v>
       </c>
     </row>
     <row r="23">
@@ -2040,10 +2040,10 @@
         <v>120</v>
       </c>
       <c r="G23" t="n">
-        <v>1912.8</v>
+        <v>1915.6</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.7463</v>
+        <v>-1.8805</v>
       </c>
       <c r="I23" t="n">
         <v>117.37</v>
@@ -2082,7 +2082,7 @@
         <v>20</v>
       </c>
       <c r="U23" t="n">
-        <v>1692.2</v>
+        <v>1693.7</v>
       </c>
     </row>
     <row r="24">
@@ -2111,10 +2111,10 @@
         <v>120</v>
       </c>
       <c r="G24" t="n">
-        <v>1830.2</v>
+        <v>1830.4</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.7351</v>
+        <v>-3.0745</v>
       </c>
       <c r="I24" t="n">
         <v>119.03</v>
@@ -2153,7 +2153,7 @@
         <v>17</v>
       </c>
       <c r="U24" t="n">
-        <v>1675</v>
+        <v>1677.2</v>
       </c>
     </row>
     <row r="25">
@@ -2182,10 +2182,10 @@
         <v>121</v>
       </c>
       <c r="G25" t="n">
-        <v>1820.1</v>
+        <v>1821.5</v>
       </c>
       <c r="H25" t="n">
-        <v>6.5295</v>
+        <v>6.4146</v>
       </c>
       <c r="I25" t="n">
         <v>114.74</v>
@@ -2224,7 +2224,7 @@
         <v>33</v>
       </c>
       <c r="U25" t="n">
-        <v>1643.5</v>
+        <v>1645.7</v>
       </c>
     </row>
     <row r="26">
@@ -2253,10 +2253,10 @@
         <v>121</v>
       </c>
       <c r="G26" t="n">
-        <v>1825.9</v>
+        <v>1824.5</v>
       </c>
       <c r="H26" t="n">
-        <v>10.4518</v>
+        <v>10.3996</v>
       </c>
       <c r="I26" t="n">
         <v>122</v>
@@ -2295,7 +2295,7 @@
         <v>24</v>
       </c>
       <c r="U26" t="n">
-        <v>1501.8</v>
+        <v>1501.2</v>
       </c>
     </row>
     <row r="27">
@@ -2324,10 +2324,10 @@
         <v>122</v>
       </c>
       <c r="G27" t="n">
-        <v>1849.8</v>
+        <v>1851.2</v>
       </c>
       <c r="H27" t="n">
-        <v>4.4435</v>
+        <v>4.4379</v>
       </c>
       <c r="I27" t="n">
         <v>119.28</v>
@@ -2366,7 +2366,7 @@
         <v>28</v>
       </c>
       <c r="U27" t="n">
-        <v>1706.7</v>
+        <v>1708.5</v>
       </c>
     </row>
     <row r="28">
@@ -2395,10 +2395,10 @@
         <v>120</v>
       </c>
       <c r="G28" t="n">
-        <v>1836.9</v>
+        <v>1835.2</v>
       </c>
       <c r="H28" t="n">
-        <v>4.4256</v>
+        <v>4.7779</v>
       </c>
       <c r="I28" t="n">
         <v>118.62</v>
@@ -2466,10 +2466,10 @@
         <v>117</v>
       </c>
       <c r="G29" t="n">
-        <v>1765.3</v>
+        <v>1765.9</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.5462</v>
+        <v>-0.7176</v>
       </c>
       <c r="I29" t="n">
         <v>117.4</v>
@@ -2508,7 +2508,7 @@
         <v>40</v>
       </c>
       <c r="U29" t="n">
-        <v>1571</v>
+        <v>1571.8</v>
       </c>
     </row>
     <row r="30">
@@ -2537,10 +2537,10 @@
         <v>121</v>
       </c>
       <c r="G30" t="n">
-        <v>1825.3</v>
+        <v>1822.6</v>
       </c>
       <c r="H30" t="n">
-        <v>4.1386</v>
+        <v>3.8299</v>
       </c>
       <c r="I30" t="n">
         <v>114.16</v>
@@ -2579,7 +2579,7 @@
         <v>42</v>
       </c>
       <c r="U30" t="n">
-        <v>1590</v>
+        <v>1587.8</v>
       </c>
     </row>
     <row r="31">
@@ -2611,7 +2611,7 @@
         <v>1563.2</v>
       </c>
       <c r="H31" t="n">
-        <v>3.2331</v>
+        <v>3.2741</v>
       </c>
       <c r="I31" t="n">
         <v>113.58</v>
@@ -2650,7 +2650,7 @@
         <v>85</v>
       </c>
       <c r="U31" t="n">
-        <v>1382.6</v>
+        <v>1383.2</v>
       </c>
     </row>
     <row r="32">
@@ -2679,10 +2679,10 @@
         <v>122</v>
       </c>
       <c r="G32" t="n">
-        <v>1589.9</v>
+        <v>1589</v>
       </c>
       <c r="H32" t="n">
-        <v>3.844</v>
+        <v>3.8176</v>
       </c>
       <c r="I32" t="n">
         <v>114.57</v>
@@ -2721,7 +2721,7 @@
         <v>117</v>
       </c>
       <c r="U32" t="n">
-        <v>1412.7</v>
+        <v>1412.3</v>
       </c>
     </row>
     <row r="33">
@@ -2750,10 +2750,10 @@
         <v>118</v>
       </c>
       <c r="G33" t="n">
-        <v>1625.8</v>
+        <v>1623.6</v>
       </c>
       <c r="H33" t="n">
-        <v>1.4157</v>
+        <v>1.3833</v>
       </c>
       <c r="I33" t="n">
         <v>111.03</v>
@@ -2792,7 +2792,7 @@
         <v>112</v>
       </c>
       <c r="U33" t="n">
-        <v>1527.8</v>
+        <v>1526.1</v>
       </c>
     </row>
     <row r="34">
@@ -2821,10 +2821,10 @@
         <v>118</v>
       </c>
       <c r="G34" t="n">
-        <v>1512.4</v>
+        <v>1513.3</v>
       </c>
       <c r="H34" t="n">
-        <v>3.91</v>
+        <v>3.9468</v>
       </c>
       <c r="I34" t="n">
         <v>107.55</v>
@@ -2863,7 +2863,7 @@
         <v>185</v>
       </c>
       <c r="U34" t="n">
-        <v>1452.7</v>
+        <v>1455.1</v>
       </c>
     </row>
     <row r="35">
@@ -2892,10 +2892,10 @@
         <v>117</v>
       </c>
       <c r="G35" t="n">
-        <v>1459.3</v>
+        <v>1458.8</v>
       </c>
       <c r="H35" t="n">
-        <v>3.6053</v>
+        <v>3.5917</v>
       </c>
       <c r="I35" t="n">
         <v>108.6</v>
@@ -2934,7 +2934,7 @@
         <v>191</v>
       </c>
       <c r="U35" t="n">
-        <v>1406.8</v>
+        <v>1406.4</v>
       </c>
     </row>
     <row r="36">
@@ -2963,10 +2963,10 @@
         <v>121</v>
       </c>
       <c r="G36" t="n">
-        <v>1414.1</v>
+        <v>1414.4</v>
       </c>
       <c r="H36" t="n">
-        <v>2.4721</v>
+        <v>2.4583</v>
       </c>
       <c r="I36" t="n">
         <v>109.35</v>
@@ -3005,7 +3005,7 @@
         <v>195</v>
       </c>
       <c r="U36" t="n">
-        <v>1378.7</v>
+        <v>1378.6</v>
       </c>
     </row>
     <row r="37">
@@ -3034,10 +3034,10 @@
         <v>122</v>
       </c>
       <c r="G37" t="n">
-        <v>2172.4</v>
+        <v>2181.2</v>
       </c>
       <c r="H37" t="n">
-        <v>8.183400000000001</v>
+        <v>7.6139</v>
       </c>
       <c r="I37" t="n">
         <v>121.54</v>
@@ -3076,7 +3076,7 @@
         <v>2</v>
       </c>
       <c r="U37" t="n">
-        <v>1756.1</v>
+        <v>1758.2</v>
       </c>
     </row>
     <row r="38">
@@ -3105,10 +3105,10 @@
         <v>121</v>
       </c>
       <c r="G38" t="n">
-        <v>2085.1</v>
+        <v>2099.2</v>
       </c>
       <c r="H38" t="n">
-        <v>2.67</v>
+        <v>1.9173</v>
       </c>
       <c r="I38" t="n">
         <v>117.81</v>
@@ -3147,7 +3147,7 @@
         <v>7</v>
       </c>
       <c r="U38" t="n">
-        <v>1703.4</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="39">
@@ -3176,10 +3176,10 @@
         <v>120</v>
       </c>
       <c r="G39" t="n">
-        <v>1990.6</v>
+        <v>1992.1</v>
       </c>
       <c r="H39" t="n">
-        <v>11.3442</v>
+        <v>11.5554</v>
       </c>
       <c r="I39" t="n">
         <v>115.07</v>
@@ -3218,7 +3218,7 @@
         <v>12</v>
       </c>
       <c r="U39" t="n">
-        <v>1658</v>
+        <v>1659.3</v>
       </c>
     </row>
     <row r="40">
@@ -3247,10 +3247,10 @@
         <v>120</v>
       </c>
       <c r="G40" t="n">
-        <v>1972.3</v>
+        <v>1971.6</v>
       </c>
       <c r="H40" t="n">
-        <v>11.3738</v>
+        <v>11.9283</v>
       </c>
       <c r="I40" t="n">
         <v>110.16</v>
@@ -3289,7 +3289,7 @@
         <v>15</v>
       </c>
       <c r="U40" t="n">
-        <v>1777.3</v>
+        <v>1779.6</v>
       </c>
     </row>
     <row r="41">
@@ -3318,10 +3318,10 @@
         <v>121</v>
       </c>
       <c r="G41" t="n">
-        <v>1932.7</v>
+        <v>1940.1</v>
       </c>
       <c r="H41" t="n">
-        <v>6.7834</v>
+        <v>5.7735</v>
       </c>
       <c r="I41" t="n">
         <v>123.18</v>
@@ -3360,7 +3360,7 @@
         <v>19</v>
       </c>
       <c r="U41" t="n">
-        <v>1725.9</v>
+        <v>1727.6</v>
       </c>
     </row>
     <row r="42">
@@ -3389,10 +3389,10 @@
         <v>120</v>
       </c>
       <c r="G42" t="n">
-        <v>1921</v>
+        <v>1918.7</v>
       </c>
       <c r="H42" t="n">
-        <v>1.9274</v>
+        <v>2.6895</v>
       </c>
       <c r="I42" t="n">
         <v>121.87</v>
@@ -3431,7 +3431,7 @@
         <v>18</v>
       </c>
       <c r="U42" t="n">
-        <v>1684</v>
+        <v>1684.4</v>
       </c>
     </row>
     <row r="43">
@@ -3463,7 +3463,7 @@
         <v>1877.4</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.2467</v>
+        <v>-0.5286</v>
       </c>
       <c r="I43" t="n">
         <v>118.87</v>
@@ -3502,7 +3502,7 @@
         <v>21</v>
       </c>
       <c r="U43" t="n">
-        <v>1595.8</v>
+        <v>1595.3</v>
       </c>
     </row>
     <row r="44">
@@ -3531,10 +3531,10 @@
         <v>120</v>
       </c>
       <c r="G44" t="n">
-        <v>1839.7</v>
+        <v>1836.4</v>
       </c>
       <c r="H44" t="n">
-        <v>3.0742</v>
+        <v>3.8425</v>
       </c>
       <c r="I44" t="n">
         <v>112.26</v>
@@ -3573,7 +3573,7 @@
         <v>35</v>
       </c>
       <c r="U44" t="n">
-        <v>1652.1</v>
+        <v>1652.4</v>
       </c>
     </row>
     <row r="45">
@@ -3602,10 +3602,10 @@
         <v>120</v>
       </c>
       <c r="G45" t="n">
-        <v>1839.8</v>
+        <v>1838.2</v>
       </c>
       <c r="H45" t="n">
-        <v>7.5365</v>
+        <v>7.6713</v>
       </c>
       <c r="I45" t="n">
         <v>115.83</v>
@@ -3644,7 +3644,7 @@
         <v>46</v>
       </c>
       <c r="U45" t="n">
-        <v>1687.9</v>
+        <v>1687.7</v>
       </c>
     </row>
     <row r="46">
@@ -3673,10 +3673,10 @@
         <v>121</v>
       </c>
       <c r="G46" t="n">
-        <v>1787.4</v>
+        <v>1789.2</v>
       </c>
       <c r="H46" t="n">
-        <v>1.3307</v>
+        <v>1.4042</v>
       </c>
       <c r="I46" t="n">
         <v>118.28</v>
@@ -3715,7 +3715,7 @@
         <v>34</v>
       </c>
       <c r="U46" t="n">
-        <v>1694.2</v>
+        <v>1696.1</v>
       </c>
     </row>
     <row r="47">
@@ -3744,10 +3744,10 @@
         <v>120</v>
       </c>
       <c r="G47" t="n">
-        <v>1772.7</v>
+        <v>1771.7</v>
       </c>
       <c r="H47" t="n">
-        <v>9.988799999999999</v>
+        <v>9.957599999999999</v>
       </c>
       <c r="I47" t="n">
         <v>120.02</v>
@@ -3786,7 +3786,7 @@
         <v>52</v>
       </c>
       <c r="U47" t="n">
-        <v>1413.1</v>
+        <v>1412.7</v>
       </c>
     </row>
     <row r="48">
@@ -3815,10 +3815,10 @@
         <v>122</v>
       </c>
       <c r="G48" t="n">
-        <v>1713.4</v>
+        <v>1709.5</v>
       </c>
       <c r="H48" t="n">
-        <v>9.475099999999999</v>
+        <v>9.3651</v>
       </c>
       <c r="I48" t="n">
         <v>115.67</v>
@@ -3857,7 +3857,7 @@
         <v>48</v>
       </c>
       <c r="U48" t="n">
-        <v>1560.8</v>
+        <v>1558.8</v>
       </c>
     </row>
     <row r="49">
@@ -3886,10 +3886,10 @@
         <v>122</v>
       </c>
       <c r="G49" t="n">
-        <v>1732.5</v>
+        <v>1729</v>
       </c>
       <c r="H49" t="n">
-        <v>3.2122</v>
+        <v>3.4996</v>
       </c>
       <c r="I49" t="n">
         <v>117.41</v>
@@ -3928,7 +3928,7 @@
         <v>94</v>
       </c>
       <c r="U49" t="n">
-        <v>1483.4</v>
+        <v>1482.9</v>
       </c>
     </row>
     <row r="50">
@@ -3957,10 +3957,10 @@
         <v>122</v>
       </c>
       <c r="G50" t="n">
-        <v>1430.5</v>
+        <v>1430.4</v>
       </c>
       <c r="H50" t="n">
-        <v>3.2584</v>
+        <v>3.2549</v>
       </c>
       <c r="I50" t="n">
         <v>113.28</v>
@@ -3999,7 +3999,7 @@
         <v>127</v>
       </c>
       <c r="U50" t="n">
-        <v>1375.7</v>
+        <v>1375.2</v>
       </c>
     </row>
     <row r="51">
@@ -4028,10 +4028,10 @@
         <v>117</v>
       </c>
       <c r="G51" t="n">
-        <v>1515</v>
+        <v>1514.8</v>
       </c>
       <c r="H51" t="n">
-        <v>0.5934</v>
+        <v>0.598</v>
       </c>
       <c r="I51" t="n">
         <v>116.43</v>
@@ -4070,7 +4070,7 @@
         <v>128</v>
       </c>
       <c r="U51" t="n">
-        <v>1424.7</v>
+        <v>1424.6</v>
       </c>
     </row>
     <row r="52">
@@ -4099,10 +4099,10 @@
         <v>122</v>
       </c>
       <c r="G52" t="n">
-        <v>1410.9</v>
+        <v>1409</v>
       </c>
       <c r="H52" t="n">
-        <v>3.2396</v>
+        <v>3.2279</v>
       </c>
       <c r="I52" t="n">
         <v>109.08</v>
@@ -4141,7 +4141,7 @@
         <v>202</v>
       </c>
       <c r="U52" t="n">
-        <v>1380.9</v>
+        <v>1380.6</v>
       </c>
     </row>
     <row r="53">
@@ -4170,10 +4170,10 @@
         <v>122</v>
       </c>
       <c r="G53" t="n">
-        <v>1375.9</v>
+        <v>1375.4</v>
       </c>
       <c r="H53" t="n">
-        <v>0.9186</v>
+        <v>0.9205</v>
       </c>
       <c r="I53" t="n">
         <v>104.96</v>
@@ -4212,7 +4212,7 @@
         <v>246</v>
       </c>
       <c r="U53" t="n">
-        <v>1436.2</v>
+        <v>1436.6</v>
       </c>
     </row>
     <row r="54">
@@ -4241,10 +4241,10 @@
         <v>119</v>
       </c>
       <c r="G54" t="n">
-        <v>2242.8</v>
+        <v>2252.6</v>
       </c>
       <c r="H54" t="n">
-        <v>8.6394</v>
+        <v>8.169700000000001</v>
       </c>
       <c r="I54" t="n">
         <v>120.84</v>
@@ -4283,7 +4283,7 @@
         <v>3</v>
       </c>
       <c r="U54" t="n">
-        <v>1747.2</v>
+        <v>1751.1</v>
       </c>
     </row>
     <row r="55">
@@ -4312,10 +4312,10 @@
         <v>120</v>
       </c>
       <c r="G55" t="n">
-        <v>1996.4</v>
+        <v>1999.8</v>
       </c>
       <c r="H55" t="n">
-        <v>8.884600000000001</v>
+        <v>8.6837</v>
       </c>
       <c r="I55" t="n">
         <v>125.29</v>
@@ -4354,7 +4354,7 @@
         <v>5</v>
       </c>
       <c r="U55" t="n">
-        <v>1710.4</v>
+        <v>1712.9</v>
       </c>
     </row>
     <row r="56">
@@ -4383,10 +4383,10 @@
         <v>117</v>
       </c>
       <c r="G56" t="n">
-        <v>2055.1</v>
+        <v>2061.6</v>
       </c>
       <c r="H56" t="n">
-        <v>6.9647</v>
+        <v>6.7538</v>
       </c>
       <c r="I56" t="n">
         <v>120.35</v>
@@ -4425,7 +4425,7 @@
         <v>6</v>
       </c>
       <c r="U56" t="n">
-        <v>1597.1</v>
+        <v>1597.9</v>
       </c>
     </row>
     <row r="57">
@@ -4454,10 +4454,10 @@
         <v>120</v>
       </c>
       <c r="G57" t="n">
-        <v>2034.5</v>
+        <v>2044.2</v>
       </c>
       <c r="H57" t="n">
-        <v>11.3167</v>
+        <v>10.5951</v>
       </c>
       <c r="I57" t="n">
         <v>118.24</v>
@@ -4496,7 +4496,7 @@
         <v>13</v>
       </c>
       <c r="U57" t="n">
-        <v>1753.9</v>
+        <v>1756.8</v>
       </c>
     </row>
     <row r="58">
@@ -4525,10 +4525,10 @@
         <v>120</v>
       </c>
       <c r="G58" t="n">
-        <v>1921.2</v>
+        <v>1921.9</v>
       </c>
       <c r="H58" t="n">
-        <v>2.4067</v>
+        <v>2.4321</v>
       </c>
       <c r="I58" t="n">
         <v>115.82</v>
@@ -4567,7 +4567,7 @@
         <v>25</v>
       </c>
       <c r="U58" t="n">
-        <v>1655.5</v>
+        <v>1655.6</v>
       </c>
     </row>
     <row r="59">
@@ -4596,10 +4596,10 @@
         <v>121</v>
       </c>
       <c r="G59" t="n">
-        <v>1837.7</v>
+        <v>1837</v>
       </c>
       <c r="H59" t="n">
-        <v>0.7673</v>
+        <v>1.4688</v>
       </c>
       <c r="I59" t="n">
         <v>118.38</v>
@@ -4638,7 +4638,7 @@
         <v>32</v>
       </c>
       <c r="U59" t="n">
-        <v>1686</v>
+        <v>1688.3</v>
       </c>
     </row>
     <row r="60">
@@ -4667,10 +4667,10 @@
         <v>120</v>
       </c>
       <c r="G60" t="n">
-        <v>1901.3</v>
+        <v>1905.8</v>
       </c>
       <c r="H60" t="n">
-        <v>2.827</v>
+        <v>2.2762</v>
       </c>
       <c r="I60" t="n">
         <v>117.49</v>
@@ -4709,7 +4709,7 @@
         <v>23</v>
       </c>
       <c r="U60" t="n">
-        <v>1712.1</v>
+        <v>1713.1</v>
       </c>
     </row>
     <row r="61">
@@ -4738,10 +4738,10 @@
         <v>120</v>
       </c>
       <c r="G61" t="n">
-        <v>1810.7</v>
+        <v>1808.8</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.8284</v>
+        <v>0.1677</v>
       </c>
       <c r="I61" t="n">
         <v>120.8</v>
@@ -4780,7 +4780,7 @@
         <v>31</v>
       </c>
       <c r="U61" t="n">
-        <v>1647.3</v>
+        <v>1648.7</v>
       </c>
     </row>
     <row r="62">
@@ -4809,10 +4809,10 @@
         <v>119</v>
       </c>
       <c r="G62" t="n">
-        <v>1751.4</v>
+        <v>1751.7</v>
       </c>
       <c r="H62" t="n">
-        <v>8.2582</v>
+        <v>8.052099999999999</v>
       </c>
       <c r="I62" t="n">
         <v>118.51</v>
@@ -4851,7 +4851,7 @@
         <v>29</v>
       </c>
       <c r="U62" t="n">
-        <v>1678.8</v>
+        <v>1678.3</v>
       </c>
     </row>
     <row r="63">
@@ -4880,10 +4880,10 @@
         <v>120</v>
       </c>
       <c r="G63" t="n">
-        <v>1824.2</v>
+        <v>1827.5</v>
       </c>
       <c r="H63" t="n">
-        <v>6.8019</v>
+        <v>6.8987</v>
       </c>
       <c r="I63" t="n">
         <v>110.58</v>
@@ -4922,7 +4922,7 @@
         <v>45</v>
       </c>
       <c r="U63" t="n">
-        <v>1678</v>
+        <v>1681.1</v>
       </c>
     </row>
     <row r="64">
@@ -4951,10 +4951,10 @@
         <v>121</v>
       </c>
       <c r="G64" t="n">
-        <v>1777.5</v>
+        <v>1775.6</v>
       </c>
       <c r="H64" t="n">
-        <v>2.2904</v>
+        <v>2.7602</v>
       </c>
       <c r="I64" t="n">
         <v>120.67</v>
@@ -4993,7 +4993,7 @@
         <v>37</v>
       </c>
       <c r="U64" t="n">
-        <v>1700.7</v>
+        <v>1702.7</v>
       </c>
     </row>
     <row r="65">
@@ -5022,10 +5022,10 @@
         <v>115</v>
       </c>
       <c r="G65" t="n">
-        <v>1623.3</v>
+        <v>1620.8</v>
       </c>
       <c r="H65" t="n">
-        <v>-1.5579</v>
+        <v>-1.4038</v>
       </c>
       <c r="I65" t="n">
         <v>121.64</v>
@@ -5093,10 +5093,10 @@
         <v>122</v>
       </c>
       <c r="G66" t="n">
-        <v>1592.1</v>
+        <v>1592.3</v>
       </c>
       <c r="H66" t="n">
-        <v>1.4758</v>
+        <v>1.4889</v>
       </c>
       <c r="I66" t="n">
         <v>107.02</v>
@@ -5135,7 +5135,7 @@
         <v>111</v>
       </c>
       <c r="U66" t="n">
-        <v>1460.6</v>
+        <v>1460.9</v>
       </c>
     </row>
     <row r="67">
@@ -5164,10 +5164,10 @@
         <v>122</v>
       </c>
       <c r="G67" t="n">
-        <v>1611.8</v>
+        <v>1610.8</v>
       </c>
       <c r="H67" t="n">
-        <v>2.2597</v>
+        <v>2.2236</v>
       </c>
       <c r="I67" t="n">
         <v>103.83</v>
@@ -5206,7 +5206,7 @@
         <v>119</v>
       </c>
       <c r="U67" t="n">
-        <v>1470.9</v>
+        <v>1470.2</v>
       </c>
     </row>
     <row r="68">
@@ -5235,10 +5235,10 @@
         <v>119</v>
       </c>
       <c r="G68" t="n">
-        <v>1458.6</v>
+        <v>1458.3</v>
       </c>
       <c r="H68" t="n">
-        <v>2.1359</v>
+        <v>2.128</v>
       </c>
       <c r="I68" t="n">
         <v>105.36</v>
@@ -5277,7 +5277,7 @@
         <v>151</v>
       </c>
       <c r="U68" t="n">
-        <v>1417.2</v>
+        <v>1416.6</v>
       </c>
     </row>
     <row r="69">
@@ -5306,10 +5306,10 @@
         <v>120</v>
       </c>
       <c r="G69" t="n">
-        <v>1390.3</v>
+        <v>1390.2</v>
       </c>
       <c r="H69" t="n">
-        <v>1.1323</v>
+        <v>1.1316</v>
       </c>
       <c r="I69" t="n">
         <v>111.8</v>
@@ -5348,7 +5348,7 @@
         <v>223</v>
       </c>
       <c r="U69" t="n">
-        <v>1368.2</v>
+        <v>1368.1</v>
       </c>
     </row>
   </sheetData>

--- a/team_stats_2026.xlsx
+++ b/team_stats_2026.xlsx
@@ -830,31 +830,31 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G6" t="n">
-        <v>1955.3</v>
+        <v>1961.4</v>
       </c>
       <c r="H6" t="n">
-        <v>5.539</v>
+        <v>5.5897</v>
       </c>
       <c r="I6" t="n">
-        <v>113.73</v>
+        <v>113.79</v>
       </c>
       <c r="J6" t="n">
-        <v>98.58</v>
+        <v>98.7</v>
       </c>
       <c r="K6" t="n">
-        <v>15.15</v>
+        <v>15.09</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3268</v>
+        <v>0.3238</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1411</v>
+        <v>0.1418</v>
       </c>
       <c r="N6" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="O6" t="n">
         <v>21</v>
@@ -875,7 +875,7 @@
         <v>22</v>
       </c>
       <c r="U6" t="n">
-        <v>1679.7</v>
+        <v>1680.5</v>
       </c>
     </row>
     <row r="7">
@@ -1682,31 +1682,31 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="G18" t="n">
-        <v>1365</v>
+        <v>1367.1</v>
       </c>
       <c r="H18" t="n">
-        <v>3.0881</v>
+        <v>3.1055</v>
       </c>
       <c r="I18" t="n">
-        <v>111.58</v>
+        <v>112.58</v>
       </c>
       <c r="J18" t="n">
-        <v>106.54</v>
+        <v>106.89</v>
       </c>
       <c r="K18" t="n">
-        <v>5.04</v>
+        <v>5.69</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2727</v>
+        <v>0.2722</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1498</v>
+        <v>0.151</v>
       </c>
       <c r="N18" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="O18" t="n">
         <v>154</v>
@@ -1727,7 +1727,7 @@
         <v>164</v>
       </c>
       <c r="U18" t="n">
-        <v>1443.7</v>
+        <v>1437.1</v>
       </c>
     </row>
     <row r="19">
@@ -2747,31 +2747,31 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="G33" t="n">
-        <v>1623.6</v>
+        <v>1627.7</v>
       </c>
       <c r="H33" t="n">
-        <v>1.3833</v>
+        <v>1.2831</v>
       </c>
       <c r="I33" t="n">
-        <v>111.03</v>
+        <v>110.42</v>
       </c>
       <c r="J33" t="n">
-        <v>106.13</v>
+        <v>105.54</v>
       </c>
       <c r="K33" t="n">
-        <v>4.91</v>
+        <v>4.88</v>
       </c>
       <c r="L33" t="n">
         <v>0.2732</v>
       </c>
       <c r="M33" t="n">
-        <v>0.1331</v>
+        <v>0.1327</v>
       </c>
       <c r="N33" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="O33" t="n">
         <v>123</v>
@@ -2792,7 +2792,7 @@
         <v>112</v>
       </c>
       <c r="U33" t="n">
-        <v>1526.1</v>
+        <v>1522.2</v>
       </c>
     </row>
     <row r="34">
@@ -2818,31 +2818,31 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="G34" t="n">
-        <v>1513.3</v>
+        <v>1515.6</v>
       </c>
       <c r="H34" t="n">
-        <v>3.9468</v>
+        <v>3.9427</v>
       </c>
       <c r="I34" t="n">
-        <v>107.55</v>
+        <v>107.67</v>
       </c>
       <c r="J34" t="n">
-        <v>104.05</v>
+        <v>102.86</v>
       </c>
       <c r="K34" t="n">
-        <v>3.5</v>
+        <v>4.81</v>
       </c>
       <c r="L34" t="n">
-        <v>0.2641</v>
+        <v>0.2665</v>
       </c>
       <c r="M34" t="n">
-        <v>0.144</v>
+        <v>0.1436</v>
       </c>
       <c r="N34" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="O34" t="n">
         <v>172</v>
@@ -2863,7 +2863,7 @@
         <v>185</v>
       </c>
       <c r="U34" t="n">
-        <v>1455.1</v>
+        <v>1452.7</v>
       </c>
     </row>
     <row r="35">
@@ -2889,31 +2889,31 @@
         <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="G35" t="n">
-        <v>1458.8</v>
+        <v>1463.5</v>
       </c>
       <c r="H35" t="n">
-        <v>3.5917</v>
+        <v>3.459</v>
       </c>
       <c r="I35" t="n">
-        <v>108.6</v>
+        <v>108.83</v>
       </c>
       <c r="J35" t="n">
-        <v>103.65</v>
+        <v>103.43</v>
       </c>
       <c r="K35" t="n">
-        <v>4.95</v>
+        <v>5.39</v>
       </c>
       <c r="L35" t="n">
-        <v>0.3274</v>
+        <v>0.3286</v>
       </c>
       <c r="M35" t="n">
-        <v>0.1566</v>
+        <v>0.1601</v>
       </c>
       <c r="N35" t="n">
-        <v>12.2</v>
+        <v>16.4</v>
       </c>
       <c r="O35" t="n">
         <v>207</v>
@@ -2934,7 +2934,7 @@
         <v>191</v>
       </c>
       <c r="U35" t="n">
-        <v>1406.4</v>
+        <v>1408.1</v>
       </c>
     </row>
     <row r="36">
@@ -3599,31 +3599,31 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G45" t="n">
-        <v>1838.2</v>
+        <v>1820.5</v>
       </c>
       <c r="H45" t="n">
-        <v>7.6713</v>
+        <v>7.025</v>
       </c>
       <c r="I45" t="n">
-        <v>115.83</v>
+        <v>114.77</v>
       </c>
       <c r="J45" t="n">
-        <v>110.45</v>
+        <v>110.49</v>
       </c>
       <c r="K45" t="n">
-        <v>5.38</v>
+        <v>4.28</v>
       </c>
       <c r="L45" t="n">
-        <v>0.3093</v>
+        <v>0.3115</v>
       </c>
       <c r="M45" t="n">
-        <v>0.1541</v>
+        <v>0.1546</v>
       </c>
       <c r="N45" t="n">
-        <v>3.6</v>
+        <v>-1.6</v>
       </c>
       <c r="O45" t="n">
         <v>48</v>
@@ -3644,7 +3644,7 @@
         <v>46</v>
       </c>
       <c r="U45" t="n">
-        <v>1687.7</v>
+        <v>1687.9</v>
       </c>
     </row>
     <row r="46">
@@ -3741,31 +3741,31 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G47" t="n">
-        <v>1771.7</v>
+        <v>1775.2</v>
       </c>
       <c r="H47" t="n">
-        <v>9.957599999999999</v>
+        <v>9.651999999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>120.02</v>
+        <v>120.89</v>
       </c>
       <c r="J47" t="n">
-        <v>103.88</v>
+        <v>105.23</v>
       </c>
       <c r="K47" t="n">
-        <v>16.14</v>
+        <v>15.66</v>
       </c>
       <c r="L47" t="n">
-        <v>0.2071</v>
+        <v>0.2107</v>
       </c>
       <c r="M47" t="n">
-        <v>0.1427</v>
+        <v>0.1402</v>
       </c>
       <c r="N47" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="O47" t="n">
         <v>87</v>
@@ -3786,7 +3786,7 @@
         <v>52</v>
       </c>
       <c r="U47" t="n">
-        <v>1412.7</v>
+        <v>1414.6</v>
       </c>
     </row>
     <row r="48">
@@ -5019,31 +5019,31 @@
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G65" t="n">
-        <v>1620.8</v>
+        <v>1618</v>
       </c>
       <c r="H65" t="n">
-        <v>-1.4038</v>
+        <v>-1.2011</v>
       </c>
       <c r="I65" t="n">
-        <v>121.64</v>
+        <v>121.43</v>
       </c>
       <c r="J65" t="n">
-        <v>100.61</v>
+        <v>99.78</v>
       </c>
       <c r="K65" t="n">
-        <v>21.04</v>
+        <v>21.65</v>
       </c>
       <c r="L65" t="n">
-        <v>0.3121</v>
+        <v>0.3136</v>
       </c>
       <c r="M65" t="n">
-        <v>0.1266</v>
+        <v>0.1281</v>
       </c>
       <c r="N65" t="n">
-        <v>16.8</v>
+        <v>16.2</v>
       </c>
       <c r="O65" t="n">
         <v>91</v>
@@ -5064,7 +5064,7 @@
         <v>76</v>
       </c>
       <c r="U65" t="n">
-        <v>1381.5</v>
+        <v>1375.9</v>
       </c>
     </row>
     <row r="66">

--- a/team_stats_2026.xlsx
+++ b/team_stats_2026.xlsx
@@ -546,31 +546,31 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="G2" t="n">
-        <v>2179.5</v>
+        <v>2183.9</v>
       </c>
       <c r="H2" t="n">
-        <v>3.6659</v>
+        <v>3.6873</v>
       </c>
       <c r="I2" t="n">
-        <v>123.79</v>
+        <v>123.11</v>
       </c>
       <c r="J2" t="n">
-        <v>93.15000000000001</v>
+        <v>93.04000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>30.64</v>
+        <v>30.07</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2823</v>
+        <v>0.2884</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1519</v>
+        <v>0.1511</v>
       </c>
       <c r="N2" t="n">
-        <v>28.2</v>
+        <v>23.8</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -591,7 +591,7 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>1692</v>
+        <v>1701.5</v>
       </c>
     </row>
     <row r="3">
@@ -688,31 +688,31 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="G4" t="n">
-        <v>2024.5</v>
+        <v>2027.4</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6605</v>
+        <v>3.1622</v>
       </c>
       <c r="I4" t="n">
-        <v>118.09</v>
+        <v>118.43</v>
       </c>
       <c r="J4" t="n">
-        <v>96.43000000000001</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>21.66</v>
+        <v>22.42</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3174</v>
+        <v>0.3184</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1477</v>
+        <v>0.1465</v>
       </c>
       <c r="N4" t="n">
-        <v>-3.2</v>
+        <v>0.4</v>
       </c>
       <c r="O4" t="n">
         <v>7</v>
@@ -733,7 +733,7 @@
         <v>10</v>
       </c>
       <c r="U4" t="n">
-        <v>1693</v>
+        <v>1686.9</v>
       </c>
     </row>
     <row r="5">
@@ -759,31 +759,31 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G5" t="n">
-        <v>1967.1</v>
+        <v>1975.1</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.6145</v>
+        <v>-1.4869</v>
       </c>
       <c r="I5" t="n">
-        <v>121.39</v>
+        <v>122.11</v>
       </c>
       <c r="J5" t="n">
-        <v>110.58</v>
+        <v>110.78</v>
       </c>
       <c r="K5" t="n">
-        <v>10.81</v>
+        <v>11.33</v>
       </c>
       <c r="L5" t="n">
-        <v>0.279</v>
+        <v>0.2853</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1296</v>
+        <v>0.1289</v>
       </c>
       <c r="N5" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="O5" t="n">
         <v>15</v>
@@ -804,7 +804,7 @@
         <v>16</v>
       </c>
       <c r="U5" t="n">
-        <v>1769.4</v>
+        <v>1772.1</v>
       </c>
     </row>
     <row r="6">
@@ -880,11 +880,11 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1246</v>
+        <v>1458</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -901,61 +901,61 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G7" t="n">
-        <v>1894.4</v>
+        <v>1859.5</v>
       </c>
       <c r="H7" t="n">
-        <v>5.7232</v>
+        <v>1.6302</v>
       </c>
       <c r="I7" t="n">
-        <v>116.85</v>
+        <v>119.64</v>
       </c>
       <c r="J7" t="n">
-        <v>105.78</v>
+        <v>108.42</v>
       </c>
       <c r="K7" t="n">
-        <v>11.07</v>
+        <v>11.21</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3101</v>
+        <v>0.276</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1466</v>
+        <v>0.1244</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6</v>
+        <v>10.6</v>
       </c>
       <c r="O7" t="n">
+        <v>30</v>
+      </c>
+      <c r="P7" t="n">
         <v>25</v>
       </c>
-      <c r="P7" t="n">
-        <v>22</v>
-      </c>
       <c r="Q7" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="R7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S7" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T7" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="U7" t="n">
-        <v>1717.2</v>
+        <v>1701.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1274</v>
+        <v>1437</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Miami FL</t>
+          <t>Villanova</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -972,52 +972,52 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G8" t="n">
-        <v>1775.8</v>
+        <v>1825.7</v>
       </c>
       <c r="H8" t="n">
-        <v>12.7773</v>
+        <v>6.1267</v>
       </c>
       <c r="I8" t="n">
-        <v>117.09</v>
+        <v>115.45</v>
       </c>
       <c r="J8" t="n">
-        <v>99.90000000000001</v>
+        <v>104.42</v>
       </c>
       <c r="K8" t="n">
-        <v>17.19</v>
+        <v>11.03</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3061</v>
+        <v>0.3111</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1624</v>
+        <v>0.1421</v>
       </c>
       <c r="N8" t="n">
-        <v>7.6</v>
+        <v>-0.2</v>
       </c>
       <c r="O8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P8" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="Q8" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="R8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="S8" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T8" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="U8" t="n">
-        <v>1609.3</v>
+        <v>1644.1</v>
       </c>
     </row>
     <row r="9">
@@ -1043,31 +1043,31 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G9" t="n">
-        <v>1858.4</v>
+        <v>1869.8</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4232</v>
+        <v>0.2419</v>
       </c>
       <c r="I9" t="n">
-        <v>119.66</v>
+        <v>120.49</v>
       </c>
       <c r="J9" t="n">
-        <v>104.27</v>
+        <v>105.01</v>
       </c>
       <c r="K9" t="n">
-        <v>15.38</v>
+        <v>15.48</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3059</v>
+        <v>0.3065</v>
       </c>
       <c r="M9" t="n">
         <v>0.1487</v>
       </c>
       <c r="N9" t="n">
-        <v>-4.6</v>
+        <v>-7.6</v>
       </c>
       <c r="O9" t="n">
         <v>26</v>
@@ -1088,16 +1088,16 @@
         <v>26</v>
       </c>
       <c r="U9" t="n">
-        <v>1589.9</v>
+        <v>1599.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1417</v>
+        <v>1234</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UCLA</t>
+          <t>Iowa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1114,52 +1114,52 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G10" t="n">
-        <v>1845.8</v>
+        <v>1851.2</v>
       </c>
       <c r="H10" t="n">
-        <v>2.0997</v>
+        <v>4.4379</v>
       </c>
       <c r="I10" t="n">
-        <v>116.51</v>
+        <v>119.28</v>
       </c>
       <c r="J10" t="n">
-        <v>106.69</v>
+        <v>103.76</v>
       </c>
       <c r="K10" t="n">
-        <v>9.82</v>
+        <v>15.52</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2986</v>
+        <v>0.2925</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1302</v>
+        <v>0.1388</v>
       </c>
       <c r="N10" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="O10" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="P10" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="Q10" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="R10" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="S10" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="T10" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="U10" t="n">
-        <v>1689.8</v>
+        <v>1708.5</v>
       </c>
     </row>
     <row r="11">
@@ -1185,31 +1185,31 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G11" t="n">
-        <v>1767.4</v>
+        <v>1757.5</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.184</v>
+        <v>-1.923</v>
       </c>
       <c r="I11" t="n">
-        <v>115.23</v>
+        <v>115.19</v>
       </c>
       <c r="J11" t="n">
-        <v>109.22</v>
+        <v>109.25</v>
       </c>
       <c r="K11" t="n">
-        <v>6.01</v>
+        <v>5.95</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3029</v>
+        <v>0.3014</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1713</v>
+        <v>0.1701</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>47</v>
@@ -1230,16 +1230,16 @@
         <v>53</v>
       </c>
       <c r="U11" t="n">
-        <v>1638.6</v>
+        <v>1651.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1374</v>
+        <v>1365</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SMU</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1256,61 +1256,61 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G12" t="n">
-        <v>1752.7</v>
+        <v>1765.9</v>
       </c>
       <c r="H12" t="n">
-        <v>1.268</v>
+        <v>-0.7176</v>
       </c>
       <c r="I12" t="n">
-        <v>118.53</v>
+        <v>117.4</v>
       </c>
       <c r="J12" t="n">
-        <v>109.67</v>
+        <v>102.2</v>
       </c>
       <c r="K12" t="n">
-        <v>8.859999999999999</v>
+        <v>15.2</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3029</v>
+        <v>0.3448</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1516</v>
+        <v>0.1494</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4</v>
+        <v>5.4</v>
       </c>
       <c r="O12" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P12" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q12" t="n">
         <v>45</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>37</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>36</v>
       </c>
-      <c r="S12" t="n">
-        <v>38</v>
-      </c>
       <c r="T12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="U12" t="n">
-        <v>1646.2</v>
+        <v>1571.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1231</v>
+        <v>1374</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Indiana</t>
+          <t>SMU</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1327,52 +1327,52 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G13" t="n">
-        <v>1752.6</v>
+        <v>1738.3</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.4765</v>
+        <v>0.9109</v>
       </c>
       <c r="I13" t="n">
-        <v>116.39</v>
+        <v>118.28</v>
       </c>
       <c r="J13" t="n">
-        <v>106.14</v>
+        <v>110.33</v>
       </c>
       <c r="K13" t="n">
-        <v>10.26</v>
+        <v>7.95</v>
       </c>
       <c r="L13" t="n">
-        <v>0.234</v>
+        <v>0.3064</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1415</v>
+        <v>0.1528</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.2</v>
+        <v>-4.2</v>
       </c>
       <c r="O13" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="P13" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q13" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="R13" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="S13" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="T13" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="U13" t="n">
-        <v>1696.5</v>
+        <v>1643.1</v>
       </c>
     </row>
     <row r="14">
@@ -1398,31 +1398,31 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="G14" t="n">
-        <v>1722.6</v>
+        <v>1720.2</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2386</v>
+        <v>1.1161</v>
       </c>
       <c r="I14" t="n">
-        <v>120.83</v>
+        <v>120.93</v>
       </c>
       <c r="J14" t="n">
-        <v>108.5</v>
+        <v>107.17</v>
       </c>
       <c r="K14" t="n">
-        <v>12.33</v>
+        <v>13.77</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2837</v>
+        <v>0.2847</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1401</v>
+        <v>0.1362</v>
       </c>
       <c r="N14" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="O14" t="n">
         <v>81</v>
@@ -1443,16 +1443,16 @@
         <v>66</v>
       </c>
       <c r="U14" t="n">
-        <v>1460.4</v>
+        <v>1457.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1423</v>
+        <v>1372</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>UNC Wilmington</t>
+          <t>SF Austin</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1469,52 +1469,52 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G15" t="n">
-        <v>1681</v>
+        <v>1563.2</v>
       </c>
       <c r="H15" t="n">
-        <v>2.0383</v>
+        <v>3.2741</v>
       </c>
       <c r="I15" t="n">
-        <v>115.35</v>
+        <v>113.58</v>
       </c>
       <c r="J15" t="n">
-        <v>102.31</v>
+        <v>98.86</v>
       </c>
       <c r="K15" t="n">
-        <v>13.04</v>
+        <v>14.72</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3159</v>
+        <v>0.311</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1414</v>
+        <v>0.1336</v>
       </c>
       <c r="N15" t="n">
-        <v>10.8</v>
+        <v>7.6</v>
       </c>
       <c r="O15" t="n">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="P15" t="n">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="Q15" t="n">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="R15" t="n">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="S15" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T15" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="U15" t="n">
-        <v>1429</v>
+        <v>1383.2</v>
       </c>
     </row>
     <row r="16">
@@ -1661,11 +1661,11 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1146</v>
+        <v>1398</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cent Arkansas</t>
+          <t>Tennessee St</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1682,61 +1682,61 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G18" t="n">
-        <v>1367.1</v>
+        <v>1466.9</v>
       </c>
       <c r="H18" t="n">
-        <v>3.1055</v>
+        <v>3.3618</v>
       </c>
       <c r="I18" t="n">
-        <v>112.58</v>
+        <v>109.9</v>
       </c>
       <c r="J18" t="n">
-        <v>106.89</v>
+        <v>103.28</v>
       </c>
       <c r="K18" t="n">
-        <v>5.69</v>
+        <v>6.62</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2722</v>
+        <v>0.328</v>
       </c>
       <c r="M18" t="n">
-        <v>0.151</v>
+        <v>0.1589</v>
       </c>
       <c r="N18" t="n">
-        <v>6.2</v>
+        <v>19.8</v>
       </c>
       <c r="O18" t="n">
-        <v>154</v>
+        <v>207</v>
       </c>
       <c r="P18" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q18" t="n">
-        <v>140</v>
+        <v>196</v>
       </c>
       <c r="R18" t="n">
-        <v>147</v>
+        <v>182</v>
       </c>
       <c r="S18" t="n">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="T18" t="n">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="U18" t="n">
-        <v>1437.1</v>
+        <v>1407.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1163</v>
+        <v>1196</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Connecticut</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1753,61 +1753,61 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="G19" t="n">
-        <v>2092.8</v>
+        <v>2014.8</v>
       </c>
       <c r="H19" t="n">
-        <v>9.4907</v>
+        <v>2.8716</v>
       </c>
       <c r="I19" t="n">
-        <v>117.38</v>
+        <v>120.95</v>
       </c>
       <c r="J19" t="n">
-        <v>97.34999999999999</v>
+        <v>99.02</v>
       </c>
       <c r="K19" t="n">
-        <v>20.03</v>
+        <v>21.92</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2903</v>
+        <v>0.3329</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1532</v>
+        <v>0.1552</v>
       </c>
       <c r="N19" t="n">
-        <v>8.6</v>
+        <v>21.4</v>
       </c>
       <c r="O19" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="P19" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q19" t="n">
         <v>4</v>
       </c>
-      <c r="Q19" t="n">
-        <v>16</v>
-      </c>
       <c r="R19" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="S19" t="n">
+        <v>11</v>
+      </c>
+      <c r="T19" t="n">
         <v>4</v>
       </c>
-      <c r="T19" t="n">
-        <v>8</v>
-      </c>
       <c r="U19" t="n">
-        <v>1667.4</v>
+        <v>1709.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1196</v>
+        <v>1222</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1824,61 +1824,61 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G20" t="n">
-        <v>2002.2</v>
+        <v>2102.9</v>
       </c>
       <c r="H20" t="n">
-        <v>2.5717</v>
+        <v>1.6401</v>
       </c>
       <c r="I20" t="n">
-        <v>121.4</v>
+        <v>117.95</v>
       </c>
       <c r="J20" t="n">
-        <v>98.63</v>
+        <v>95.43000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>22.77</v>
+        <v>22.51</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3333</v>
+        <v>0.3379</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1547</v>
+        <v>0.1199</v>
       </c>
       <c r="N20" t="n">
-        <v>22.8</v>
+        <v>8</v>
       </c>
       <c r="O20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S20" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T20" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U20" t="n">
-        <v>1700.4</v>
+        <v>1706.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1345</v>
+        <v>1304</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Purdue</t>
+          <t>Nebraska</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1895,61 +1895,61 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G21" t="n">
-        <v>1978.1</v>
+        <v>1992.1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7736</v>
+        <v>11.5554</v>
       </c>
       <c r="I21" t="n">
-        <v>123.88</v>
+        <v>115.07</v>
       </c>
       <c r="J21" t="n">
-        <v>105.93</v>
+        <v>98.04000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>17.95</v>
+        <v>17.03</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2977</v>
+        <v>0.2419</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1374</v>
+        <v>0.1401</v>
       </c>
       <c r="N21" t="n">
-        <v>2.4</v>
+        <v>5.2</v>
       </c>
       <c r="O21" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P21" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q21" t="n">
         <v>12</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
+        <v>12</v>
+      </c>
+      <c r="S21" t="n">
         <v>9</v>
       </c>
-      <c r="R21" t="n">
-        <v>8</v>
-      </c>
-      <c r="S21" t="n">
-        <v>7</v>
-      </c>
       <c r="T21" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="U21" t="n">
-        <v>1741</v>
+        <v>1659.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1438</v>
+        <v>1242</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1966,61 +1966,61 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G22" t="n">
-        <v>1951.6</v>
+        <v>1973.7</v>
       </c>
       <c r="H22" t="n">
-        <v>14.014</v>
+        <v>11.337</v>
       </c>
       <c r="I22" t="n">
-        <v>118.9</v>
+        <v>111.61</v>
       </c>
       <c r="J22" t="n">
-        <v>99.7</v>
+        <v>100.9</v>
       </c>
       <c r="K22" t="n">
-        <v>19.2</v>
+        <v>10.71</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3157</v>
+        <v>0.2487</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1519</v>
+        <v>0.1523</v>
       </c>
       <c r="N22" t="n">
-        <v>7.4</v>
+        <v>-3.4</v>
       </c>
       <c r="O22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P22" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q22" t="n">
         <v>19</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>15</v>
       </c>
-      <c r="R22" t="n">
-        <v>18</v>
-      </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U22" t="n">
-        <v>1635.8</v>
+        <v>1772.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1397</v>
+        <v>1116</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2037,52 +2037,52 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G23" t="n">
-        <v>1915.6</v>
+        <v>1950</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.8805</v>
+        <v>5.5428</v>
       </c>
       <c r="I23" t="n">
-        <v>117.37</v>
+        <v>122.85</v>
       </c>
       <c r="J23" t="n">
-        <v>101.08</v>
+        <v>108.88</v>
       </c>
       <c r="K23" t="n">
-        <v>16.3</v>
+        <v>13.96</v>
       </c>
       <c r="L23" t="n">
-        <v>0.3535</v>
+        <v>0.3009</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1667</v>
+        <v>0.1205</v>
       </c>
       <c r="N23" t="n">
-        <v>8</v>
+        <v>2.6</v>
       </c>
       <c r="O23" t="n">
+        <v>20</v>
+      </c>
+      <c r="P23" t="n">
         <v>18</v>
       </c>
-      <c r="P23" t="n">
-        <v>16</v>
-      </c>
       <c r="Q23" t="n">
+        <v>24</v>
+      </c>
+      <c r="R23" t="n">
+        <v>19</v>
+      </c>
+      <c r="S23" t="n">
         <v>20</v>
       </c>
-      <c r="R23" t="n">
-        <v>20</v>
-      </c>
-      <c r="S23" t="n">
-        <v>24</v>
-      </c>
       <c r="T23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="U23" t="n">
-        <v>1693.7</v>
+        <v>1728.7</v>
       </c>
     </row>
     <row r="24">
@@ -2108,31 +2108,31 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G24" t="n">
-        <v>1830.4</v>
+        <v>1845.2</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.0745</v>
+        <v>-2.9919</v>
       </c>
       <c r="I24" t="n">
-        <v>119.03</v>
+        <v>120.19</v>
       </c>
       <c r="J24" t="n">
-        <v>100.17</v>
+        <v>101.95</v>
       </c>
       <c r="K24" t="n">
-        <v>18.86</v>
+        <v>18.24</v>
       </c>
       <c r="L24" t="n">
-        <v>0.29</v>
+        <v>0.2897</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1596</v>
+        <v>0.1578</v>
       </c>
       <c r="N24" t="n">
-        <v>2.8</v>
+        <v>5.4</v>
       </c>
       <c r="O24" t="n">
         <v>19</v>
@@ -2153,16 +2153,16 @@
         <v>17</v>
       </c>
       <c r="U24" t="n">
-        <v>1677.2</v>
+        <v>1682.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1437</v>
+        <v>1388</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Villanova</t>
+          <t>St Mary's CA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2179,61 +2179,61 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G25" t="n">
-        <v>1821.5</v>
+        <v>1877.4</v>
       </c>
       <c r="H25" t="n">
-        <v>6.4146</v>
+        <v>-0.5286</v>
       </c>
       <c r="I25" t="n">
-        <v>114.74</v>
+        <v>118.87</v>
       </c>
       <c r="J25" t="n">
-        <v>103.88</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>10.87</v>
+        <v>20.05</v>
       </c>
       <c r="L25" t="n">
-        <v>0.3148</v>
+        <v>0.2966</v>
       </c>
       <c r="M25" t="n">
-        <v>0.141</v>
+        <v>0.1557</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.2</v>
+        <v>11.8</v>
       </c>
       <c r="O25" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="P25" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Q25" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="R25" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="T25" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="U25" t="n">
-        <v>1645.7</v>
+        <v>1595.3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1387</v>
+        <v>1274</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>St Louis</t>
+          <t>Miami FL</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2250,61 +2250,61 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G26" t="n">
-        <v>1824.5</v>
+        <v>1761</v>
       </c>
       <c r="H26" t="n">
-        <v>10.3996</v>
+        <v>12.4806</v>
       </c>
       <c r="I26" t="n">
-        <v>122</v>
+        <v>118.15</v>
       </c>
       <c r="J26" t="n">
-        <v>96.95</v>
+        <v>101.88</v>
       </c>
       <c r="K26" t="n">
-        <v>25.05</v>
+        <v>16.27</v>
       </c>
       <c r="L26" t="n">
-        <v>0.2326</v>
+        <v>0.3077</v>
       </c>
       <c r="M26" t="n">
-        <v>0.167</v>
+        <v>0.1596</v>
       </c>
       <c r="N26" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="O26" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="P26" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Q26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R26" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="S26" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="T26" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="U26" t="n">
-        <v>1501.2</v>
+        <v>1617.1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1234</v>
+        <v>1326</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Iowa</t>
+          <t>Ohio St</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2321,61 +2321,61 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G27" t="n">
-        <v>1851.2</v>
+        <v>1799.9</v>
       </c>
       <c r="H27" t="n">
-        <v>4.4379</v>
+        <v>1.5472</v>
       </c>
       <c r="I27" t="n">
-        <v>119.28</v>
+        <v>118.74</v>
       </c>
       <c r="J27" t="n">
-        <v>103.76</v>
+        <v>107.91</v>
       </c>
       <c r="K27" t="n">
-        <v>15.52</v>
+        <v>10.83</v>
       </c>
       <c r="L27" t="n">
-        <v>0.2925</v>
+        <v>0.2524</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1388</v>
+        <v>0.1503</v>
       </c>
       <c r="N27" t="n">
-        <v>0.8</v>
+        <v>6</v>
       </c>
       <c r="O27" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="P27" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="Q27" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="R27" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="S27" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="T27" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="U27" t="n">
-        <v>1708.5</v>
+        <v>1700.1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Texas A&amp;M</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2392,61 +2392,61 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G28" t="n">
-        <v>1835.2</v>
+        <v>1757.7</v>
       </c>
       <c r="H28" t="n">
-        <v>4.7779</v>
+        <v>2.865</v>
       </c>
       <c r="I28" t="n">
-        <v>118.62</v>
+        <v>120.37</v>
       </c>
       <c r="J28" t="n">
-        <v>106.73</v>
+        <v>111.34</v>
       </c>
       <c r="K28" t="n">
-        <v>11.89</v>
+        <v>9.02</v>
       </c>
       <c r="L28" t="n">
-        <v>0.3028</v>
+        <v>0.3098</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1406</v>
+        <v>0.1494</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.6</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="O28" t="n">
+        <v>29</v>
+      </c>
+      <c r="P28" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>34</v>
+      </c>
+      <c r="R28" t="n">
         <v>38</v>
       </c>
-      <c r="P28" t="n">
-        <v>34</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>36</v>
-      </c>
-      <c r="R28" t="n">
-        <v>39</v>
-      </c>
       <c r="S28" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="T28" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="U28" t="n">
-        <v>1655.1</v>
+        <v>1699.4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1365</v>
+        <v>1416</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>UCF</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2456,68 +2456,68 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>11a</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="G29" t="n">
-        <v>1765.9</v>
+        <v>1820.5</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.7176</v>
+        <v>7.025</v>
       </c>
       <c r="I29" t="n">
-        <v>117.4</v>
+        <v>114.77</v>
       </c>
       <c r="J29" t="n">
-        <v>102.2</v>
+        <v>110.49</v>
       </c>
       <c r="K29" t="n">
-        <v>15.2</v>
+        <v>4.28</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3448</v>
+        <v>0.3115</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1494</v>
+        <v>0.1546</v>
       </c>
       <c r="N29" t="n">
-        <v>5.4</v>
+        <v>-1.6</v>
       </c>
       <c r="O29" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="P29" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="Q29" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="R29" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="S29" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="T29" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="U29" t="n">
-        <v>1571.8</v>
+        <v>1687.9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1307</v>
+        <v>1378</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>New Mexico</t>
+          <t>South Florida</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2527,68 +2527,68 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>11b</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G30" t="n">
-        <v>1822.6</v>
+        <v>1709.5</v>
       </c>
       <c r="H30" t="n">
-        <v>3.8299</v>
+        <v>9.3651</v>
       </c>
       <c r="I30" t="n">
-        <v>114.16</v>
+        <v>115.67</v>
       </c>
       <c r="J30" t="n">
-        <v>101.47</v>
+        <v>102.39</v>
       </c>
       <c r="K30" t="n">
-        <v>12.7</v>
+        <v>13.28</v>
       </c>
       <c r="L30" t="n">
-        <v>0.2721</v>
+        <v>0.336</v>
       </c>
       <c r="M30" t="n">
-        <v>0.1448</v>
+        <v>0.1478</v>
       </c>
       <c r="N30" t="n">
-        <v>5.8</v>
+        <v>15.4</v>
       </c>
       <c r="O30" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="P30" t="n">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="Q30" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="R30" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="S30" t="n">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="T30" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="U30" t="n">
-        <v>1587.8</v>
+        <v>1558.8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1372</v>
+        <v>1423</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SF Austin</t>
+          <t>UNC Wilmington</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2598,68 +2598,68 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E31" t="b">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G31" t="n">
-        <v>1563.2</v>
+        <v>1681</v>
       </c>
       <c r="H31" t="n">
-        <v>3.2741</v>
+        <v>2.0383</v>
       </c>
       <c r="I31" t="n">
-        <v>113.58</v>
+        <v>115.35</v>
       </c>
       <c r="J31" t="n">
-        <v>98.86</v>
+        <v>102.31</v>
       </c>
       <c r="K31" t="n">
-        <v>14.72</v>
+        <v>13.04</v>
       </c>
       <c r="L31" t="n">
-        <v>0.311</v>
+        <v>0.3159</v>
       </c>
       <c r="M31" t="n">
-        <v>0.1336</v>
+        <v>0.1414</v>
       </c>
       <c r="N31" t="n">
-        <v>7.6</v>
+        <v>10.8</v>
       </c>
       <c r="O31" t="n">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="P31" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="Q31" t="n">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="R31" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="S31" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T31" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="U31" t="n">
-        <v>1383.2</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1295</v>
+        <v>1190</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>N Dakota St</t>
+          <t>ETSU</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2669,68 +2669,68 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E32" t="b">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G32" t="n">
-        <v>1589</v>
+        <v>1515.6</v>
       </c>
       <c r="H32" t="n">
-        <v>3.8176</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>114.57</v>
+        <v>116.98</v>
       </c>
       <c r="J32" t="n">
-        <v>103.26</v>
+        <v>105.72</v>
       </c>
       <c r="K32" t="n">
-        <v>11.31</v>
+        <v>11.26</v>
       </c>
       <c r="L32" t="n">
-        <v>0.3149</v>
+        <v>0.2696</v>
       </c>
       <c r="M32" t="n">
-        <v>0.1499</v>
+        <v>0.1444</v>
       </c>
       <c r="N32" t="n">
-        <v>13.2</v>
+        <v>3.8</v>
       </c>
       <c r="O32" t="n">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="P32" t="n">
-        <v>121</v>
+        <v>149</v>
       </c>
       <c r="Q32" t="n">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="R32" t="n">
+        <v>136</v>
+      </c>
+      <c r="S32" t="n">
+        <v>151</v>
+      </c>
+      <c r="T32" t="n">
         <v>128</v>
       </c>
-      <c r="S32" t="n">
-        <v>94</v>
-      </c>
-      <c r="T32" t="n">
-        <v>117</v>
-      </c>
       <c r="U32" t="n">
-        <v>1412.3</v>
+        <v>1416.1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1133</v>
+        <v>1146</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bradley</t>
+          <t>Cent Arkansas</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2740,68 +2740,68 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E33" t="b">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G33" t="n">
-        <v>1627.7</v>
+        <v>1369.9</v>
       </c>
       <c r="H33" t="n">
-        <v>1.2831</v>
+        <v>3.1128</v>
       </c>
       <c r="I33" t="n">
-        <v>110.42</v>
+        <v>112.04</v>
       </c>
       <c r="J33" t="n">
-        <v>105.54</v>
+        <v>106.14</v>
       </c>
       <c r="K33" t="n">
-        <v>4.88</v>
+        <v>5.91</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2732</v>
+        <v>0.271</v>
       </c>
       <c r="M33" t="n">
-        <v>0.1327</v>
+        <v>0.1505</v>
       </c>
       <c r="N33" t="n">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="O33" t="n">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="P33" t="n">
-        <v>107</v>
+        <v>197</v>
       </c>
       <c r="Q33" t="n">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="R33" t="n">
-        <v>109</v>
+        <v>147</v>
       </c>
       <c r="S33" t="n">
-        <v>108</v>
+        <v>162</v>
       </c>
       <c r="T33" t="n">
-        <v>112</v>
+        <v>164</v>
       </c>
       <c r="U33" t="n">
-        <v>1522.2</v>
+        <v>1437.1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1467</v>
+        <v>1224</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Merrimack</t>
+          <t>Howard</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2811,68 +2811,68 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16a</t>
         </is>
       </c>
       <c r="E34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G34" t="n">
-        <v>1515.6</v>
+        <v>1409</v>
       </c>
       <c r="H34" t="n">
-        <v>3.9427</v>
+        <v>3.2279</v>
       </c>
       <c r="I34" t="n">
-        <v>107.67</v>
+        <v>109.08</v>
       </c>
       <c r="J34" t="n">
-        <v>102.86</v>
+        <v>98.81</v>
       </c>
       <c r="K34" t="n">
-        <v>4.81</v>
+        <v>10.27</v>
       </c>
       <c r="L34" t="n">
-        <v>0.2665</v>
+        <v>0.3126</v>
       </c>
       <c r="M34" t="n">
-        <v>0.1436</v>
+        <v>0.1855</v>
       </c>
       <c r="N34" t="n">
-        <v>6.6</v>
+        <v>23.6</v>
       </c>
       <c r="O34" t="n">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="P34" t="n">
-        <v>172</v>
+        <v>260</v>
       </c>
       <c r="Q34" t="n">
-        <v>192</v>
+        <v>277</v>
       </c>
       <c r="R34" t="n">
-        <v>158</v>
+        <v>196</v>
       </c>
       <c r="S34" t="n">
-        <v>119</v>
+        <v>237</v>
       </c>
       <c r="T34" t="n">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="U34" t="n">
-        <v>1452.7</v>
+        <v>1380.6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1398</v>
+        <v>1126</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tennessee St</t>
+          <t>Bethune-Cookman</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2882,139 +2882,139 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>16a</t>
+          <t>16b</t>
         </is>
       </c>
       <c r="E35" t="b">
         <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G35" t="n">
-        <v>1463.5</v>
+        <v>1375.4</v>
       </c>
       <c r="H35" t="n">
-        <v>3.459</v>
+        <v>0.9205</v>
       </c>
       <c r="I35" t="n">
-        <v>108.83</v>
+        <v>104.96</v>
       </c>
       <c r="J35" t="n">
-        <v>103.43</v>
+        <v>108.7</v>
       </c>
       <c r="K35" t="n">
-        <v>5.39</v>
+        <v>-3.74</v>
       </c>
       <c r="L35" t="n">
-        <v>0.3286</v>
+        <v>0.2778</v>
       </c>
       <c r="M35" t="n">
-        <v>0.1601</v>
+        <v>0.1862</v>
       </c>
       <c r="N35" t="n">
-        <v>16.4</v>
+        <v>4.8</v>
       </c>
       <c r="O35" t="n">
-        <v>207</v>
+        <v>233</v>
       </c>
       <c r="P35" t="n">
-        <v>199</v>
+        <v>267</v>
       </c>
       <c r="Q35" t="n">
-        <v>196</v>
+        <v>256</v>
       </c>
       <c r="R35" t="n">
-        <v>182</v>
+        <v>208</v>
       </c>
       <c r="S35" t="n">
-        <v>184</v>
+        <v>224</v>
       </c>
       <c r="T35" t="n">
-        <v>191</v>
+        <v>246</v>
       </c>
       <c r="U35" t="n">
-        <v>1408.1</v>
+        <v>1436.6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1254</v>
+        <v>1276</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LIU Brooklyn</t>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>MW</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>16b</t>
+          <t>01</t>
         </is>
       </c>
       <c r="E36" t="b">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>122</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2181.2</v>
+      </c>
+      <c r="H36" t="n">
+        <v>7.6139</v>
+      </c>
+      <c r="I36" t="n">
+        <v>121.54</v>
+      </c>
+      <c r="J36" t="n">
+        <v>95.23</v>
+      </c>
+      <c r="K36" t="n">
+        <v>26.31</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.2642</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.1678</v>
+      </c>
+      <c r="N36" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O36" t="n">
+        <v>2</v>
+      </c>
+      <c r="P36" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q36" t="n">
         <v>1</v>
       </c>
-      <c r="F36" t="n">
-        <v>121</v>
-      </c>
-      <c r="G36" t="n">
-        <v>1414.4</v>
-      </c>
-      <c r="H36" t="n">
-        <v>2.4583</v>
-      </c>
-      <c r="I36" t="n">
-        <v>109.35</v>
-      </c>
-      <c r="J36" t="n">
-        <v>104.93</v>
-      </c>
-      <c r="K36" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0.1885</v>
-      </c>
-      <c r="N36" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O36" t="n">
-        <v>210</v>
-      </c>
-      <c r="P36" t="n">
-        <v>228</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>211</v>
-      </c>
       <c r="R36" t="n">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="S36" t="n">
-        <v>173</v>
+        <v>3</v>
       </c>
       <c r="T36" t="n">
-        <v>195</v>
+        <v>2</v>
       </c>
       <c r="U36" t="n">
-        <v>1378.6</v>
+        <v>1758.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1276</v>
+        <v>1163</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Connecticut</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3024,68 +3024,68 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="E37" t="b">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G37" t="n">
-        <v>2181.2</v>
+        <v>2064.2</v>
       </c>
       <c r="H37" t="n">
-        <v>7.6139</v>
+        <v>8.950200000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>121.54</v>
+        <v>116.34</v>
       </c>
       <c r="J37" t="n">
-        <v>95.23</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>26.31</v>
+        <v>18.93</v>
       </c>
       <c r="L37" t="n">
-        <v>0.2642</v>
+        <v>0.2937</v>
       </c>
       <c r="M37" t="n">
-        <v>0.1678</v>
+        <v>0.1558</v>
       </c>
       <c r="N37" t="n">
         <v>6.6</v>
       </c>
       <c r="O37" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="P37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="R37" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T37" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U37" t="n">
-        <v>1758.2</v>
+        <v>1660.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1222</v>
+        <v>1345</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Purdue</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3095,68 +3095,68 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="E38" t="b">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G38" t="n">
-        <v>2099.2</v>
+        <v>1955.6</v>
       </c>
       <c r="H38" t="n">
-        <v>1.9173</v>
+        <v>0.3963</v>
       </c>
       <c r="I38" t="n">
-        <v>117.81</v>
+        <v>124.64</v>
       </c>
       <c r="J38" t="n">
-        <v>94.78</v>
+        <v>107.6</v>
       </c>
       <c r="K38" t="n">
-        <v>23.03</v>
+        <v>17.04</v>
       </c>
       <c r="L38" t="n">
-        <v>0.3414</v>
+        <v>0.3051</v>
       </c>
       <c r="M38" t="n">
-        <v>0.1193</v>
+        <v>0.1348</v>
       </c>
       <c r="N38" t="n">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="O38" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P38" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="Q38" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="R38" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T38" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U38" t="n">
-        <v>1706</v>
+        <v>1746.9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1304</v>
+        <v>1438</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nebraska</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3166,68 +3166,68 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="E39" t="b">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G39" t="n">
-        <v>1992.1</v>
+        <v>1956.5</v>
       </c>
       <c r="H39" t="n">
-        <v>11.5554</v>
+        <v>13.4946</v>
       </c>
       <c r="I39" t="n">
-        <v>115.07</v>
+        <v>118.84</v>
       </c>
       <c r="J39" t="n">
-        <v>98.04000000000001</v>
+        <v>100.06</v>
       </c>
       <c r="K39" t="n">
-        <v>17.03</v>
+        <v>18.77</v>
       </c>
       <c r="L39" t="n">
-        <v>0.2419</v>
+        <v>0.3168</v>
       </c>
       <c r="M39" t="n">
-        <v>0.1401</v>
+        <v>0.1532</v>
       </c>
       <c r="N39" t="n">
-        <v>5.2</v>
+        <v>3</v>
       </c>
       <c r="O39" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="P39" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="Q39" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="R39" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T39" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="U39" t="n">
-        <v>1659.3</v>
+        <v>1639.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1242</v>
+        <v>1397</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3237,68 +3237,68 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>05</t>
         </is>
       </c>
       <c r="E40" t="b">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G40" t="n">
-        <v>1971.6</v>
+        <v>1898.6</v>
       </c>
       <c r="H40" t="n">
-        <v>11.9283</v>
+        <v>-1.6704</v>
       </c>
       <c r="I40" t="n">
-        <v>110.16</v>
+        <v>117.06</v>
       </c>
       <c r="J40" t="n">
-        <v>100.46</v>
+        <v>101.96</v>
       </c>
       <c r="K40" t="n">
-        <v>9.699999999999999</v>
+        <v>15.09</v>
       </c>
       <c r="L40" t="n">
-        <v>0.2509</v>
+        <v>0.3583</v>
       </c>
       <c r="M40" t="n">
-        <v>0.1535</v>
+        <v>0.1671</v>
       </c>
       <c r="N40" t="n">
-        <v>-4.8</v>
+        <v>2.6</v>
       </c>
       <c r="O40" t="n">
+        <v>18</v>
+      </c>
+      <c r="P40" t="n">
         <v>16</v>
       </c>
-      <c r="P40" t="n">
-        <v>15</v>
-      </c>
       <c r="Q40" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R40" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="S40" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="T40" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="U40" t="n">
-        <v>1779.6</v>
+        <v>1706.1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1116</v>
+        <v>1314</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3308,68 +3308,68 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>06</t>
         </is>
       </c>
       <c r="E41" t="b">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G41" t="n">
-        <v>1940.1</v>
+        <v>1917.6</v>
       </c>
       <c r="H41" t="n">
-        <v>5.7735</v>
+        <v>2.3735</v>
       </c>
       <c r="I41" t="n">
-        <v>123.18</v>
+        <v>115.09</v>
       </c>
       <c r="J41" t="n">
-        <v>108.72</v>
+        <v>103.39</v>
       </c>
       <c r="K41" t="n">
-        <v>14.46</v>
+        <v>11.71</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2975</v>
+        <v>0.2653</v>
       </c>
       <c r="M41" t="n">
-        <v>0.1194</v>
+        <v>0.14</v>
       </c>
       <c r="N41" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="O41" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="P41" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Q41" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="R41" t="n">
+        <v>25</v>
+      </c>
+      <c r="S41" t="n">
         <v>19</v>
       </c>
-      <c r="S41" t="n">
-        <v>20</v>
-      </c>
       <c r="T41" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="U41" t="n">
-        <v>1727.6</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1435</v>
+        <v>1208</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Vanderbilt</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3379,68 +3379,68 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>07</t>
         </is>
       </c>
       <c r="E42" t="b">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G42" t="n">
-        <v>1918.7</v>
+        <v>1816.9</v>
       </c>
       <c r="H42" t="n">
-        <v>2.6895</v>
+        <v>0.2065</v>
       </c>
       <c r="I42" t="n">
-        <v>121.87</v>
+        <v>121.14</v>
       </c>
       <c r="J42" t="n">
-        <v>105.42</v>
+        <v>107.06</v>
       </c>
       <c r="K42" t="n">
-        <v>16.45</v>
+        <v>14.09</v>
       </c>
       <c r="L42" t="n">
-        <v>0.2854</v>
+        <v>0.3227</v>
       </c>
       <c r="M42" t="n">
-        <v>0.1247</v>
+        <v>0.1388</v>
       </c>
       <c r="N42" t="n">
-        <v>-1.6</v>
+        <v>7.6</v>
       </c>
       <c r="O42" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="P42" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="Q42" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="R42" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="S42" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="T42" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="U42" t="n">
-        <v>1684.4</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>St Mary's CA</t>
+          <t>St Louis</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3450,68 +3450,68 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>08</t>
         </is>
       </c>
       <c r="E43" t="b">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="G43" t="n">
-        <v>1877.4</v>
+        <v>1807.8</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.5286</v>
+        <v>9.839</v>
       </c>
       <c r="I43" t="n">
-        <v>118.87</v>
+        <v>120.36</v>
       </c>
       <c r="J43" t="n">
-        <v>98.81999999999999</v>
+        <v>98.52</v>
       </c>
       <c r="K43" t="n">
-        <v>20.05</v>
+        <v>21.84</v>
       </c>
       <c r="L43" t="n">
-        <v>0.2966</v>
+        <v>0.2436</v>
       </c>
       <c r="M43" t="n">
-        <v>0.1557</v>
+        <v>0.1686</v>
       </c>
       <c r="N43" t="n">
-        <v>11.8</v>
+        <v>-0.4</v>
       </c>
       <c r="O43" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="P43" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="Q43" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="R43" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S43" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="T43" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="U43" t="n">
-        <v>1595.3</v>
+        <v>1512.1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1155</v>
+        <v>1395</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Clemson</t>
+          <t>TCU</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3521,68 +3521,68 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>09</t>
         </is>
       </c>
       <c r="E44" t="b">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G44" t="n">
-        <v>1836.4</v>
+        <v>1836.3</v>
       </c>
       <c r="H44" t="n">
-        <v>3.8425</v>
+        <v>6.8916</v>
       </c>
       <c r="I44" t="n">
-        <v>112.26</v>
+        <v>110.72</v>
       </c>
       <c r="J44" t="n">
-        <v>99.90000000000001</v>
+        <v>101.25</v>
       </c>
       <c r="K44" t="n">
-        <v>12.36</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="L44" t="n">
-        <v>0.2417</v>
+        <v>0.3192</v>
       </c>
       <c r="M44" t="n">
-        <v>0.1398</v>
+        <v>0.1507</v>
       </c>
       <c r="N44" t="n">
-        <v>-5</v>
+        <v>9</v>
       </c>
       <c r="O44" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="P44" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="Q44" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="R44" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="S44" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="T44" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="U44" t="n">
-        <v>1652.4</v>
+        <v>1679.3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1416</v>
+        <v>1301</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>UCF</t>
+          <t>NC State</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3592,68 +3592,68 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E45" t="b">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G45" t="n">
-        <v>1820.5</v>
+        <v>1735.9</v>
       </c>
       <c r="H45" t="n">
-        <v>7.025</v>
+        <v>7.7247</v>
       </c>
       <c r="I45" t="n">
-        <v>114.77</v>
+        <v>118.75</v>
       </c>
       <c r="J45" t="n">
-        <v>110.49</v>
+        <v>108.16</v>
       </c>
       <c r="K45" t="n">
-        <v>4.28</v>
+        <v>10.59</v>
       </c>
       <c r="L45" t="n">
-        <v>0.3115</v>
+        <v>0.2829</v>
       </c>
       <c r="M45" t="n">
-        <v>0.1546</v>
+        <v>0.1296</v>
       </c>
       <c r="N45" t="n">
-        <v>-1.6</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="O45" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="P45" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="Q45" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="R45" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="S45" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="T45" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="U45" t="n">
-        <v>1687.9</v>
+        <v>1675.6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1326</v>
+        <v>1433</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ohio St</t>
+          <t>VCU</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3663,68 +3663,68 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11a</t>
         </is>
       </c>
       <c r="E46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G46" t="n">
-        <v>1789.2</v>
+        <v>1739.9</v>
       </c>
       <c r="H46" t="n">
-        <v>1.4042</v>
+        <v>2.9764</v>
       </c>
       <c r="I46" t="n">
-        <v>118.28</v>
+        <v>118.46</v>
       </c>
       <c r="J46" t="n">
-        <v>107.42</v>
+        <v>103.76</v>
       </c>
       <c r="K46" t="n">
-        <v>10.87</v>
+        <v>14.7</v>
       </c>
       <c r="L46" t="n">
-        <v>0.255</v>
+        <v>0.2979</v>
       </c>
       <c r="M46" t="n">
-        <v>0.1501</v>
+        <v>0.1497</v>
       </c>
       <c r="N46" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="O46" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="P46" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="Q46" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="R46" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="S46" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="T46" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="U46" t="n">
-        <v>1696.1</v>
+        <v>1554.6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1275</v>
+        <v>1120</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Miami OH</t>
+          <t>Auburn</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3734,68 +3734,68 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>11b</t>
         </is>
       </c>
       <c r="E47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G47" t="n">
-        <v>1775.2</v>
+        <v>1831.7</v>
       </c>
       <c r="H47" t="n">
-        <v>9.651999999999999</v>
+        <v>-7.7196</v>
       </c>
       <c r="I47" t="n">
-        <v>120.89</v>
+        <v>119.16</v>
       </c>
       <c r="J47" t="n">
-        <v>105.23</v>
+        <v>114.92</v>
       </c>
       <c r="K47" t="n">
-        <v>15.66</v>
+        <v>4.25</v>
       </c>
       <c r="L47" t="n">
-        <v>0.2107</v>
+        <v>0.3497</v>
       </c>
       <c r="M47" t="n">
-        <v>0.1402</v>
+        <v>0.1459</v>
       </c>
       <c r="N47" t="n">
-        <v>6</v>
+        <v>-3</v>
       </c>
       <c r="O47" t="n">
-        <v>87</v>
+        <v>40</v>
       </c>
       <c r="P47" t="n">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="Q47" t="n">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="R47" t="n">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="S47" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="T47" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U47" t="n">
-        <v>1414.6</v>
+        <v>1758.3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1378</v>
+        <v>1251</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>South Florida</t>
+          <t>Liberty</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3812,61 +3812,61 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G48" t="n">
-        <v>1709.5</v>
+        <v>1733.1</v>
       </c>
       <c r="H48" t="n">
-        <v>9.3651</v>
+        <v>3.2041</v>
       </c>
       <c r="I48" t="n">
-        <v>115.67</v>
+        <v>117.83</v>
       </c>
       <c r="J48" t="n">
-        <v>102.39</v>
+        <v>110.75</v>
       </c>
       <c r="K48" t="n">
-        <v>13.28</v>
+        <v>7.08</v>
       </c>
       <c r="L48" t="n">
-        <v>0.336</v>
+        <v>0.1699</v>
       </c>
       <c r="M48" t="n">
-        <v>0.1478</v>
+        <v>0.1316</v>
       </c>
       <c r="N48" t="n">
-        <v>15.4</v>
+        <v>-5</v>
       </c>
       <c r="O48" t="n">
-        <v>52</v>
+        <v>111</v>
       </c>
       <c r="P48" t="n">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="Q48" t="n">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="R48" t="n">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="S48" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="T48" t="n">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="U48" t="n">
-        <v>1558.8</v>
+        <v>1485.6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1251</v>
+        <v>1295</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Liberty</t>
+          <t>N Dakota St</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3883,52 +3883,52 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G49" t="n">
-        <v>1729</v>
+        <v>1591.4</v>
       </c>
       <c r="H49" t="n">
-        <v>3.4996</v>
+        <v>3.6609</v>
       </c>
       <c r="I49" t="n">
-        <v>117.41</v>
+        <v>114.4</v>
       </c>
       <c r="J49" t="n">
-        <v>110.66</v>
+        <v>102.12</v>
       </c>
       <c r="K49" t="n">
-        <v>6.75</v>
+        <v>12.28</v>
       </c>
       <c r="L49" t="n">
-        <v>0.1701</v>
+        <v>0.3105</v>
       </c>
       <c r="M49" t="n">
-        <v>0.1316</v>
+        <v>0.1495</v>
       </c>
       <c r="N49" t="n">
-        <v>-6.2</v>
+        <v>16.4</v>
       </c>
       <c r="O49" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="P49" t="n">
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="Q49" t="n">
-        <v>111</v>
+        <v>155</v>
       </c>
       <c r="R49" t="n">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="S49" t="n">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="T49" t="n">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="U49" t="n">
-        <v>1482.9</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="50">
@@ -4004,11 +4004,11 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1190</v>
+        <v>1467</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ETSU</t>
+          <t>Merrimack</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4025,61 +4025,61 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="G51" t="n">
-        <v>1514.8</v>
+        <v>1515.6</v>
       </c>
       <c r="H51" t="n">
-        <v>0.598</v>
+        <v>3.9427</v>
       </c>
       <c r="I51" t="n">
-        <v>116.43</v>
+        <v>107.67</v>
       </c>
       <c r="J51" t="n">
-        <v>105.39</v>
+        <v>102.86</v>
       </c>
       <c r="K51" t="n">
-        <v>11.04</v>
+        <v>4.81</v>
       </c>
       <c r="L51" t="n">
-        <v>0.2692</v>
+        <v>0.2665</v>
       </c>
       <c r="M51" t="n">
-        <v>0.1444</v>
+        <v>0.1436</v>
       </c>
       <c r="N51" t="n">
-        <v>0.4</v>
+        <v>6.6</v>
       </c>
       <c r="O51" t="n">
-        <v>140</v>
+        <v>172</v>
       </c>
       <c r="P51" t="n">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="Q51" t="n">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="R51" t="n">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="S51" t="n">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="T51" t="n">
-        <v>128</v>
+        <v>185</v>
       </c>
       <c r="U51" t="n">
-        <v>1424.6</v>
+        <v>1452.7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1224</v>
+        <v>1420</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Howard</t>
+          <t>UMBC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4096,61 +4096,61 @@
         <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G52" t="n">
-        <v>1409</v>
+        <v>1391.7</v>
       </c>
       <c r="H52" t="n">
-        <v>3.2279</v>
+        <v>1.2162</v>
       </c>
       <c r="I52" t="n">
-        <v>109.08</v>
+        <v>112.51</v>
       </c>
       <c r="J52" t="n">
-        <v>98.81</v>
+        <v>102.24</v>
       </c>
       <c r="K52" t="n">
-        <v>10.27</v>
+        <v>10.26</v>
       </c>
       <c r="L52" t="n">
-        <v>0.3126</v>
+        <v>0.2126</v>
       </c>
       <c r="M52" t="n">
-        <v>0.1855</v>
+        <v>0.1361</v>
       </c>
       <c r="N52" t="n">
-        <v>23.6</v>
+        <v>18.8</v>
       </c>
       <c r="O52" t="n">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="P52" t="n">
-        <v>260</v>
+        <v>238</v>
       </c>
       <c r="Q52" t="n">
-        <v>277</v>
+        <v>200</v>
       </c>
       <c r="R52" t="n">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="S52" t="n">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="T52" t="n">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="U52" t="n">
-        <v>1380.6</v>
+        <v>1364.8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1126</v>
+        <v>1254</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Bethune-Cookman</t>
+          <t>LIU Brooklyn</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4167,52 +4167,52 @@
         <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G53" t="n">
-        <v>1375.4</v>
+        <v>1416</v>
       </c>
       <c r="H53" t="n">
-        <v>0.9205</v>
+        <v>2.4057</v>
       </c>
       <c r="I53" t="n">
-        <v>104.96</v>
+        <v>108.81</v>
       </c>
       <c r="J53" t="n">
-        <v>108.7</v>
+        <v>104.08</v>
       </c>
       <c r="K53" t="n">
-        <v>-3.74</v>
+        <v>4.73</v>
       </c>
       <c r="L53" t="n">
-        <v>0.2778</v>
+        <v>0.3167</v>
       </c>
       <c r="M53" t="n">
-        <v>0.1862</v>
+        <v>0.1861</v>
       </c>
       <c r="N53" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="O53" t="n">
-        <v>233</v>
+        <v>210</v>
       </c>
       <c r="P53" t="n">
-        <v>267</v>
+        <v>228</v>
       </c>
       <c r="Q53" t="n">
-        <v>256</v>
+        <v>211</v>
       </c>
       <c r="R53" t="n">
-        <v>208</v>
+        <v>180</v>
       </c>
       <c r="S53" t="n">
-        <v>224</v>
+        <v>173</v>
       </c>
       <c r="T53" t="n">
-        <v>246</v>
+        <v>195</v>
       </c>
       <c r="U53" t="n">
-        <v>1436.6</v>
+        <v>1378.3</v>
       </c>
     </row>
     <row r="54">
@@ -4238,31 +4238,31 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="G54" t="n">
-        <v>2252.6</v>
+        <v>2253.6</v>
       </c>
       <c r="H54" t="n">
-        <v>8.169700000000001</v>
+        <v>7.7769</v>
       </c>
       <c r="I54" t="n">
-        <v>120.84</v>
+        <v>121.09</v>
       </c>
       <c r="J54" t="n">
-        <v>95.38</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>25.46</v>
+        <v>24.99</v>
       </c>
       <c r="L54" t="n">
-        <v>0.2935</v>
+        <v>0.291</v>
       </c>
       <c r="M54" t="n">
-        <v>0.1524</v>
+        <v>0.1505</v>
       </c>
       <c r="N54" t="n">
-        <v>12</v>
+        <v>12.6</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -4283,7 +4283,7 @@
         <v>3</v>
       </c>
       <c r="U54" t="n">
-        <v>1751.1</v>
+        <v>1742.6</v>
       </c>
     </row>
     <row r="55">
@@ -4451,31 +4451,31 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G57" t="n">
-        <v>2044.2</v>
+        <v>2025.5</v>
       </c>
       <c r="H57" t="n">
-        <v>10.5951</v>
+        <v>10.1327</v>
       </c>
       <c r="I57" t="n">
-        <v>118.24</v>
+        <v>118.86</v>
       </c>
       <c r="J57" t="n">
-        <v>105.38</v>
+        <v>106.69</v>
       </c>
       <c r="K57" t="n">
-        <v>12.86</v>
+        <v>12.16</v>
       </c>
       <c r="L57" t="n">
-        <v>0.2929</v>
+        <v>0.2944</v>
       </c>
       <c r="M57" t="n">
-        <v>0.1562</v>
+        <v>0.155</v>
       </c>
       <c r="N57" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="O57" t="n">
         <v>13</v>
@@ -4496,16 +4496,16 @@
         <v>13</v>
       </c>
       <c r="U57" t="n">
-        <v>1756.8</v>
+        <v>1762.7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1314</v>
+        <v>1435</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Vanderbilt</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4522,61 +4522,61 @@
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G58" t="n">
-        <v>1921.9</v>
+        <v>1935.7</v>
       </c>
       <c r="H58" t="n">
-        <v>2.4321</v>
+        <v>2.1989</v>
       </c>
       <c r="I58" t="n">
-        <v>115.82</v>
+        <v>121.8</v>
       </c>
       <c r="J58" t="n">
-        <v>102.6</v>
+        <v>105.67</v>
       </c>
       <c r="K58" t="n">
-        <v>13.22</v>
+        <v>16.12</v>
       </c>
       <c r="L58" t="n">
-        <v>0.2692</v>
+        <v>0.2802</v>
       </c>
       <c r="M58" t="n">
-        <v>0.1364</v>
+        <v>0.1278</v>
       </c>
       <c r="N58" t="n">
-        <v>0.6</v>
+        <v>-0.6</v>
       </c>
       <c r="O58" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="P58" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q58" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="R58" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="S58" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="T58" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="U58" t="n">
-        <v>1655.6</v>
+        <v>1694.9</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1458</v>
+        <v>1246</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4593,52 +4593,52 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G59" t="n">
-        <v>1837</v>
+        <v>1881.8</v>
       </c>
       <c r="H59" t="n">
-        <v>1.4688</v>
+        <v>5.4881</v>
       </c>
       <c r="I59" t="n">
-        <v>118.38</v>
+        <v>116.58</v>
       </c>
       <c r="J59" t="n">
-        <v>106.47</v>
+        <v>106.11</v>
       </c>
       <c r="K59" t="n">
-        <v>11.91</v>
+        <v>10.47</v>
       </c>
       <c r="L59" t="n">
-        <v>0.2733</v>
+        <v>0.3117</v>
       </c>
       <c r="M59" t="n">
-        <v>0.1236</v>
+        <v>0.1455</v>
       </c>
       <c r="N59" t="n">
-        <v>6.4</v>
+        <v>0.8</v>
       </c>
       <c r="O59" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P59" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Q59" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="R59" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S59" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T59" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="U59" t="n">
-        <v>1688.3</v>
+        <v>1728.4</v>
       </c>
     </row>
     <row r="60">
@@ -4664,31 +4664,31 @@
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G60" t="n">
-        <v>1905.8</v>
+        <v>1924.5</v>
       </c>
       <c r="H60" t="n">
-        <v>2.2762</v>
+        <v>1.6354</v>
       </c>
       <c r="I60" t="n">
-        <v>117.49</v>
+        <v>118.39</v>
       </c>
       <c r="J60" t="n">
-        <v>106.29</v>
+        <v>106.82</v>
       </c>
       <c r="K60" t="n">
-        <v>11.21</v>
+        <v>11.57</v>
       </c>
       <c r="L60" t="n">
-        <v>0.2953</v>
+        <v>0.3034</v>
       </c>
       <c r="M60" t="n">
-        <v>0.1466</v>
+        <v>0.1419</v>
       </c>
       <c r="N60" t="n">
-        <v>-8</v>
+        <v>-5.4</v>
       </c>
       <c r="O60" t="n">
         <v>23</v>
@@ -4709,16 +4709,16 @@
         <v>23</v>
       </c>
       <c r="U60" t="n">
-        <v>1713.1</v>
+        <v>1726.9</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1208</v>
+        <v>1155</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Clemson</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4735,61 +4735,61 @@
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G61" t="n">
-        <v>1808.8</v>
+        <v>1838.2</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1677</v>
+        <v>3.3876</v>
       </c>
       <c r="I61" t="n">
-        <v>120.8</v>
+        <v>112.83</v>
       </c>
       <c r="J61" t="n">
-        <v>106.43</v>
+        <v>100.58</v>
       </c>
       <c r="K61" t="n">
-        <v>14.38</v>
+        <v>12.25</v>
       </c>
       <c r="L61" t="n">
-        <v>0.3238</v>
+        <v>0.2488</v>
       </c>
       <c r="M61" t="n">
-        <v>0.1381</v>
+        <v>0.1395</v>
       </c>
       <c r="N61" t="n">
-        <v>8</v>
+        <v>-1.8</v>
       </c>
       <c r="O61" t="n">
+        <v>36</v>
+      </c>
+      <c r="P61" t="n">
         <v>33</v>
       </c>
-      <c r="P61" t="n">
-        <v>31</v>
-      </c>
       <c r="Q61" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R61" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="S61" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="T61" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="U61" t="n">
-        <v>1648.7</v>
+        <v>1641.6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1301</v>
+        <v>1417</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NC State</t>
+          <t>UCLA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4806,61 +4806,61 @@
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="G62" t="n">
-        <v>1751.7</v>
+        <v>1859.1</v>
       </c>
       <c r="H62" t="n">
-        <v>8.052099999999999</v>
+        <v>2.2498</v>
       </c>
       <c r="I62" t="n">
-        <v>118.51</v>
+        <v>117.64</v>
       </c>
       <c r="J62" t="n">
-        <v>107.99</v>
+        <v>107.04</v>
       </c>
       <c r="K62" t="n">
-        <v>10.52</v>
+        <v>10.59</v>
       </c>
       <c r="L62" t="n">
-        <v>0.2827</v>
+        <v>0.2985</v>
       </c>
       <c r="M62" t="n">
-        <v>0.1274</v>
+        <v>0.1288</v>
       </c>
       <c r="N62" t="n">
-        <v>-8.199999999999999</v>
+        <v>11.2</v>
       </c>
       <c r="O62" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="P62" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="Q62" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="R62" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="S62" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="T62" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="U62" t="n">
-        <v>1678.3</v>
+        <v>1689.3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1395</v>
+        <v>1401</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>TCU</t>
+          <t>Texas A&amp;M</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4877,61 +4877,61 @@
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G63" t="n">
-        <v>1827.5</v>
+        <v>1843.5</v>
       </c>
       <c r="H63" t="n">
-        <v>6.8987</v>
+        <v>4.536</v>
       </c>
       <c r="I63" t="n">
-        <v>110.58</v>
+        <v>117.79</v>
       </c>
       <c r="J63" t="n">
-        <v>101.35</v>
+        <v>106.34</v>
       </c>
       <c r="K63" t="n">
-        <v>9.23</v>
+        <v>11.45</v>
       </c>
       <c r="L63" t="n">
-        <v>0.3181</v>
+        <v>0.3067</v>
       </c>
       <c r="M63" t="n">
-        <v>0.1536</v>
+        <v>0.1399</v>
       </c>
       <c r="N63" t="n">
-        <v>4.8</v>
+        <v>-0.6</v>
       </c>
       <c r="O63" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="P63" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="Q63" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="R63" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="S63" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="T63" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="U63" t="n">
-        <v>1681.1</v>
+        <v>1651.1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1400</v>
+        <v>1275</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Miami OH</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4948,52 +4948,52 @@
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G64" t="n">
-        <v>1775.6</v>
+        <v>1775.2</v>
       </c>
       <c r="H64" t="n">
-        <v>2.7602</v>
+        <v>9.651999999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>120.67</v>
+        <v>120.89</v>
       </c>
       <c r="J64" t="n">
-        <v>111.46</v>
+        <v>105.23</v>
       </c>
       <c r="K64" t="n">
-        <v>9.210000000000001</v>
+        <v>15.66</v>
       </c>
       <c r="L64" t="n">
-        <v>0.3123</v>
+        <v>0.2107</v>
       </c>
       <c r="M64" t="n">
-        <v>0.1488</v>
+        <v>0.1402</v>
       </c>
       <c r="N64" t="n">
-        <v>-7</v>
+        <v>6</v>
       </c>
       <c r="O64" t="n">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="P64" t="n">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="Q64" t="n">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="R64" t="n">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="S64" t="n">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="T64" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="U64" t="n">
-        <v>1702.7</v>
+        <v>1414.6</v>
       </c>
     </row>
     <row r="65">
@@ -5019,31 +5019,31 @@
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G65" t="n">
-        <v>1618</v>
+        <v>1620.5</v>
       </c>
       <c r="H65" t="n">
-        <v>-1.2011</v>
+        <v>-1.0234</v>
       </c>
       <c r="I65" t="n">
-        <v>121.43</v>
+        <v>121.05</v>
       </c>
       <c r="J65" t="n">
-        <v>99.78</v>
+        <v>100.19</v>
       </c>
       <c r="K65" t="n">
-        <v>21.65</v>
+        <v>20.86</v>
       </c>
       <c r="L65" t="n">
-        <v>0.3136</v>
+        <v>0.3114</v>
       </c>
       <c r="M65" t="n">
-        <v>0.1281</v>
+        <v>0.128</v>
       </c>
       <c r="N65" t="n">
-        <v>16.2</v>
+        <v>12</v>
       </c>
       <c r="O65" t="n">
         <v>91</v>
@@ -5064,7 +5064,7 @@
         <v>76</v>
       </c>
       <c r="U65" t="n">
-        <v>1375.9</v>
+        <v>1377.7</v>
       </c>
     </row>
     <row r="66">
@@ -5090,31 +5090,31 @@
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G66" t="n">
-        <v>1592.3</v>
+        <v>1594.5</v>
       </c>
       <c r="H66" t="n">
-        <v>1.4889</v>
+        <v>1.5103</v>
       </c>
       <c r="I66" t="n">
-        <v>107.02</v>
+        <v>107.31</v>
       </c>
       <c r="J66" t="n">
-        <v>98.72</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="K66" t="n">
-        <v>8.300000000000001</v>
+        <v>7.82</v>
       </c>
       <c r="L66" t="n">
-        <v>0.3312</v>
+        <v>0.3297</v>
       </c>
       <c r="M66" t="n">
-        <v>0.1721</v>
+        <v>0.1719</v>
       </c>
       <c r="N66" t="n">
-        <v>8.4</v>
+        <v>10.8</v>
       </c>
       <c r="O66" t="n">
         <v>119</v>
@@ -5135,7 +5135,7 @@
         <v>111</v>
       </c>
       <c r="U66" t="n">
-        <v>1460.9</v>
+        <v>1455.6</v>
       </c>
     </row>
     <row r="67">
@@ -5161,31 +5161,31 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G67" t="n">
-        <v>1610.8</v>
+        <v>1614.5</v>
       </c>
       <c r="H67" t="n">
-        <v>2.2236</v>
+        <v>2.2068</v>
       </c>
       <c r="I67" t="n">
-        <v>103.83</v>
+        <v>103.59</v>
       </c>
       <c r="J67" t="n">
-        <v>96.66</v>
+        <v>96.37</v>
       </c>
       <c r="K67" t="n">
-        <v>7.18</v>
+        <v>7.22</v>
       </c>
       <c r="L67" t="n">
-        <v>0.2682</v>
+        <v>0.2658</v>
       </c>
       <c r="M67" t="n">
-        <v>0.1661</v>
+        <v>0.1712</v>
       </c>
       <c r="N67" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="O67" t="n">
         <v>109</v>
@@ -5206,16 +5206,16 @@
         <v>119</v>
       </c>
       <c r="U67" t="n">
-        <v>1470.2</v>
+        <v>1471.2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1340</v>
+        <v>1227</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Portland St</t>
+          <t>IL Chicago</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5232,61 +5232,61 @@
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="G68" t="n">
-        <v>1458.3</v>
+        <v>1535.5</v>
       </c>
       <c r="H68" t="n">
-        <v>2.128</v>
+        <v>2.1038</v>
       </c>
       <c r="I68" t="n">
-        <v>105.36</v>
+        <v>108.47</v>
       </c>
       <c r="J68" t="n">
-        <v>101.08</v>
+        <v>102.47</v>
       </c>
       <c r="K68" t="n">
-        <v>4.28</v>
+        <v>6</v>
       </c>
       <c r="L68" t="n">
-        <v>0.2592</v>
+        <v>0.3429</v>
       </c>
       <c r="M68" t="n">
-        <v>0.1706</v>
+        <v>0.1641</v>
       </c>
       <c r="N68" t="n">
-        <v>0.2</v>
+        <v>4.2</v>
       </c>
       <c r="O68" t="n">
-        <v>159</v>
+        <v>110</v>
       </c>
       <c r="P68" t="n">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="Q68" t="n">
-        <v>174</v>
+        <v>129</v>
       </c>
       <c r="R68" t="n">
-        <v>167</v>
+        <v>117</v>
       </c>
       <c r="S68" t="n">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="T68" t="n">
-        <v>151</v>
+        <v>116</v>
       </c>
       <c r="U68" t="n">
-        <v>1416.6</v>
+        <v>1506.5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1420</v>
+        <v>1340</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>UMBC</t>
+          <t>Portland St</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5303,52 +5303,52 @@
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G69" t="n">
-        <v>1390.2</v>
+        <v>1458.3</v>
       </c>
       <c r="H69" t="n">
-        <v>1.1316</v>
+        <v>2.128</v>
       </c>
       <c r="I69" t="n">
-        <v>111.8</v>
+        <v>105.36</v>
       </c>
       <c r="J69" t="n">
-        <v>101.74</v>
+        <v>101.08</v>
       </c>
       <c r="K69" t="n">
-        <v>10.06</v>
+        <v>4.28</v>
       </c>
       <c r="L69" t="n">
-        <v>0.2176</v>
+        <v>0.2592</v>
       </c>
       <c r="M69" t="n">
-        <v>0.1378</v>
+        <v>0.1706</v>
       </c>
       <c r="N69" t="n">
-        <v>18.4</v>
+        <v>0.2</v>
       </c>
       <c r="O69" t="n">
-        <v>221</v>
+        <v>159</v>
       </c>
       <c r="P69" t="n">
-        <v>238</v>
+        <v>158</v>
       </c>
       <c r="Q69" t="n">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="R69" t="n">
-        <v>206</v>
+        <v>167</v>
       </c>
       <c r="S69" t="n">
-        <v>221</v>
+        <v>124</v>
       </c>
       <c r="T69" t="n">
-        <v>223</v>
+        <v>151</v>
       </c>
       <c r="U69" t="n">
-        <v>1368.1</v>
+        <v>1416.6</v>
       </c>
     </row>
   </sheetData>

--- a/team_stats_2026.xlsx
+++ b/team_stats_2026.xlsx
@@ -738,11 +738,11 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1104</v>
+        <v>1403</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alabama</t>
+          <t>Texas Tech</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -762,58 +762,58 @@
         <v>124</v>
       </c>
       <c r="G5" t="n">
-        <v>1975.1</v>
+        <v>2025.5</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.4869</v>
+        <v>10.1327</v>
       </c>
       <c r="I5" t="n">
-        <v>122.11</v>
+        <v>118.86</v>
       </c>
       <c r="J5" t="n">
-        <v>110.78</v>
+        <v>106.69</v>
       </c>
       <c r="K5" t="n">
-        <v>11.33</v>
+        <v>12.16</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2853</v>
+        <v>0.2944</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1289</v>
+        <v>0.155</v>
       </c>
       <c r="N5" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="O5" t="n">
+        <v>13</v>
+      </c>
+      <c r="P5" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>11</v>
+      </c>
+      <c r="R5" t="n">
+        <v>11</v>
+      </c>
+      <c r="S5" t="n">
         <v>15</v>
       </c>
-      <c r="P5" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="T5" t="n">
         <v>13</v>
       </c>
-      <c r="R5" t="n">
-        <v>14</v>
-      </c>
-      <c r="S5" t="n">
-        <v>16</v>
-      </c>
-      <c r="T5" t="n">
-        <v>16</v>
-      </c>
       <c r="U5" t="n">
-        <v>1772.1</v>
+        <v>1762.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1385</v>
+        <v>1116</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>St John's</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -830,52 +830,52 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G6" t="n">
-        <v>1961.4</v>
+        <v>1950</v>
       </c>
       <c r="H6" t="n">
-        <v>5.5897</v>
+        <v>5.5428</v>
       </c>
       <c r="I6" t="n">
-        <v>113.79</v>
+        <v>122.85</v>
       </c>
       <c r="J6" t="n">
-        <v>98.7</v>
+        <v>108.88</v>
       </c>
       <c r="K6" t="n">
-        <v>15.09</v>
+        <v>13.96</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3238</v>
+        <v>0.3009</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1418</v>
+        <v>0.1205</v>
       </c>
       <c r="N6" t="n">
-        <v>7.8</v>
+        <v>2.6</v>
       </c>
       <c r="O6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q6" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="R6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="S6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T6" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="U6" t="n">
-        <v>1680.5</v>
+        <v>1728.7</v>
       </c>
     </row>
     <row r="7">
@@ -1022,11 +1022,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1429</v>
+        <v>1208</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Utah St</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1046,58 +1046,58 @@
         <v>124</v>
       </c>
       <c r="G9" t="n">
-        <v>1869.8</v>
+        <v>1816.9</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2419</v>
+        <v>0.2065</v>
       </c>
       <c r="I9" t="n">
-        <v>120.49</v>
+        <v>121.14</v>
       </c>
       <c r="J9" t="n">
-        <v>105.01</v>
+        <v>107.06</v>
       </c>
       <c r="K9" t="n">
-        <v>15.48</v>
+        <v>14.09</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3065</v>
+        <v>0.3227</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1487</v>
+        <v>0.1388</v>
       </c>
       <c r="N9" t="n">
-        <v>-7.6</v>
+        <v>7.6</v>
       </c>
       <c r="O9" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="P9" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q9" t="n">
+        <v>30</v>
+      </c>
+      <c r="R9" t="n">
         <v>31</v>
       </c>
-      <c r="R9" t="n">
-        <v>26</v>
-      </c>
       <c r="S9" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="T9" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="U9" t="n">
-        <v>1599.2</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1234</v>
+        <v>1326</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Iowa</t>
+          <t>Ohio St</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1114,61 +1114,61 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G10" t="n">
-        <v>1851.2</v>
+        <v>1799.9</v>
       </c>
       <c r="H10" t="n">
-        <v>4.4379</v>
+        <v>1.5472</v>
       </c>
       <c r="I10" t="n">
-        <v>119.28</v>
+        <v>118.74</v>
       </c>
       <c r="J10" t="n">
-        <v>103.76</v>
+        <v>107.91</v>
       </c>
       <c r="K10" t="n">
-        <v>15.52</v>
+        <v>10.83</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2925</v>
+        <v>0.2524</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1388</v>
+        <v>0.1503</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8</v>
+        <v>6</v>
       </c>
       <c r="O10" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="P10" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="Q10" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="R10" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="S10" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="T10" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="U10" t="n">
-        <v>1708.5</v>
+        <v>1700.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1281</v>
+        <v>1301</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>NC State</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1188,49 +1188,49 @@
         <v>124</v>
       </c>
       <c r="G11" t="n">
-        <v>1757.5</v>
+        <v>1735.9</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.923</v>
+        <v>7.7247</v>
       </c>
       <c r="I11" t="n">
-        <v>115.19</v>
+        <v>118.75</v>
       </c>
       <c r="J11" t="n">
-        <v>109.25</v>
+        <v>108.16</v>
       </c>
       <c r="K11" t="n">
-        <v>5.95</v>
+        <v>10.59</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3014</v>
+        <v>0.2829</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1701</v>
+        <v>0.1296</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="P11" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="Q11" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="R11" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="S11" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="T11" t="n">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="U11" t="n">
-        <v>1651.9</v>
+        <v>1675.6</v>
       </c>
     </row>
     <row r="12">
@@ -1377,11 +1377,11 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1463</v>
+        <v>1378</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Yale</t>
+          <t>South Florida</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1398,52 +1398,52 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G14" t="n">
-        <v>1720.2</v>
+        <v>1709.5</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1161</v>
+        <v>9.3651</v>
       </c>
       <c r="I14" t="n">
-        <v>120.93</v>
+        <v>115.67</v>
       </c>
       <c r="J14" t="n">
-        <v>107.17</v>
+        <v>102.39</v>
       </c>
       <c r="K14" t="n">
-        <v>13.77</v>
+        <v>13.28</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2847</v>
+        <v>0.336</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1362</v>
+        <v>0.1478</v>
       </c>
       <c r="N14" t="n">
-        <v>6.6</v>
+        <v>15.4</v>
       </c>
       <c r="O14" t="n">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="P14" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="Q14" t="n">
-        <v>105</v>
+        <v>55</v>
       </c>
       <c r="R14" t="n">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="S14" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="T14" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="U14" t="n">
-        <v>1457.4</v>
+        <v>1558.8</v>
       </c>
     </row>
     <row r="15">
@@ -1519,11 +1519,11 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1407</v>
+        <v>1190</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Troy</t>
+          <t>ETSU</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1540,61 +1540,61 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="G16" t="n">
-        <v>1593.7</v>
+        <v>1515.6</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3343</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>112.11</v>
+        <v>116.98</v>
       </c>
       <c r="J16" t="n">
-        <v>106.85</v>
+        <v>105.72</v>
       </c>
       <c r="K16" t="n">
-        <v>5.26</v>
+        <v>11.26</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3162</v>
+        <v>0.2696</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1601</v>
+        <v>0.1444</v>
       </c>
       <c r="N16" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="O16" t="n">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="P16" t="n">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="Q16" t="n">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="R16" t="n">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="S16" t="n">
+        <v>151</v>
+      </c>
+      <c r="T16" t="n">
         <v>128</v>
       </c>
-      <c r="T16" t="n">
-        <v>138</v>
-      </c>
       <c r="U16" t="n">
-        <v>1464.1</v>
+        <v>1416.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1460</v>
+        <v>1398</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Wright St</t>
+          <t>Tennessee St</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1611,61 +1611,61 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G17" t="n">
-        <v>1464.5</v>
+        <v>1466.9</v>
       </c>
       <c r="H17" t="n">
-        <v>2.7711</v>
+        <v>3.3618</v>
       </c>
       <c r="I17" t="n">
-        <v>115.65</v>
+        <v>109.9</v>
       </c>
       <c r="J17" t="n">
-        <v>109.07</v>
+        <v>103.28</v>
       </c>
       <c r="K17" t="n">
-        <v>6.58</v>
+        <v>6.62</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2992</v>
+        <v>0.328</v>
       </c>
       <c r="M17" t="n">
-        <v>0.158</v>
+        <v>0.1589</v>
       </c>
       <c r="N17" t="n">
-        <v>6.6</v>
+        <v>19.8</v>
       </c>
       <c r="O17" t="n">
-        <v>153</v>
+        <v>207</v>
       </c>
       <c r="P17" t="n">
-        <v>148</v>
+        <v>199</v>
       </c>
       <c r="Q17" t="n">
-        <v>135</v>
+        <v>196</v>
       </c>
       <c r="R17" t="n">
-        <v>142</v>
+        <v>182</v>
       </c>
       <c r="S17" t="n">
-        <v>152</v>
+        <v>184</v>
       </c>
       <c r="T17" t="n">
-        <v>140</v>
+        <v>191</v>
       </c>
       <c r="U17" t="n">
-        <v>1435.1</v>
+        <v>1407.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1398</v>
+        <v>1420</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tennessee St</t>
+          <t>UMBC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1685,49 +1685,49 @@
         <v>124</v>
       </c>
       <c r="G18" t="n">
-        <v>1466.9</v>
+        <v>1391.7</v>
       </c>
       <c r="H18" t="n">
-        <v>3.3618</v>
+        <v>1.2162</v>
       </c>
       <c r="I18" t="n">
-        <v>109.9</v>
+        <v>112.51</v>
       </c>
       <c r="J18" t="n">
-        <v>103.28</v>
+        <v>102.24</v>
       </c>
       <c r="K18" t="n">
-        <v>6.62</v>
+        <v>10.26</v>
       </c>
       <c r="L18" t="n">
-        <v>0.328</v>
+        <v>0.2126</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1589</v>
+        <v>0.1361</v>
       </c>
       <c r="N18" t="n">
-        <v>19.8</v>
+        <v>18.8</v>
       </c>
       <c r="O18" t="n">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="P18" t="n">
-        <v>199</v>
+        <v>238</v>
       </c>
       <c r="Q18" t="n">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="R18" t="n">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="S18" t="n">
-        <v>184</v>
+        <v>221</v>
       </c>
       <c r="T18" t="n">
-        <v>191</v>
+        <v>223</v>
       </c>
       <c r="U18" t="n">
-        <v>1407.8</v>
+        <v>1364.8</v>
       </c>
     </row>
     <row r="19">
@@ -1945,11 +1945,11 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1242</v>
+        <v>1438</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>124</v>
       </c>
       <c r="G22" t="n">
-        <v>1973.7</v>
+        <v>1956.5</v>
       </c>
       <c r="H22" t="n">
-        <v>11.337</v>
+        <v>13.4946</v>
       </c>
       <c r="I22" t="n">
-        <v>111.61</v>
+        <v>118.84</v>
       </c>
       <c r="J22" t="n">
-        <v>100.9</v>
+        <v>100.06</v>
       </c>
       <c r="K22" t="n">
-        <v>10.71</v>
+        <v>18.77</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2487</v>
+        <v>0.3168</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1523</v>
+        <v>0.1532</v>
       </c>
       <c r="N22" t="n">
-        <v>-3.4</v>
+        <v>3</v>
       </c>
       <c r="O22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P22" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q22" t="n">
         <v>15</v>
       </c>
-      <c r="Q22" t="n">
-        <v>19</v>
-      </c>
       <c r="R22" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="S22" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="U22" t="n">
-        <v>1772.3</v>
+        <v>1639.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1116</v>
+        <v>1385</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>St John's</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2037,52 +2037,52 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G23" t="n">
-        <v>1950</v>
+        <v>1961.4</v>
       </c>
       <c r="H23" t="n">
-        <v>5.5428</v>
+        <v>5.5897</v>
       </c>
       <c r="I23" t="n">
-        <v>122.85</v>
+        <v>113.79</v>
       </c>
       <c r="J23" t="n">
-        <v>108.88</v>
+        <v>98.7</v>
       </c>
       <c r="K23" t="n">
-        <v>13.96</v>
+        <v>15.09</v>
       </c>
       <c r="L23" t="n">
-        <v>0.3009</v>
+        <v>0.3238</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1205</v>
+        <v>0.1418</v>
       </c>
       <c r="N23" t="n">
-        <v>2.6</v>
+        <v>7.8</v>
       </c>
       <c r="O23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q23" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="R23" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="T23" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U23" t="n">
-        <v>1728.7</v>
+        <v>1680.5</v>
       </c>
     </row>
     <row r="24">
@@ -2229,11 +2229,11 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1274</v>
+        <v>1429</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Miami FL</t>
+          <t>Utah St</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2253,58 +2253,58 @@
         <v>124</v>
       </c>
       <c r="G26" t="n">
-        <v>1761</v>
+        <v>1869.8</v>
       </c>
       <c r="H26" t="n">
-        <v>12.4806</v>
+        <v>0.2419</v>
       </c>
       <c r="I26" t="n">
-        <v>118.15</v>
+        <v>120.49</v>
       </c>
       <c r="J26" t="n">
-        <v>101.88</v>
+        <v>105.01</v>
       </c>
       <c r="K26" t="n">
-        <v>16.27</v>
+        <v>15.48</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3077</v>
+        <v>0.3065</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1596</v>
+        <v>0.1487</v>
       </c>
       <c r="N26" t="n">
-        <v>6.8</v>
+        <v>-7.6</v>
       </c>
       <c r="O26" t="n">
+        <v>26</v>
+      </c>
+      <c r="P26" t="n">
         <v>32</v>
       </c>
-      <c r="P26" t="n">
-        <v>38</v>
-      </c>
       <c r="Q26" t="n">
+        <v>31</v>
+      </c>
+      <c r="R26" t="n">
         <v>26</v>
       </c>
-      <c r="R26" t="n">
-        <v>32</v>
-      </c>
       <c r="S26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T26" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U26" t="n">
-        <v>1617.1</v>
+        <v>1599.2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1326</v>
+        <v>1395</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ohio St</t>
+          <t>TCU</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2324,58 +2324,58 @@
         <v>124</v>
       </c>
       <c r="G27" t="n">
-        <v>1799.9</v>
+        <v>1836.3</v>
       </c>
       <c r="H27" t="n">
-        <v>1.5472</v>
+        <v>6.8916</v>
       </c>
       <c r="I27" t="n">
-        <v>118.74</v>
+        <v>110.72</v>
       </c>
       <c r="J27" t="n">
-        <v>107.91</v>
+        <v>101.25</v>
       </c>
       <c r="K27" t="n">
-        <v>10.83</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>0.2524</v>
+        <v>0.3192</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1503</v>
+        <v>0.1507</v>
       </c>
       <c r="N27" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O27" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="P27" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Q27" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="R27" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="S27" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T27" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="U27" t="n">
-        <v>1700.1</v>
+        <v>1679.3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1400</v>
+        <v>1281</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2395,58 +2395,58 @@
         <v>124</v>
       </c>
       <c r="G28" t="n">
-        <v>1757.7</v>
+        <v>1757.5</v>
       </c>
       <c r="H28" t="n">
-        <v>2.865</v>
+        <v>-1.923</v>
       </c>
       <c r="I28" t="n">
-        <v>120.37</v>
+        <v>115.19</v>
       </c>
       <c r="J28" t="n">
-        <v>111.34</v>
+        <v>109.25</v>
       </c>
       <c r="K28" t="n">
-        <v>9.02</v>
+        <v>5.95</v>
       </c>
       <c r="L28" t="n">
-        <v>0.3098</v>
+        <v>0.3014</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1494</v>
+        <v>0.1701</v>
       </c>
       <c r="N28" t="n">
-        <v>-8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="P28" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="Q28" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R28" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="S28" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="T28" t="n">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="U28" t="n">
-        <v>1699.4</v>
+        <v>1651.9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1416</v>
+        <v>1433</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>UCF</t>
+          <t>VCU</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2456,68 +2456,68 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>11a</t>
         </is>
       </c>
       <c r="E29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
         <v>123</v>
       </c>
       <c r="G29" t="n">
-        <v>1820.5</v>
+        <v>1739.9</v>
       </c>
       <c r="H29" t="n">
-        <v>7.025</v>
+        <v>2.9764</v>
       </c>
       <c r="I29" t="n">
-        <v>114.77</v>
+        <v>118.46</v>
       </c>
       <c r="J29" t="n">
-        <v>110.49</v>
+        <v>103.76</v>
       </c>
       <c r="K29" t="n">
-        <v>4.28</v>
+        <v>14.7</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3115</v>
+        <v>0.2979</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1546</v>
+        <v>0.1497</v>
       </c>
       <c r="N29" t="n">
-        <v>-1.6</v>
+        <v>6.2</v>
       </c>
       <c r="O29" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="P29" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="Q29" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R29" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="S29" t="n">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="T29" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U29" t="n">
-        <v>1687.9</v>
+        <v>1554.6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1378</v>
+        <v>1120</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>South Florida</t>
+          <t>Auburn</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2527,68 +2527,68 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11b</t>
         </is>
       </c>
       <c r="E30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G30" t="n">
-        <v>1709.5</v>
+        <v>1831.7</v>
       </c>
       <c r="H30" t="n">
-        <v>9.3651</v>
+        <v>-7.7196</v>
       </c>
       <c r="I30" t="n">
-        <v>115.67</v>
+        <v>119.16</v>
       </c>
       <c r="J30" t="n">
-        <v>102.39</v>
+        <v>114.92</v>
       </c>
       <c r="K30" t="n">
-        <v>13.28</v>
+        <v>4.25</v>
       </c>
       <c r="L30" t="n">
-        <v>0.336</v>
+        <v>0.3497</v>
       </c>
       <c r="M30" t="n">
-        <v>0.1478</v>
+        <v>0.1459</v>
       </c>
       <c r="N30" t="n">
-        <v>15.4</v>
+        <v>-3</v>
       </c>
       <c r="O30" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="P30" t="n">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="Q30" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="R30" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="S30" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="T30" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="U30" t="n">
-        <v>1558.8</v>
+        <v>1758.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1423</v>
+        <v>1463</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>UNC Wilmington</t>
+          <t>Yale</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2598,68 +2598,68 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E31" t="b">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G31" t="n">
-        <v>1681</v>
+        <v>1720.2</v>
       </c>
       <c r="H31" t="n">
-        <v>2.0383</v>
+        <v>1.1161</v>
       </c>
       <c r="I31" t="n">
-        <v>115.35</v>
+        <v>120.93</v>
       </c>
       <c r="J31" t="n">
-        <v>102.31</v>
+        <v>107.17</v>
       </c>
       <c r="K31" t="n">
-        <v>13.04</v>
+        <v>13.77</v>
       </c>
       <c r="L31" t="n">
-        <v>0.3159</v>
+        <v>0.2847</v>
       </c>
       <c r="M31" t="n">
-        <v>0.1414</v>
+        <v>0.1362</v>
       </c>
       <c r="N31" t="n">
-        <v>10.8</v>
+        <v>6.6</v>
       </c>
       <c r="O31" t="n">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="P31" t="n">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="Q31" t="n">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="R31" t="n">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="S31" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="T31" t="n">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="U31" t="n">
-        <v>1429</v>
+        <v>1457.4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1190</v>
+        <v>1251</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ETSU</t>
+          <t>Liberty</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E32" t="b">
@@ -2679,58 +2679,58 @@
         <v>124</v>
       </c>
       <c r="G32" t="n">
-        <v>1515.6</v>
+        <v>1733.1</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5387999999999999</v>
+        <v>3.2041</v>
       </c>
       <c r="I32" t="n">
-        <v>116.98</v>
+        <v>117.83</v>
       </c>
       <c r="J32" t="n">
-        <v>105.72</v>
+        <v>110.75</v>
       </c>
       <c r="K32" t="n">
-        <v>11.26</v>
+        <v>7.08</v>
       </c>
       <c r="L32" t="n">
-        <v>0.2696</v>
+        <v>0.1699</v>
       </c>
       <c r="M32" t="n">
-        <v>0.1444</v>
+        <v>0.1316</v>
       </c>
       <c r="N32" t="n">
-        <v>3.8</v>
+        <v>-5</v>
       </c>
       <c r="O32" t="n">
-        <v>140</v>
+        <v>111</v>
       </c>
       <c r="P32" t="n">
-        <v>149</v>
+        <v>87</v>
       </c>
       <c r="Q32" t="n">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="R32" t="n">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="S32" t="n">
-        <v>151</v>
+        <v>59</v>
       </c>
       <c r="T32" t="n">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="U32" t="n">
-        <v>1416.1</v>
+        <v>1485.6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1146</v>
+        <v>1414</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Cent Arkansas</t>
+          <t>UC Irvine</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E33" t="b">
@@ -2750,58 +2750,58 @@
         <v>124</v>
       </c>
       <c r="G33" t="n">
-        <v>1369.9</v>
+        <v>1614.5</v>
       </c>
       <c r="H33" t="n">
-        <v>3.1128</v>
+        <v>2.2068</v>
       </c>
       <c r="I33" t="n">
-        <v>112.04</v>
+        <v>103.59</v>
       </c>
       <c r="J33" t="n">
-        <v>106.14</v>
+        <v>96.37</v>
       </c>
       <c r="K33" t="n">
-        <v>5.91</v>
+        <v>7.22</v>
       </c>
       <c r="L33" t="n">
-        <v>0.271</v>
+        <v>0.2658</v>
       </c>
       <c r="M33" t="n">
-        <v>0.1505</v>
+        <v>0.1712</v>
       </c>
       <c r="N33" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="O33" t="n">
-        <v>154</v>
+        <v>109</v>
       </c>
       <c r="P33" t="n">
-        <v>197</v>
+        <v>122</v>
       </c>
       <c r="Q33" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="R33" t="n">
-        <v>147</v>
+        <v>115</v>
       </c>
       <c r="S33" t="n">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="T33" t="n">
-        <v>164</v>
+        <v>119</v>
       </c>
       <c r="U33" t="n">
-        <v>1437.1</v>
+        <v>1471.2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1224</v>
+        <v>1340</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Howard</t>
+          <t>Portland St</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2811,68 +2811,68 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>16a</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G34" t="n">
-        <v>1409</v>
+        <v>1458.3</v>
       </c>
       <c r="H34" t="n">
-        <v>3.2279</v>
+        <v>2.128</v>
       </c>
       <c r="I34" t="n">
-        <v>109.08</v>
+        <v>105.36</v>
       </c>
       <c r="J34" t="n">
-        <v>98.81</v>
+        <v>101.08</v>
       </c>
       <c r="K34" t="n">
-        <v>10.27</v>
+        <v>4.28</v>
       </c>
       <c r="L34" t="n">
-        <v>0.3126</v>
+        <v>0.2592</v>
       </c>
       <c r="M34" t="n">
-        <v>0.1855</v>
+        <v>0.1706</v>
       </c>
       <c r="N34" t="n">
-        <v>23.6</v>
+        <v>0.2</v>
       </c>
       <c r="O34" t="n">
-        <v>199</v>
+        <v>159</v>
       </c>
       <c r="P34" t="n">
-        <v>260</v>
+        <v>158</v>
       </c>
       <c r="Q34" t="n">
-        <v>277</v>
+        <v>174</v>
       </c>
       <c r="R34" t="n">
-        <v>196</v>
+        <v>167</v>
       </c>
       <c r="S34" t="n">
-        <v>237</v>
+        <v>124</v>
       </c>
       <c r="T34" t="n">
-        <v>202</v>
+        <v>151</v>
       </c>
       <c r="U34" t="n">
-        <v>1380.6</v>
+        <v>1416.6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1126</v>
+        <v>1250</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bethune-Cookman</t>
+          <t>Lehigh</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>16b</t>
+          <t>16a</t>
         </is>
       </c>
       <c r="E35" t="b">
@@ -2892,129 +2892,129 @@
         <v>122</v>
       </c>
       <c r="G35" t="n">
-        <v>1375.4</v>
+        <v>1320.1</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9205</v>
+        <v>-0.7048</v>
       </c>
       <c r="I35" t="n">
-        <v>104.96</v>
+        <v>104.37</v>
       </c>
       <c r="J35" t="n">
-        <v>108.7</v>
+        <v>108.74</v>
       </c>
       <c r="K35" t="n">
-        <v>-3.74</v>
+        <v>-4.37</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2778</v>
+        <v>0.2183</v>
       </c>
       <c r="M35" t="n">
-        <v>0.1862</v>
+        <v>0.1735</v>
       </c>
       <c r="N35" t="n">
-        <v>4.8</v>
+        <v>-0.4</v>
       </c>
       <c r="O35" t="n">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="P35" t="n">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="Q35" t="n">
-        <v>256</v>
+        <v>290</v>
       </c>
       <c r="R35" t="n">
-        <v>208</v>
+        <v>289</v>
       </c>
       <c r="S35" t="n">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="T35" t="n">
-        <v>246</v>
+        <v>290</v>
       </c>
       <c r="U35" t="n">
-        <v>1436.6</v>
+        <v>1399.1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1276</v>
+        <v>1126</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Bethune-Cookman</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>16b</t>
         </is>
       </c>
       <c r="E36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
         <v>122</v>
       </c>
       <c r="G36" t="n">
-        <v>2181.2</v>
+        <v>1375.4</v>
       </c>
       <c r="H36" t="n">
-        <v>7.6139</v>
+        <v>0.9205</v>
       </c>
       <c r="I36" t="n">
-        <v>121.54</v>
+        <v>104.96</v>
       </c>
       <c r="J36" t="n">
-        <v>95.23</v>
+        <v>108.7</v>
       </c>
       <c r="K36" t="n">
-        <v>26.31</v>
+        <v>-3.74</v>
       </c>
       <c r="L36" t="n">
-        <v>0.2642</v>
+        <v>0.2778</v>
       </c>
       <c r="M36" t="n">
-        <v>0.1678</v>
+        <v>0.1862</v>
       </c>
       <c r="N36" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="O36" t="n">
-        <v>2</v>
+        <v>233</v>
       </c>
       <c r="P36" t="n">
-        <v>3</v>
+        <v>267</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>256</v>
       </c>
       <c r="R36" t="n">
-        <v>1</v>
+        <v>208</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>224</v>
       </c>
       <c r="T36" t="n">
-        <v>2</v>
+        <v>246</v>
       </c>
       <c r="U36" t="n">
-        <v>1758.2</v>
+        <v>1436.6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1163</v>
+        <v>1276</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Connecticut</t>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3024,68 +3024,68 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="E37" t="b">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G37" t="n">
-        <v>2064.2</v>
+        <v>2181.2</v>
       </c>
       <c r="H37" t="n">
-        <v>8.950200000000001</v>
+        <v>7.6139</v>
       </c>
       <c r="I37" t="n">
-        <v>116.34</v>
+        <v>121.54</v>
       </c>
       <c r="J37" t="n">
-        <v>97.40000000000001</v>
+        <v>95.23</v>
       </c>
       <c r="K37" t="n">
-        <v>18.93</v>
+        <v>26.31</v>
       </c>
       <c r="L37" t="n">
-        <v>0.2937</v>
+        <v>0.2642</v>
       </c>
       <c r="M37" t="n">
-        <v>0.1558</v>
+        <v>0.1678</v>
       </c>
       <c r="N37" t="n">
         <v>6.6</v>
       </c>
       <c r="O37" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T37" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="U37" t="n">
-        <v>1660.9</v>
+        <v>1758.2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1345</v>
+        <v>1163</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Purdue</t>
+          <t>Connecticut</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="E38" t="b">
@@ -3105,58 +3105,58 @@
         <v>124</v>
       </c>
       <c r="G38" t="n">
-        <v>1955.6</v>
+        <v>2064.2</v>
       </c>
       <c r="H38" t="n">
-        <v>0.3963</v>
+        <v>8.950200000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>124.64</v>
+        <v>116.34</v>
       </c>
       <c r="J38" t="n">
-        <v>107.6</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>17.04</v>
+        <v>18.93</v>
       </c>
       <c r="L38" t="n">
-        <v>0.3051</v>
+        <v>0.2937</v>
       </c>
       <c r="M38" t="n">
-        <v>0.1348</v>
+        <v>0.1558</v>
       </c>
       <c r="N38" t="n">
-        <v>3.8</v>
+        <v>6.6</v>
       </c>
       <c r="O38" t="n">
+        <v>10</v>
+      </c>
+      <c r="P38" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>16</v>
+      </c>
+      <c r="R38" t="n">
+        <v>9</v>
+      </c>
+      <c r="S38" t="n">
+        <v>4</v>
+      </c>
+      <c r="T38" t="n">
         <v>8</v>
       </c>
-      <c r="P38" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>9</v>
-      </c>
-      <c r="R38" t="n">
-        <v>8</v>
-      </c>
-      <c r="S38" t="n">
-        <v>7</v>
-      </c>
-      <c r="T38" t="n">
-        <v>9</v>
-      </c>
       <c r="U38" t="n">
-        <v>1746.9</v>
+        <v>1660.9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1438</v>
+        <v>1345</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>Purdue</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="E39" t="b">
@@ -3176,58 +3176,58 @@
         <v>124</v>
       </c>
       <c r="G39" t="n">
-        <v>1956.5</v>
+        <v>1955.6</v>
       </c>
       <c r="H39" t="n">
-        <v>13.4946</v>
+        <v>0.3963</v>
       </c>
       <c r="I39" t="n">
-        <v>118.84</v>
+        <v>124.64</v>
       </c>
       <c r="J39" t="n">
-        <v>100.06</v>
+        <v>107.6</v>
       </c>
       <c r="K39" t="n">
-        <v>18.77</v>
+        <v>17.04</v>
       </c>
       <c r="L39" t="n">
-        <v>0.3168</v>
+        <v>0.3051</v>
       </c>
       <c r="M39" t="n">
-        <v>0.1532</v>
+        <v>0.1348</v>
       </c>
       <c r="N39" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="O39" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="P39" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="Q39" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="R39" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T39" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="U39" t="n">
-        <v>1639.2</v>
+        <v>1746.9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1397</v>
+        <v>1242</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>04</t>
         </is>
       </c>
       <c r="E40" t="b">
@@ -3247,58 +3247,58 @@
         <v>124</v>
       </c>
       <c r="G40" t="n">
-        <v>1898.6</v>
+        <v>1973.7</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.6704</v>
+        <v>11.337</v>
       </c>
       <c r="I40" t="n">
-        <v>117.06</v>
+        <v>111.61</v>
       </c>
       <c r="J40" t="n">
-        <v>101.96</v>
+        <v>100.9</v>
       </c>
       <c r="K40" t="n">
-        <v>15.09</v>
+        <v>10.71</v>
       </c>
       <c r="L40" t="n">
-        <v>0.3583</v>
+        <v>0.2487</v>
       </c>
       <c r="M40" t="n">
-        <v>0.1671</v>
+        <v>0.1523</v>
       </c>
       <c r="N40" t="n">
-        <v>2.6</v>
+        <v>-3.4</v>
       </c>
       <c r="O40" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P40" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q40" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R40" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="S40" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="T40" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="U40" t="n">
-        <v>1706.1</v>
+        <v>1772.3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1314</v>
+        <v>1435</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Vanderbilt</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>05</t>
         </is>
       </c>
       <c r="E41" t="b">
@@ -3318,58 +3318,58 @@
         <v>124</v>
       </c>
       <c r="G41" t="n">
-        <v>1917.6</v>
+        <v>1935.7</v>
       </c>
       <c r="H41" t="n">
-        <v>2.3735</v>
+        <v>2.1989</v>
       </c>
       <c r="I41" t="n">
-        <v>115.09</v>
+        <v>121.8</v>
       </c>
       <c r="J41" t="n">
-        <v>103.39</v>
+        <v>105.67</v>
       </c>
       <c r="K41" t="n">
-        <v>11.71</v>
+        <v>16.12</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2653</v>
+        <v>0.2802</v>
       </c>
       <c r="M41" t="n">
-        <v>0.14</v>
+        <v>0.1278</v>
       </c>
       <c r="N41" t="n">
-        <v>2.4</v>
+        <v>-0.6</v>
       </c>
       <c r="O41" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="P41" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q41" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="R41" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="S41" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="T41" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="U41" t="n">
-        <v>1676</v>
+        <v>1694.9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1208</v>
+        <v>1314</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>06</t>
         </is>
       </c>
       <c r="E42" t="b">
@@ -3389,58 +3389,58 @@
         <v>124</v>
       </c>
       <c r="G42" t="n">
-        <v>1816.9</v>
+        <v>1917.6</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2065</v>
+        <v>2.3735</v>
       </c>
       <c r="I42" t="n">
-        <v>121.14</v>
+        <v>115.09</v>
       </c>
       <c r="J42" t="n">
-        <v>107.06</v>
+        <v>103.39</v>
       </c>
       <c r="K42" t="n">
-        <v>14.09</v>
+        <v>11.71</v>
       </c>
       <c r="L42" t="n">
-        <v>0.3227</v>
+        <v>0.2653</v>
       </c>
       <c r="M42" t="n">
-        <v>0.1388</v>
+        <v>0.14</v>
       </c>
       <c r="N42" t="n">
-        <v>7.6</v>
+        <v>2.4</v>
       </c>
       <c r="O42" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="P42" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="Q42" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="R42" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="S42" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="T42" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="U42" t="n">
-        <v>1643</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1387</v>
+        <v>1246</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>St Louis</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>07</t>
         </is>
       </c>
       <c r="E43" t="b">
@@ -3460,58 +3460,58 @@
         <v>124</v>
       </c>
       <c r="G43" t="n">
-        <v>1807.8</v>
+        <v>1881.8</v>
       </c>
       <c r="H43" t="n">
-        <v>9.839</v>
+        <v>5.4881</v>
       </c>
       <c r="I43" t="n">
-        <v>120.36</v>
+        <v>116.58</v>
       </c>
       <c r="J43" t="n">
-        <v>98.52</v>
+        <v>106.11</v>
       </c>
       <c r="K43" t="n">
-        <v>21.84</v>
+        <v>10.47</v>
       </c>
       <c r="L43" t="n">
-        <v>0.2436</v>
+        <v>0.3117</v>
       </c>
       <c r="M43" t="n">
-        <v>0.1686</v>
+        <v>0.1455</v>
       </c>
       <c r="N43" t="n">
-        <v>-0.4</v>
+        <v>0.8</v>
       </c>
       <c r="O43" t="n">
+        <v>25</v>
+      </c>
+      <c r="P43" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>23</v>
+      </c>
+      <c r="R43" t="n">
         <v>27</v>
       </c>
-      <c r="P43" t="n">
-        <v>40</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>25</v>
-      </c>
-      <c r="R43" t="n">
-        <v>24</v>
-      </c>
       <c r="S43" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="T43" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="U43" t="n">
-        <v>1512.1</v>
+        <v>1728.4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1395</v>
+        <v>1155</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>TCU</t>
+          <t>Clemson</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>08</t>
         </is>
       </c>
       <c r="E44" t="b">
@@ -3531,58 +3531,58 @@
         <v>124</v>
       </c>
       <c r="G44" t="n">
-        <v>1836.3</v>
+        <v>1838.2</v>
       </c>
       <c r="H44" t="n">
-        <v>6.8916</v>
+        <v>3.3876</v>
       </c>
       <c r="I44" t="n">
-        <v>110.72</v>
+        <v>112.83</v>
       </c>
       <c r="J44" t="n">
-        <v>101.25</v>
+        <v>100.58</v>
       </c>
       <c r="K44" t="n">
-        <v>9.460000000000001</v>
+        <v>12.25</v>
       </c>
       <c r="L44" t="n">
-        <v>0.3192</v>
+        <v>0.2488</v>
       </c>
       <c r="M44" t="n">
-        <v>0.1507</v>
+        <v>0.1395</v>
       </c>
       <c r="N44" t="n">
-        <v>9</v>
+        <v>-1.8</v>
       </c>
       <c r="O44" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="P44" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="Q44" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="R44" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="S44" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="T44" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="U44" t="n">
-        <v>1679.3</v>
+        <v>1641.6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1301</v>
+        <v>1387</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NC State</t>
+          <t>St Louis</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>09</t>
         </is>
       </c>
       <c r="E45" t="b">
@@ -3602,58 +3602,58 @@
         <v>124</v>
       </c>
       <c r="G45" t="n">
-        <v>1735.9</v>
+        <v>1807.8</v>
       </c>
       <c r="H45" t="n">
-        <v>7.7247</v>
+        <v>9.839</v>
       </c>
       <c r="I45" t="n">
-        <v>118.75</v>
+        <v>120.36</v>
       </c>
       <c r="J45" t="n">
-        <v>108.16</v>
+        <v>98.52</v>
       </c>
       <c r="K45" t="n">
-        <v>10.59</v>
+        <v>21.84</v>
       </c>
       <c r="L45" t="n">
-        <v>0.2829</v>
+        <v>0.2436</v>
       </c>
       <c r="M45" t="n">
-        <v>0.1296</v>
+        <v>0.1686</v>
       </c>
       <c r="N45" t="n">
-        <v>-8.199999999999999</v>
+        <v>-0.4</v>
       </c>
       <c r="O45" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="P45" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q45" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="R45" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="S45" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="T45" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="U45" t="n">
-        <v>1675.6</v>
+        <v>1512.1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1433</v>
+        <v>1234</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>VCU</t>
+          <t>Iowa</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3663,68 +3663,68 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>11a</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G46" t="n">
-        <v>1739.9</v>
+        <v>1851.2</v>
       </c>
       <c r="H46" t="n">
-        <v>2.9764</v>
+        <v>4.4379</v>
       </c>
       <c r="I46" t="n">
-        <v>118.46</v>
+        <v>119.28</v>
       </c>
       <c r="J46" t="n">
         <v>103.76</v>
       </c>
       <c r="K46" t="n">
-        <v>14.7</v>
+        <v>15.52</v>
       </c>
       <c r="L46" t="n">
-        <v>0.2979</v>
+        <v>0.2925</v>
       </c>
       <c r="M46" t="n">
-        <v>0.1497</v>
+        <v>0.1388</v>
       </c>
       <c r="N46" t="n">
-        <v>6.2</v>
+        <v>0.8</v>
       </c>
       <c r="O46" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="P46" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="Q46" t="n">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="R46" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="S46" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="T46" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="U46" t="n">
-        <v>1554.6</v>
+        <v>1708.5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1120</v>
+        <v>1275</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Auburn</t>
+          <t>Miami OH</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3734,68 +3734,68 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>11b</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G47" t="n">
-        <v>1831.7</v>
+        <v>1775.2</v>
       </c>
       <c r="H47" t="n">
-        <v>-7.7196</v>
+        <v>9.651999999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>119.16</v>
+        <v>120.89</v>
       </c>
       <c r="J47" t="n">
-        <v>114.92</v>
+        <v>105.23</v>
       </c>
       <c r="K47" t="n">
-        <v>4.25</v>
+        <v>15.66</v>
       </c>
       <c r="L47" t="n">
-        <v>0.3497</v>
+        <v>0.2107</v>
       </c>
       <c r="M47" t="n">
-        <v>0.1459</v>
+        <v>0.1402</v>
       </c>
       <c r="N47" t="n">
-        <v>-3</v>
+        <v>6</v>
       </c>
       <c r="O47" t="n">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="P47" t="n">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="Q47" t="n">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="R47" t="n">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="S47" t="n">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="T47" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="U47" t="n">
-        <v>1758.3</v>
+        <v>1414.6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1251</v>
+        <v>1219</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Liberty</t>
+          <t>High Point</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3815,49 +3815,49 @@
         <v>124</v>
       </c>
       <c r="G48" t="n">
-        <v>1733.1</v>
+        <v>1620.5</v>
       </c>
       <c r="H48" t="n">
-        <v>3.2041</v>
+        <v>-1.0234</v>
       </c>
       <c r="I48" t="n">
-        <v>117.83</v>
+        <v>121.05</v>
       </c>
       <c r="J48" t="n">
-        <v>110.75</v>
+        <v>100.19</v>
       </c>
       <c r="K48" t="n">
-        <v>7.08</v>
+        <v>20.86</v>
       </c>
       <c r="L48" t="n">
-        <v>0.1699</v>
+        <v>0.3114</v>
       </c>
       <c r="M48" t="n">
-        <v>0.1316</v>
+        <v>0.128</v>
       </c>
       <c r="N48" t="n">
-        <v>-5</v>
+        <v>12</v>
       </c>
       <c r="O48" t="n">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="P48" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="Q48" t="n">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="R48" t="n">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="S48" t="n">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="T48" t="n">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="U48" t="n">
-        <v>1485.6</v>
+        <v>1377.7</v>
       </c>
     </row>
     <row r="49">
@@ -3933,11 +3933,11 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1298</v>
+        <v>1220</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Navy</t>
+          <t>Hofstra</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3954,52 +3954,52 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G50" t="n">
-        <v>1430.4</v>
+        <v>1567.8</v>
       </c>
       <c r="H50" t="n">
-        <v>3.2549</v>
+        <v>4.0005</v>
       </c>
       <c r="I50" t="n">
-        <v>113.28</v>
+        <v>112.7</v>
       </c>
       <c r="J50" t="n">
-        <v>98.59</v>
+        <v>102.71</v>
       </c>
       <c r="K50" t="n">
-        <v>14.69</v>
+        <v>10</v>
       </c>
       <c r="L50" t="n">
-        <v>0.2673</v>
+        <v>0.3013</v>
       </c>
       <c r="M50" t="n">
-        <v>0.1673</v>
+        <v>0.1549</v>
       </c>
       <c r="N50" t="n">
-        <v>17.8</v>
+        <v>13.2</v>
       </c>
       <c r="O50" t="n">
-        <v>136</v>
+        <v>92</v>
       </c>
       <c r="P50" t="n">
-        <v>164</v>
+        <v>127</v>
       </c>
       <c r="Q50" t="n">
-        <v>143</v>
+        <v>95</v>
       </c>
       <c r="R50" t="n">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="S50" t="n">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="T50" t="n">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="U50" t="n">
-        <v>1375.2</v>
+        <v>1478.9</v>
       </c>
     </row>
     <row r="51">
@@ -4075,11 +4075,11 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1420</v>
+        <v>1224</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>UMBC</t>
+          <t>Howard</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4096,52 +4096,52 @@
         <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G52" t="n">
-        <v>1391.7</v>
+        <v>1409</v>
       </c>
       <c r="H52" t="n">
-        <v>1.2162</v>
+        <v>3.2279</v>
       </c>
       <c r="I52" t="n">
-        <v>112.51</v>
+        <v>109.08</v>
       </c>
       <c r="J52" t="n">
-        <v>102.24</v>
+        <v>98.81</v>
       </c>
       <c r="K52" t="n">
-        <v>10.26</v>
+        <v>10.27</v>
       </c>
       <c r="L52" t="n">
-        <v>0.2126</v>
+        <v>0.3126</v>
       </c>
       <c r="M52" t="n">
-        <v>0.1361</v>
+        <v>0.1855</v>
       </c>
       <c r="N52" t="n">
-        <v>18.8</v>
+        <v>23.6</v>
       </c>
       <c r="O52" t="n">
-        <v>221</v>
+        <v>199</v>
       </c>
       <c r="P52" t="n">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="Q52" t="n">
-        <v>200</v>
+        <v>277</v>
       </c>
       <c r="R52" t="n">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="S52" t="n">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="T52" t="n">
-        <v>223</v>
+        <v>202</v>
       </c>
       <c r="U52" t="n">
-        <v>1364.8</v>
+        <v>1380.6</v>
       </c>
     </row>
     <row r="53">
@@ -4359,11 +4359,11 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1211</v>
+        <v>1104</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Gonzaga</t>
+          <t>Alabama</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4380,61 +4380,61 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="G56" t="n">
-        <v>2061.6</v>
+        <v>1975.1</v>
       </c>
       <c r="H56" t="n">
-        <v>6.7538</v>
+        <v>-1.4869</v>
       </c>
       <c r="I56" t="n">
-        <v>120.35</v>
+        <v>122.11</v>
       </c>
       <c r="J56" t="n">
-        <v>93.25</v>
+        <v>110.78</v>
       </c>
       <c r="K56" t="n">
-        <v>27.1</v>
+        <v>11.33</v>
       </c>
       <c r="L56" t="n">
-        <v>0.2992</v>
+        <v>0.2853</v>
       </c>
       <c r="M56" t="n">
-        <v>0.1329</v>
+        <v>0.1289</v>
       </c>
       <c r="N56" t="n">
-        <v>13.6</v>
+        <v>7.2</v>
       </c>
       <c r="O56" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="P56" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q56" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="R56" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T56" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="U56" t="n">
-        <v>1597.9</v>
+        <v>1772.1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1403</v>
+        <v>1211</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Texas Tech</t>
+          <t>Gonzaga</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4451,61 +4451,61 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="G57" t="n">
-        <v>2025.5</v>
+        <v>2061.6</v>
       </c>
       <c r="H57" t="n">
-        <v>10.1327</v>
+        <v>6.7538</v>
       </c>
       <c r="I57" t="n">
-        <v>118.86</v>
+        <v>120.35</v>
       </c>
       <c r="J57" t="n">
-        <v>106.69</v>
+        <v>93.25</v>
       </c>
       <c r="K57" t="n">
-        <v>12.16</v>
+        <v>27.1</v>
       </c>
       <c r="L57" t="n">
-        <v>0.2944</v>
+        <v>0.2992</v>
       </c>
       <c r="M57" t="n">
-        <v>0.155</v>
+        <v>0.1329</v>
       </c>
       <c r="N57" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="O57" t="n">
+        <v>12</v>
+      </c>
+      <c r="P57" t="n">
         <v>7</v>
       </c>
-      <c r="O57" t="n">
+      <c r="Q57" t="n">
+        <v>17</v>
+      </c>
+      <c r="R57" t="n">
         <v>13</v>
       </c>
-      <c r="P57" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>11</v>
-      </c>
-      <c r="R57" t="n">
-        <v>11</v>
-      </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T57" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="U57" t="n">
-        <v>1762.7</v>
+        <v>1597.9</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1435</v>
+        <v>1397</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Vanderbilt</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4525,58 +4525,58 @@
         <v>124</v>
       </c>
       <c r="G58" t="n">
-        <v>1935.7</v>
+        <v>1898.6</v>
       </c>
       <c r="H58" t="n">
-        <v>2.1989</v>
+        <v>-1.6704</v>
       </c>
       <c r="I58" t="n">
-        <v>121.8</v>
+        <v>117.06</v>
       </c>
       <c r="J58" t="n">
-        <v>105.67</v>
+        <v>101.96</v>
       </c>
       <c r="K58" t="n">
-        <v>16.12</v>
+        <v>15.09</v>
       </c>
       <c r="L58" t="n">
-        <v>0.2802</v>
+        <v>0.3583</v>
       </c>
       <c r="M58" t="n">
-        <v>0.1278</v>
+        <v>0.1671</v>
       </c>
       <c r="N58" t="n">
-        <v>-0.6</v>
+        <v>2.6</v>
       </c>
       <c r="O58" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="P58" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q58" t="n">
         <v>20</v>
       </c>
-      <c r="Q58" t="n">
-        <v>18</v>
-      </c>
       <c r="R58" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="S58" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="T58" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="U58" t="n">
-        <v>1694.9</v>
+        <v>1706.1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1246</v>
+        <v>1140</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>BYU</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4596,58 +4596,58 @@
         <v>124</v>
       </c>
       <c r="G59" t="n">
-        <v>1881.8</v>
+        <v>1924.5</v>
       </c>
       <c r="H59" t="n">
-        <v>5.4881</v>
+        <v>1.6354</v>
       </c>
       <c r="I59" t="n">
-        <v>116.58</v>
+        <v>118.39</v>
       </c>
       <c r="J59" t="n">
-        <v>106.11</v>
+        <v>106.82</v>
       </c>
       <c r="K59" t="n">
-        <v>10.47</v>
+        <v>11.57</v>
       </c>
       <c r="L59" t="n">
-        <v>0.3117</v>
+        <v>0.3034</v>
       </c>
       <c r="M59" t="n">
-        <v>0.1455</v>
+        <v>0.1419</v>
       </c>
       <c r="N59" t="n">
-        <v>0.8</v>
+        <v>-5.4</v>
       </c>
       <c r="O59" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P59" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q59" t="n">
         <v>22</v>
       </c>
-      <c r="Q59" t="n">
+      <c r="R59" t="n">
+        <v>22</v>
+      </c>
+      <c r="S59" t="n">
+        <v>21</v>
+      </c>
+      <c r="T59" t="n">
         <v>23</v>
       </c>
-      <c r="R59" t="n">
-        <v>27</v>
-      </c>
-      <c r="S59" t="n">
-        <v>33</v>
-      </c>
-      <c r="T59" t="n">
-        <v>27</v>
-      </c>
       <c r="U59" t="n">
-        <v>1728.4</v>
+        <v>1726.9</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1140</v>
+        <v>1274</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BYU</t>
+          <t>Miami FL</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4667,58 +4667,58 @@
         <v>124</v>
       </c>
       <c r="G60" t="n">
-        <v>1924.5</v>
+        <v>1761</v>
       </c>
       <c r="H60" t="n">
-        <v>1.6354</v>
+        <v>12.4806</v>
       </c>
       <c r="I60" t="n">
-        <v>118.39</v>
+        <v>118.15</v>
       </c>
       <c r="J60" t="n">
-        <v>106.82</v>
+        <v>101.88</v>
       </c>
       <c r="K60" t="n">
-        <v>11.57</v>
+        <v>16.27</v>
       </c>
       <c r="L60" t="n">
-        <v>0.3034</v>
+        <v>0.3077</v>
       </c>
       <c r="M60" t="n">
-        <v>0.1419</v>
+        <v>0.1596</v>
       </c>
       <c r="N60" t="n">
-        <v>-5.4</v>
+        <v>6.8</v>
       </c>
       <c r="O60" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="P60" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="Q60" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="R60" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="S60" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="T60" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="U60" t="n">
-        <v>1726.9</v>
+        <v>1617.1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1155</v>
+        <v>1417</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Clemson</t>
+          <t>UCLA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4738,58 +4738,58 @@
         <v>124</v>
       </c>
       <c r="G61" t="n">
-        <v>1838.2</v>
+        <v>1859.1</v>
       </c>
       <c r="H61" t="n">
-        <v>3.3876</v>
+        <v>2.2498</v>
       </c>
       <c r="I61" t="n">
-        <v>112.83</v>
+        <v>117.64</v>
       </c>
       <c r="J61" t="n">
-        <v>100.58</v>
+        <v>107.04</v>
       </c>
       <c r="K61" t="n">
-        <v>12.25</v>
+        <v>10.59</v>
       </c>
       <c r="L61" t="n">
-        <v>0.2488</v>
+        <v>0.2985</v>
       </c>
       <c r="M61" t="n">
-        <v>0.1395</v>
+        <v>0.1288</v>
       </c>
       <c r="N61" t="n">
-        <v>-1.8</v>
+        <v>11.2</v>
       </c>
       <c r="O61" t="n">
+        <v>41</v>
+      </c>
+      <c r="P61" t="n">
         <v>36</v>
       </c>
-      <c r="P61" t="n">
-        <v>33</v>
-      </c>
       <c r="Q61" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="R61" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="S61" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="T61" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="U61" t="n">
-        <v>1641.6</v>
+        <v>1689.3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1417</v>
+        <v>1401</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>UCLA</t>
+          <t>Texas A&amp;M</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4809,58 +4809,58 @@
         <v>124</v>
       </c>
       <c r="G62" t="n">
-        <v>1859.1</v>
+        <v>1843.5</v>
       </c>
       <c r="H62" t="n">
-        <v>2.2498</v>
+        <v>4.536</v>
       </c>
       <c r="I62" t="n">
-        <v>117.64</v>
+        <v>117.79</v>
       </c>
       <c r="J62" t="n">
-        <v>107.04</v>
+        <v>106.34</v>
       </c>
       <c r="K62" t="n">
-        <v>10.59</v>
+        <v>11.45</v>
       </c>
       <c r="L62" t="n">
-        <v>0.2985</v>
+        <v>0.3067</v>
       </c>
       <c r="M62" t="n">
-        <v>0.1288</v>
+        <v>0.1399</v>
       </c>
       <c r="N62" t="n">
-        <v>11.2</v>
+        <v>-0.6</v>
       </c>
       <c r="O62" t="n">
+        <v>38</v>
+      </c>
+      <c r="P62" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>36</v>
+      </c>
+      <c r="R62" t="n">
+        <v>39</v>
+      </c>
+      <c r="S62" t="n">
         <v>41</v>
       </c>
-      <c r="P62" t="n">
-        <v>36</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>39</v>
-      </c>
-      <c r="R62" t="n">
-        <v>40</v>
-      </c>
-      <c r="S62" t="n">
-        <v>35</v>
-      </c>
       <c r="T62" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="U62" t="n">
-        <v>1689.3</v>
+        <v>1651.1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Texas A&amp;M</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4880,58 +4880,58 @@
         <v>124</v>
       </c>
       <c r="G63" t="n">
-        <v>1843.5</v>
+        <v>1757.7</v>
       </c>
       <c r="H63" t="n">
-        <v>4.536</v>
+        <v>2.865</v>
       </c>
       <c r="I63" t="n">
-        <v>117.79</v>
+        <v>120.37</v>
       </c>
       <c r="J63" t="n">
-        <v>106.34</v>
+        <v>111.34</v>
       </c>
       <c r="K63" t="n">
-        <v>11.45</v>
+        <v>9.02</v>
       </c>
       <c r="L63" t="n">
-        <v>0.3067</v>
+        <v>0.3098</v>
       </c>
       <c r="M63" t="n">
-        <v>0.1399</v>
+        <v>0.1494</v>
       </c>
       <c r="N63" t="n">
-        <v>-0.6</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="O63" t="n">
+        <v>29</v>
+      </c>
+      <c r="P63" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>34</v>
+      </c>
+      <c r="R63" t="n">
         <v>38</v>
       </c>
-      <c r="P63" t="n">
-        <v>34</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>36</v>
-      </c>
-      <c r="R63" t="n">
-        <v>39</v>
-      </c>
       <c r="S63" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="T63" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="U63" t="n">
-        <v>1651.1</v>
+        <v>1699.4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1275</v>
+        <v>1416</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Miami OH</t>
+          <t>UCF</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4951,58 +4951,58 @@
         <v>123</v>
       </c>
       <c r="G64" t="n">
-        <v>1775.2</v>
+        <v>1820.5</v>
       </c>
       <c r="H64" t="n">
-        <v>9.651999999999999</v>
+        <v>7.025</v>
       </c>
       <c r="I64" t="n">
-        <v>120.89</v>
+        <v>114.77</v>
       </c>
       <c r="J64" t="n">
-        <v>105.23</v>
+        <v>110.49</v>
       </c>
       <c r="K64" t="n">
-        <v>15.66</v>
+        <v>4.28</v>
       </c>
       <c r="L64" t="n">
-        <v>0.2107</v>
+        <v>0.3115</v>
       </c>
       <c r="M64" t="n">
-        <v>0.1402</v>
+        <v>0.1546</v>
       </c>
       <c r="N64" t="n">
-        <v>6</v>
+        <v>-1.6</v>
       </c>
       <c r="O64" t="n">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="P64" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="Q64" t="n">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="R64" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="S64" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="T64" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="U64" t="n">
-        <v>1414.6</v>
+        <v>1687.9</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1219</v>
+        <v>1320</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>High Point</t>
+          <t>Northern Iowa</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5022,58 +5022,58 @@
         <v>124</v>
       </c>
       <c r="G65" t="n">
-        <v>1620.5</v>
+        <v>1567</v>
       </c>
       <c r="H65" t="n">
-        <v>-1.0234</v>
+        <v>-3.9617</v>
       </c>
       <c r="I65" t="n">
-        <v>121.05</v>
+        <v>107.53</v>
       </c>
       <c r="J65" t="n">
-        <v>100.19</v>
+        <v>96.87</v>
       </c>
       <c r="K65" t="n">
-        <v>20.86</v>
+        <v>10.66</v>
       </c>
       <c r="L65" t="n">
-        <v>0.3114</v>
+        <v>0.214</v>
       </c>
       <c r="M65" t="n">
-        <v>0.128</v>
+        <v>0.1374</v>
       </c>
       <c r="N65" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O65" t="n">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="P65" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="Q65" t="n">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="R65" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="S65" t="n">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="T65" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="U65" t="n">
-        <v>1377.7</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1465</v>
+        <v>1430</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cal Baptist</t>
+          <t>Utah Valley</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5093,58 +5093,58 @@
         <v>124</v>
       </c>
       <c r="G66" t="n">
-        <v>1594.5</v>
+        <v>1637</v>
       </c>
       <c r="H66" t="n">
-        <v>1.5103</v>
+        <v>3.1528</v>
       </c>
       <c r="I66" t="n">
-        <v>107.31</v>
+        <v>111.58</v>
       </c>
       <c r="J66" t="n">
-        <v>99.48999999999999</v>
+        <v>100.45</v>
       </c>
       <c r="K66" t="n">
-        <v>7.82</v>
+        <v>11.12</v>
       </c>
       <c r="L66" t="n">
-        <v>0.3297</v>
+        <v>0.3056</v>
       </c>
       <c r="M66" t="n">
-        <v>0.1719</v>
+        <v>0.1962</v>
       </c>
       <c r="N66" t="n">
-        <v>10.8</v>
+        <v>6.6</v>
       </c>
       <c r="O66" t="n">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="P66" t="n">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="Q66" t="n">
-        <v>130</v>
+        <v>87</v>
       </c>
       <c r="R66" t="n">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="S66" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="T66" t="n">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="U66" t="n">
-        <v>1455.6</v>
+        <v>1455.5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1414</v>
+        <v>1407</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>UC Irvine</t>
+          <t>Troy</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5161,61 +5161,61 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="G67" t="n">
-        <v>1614.5</v>
+        <v>1593.7</v>
       </c>
       <c r="H67" t="n">
-        <v>2.2068</v>
+        <v>1.3343</v>
       </c>
       <c r="I67" t="n">
-        <v>103.59</v>
+        <v>112.11</v>
       </c>
       <c r="J67" t="n">
-        <v>96.37</v>
+        <v>106.85</v>
       </c>
       <c r="K67" t="n">
-        <v>7.22</v>
+        <v>5.26</v>
       </c>
       <c r="L67" t="n">
-        <v>0.2658</v>
+        <v>0.3162</v>
       </c>
       <c r="M67" t="n">
-        <v>0.1712</v>
+        <v>0.1601</v>
       </c>
       <c r="N67" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O67" t="n">
-        <v>109</v>
+        <v>156</v>
       </c>
       <c r="P67" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="Q67" t="n">
-        <v>110</v>
+        <v>139</v>
       </c>
       <c r="R67" t="n">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="S67" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="T67" t="n">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="U67" t="n">
-        <v>1471.2</v>
+        <v>1464.1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1227</v>
+        <v>1460</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>IL Chicago</t>
+          <t>Wright St</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5232,61 +5232,61 @@
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G68" t="n">
-        <v>1535.5</v>
+        <v>1464.5</v>
       </c>
       <c r="H68" t="n">
-        <v>2.1038</v>
+        <v>2.7711</v>
       </c>
       <c r="I68" t="n">
-        <v>108.47</v>
+        <v>115.65</v>
       </c>
       <c r="J68" t="n">
-        <v>102.47</v>
+        <v>109.07</v>
       </c>
       <c r="K68" t="n">
-        <v>6</v>
+        <v>6.58</v>
       </c>
       <c r="L68" t="n">
-        <v>0.3429</v>
+        <v>0.2992</v>
       </c>
       <c r="M68" t="n">
-        <v>0.1641</v>
+        <v>0.158</v>
       </c>
       <c r="N68" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="O68" t="n">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="P68" t="n">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="Q68" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="R68" t="n">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="S68" t="n">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="T68" t="n">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="U68" t="n">
-        <v>1506.5</v>
+        <v>1435.1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1340</v>
+        <v>1474</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Portland St</t>
+          <t>Queens NC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5303,52 +5303,52 @@
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="G69" t="n">
-        <v>1458.3</v>
+        <v>1424.9</v>
       </c>
       <c r="H69" t="n">
-        <v>2.128</v>
+        <v>0.9866</v>
       </c>
       <c r="I69" t="n">
-        <v>105.36</v>
+        <v>119.08</v>
       </c>
       <c r="J69" t="n">
-        <v>101.08</v>
+        <v>116.55</v>
       </c>
       <c r="K69" t="n">
-        <v>4.28</v>
+        <v>2.53</v>
       </c>
       <c r="L69" t="n">
-        <v>0.2592</v>
+        <v>0.2802</v>
       </c>
       <c r="M69" t="n">
-        <v>0.1706</v>
+        <v>0.1443</v>
       </c>
       <c r="N69" t="n">
-        <v>0.2</v>
+        <v>6.8</v>
       </c>
       <c r="O69" t="n">
-        <v>159</v>
+        <v>191</v>
       </c>
       <c r="P69" t="n">
-        <v>158</v>
+        <v>203</v>
       </c>
       <c r="Q69" t="n">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="R69" t="n">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="S69" t="n">
-        <v>124</v>
+        <v>192</v>
       </c>
       <c r="T69" t="n">
-        <v>151</v>
+        <v>201</v>
       </c>
       <c r="U69" t="n">
-        <v>1416.6</v>
+        <v>1433.6</v>
       </c>
     </row>
   </sheetData>

--- a/team_stats_2026.xlsx
+++ b/team_stats_2026.xlsx
@@ -617,31 +617,31 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G3" t="n">
-        <v>2057.8</v>
+        <v>2049.8</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2001</v>
+        <v>0.2376</v>
       </c>
       <c r="I3" t="n">
-        <v>117.41</v>
+        <v>117.05</v>
       </c>
       <c r="J3" t="n">
-        <v>100.06</v>
+        <v>100.92</v>
       </c>
       <c r="K3" t="n">
-        <v>17.36</v>
+        <v>16.13</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2989</v>
+        <v>0.2993</v>
       </c>
       <c r="M3" t="n">
-        <v>0.165</v>
+        <v>0.1615</v>
       </c>
       <c r="N3" t="n">
-        <v>9.6</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
         <v>9</v>
@@ -662,7 +662,7 @@
         <v>11</v>
       </c>
       <c r="U3" t="n">
-        <v>1707.1</v>
+        <v>1729.6</v>
       </c>
     </row>
     <row r="4">
@@ -1256,31 +1256,31 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="G12" t="n">
-        <v>1765.9</v>
+        <v>1768.3</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.7176</v>
+        <v>-0.4727</v>
       </c>
       <c r="I12" t="n">
-        <v>117.4</v>
+        <v>117.67</v>
       </c>
       <c r="J12" t="n">
-        <v>102.2</v>
+        <v>102.69</v>
       </c>
       <c r="K12" t="n">
-        <v>15.2</v>
+        <v>14.97</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3448</v>
+        <v>0.3472</v>
       </c>
       <c r="M12" t="n">
         <v>0.1494</v>
       </c>
       <c r="N12" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="O12" t="n">
         <v>37</v>
@@ -1301,7 +1301,7 @@
         <v>40</v>
       </c>
       <c r="U12" t="n">
-        <v>1571.8</v>
+        <v>1566.6</v>
       </c>
     </row>
     <row r="13">
@@ -1398,31 +1398,31 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G14" t="n">
-        <v>1709.5</v>
+        <v>1711.8</v>
       </c>
       <c r="H14" t="n">
-        <v>9.3651</v>
+        <v>9.207800000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>115.67</v>
+        <v>116.06</v>
       </c>
       <c r="J14" t="n">
-        <v>102.39</v>
+        <v>101.73</v>
       </c>
       <c r="K14" t="n">
-        <v>13.28</v>
+        <v>14.32</v>
       </c>
       <c r="L14" t="n">
-        <v>0.336</v>
+        <v>0.3392</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1478</v>
+        <v>0.1453</v>
       </c>
       <c r="N14" t="n">
-        <v>15.4</v>
+        <v>19.6</v>
       </c>
       <c r="O14" t="n">
         <v>52</v>
@@ -1443,7 +1443,7 @@
         <v>48</v>
       </c>
       <c r="U14" t="n">
-        <v>1558.8</v>
+        <v>1553.3</v>
       </c>
     </row>
     <row r="15">
@@ -1540,31 +1540,31 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G16" t="n">
-        <v>1515.6</v>
+        <v>1518.5</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5387999999999999</v>
+        <v>0.4929</v>
       </c>
       <c r="I16" t="n">
-        <v>116.98</v>
+        <v>116.45</v>
       </c>
       <c r="J16" t="n">
-        <v>105.72</v>
+        <v>105.53</v>
       </c>
       <c r="K16" t="n">
-        <v>11.26</v>
+        <v>10.92</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2696</v>
+        <v>0.268</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1444</v>
+        <v>0.1456</v>
       </c>
       <c r="N16" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="O16" t="n">
         <v>140</v>
@@ -1585,7 +1585,7 @@
         <v>128</v>
       </c>
       <c r="U16" t="n">
-        <v>1416.1</v>
+        <v>1416.5</v>
       </c>
     </row>
     <row r="17">
@@ -1895,31 +1895,31 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G21" t="n">
-        <v>1992.1</v>
+        <v>1999.6</v>
       </c>
       <c r="H21" t="n">
-        <v>11.5554</v>
+        <v>10.6735</v>
       </c>
       <c r="I21" t="n">
-        <v>115.07</v>
+        <v>115.4</v>
       </c>
       <c r="J21" t="n">
-        <v>98.04000000000001</v>
+        <v>97.95</v>
       </c>
       <c r="K21" t="n">
-        <v>17.03</v>
+        <v>17.45</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2419</v>
+        <v>0.2379</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1401</v>
+        <v>0.1402</v>
       </c>
       <c r="N21" t="n">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="O21" t="n">
         <v>11</v>
@@ -1940,7 +1940,7 @@
         <v>12</v>
       </c>
       <c r="U21" t="n">
-        <v>1659.3</v>
+        <v>1665.7</v>
       </c>
     </row>
     <row r="22">
@@ -2818,31 +2818,31 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="G34" t="n">
-        <v>1458.3</v>
+        <v>1460.1</v>
       </c>
       <c r="H34" t="n">
-        <v>2.128</v>
+        <v>2.001</v>
       </c>
       <c r="I34" t="n">
-        <v>105.36</v>
+        <v>105.77</v>
       </c>
       <c r="J34" t="n">
-        <v>101.08</v>
+        <v>101.47</v>
       </c>
       <c r="K34" t="n">
-        <v>4.28</v>
+        <v>4.29</v>
       </c>
       <c r="L34" t="n">
-        <v>0.2592</v>
+        <v>0.2576</v>
       </c>
       <c r="M34" t="n">
-        <v>0.1706</v>
+        <v>0.1661</v>
       </c>
       <c r="N34" t="n">
-        <v>0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="O34" t="n">
         <v>159</v>
@@ -2863,7 +2863,7 @@
         <v>151</v>
       </c>
       <c r="U34" t="n">
-        <v>1416.6</v>
+        <v>1413.3</v>
       </c>
     </row>
     <row r="35">
@@ -2889,31 +2889,31 @@
         <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G35" t="n">
-        <v>1320.1</v>
+        <v>1323.1</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7048</v>
+        <v>-0.5849</v>
       </c>
       <c r="I35" t="n">
-        <v>104.37</v>
+        <v>104.76</v>
       </c>
       <c r="J35" t="n">
-        <v>108.74</v>
+        <v>108.58</v>
       </c>
       <c r="K35" t="n">
-        <v>-4.37</v>
+        <v>-3.82</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2183</v>
+        <v>0.214</v>
       </c>
       <c r="M35" t="n">
-        <v>0.1735</v>
+        <v>0.1729</v>
       </c>
       <c r="N35" t="n">
-        <v>-0.4</v>
+        <v>5.6</v>
       </c>
       <c r="O35" t="n">
         <v>295</v>
@@ -2934,7 +2934,7 @@
         <v>290</v>
       </c>
       <c r="U35" t="n">
-        <v>1399.1</v>
+        <v>1401.7</v>
       </c>
     </row>
     <row r="36">
@@ -3031,31 +3031,31 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G37" t="n">
-        <v>2181.2</v>
+        <v>2189.2</v>
       </c>
       <c r="H37" t="n">
-        <v>7.6139</v>
+        <v>7.2681</v>
       </c>
       <c r="I37" t="n">
-        <v>121.54</v>
+        <v>121.97</v>
       </c>
       <c r="J37" t="n">
-        <v>95.23</v>
+        <v>95.94</v>
       </c>
       <c r="K37" t="n">
-        <v>26.31</v>
+        <v>26.03</v>
       </c>
       <c r="L37" t="n">
-        <v>0.2642</v>
+        <v>0.2632</v>
       </c>
       <c r="M37" t="n">
-        <v>0.1678</v>
+        <v>0.1657</v>
       </c>
       <c r="N37" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="O37" t="n">
         <v>2</v>
@@ -3076,7 +3076,7 @@
         <v>2</v>
       </c>
       <c r="U37" t="n">
-        <v>1758.2</v>
+        <v>1769.7</v>
       </c>
     </row>
     <row r="38">
@@ -3670,31 +3670,31 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G46" t="n">
-        <v>1851.2</v>
+        <v>1843.7</v>
       </c>
       <c r="H46" t="n">
-        <v>4.4379</v>
+        <v>4.0673</v>
       </c>
       <c r="I46" t="n">
-        <v>119.28</v>
+        <v>118.63</v>
       </c>
       <c r="J46" t="n">
-        <v>103.76</v>
+        <v>104.06</v>
       </c>
       <c r="K46" t="n">
-        <v>15.52</v>
+        <v>14.56</v>
       </c>
       <c r="L46" t="n">
-        <v>0.2925</v>
+        <v>0.288</v>
       </c>
       <c r="M46" t="n">
-        <v>0.1388</v>
+        <v>0.1446</v>
       </c>
       <c r="N46" t="n">
-        <v>0.8</v>
+        <v>-2</v>
       </c>
       <c r="O46" t="n">
         <v>24</v>
@@ -3715,7 +3715,7 @@
         <v>28</v>
       </c>
       <c r="U46" t="n">
-        <v>1708.5</v>
+        <v>1715.1</v>
       </c>
     </row>
     <row r="47">
@@ -3812,31 +3812,31 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G48" t="n">
-        <v>1620.5</v>
+        <v>1625.5</v>
       </c>
       <c r="H48" t="n">
-        <v>-1.0234</v>
+        <v>-0.8564000000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>121.05</v>
+        <v>121.16</v>
       </c>
       <c r="J48" t="n">
         <v>100.19</v>
       </c>
       <c r="K48" t="n">
-        <v>20.86</v>
+        <v>20.97</v>
       </c>
       <c r="L48" t="n">
-        <v>0.3114</v>
+        <v>0.3061</v>
       </c>
       <c r="M48" t="n">
-        <v>0.128</v>
+        <v>0.1276</v>
       </c>
       <c r="N48" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O48" t="n">
         <v>91</v>
@@ -3857,7 +3857,7 @@
         <v>76</v>
       </c>
       <c r="U48" t="n">
-        <v>1377.7</v>
+        <v>1382.5</v>
       </c>
     </row>
     <row r="49">
@@ -3883,31 +3883,31 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G49" t="n">
-        <v>1591.4</v>
+        <v>1593.8</v>
       </c>
       <c r="H49" t="n">
-        <v>3.6609</v>
+        <v>3.5257</v>
       </c>
       <c r="I49" t="n">
-        <v>114.4</v>
+        <v>114.28</v>
       </c>
       <c r="J49" t="n">
-        <v>102.12</v>
+        <v>102.18</v>
       </c>
       <c r="K49" t="n">
-        <v>12.28</v>
+        <v>12.1</v>
       </c>
       <c r="L49" t="n">
-        <v>0.3105</v>
+        <v>0.3104</v>
       </c>
       <c r="M49" t="n">
-        <v>0.1495</v>
+        <v>0.1506</v>
       </c>
       <c r="N49" t="n">
-        <v>16.4</v>
+        <v>10.8</v>
       </c>
       <c r="O49" t="n">
         <v>118</v>
@@ -3928,7 +3928,7 @@
         <v>117</v>
       </c>
       <c r="U49" t="n">
-        <v>1412</v>
+        <v>1410.6</v>
       </c>
     </row>
     <row r="50">
@@ -3954,31 +3954,31 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G50" t="n">
-        <v>1567.8</v>
+        <v>1574.5</v>
       </c>
       <c r="H50" t="n">
-        <v>4.0005</v>
+        <v>3.7174</v>
       </c>
       <c r="I50" t="n">
-        <v>112.7</v>
+        <v>113.98</v>
       </c>
       <c r="J50" t="n">
-        <v>102.71</v>
+        <v>102.46</v>
       </c>
       <c r="K50" t="n">
-        <v>10</v>
+        <v>11.53</v>
       </c>
       <c r="L50" t="n">
-        <v>0.3013</v>
+        <v>0.3039</v>
       </c>
       <c r="M50" t="n">
-        <v>0.1549</v>
+        <v>0.1512</v>
       </c>
       <c r="N50" t="n">
-        <v>13.2</v>
+        <v>20.2</v>
       </c>
       <c r="O50" t="n">
         <v>92</v>
@@ -3999,7 +3999,7 @@
         <v>92</v>
       </c>
       <c r="U50" t="n">
-        <v>1478.9</v>
+        <v>1481.7</v>
       </c>
     </row>
     <row r="51">
@@ -4025,31 +4025,31 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G51" t="n">
-        <v>1515.6</v>
+        <v>1521.4</v>
       </c>
       <c r="H51" t="n">
-        <v>3.9427</v>
+        <v>3.9296</v>
       </c>
       <c r="I51" t="n">
-        <v>107.67</v>
+        <v>107.03</v>
       </c>
       <c r="J51" t="n">
-        <v>102.86</v>
+        <v>102.73</v>
       </c>
       <c r="K51" t="n">
-        <v>4.81</v>
+        <v>4.29</v>
       </c>
       <c r="L51" t="n">
-        <v>0.2665</v>
+        <v>0.2687</v>
       </c>
       <c r="M51" t="n">
         <v>0.1436</v>
       </c>
       <c r="N51" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="O51" t="n">
         <v>172</v>
@@ -4070,7 +4070,7 @@
         <v>185</v>
       </c>
       <c r="U51" t="n">
-        <v>1452.7</v>
+        <v>1455.8</v>
       </c>
     </row>
     <row r="52">
@@ -4309,31 +4309,31 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G55" t="n">
-        <v>1999.8</v>
+        <v>2003.3</v>
       </c>
       <c r="H55" t="n">
-        <v>8.6837</v>
+        <v>8.2525</v>
       </c>
       <c r="I55" t="n">
-        <v>125.29</v>
+        <v>125.48</v>
       </c>
       <c r="J55" t="n">
-        <v>102.13</v>
+        <v>103.07</v>
       </c>
       <c r="K55" t="n">
-        <v>23.17</v>
+        <v>22.41</v>
       </c>
       <c r="L55" t="n">
-        <v>0.3216</v>
+        <v>0.3238</v>
       </c>
       <c r="M55" t="n">
-        <v>0.1296</v>
+        <v>0.1295</v>
       </c>
       <c r="N55" t="n">
-        <v>13.4</v>
+        <v>10.6</v>
       </c>
       <c r="O55" t="n">
         <v>5</v>
@@ -4354,7 +4354,7 @@
         <v>5</v>
       </c>
       <c r="U55" t="n">
-        <v>1712.9</v>
+        <v>1709.5</v>
       </c>
     </row>
     <row r="56">
@@ -5019,31 +5019,31 @@
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G65" t="n">
-        <v>1567</v>
+        <v>1573.9</v>
       </c>
       <c r="H65" t="n">
-        <v>-3.9617</v>
+        <v>-3.696</v>
       </c>
       <c r="I65" t="n">
-        <v>107.53</v>
+        <v>108.74</v>
       </c>
       <c r="J65" t="n">
-        <v>96.87</v>
+        <v>97.5</v>
       </c>
       <c r="K65" t="n">
-        <v>10.66</v>
+        <v>11.25</v>
       </c>
       <c r="L65" t="n">
-        <v>0.214</v>
+        <v>0.225</v>
       </c>
       <c r="M65" t="n">
-        <v>0.1374</v>
+        <v>0.1354</v>
       </c>
       <c r="N65" t="n">
-        <v>11</v>
+        <v>14.4</v>
       </c>
       <c r="O65" t="n">
         <v>80</v>
@@ -5064,7 +5064,7 @@
         <v>81</v>
       </c>
       <c r="U65" t="n">
-        <v>1516</v>
+        <v>1515.8</v>
       </c>
     </row>
     <row r="66">
@@ -5161,31 +5161,31 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="G67" t="n">
-        <v>1593.7</v>
+        <v>1597</v>
       </c>
       <c r="H67" t="n">
-        <v>1.3343</v>
+        <v>1.2134</v>
       </c>
       <c r="I67" t="n">
-        <v>112.11</v>
+        <v>111.85</v>
       </c>
       <c r="J67" t="n">
-        <v>106.85</v>
+        <v>106.58</v>
       </c>
       <c r="K67" t="n">
-        <v>5.26</v>
+        <v>5.27</v>
       </c>
       <c r="L67" t="n">
-        <v>0.3162</v>
+        <v>0.3163</v>
       </c>
       <c r="M67" t="n">
-        <v>0.1601</v>
+        <v>0.1636</v>
       </c>
       <c r="N67" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="O67" t="n">
         <v>156</v>
@@ -5206,7 +5206,7 @@
         <v>138</v>
       </c>
       <c r="U67" t="n">
-        <v>1464.1</v>
+        <v>1466.1</v>
       </c>
     </row>
     <row r="68">
@@ -5303,31 +5303,31 @@
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G69" t="n">
-        <v>1424.9</v>
+        <v>1427.4</v>
       </c>
       <c r="H69" t="n">
-        <v>0.9866</v>
+        <v>1.0039</v>
       </c>
       <c r="I69" t="n">
-        <v>119.08</v>
+        <v>119.17</v>
       </c>
       <c r="J69" t="n">
-        <v>116.55</v>
+        <v>116.56</v>
       </c>
       <c r="K69" t="n">
-        <v>2.53</v>
+        <v>2.61</v>
       </c>
       <c r="L69" t="n">
-        <v>0.2802</v>
+        <v>0.2859</v>
       </c>
       <c r="M69" t="n">
-        <v>0.1443</v>
+        <v>0.1441</v>
       </c>
       <c r="N69" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="O69" t="n">
         <v>191</v>
@@ -5348,7 +5348,7 @@
         <v>201</v>
       </c>
       <c r="U69" t="n">
-        <v>1433.6</v>
+        <v>1430.9</v>
       </c>
     </row>
   </sheetData>

--- a/team_stats_2026.xlsx
+++ b/team_stats_2026.xlsx
@@ -582,10 +582,10 @@
         <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -647,16 +647,16 @@
         <v>9</v>
       </c>
       <c r="P3" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>10</v>
+      </c>
+      <c r="R3" t="n">
         <v>9</v>
       </c>
-      <c r="Q3" t="n">
-        <v>8</v>
-      </c>
-      <c r="R3" t="n">
-        <v>10</v>
-      </c>
       <c r="S3" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="T3" t="n">
         <v>11</v>
@@ -721,16 +721,16 @@
         <v>10</v>
       </c>
       <c r="Q4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R4" t="n">
         <v>6</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U4" t="n">
         <v>1686.9</v>
@@ -786,22 +786,22 @@
         <v>7</v>
       </c>
       <c r="O5" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="P5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q5" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="R5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="S5" t="n">
+        <v>17</v>
+      </c>
+      <c r="T5" t="n">
         <v>15</v>
-      </c>
-      <c r="T5" t="n">
-        <v>13</v>
       </c>
       <c r="U5" t="n">
         <v>1762.7</v>
@@ -857,22 +857,22 @@
         <v>2.6</v>
       </c>
       <c r="O6" t="n">
+        <v>18</v>
+      </c>
+      <c r="P6" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q6" t="n">
         <v>20</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
+        <v>16</v>
+      </c>
+      <c r="S6" t="n">
+        <v>21</v>
+      </c>
+      <c r="T6" t="n">
         <v>18</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>24</v>
-      </c>
-      <c r="R6" t="n">
-        <v>19</v>
-      </c>
-      <c r="S6" t="n">
-        <v>20</v>
-      </c>
-      <c r="T6" t="n">
-        <v>19</v>
       </c>
       <c r="U6" t="n">
         <v>1728.7</v>
@@ -928,22 +928,22 @@
         <v>10.6</v>
       </c>
       <c r="O7" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="P7" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>23</v>
+      </c>
+      <c r="R7" t="n">
         <v>25</v>
       </c>
-      <c r="Q7" t="n">
-        <v>28</v>
-      </c>
-      <c r="R7" t="n">
-        <v>28</v>
-      </c>
       <c r="S7" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="T7" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="U7" t="n">
         <v>1701.3</v>
@@ -999,19 +999,19 @@
         <v>-0.2</v>
       </c>
       <c r="O8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P8" t="n">
         <v>26</v>
       </c>
       <c r="Q8" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="R8" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="T8" t="n">
         <v>33</v>
@@ -1070,19 +1070,19 @@
         <v>7.6</v>
       </c>
       <c r="O9" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P9" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="Q9" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="R9" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="S9" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="T9" t="n">
         <v>31</v>
@@ -1141,22 +1141,22 @@
         <v>6</v>
       </c>
       <c r="O10" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="P10" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="Q10" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R10" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="S10" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="T10" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="U10" t="n">
         <v>1700.1</v>
@@ -1212,22 +1212,22 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="P11" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="Q11" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R11" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="S11" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="T11" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="U11" t="n">
         <v>1675.6</v>
@@ -1286,19 +1286,19 @@
         <v>37</v>
       </c>
       <c r="P12" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R12" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S12" t="n">
         <v>36</v>
       </c>
       <c r="T12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="U12" t="n">
         <v>1566.6</v>
@@ -1354,22 +1354,22 @@
         <v>-4.2</v>
       </c>
       <c r="O13" t="n">
+        <v>43</v>
+      </c>
+      <c r="P13" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q13" t="n">
         <v>39</v>
       </c>
-      <c r="P13" t="n">
-        <v>45</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>37</v>
-      </c>
       <c r="R13" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="S13" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="T13" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="U13" t="n">
         <v>1643.1</v>
@@ -1425,22 +1425,22 @@
         <v>19.6</v>
       </c>
       <c r="O14" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P14" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="Q14" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="R14" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="S14" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="T14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="U14" t="n">
         <v>1553.3</v>
@@ -1496,22 +1496,22 @@
         <v>7.6</v>
       </c>
       <c r="O15" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P15" t="n">
         <v>102</v>
       </c>
       <c r="Q15" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="R15" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="S15" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T15" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="U15" t="n">
         <v>1383.2</v>
@@ -1567,7 +1567,7 @@
         <v>2.4</v>
       </c>
       <c r="O16" t="n">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="P16" t="n">
         <v>149</v>
@@ -1576,13 +1576,13 @@
         <v>162</v>
       </c>
       <c r="R16" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="S16" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="T16" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="U16" t="n">
         <v>1416.5</v>
@@ -1638,22 +1638,22 @@
         <v>19.8</v>
       </c>
       <c r="O17" t="n">
-        <v>207</v>
+        <v>186</v>
       </c>
       <c r="P17" t="n">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="Q17" t="n">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="R17" t="n">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="S17" t="n">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="T17" t="n">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="U17" t="n">
         <v>1407.8</v>
@@ -1709,22 +1709,22 @@
         <v>18.8</v>
       </c>
       <c r="O18" t="n">
-        <v>221</v>
+        <v>198</v>
       </c>
       <c r="P18" t="n">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="Q18" t="n">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="R18" t="n">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="S18" t="n">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="T18" t="n">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="U18" t="n">
         <v>1364.8</v>
@@ -1783,7 +1783,7 @@
         <v>4</v>
       </c>
       <c r="P19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q19" t="n">
         <v>4</v>
@@ -1792,7 +1792,7 @@
         <v>4</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T19" t="n">
         <v>4</v>
@@ -1857,13 +1857,13 @@
         <v>5</v>
       </c>
       <c r="Q20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R20" t="n">
         <v>5</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T20" t="n">
         <v>7</v>
@@ -1922,19 +1922,19 @@
         <v>8</v>
       </c>
       <c r="O21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P21" t="n">
         <v>13</v>
       </c>
       <c r="Q21" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="R21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T21" t="n">
         <v>12</v>
@@ -1993,22 +1993,22 @@
         <v>3</v>
       </c>
       <c r="O22" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="P22" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>11</v>
+      </c>
+      <c r="R22" t="n">
         <v>19</v>
       </c>
-      <c r="Q22" t="n">
-        <v>15</v>
-      </c>
-      <c r="R22" t="n">
-        <v>18</v>
-      </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="U22" t="n">
         <v>1639.2</v>
@@ -2067,16 +2067,16 @@
         <v>21</v>
       </c>
       <c r="P23" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q23" t="n">
         <v>17</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>10</v>
       </c>
       <c r="R23" t="n">
         <v>17</v>
       </c>
       <c r="S23" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T23" t="n">
         <v>22</v>
@@ -2135,13 +2135,13 @@
         <v>5.4</v>
       </c>
       <c r="O24" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="P24" t="n">
         <v>27</v>
       </c>
       <c r="Q24" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="R24" t="n">
         <v>21</v>
@@ -2150,7 +2150,7 @@
         <v>27</v>
       </c>
       <c r="T24" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="U24" t="n">
         <v>1682.1</v>
@@ -2212,16 +2212,16 @@
         <v>23</v>
       </c>
       <c r="Q25" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="R25" t="n">
         <v>23</v>
       </c>
       <c r="S25" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="T25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U25" t="n">
         <v>1595.3</v>
@@ -2277,22 +2277,22 @@
         <v>-7.6</v>
       </c>
       <c r="O26" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="P26" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Q26" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="R26" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="S26" t="n">
+        <v>30</v>
+      </c>
+      <c r="T26" t="n">
         <v>29</v>
-      </c>
-      <c r="T26" t="n">
-        <v>26</v>
       </c>
       <c r="U26" t="n">
         <v>1599.2</v>
@@ -2348,22 +2348,22 @@
         <v>9</v>
       </c>
       <c r="O27" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="P27" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="Q27" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="R27" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="S27" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="T27" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="U27" t="n">
         <v>1679.3</v>
@@ -2419,22 +2419,22 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="P28" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Q28" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="R28" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="S28" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="T28" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="U28" t="n">
         <v>1651.9</v>
@@ -2493,19 +2493,19 @@
         <v>45</v>
       </c>
       <c r="P29" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Q29" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R29" t="n">
+        <v>45</v>
+      </c>
+      <c r="S29" t="n">
+        <v>40</v>
+      </c>
+      <c r="T29" t="n">
         <v>44</v>
-      </c>
-      <c r="S29" t="n">
-        <v>43</v>
-      </c>
-      <c r="T29" t="n">
-        <v>47</v>
       </c>
       <c r="U29" t="n">
         <v>1554.6</v>
@@ -2561,19 +2561,19 @@
         <v>-3</v>
       </c>
       <c r="O30" t="n">
+        <v>39</v>
+      </c>
+      <c r="P30" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>44</v>
+      </c>
+      <c r="R30" t="n">
         <v>40</v>
       </c>
-      <c r="P30" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>42</v>
-      </c>
-      <c r="R30" t="n">
-        <v>41</v>
-      </c>
       <c r="S30" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T30" t="n">
         <v>38</v>
@@ -2632,19 +2632,19 @@
         <v>6.6</v>
       </c>
       <c r="O31" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="P31" t="n">
         <v>89</v>
       </c>
       <c r="Q31" t="n">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="R31" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S31" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="T31" t="n">
         <v>66</v>
@@ -2703,22 +2703,22 @@
         <v>-5</v>
       </c>
       <c r="O32" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="P32" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="Q32" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="R32" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="S32" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="T32" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="U32" t="n">
         <v>1485.6</v>
@@ -2774,22 +2774,22 @@
         <v>7</v>
       </c>
       <c r="O33" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="P33" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="Q33" t="n">
+        <v>105</v>
+      </c>
+      <c r="R33" t="n">
         <v>110</v>
       </c>
-      <c r="R33" t="n">
-        <v>115</v>
-      </c>
       <c r="S33" t="n">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="T33" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="U33" t="n">
         <v>1471.2</v>
@@ -2845,22 +2845,22 @@
         <v>-0.4</v>
       </c>
       <c r="O34" t="n">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="P34" t="n">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="Q34" t="n">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="R34" t="n">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="S34" t="n">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="T34" t="n">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="U34" t="n">
         <v>1413.3</v>
@@ -2916,22 +2916,22 @@
         <v>5.6</v>
       </c>
       <c r="O35" t="n">
+        <v>290</v>
+      </c>
+      <c r="P35" t="n">
         <v>295</v>
       </c>
-      <c r="P35" t="n">
-        <v>301</v>
-      </c>
       <c r="Q35" t="n">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="R35" t="n">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="S35" t="n">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="T35" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="U35" t="n">
         <v>1401.7</v>
@@ -2987,22 +2987,22 @@
         <v>4.8</v>
       </c>
       <c r="O36" t="n">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="P36" t="n">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q36" t="n">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="R36" t="n">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="S36" t="n">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="T36" t="n">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="U36" t="n">
         <v>1436.6</v>
@@ -3129,22 +3129,22 @@
         <v>6.6</v>
       </c>
       <c r="O38" t="n">
+        <v>11</v>
+      </c>
+      <c r="P38" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>21</v>
+      </c>
+      <c r="R38" t="n">
         <v>10</v>
-      </c>
-      <c r="P38" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>16</v>
-      </c>
-      <c r="R38" t="n">
-        <v>9</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
       </c>
       <c r="T38" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U38" t="n">
         <v>1660.9</v>
@@ -3206,16 +3206,16 @@
         <v>12</v>
       </c>
       <c r="Q39" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R39" t="n">
         <v>8</v>
       </c>
       <c r="S39" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U39" t="n">
         <v>1746.9</v>
@@ -3271,22 +3271,22 @@
         <v>-3.4</v>
       </c>
       <c r="O40" t="n">
+        <v>19</v>
+      </c>
+      <c r="P40" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>14</v>
+      </c>
+      <c r="R40" t="n">
+        <v>18</v>
+      </c>
+      <c r="S40" t="n">
         <v>16</v>
       </c>
-      <c r="P40" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q40" t="n">
+      <c r="T40" t="n">
         <v>19</v>
-      </c>
-      <c r="R40" t="n">
-        <v>15</v>
-      </c>
-      <c r="S40" t="n">
-        <v>13</v>
-      </c>
-      <c r="T40" t="n">
-        <v>15</v>
       </c>
       <c r="U40" t="n">
         <v>1772.3</v>
@@ -3342,22 +3342,22 @@
         <v>-0.6</v>
       </c>
       <c r="O41" t="n">
+        <v>13</v>
+      </c>
+      <c r="P41" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>13</v>
+      </c>
+      <c r="R41" t="n">
         <v>14</v>
       </c>
-      <c r="P41" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>18</v>
-      </c>
-      <c r="R41" t="n">
+      <c r="S41" t="n">
+        <v>22</v>
+      </c>
+      <c r="T41" t="n">
         <v>16</v>
-      </c>
-      <c r="S41" t="n">
-        <v>18</v>
-      </c>
-      <c r="T41" t="n">
-        <v>18</v>
       </c>
       <c r="U41" t="n">
         <v>1694.9</v>
@@ -3413,22 +3413,22 @@
         <v>2.4</v>
       </c>
       <c r="O42" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="P42" t="n">
         <v>21</v>
       </c>
       <c r="Q42" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R42" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="S42" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="T42" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="U42" t="n">
         <v>1676</v>
@@ -3484,22 +3484,22 @@
         <v>0.8</v>
       </c>
       <c r="O43" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="P43" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q43" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="R43" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="S43" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="T43" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="U43" t="n">
         <v>1728.4</v>
@@ -3555,22 +3555,22 @@
         <v>-1.8</v>
       </c>
       <c r="O44" t="n">
+        <v>38</v>
+      </c>
+      <c r="P44" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>32</v>
+      </c>
+      <c r="R44" t="n">
+        <v>35</v>
+      </c>
+      <c r="S44" t="n">
+        <v>34</v>
+      </c>
+      <c r="T44" t="n">
         <v>36</v>
-      </c>
-      <c r="P44" t="n">
-        <v>33</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>29</v>
-      </c>
-      <c r="R44" t="n">
-        <v>34</v>
-      </c>
-      <c r="S44" t="n">
-        <v>37</v>
-      </c>
-      <c r="T44" t="n">
-        <v>35</v>
       </c>
       <c r="U44" t="n">
         <v>1641.6</v>
@@ -3626,22 +3626,22 @@
         <v>-0.4</v>
       </c>
       <c r="O45" t="n">
+        <v>40</v>
+      </c>
+      <c r="P45" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>36</v>
+      </c>
+      <c r="R45" t="n">
+        <v>30</v>
+      </c>
+      <c r="S45" t="n">
+        <v>28</v>
+      </c>
+      <c r="T45" t="n">
         <v>27</v>
-      </c>
-      <c r="P45" t="n">
-        <v>40</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>25</v>
-      </c>
-      <c r="R45" t="n">
-        <v>24</v>
-      </c>
-      <c r="S45" t="n">
-        <v>26</v>
-      </c>
-      <c r="T45" t="n">
-        <v>24</v>
       </c>
       <c r="U45" t="n">
         <v>1512.1</v>
@@ -3700,19 +3700,19 @@
         <v>24</v>
       </c>
       <c r="P46" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>30</v>
+      </c>
+      <c r="R46" t="n">
         <v>28</v>
       </c>
-      <c r="Q46" t="n">
-        <v>32</v>
-      </c>
-      <c r="R46" t="n">
-        <v>29</v>
-      </c>
       <c r="S46" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="T46" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="U46" t="n">
         <v>1715.1</v>
@@ -3768,22 +3768,22 @@
         <v>6</v>
       </c>
       <c r="O47" t="n">
+        <v>91</v>
+      </c>
+      <c r="P47" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q47" t="n">
         <v>87</v>
       </c>
-      <c r="P47" t="n">
-        <v>52</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>83</v>
-      </c>
       <c r="R47" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="S47" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="T47" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="U47" t="n">
         <v>1414.6</v>
@@ -3839,19 +3839,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="O48" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="P48" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="Q48" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="R48" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="S48" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="T48" t="n">
         <v>76</v>
@@ -3910,22 +3910,22 @@
         <v>10.8</v>
       </c>
       <c r="O49" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="P49" t="n">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="Q49" t="n">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="R49" t="n">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="S49" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="T49" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="U49" t="n">
         <v>1410.6</v>
@@ -3981,22 +3981,22 @@
         <v>20.2</v>
       </c>
       <c r="O50" t="n">
+        <v>84</v>
+      </c>
+      <c r="P50" t="n">
+        <v>125</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>84</v>
+      </c>
+      <c r="R50" t="n">
+        <v>88</v>
+      </c>
+      <c r="S50" t="n">
         <v>92</v>
       </c>
-      <c r="P50" t="n">
-        <v>127</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>95</v>
-      </c>
-      <c r="R50" t="n">
-        <v>94</v>
-      </c>
-      <c r="S50" t="n">
-        <v>104</v>
-      </c>
       <c r="T50" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="U50" t="n">
         <v>1481.7</v>
@@ -4052,22 +4052,22 @@
         <v>5.4</v>
       </c>
       <c r="O51" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="P51" t="n">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="Q51" t="n">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="R51" t="n">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="S51" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="T51" t="n">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="U51" t="n">
         <v>1455.8</v>
@@ -4123,19 +4123,19 @@
         <v>23.6</v>
       </c>
       <c r="O52" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="P52" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="Q52" t="n">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="R52" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="S52" t="n">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="T52" t="n">
         <v>202</v>
@@ -4194,22 +4194,22 @@
         <v>7</v>
       </c>
       <c r="O53" t="n">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="P53" t="n">
         <v>228</v>
       </c>
       <c r="Q53" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="R53" t="n">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="S53" t="n">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="T53" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="U53" t="n">
         <v>1378.3</v>
@@ -4274,10 +4274,10 @@
         <v>3</v>
       </c>
       <c r="R54" t="n">
+        <v>3</v>
+      </c>
+      <c r="S54" t="n">
         <v>2</v>
-      </c>
-      <c r="S54" t="n">
-        <v>1</v>
       </c>
       <c r="T54" t="n">
         <v>3</v>
@@ -4339,10 +4339,10 @@
         <v>5</v>
       </c>
       <c r="P55" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q55" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R55" t="n">
         <v>7</v>
@@ -4351,7 +4351,7 @@
         <v>12</v>
       </c>
       <c r="T55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U55" t="n">
         <v>1709.5</v>
@@ -4413,16 +4413,16 @@
         <v>8</v>
       </c>
       <c r="Q56" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R56" t="n">
+        <v>12</v>
+      </c>
+      <c r="S56" t="n">
         <v>14</v>
       </c>
-      <c r="S56" t="n">
-        <v>16</v>
-      </c>
       <c r="T56" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U56" t="n">
         <v>1772.1</v>
@@ -4478,22 +4478,22 @@
         <v>13.6</v>
       </c>
       <c r="O57" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P57" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q57" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R57" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
       </c>
       <c r="T57" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U57" t="n">
         <v>1597.9</v>
@@ -4549,13 +4549,13 @@
         <v>2.6</v>
       </c>
       <c r="O58" t="n">
+        <v>14</v>
+      </c>
+      <c r="P58" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q58" t="n">
         <v>18</v>
-      </c>
-      <c r="P58" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>20</v>
       </c>
       <c r="R58" t="n">
         <v>20</v>
@@ -4564,7 +4564,7 @@
         <v>24</v>
       </c>
       <c r="T58" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U58" t="n">
         <v>1706.1</v>
@@ -4620,10 +4620,10 @@
         <v>-5.4</v>
       </c>
       <c r="O59" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="P59" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q59" t="n">
         <v>22</v>
@@ -4632,10 +4632,10 @@
         <v>22</v>
       </c>
       <c r="S59" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="T59" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U59" t="n">
         <v>1726.9</v>
@@ -4691,22 +4691,22 @@
         <v>6.8</v>
       </c>
       <c r="O60" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="P60" t="n">
         <v>38</v>
       </c>
       <c r="Q60" t="n">
+        <v>27</v>
+      </c>
+      <c r="R60" t="n">
+        <v>31</v>
+      </c>
+      <c r="S60" t="n">
         <v>26</v>
       </c>
-      <c r="R60" t="n">
+      <c r="T60" t="n">
         <v>32</v>
-      </c>
-      <c r="S60" t="n">
-        <v>30</v>
-      </c>
-      <c r="T60" t="n">
-        <v>30</v>
       </c>
       <c r="U60" t="n">
         <v>1617.1</v>
@@ -4762,22 +4762,22 @@
         <v>11.2</v>
       </c>
       <c r="O61" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="P61" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="Q61" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="R61" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="S61" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="T61" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="U61" t="n">
         <v>1689.3</v>
@@ -4833,16 +4833,16 @@
         <v>-0.6</v>
       </c>
       <c r="O62" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P62" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Q62" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="R62" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="S62" t="n">
         <v>41</v>
@@ -4904,22 +4904,22 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="O63" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="P63" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="Q63" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="R63" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="S63" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="T63" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="U63" t="n">
         <v>1699.4</v>
@@ -4975,22 +4975,22 @@
         <v>-1.6</v>
       </c>
       <c r="O64" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="P64" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="Q64" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="R64" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S64" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="T64" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="U64" t="n">
         <v>1687.9</v>
@@ -5046,22 +5046,22 @@
         <v>14.4</v>
       </c>
       <c r="O65" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="P65" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="Q65" t="n">
+        <v>72</v>
+      </c>
+      <c r="R65" t="n">
         <v>76</v>
       </c>
-      <c r="R65" t="n">
-        <v>86</v>
-      </c>
       <c r="S65" t="n">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="T65" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="U65" t="n">
         <v>1515.8</v>
@@ -5117,13 +5117,13 @@
         <v>6.6</v>
       </c>
       <c r="O66" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="P66" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q66" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="R66" t="n">
         <v>82</v>
@@ -5132,7 +5132,7 @@
         <v>77</v>
       </c>
       <c r="T66" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="U66" t="n">
         <v>1455.5</v>
@@ -5188,22 +5188,22 @@
         <v>6.4</v>
       </c>
       <c r="O67" t="n">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P67" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="Q67" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="R67" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="S67" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="T67" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="U67" t="n">
         <v>1466.1</v>
@@ -5259,22 +5259,22 @@
         <v>6.6</v>
       </c>
       <c r="O68" t="n">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="P68" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="Q68" t="n">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="R68" t="n">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="S68" t="n">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="T68" t="n">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="U68" t="n">
         <v>1435.1</v>
@@ -5330,22 +5330,22 @@
         <v>6.4</v>
       </c>
       <c r="O69" t="n">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="P69" t="n">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="Q69" t="n">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="R69" t="n">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="S69" t="n">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="T69" t="n">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="U69" t="n">
         <v>1430.9</v>

--- a/team_stats_2026.xlsx
+++ b/team_stats_2026.xlsx
@@ -1519,11 +1519,11 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1190</v>
+        <v>1460</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ETSU</t>
+          <t>Wright St</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1540,61 +1540,61 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
+        <v>121</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1464.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.7711</v>
+      </c>
+      <c r="I16" t="n">
+        <v>115.65</v>
+      </c>
+      <c r="J16" t="n">
+        <v>109.07</v>
+      </c>
+      <c r="K16" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="N16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O16" t="n">
+        <v>144</v>
+      </c>
+      <c r="P16" t="n">
+        <v>145</v>
+      </c>
+      <c r="Q16" t="n">
         <v>125</v>
       </c>
-      <c r="G16" t="n">
-        <v>1518.5</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.4929</v>
-      </c>
-      <c r="I16" t="n">
-        <v>116.45</v>
-      </c>
-      <c r="J16" t="n">
-        <v>105.53</v>
-      </c>
-      <c r="K16" t="n">
-        <v>10.92</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.268</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.1456</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O16" t="n">
-        <v>147</v>
-      </c>
-      <c r="P16" t="n">
-        <v>149</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>162</v>
-      </c>
       <c r="R16" t="n">
+        <v>136</v>
+      </c>
+      <c r="S16" t="n">
         <v>138</v>
       </c>
-      <c r="S16" t="n">
-        <v>154</v>
-      </c>
       <c r="T16" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="U16" t="n">
-        <v>1416.5</v>
+        <v>1435.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1398</v>
+        <v>1474</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tennessee St</t>
+          <t>Queens NC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1611,52 +1611,52 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G17" t="n">
-        <v>1466.9</v>
+        <v>1427.4</v>
       </c>
       <c r="H17" t="n">
-        <v>3.3618</v>
+        <v>1.0039</v>
       </c>
       <c r="I17" t="n">
-        <v>109.9</v>
+        <v>119.17</v>
       </c>
       <c r="J17" t="n">
-        <v>103.28</v>
+        <v>116.56</v>
       </c>
       <c r="K17" t="n">
-        <v>6.62</v>
+        <v>2.61</v>
       </c>
       <c r="L17" t="n">
-        <v>0.328</v>
+        <v>0.2859</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1589</v>
+        <v>0.1441</v>
       </c>
       <c r="N17" t="n">
-        <v>19.8</v>
+        <v>6.4</v>
       </c>
       <c r="O17" t="n">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="P17" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q17" t="n">
+        <v>181</v>
+      </c>
+      <c r="R17" t="n">
+        <v>177</v>
+      </c>
+      <c r="S17" t="n">
+        <v>171</v>
+      </c>
+      <c r="T17" t="n">
         <v>187</v>
       </c>
-      <c r="R17" t="n">
-        <v>168</v>
-      </c>
-      <c r="S17" t="n">
-        <v>153</v>
-      </c>
-      <c r="T17" t="n">
-        <v>172</v>
-      </c>
       <c r="U17" t="n">
-        <v>1407.8</v>
+        <v>1430.9</v>
       </c>
     </row>
     <row r="18">
@@ -2868,11 +2868,11 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1250</v>
+        <v>1202</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lehigh</t>
+          <t>Furman</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2892,58 +2892,58 @@
         <v>125</v>
       </c>
       <c r="G35" t="n">
-        <v>1323.1</v>
+        <v>1536.4</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.5849</v>
+        <v>0.9002</v>
       </c>
       <c r="I35" t="n">
-        <v>104.76</v>
+        <v>111.68</v>
       </c>
       <c r="J35" t="n">
-        <v>108.58</v>
+        <v>107.71</v>
       </c>
       <c r="K35" t="n">
-        <v>-3.82</v>
+        <v>3.97</v>
       </c>
       <c r="L35" t="n">
-        <v>0.214</v>
+        <v>0.2563</v>
       </c>
       <c r="M35" t="n">
-        <v>0.1729</v>
+        <v>0.1715</v>
       </c>
       <c r="N35" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="O35" t="n">
-        <v>290</v>
+        <v>199</v>
       </c>
       <c r="P35" t="n">
-        <v>295</v>
+        <v>170</v>
       </c>
       <c r="Q35" t="n">
-        <v>279</v>
+        <v>193</v>
       </c>
       <c r="R35" t="n">
-        <v>282</v>
+        <v>189</v>
       </c>
       <c r="S35" t="n">
-        <v>268</v>
+        <v>192</v>
       </c>
       <c r="T35" t="n">
-        <v>282</v>
+        <v>194</v>
       </c>
       <c r="U35" t="n">
-        <v>1401.7</v>
+        <v>1417.8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1126</v>
+        <v>1224</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Bethune-Cookman</t>
+          <t>Howard</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2963,49 +2963,49 @@
         <v>122</v>
       </c>
       <c r="G36" t="n">
-        <v>1375.4</v>
+        <v>1409</v>
       </c>
       <c r="H36" t="n">
-        <v>0.9205</v>
+        <v>3.2279</v>
       </c>
       <c r="I36" t="n">
-        <v>104.96</v>
+        <v>109.08</v>
       </c>
       <c r="J36" t="n">
-        <v>108.7</v>
+        <v>98.81</v>
       </c>
       <c r="K36" t="n">
-        <v>-3.74</v>
+        <v>10.27</v>
       </c>
       <c r="L36" t="n">
-        <v>0.2778</v>
+        <v>0.3126</v>
       </c>
       <c r="M36" t="n">
-        <v>0.1862</v>
+        <v>0.1855</v>
       </c>
       <c r="N36" t="n">
-        <v>4.8</v>
+        <v>23.6</v>
       </c>
       <c r="O36" t="n">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="P36" t="n">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="Q36" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="R36" t="n">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="S36" t="n">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="T36" t="n">
-        <v>255</v>
+        <v>202</v>
       </c>
       <c r="U36" t="n">
-        <v>1436.6</v>
+        <v>1380.6</v>
       </c>
     </row>
     <row r="37">
@@ -4075,11 +4075,11 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1224</v>
+        <v>1250</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Howard</t>
+          <t>Lehigh</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4096,61 +4096,61 @@
         <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G52" t="n">
-        <v>1409</v>
+        <v>1323.1</v>
       </c>
       <c r="H52" t="n">
-        <v>3.2279</v>
+        <v>-0.5849</v>
       </c>
       <c r="I52" t="n">
-        <v>109.08</v>
+        <v>104.76</v>
       </c>
       <c r="J52" t="n">
-        <v>98.81</v>
+        <v>108.58</v>
       </c>
       <c r="K52" t="n">
-        <v>10.27</v>
+        <v>-3.82</v>
       </c>
       <c r="L52" t="n">
-        <v>0.3126</v>
+        <v>0.214</v>
       </c>
       <c r="M52" t="n">
-        <v>0.1855</v>
+        <v>0.1729</v>
       </c>
       <c r="N52" t="n">
-        <v>23.6</v>
+        <v>5.6</v>
       </c>
       <c r="O52" t="n">
-        <v>202</v>
+        <v>290</v>
       </c>
       <c r="P52" t="n">
-        <v>250</v>
+        <v>295</v>
       </c>
       <c r="Q52" t="n">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="R52" t="n">
-        <v>198</v>
+        <v>282</v>
       </c>
       <c r="S52" t="n">
-        <v>232</v>
+        <v>268</v>
       </c>
       <c r="T52" t="n">
-        <v>202</v>
+        <v>282</v>
       </c>
       <c r="U52" t="n">
-        <v>1380.6</v>
+        <v>1401.7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1254</v>
+        <v>1126</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LIU Brooklyn</t>
+          <t>Bethune-Cookman</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4167,52 +4167,52 @@
         <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G53" t="n">
-        <v>1416</v>
+        <v>1375.4</v>
       </c>
       <c r="H53" t="n">
-        <v>2.4057</v>
+        <v>0.9205</v>
       </c>
       <c r="I53" t="n">
-        <v>108.81</v>
+        <v>104.96</v>
       </c>
       <c r="J53" t="n">
-        <v>104.08</v>
+        <v>108.7</v>
       </c>
       <c r="K53" t="n">
-        <v>4.73</v>
+        <v>-3.74</v>
       </c>
       <c r="L53" t="n">
-        <v>0.3167</v>
+        <v>0.2778</v>
       </c>
       <c r="M53" t="n">
-        <v>0.1861</v>
+        <v>0.1862</v>
       </c>
       <c r="N53" t="n">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="O53" t="n">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="P53" t="n">
-        <v>228</v>
+        <v>271</v>
       </c>
       <c r="Q53" t="n">
-        <v>213</v>
+        <v>268</v>
       </c>
       <c r="R53" t="n">
-        <v>188</v>
+        <v>214</v>
       </c>
       <c r="S53" t="n">
-        <v>166</v>
+        <v>216</v>
       </c>
       <c r="T53" t="n">
-        <v>200</v>
+        <v>255</v>
       </c>
       <c r="U53" t="n">
-        <v>1378.3</v>
+        <v>1436.6</v>
       </c>
     </row>
     <row r="54">
@@ -5211,11 +5211,11 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1460</v>
+        <v>1398</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Wright St</t>
+          <t>Tennessee St</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5232,61 +5232,61 @@
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G68" t="n">
-        <v>1464.5</v>
+        <v>1466.9</v>
       </c>
       <c r="H68" t="n">
-        <v>2.7711</v>
+        <v>3.3618</v>
       </c>
       <c r="I68" t="n">
-        <v>115.65</v>
+        <v>109.9</v>
       </c>
       <c r="J68" t="n">
-        <v>109.07</v>
+        <v>103.28</v>
       </c>
       <c r="K68" t="n">
-        <v>6.58</v>
+        <v>6.62</v>
       </c>
       <c r="L68" t="n">
-        <v>0.2992</v>
+        <v>0.328</v>
       </c>
       <c r="M68" t="n">
-        <v>0.158</v>
+        <v>0.1589</v>
       </c>
       <c r="N68" t="n">
-        <v>6.6</v>
+        <v>19.8</v>
       </c>
       <c r="O68" t="n">
-        <v>144</v>
+        <v>186</v>
       </c>
       <c r="P68" t="n">
-        <v>145</v>
+        <v>190</v>
       </c>
       <c r="Q68" t="n">
-        <v>125</v>
+        <v>187</v>
       </c>
       <c r="R68" t="n">
-        <v>136</v>
+        <v>168</v>
       </c>
       <c r="S68" t="n">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="T68" t="n">
-        <v>133</v>
+        <v>172</v>
       </c>
       <c r="U68" t="n">
-        <v>1435.1</v>
+        <v>1407.8</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1474</v>
+        <v>1254</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Queens NC</t>
+          <t>LIU Brooklyn</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5303,52 +5303,52 @@
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G69" t="n">
-        <v>1427.4</v>
+        <v>1416</v>
       </c>
       <c r="H69" t="n">
-        <v>1.0039</v>
+        <v>2.4057</v>
       </c>
       <c r="I69" t="n">
-        <v>119.17</v>
+        <v>108.81</v>
       </c>
       <c r="J69" t="n">
-        <v>116.56</v>
+        <v>104.08</v>
       </c>
       <c r="K69" t="n">
-        <v>2.61</v>
+        <v>4.73</v>
       </c>
       <c r="L69" t="n">
-        <v>0.2859</v>
+        <v>0.3167</v>
       </c>
       <c r="M69" t="n">
-        <v>0.1441</v>
+        <v>0.1861</v>
       </c>
       <c r="N69" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="O69" t="n">
-        <v>183</v>
+        <v>217</v>
       </c>
       <c r="P69" t="n">
-        <v>192</v>
+        <v>228</v>
       </c>
       <c r="Q69" t="n">
-        <v>181</v>
+        <v>213</v>
       </c>
       <c r="R69" t="n">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="S69" t="n">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="T69" t="n">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="U69" t="n">
-        <v>1430.9</v>
+        <v>1378.3</v>
       </c>
     </row>
   </sheetData>

--- a/team_stats_2026.xlsx
+++ b/team_stats_2026.xlsx
@@ -1256,31 +1256,31 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G12" t="n">
-        <v>1768.3</v>
+        <v>1787.9</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4727</v>
+        <v>-0.2548</v>
       </c>
       <c r="I12" t="n">
-        <v>117.67</v>
+        <v>117.9</v>
       </c>
       <c r="J12" t="n">
-        <v>102.69</v>
+        <v>103.18</v>
       </c>
       <c r="K12" t="n">
-        <v>14.97</v>
+        <v>14.72</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3472</v>
+        <v>0.3445</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1494</v>
+        <v>0.15</v>
       </c>
       <c r="N12" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="O12" t="n">
         <v>37</v>
@@ -1301,7 +1301,7 @@
         <v>42</v>
       </c>
       <c r="U12" t="n">
-        <v>1566.6</v>
+        <v>1580.2</v>
       </c>
     </row>
     <row r="13">
@@ -1540,31 +1540,31 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G16" t="n">
-        <v>1464.5</v>
+        <v>1468.7</v>
       </c>
       <c r="H16" t="n">
-        <v>2.7711</v>
+        <v>2.7502</v>
       </c>
       <c r="I16" t="n">
-        <v>115.65</v>
+        <v>116.22</v>
       </c>
       <c r="J16" t="n">
-        <v>109.07</v>
+        <v>109.52</v>
       </c>
       <c r="K16" t="n">
-        <v>6.58</v>
+        <v>6.7</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2992</v>
+        <v>0.2952</v>
       </c>
       <c r="M16" t="n">
-        <v>0.158</v>
+        <v>0.1569</v>
       </c>
       <c r="N16" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O16" t="n">
         <v>144</v>
@@ -1585,7 +1585,7 @@
         <v>133</v>
       </c>
       <c r="U16" t="n">
-        <v>1435.1</v>
+        <v>1435.9</v>
       </c>
     </row>
     <row r="17">
@@ -2179,31 +2179,31 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="G25" t="n">
-        <v>1877.4</v>
+        <v>1857.8</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.5286</v>
+        <v>-0.2818</v>
       </c>
       <c r="I25" t="n">
-        <v>118.87</v>
+        <v>118.73</v>
       </c>
       <c r="J25" t="n">
-        <v>98.81999999999999</v>
+        <v>99.88</v>
       </c>
       <c r="K25" t="n">
-        <v>20.05</v>
+        <v>18.85</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2966</v>
+        <v>0.2975</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1557</v>
+        <v>0.1525</v>
       </c>
       <c r="N25" t="n">
-        <v>11.8</v>
+        <v>8.6</v>
       </c>
       <c r="O25" t="n">
         <v>22</v>
@@ -2224,7 +2224,7 @@
         <v>20</v>
       </c>
       <c r="U25" t="n">
-        <v>1595.3</v>
+        <v>1596.9</v>
       </c>
     </row>
     <row r="26">
@@ -2889,31 +2889,31 @@
         <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G35" t="n">
-        <v>1536.4</v>
+        <v>1542.9</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9002</v>
+        <v>0.8197</v>
       </c>
       <c r="I35" t="n">
-        <v>111.68</v>
+        <v>112.01</v>
       </c>
       <c r="J35" t="n">
-        <v>107.71</v>
+        <v>107.28</v>
       </c>
       <c r="K35" t="n">
-        <v>3.97</v>
+        <v>4.73</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2563</v>
+        <v>0.2562</v>
       </c>
       <c r="M35" t="n">
-        <v>0.1715</v>
+        <v>0.171</v>
       </c>
       <c r="N35" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="O35" t="n">
         <v>199</v>
@@ -2934,7 +2934,7 @@
         <v>194</v>
       </c>
       <c r="U35" t="n">
-        <v>1417.8</v>
+        <v>1422.2</v>
       </c>
     </row>
     <row r="36">
@@ -3954,31 +3954,31 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G50" t="n">
-        <v>1574.5</v>
+        <v>1582</v>
       </c>
       <c r="H50" t="n">
-        <v>3.7174</v>
+        <v>3.5064</v>
       </c>
       <c r="I50" t="n">
-        <v>113.98</v>
+        <v>113.54</v>
       </c>
       <c r="J50" t="n">
-        <v>102.46</v>
+        <v>102.66</v>
       </c>
       <c r="K50" t="n">
-        <v>11.53</v>
+        <v>10.88</v>
       </c>
       <c r="L50" t="n">
-        <v>0.3039</v>
+        <v>0.3074</v>
       </c>
       <c r="M50" t="n">
-        <v>0.1512</v>
+        <v>0.1523</v>
       </c>
       <c r="N50" t="n">
-        <v>20.2</v>
+        <v>13.6</v>
       </c>
       <c r="O50" t="n">
         <v>84</v>
@@ -3999,7 +3999,7 @@
         <v>88</v>
       </c>
       <c r="U50" t="n">
-        <v>1481.7</v>
+        <v>1484.4</v>
       </c>
     </row>
     <row r="51">
@@ -4451,31 +4451,31 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="G57" t="n">
-        <v>2061.6</v>
+        <v>2063.2</v>
       </c>
       <c r="H57" t="n">
-        <v>6.7538</v>
+        <v>6.2559</v>
       </c>
       <c r="I57" t="n">
-        <v>120.35</v>
+        <v>120.06</v>
       </c>
       <c r="J57" t="n">
-        <v>93.25</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="K57" t="n">
-        <v>27.1</v>
+        <v>27.07</v>
       </c>
       <c r="L57" t="n">
-        <v>0.2992</v>
+        <v>0.2963</v>
       </c>
       <c r="M57" t="n">
-        <v>0.1329</v>
+        <v>0.1337</v>
       </c>
       <c r="N57" t="n">
-        <v>13.6</v>
+        <v>13.8</v>
       </c>
       <c r="O57" t="n">
         <v>10</v>
@@ -4496,7 +4496,7 @@
         <v>5</v>
       </c>
       <c r="U57" t="n">
-        <v>1597.9</v>
+        <v>1593.1</v>
       </c>
     </row>
     <row r="58">
@@ -5161,31 +5161,31 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G67" t="n">
-        <v>1597</v>
+        <v>1601</v>
       </c>
       <c r="H67" t="n">
-        <v>1.2134</v>
+        <v>1.1284</v>
       </c>
       <c r="I67" t="n">
-        <v>111.85</v>
+        <v>112.28</v>
       </c>
       <c r="J67" t="n">
-        <v>106.58</v>
+        <v>106.19</v>
       </c>
       <c r="K67" t="n">
-        <v>5.27</v>
+        <v>6.08</v>
       </c>
       <c r="L67" t="n">
-        <v>0.3163</v>
+        <v>0.316</v>
       </c>
       <c r="M67" t="n">
-        <v>0.1636</v>
+        <v>0.1667</v>
       </c>
       <c r="N67" t="n">
-        <v>6.4</v>
+        <v>9.4</v>
       </c>
       <c r="O67" t="n">
         <v>153</v>
@@ -5206,7 +5206,7 @@
         <v>132</v>
       </c>
       <c r="U67" t="n">
-        <v>1466.1</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="68">

--- a/team_stats_2026.xlsx
+++ b/team_stats_2026.xlsx
@@ -667,11 +667,11 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1235</v>
+        <v>1104</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Iowa St</t>
+          <t>Alabama</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,58 +691,58 @@
         <v>124</v>
       </c>
       <c r="G4" t="n">
-        <v>2027.4</v>
+        <v>1975.1</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1622</v>
+        <v>-1.4869</v>
       </c>
       <c r="I4" t="n">
-        <v>118.43</v>
+        <v>122.11</v>
       </c>
       <c r="J4" t="n">
-        <v>96.01000000000001</v>
+        <v>110.78</v>
       </c>
       <c r="K4" t="n">
-        <v>22.42</v>
+        <v>11.33</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3184</v>
+        <v>0.2853</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1465</v>
+        <v>0.1289</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4</v>
+        <v>7.2</v>
       </c>
       <c r="O4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="P4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="U4" t="n">
-        <v>1686.9</v>
+        <v>1772.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1403</v>
+        <v>1242</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Texas Tech</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -762,58 +762,58 @@
         <v>124</v>
       </c>
       <c r="G5" t="n">
-        <v>2025.5</v>
+        <v>1973.7</v>
       </c>
       <c r="H5" t="n">
-        <v>10.1327</v>
+        <v>11.337</v>
       </c>
       <c r="I5" t="n">
-        <v>118.86</v>
+        <v>111.61</v>
       </c>
       <c r="J5" t="n">
-        <v>106.69</v>
+        <v>100.9</v>
       </c>
       <c r="K5" t="n">
-        <v>12.16</v>
+        <v>10.71</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2944</v>
+        <v>0.2487</v>
       </c>
       <c r="M5" t="n">
-        <v>0.155</v>
+        <v>0.1523</v>
       </c>
       <c r="N5" t="n">
-        <v>7</v>
+        <v>-3.4</v>
       </c>
       <c r="O5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P5" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>14</v>
+      </c>
+      <c r="R5" t="n">
+        <v>18</v>
+      </c>
+      <c r="S5" t="n">
         <v>16</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="T5" t="n">
         <v>19</v>
       </c>
-      <c r="R5" t="n">
-        <v>15</v>
-      </c>
-      <c r="S5" t="n">
-        <v>17</v>
-      </c>
-      <c r="T5" t="n">
-        <v>15</v>
-      </c>
       <c r="U5" t="n">
-        <v>1762.7</v>
+        <v>1772.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1116</v>
+        <v>1435</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>Vanderbilt</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -833,58 +833,58 @@
         <v>124</v>
       </c>
       <c r="G6" t="n">
-        <v>1950</v>
+        <v>1935.7</v>
       </c>
       <c r="H6" t="n">
-        <v>5.5428</v>
+        <v>2.1989</v>
       </c>
       <c r="I6" t="n">
-        <v>122.85</v>
+        <v>121.8</v>
       </c>
       <c r="J6" t="n">
-        <v>108.88</v>
+        <v>105.67</v>
       </c>
       <c r="K6" t="n">
-        <v>13.96</v>
+        <v>16.12</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3009</v>
+        <v>0.2802</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1205</v>
+        <v>0.1278</v>
       </c>
       <c r="N6" t="n">
-        <v>2.6</v>
+        <v>-0.6</v>
       </c>
       <c r="O6" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="P6" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>13</v>
+      </c>
+      <c r="R6" t="n">
         <v>14</v>
       </c>
-      <c r="Q6" t="n">
-        <v>20</v>
-      </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
+        <v>22</v>
+      </c>
+      <c r="T6" t="n">
         <v>16</v>
       </c>
-      <c r="S6" t="n">
-        <v>21</v>
-      </c>
-      <c r="T6" t="n">
-        <v>18</v>
-      </c>
       <c r="U6" t="n">
-        <v>1728.7</v>
+        <v>1694.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1458</v>
+        <v>1314</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -904,49 +904,49 @@
         <v>124</v>
       </c>
       <c r="G7" t="n">
-        <v>1859.5</v>
+        <v>1917.6</v>
       </c>
       <c r="H7" t="n">
-        <v>1.6302</v>
+        <v>2.3735</v>
       </c>
       <c r="I7" t="n">
-        <v>119.64</v>
+        <v>115.09</v>
       </c>
       <c r="J7" t="n">
-        <v>108.42</v>
+        <v>103.39</v>
       </c>
       <c r="K7" t="n">
-        <v>11.21</v>
+        <v>11.71</v>
       </c>
       <c r="L7" t="n">
-        <v>0.276</v>
+        <v>0.2653</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1244</v>
+        <v>0.14</v>
       </c>
       <c r="N7" t="n">
-        <v>10.6</v>
+        <v>2.4</v>
       </c>
       <c r="O7" t="n">
+        <v>30</v>
+      </c>
+      <c r="P7" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>24</v>
+      </c>
+      <c r="R7" t="n">
+        <v>24</v>
+      </c>
+      <c r="S7" t="n">
+        <v>18</v>
+      </c>
+      <c r="T7" t="n">
         <v>23</v>
       </c>
-      <c r="P7" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>23</v>
-      </c>
-      <c r="R7" t="n">
-        <v>25</v>
-      </c>
-      <c r="S7" t="n">
-        <v>29</v>
-      </c>
-      <c r="T7" t="n">
-        <v>26</v>
-      </c>
       <c r="U7" t="n">
-        <v>1701.3</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="8">
@@ -1022,11 +1022,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1208</v>
+        <v>1429</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Utah St</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1046,58 +1046,58 @@
         <v>124</v>
       </c>
       <c r="G9" t="n">
-        <v>1816.9</v>
+        <v>1869.8</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2065</v>
+        <v>0.2419</v>
       </c>
       <c r="I9" t="n">
-        <v>121.14</v>
+        <v>120.49</v>
       </c>
       <c r="J9" t="n">
-        <v>107.06</v>
+        <v>105.01</v>
       </c>
       <c r="K9" t="n">
-        <v>14.09</v>
+        <v>15.48</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3227</v>
+        <v>0.3065</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1388</v>
+        <v>0.1487</v>
       </c>
       <c r="N9" t="n">
-        <v>7.6</v>
+        <v>-7.6</v>
       </c>
       <c r="O9" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="P9" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="Q9" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="R9" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="S9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="T9" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="U9" t="n">
-        <v>1643</v>
+        <v>1599.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1326</v>
+        <v>1234</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ohio St</t>
+          <t>Iowa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1114,61 +1114,61 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G10" t="n">
-        <v>1799.9</v>
+        <v>1843.7</v>
       </c>
       <c r="H10" t="n">
-        <v>1.5472</v>
+        <v>4.0673</v>
       </c>
       <c r="I10" t="n">
-        <v>118.74</v>
+        <v>118.63</v>
       </c>
       <c r="J10" t="n">
-        <v>107.91</v>
+        <v>104.06</v>
       </c>
       <c r="K10" t="n">
-        <v>10.83</v>
+        <v>14.56</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2524</v>
+        <v>0.288</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1503</v>
+        <v>0.1446</v>
       </c>
       <c r="N10" t="n">
-        <v>6</v>
+        <v>-2</v>
       </c>
       <c r="O10" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="P10" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T10" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="U10" t="n">
-        <v>1700.1</v>
+        <v>1715.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1301</v>
+        <v>1365</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NC State</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1185,61 +1185,61 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G11" t="n">
-        <v>1735.9</v>
+        <v>1782.8</v>
       </c>
       <c r="H11" t="n">
-        <v>7.7247</v>
+        <v>0.0374</v>
       </c>
       <c r="I11" t="n">
-        <v>118.75</v>
+        <v>117.62</v>
       </c>
       <c r="J11" t="n">
-        <v>108.16</v>
+        <v>104.11</v>
       </c>
       <c r="K11" t="n">
-        <v>10.59</v>
+        <v>13.51</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2829</v>
+        <v>0.3504</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1296</v>
+        <v>0.1498</v>
       </c>
       <c r="N11" t="n">
-        <v>-8.199999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="O11" t="n">
+        <v>37</v>
+      </c>
+      <c r="P11" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>46</v>
+      </c>
+      <c r="R11" t="n">
         <v>36</v>
       </c>
-      <c r="P11" t="n">
-        <v>45</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>34</v>
-      </c>
-      <c r="R11" t="n">
-        <v>38</v>
-      </c>
       <c r="S11" t="n">
+        <v>36</v>
+      </c>
+      <c r="T11" t="n">
         <v>42</v>
       </c>
-      <c r="T11" t="n">
-        <v>35</v>
-      </c>
       <c r="U11" t="n">
-        <v>1675.6</v>
+        <v>1596.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1365</v>
+        <v>1416</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>UCF</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1256,61 +1256,61 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G12" t="n">
-        <v>1787.9</v>
+        <v>1820.5</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2548</v>
+        <v>7.025</v>
       </c>
       <c r="I12" t="n">
-        <v>117.9</v>
+        <v>114.77</v>
       </c>
       <c r="J12" t="n">
-        <v>103.18</v>
+        <v>110.49</v>
       </c>
       <c r="K12" t="n">
-        <v>14.72</v>
+        <v>4.28</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3445</v>
+        <v>0.3115</v>
       </c>
       <c r="M12" t="n">
-        <v>0.15</v>
+        <v>0.1546</v>
       </c>
       <c r="N12" t="n">
-        <v>7.2</v>
+        <v>-1.6</v>
       </c>
       <c r="O12" t="n">
+        <v>53</v>
+      </c>
+      <c r="P12" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>57</v>
+      </c>
+      <c r="R12" t="n">
+        <v>46</v>
+      </c>
+      <c r="S12" t="n">
         <v>37</v>
       </c>
-      <c r="P12" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>46</v>
-      </c>
-      <c r="R12" t="n">
-        <v>36</v>
-      </c>
-      <c r="S12" t="n">
-        <v>36</v>
-      </c>
       <c r="T12" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="U12" t="n">
-        <v>1580.2</v>
+        <v>1687.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1374</v>
+        <v>1231</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SMU</t>
+          <t>Indiana</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1330,58 +1330,58 @@
         <v>124</v>
       </c>
       <c r="G13" t="n">
-        <v>1738.3</v>
+        <v>1741.9</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9109</v>
+        <v>-2.3683</v>
       </c>
       <c r="I13" t="n">
-        <v>118.28</v>
+        <v>116.27</v>
       </c>
       <c r="J13" t="n">
-        <v>110.33</v>
+        <v>107.64</v>
       </c>
       <c r="K13" t="n">
-        <v>7.95</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3064</v>
+        <v>0.2347</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1528</v>
+        <v>0.1428</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.2</v>
+        <v>-5.8</v>
       </c>
       <c r="O13" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="P13" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="Q13" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="R13" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="S13" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="T13" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="U13" t="n">
-        <v>1643.1</v>
+        <v>1701.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1378</v>
+        <v>1219</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>South Florida</t>
+          <t>High Point</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1401,58 +1401,58 @@
         <v>125</v>
       </c>
       <c r="G14" t="n">
-        <v>1711.8</v>
+        <v>1625.5</v>
       </c>
       <c r="H14" t="n">
-        <v>9.207800000000001</v>
+        <v>-0.8564000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>116.06</v>
+        <v>121.16</v>
       </c>
       <c r="J14" t="n">
-        <v>101.73</v>
+        <v>100.19</v>
       </c>
       <c r="K14" t="n">
-        <v>14.32</v>
+        <v>20.97</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3392</v>
+        <v>0.3061</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1453</v>
+        <v>0.1276</v>
       </c>
       <c r="N14" t="n">
-        <v>19.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="P14" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="Q14" t="n">
-        <v>51</v>
+        <v>95</v>
       </c>
       <c r="R14" t="n">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="S14" t="n">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="T14" t="n">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="U14" t="n">
-        <v>1553.3</v>
+        <v>1382.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1372</v>
+        <v>1220</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SF Austin</t>
+          <t>Hofstra</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1469,61 +1469,61 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="G15" t="n">
-        <v>1563.2</v>
+        <v>1586.2</v>
       </c>
       <c r="H15" t="n">
-        <v>3.2741</v>
+        <v>3.3583</v>
       </c>
       <c r="I15" t="n">
-        <v>113.58</v>
+        <v>113.56</v>
       </c>
       <c r="J15" t="n">
-        <v>98.86</v>
+        <v>102.69</v>
       </c>
       <c r="K15" t="n">
-        <v>14.72</v>
+        <v>10.87</v>
       </c>
       <c r="L15" t="n">
-        <v>0.311</v>
+        <v>0.3081</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1336</v>
+        <v>0.1527</v>
       </c>
       <c r="N15" t="n">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="O15" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="P15" t="n">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="Q15" t="n">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="R15" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="S15" t="n">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="T15" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="U15" t="n">
-        <v>1383.2</v>
+        <v>1482.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1460</v>
+        <v>1407</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wright St</t>
+          <t>Troy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1543,58 +1543,58 @@
         <v>126</v>
       </c>
       <c r="G16" t="n">
-        <v>1468.7</v>
+        <v>1601</v>
       </c>
       <c r="H16" t="n">
-        <v>2.7502</v>
+        <v>1.1284</v>
       </c>
       <c r="I16" t="n">
-        <v>116.22</v>
+        <v>112.28</v>
       </c>
       <c r="J16" t="n">
-        <v>109.52</v>
+        <v>106.19</v>
       </c>
       <c r="K16" t="n">
-        <v>6.7</v>
+        <v>6.08</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2952</v>
+        <v>0.316</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1569</v>
+        <v>0.1667</v>
       </c>
       <c r="N16" t="n">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="O16" t="n">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="P16" t="n">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="Q16" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="R16" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="S16" t="n">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="T16" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="U16" t="n">
-        <v>1435.9</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1474</v>
+        <v>1420</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Queens NC</t>
+          <t>UMBC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1611,61 +1611,61 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G17" t="n">
-        <v>1427.4</v>
+        <v>1393.7</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0039</v>
+        <v>1.2859</v>
       </c>
       <c r="I17" t="n">
-        <v>119.17</v>
+        <v>113.44</v>
       </c>
       <c r="J17" t="n">
-        <v>116.56</v>
+        <v>102.32</v>
       </c>
       <c r="K17" t="n">
-        <v>2.61</v>
+        <v>11.13</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2859</v>
+        <v>0.2168</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1441</v>
+        <v>0.1344</v>
       </c>
       <c r="N17" t="n">
-        <v>6.4</v>
+        <v>22.4</v>
       </c>
       <c r="O17" t="n">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="P17" t="n">
-        <v>192</v>
+        <v>225</v>
       </c>
       <c r="Q17" t="n">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="R17" t="n">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="S17" t="n">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="T17" t="n">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="U17" t="n">
-        <v>1430.9</v>
+        <v>1364.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1420</v>
+        <v>1224</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>UMBC</t>
+          <t>Howard</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1675,139 +1675,139 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>16a</t>
         </is>
       </c>
       <c r="E18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G18" t="n">
-        <v>1391.7</v>
+        <v>1409</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2162</v>
+        <v>3.2279</v>
       </c>
       <c r="I18" t="n">
-        <v>112.51</v>
+        <v>109.08</v>
       </c>
       <c r="J18" t="n">
-        <v>102.24</v>
+        <v>98.81</v>
       </c>
       <c r="K18" t="n">
-        <v>10.26</v>
+        <v>10.27</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2126</v>
+        <v>0.3126</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1361</v>
+        <v>0.1855</v>
       </c>
       <c r="N18" t="n">
-        <v>18.8</v>
+        <v>23.6</v>
       </c>
       <c r="O18" t="n">
+        <v>202</v>
+      </c>
+      <c r="P18" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>270</v>
+      </c>
+      <c r="R18" t="n">
         <v>198</v>
       </c>
-      <c r="P18" t="n">
-        <v>225</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>191</v>
-      </c>
-      <c r="R18" t="n">
-        <v>194</v>
-      </c>
       <c r="S18" t="n">
-        <v>197</v>
+        <v>232</v>
       </c>
       <c r="T18" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="U18" t="n">
-        <v>1364.8</v>
+        <v>1380.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1196</v>
+        <v>1186</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>E Washington</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>16b</t>
         </is>
       </c>
       <c r="E19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G19" t="n">
-        <v>2014.8</v>
+        <v>1317</v>
       </c>
       <c r="H19" t="n">
-        <v>2.8716</v>
+        <v>-1.0019</v>
       </c>
       <c r="I19" t="n">
-        <v>120.95</v>
+        <v>111.6</v>
       </c>
       <c r="J19" t="n">
-        <v>99.02</v>
+        <v>113.34</v>
       </c>
       <c r="K19" t="n">
-        <v>21.92</v>
+        <v>-1.74</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3329</v>
+        <v>0.287</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1552</v>
+        <v>0.1681</v>
       </c>
       <c r="N19" t="n">
-        <v>21.4</v>
+        <v>5.8</v>
       </c>
       <c r="O19" t="n">
-        <v>4</v>
+        <v>166</v>
       </c>
       <c r="P19" t="n">
-        <v>4</v>
+        <v>203</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>210</v>
       </c>
       <c r="R19" t="n">
-        <v>4</v>
+        <v>204</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>228</v>
       </c>
       <c r="T19" t="n">
-        <v>4</v>
+        <v>201</v>
       </c>
       <c r="U19" t="n">
-        <v>1709.6</v>
+        <v>1450.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1222</v>
+        <v>1196</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="E20" t="b">
@@ -1827,58 +1827,58 @@
         <v>124</v>
       </c>
       <c r="G20" t="n">
-        <v>2102.9</v>
+        <v>2014.8</v>
       </c>
       <c r="H20" t="n">
-        <v>1.6401</v>
+        <v>2.8716</v>
       </c>
       <c r="I20" t="n">
-        <v>117.95</v>
+        <v>120.95</v>
       </c>
       <c r="J20" t="n">
-        <v>95.43000000000001</v>
+        <v>99.02</v>
       </c>
       <c r="K20" t="n">
-        <v>22.51</v>
+        <v>21.92</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3379</v>
+        <v>0.3329</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1199</v>
+        <v>0.1552</v>
       </c>
       <c r="N20" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="O20" t="n">
+        <v>4</v>
+      </c>
+      <c r="P20" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4</v>
+      </c>
+      <c r="R20" t="n">
+        <v>4</v>
+      </c>
+      <c r="S20" t="n">
         <v>8</v>
       </c>
-      <c r="O20" t="n">
-        <v>6</v>
-      </c>
-      <c r="P20" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>7</v>
-      </c>
-      <c r="R20" t="n">
-        <v>5</v>
-      </c>
-      <c r="S20" t="n">
-        <v>6</v>
-      </c>
       <c r="T20" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U20" t="n">
-        <v>1706.6</v>
+        <v>1709.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1304</v>
+        <v>1222</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nebraska</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1888,68 +1888,68 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="E21" t="b">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G21" t="n">
-        <v>1999.6</v>
+        <v>2102.9</v>
       </c>
       <c r="H21" t="n">
-        <v>10.6735</v>
+        <v>1.6401</v>
       </c>
       <c r="I21" t="n">
-        <v>115.4</v>
+        <v>117.95</v>
       </c>
       <c r="J21" t="n">
-        <v>97.95</v>
+        <v>95.43000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>17.45</v>
+        <v>22.51</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2379</v>
+        <v>0.3379</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1402</v>
+        <v>0.1199</v>
       </c>
       <c r="N21" t="n">
         <v>8</v>
       </c>
       <c r="O21" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="P21" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="Q21" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="R21" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T21" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="U21" t="n">
-        <v>1665.7</v>
+        <v>1706.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1438</v>
+        <v>1304</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>Nebraska</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1959,68 +1959,68 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="E22" t="b">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G22" t="n">
-        <v>1956.5</v>
+        <v>1999.6</v>
       </c>
       <c r="H22" t="n">
-        <v>13.4946</v>
+        <v>10.6735</v>
       </c>
       <c r="I22" t="n">
-        <v>118.84</v>
+        <v>115.4</v>
       </c>
       <c r="J22" t="n">
-        <v>100.06</v>
+        <v>97.95</v>
       </c>
       <c r="K22" t="n">
-        <v>18.77</v>
+        <v>17.45</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3168</v>
+        <v>0.2379</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1532</v>
+        <v>0.1402</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O22" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="P22" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="Q22" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="R22" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U22" t="n">
-        <v>1639.2</v>
+        <v>1665.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1385</v>
+        <v>1345</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>St John's</t>
+          <t>Purdue</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2030,68 +2030,68 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>04</t>
         </is>
       </c>
       <c r="E23" t="b">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G23" t="n">
-        <v>1961.4</v>
+        <v>1955.6</v>
       </c>
       <c r="H23" t="n">
-        <v>5.5897</v>
+        <v>0.3963</v>
       </c>
       <c r="I23" t="n">
-        <v>113.79</v>
+        <v>124.64</v>
       </c>
       <c r="J23" t="n">
-        <v>98.7</v>
+        <v>107.6</v>
       </c>
       <c r="K23" t="n">
-        <v>15.09</v>
+        <v>17.04</v>
       </c>
       <c r="L23" t="n">
-        <v>0.3238</v>
+        <v>0.3051</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1418</v>
+        <v>0.1348</v>
       </c>
       <c r="N23" t="n">
-        <v>7.8</v>
+        <v>3.8</v>
       </c>
       <c r="O23" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="P23" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q23" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="R23" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="T23" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="U23" t="n">
-        <v>1680.5</v>
+        <v>1746.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1257</v>
+        <v>1385</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Louisville</t>
+          <t>St John's</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2101,68 +2101,68 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>05</t>
         </is>
       </c>
       <c r="E24" t="b">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G24" t="n">
-        <v>1845.2</v>
+        <v>1961.4</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.9919</v>
+        <v>5.5897</v>
       </c>
       <c r="I24" t="n">
-        <v>120.19</v>
+        <v>113.79</v>
       </c>
       <c r="J24" t="n">
-        <v>101.95</v>
+        <v>98.7</v>
       </c>
       <c r="K24" t="n">
-        <v>18.24</v>
+        <v>15.09</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2897</v>
+        <v>0.3238</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1578</v>
+        <v>0.1418</v>
       </c>
       <c r="N24" t="n">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="O24" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="P24" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="Q24" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="R24" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="S24" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="T24" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="U24" t="n">
-        <v>1682.1</v>
+        <v>1680.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1388</v>
+        <v>1257</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>St Mary's CA</t>
+          <t>Louisville</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2172,68 +2172,68 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>06</t>
         </is>
       </c>
       <c r="E25" t="b">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G25" t="n">
-        <v>1857.8</v>
+        <v>1845.2</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.2818</v>
+        <v>-2.9919</v>
       </c>
       <c r="I25" t="n">
-        <v>118.73</v>
+        <v>120.19</v>
       </c>
       <c r="J25" t="n">
-        <v>99.88</v>
+        <v>101.95</v>
       </c>
       <c r="K25" t="n">
-        <v>18.85</v>
+        <v>18.24</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2975</v>
+        <v>0.2897</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1525</v>
+        <v>0.1578</v>
       </c>
       <c r="N25" t="n">
-        <v>8.6</v>
+        <v>5.4</v>
       </c>
       <c r="O25" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="P25" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q25" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="R25" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="S25" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="T25" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="U25" t="n">
-        <v>1596.9</v>
+        <v>1682.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1429</v>
+        <v>1388</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Utah St</t>
+          <t>St Mary's CA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2243,68 +2243,68 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>07</t>
         </is>
       </c>
       <c r="E26" t="b">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G26" t="n">
-        <v>1869.8</v>
+        <v>1857.8</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2419</v>
+        <v>-0.2818</v>
       </c>
       <c r="I26" t="n">
-        <v>120.49</v>
+        <v>118.73</v>
       </c>
       <c r="J26" t="n">
-        <v>105.01</v>
+        <v>99.88</v>
       </c>
       <c r="K26" t="n">
-        <v>15.48</v>
+        <v>18.85</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3065</v>
+        <v>0.2975</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1487</v>
+        <v>0.1525</v>
       </c>
       <c r="N26" t="n">
-        <v>-7.6</v>
+        <v>8.6</v>
       </c>
       <c r="O26" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="P26" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="Q26" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="R26" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="S26" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="T26" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="U26" t="n">
-        <v>1599.2</v>
+        <v>1596.9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1395</v>
+        <v>1274</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TCU</t>
+          <t>Miami FL</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>08</t>
         </is>
       </c>
       <c r="E27" t="b">
@@ -2324,58 +2324,58 @@
         <v>124</v>
       </c>
       <c r="G27" t="n">
-        <v>1836.3</v>
+        <v>1761</v>
       </c>
       <c r="H27" t="n">
-        <v>6.8916</v>
+        <v>12.4806</v>
       </c>
       <c r="I27" t="n">
-        <v>110.72</v>
+        <v>118.15</v>
       </c>
       <c r="J27" t="n">
-        <v>101.25</v>
+        <v>101.88</v>
       </c>
       <c r="K27" t="n">
-        <v>9.460000000000001</v>
+        <v>16.27</v>
       </c>
       <c r="L27" t="n">
-        <v>0.3192</v>
+        <v>0.3077</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1507</v>
+        <v>0.1596</v>
       </c>
       <c r="N27" t="n">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="O27" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="P27" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="Q27" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="R27" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="S27" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="T27" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="U27" t="n">
-        <v>1679.3</v>
+        <v>1617.1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1281</v>
+        <v>1395</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>TCU</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>09</t>
         </is>
       </c>
       <c r="E28" t="b">
@@ -2395,58 +2395,58 @@
         <v>124</v>
       </c>
       <c r="G28" t="n">
-        <v>1757.5</v>
+        <v>1836.3</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.923</v>
+        <v>6.8916</v>
       </c>
       <c r="I28" t="n">
-        <v>115.19</v>
+        <v>110.72</v>
       </c>
       <c r="J28" t="n">
-        <v>109.25</v>
+        <v>101.25</v>
       </c>
       <c r="K28" t="n">
-        <v>5.95</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="L28" t="n">
-        <v>0.3014</v>
+        <v>0.3192</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1701</v>
+        <v>0.1507</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O28" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="P28" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="Q28" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="R28" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="S28" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="T28" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="U28" t="n">
-        <v>1651.9</v>
+        <v>1679.3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1433</v>
+        <v>1400</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VCU</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2456,68 +2456,68 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>11a</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G29" t="n">
-        <v>1739.9</v>
+        <v>1757.7</v>
       </c>
       <c r="H29" t="n">
-        <v>2.9764</v>
+        <v>2.865</v>
       </c>
       <c r="I29" t="n">
-        <v>118.46</v>
+        <v>120.37</v>
       </c>
       <c r="J29" t="n">
-        <v>103.76</v>
+        <v>111.34</v>
       </c>
       <c r="K29" t="n">
-        <v>14.7</v>
+        <v>9.02</v>
       </c>
       <c r="L29" t="n">
-        <v>0.2979</v>
+        <v>0.3098</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1497</v>
+        <v>0.1494</v>
       </c>
       <c r="N29" t="n">
-        <v>6.2</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="O29" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="P29" t="n">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="Q29" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="R29" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="S29" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="T29" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="U29" t="n">
-        <v>1554.6</v>
+        <v>1699.4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1120</v>
+        <v>1281</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Auburn</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2527,68 +2527,68 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>11b</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>124</v>
       </c>
       <c r="G30" t="n">
-        <v>1831.7</v>
+        <v>1757.5</v>
       </c>
       <c r="H30" t="n">
-        <v>-7.7196</v>
+        <v>-1.923</v>
       </c>
       <c r="I30" t="n">
-        <v>119.16</v>
+        <v>115.19</v>
       </c>
       <c r="J30" t="n">
-        <v>114.92</v>
+        <v>109.25</v>
       </c>
       <c r="K30" t="n">
-        <v>4.25</v>
+        <v>5.95</v>
       </c>
       <c r="L30" t="n">
-        <v>0.3497</v>
+        <v>0.3014</v>
       </c>
       <c r="M30" t="n">
-        <v>0.1459</v>
+        <v>0.1701</v>
       </c>
       <c r="N30" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
+        <v>50</v>
+      </c>
+      <c r="P30" t="n">
         <v>39</v>
       </c>
-      <c r="P30" t="n">
-        <v>31</v>
-      </c>
       <c r="Q30" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="R30" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="S30" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="T30" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="U30" t="n">
-        <v>1758.3</v>
+        <v>1651.9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1463</v>
+        <v>1378</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Yale</t>
+          <t>South Florida</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2605,52 +2605,52 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G31" t="n">
-        <v>1720.2</v>
+        <v>1711.8</v>
       </c>
       <c r="H31" t="n">
-        <v>1.1161</v>
+        <v>9.207800000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>120.93</v>
+        <v>116.06</v>
       </c>
       <c r="J31" t="n">
-        <v>107.17</v>
+        <v>101.73</v>
       </c>
       <c r="K31" t="n">
-        <v>13.77</v>
+        <v>14.32</v>
       </c>
       <c r="L31" t="n">
-        <v>0.2847</v>
+        <v>0.3392</v>
       </c>
       <c r="M31" t="n">
-        <v>0.1362</v>
+        <v>0.1453</v>
       </c>
       <c r="N31" t="n">
-        <v>6.6</v>
+        <v>19.6</v>
       </c>
       <c r="O31" t="n">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="P31" t="n">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="Q31" t="n">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="R31" t="n">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="S31" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="T31" t="n">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="U31" t="n">
-        <v>1457.4</v>
+        <v>1553.3</v>
       </c>
     </row>
     <row r="32">
@@ -2726,11 +2726,11 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1414</v>
+        <v>1460</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>UC Irvine</t>
+          <t>Wright St</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2747,61 +2747,61 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G33" t="n">
-        <v>1614.5</v>
+        <v>1470.5</v>
       </c>
       <c r="H33" t="n">
-        <v>2.2068</v>
+        <v>2.7419</v>
       </c>
       <c r="I33" t="n">
-        <v>103.59</v>
+        <v>115.44</v>
       </c>
       <c r="J33" t="n">
-        <v>96.37</v>
+        <v>108.91</v>
       </c>
       <c r="K33" t="n">
-        <v>7.22</v>
+        <v>6.53</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2658</v>
+        <v>0.2971</v>
       </c>
       <c r="M33" t="n">
-        <v>0.1712</v>
+        <v>0.1569</v>
       </c>
       <c r="N33" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O33" t="n">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="P33" t="n">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="Q33" t="n">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="R33" t="n">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="S33" t="n">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="T33" t="n">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="U33" t="n">
-        <v>1471.2</v>
+        <v>1431.7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1340</v>
+        <v>1202</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Portland St</t>
+          <t>Furman</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2818,61 +2818,61 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G34" t="n">
-        <v>1460.1</v>
+        <v>1542.9</v>
       </c>
       <c r="H34" t="n">
-        <v>2.001</v>
+        <v>0.8197</v>
       </c>
       <c r="I34" t="n">
-        <v>105.77</v>
+        <v>112.01</v>
       </c>
       <c r="J34" t="n">
-        <v>101.47</v>
+        <v>107.28</v>
       </c>
       <c r="K34" t="n">
-        <v>4.29</v>
+        <v>4.73</v>
       </c>
       <c r="L34" t="n">
-        <v>0.2576</v>
+        <v>0.2562</v>
       </c>
       <c r="M34" t="n">
-        <v>0.1661</v>
+        <v>0.171</v>
       </c>
       <c r="N34" t="n">
-        <v>-0.4</v>
+        <v>5.6</v>
       </c>
       <c r="O34" t="n">
-        <v>141</v>
+        <v>199</v>
       </c>
       <c r="P34" t="n">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="Q34" t="n">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="R34" t="n">
-        <v>157</v>
+        <v>189</v>
       </c>
       <c r="S34" t="n">
-        <v>139</v>
+        <v>192</v>
       </c>
       <c r="T34" t="n">
-        <v>136</v>
+        <v>194</v>
       </c>
       <c r="U34" t="n">
-        <v>1413.3</v>
+        <v>1422.2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1202</v>
+        <v>1126</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Furman</t>
+          <t>Bethune-Cookman</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2889,61 +2889,61 @@
         <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G35" t="n">
-        <v>1542.9</v>
+        <v>1375.4</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8197</v>
+        <v>0.9205</v>
       </c>
       <c r="I35" t="n">
-        <v>112.01</v>
+        <v>104.96</v>
       </c>
       <c r="J35" t="n">
-        <v>107.28</v>
+        <v>108.7</v>
       </c>
       <c r="K35" t="n">
-        <v>4.73</v>
+        <v>-3.74</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2562</v>
+        <v>0.2778</v>
       </c>
       <c r="M35" t="n">
-        <v>0.171</v>
+        <v>0.1862</v>
       </c>
       <c r="N35" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="O35" t="n">
-        <v>199</v>
+        <v>238</v>
       </c>
       <c r="P35" t="n">
-        <v>170</v>
+        <v>271</v>
       </c>
       <c r="Q35" t="n">
-        <v>193</v>
+        <v>268</v>
       </c>
       <c r="R35" t="n">
-        <v>189</v>
+        <v>214</v>
       </c>
       <c r="S35" t="n">
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="T35" t="n">
-        <v>194</v>
+        <v>255</v>
       </c>
       <c r="U35" t="n">
-        <v>1422.2</v>
+        <v>1436.6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1224</v>
+        <v>1250</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Howard</t>
+          <t>Lehigh</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2960,52 +2960,52 @@
         <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G36" t="n">
-        <v>1409</v>
+        <v>1323.1</v>
       </c>
       <c r="H36" t="n">
-        <v>3.2279</v>
+        <v>-0.5849</v>
       </c>
       <c r="I36" t="n">
-        <v>109.08</v>
+        <v>104.76</v>
       </c>
       <c r="J36" t="n">
-        <v>98.81</v>
+        <v>108.58</v>
       </c>
       <c r="K36" t="n">
-        <v>10.27</v>
+        <v>-3.82</v>
       </c>
       <c r="L36" t="n">
-        <v>0.3126</v>
+        <v>0.214</v>
       </c>
       <c r="M36" t="n">
-        <v>0.1855</v>
+        <v>0.1729</v>
       </c>
       <c r="N36" t="n">
-        <v>23.6</v>
+        <v>5.6</v>
       </c>
       <c r="O36" t="n">
-        <v>202</v>
+        <v>290</v>
       </c>
       <c r="P36" t="n">
-        <v>250</v>
+        <v>295</v>
       </c>
       <c r="Q36" t="n">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="R36" t="n">
-        <v>198</v>
+        <v>282</v>
       </c>
       <c r="S36" t="n">
-        <v>232</v>
+        <v>268</v>
       </c>
       <c r="T36" t="n">
-        <v>202</v>
+        <v>282</v>
       </c>
       <c r="U36" t="n">
-        <v>1380.6</v>
+        <v>1401.7</v>
       </c>
     </row>
     <row r="37">
@@ -3152,11 +3152,11 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1345</v>
+        <v>1235</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Purdue</t>
+          <t>Iowa St</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3176,58 +3176,58 @@
         <v>124</v>
       </c>
       <c r="G39" t="n">
-        <v>1955.6</v>
+        <v>2027.4</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3963</v>
+        <v>3.1622</v>
       </c>
       <c r="I39" t="n">
-        <v>124.64</v>
+        <v>118.43</v>
       </c>
       <c r="J39" t="n">
-        <v>107.6</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>17.04</v>
+        <v>22.42</v>
       </c>
       <c r="L39" t="n">
-        <v>0.3051</v>
+        <v>0.3184</v>
       </c>
       <c r="M39" t="n">
-        <v>0.1348</v>
+        <v>0.1465</v>
       </c>
       <c r="N39" t="n">
-        <v>3.8</v>
+        <v>0.4</v>
       </c>
       <c r="O39" t="n">
+        <v>7</v>
+      </c>
+      <c r="P39" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>6</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6</v>
+      </c>
+      <c r="S39" t="n">
+        <v>11</v>
+      </c>
+      <c r="T39" t="n">
         <v>8</v>
       </c>
-      <c r="P39" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>8</v>
-      </c>
-      <c r="R39" t="n">
-        <v>8</v>
-      </c>
-      <c r="S39" t="n">
-        <v>13</v>
-      </c>
-      <c r="T39" t="n">
-        <v>10</v>
-      </c>
       <c r="U39" t="n">
-        <v>1746.9</v>
+        <v>1686.9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1242</v>
+        <v>1403</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Texas Tech</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3247,58 +3247,58 @@
         <v>124</v>
       </c>
       <c r="G40" t="n">
-        <v>1973.7</v>
+        <v>2025.5</v>
       </c>
       <c r="H40" t="n">
-        <v>11.337</v>
+        <v>10.1327</v>
       </c>
       <c r="I40" t="n">
-        <v>111.61</v>
+        <v>118.86</v>
       </c>
       <c r="J40" t="n">
-        <v>100.9</v>
+        <v>106.69</v>
       </c>
       <c r="K40" t="n">
-        <v>10.71</v>
+        <v>12.16</v>
       </c>
       <c r="L40" t="n">
-        <v>0.2487</v>
+        <v>0.2944</v>
       </c>
       <c r="M40" t="n">
-        <v>0.1523</v>
+        <v>0.155</v>
       </c>
       <c r="N40" t="n">
-        <v>-3.4</v>
+        <v>7</v>
       </c>
       <c r="O40" t="n">
+        <v>17</v>
+      </c>
+      <c r="P40" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q40" t="n">
         <v>19</v>
       </c>
-      <c r="P40" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>14</v>
-      </c>
       <c r="R40" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="S40" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T40" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="U40" t="n">
-        <v>1772.3</v>
+        <v>1762.7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1435</v>
+        <v>1397</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Vanderbilt</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3318,58 +3318,58 @@
         <v>124</v>
       </c>
       <c r="G41" t="n">
-        <v>1935.7</v>
+        <v>1898.6</v>
       </c>
       <c r="H41" t="n">
-        <v>2.1989</v>
+        <v>-1.6704</v>
       </c>
       <c r="I41" t="n">
-        <v>121.8</v>
+        <v>117.06</v>
       </c>
       <c r="J41" t="n">
-        <v>105.67</v>
+        <v>101.96</v>
       </c>
       <c r="K41" t="n">
-        <v>16.12</v>
+        <v>15.09</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2802</v>
+        <v>0.3583</v>
       </c>
       <c r="M41" t="n">
-        <v>0.1278</v>
+        <v>0.1671</v>
       </c>
       <c r="N41" t="n">
-        <v>-0.6</v>
+        <v>2.6</v>
       </c>
       <c r="O41" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P41" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Q41" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="R41" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="S41" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="T41" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="U41" t="n">
-        <v>1694.9</v>
+        <v>1706.1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1314</v>
+        <v>1458</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3389,58 +3389,58 @@
         <v>124</v>
       </c>
       <c r="G42" t="n">
-        <v>1917.6</v>
+        <v>1859.5</v>
       </c>
       <c r="H42" t="n">
-        <v>2.3735</v>
+        <v>1.6302</v>
       </c>
       <c r="I42" t="n">
-        <v>115.09</v>
+        <v>119.64</v>
       </c>
       <c r="J42" t="n">
-        <v>103.39</v>
+        <v>108.42</v>
       </c>
       <c r="K42" t="n">
-        <v>11.71</v>
+        <v>11.21</v>
       </c>
       <c r="L42" t="n">
-        <v>0.2653</v>
+        <v>0.276</v>
       </c>
       <c r="M42" t="n">
-        <v>0.14</v>
+        <v>0.1244</v>
       </c>
       <c r="N42" t="n">
-        <v>2.4</v>
+        <v>10.6</v>
       </c>
       <c r="O42" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="P42" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q42" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R42" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S42" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="T42" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="U42" t="n">
-        <v>1676</v>
+        <v>1701.3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1246</v>
+        <v>1208</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3460,58 +3460,58 @@
         <v>124</v>
       </c>
       <c r="G43" t="n">
-        <v>1881.8</v>
+        <v>1816.9</v>
       </c>
       <c r="H43" t="n">
-        <v>5.4881</v>
+        <v>0.2065</v>
       </c>
       <c r="I43" t="n">
-        <v>116.58</v>
+        <v>121.14</v>
       </c>
       <c r="J43" t="n">
-        <v>106.11</v>
+        <v>107.06</v>
       </c>
       <c r="K43" t="n">
-        <v>10.47</v>
+        <v>14.09</v>
       </c>
       <c r="L43" t="n">
-        <v>0.3117</v>
+        <v>0.3227</v>
       </c>
       <c r="M43" t="n">
-        <v>0.1455</v>
+        <v>0.1388</v>
       </c>
       <c r="N43" t="n">
-        <v>0.8</v>
+        <v>7.6</v>
       </c>
       <c r="O43" t="n">
+        <v>31</v>
+      </c>
+      <c r="P43" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>28</v>
+      </c>
+      <c r="R43" t="n">
         <v>27</v>
       </c>
-      <c r="P43" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>26</v>
-      </c>
-      <c r="R43" t="n">
+      <c r="S43" t="n">
         <v>32</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>31</v>
       </c>
-      <c r="T43" t="n">
-        <v>28</v>
-      </c>
       <c r="U43" t="n">
-        <v>1728.4</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1155</v>
+        <v>1326</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Clemson</t>
+          <t>Ohio St</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3531,58 +3531,58 @@
         <v>124</v>
       </c>
       <c r="G44" t="n">
-        <v>1838.2</v>
+        <v>1799.9</v>
       </c>
       <c r="H44" t="n">
-        <v>3.3876</v>
+        <v>1.5472</v>
       </c>
       <c r="I44" t="n">
-        <v>112.83</v>
+        <v>118.74</v>
       </c>
       <c r="J44" t="n">
-        <v>100.58</v>
+        <v>107.91</v>
       </c>
       <c r="K44" t="n">
-        <v>12.25</v>
+        <v>10.83</v>
       </c>
       <c r="L44" t="n">
-        <v>0.2488</v>
+        <v>0.2524</v>
       </c>
       <c r="M44" t="n">
-        <v>0.1395</v>
+        <v>0.1503</v>
       </c>
       <c r="N44" t="n">
-        <v>-1.8</v>
+        <v>6</v>
       </c>
       <c r="O44" t="n">
+        <v>26</v>
+      </c>
+      <c r="P44" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>29</v>
+      </c>
+      <c r="R44" t="n">
+        <v>29</v>
+      </c>
+      <c r="S44" t="n">
         <v>38</v>
       </c>
-      <c r="P44" t="n">
-        <v>34</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>32</v>
-      </c>
-      <c r="R44" t="n">
-        <v>35</v>
-      </c>
-      <c r="S44" t="n">
-        <v>34</v>
-      </c>
       <c r="T44" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="U44" t="n">
-        <v>1641.6</v>
+        <v>1700.1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1387</v>
+        <v>1155</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>St Louis</t>
+          <t>Clemson</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3602,58 +3602,58 @@
         <v>124</v>
       </c>
       <c r="G45" t="n">
-        <v>1807.8</v>
+        <v>1838.2</v>
       </c>
       <c r="H45" t="n">
-        <v>9.839</v>
+        <v>3.3876</v>
       </c>
       <c r="I45" t="n">
-        <v>120.36</v>
+        <v>112.83</v>
       </c>
       <c r="J45" t="n">
-        <v>98.52</v>
+        <v>100.58</v>
       </c>
       <c r="K45" t="n">
-        <v>21.84</v>
+        <v>12.25</v>
       </c>
       <c r="L45" t="n">
-        <v>0.2436</v>
+        <v>0.2488</v>
       </c>
       <c r="M45" t="n">
-        <v>0.1686</v>
+        <v>0.1395</v>
       </c>
       <c r="N45" t="n">
-        <v>-0.4</v>
+        <v>-1.8</v>
       </c>
       <c r="O45" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="P45" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="Q45" t="n">
+        <v>32</v>
+      </c>
+      <c r="R45" t="n">
+        <v>35</v>
+      </c>
+      <c r="S45" t="n">
+        <v>34</v>
+      </c>
+      <c r="T45" t="n">
         <v>36</v>
       </c>
-      <c r="R45" t="n">
-        <v>30</v>
-      </c>
-      <c r="S45" t="n">
-        <v>28</v>
-      </c>
-      <c r="T45" t="n">
-        <v>27</v>
-      </c>
       <c r="U45" t="n">
-        <v>1512.1</v>
+        <v>1641.6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1234</v>
+        <v>1301</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Iowa</t>
+          <t>NC State</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3670,61 +3670,61 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G46" t="n">
-        <v>1843.7</v>
+        <v>1735.9</v>
       </c>
       <c r="H46" t="n">
-        <v>4.0673</v>
+        <v>7.7247</v>
       </c>
       <c r="I46" t="n">
-        <v>118.63</v>
+        <v>118.75</v>
       </c>
       <c r="J46" t="n">
-        <v>104.06</v>
+        <v>108.16</v>
       </c>
       <c r="K46" t="n">
-        <v>14.56</v>
+        <v>10.59</v>
       </c>
       <c r="L46" t="n">
-        <v>0.288</v>
+        <v>0.2829</v>
       </c>
       <c r="M46" t="n">
-        <v>0.1446</v>
+        <v>0.1296</v>
       </c>
       <c r="N46" t="n">
-        <v>-2</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="O46" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="P46" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Q46" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="R46" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="S46" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="T46" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="U46" t="n">
-        <v>1715.1</v>
+        <v>1675.6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1275</v>
+        <v>1374</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Miami OH</t>
+          <t>SMU</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3734,68 +3734,68 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>11a</t>
         </is>
       </c>
       <c r="E47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G47" t="n">
-        <v>1775.2</v>
+        <v>1744.5</v>
       </c>
       <c r="H47" t="n">
-        <v>9.651999999999999</v>
+        <v>0.5256999999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>120.89</v>
+        <v>119.02</v>
       </c>
       <c r="J47" t="n">
-        <v>105.23</v>
+        <v>110.02</v>
       </c>
       <c r="K47" t="n">
-        <v>15.66</v>
+        <v>9</v>
       </c>
       <c r="L47" t="n">
-        <v>0.2107</v>
+        <v>0.3105</v>
       </c>
       <c r="M47" t="n">
-        <v>0.1402</v>
+        <v>0.1505</v>
       </c>
       <c r="N47" t="n">
-        <v>6</v>
+        <v>-5.6</v>
       </c>
       <c r="O47" t="n">
-        <v>91</v>
+        <v>43</v>
       </c>
       <c r="P47" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q47" t="n">
-        <v>87</v>
+        <v>39</v>
       </c>
       <c r="R47" t="n">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="T47" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="U47" t="n">
-        <v>1414.6</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1219</v>
+        <v>1433</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>High Point</t>
+          <t>VCU</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3805,68 +3805,68 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11b</t>
         </is>
       </c>
       <c r="E48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G48" t="n">
-        <v>1625.5</v>
+        <v>1739.9</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.8564000000000001</v>
+        <v>2.9764</v>
       </c>
       <c r="I48" t="n">
-        <v>121.16</v>
+        <v>118.46</v>
       </c>
       <c r="J48" t="n">
-        <v>100.19</v>
+        <v>103.76</v>
       </c>
       <c r="K48" t="n">
-        <v>20.97</v>
+        <v>14.7</v>
       </c>
       <c r="L48" t="n">
-        <v>0.3061</v>
+        <v>0.2979</v>
       </c>
       <c r="M48" t="n">
-        <v>0.1276</v>
+        <v>0.1497</v>
       </c>
       <c r="N48" t="n">
-        <v>9.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="O48" t="n">
-        <v>93</v>
+        <v>45</v>
       </c>
       <c r="P48" t="n">
-        <v>93</v>
+        <v>54</v>
       </c>
       <c r="Q48" t="n">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="R48" t="n">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="S48" t="n">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="T48" t="n">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="U48" t="n">
-        <v>1382.5</v>
+        <v>1554.6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1295</v>
+        <v>1320</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>N Dakota St</t>
+          <t>Northern Iowa</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E49" t="b">
@@ -3886,58 +3886,58 @@
         <v>125</v>
       </c>
       <c r="G49" t="n">
-        <v>1593.8</v>
+        <v>1573.9</v>
       </c>
       <c r="H49" t="n">
-        <v>3.5257</v>
+        <v>-3.696</v>
       </c>
       <c r="I49" t="n">
-        <v>114.28</v>
+        <v>108.74</v>
       </c>
       <c r="J49" t="n">
-        <v>102.18</v>
+        <v>97.5</v>
       </c>
       <c r="K49" t="n">
-        <v>12.1</v>
+        <v>11.25</v>
       </c>
       <c r="L49" t="n">
-        <v>0.3104</v>
+        <v>0.225</v>
       </c>
       <c r="M49" t="n">
-        <v>0.1506</v>
+        <v>0.1354</v>
       </c>
       <c r="N49" t="n">
-        <v>10.8</v>
+        <v>14.4</v>
       </c>
       <c r="O49" t="n">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="P49" t="n">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="Q49" t="n">
-        <v>163</v>
+        <v>72</v>
       </c>
       <c r="R49" t="n">
-        <v>115</v>
+        <v>76</v>
       </c>
       <c r="S49" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="T49" t="n">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="U49" t="n">
-        <v>1410.6</v>
+        <v>1515.8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1220</v>
+        <v>1430</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Hofstra</t>
+          <t>Utah Valley</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3947,68 +3947,68 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E50" t="b">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G50" t="n">
-        <v>1582</v>
+        <v>1637</v>
       </c>
       <c r="H50" t="n">
-        <v>3.5064</v>
+        <v>3.1528</v>
       </c>
       <c r="I50" t="n">
-        <v>113.54</v>
+        <v>111.58</v>
       </c>
       <c r="J50" t="n">
-        <v>102.66</v>
+        <v>100.45</v>
       </c>
       <c r="K50" t="n">
-        <v>10.88</v>
+        <v>11.12</v>
       </c>
       <c r="L50" t="n">
-        <v>0.3074</v>
+        <v>0.3056</v>
       </c>
       <c r="M50" t="n">
-        <v>0.1523</v>
+        <v>0.1962</v>
       </c>
       <c r="N50" t="n">
-        <v>13.6</v>
+        <v>6.6</v>
       </c>
       <c r="O50" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="P50" t="n">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="Q50" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="R50" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="S50" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="T50" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="U50" t="n">
-        <v>1484.4</v>
+        <v>1455.5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1467</v>
+        <v>1295</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Merrimack</t>
+          <t>N Dakota St</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E51" t="b">
@@ -4028,58 +4028,58 @@
         <v>125</v>
       </c>
       <c r="G51" t="n">
-        <v>1521.4</v>
+        <v>1593.8</v>
       </c>
       <c r="H51" t="n">
-        <v>3.9296</v>
+        <v>3.5257</v>
       </c>
       <c r="I51" t="n">
-        <v>107.03</v>
+        <v>114.28</v>
       </c>
       <c r="J51" t="n">
-        <v>102.73</v>
+        <v>102.18</v>
       </c>
       <c r="K51" t="n">
-        <v>4.29</v>
+        <v>12.1</v>
       </c>
       <c r="L51" t="n">
-        <v>0.2687</v>
+        <v>0.3104</v>
       </c>
       <c r="M51" t="n">
-        <v>0.1436</v>
+        <v>0.1506</v>
       </c>
       <c r="N51" t="n">
-        <v>5.4</v>
+        <v>10.8</v>
       </c>
       <c r="O51" t="n">
-        <v>174</v>
+        <v>114</v>
       </c>
       <c r="P51" t="n">
-        <v>169</v>
+        <v>116</v>
       </c>
       <c r="Q51" t="n">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="R51" t="n">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="S51" t="n">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="T51" t="n">
-        <v>173</v>
+        <v>115</v>
       </c>
       <c r="U51" t="n">
-        <v>1455.8</v>
+        <v>1410.6</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1250</v>
+        <v>1474</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Lehigh</t>
+          <t>Queens NC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4089,68 +4089,68 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>16a</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
         <v>125</v>
       </c>
       <c r="G52" t="n">
-        <v>1323.1</v>
+        <v>1427.4</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.5849</v>
+        <v>1.0039</v>
       </c>
       <c r="I52" t="n">
-        <v>104.76</v>
+        <v>119.17</v>
       </c>
       <c r="J52" t="n">
-        <v>108.58</v>
+        <v>116.56</v>
       </c>
       <c r="K52" t="n">
-        <v>-3.82</v>
+        <v>2.61</v>
       </c>
       <c r="L52" t="n">
-        <v>0.214</v>
+        <v>0.2859</v>
       </c>
       <c r="M52" t="n">
-        <v>0.1729</v>
+        <v>0.1441</v>
       </c>
       <c r="N52" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="O52" t="n">
-        <v>290</v>
+        <v>183</v>
       </c>
       <c r="P52" t="n">
-        <v>295</v>
+        <v>192</v>
       </c>
       <c r="Q52" t="n">
-        <v>279</v>
+        <v>181</v>
       </c>
       <c r="R52" t="n">
-        <v>282</v>
+        <v>177</v>
       </c>
       <c r="S52" t="n">
-        <v>268</v>
+        <v>171</v>
       </c>
       <c r="T52" t="n">
-        <v>282</v>
+        <v>187</v>
       </c>
       <c r="U52" t="n">
-        <v>1401.7</v>
+        <v>1430.9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1126</v>
+        <v>1254</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Bethune-Cookman</t>
+          <t>LIU Brooklyn</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4160,59 +4160,59 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>16b</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G53" t="n">
-        <v>1375.4</v>
+        <v>1418.2</v>
       </c>
       <c r="H53" t="n">
-        <v>0.9205</v>
+        <v>2.3581</v>
       </c>
       <c r="I53" t="n">
-        <v>104.96</v>
+        <v>109.38</v>
       </c>
       <c r="J53" t="n">
-        <v>108.7</v>
+        <v>104.38</v>
       </c>
       <c r="K53" t="n">
-        <v>-3.74</v>
+        <v>5</v>
       </c>
       <c r="L53" t="n">
-        <v>0.2778</v>
+        <v>0.3119</v>
       </c>
       <c r="M53" t="n">
-        <v>0.1862</v>
+        <v>0.183</v>
       </c>
       <c r="N53" t="n">
-        <v>4.8</v>
+        <v>10.4</v>
       </c>
       <c r="O53" t="n">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="P53" t="n">
-        <v>271</v>
+        <v>228</v>
       </c>
       <c r="Q53" t="n">
-        <v>268</v>
+        <v>213</v>
       </c>
       <c r="R53" t="n">
-        <v>214</v>
+        <v>188</v>
       </c>
       <c r="S53" t="n">
-        <v>216</v>
+        <v>166</v>
       </c>
       <c r="T53" t="n">
-        <v>255</v>
+        <v>200</v>
       </c>
       <c r="U53" t="n">
-        <v>1436.6</v>
+        <v>1378.8</v>
       </c>
     </row>
     <row r="54">
@@ -4359,11 +4359,11 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1104</v>
+        <v>1211</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Alabama</t>
+          <t>Gonzaga</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4380,61 +4380,61 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G56" t="n">
-        <v>1975.1</v>
+        <v>2068.3</v>
       </c>
       <c r="H56" t="n">
-        <v>-1.4869</v>
+        <v>5.8188</v>
       </c>
       <c r="I56" t="n">
-        <v>122.11</v>
+        <v>120.75</v>
       </c>
       <c r="J56" t="n">
-        <v>110.78</v>
+        <v>93.89</v>
       </c>
       <c r="K56" t="n">
-        <v>11.33</v>
+        <v>26.86</v>
       </c>
       <c r="L56" t="n">
-        <v>0.2853</v>
+        <v>0.2992</v>
       </c>
       <c r="M56" t="n">
-        <v>0.1289</v>
+        <v>0.1335</v>
       </c>
       <c r="N56" t="n">
-        <v>7.2</v>
+        <v>11.8</v>
       </c>
       <c r="O56" t="n">
+        <v>10</v>
+      </c>
+      <c r="P56" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q56" t="n">
         <v>15</v>
       </c>
-      <c r="P56" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>12</v>
-      </c>
       <c r="R56" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="S56" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T56" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="U56" t="n">
-        <v>1772.1</v>
+        <v>1601.3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1211</v>
+        <v>1438</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Gonzaga</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4451,61 +4451,61 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G57" t="n">
-        <v>2063.2</v>
+        <v>1956.5</v>
       </c>
       <c r="H57" t="n">
-        <v>6.2559</v>
+        <v>13.4946</v>
       </c>
       <c r="I57" t="n">
-        <v>120.06</v>
+        <v>118.84</v>
       </c>
       <c r="J57" t="n">
-        <v>92.98999999999999</v>
+        <v>100.06</v>
       </c>
       <c r="K57" t="n">
-        <v>27.07</v>
+        <v>18.77</v>
       </c>
       <c r="L57" t="n">
-        <v>0.2963</v>
+        <v>0.3168</v>
       </c>
       <c r="M57" t="n">
-        <v>0.1337</v>
+        <v>0.1532</v>
       </c>
       <c r="N57" t="n">
-        <v>13.8</v>
+        <v>3</v>
       </c>
       <c r="O57" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="P57" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="Q57" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="R57" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T57" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="U57" t="n">
-        <v>1593.1</v>
+        <v>1639.2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1397</v>
+        <v>1116</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4525,49 +4525,49 @@
         <v>124</v>
       </c>
       <c r="G58" t="n">
-        <v>1898.6</v>
+        <v>1950</v>
       </c>
       <c r="H58" t="n">
-        <v>-1.6704</v>
+        <v>5.5428</v>
       </c>
       <c r="I58" t="n">
-        <v>117.06</v>
+        <v>122.85</v>
       </c>
       <c r="J58" t="n">
-        <v>101.96</v>
+        <v>108.88</v>
       </c>
       <c r="K58" t="n">
-        <v>15.09</v>
+        <v>13.96</v>
       </c>
       <c r="L58" t="n">
-        <v>0.3583</v>
+        <v>0.3009</v>
       </c>
       <c r="M58" t="n">
-        <v>0.1671</v>
+        <v>0.1205</v>
       </c>
       <c r="N58" t="n">
         <v>2.6</v>
       </c>
       <c r="O58" t="n">
+        <v>18</v>
+      </c>
+      <c r="P58" t="n">
         <v>14</v>
       </c>
-      <c r="P58" t="n">
-        <v>17</v>
-      </c>
       <c r="Q58" t="n">
+        <v>20</v>
+      </c>
+      <c r="R58" t="n">
+        <v>16</v>
+      </c>
+      <c r="S58" t="n">
+        <v>21</v>
+      </c>
+      <c r="T58" t="n">
         <v>18</v>
       </c>
-      <c r="R58" t="n">
-        <v>20</v>
-      </c>
-      <c r="S58" t="n">
-        <v>24</v>
-      </c>
-      <c r="T58" t="n">
-        <v>21</v>
-      </c>
       <c r="U58" t="n">
-        <v>1706.1</v>
+        <v>1728.7</v>
       </c>
     </row>
     <row r="59">
@@ -4593,31 +4593,31 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G59" t="n">
-        <v>1924.5</v>
+        <v>1927.8</v>
       </c>
       <c r="H59" t="n">
-        <v>1.6354</v>
+        <v>1.2144</v>
       </c>
       <c r="I59" t="n">
-        <v>118.39</v>
+        <v>118.9</v>
       </c>
       <c r="J59" t="n">
-        <v>106.82</v>
+        <v>107.06</v>
       </c>
       <c r="K59" t="n">
-        <v>11.57</v>
+        <v>11.85</v>
       </c>
       <c r="L59" t="n">
-        <v>0.3034</v>
+        <v>0.3035</v>
       </c>
       <c r="M59" t="n">
-        <v>0.1419</v>
+        <v>0.1427</v>
       </c>
       <c r="N59" t="n">
-        <v>-5.4</v>
+        <v>-4.6</v>
       </c>
       <c r="O59" t="n">
         <v>25</v>
@@ -4638,16 +4638,16 @@
         <v>24</v>
       </c>
       <c r="U59" t="n">
-        <v>1726.9</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1274</v>
+        <v>1246</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Miami FL</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4667,49 +4667,49 @@
         <v>124</v>
       </c>
       <c r="G60" t="n">
-        <v>1761</v>
+        <v>1881.8</v>
       </c>
       <c r="H60" t="n">
-        <v>12.4806</v>
+        <v>5.4881</v>
       </c>
       <c r="I60" t="n">
-        <v>118.15</v>
+        <v>116.58</v>
       </c>
       <c r="J60" t="n">
-        <v>101.88</v>
+        <v>106.11</v>
       </c>
       <c r="K60" t="n">
-        <v>16.27</v>
+        <v>10.47</v>
       </c>
       <c r="L60" t="n">
-        <v>0.3077</v>
+        <v>0.3117</v>
       </c>
       <c r="M60" t="n">
-        <v>0.1596</v>
+        <v>0.1455</v>
       </c>
       <c r="N60" t="n">
-        <v>6.8</v>
+        <v>0.8</v>
       </c>
       <c r="O60" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P60" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="Q60" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R60" t="n">
+        <v>32</v>
+      </c>
+      <c r="S60" t="n">
         <v>31</v>
       </c>
-      <c r="S60" t="n">
-        <v>26</v>
-      </c>
       <c r="T60" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="U60" t="n">
-        <v>1617.1</v>
+        <v>1728.4</v>
       </c>
     </row>
     <row r="61">
@@ -4856,11 +4856,11 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1400</v>
+        <v>1387</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>St Louis</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4880,58 +4880,58 @@
         <v>124</v>
       </c>
       <c r="G63" t="n">
-        <v>1757.7</v>
+        <v>1807.8</v>
       </c>
       <c r="H63" t="n">
-        <v>2.865</v>
+        <v>9.839</v>
       </c>
       <c r="I63" t="n">
-        <v>120.37</v>
+        <v>120.36</v>
       </c>
       <c r="J63" t="n">
-        <v>111.34</v>
+        <v>98.52</v>
       </c>
       <c r="K63" t="n">
-        <v>9.02</v>
+        <v>21.84</v>
       </c>
       <c r="L63" t="n">
-        <v>0.3098</v>
+        <v>0.2436</v>
       </c>
       <c r="M63" t="n">
-        <v>0.1494</v>
+        <v>0.1686</v>
       </c>
       <c r="N63" t="n">
-        <v>-8.199999999999999</v>
+        <v>-0.4</v>
       </c>
       <c r="O63" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="P63" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="Q63" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="R63" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="S63" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="T63" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="U63" t="n">
-        <v>1699.4</v>
+        <v>1512.1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1416</v>
+        <v>1275</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>UCF</t>
+          <t>Miami OH</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4951,58 +4951,58 @@
         <v>123</v>
       </c>
       <c r="G64" t="n">
-        <v>1820.5</v>
+        <v>1775.2</v>
       </c>
       <c r="H64" t="n">
-        <v>7.025</v>
+        <v>9.651999999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>114.77</v>
+        <v>120.89</v>
       </c>
       <c r="J64" t="n">
-        <v>110.49</v>
+        <v>105.23</v>
       </c>
       <c r="K64" t="n">
-        <v>4.28</v>
+        <v>15.66</v>
       </c>
       <c r="L64" t="n">
-        <v>0.3115</v>
+        <v>0.2107</v>
       </c>
       <c r="M64" t="n">
-        <v>0.1546</v>
+        <v>0.1402</v>
       </c>
       <c r="N64" t="n">
-        <v>-1.6</v>
+        <v>6</v>
       </c>
       <c r="O64" t="n">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="P64" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="Q64" t="n">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="R64" t="n">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="S64" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="T64" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="U64" t="n">
-        <v>1687.9</v>
+        <v>1414.6</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1320</v>
+        <v>1463</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Northern Iowa</t>
+          <t>Yale</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5019,61 +5019,61 @@
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G65" t="n">
-        <v>1573.9</v>
+        <v>1720.2</v>
       </c>
       <c r="H65" t="n">
-        <v>-3.696</v>
+        <v>1.1161</v>
       </c>
       <c r="I65" t="n">
-        <v>108.74</v>
+        <v>120.93</v>
       </c>
       <c r="J65" t="n">
-        <v>97.5</v>
+        <v>107.17</v>
       </c>
       <c r="K65" t="n">
-        <v>11.25</v>
+        <v>13.77</v>
       </c>
       <c r="L65" t="n">
-        <v>0.225</v>
+        <v>0.2847</v>
       </c>
       <c r="M65" t="n">
-        <v>0.1354</v>
+        <v>0.1362</v>
       </c>
       <c r="N65" t="n">
-        <v>14.4</v>
+        <v>6.6</v>
       </c>
       <c r="O65" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="P65" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="Q65" t="n">
+        <v>96</v>
+      </c>
+      <c r="R65" t="n">
         <v>72</v>
       </c>
-      <c r="R65" t="n">
-        <v>76</v>
-      </c>
       <c r="S65" t="n">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="T65" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="U65" t="n">
-        <v>1515.8</v>
+        <v>1457.4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1430</v>
+        <v>1372</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Utah Valley</t>
+          <t>SF Austin</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5090,61 +5090,61 @@
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G66" t="n">
-        <v>1637</v>
+        <v>1565.8</v>
       </c>
       <c r="H66" t="n">
-        <v>3.1528</v>
+        <v>3.2279</v>
       </c>
       <c r="I66" t="n">
-        <v>111.58</v>
+        <v>112.79</v>
       </c>
       <c r="J66" t="n">
-        <v>100.45</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="K66" t="n">
-        <v>11.12</v>
+        <v>14.26</v>
       </c>
       <c r="L66" t="n">
-        <v>0.3056</v>
+        <v>0.3083</v>
       </c>
       <c r="M66" t="n">
-        <v>0.1962</v>
+        <v>0.1321</v>
       </c>
       <c r="N66" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="O66" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P66" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="Q66" t="n">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="R66" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="S66" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="T66" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="U66" t="n">
-        <v>1455.5</v>
+        <v>1383.6</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1407</v>
+        <v>1414</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Troy</t>
+          <t>UC Irvine</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5161,52 +5161,52 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G67" t="n">
-        <v>1601</v>
+        <v>1614.5</v>
       </c>
       <c r="H67" t="n">
-        <v>1.1284</v>
+        <v>2.2068</v>
       </c>
       <c r="I67" t="n">
-        <v>112.28</v>
+        <v>103.59</v>
       </c>
       <c r="J67" t="n">
-        <v>106.19</v>
+        <v>96.37</v>
       </c>
       <c r="K67" t="n">
-        <v>6.08</v>
+        <v>7.22</v>
       </c>
       <c r="L67" t="n">
-        <v>0.316</v>
+        <v>0.2658</v>
       </c>
       <c r="M67" t="n">
-        <v>0.1667</v>
+        <v>0.1712</v>
       </c>
       <c r="N67" t="n">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="O67" t="n">
-        <v>153</v>
+        <v>106</v>
       </c>
       <c r="P67" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="Q67" t="n">
-        <v>137</v>
+        <v>105</v>
       </c>
       <c r="R67" t="n">
-        <v>137</v>
+        <v>110</v>
       </c>
       <c r="S67" t="n">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="T67" t="n">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="U67" t="n">
-        <v>1466</v>
+        <v>1471.2</v>
       </c>
     </row>
     <row r="68">
@@ -5282,11 +5282,11 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1254</v>
+        <v>1373</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>LIU Brooklyn</t>
+          <t>Siena</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5303,52 +5303,52 @@
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G69" t="n">
-        <v>1416</v>
+        <v>1478</v>
       </c>
       <c r="H69" t="n">
-        <v>2.4057</v>
+        <v>0.9489</v>
       </c>
       <c r="I69" t="n">
-        <v>108.81</v>
+        <v>109.73</v>
       </c>
       <c r="J69" t="n">
-        <v>104.08</v>
+        <v>101.77</v>
       </c>
       <c r="K69" t="n">
-        <v>4.73</v>
+        <v>7.95</v>
       </c>
       <c r="L69" t="n">
-        <v>0.3167</v>
+        <v>0.2799</v>
       </c>
       <c r="M69" t="n">
-        <v>0.1861</v>
+        <v>0.1508</v>
       </c>
       <c r="N69" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="O69" t="n">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="P69" t="n">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="Q69" t="n">
-        <v>213</v>
+        <v>180</v>
       </c>
       <c r="R69" t="n">
+        <v>172</v>
+      </c>
+      <c r="S69" t="n">
+        <v>177</v>
+      </c>
+      <c r="T69" t="n">
         <v>188</v>
       </c>
-      <c r="S69" t="n">
-        <v>166</v>
-      </c>
-      <c r="T69" t="n">
-        <v>200</v>
-      </c>
       <c r="U69" t="n">
-        <v>1378.3</v>
+        <v>1430.3</v>
       </c>
     </row>
   </sheetData>

--- a/team_stats_2026.xlsx
+++ b/team_stats_2026.xlsx
@@ -1732,11 +1732,11 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1186</v>
+        <v>1285</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>E Washington</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1756,49 +1756,49 @@
         <v>127</v>
       </c>
       <c r="G19" t="n">
-        <v>1317</v>
+        <v>1469.4</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0019</v>
+        <v>-1.5005</v>
       </c>
       <c r="I19" t="n">
-        <v>111.6</v>
+        <v>107.3</v>
       </c>
       <c r="J19" t="n">
-        <v>113.34</v>
+        <v>109.17</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.74</v>
+        <v>-1.87</v>
       </c>
       <c r="L19" t="n">
-        <v>0.287</v>
+        <v>0.1941</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1681</v>
+        <v>0.1861</v>
       </c>
       <c r="N19" t="n">
-        <v>5.8</v>
+        <v>-1</v>
       </c>
       <c r="O19" t="n">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="P19" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="Q19" t="n">
-        <v>210</v>
+        <v>263</v>
       </c>
       <c r="R19" t="n">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="S19" t="n">
-        <v>228</v>
+        <v>199</v>
       </c>
       <c r="T19" t="n">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="U19" t="n">
-        <v>1450.3</v>
+        <v>1435.4</v>
       </c>
     </row>
     <row r="20">

--- a/team_stats_2026.xlsx
+++ b/team_stats_2026.xlsx
@@ -809,11 +809,11 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1435</v>
+        <v>1397</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vanderbilt</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -833,49 +833,49 @@
         <v>124</v>
       </c>
       <c r="G6" t="n">
-        <v>1935.7</v>
+        <v>1898.6</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1989</v>
+        <v>-1.6704</v>
       </c>
       <c r="I6" t="n">
-        <v>121.8</v>
+        <v>117.06</v>
       </c>
       <c r="J6" t="n">
-        <v>105.67</v>
+        <v>101.96</v>
       </c>
       <c r="K6" t="n">
-        <v>16.12</v>
+        <v>15.09</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2802</v>
+        <v>0.3583</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1278</v>
+        <v>0.1671</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6</v>
+        <v>2.6</v>
       </c>
       <c r="O6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Q6" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="R6" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="S6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="T6" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="U6" t="n">
-        <v>1694.9</v>
+        <v>1706.1</v>
       </c>
     </row>
     <row r="7">
@@ -1022,11 +1022,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1429</v>
+        <v>1274</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Utah St</t>
+          <t>Miami FL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1046,49 +1046,49 @@
         <v>124</v>
       </c>
       <c r="G9" t="n">
-        <v>1869.8</v>
+        <v>1761</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2419</v>
+        <v>12.4806</v>
       </c>
       <c r="I9" t="n">
-        <v>120.49</v>
+        <v>118.15</v>
       </c>
       <c r="J9" t="n">
-        <v>105.01</v>
+        <v>101.88</v>
       </c>
       <c r="K9" t="n">
-        <v>15.48</v>
+        <v>16.27</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3065</v>
+        <v>0.3077</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1487</v>
+        <v>0.1596</v>
       </c>
       <c r="N9" t="n">
-        <v>-7.6</v>
+        <v>6.8</v>
       </c>
       <c r="O9" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="P9" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Q9" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="R9" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S9" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="T9" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="U9" t="n">
-        <v>1599.2</v>
+        <v>1617.1</v>
       </c>
     </row>
     <row r="10">
@@ -1114,31 +1114,31 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G10" t="n">
-        <v>1843.7</v>
+        <v>1848.9</v>
       </c>
       <c r="H10" t="n">
-        <v>4.0673</v>
+        <v>3.6941</v>
       </c>
       <c r="I10" t="n">
-        <v>118.63</v>
+        <v>118.64</v>
       </c>
       <c r="J10" t="n">
-        <v>104.06</v>
+        <v>103.68</v>
       </c>
       <c r="K10" t="n">
-        <v>14.56</v>
+        <v>14.95</v>
       </c>
       <c r="L10" t="n">
-        <v>0.288</v>
+        <v>0.2884</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1446</v>
+        <v>0.1443</v>
       </c>
       <c r="N10" t="n">
-        <v>-2</v>
+        <v>2.8</v>
       </c>
       <c r="O10" t="n">
         <v>24</v>
@@ -1159,16 +1159,16 @@
         <v>25</v>
       </c>
       <c r="U10" t="n">
-        <v>1715.1</v>
+        <v>1707.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1365</v>
+        <v>1416</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>UCF</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1185,61 +1185,61 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G11" t="n">
-        <v>1782.8</v>
+        <v>1831.1</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0374</v>
+        <v>6.3402</v>
       </c>
       <c r="I11" t="n">
-        <v>117.62</v>
+        <v>113.8</v>
       </c>
       <c r="J11" t="n">
-        <v>104.11</v>
+        <v>109.32</v>
       </c>
       <c r="K11" t="n">
-        <v>13.51</v>
+        <v>4.47</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3504</v>
+        <v>0.3133</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1498</v>
+        <v>0.1536</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8</v>
+        <v>-1.8</v>
       </c>
       <c r="O11" t="n">
+        <v>53</v>
+      </c>
+      <c r="P11" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>57</v>
+      </c>
+      <c r="R11" t="n">
+        <v>46</v>
+      </c>
+      <c r="S11" t="n">
         <v>37</v>
       </c>
-      <c r="P11" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>46</v>
-      </c>
-      <c r="R11" t="n">
-        <v>36</v>
-      </c>
-      <c r="S11" t="n">
-        <v>36</v>
-      </c>
       <c r="T11" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="U11" t="n">
-        <v>1596.2</v>
+        <v>1689.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1416</v>
+        <v>1275</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UCF</t>
+          <t>Miami OH</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1249,68 +1249,68 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>11a</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>123</v>
       </c>
       <c r="G12" t="n">
-        <v>1820.5</v>
+        <v>1775.2</v>
       </c>
       <c r="H12" t="n">
-        <v>7.025</v>
+        <v>9.651999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>114.77</v>
+        <v>120.89</v>
       </c>
       <c r="J12" t="n">
-        <v>110.49</v>
+        <v>105.23</v>
       </c>
       <c r="K12" t="n">
-        <v>4.28</v>
+        <v>15.66</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3115</v>
+        <v>0.2107</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1546</v>
+        <v>0.1402</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.6</v>
+        <v>6</v>
       </c>
       <c r="O12" t="n">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="P12" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="Q12" t="n">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="R12" t="n">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="S12" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="T12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="U12" t="n">
-        <v>1687.9</v>
+        <v>1414.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1231</v>
+        <v>1320</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Indiana</t>
+          <t>Northern Iowa</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1320,68 +1320,68 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>11b</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G13" t="n">
-        <v>1741.9</v>
+        <v>1573.9</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.3683</v>
+        <v>-3.696</v>
       </c>
       <c r="I13" t="n">
-        <v>116.27</v>
+        <v>108.74</v>
       </c>
       <c r="J13" t="n">
-        <v>107.64</v>
+        <v>97.5</v>
       </c>
       <c r="K13" t="n">
-        <v>8.619999999999999</v>
+        <v>11.25</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2347</v>
+        <v>0.225</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1428</v>
+        <v>0.1354</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.8</v>
+        <v>14.4</v>
       </c>
       <c r="O13" t="n">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="P13" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="Q13" t="n">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="R13" t="n">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="S13" t="n">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="T13" t="n">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="U13" t="n">
-        <v>1701.1</v>
+        <v>1515.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1219</v>
+        <v>1358</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>High Point</t>
+          <t>Sam Houston St</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1391,68 +1391,68 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E14" t="b">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G14" t="n">
-        <v>1625.5</v>
+        <v>1545</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.8564000000000001</v>
+        <v>4.4295</v>
       </c>
       <c r="I14" t="n">
-        <v>121.16</v>
+        <v>112.95</v>
       </c>
       <c r="J14" t="n">
-        <v>100.19</v>
+        <v>106.4</v>
       </c>
       <c r="K14" t="n">
-        <v>20.97</v>
+        <v>6.55</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3061</v>
+        <v>0.3122</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1276</v>
+        <v>0.1587</v>
       </c>
       <c r="N14" t="n">
-        <v>9.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="O14" t="n">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="P14" t="n">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="Q14" t="n">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="R14" t="n">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="S14" t="n">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="T14" t="n">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="U14" t="n">
-        <v>1382.5</v>
+        <v>1499.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1220</v>
+        <v>1407</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hofstra</t>
+          <t>Troy</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1462,68 +1462,68 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E15" t="b">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G15" t="n">
-        <v>1586.2</v>
+        <v>1601</v>
       </c>
       <c r="H15" t="n">
-        <v>3.3583</v>
+        <v>1.1284</v>
       </c>
       <c r="I15" t="n">
-        <v>113.56</v>
+        <v>112.28</v>
       </c>
       <c r="J15" t="n">
-        <v>102.69</v>
+        <v>106.19</v>
       </c>
       <c r="K15" t="n">
-        <v>10.87</v>
+        <v>6.08</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3081</v>
+        <v>0.316</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1527</v>
+        <v>0.1667</v>
       </c>
       <c r="N15" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="O15" t="n">
-        <v>84</v>
+        <v>153</v>
       </c>
       <c r="P15" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="Q15" t="n">
-        <v>84</v>
+        <v>137</v>
       </c>
       <c r="R15" t="n">
-        <v>88</v>
+        <v>137</v>
       </c>
       <c r="S15" t="n">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="T15" t="n">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="U15" t="n">
-        <v>1482.3</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1407</v>
+        <v>1474</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Troy</t>
+          <t>Queens NC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1533,68 +1533,68 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E16" t="b">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G16" t="n">
-        <v>1601</v>
+        <v>1427.4</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1284</v>
+        <v>1.0039</v>
       </c>
       <c r="I16" t="n">
-        <v>112.28</v>
+        <v>119.17</v>
       </c>
       <c r="J16" t="n">
-        <v>106.19</v>
+        <v>116.56</v>
       </c>
       <c r="K16" t="n">
-        <v>6.08</v>
+        <v>2.61</v>
       </c>
       <c r="L16" t="n">
-        <v>0.316</v>
+        <v>0.2859</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1667</v>
+        <v>0.1441</v>
       </c>
       <c r="N16" t="n">
-        <v>9.4</v>
+        <v>6.4</v>
       </c>
       <c r="O16" t="n">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="P16" t="n">
-        <v>130</v>
+        <v>192</v>
       </c>
       <c r="Q16" t="n">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="R16" t="n">
-        <v>137</v>
+        <v>177</v>
       </c>
       <c r="S16" t="n">
-        <v>124</v>
+        <v>171</v>
       </c>
       <c r="T16" t="n">
-        <v>132</v>
+        <v>187</v>
       </c>
       <c r="U16" t="n">
-        <v>1466</v>
+        <v>1430.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1420</v>
+        <v>1373</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>UMBC</t>
+          <t>Siena</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E17" t="b">
@@ -1614,200 +1614,200 @@
         <v>127</v>
       </c>
       <c r="G17" t="n">
-        <v>1393.7</v>
+        <v>1478</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2859</v>
+        <v>0.9489</v>
       </c>
       <c r="I17" t="n">
-        <v>113.44</v>
+        <v>109.73</v>
       </c>
       <c r="J17" t="n">
-        <v>102.32</v>
+        <v>101.77</v>
       </c>
       <c r="K17" t="n">
-        <v>11.13</v>
+        <v>7.95</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2168</v>
+        <v>0.2799</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1344</v>
+        <v>0.1508</v>
       </c>
       <c r="N17" t="n">
-        <v>22.4</v>
+        <v>6.2</v>
       </c>
       <c r="O17" t="n">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="P17" t="n">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="Q17" t="n">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="R17" t="n">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="S17" t="n">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="T17" t="n">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="U17" t="n">
-        <v>1364.8</v>
+        <v>1430.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1224</v>
+        <v>1196</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Howard</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>16a</t>
+          <t>01</t>
         </is>
       </c>
       <c r="E18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G18" t="n">
-        <v>1409</v>
+        <v>2014.8</v>
       </c>
       <c r="H18" t="n">
-        <v>3.2279</v>
+        <v>2.8716</v>
       </c>
       <c r="I18" t="n">
-        <v>109.08</v>
+        <v>120.95</v>
       </c>
       <c r="J18" t="n">
-        <v>98.81</v>
+        <v>99.02</v>
       </c>
       <c r="K18" t="n">
-        <v>10.27</v>
+        <v>21.92</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3126</v>
+        <v>0.3329</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1855</v>
+        <v>0.1552</v>
       </c>
       <c r="N18" t="n">
-        <v>23.6</v>
+        <v>21.4</v>
       </c>
       <c r="O18" t="n">
-        <v>202</v>
+        <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>250</v>
+        <v>4</v>
       </c>
       <c r="Q18" t="n">
-        <v>270</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>198</v>
+        <v>4</v>
       </c>
       <c r="S18" t="n">
-        <v>232</v>
+        <v>8</v>
       </c>
       <c r="T18" t="n">
-        <v>202</v>
+        <v>4</v>
       </c>
       <c r="U18" t="n">
-        <v>1380.6</v>
+        <v>1709.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1285</v>
+        <v>1222</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>16b</t>
+          <t>02</t>
         </is>
       </c>
       <c r="E19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G19" t="n">
-        <v>1469.4</v>
+        <v>2102.9</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.5005</v>
+        <v>1.6401</v>
       </c>
       <c r="I19" t="n">
-        <v>107.3</v>
+        <v>117.95</v>
       </c>
       <c r="J19" t="n">
-        <v>109.17</v>
+        <v>95.43000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.87</v>
+        <v>22.51</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1941</v>
+        <v>0.3379</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1861</v>
+        <v>0.1199</v>
       </c>
       <c r="N19" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19" t="n">
-        <v>187</v>
+        <v>6</v>
       </c>
       <c r="P19" t="n">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="Q19" t="n">
-        <v>263</v>
+        <v>7</v>
       </c>
       <c r="R19" t="n">
-        <v>227</v>
+        <v>5</v>
       </c>
       <c r="S19" t="n">
-        <v>199</v>
+        <v>6</v>
       </c>
       <c r="T19" t="n">
-        <v>199</v>
+        <v>7</v>
       </c>
       <c r="U19" t="n">
-        <v>1435.4</v>
+        <v>1706.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1196</v>
+        <v>1304</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Nebraska</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1817,68 +1817,68 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>03</t>
         </is>
       </c>
       <c r="E20" t="b">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G20" t="n">
-        <v>2014.8</v>
+        <v>1999.6</v>
       </c>
       <c r="H20" t="n">
-        <v>2.8716</v>
+        <v>10.6735</v>
       </c>
       <c r="I20" t="n">
-        <v>120.95</v>
+        <v>115.4</v>
       </c>
       <c r="J20" t="n">
-        <v>99.02</v>
+        <v>97.95</v>
       </c>
       <c r="K20" t="n">
-        <v>21.92</v>
+        <v>17.45</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3329</v>
+        <v>0.2379</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1552</v>
+        <v>0.1402</v>
       </c>
       <c r="N20" t="n">
-        <v>21.4</v>
+        <v>8</v>
       </c>
       <c r="O20" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P20" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="R20" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="U20" t="n">
-        <v>1709.6</v>
+        <v>1665.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1222</v>
+        <v>1345</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Purdue</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>04</t>
         </is>
       </c>
       <c r="E21" t="b">
@@ -1898,58 +1898,58 @@
         <v>124</v>
       </c>
       <c r="G21" t="n">
-        <v>2102.9</v>
+        <v>1955.6</v>
       </c>
       <c r="H21" t="n">
-        <v>1.6401</v>
+        <v>0.3963</v>
       </c>
       <c r="I21" t="n">
-        <v>117.95</v>
+        <v>124.64</v>
       </c>
       <c r="J21" t="n">
-        <v>95.43000000000001</v>
+        <v>107.6</v>
       </c>
       <c r="K21" t="n">
-        <v>22.51</v>
+        <v>17.04</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3379</v>
+        <v>0.3051</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1199</v>
+        <v>0.1348</v>
       </c>
       <c r="N21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O21" t="n">
         <v>8</v>
       </c>
-      <c r="O21" t="n">
-        <v>6</v>
-      </c>
       <c r="P21" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="Q21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T21" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U21" t="n">
-        <v>1706.6</v>
+        <v>1746.9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1304</v>
+        <v>1385</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nebraska</t>
+          <t>St John's</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1959,68 +1959,68 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>05</t>
         </is>
       </c>
       <c r="E22" t="b">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G22" t="n">
-        <v>1999.6</v>
+        <v>1961.4</v>
       </c>
       <c r="H22" t="n">
-        <v>10.6735</v>
+        <v>5.5897</v>
       </c>
       <c r="I22" t="n">
-        <v>115.4</v>
+        <v>113.79</v>
       </c>
       <c r="J22" t="n">
-        <v>97.95</v>
+        <v>98.7</v>
       </c>
       <c r="K22" t="n">
-        <v>17.45</v>
+        <v>15.09</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2379</v>
+        <v>0.3238</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1402</v>
+        <v>0.1418</v>
       </c>
       <c r="N22" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="O22" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="P22" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R22" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="U22" t="n">
-        <v>1665.7</v>
+        <v>1680.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1345</v>
+        <v>1140</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Purdue</t>
+          <t>BYU</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2030,68 +2030,68 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>06</t>
         </is>
       </c>
       <c r="E23" t="b">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G23" t="n">
-        <v>1955.6</v>
+        <v>1934.4</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3963</v>
+        <v>0.879</v>
       </c>
       <c r="I23" t="n">
-        <v>124.64</v>
+        <v>118.42</v>
       </c>
       <c r="J23" t="n">
-        <v>107.6</v>
+        <v>105.83</v>
       </c>
       <c r="K23" t="n">
-        <v>17.04</v>
+        <v>12.58</v>
       </c>
       <c r="L23" t="n">
-        <v>0.3051</v>
+        <v>0.3042</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1348</v>
+        <v>0.1509</v>
       </c>
       <c r="N23" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="O23" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="P23" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="Q23" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="R23" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="S23" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="T23" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="U23" t="n">
-        <v>1746.9</v>
+        <v>1718.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>St John's</t>
+          <t>St Mary's CA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2101,68 +2101,68 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>07</t>
         </is>
       </c>
       <c r="E24" t="b">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G24" t="n">
-        <v>1961.4</v>
+        <v>1857.8</v>
       </c>
       <c r="H24" t="n">
-        <v>5.5897</v>
+        <v>-0.2818</v>
       </c>
       <c r="I24" t="n">
-        <v>113.79</v>
+        <v>118.73</v>
       </c>
       <c r="J24" t="n">
-        <v>98.7</v>
+        <v>99.88</v>
       </c>
       <c r="K24" t="n">
-        <v>15.09</v>
+        <v>18.85</v>
       </c>
       <c r="L24" t="n">
-        <v>0.3238</v>
+        <v>0.2975</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1418</v>
+        <v>0.1525</v>
       </c>
       <c r="N24" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="O24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P24" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="Q24" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="R24" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="S24" t="n">
+        <v>19</v>
+      </c>
+      <c r="T24" t="n">
         <v>20</v>
       </c>
-      <c r="T24" t="n">
-        <v>22</v>
-      </c>
       <c r="U24" t="n">
-        <v>1680.5</v>
+        <v>1596.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1257</v>
+        <v>1395</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Louisville</t>
+          <t>TCU</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2172,68 +2172,68 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>08</t>
         </is>
       </c>
       <c r="E25" t="b">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G25" t="n">
-        <v>1845.2</v>
+        <v>1845.8</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.9919</v>
+        <v>6.897</v>
       </c>
       <c r="I25" t="n">
-        <v>120.19</v>
+        <v>111.93</v>
       </c>
       <c r="J25" t="n">
-        <v>101.95</v>
+        <v>102.48</v>
       </c>
       <c r="K25" t="n">
-        <v>18.24</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2897</v>
+        <v>0.3255</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1578</v>
+        <v>0.1494</v>
       </c>
       <c r="N25" t="n">
-        <v>5.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="P25" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="Q25" t="n">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="R25" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="S25" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="T25" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="U25" t="n">
-        <v>1682.1</v>
+        <v>1680.3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1388</v>
+        <v>1326</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>St Mary's CA</t>
+          <t>Ohio St</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2243,68 +2243,68 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>09</t>
         </is>
       </c>
       <c r="E26" t="b">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G26" t="n">
-        <v>1857.8</v>
+        <v>1799.9</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.2818</v>
+        <v>1.5472</v>
       </c>
       <c r="I26" t="n">
-        <v>118.73</v>
+        <v>118.74</v>
       </c>
       <c r="J26" t="n">
-        <v>99.88</v>
+        <v>107.91</v>
       </c>
       <c r="K26" t="n">
-        <v>18.85</v>
+        <v>10.83</v>
       </c>
       <c r="L26" t="n">
-        <v>0.2975</v>
+        <v>0.2524</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1525</v>
+        <v>0.1503</v>
       </c>
       <c r="N26" t="n">
-        <v>8.6</v>
+        <v>6</v>
       </c>
       <c r="O26" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="P26" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="Q26" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="R26" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S26" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="T26" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="U26" t="n">
-        <v>1596.9</v>
+        <v>1700.1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1274</v>
+        <v>1301</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Miami FL</t>
+          <t>NC State</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2314,68 +2314,68 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E27" t="b">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G27" t="n">
-        <v>1761</v>
+        <v>1740.7</v>
       </c>
       <c r="H27" t="n">
-        <v>12.4806</v>
+        <v>7.3141</v>
       </c>
       <c r="I27" t="n">
-        <v>118.15</v>
+        <v>120.03</v>
       </c>
       <c r="J27" t="n">
-        <v>101.88</v>
+        <v>109.14</v>
       </c>
       <c r="K27" t="n">
-        <v>16.27</v>
+        <v>10.89</v>
       </c>
       <c r="L27" t="n">
-        <v>0.3077</v>
+        <v>0.2784</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1596</v>
+        <v>0.1277</v>
       </c>
       <c r="N27" t="n">
-        <v>6.8</v>
+        <v>-11</v>
       </c>
       <c r="O27" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="P27" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>34</v>
+      </c>
+      <c r="R27" t="n">
         <v>38</v>
       </c>
-      <c r="Q27" t="n">
-        <v>27</v>
-      </c>
-      <c r="R27" t="n">
-        <v>31</v>
-      </c>
       <c r="S27" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="T27" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="U27" t="n">
-        <v>1617.1</v>
+        <v>1669.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1395</v>
+        <v>1374</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TCU</t>
+          <t>SMU</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2385,68 +2385,68 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>11a</t>
         </is>
       </c>
       <c r="E28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G28" t="n">
-        <v>1836.3</v>
+        <v>1733.9</v>
       </c>
       <c r="H28" t="n">
-        <v>6.8916</v>
+        <v>0.2411</v>
       </c>
       <c r="I28" t="n">
-        <v>110.72</v>
+        <v>117.96</v>
       </c>
       <c r="J28" t="n">
-        <v>101.25</v>
+        <v>109.76</v>
       </c>
       <c r="K28" t="n">
-        <v>9.460000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>0.3192</v>
+        <v>0.3098</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1507</v>
+        <v>0.1542</v>
       </c>
       <c r="N28" t="n">
-        <v>9</v>
+        <v>-5.6</v>
       </c>
       <c r="O28" t="n">
+        <v>43</v>
+      </c>
+      <c r="P28" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>39</v>
+      </c>
+      <c r="R28" t="n">
+        <v>39</v>
+      </c>
+      <c r="S28" t="n">
         <v>44</v>
       </c>
-      <c r="P28" t="n">
-        <v>35</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>43</v>
-      </c>
-      <c r="R28" t="n">
-        <v>44</v>
-      </c>
-      <c r="S28" t="n">
-        <v>35</v>
-      </c>
       <c r="T28" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="U28" t="n">
-        <v>1679.3</v>
+        <v>1649.8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1400</v>
+        <v>1120</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Auburn</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2456,68 +2456,68 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11b</t>
         </is>
       </c>
       <c r="E29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G29" t="n">
-        <v>1757.7</v>
+        <v>1837.5</v>
       </c>
       <c r="H29" t="n">
-        <v>2.865</v>
+        <v>-7.6154</v>
       </c>
       <c r="I29" t="n">
-        <v>120.37</v>
+        <v>118.87</v>
       </c>
       <c r="J29" t="n">
-        <v>111.34</v>
+        <v>113.5</v>
       </c>
       <c r="K29" t="n">
-        <v>9.02</v>
+        <v>5.37</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3098</v>
+        <v>0.3462</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1494</v>
+        <v>0.1435</v>
       </c>
       <c r="N29" t="n">
-        <v>-8.199999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="O29" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="P29" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="Q29" t="n">
+        <v>44</v>
+      </c>
+      <c r="R29" t="n">
+        <v>40</v>
+      </c>
+      <c r="S29" t="n">
+        <v>50</v>
+      </c>
+      <c r="T29" t="n">
         <v>38</v>
       </c>
-      <c r="R29" t="n">
-        <v>42</v>
-      </c>
-      <c r="S29" t="n">
-        <v>46</v>
-      </c>
-      <c r="T29" t="n">
-        <v>41</v>
-      </c>
       <c r="U29" t="n">
-        <v>1699.4</v>
+        <v>1750.3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1281</v>
+        <v>1378</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>South Florida</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2527,68 +2527,68 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E30" t="b">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G30" t="n">
-        <v>1757.5</v>
+        <v>1711.8</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.923</v>
+        <v>9.207800000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>115.19</v>
+        <v>116.06</v>
       </c>
       <c r="J30" t="n">
-        <v>109.25</v>
+        <v>101.73</v>
       </c>
       <c r="K30" t="n">
-        <v>5.95</v>
+        <v>14.32</v>
       </c>
       <c r="L30" t="n">
-        <v>0.3014</v>
+        <v>0.3392</v>
       </c>
       <c r="M30" t="n">
-        <v>0.1701</v>
+        <v>0.1453</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>19.6</v>
       </c>
       <c r="O30" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P30" t="n">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="Q30" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R30" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="S30" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="T30" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="U30" t="n">
-        <v>1651.9</v>
+        <v>1553.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1378</v>
+        <v>1220</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>South Florida</t>
+          <t>Hofstra</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2598,68 +2598,68 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E31" t="b">
         <v>0</v>
       </c>
       <c r="F31" t="n">
+        <v>127</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1586.2</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3.3583</v>
+      </c>
+      <c r="I31" t="n">
+        <v>113.56</v>
+      </c>
+      <c r="J31" t="n">
+        <v>102.69</v>
+      </c>
+      <c r="K31" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.1527</v>
+      </c>
+      <c r="N31" t="n">
+        <v>12</v>
+      </c>
+      <c r="O31" t="n">
+        <v>84</v>
+      </c>
+      <c r="P31" t="n">
         <v>125</v>
       </c>
-      <c r="G31" t="n">
-        <v>1711.8</v>
-      </c>
-      <c r="H31" t="n">
-        <v>9.207800000000001</v>
-      </c>
-      <c r="I31" t="n">
-        <v>116.06</v>
-      </c>
-      <c r="J31" t="n">
-        <v>101.73</v>
-      </c>
-      <c r="K31" t="n">
-        <v>14.32</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0.3392</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0.1453</v>
-      </c>
-      <c r="N31" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="O31" t="n">
-        <v>51</v>
-      </c>
-      <c r="P31" t="n">
-        <v>64</v>
-      </c>
       <c r="Q31" t="n">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="R31" t="n">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="S31" t="n">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="T31" t="n">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="U31" t="n">
-        <v>1553.3</v>
+        <v>1482.3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1251</v>
+        <v>1460</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Liberty</t>
+          <t>Wright St</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2669,68 +2669,68 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E32" t="b">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G32" t="n">
-        <v>1733.1</v>
+        <v>1470.5</v>
       </c>
       <c r="H32" t="n">
-        <v>3.2041</v>
+        <v>2.7419</v>
       </c>
       <c r="I32" t="n">
-        <v>117.83</v>
+        <v>115.44</v>
       </c>
       <c r="J32" t="n">
-        <v>110.75</v>
+        <v>108.91</v>
       </c>
       <c r="K32" t="n">
-        <v>7.08</v>
+        <v>6.53</v>
       </c>
       <c r="L32" t="n">
-        <v>0.1699</v>
+        <v>0.2971</v>
       </c>
       <c r="M32" t="n">
-        <v>0.1316</v>
+        <v>0.1569</v>
       </c>
       <c r="N32" t="n">
-        <v>-5</v>
+        <v>10</v>
       </c>
       <c r="O32" t="n">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="P32" t="n">
-        <v>94</v>
+        <v>145</v>
       </c>
       <c r="Q32" t="n">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="R32" t="n">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="S32" t="n">
-        <v>72</v>
+        <v>138</v>
       </c>
       <c r="T32" t="n">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="U32" t="n">
-        <v>1485.6</v>
+        <v>1431.7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1460</v>
+        <v>1202</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Wright St</t>
+          <t>Furman</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2740,68 +2740,68 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E33" t="b">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G33" t="n">
-        <v>1470.5</v>
+        <v>1542.9</v>
       </c>
       <c r="H33" t="n">
-        <v>2.7419</v>
+        <v>0.8197</v>
       </c>
       <c r="I33" t="n">
-        <v>115.44</v>
+        <v>112.01</v>
       </c>
       <c r="J33" t="n">
-        <v>108.91</v>
+        <v>107.28</v>
       </c>
       <c r="K33" t="n">
-        <v>6.53</v>
+        <v>4.73</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2971</v>
+        <v>0.2562</v>
       </c>
       <c r="M33" t="n">
-        <v>0.1569</v>
+        <v>0.171</v>
       </c>
       <c r="N33" t="n">
-        <v>10</v>
+        <v>5.6</v>
       </c>
       <c r="O33" t="n">
-        <v>144</v>
+        <v>199</v>
       </c>
       <c r="P33" t="n">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="Q33" t="n">
-        <v>125</v>
+        <v>193</v>
       </c>
       <c r="R33" t="n">
-        <v>136</v>
+        <v>189</v>
       </c>
       <c r="S33" t="n">
-        <v>138</v>
+        <v>192</v>
       </c>
       <c r="T33" t="n">
-        <v>133</v>
+        <v>194</v>
       </c>
       <c r="U33" t="n">
-        <v>1431.7</v>
+        <v>1422.2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1202</v>
+        <v>1380</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Furman</t>
+          <t>Southern Univ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2811,68 +2811,68 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16a</t>
         </is>
       </c>
       <c r="E34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G34" t="n">
-        <v>1542.9</v>
+        <v>1374.1</v>
       </c>
       <c r="H34" t="n">
-        <v>0.8197</v>
+        <v>-2.5631</v>
       </c>
       <c r="I34" t="n">
-        <v>112.01</v>
+        <v>105.51</v>
       </c>
       <c r="J34" t="n">
-        <v>107.28</v>
+        <v>111.44</v>
       </c>
       <c r="K34" t="n">
-        <v>4.73</v>
+        <v>-5.93</v>
       </c>
       <c r="L34" t="n">
-        <v>0.2562</v>
+        <v>0.3235</v>
       </c>
       <c r="M34" t="n">
-        <v>0.171</v>
+        <v>0.1584</v>
       </c>
       <c r="N34" t="n">
-        <v>5.6</v>
+        <v>2</v>
       </c>
       <c r="O34" t="n">
-        <v>199</v>
+        <v>275</v>
       </c>
       <c r="P34" t="n">
-        <v>170</v>
+        <v>280</v>
       </c>
       <c r="Q34" t="n">
-        <v>193</v>
+        <v>256</v>
       </c>
       <c r="R34" t="n">
-        <v>189</v>
+        <v>259</v>
       </c>
       <c r="S34" t="n">
-        <v>192</v>
+        <v>272</v>
       </c>
       <c r="T34" t="n">
-        <v>194</v>
+        <v>277</v>
       </c>
       <c r="U34" t="n">
-        <v>1422.2</v>
+        <v>1401.7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1126</v>
+        <v>1250</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bethune-Cookman</t>
+          <t>Lehigh</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2882,139 +2882,139 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>16a</t>
+          <t>16b</t>
         </is>
       </c>
       <c r="E35" t="b">
         <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="G35" t="n">
-        <v>1375.4</v>
+        <v>1325.5</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9205</v>
+        <v>-0.465</v>
       </c>
       <c r="I35" t="n">
-        <v>104.96</v>
+        <v>105.58</v>
       </c>
       <c r="J35" t="n">
-        <v>108.7</v>
+        <v>108.39</v>
       </c>
       <c r="K35" t="n">
-        <v>-3.74</v>
+        <v>-2.8</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2778</v>
+        <v>0.2229</v>
       </c>
       <c r="M35" t="n">
-        <v>0.1862</v>
+        <v>0.1707</v>
       </c>
       <c r="N35" t="n">
-        <v>4.8</v>
+        <v>7.8</v>
       </c>
       <c r="O35" t="n">
-        <v>238</v>
+        <v>290</v>
       </c>
       <c r="P35" t="n">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="Q35" t="n">
+        <v>279</v>
+      </c>
+      <c r="R35" t="n">
+        <v>282</v>
+      </c>
+      <c r="S35" t="n">
         <v>268</v>
       </c>
-      <c r="R35" t="n">
-        <v>214</v>
-      </c>
-      <c r="S35" t="n">
-        <v>216</v>
-      </c>
       <c r="T35" t="n">
-        <v>255</v>
+        <v>282</v>
       </c>
       <c r="U35" t="n">
-        <v>1436.6</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1250</v>
+        <v>1276</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lehigh</t>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>MW</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>16b</t>
+          <t>01</t>
         </is>
       </c>
       <c r="E36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>125</v>
       </c>
       <c r="G36" t="n">
-        <v>1323.1</v>
+        <v>2189.2</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.5849</v>
+        <v>7.2681</v>
       </c>
       <c r="I36" t="n">
-        <v>104.76</v>
+        <v>121.97</v>
       </c>
       <c r="J36" t="n">
-        <v>108.58</v>
+        <v>95.94</v>
       </c>
       <c r="K36" t="n">
-        <v>-3.82</v>
+        <v>26.03</v>
       </c>
       <c r="L36" t="n">
-        <v>0.214</v>
+        <v>0.2632</v>
       </c>
       <c r="M36" t="n">
-        <v>0.1729</v>
+        <v>0.1657</v>
       </c>
       <c r="N36" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="O36" t="n">
-        <v>290</v>
+        <v>2</v>
       </c>
       <c r="P36" t="n">
-        <v>295</v>
+        <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>279</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>282</v>
+        <v>1</v>
       </c>
       <c r="S36" t="n">
-        <v>268</v>
+        <v>3</v>
       </c>
       <c r="T36" t="n">
-        <v>282</v>
+        <v>2</v>
       </c>
       <c r="U36" t="n">
-        <v>1401.7</v>
+        <v>1769.7</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1276</v>
+        <v>1163</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Connecticut</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3024,68 +3024,68 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="E37" t="b">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G37" t="n">
-        <v>2189.2</v>
+        <v>2064.2</v>
       </c>
       <c r="H37" t="n">
-        <v>7.2681</v>
+        <v>8.950200000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>121.97</v>
+        <v>116.34</v>
       </c>
       <c r="J37" t="n">
-        <v>95.94</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>26.03</v>
+        <v>18.93</v>
       </c>
       <c r="L37" t="n">
-        <v>0.2632</v>
+        <v>0.2937</v>
       </c>
       <c r="M37" t="n">
-        <v>0.1657</v>
+        <v>0.1558</v>
       </c>
       <c r="N37" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O37" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="P37" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="R37" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T37" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U37" t="n">
-        <v>1769.7</v>
+        <v>1660.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1163</v>
+        <v>1235</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Connecticut</t>
+          <t>Iowa St</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3095,68 +3095,68 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="E38" t="b">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G38" t="n">
-        <v>2064.2</v>
+        <v>2031.1</v>
       </c>
       <c r="H38" t="n">
-        <v>8.950200000000001</v>
+        <v>2.7523</v>
       </c>
       <c r="I38" t="n">
-        <v>116.34</v>
+        <v>118.89</v>
       </c>
       <c r="J38" t="n">
-        <v>97.40000000000001</v>
+        <v>94.63</v>
       </c>
       <c r="K38" t="n">
-        <v>18.93</v>
+        <v>24.26</v>
       </c>
       <c r="L38" t="n">
-        <v>0.2937</v>
+        <v>0.3199</v>
       </c>
       <c r="M38" t="n">
-        <v>0.1558</v>
+        <v>0.1454</v>
       </c>
       <c r="N38" t="n">
-        <v>6.6</v>
+        <v>12.2</v>
       </c>
       <c r="O38" t="n">
+        <v>7</v>
+      </c>
+      <c r="P38" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>6</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6</v>
+      </c>
+      <c r="S38" t="n">
         <v>11</v>
       </c>
-      <c r="P38" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>21</v>
-      </c>
-      <c r="R38" t="n">
-        <v>10</v>
-      </c>
-      <c r="S38" t="n">
-        <v>4</v>
-      </c>
       <c r="T38" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U38" t="n">
-        <v>1660.9</v>
+        <v>1687.1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1235</v>
+        <v>1403</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Iowa St</t>
+          <t>Texas Tech</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="E39" t="b">
@@ -3176,58 +3176,58 @@
         <v>124</v>
       </c>
       <c r="G39" t="n">
-        <v>2027.4</v>
+        <v>2025.5</v>
       </c>
       <c r="H39" t="n">
-        <v>3.1622</v>
+        <v>10.1327</v>
       </c>
       <c r="I39" t="n">
-        <v>118.43</v>
+        <v>118.86</v>
       </c>
       <c r="J39" t="n">
-        <v>96.01000000000001</v>
+        <v>106.69</v>
       </c>
       <c r="K39" t="n">
-        <v>22.42</v>
+        <v>12.16</v>
       </c>
       <c r="L39" t="n">
-        <v>0.3184</v>
+        <v>0.2944</v>
       </c>
       <c r="M39" t="n">
-        <v>0.1465</v>
+        <v>0.155</v>
       </c>
       <c r="N39" t="n">
-        <v>0.4</v>
+        <v>7</v>
       </c>
       <c r="O39" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="P39" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="Q39" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="R39" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="S39" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="T39" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="U39" t="n">
-        <v>1686.9</v>
+        <v>1762.7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1403</v>
+        <v>1435</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Texas Tech</t>
+          <t>Vanderbilt</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>05</t>
         </is>
       </c>
       <c r="E40" t="b">
@@ -3247,58 +3247,58 @@
         <v>124</v>
       </c>
       <c r="G40" t="n">
-        <v>2025.5</v>
+        <v>1935.7</v>
       </c>
       <c r="H40" t="n">
-        <v>10.1327</v>
+        <v>2.1989</v>
       </c>
       <c r="I40" t="n">
-        <v>118.86</v>
+        <v>121.8</v>
       </c>
       <c r="J40" t="n">
-        <v>106.69</v>
+        <v>105.67</v>
       </c>
       <c r="K40" t="n">
-        <v>12.16</v>
+        <v>16.12</v>
       </c>
       <c r="L40" t="n">
-        <v>0.2944</v>
+        <v>0.2802</v>
       </c>
       <c r="M40" t="n">
-        <v>0.155</v>
+        <v>0.1278</v>
       </c>
       <c r="N40" t="n">
-        <v>7</v>
+        <v>-0.6</v>
       </c>
       <c r="O40" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="P40" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>13</v>
+      </c>
+      <c r="R40" t="n">
+        <v>14</v>
+      </c>
+      <c r="S40" t="n">
+        <v>22</v>
+      </c>
+      <c r="T40" t="n">
         <v>16</v>
       </c>
-      <c r="Q40" t="n">
-        <v>19</v>
-      </c>
-      <c r="R40" t="n">
-        <v>15</v>
-      </c>
-      <c r="S40" t="n">
-        <v>17</v>
-      </c>
-      <c r="T40" t="n">
-        <v>15</v>
-      </c>
       <c r="U40" t="n">
-        <v>1762.7</v>
+        <v>1694.9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1397</v>
+        <v>1257</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>Louisville</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3308,68 +3308,68 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>06</t>
         </is>
       </c>
       <c r="E41" t="b">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G41" t="n">
-        <v>1898.6</v>
+        <v>1855.9</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.6704</v>
+        <v>-2.8167</v>
       </c>
       <c r="I41" t="n">
-        <v>117.06</v>
+        <v>119.15</v>
       </c>
       <c r="J41" t="n">
-        <v>101.96</v>
+        <v>101.26</v>
       </c>
       <c r="K41" t="n">
-        <v>15.09</v>
+        <v>17.89</v>
       </c>
       <c r="L41" t="n">
-        <v>0.3583</v>
+        <v>0.2908</v>
       </c>
       <c r="M41" t="n">
-        <v>0.1671</v>
+        <v>0.1584</v>
       </c>
       <c r="N41" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="O41" t="n">
+        <v>16</v>
+      </c>
+      <c r="P41" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>9</v>
+      </c>
+      <c r="R41" t="n">
+        <v>21</v>
+      </c>
+      <c r="S41" t="n">
+        <v>27</v>
+      </c>
+      <c r="T41" t="n">
         <v>14</v>
       </c>
-      <c r="P41" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>18</v>
-      </c>
-      <c r="R41" t="n">
-        <v>20</v>
-      </c>
-      <c r="S41" t="n">
-        <v>24</v>
-      </c>
-      <c r="T41" t="n">
-        <v>21</v>
-      </c>
       <c r="U41" t="n">
-        <v>1706.1</v>
+        <v>1683.7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1458</v>
+        <v>1208</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>07</t>
         </is>
       </c>
       <c r="E42" t="b">
@@ -3389,58 +3389,58 @@
         <v>124</v>
       </c>
       <c r="G42" t="n">
-        <v>1859.5</v>
+        <v>1816.9</v>
       </c>
       <c r="H42" t="n">
-        <v>1.6302</v>
+        <v>0.2065</v>
       </c>
       <c r="I42" t="n">
-        <v>119.64</v>
+        <v>121.14</v>
       </c>
       <c r="J42" t="n">
-        <v>108.42</v>
+        <v>107.06</v>
       </c>
       <c r="K42" t="n">
-        <v>11.21</v>
+        <v>14.09</v>
       </c>
       <c r="L42" t="n">
-        <v>0.276</v>
+        <v>0.3227</v>
       </c>
       <c r="M42" t="n">
-        <v>0.1244</v>
+        <v>0.1388</v>
       </c>
       <c r="N42" t="n">
-        <v>10.6</v>
+        <v>7.6</v>
       </c>
       <c r="O42" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="P42" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="Q42" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="R42" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="S42" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="T42" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="U42" t="n">
-        <v>1701.3</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1208</v>
+        <v>1429</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Utah St</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>08</t>
         </is>
       </c>
       <c r="E43" t="b">
@@ -3460,58 +3460,58 @@
         <v>124</v>
       </c>
       <c r="G43" t="n">
-        <v>1816.9</v>
+        <v>1869.8</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2065</v>
+        <v>0.2419</v>
       </c>
       <c r="I43" t="n">
-        <v>121.14</v>
+        <v>120.49</v>
       </c>
       <c r="J43" t="n">
-        <v>107.06</v>
+        <v>105.01</v>
       </c>
       <c r="K43" t="n">
-        <v>14.09</v>
+        <v>15.48</v>
       </c>
       <c r="L43" t="n">
-        <v>0.3227</v>
+        <v>0.3065</v>
       </c>
       <c r="M43" t="n">
-        <v>0.1388</v>
+        <v>0.1487</v>
       </c>
       <c r="N43" t="n">
-        <v>7.6</v>
+        <v>-7.6</v>
       </c>
       <c r="O43" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="P43" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="Q43" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="R43" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="S43" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="T43" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="U43" t="n">
-        <v>1643</v>
+        <v>1599.2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1326</v>
+        <v>1155</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ohio St</t>
+          <t>Clemson</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3521,68 +3521,68 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>09</t>
         </is>
       </c>
       <c r="E44" t="b">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G44" t="n">
-        <v>1799.9</v>
+        <v>1845.5</v>
       </c>
       <c r="H44" t="n">
-        <v>1.5472</v>
+        <v>3.0058</v>
       </c>
       <c r="I44" t="n">
-        <v>118.74</v>
+        <v>113.18</v>
       </c>
       <c r="J44" t="n">
-        <v>107.91</v>
+        <v>100.7</v>
       </c>
       <c r="K44" t="n">
-        <v>10.83</v>
+        <v>12.47</v>
       </c>
       <c r="L44" t="n">
-        <v>0.2524</v>
+        <v>0.2545</v>
       </c>
       <c r="M44" t="n">
-        <v>0.1503</v>
+        <v>0.1366</v>
       </c>
       <c r="N44" t="n">
-        <v>6</v>
+        <v>1.6</v>
       </c>
       <c r="O44" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="P44" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q44" t="n">
         <v>32</v>
       </c>
-      <c r="Q44" t="n">
-        <v>29</v>
-      </c>
       <c r="R44" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="S44" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="T44" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="U44" t="n">
-        <v>1700.1</v>
+        <v>1644.4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1155</v>
+        <v>1365</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Clemson</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3592,68 +3592,68 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E45" t="b">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G45" t="n">
-        <v>1838.2</v>
+        <v>1782.8</v>
       </c>
       <c r="H45" t="n">
-        <v>3.3876</v>
+        <v>0.0374</v>
       </c>
       <c r="I45" t="n">
-        <v>112.83</v>
+        <v>117.62</v>
       </c>
       <c r="J45" t="n">
-        <v>100.58</v>
+        <v>104.11</v>
       </c>
       <c r="K45" t="n">
-        <v>12.25</v>
+        <v>13.51</v>
       </c>
       <c r="L45" t="n">
-        <v>0.2488</v>
+        <v>0.3504</v>
       </c>
       <c r="M45" t="n">
-        <v>0.1395</v>
+        <v>0.1498</v>
       </c>
       <c r="N45" t="n">
-        <v>-1.8</v>
+        <v>0.8</v>
       </c>
       <c r="O45" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P45" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q45" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="R45" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S45" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T45" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="U45" t="n">
-        <v>1641.6</v>
+        <v>1596.2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1301</v>
+        <v>1281</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NC State</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3663,68 +3663,68 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11a</t>
         </is>
       </c>
       <c r="E46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
         <v>124</v>
       </c>
       <c r="G46" t="n">
-        <v>1735.9</v>
+        <v>1757.5</v>
       </c>
       <c r="H46" t="n">
-        <v>7.7247</v>
+        <v>-1.923</v>
       </c>
       <c r="I46" t="n">
-        <v>118.75</v>
+        <v>115.19</v>
       </c>
       <c r="J46" t="n">
-        <v>108.16</v>
+        <v>109.25</v>
       </c>
       <c r="K46" t="n">
-        <v>10.59</v>
+        <v>5.95</v>
       </c>
       <c r="L46" t="n">
-        <v>0.2829</v>
+        <v>0.3014</v>
       </c>
       <c r="M46" t="n">
-        <v>0.1296</v>
+        <v>0.1701</v>
       </c>
       <c r="N46" t="n">
-        <v>-8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="P46" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="Q46" t="n">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="R46" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="S46" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T46" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="U46" t="n">
-        <v>1675.6</v>
+        <v>1651.9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1374</v>
+        <v>1433</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SMU</t>
+          <t>VCU</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3734,68 +3734,68 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>11a</t>
+          <t>11b</t>
         </is>
       </c>
       <c r="E47" t="b">
         <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G47" t="n">
-        <v>1744.5</v>
+        <v>1739.9</v>
       </c>
       <c r="H47" t="n">
-        <v>0.5256999999999999</v>
+        <v>2.9764</v>
       </c>
       <c r="I47" t="n">
-        <v>119.02</v>
+        <v>118.46</v>
       </c>
       <c r="J47" t="n">
-        <v>110.02</v>
+        <v>103.76</v>
       </c>
       <c r="K47" t="n">
-        <v>9</v>
+        <v>14.7</v>
       </c>
       <c r="L47" t="n">
-        <v>0.3105</v>
+        <v>0.2979</v>
       </c>
       <c r="M47" t="n">
-        <v>0.1505</v>
+        <v>0.1497</v>
       </c>
       <c r="N47" t="n">
-        <v>-5.6</v>
+        <v>6.2</v>
       </c>
       <c r="O47" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P47" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="Q47" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="R47" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="S47" t="n">
+        <v>40</v>
+      </c>
+      <c r="T47" t="n">
         <v>44</v>
       </c>
-      <c r="T47" t="n">
-        <v>39</v>
-      </c>
       <c r="U47" t="n">
-        <v>1641</v>
+        <v>1554.6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1433</v>
+        <v>1219</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>VCU</t>
+          <t>High Point</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3805,68 +3805,68 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>11b</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G48" t="n">
-        <v>1739.9</v>
+        <v>1625.5</v>
       </c>
       <c r="H48" t="n">
-        <v>2.9764</v>
+        <v>-0.8564000000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>118.46</v>
+        <v>121.16</v>
       </c>
       <c r="J48" t="n">
-        <v>103.76</v>
+        <v>100.19</v>
       </c>
       <c r="K48" t="n">
-        <v>14.7</v>
+        <v>20.97</v>
       </c>
       <c r="L48" t="n">
-        <v>0.2979</v>
+        <v>0.3061</v>
       </c>
       <c r="M48" t="n">
-        <v>0.1497</v>
+        <v>0.1276</v>
       </c>
       <c r="N48" t="n">
-        <v>6.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O48" t="n">
-        <v>45</v>
+        <v>93</v>
       </c>
       <c r="P48" t="n">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="Q48" t="n">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="R48" t="n">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="S48" t="n">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="T48" t="n">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="U48" t="n">
-        <v>1554.6</v>
+        <v>1382.5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1320</v>
+        <v>1430</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Northern Iowa</t>
+          <t>Utah Valley</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3876,68 +3876,68 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E49" t="b">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G49" t="n">
-        <v>1573.9</v>
+        <v>1637</v>
       </c>
       <c r="H49" t="n">
-        <v>-3.696</v>
+        <v>3.1528</v>
       </c>
       <c r="I49" t="n">
-        <v>108.74</v>
+        <v>111.58</v>
       </c>
       <c r="J49" t="n">
-        <v>97.5</v>
+        <v>100.45</v>
       </c>
       <c r="K49" t="n">
-        <v>11.25</v>
+        <v>11.12</v>
       </c>
       <c r="L49" t="n">
-        <v>0.225</v>
+        <v>0.3056</v>
       </c>
       <c r="M49" t="n">
-        <v>0.1354</v>
+        <v>0.1962</v>
       </c>
       <c r="N49" t="n">
-        <v>14.4</v>
+        <v>6.6</v>
       </c>
       <c r="O49" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="P49" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q49" t="n">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="R49" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="S49" t="n">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="T49" t="n">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="U49" t="n">
-        <v>1515.8</v>
+        <v>1455.5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1430</v>
+        <v>1295</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Utah Valley</t>
+          <t>N Dakota St</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3947,68 +3947,68 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E50" t="b">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G50" t="n">
-        <v>1637</v>
+        <v>1593.8</v>
       </c>
       <c r="H50" t="n">
-        <v>3.1528</v>
+        <v>3.5257</v>
       </c>
       <c r="I50" t="n">
-        <v>111.58</v>
+        <v>114.28</v>
       </c>
       <c r="J50" t="n">
-        <v>100.45</v>
+        <v>102.18</v>
       </c>
       <c r="K50" t="n">
-        <v>11.12</v>
+        <v>12.1</v>
       </c>
       <c r="L50" t="n">
-        <v>0.3056</v>
+        <v>0.3104</v>
       </c>
       <c r="M50" t="n">
-        <v>0.1962</v>
+        <v>0.1506</v>
       </c>
       <c r="N50" t="n">
-        <v>6.6</v>
+        <v>10.8</v>
       </c>
       <c r="O50" t="n">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="P50" t="n">
+        <v>116</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>163</v>
+      </c>
+      <c r="R50" t="n">
+        <v>115</v>
+      </c>
+      <c r="S50" t="n">
         <v>98</v>
       </c>
-      <c r="Q50" t="n">
-        <v>93</v>
-      </c>
-      <c r="R50" t="n">
-        <v>82</v>
-      </c>
-      <c r="S50" t="n">
-        <v>77</v>
-      </c>
       <c r="T50" t="n">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="U50" t="n">
-        <v>1455.5</v>
+        <v>1410.6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1295</v>
+        <v>1420</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>N Dakota St</t>
+          <t>UMBC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4018,68 +4018,68 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E51" t="b">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G51" t="n">
-        <v>1593.8</v>
+        <v>1393.7</v>
       </c>
       <c r="H51" t="n">
-        <v>3.5257</v>
+        <v>1.2859</v>
       </c>
       <c r="I51" t="n">
-        <v>114.28</v>
+        <v>113.44</v>
       </c>
       <c r="J51" t="n">
-        <v>102.18</v>
+        <v>102.32</v>
       </c>
       <c r="K51" t="n">
-        <v>12.1</v>
+        <v>11.13</v>
       </c>
       <c r="L51" t="n">
-        <v>0.3104</v>
+        <v>0.2168</v>
       </c>
       <c r="M51" t="n">
-        <v>0.1506</v>
+        <v>0.1344</v>
       </c>
       <c r="N51" t="n">
-        <v>10.8</v>
+        <v>22.4</v>
       </c>
       <c r="O51" t="n">
-        <v>114</v>
+        <v>198</v>
       </c>
       <c r="P51" t="n">
-        <v>116</v>
+        <v>225</v>
       </c>
       <c r="Q51" t="n">
-        <v>163</v>
+        <v>191</v>
       </c>
       <c r="R51" t="n">
-        <v>115</v>
+        <v>194</v>
       </c>
       <c r="S51" t="n">
-        <v>98</v>
+        <v>197</v>
       </c>
       <c r="T51" t="n">
-        <v>115</v>
+        <v>205</v>
       </c>
       <c r="U51" t="n">
-        <v>1410.6</v>
+        <v>1364.8</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1474</v>
+        <v>1224</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Queens NC</t>
+          <t>Howard</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4089,68 +4089,68 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16a</t>
         </is>
       </c>
       <c r="E52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G52" t="n">
-        <v>1427.4</v>
+        <v>1409</v>
       </c>
       <c r="H52" t="n">
-        <v>1.0039</v>
+        <v>3.2279</v>
       </c>
       <c r="I52" t="n">
-        <v>119.17</v>
+        <v>109.08</v>
       </c>
       <c r="J52" t="n">
-        <v>116.56</v>
+        <v>98.81</v>
       </c>
       <c r="K52" t="n">
-        <v>2.61</v>
+        <v>10.27</v>
       </c>
       <c r="L52" t="n">
-        <v>0.2859</v>
+        <v>0.3126</v>
       </c>
       <c r="M52" t="n">
-        <v>0.1441</v>
+        <v>0.1855</v>
       </c>
       <c r="N52" t="n">
-        <v>6.4</v>
+        <v>23.6</v>
       </c>
       <c r="O52" t="n">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="P52" t="n">
-        <v>192</v>
+        <v>250</v>
       </c>
       <c r="Q52" t="n">
-        <v>181</v>
+        <v>270</v>
       </c>
       <c r="R52" t="n">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="S52" t="n">
-        <v>171</v>
+        <v>232</v>
       </c>
       <c r="T52" t="n">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="U52" t="n">
-        <v>1430.9</v>
+        <v>1380.6</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1254</v>
+        <v>1225</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LIU Brooklyn</t>
+          <t>Idaho</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4160,59 +4160,59 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>16b</t>
         </is>
       </c>
       <c r="E53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G53" t="n">
-        <v>1418.2</v>
+        <v>1410</v>
       </c>
       <c r="H53" t="n">
-        <v>2.3581</v>
+        <v>-0.3498</v>
       </c>
       <c r="I53" t="n">
-        <v>109.38</v>
+        <v>110.28</v>
       </c>
       <c r="J53" t="n">
-        <v>104.38</v>
+        <v>106.53</v>
       </c>
       <c r="K53" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="L53" t="n">
-        <v>0.3119</v>
+        <v>0.2693</v>
       </c>
       <c r="M53" t="n">
-        <v>0.183</v>
+        <v>0.1475</v>
       </c>
       <c r="N53" t="n">
-        <v>10.4</v>
+        <v>11</v>
       </c>
       <c r="O53" t="n">
-        <v>217</v>
+        <v>165</v>
       </c>
       <c r="P53" t="n">
-        <v>228</v>
+        <v>184</v>
       </c>
       <c r="Q53" t="n">
-        <v>213</v>
+        <v>179</v>
       </c>
       <c r="R53" t="n">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="S53" t="n">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="T53" t="n">
-        <v>200</v>
+        <v>161</v>
       </c>
       <c r="U53" t="n">
-        <v>1378.8</v>
+        <v>1415.2</v>
       </c>
     </row>
     <row r="54">
@@ -4572,11 +4572,11 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1140</v>
+        <v>1458</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BYU</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4593,52 +4593,52 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G59" t="n">
-        <v>1927.8</v>
+        <v>1859.5</v>
       </c>
       <c r="H59" t="n">
-        <v>1.2144</v>
+        <v>1.6302</v>
       </c>
       <c r="I59" t="n">
-        <v>118.9</v>
+        <v>119.64</v>
       </c>
       <c r="J59" t="n">
-        <v>107.06</v>
+        <v>108.42</v>
       </c>
       <c r="K59" t="n">
-        <v>11.85</v>
+        <v>11.21</v>
       </c>
       <c r="L59" t="n">
-        <v>0.3035</v>
+        <v>0.276</v>
       </c>
       <c r="M59" t="n">
-        <v>0.1427</v>
+        <v>0.1244</v>
       </c>
       <c r="N59" t="n">
-        <v>-4.6</v>
+        <v>10.6</v>
       </c>
       <c r="O59" t="n">
+        <v>23</v>
+      </c>
+      <c r="P59" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>23</v>
+      </c>
+      <c r="R59" t="n">
         <v>25</v>
       </c>
-      <c r="P59" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>22</v>
-      </c>
-      <c r="R59" t="n">
-        <v>22</v>
-      </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="T59" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="U59" t="n">
-        <v>1718</v>
+        <v>1701.3</v>
       </c>
     </row>
     <row r="60">
@@ -4664,31 +4664,31 @@
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G60" t="n">
-        <v>1881.8</v>
+        <v>1887.4</v>
       </c>
       <c r="H60" t="n">
-        <v>5.4881</v>
+        <v>5.1867</v>
       </c>
       <c r="I60" t="n">
-        <v>116.58</v>
+        <v>117.12</v>
       </c>
       <c r="J60" t="n">
-        <v>106.11</v>
+        <v>106.56</v>
       </c>
       <c r="K60" t="n">
-        <v>10.47</v>
+        <v>10.57</v>
       </c>
       <c r="L60" t="n">
-        <v>0.3117</v>
+        <v>0.3122</v>
       </c>
       <c r="M60" t="n">
-        <v>0.1455</v>
+        <v>0.1426</v>
       </c>
       <c r="N60" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="O60" t="n">
         <v>27</v>
@@ -4709,7 +4709,7 @@
         <v>28</v>
       </c>
       <c r="U60" t="n">
-        <v>1728.4</v>
+        <v>1721.6</v>
       </c>
     </row>
     <row r="61">
@@ -4927,11 +4927,11 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1275</v>
+        <v>1400</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Miami OH</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4948,52 +4948,52 @@
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="G64" t="n">
-        <v>1775.2</v>
+        <v>1741.7</v>
       </c>
       <c r="H64" t="n">
-        <v>9.651999999999999</v>
+        <v>2.8164</v>
       </c>
       <c r="I64" t="n">
-        <v>120.89</v>
+        <v>119.5</v>
       </c>
       <c r="J64" t="n">
-        <v>105.23</v>
+        <v>111.34</v>
       </c>
       <c r="K64" t="n">
-        <v>15.66</v>
+        <v>8.16</v>
       </c>
       <c r="L64" t="n">
-        <v>0.2107</v>
+        <v>0.3072</v>
       </c>
       <c r="M64" t="n">
-        <v>0.1402</v>
+        <v>0.145</v>
       </c>
       <c r="N64" t="n">
-        <v>6</v>
+        <v>-8</v>
       </c>
       <c r="O64" t="n">
-        <v>91</v>
+        <v>33</v>
       </c>
       <c r="P64" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="Q64" t="n">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="R64" t="n">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="T64" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="U64" t="n">
-        <v>1414.6</v>
+        <v>1696.4</v>
       </c>
     </row>
     <row r="65">
@@ -5069,11 +5069,11 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1372</v>
+        <v>1270</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SF Austin</t>
+          <t>McNeese St</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5090,52 +5090,52 @@
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G66" t="n">
-        <v>1565.8</v>
+        <v>1726.8</v>
       </c>
       <c r="H66" t="n">
-        <v>3.2279</v>
+        <v>2.6895</v>
       </c>
       <c r="I66" t="n">
-        <v>112.79</v>
+        <v>115.07</v>
       </c>
       <c r="J66" t="n">
-        <v>98.54000000000001</v>
+        <v>100.01</v>
       </c>
       <c r="K66" t="n">
-        <v>14.26</v>
+        <v>15.06</v>
       </c>
       <c r="L66" t="n">
-        <v>0.3083</v>
+        <v>0.3483</v>
       </c>
       <c r="M66" t="n">
-        <v>0.1321</v>
+        <v>0.139</v>
       </c>
       <c r="N66" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O66" t="n">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="P66" t="n">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="Q66" t="n">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="R66" t="n">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="S66" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="T66" t="n">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="U66" t="n">
-        <v>1383.6</v>
+        <v>1428.4</v>
       </c>
     </row>
     <row r="67">
@@ -5282,11 +5282,11 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1373</v>
+        <v>1254</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Siena</t>
+          <t>LIU Brooklyn</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5306,49 +5306,49 @@
         <v>127</v>
       </c>
       <c r="G69" t="n">
-        <v>1478</v>
+        <v>1418.2</v>
       </c>
       <c r="H69" t="n">
-        <v>0.9489</v>
+        <v>2.3581</v>
       </c>
       <c r="I69" t="n">
-        <v>109.73</v>
+        <v>109.38</v>
       </c>
       <c r="J69" t="n">
-        <v>101.77</v>
+        <v>104.38</v>
       </c>
       <c r="K69" t="n">
-        <v>7.95</v>
+        <v>5</v>
       </c>
       <c r="L69" t="n">
-        <v>0.2799</v>
+        <v>0.3119</v>
       </c>
       <c r="M69" t="n">
-        <v>0.1508</v>
+        <v>0.183</v>
       </c>
       <c r="N69" t="n">
-        <v>6.2</v>
+        <v>10.4</v>
       </c>
       <c r="O69" t="n">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="P69" t="n">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="Q69" t="n">
-        <v>180</v>
+        <v>213</v>
       </c>
       <c r="R69" t="n">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="S69" t="n">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="T69" t="n">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="U69" t="n">
-        <v>1430.3</v>
+        <v>1378.8</v>
       </c>
     </row>
   </sheetData>

--- a/team_stats_2026.xlsx
+++ b/team_stats_2026.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,107 +429,107 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Is_FirstFour</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -546,31 +558,31 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G2" t="n">
-        <v>2183.9</v>
+        <v>2185.1</v>
       </c>
       <c r="H2" t="n">
-        <v>3.6873</v>
+        <v>3.7089</v>
       </c>
       <c r="I2" t="n">
-        <v>123.11</v>
+        <v>123.04</v>
       </c>
       <c r="J2" t="n">
-        <v>93.04000000000001</v>
+        <v>94.12</v>
       </c>
       <c r="K2" t="n">
-        <v>30.07</v>
+        <v>28.93</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2884</v>
+        <v>0.2948</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1511</v>
+        <v>0.1547</v>
       </c>
       <c r="N2" t="n">
-        <v>23.8</v>
+        <v>23</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -591,16 +603,16 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>1701.5</v>
+        <v>1695.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1277</v>
+        <v>1235</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Michigan St</t>
+          <t>Iowa St</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,61 +629,61 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G3" t="n">
-        <v>2049.8</v>
+        <v>2045.9</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2376</v>
+        <v>2.4203</v>
       </c>
       <c r="I3" t="n">
-        <v>117.05</v>
+        <v>118.77</v>
       </c>
       <c r="J3" t="n">
-        <v>100.92</v>
+        <v>94.51000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>16.13</v>
+        <v>24.26</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2993</v>
+        <v>0.3164</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1615</v>
+        <v>0.1462</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>13.4</v>
       </c>
       <c r="O3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>6</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6</v>
+      </c>
+      <c r="S3" t="n">
         <v>11</v>
       </c>
-      <c r="Q3" t="n">
-        <v>10</v>
-      </c>
-      <c r="R3" t="n">
-        <v>9</v>
-      </c>
-      <c r="S3" t="n">
-        <v>7</v>
-      </c>
       <c r="T3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="U3" t="n">
-        <v>1729.6</v>
+        <v>1700.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1104</v>
+        <v>1228</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Alabama</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -688,61 +700,61 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G4" t="n">
-        <v>1975.1</v>
+        <v>2003.3</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.4869</v>
+        <v>8.2525</v>
       </c>
       <c r="I4" t="n">
-        <v>122.11</v>
+        <v>125.48</v>
       </c>
       <c r="J4" t="n">
-        <v>110.78</v>
+        <v>103.07</v>
       </c>
       <c r="K4" t="n">
-        <v>11.33</v>
+        <v>22.41</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2853</v>
+        <v>0.3238</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1289</v>
+        <v>0.1295</v>
       </c>
       <c r="N4" t="n">
-        <v>7.2</v>
+        <v>10.6</v>
       </c>
       <c r="O4" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="P4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7</v>
+      </c>
+      <c r="S4" t="n">
         <v>12</v>
       </c>
-      <c r="R4" t="n">
-        <v>12</v>
-      </c>
-      <c r="S4" t="n">
-        <v>14</v>
-      </c>
       <c r="T4" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="U4" t="n">
-        <v>1772.1</v>
+        <v>1709.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1242</v>
+        <v>1345</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Purdue</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -759,61 +771,61 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G5" t="n">
-        <v>1973.7</v>
+        <v>1959</v>
       </c>
       <c r="H5" t="n">
-        <v>11.337</v>
+        <v>-0.051</v>
       </c>
       <c r="I5" t="n">
-        <v>111.61</v>
+        <v>124.95</v>
       </c>
       <c r="J5" t="n">
-        <v>100.9</v>
+        <v>107.45</v>
       </c>
       <c r="K5" t="n">
-        <v>10.71</v>
+        <v>17.5</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2487</v>
+        <v>0.3095</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1523</v>
+        <v>0.1344</v>
       </c>
       <c r="N5" t="n">
-        <v>-3.4</v>
+        <v>0.6</v>
       </c>
       <c r="O5" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="P5" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="Q5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="R5" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="S5" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="T5" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="U5" t="n">
-        <v>1772.3</v>
+        <v>1740.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1397</v>
+        <v>1116</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -833,58 +845,58 @@
         <v>124</v>
       </c>
       <c r="G6" t="n">
-        <v>1898.6</v>
+        <v>1950</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.6704</v>
+        <v>5.5428</v>
       </c>
       <c r="I6" t="n">
-        <v>117.06</v>
+        <v>122.85</v>
       </c>
       <c r="J6" t="n">
-        <v>101.96</v>
+        <v>108.88</v>
       </c>
       <c r="K6" t="n">
-        <v>15.09</v>
+        <v>13.96</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3583</v>
+        <v>0.3009</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1671</v>
+        <v>0.1205</v>
       </c>
       <c r="N6" t="n">
         <v>2.6</v>
       </c>
       <c r="O6" t="n">
+        <v>18</v>
+      </c>
+      <c r="P6" t="n">
         <v>14</v>
       </c>
-      <c r="P6" t="n">
-        <v>17</v>
-      </c>
       <c r="Q6" t="n">
+        <v>20</v>
+      </c>
+      <c r="R6" t="n">
+        <v>16</v>
+      </c>
+      <c r="S6" t="n">
+        <v>21</v>
+      </c>
+      <c r="T6" t="n">
         <v>18</v>
       </c>
-      <c r="R6" t="n">
-        <v>20</v>
-      </c>
-      <c r="S6" t="n">
-        <v>24</v>
-      </c>
-      <c r="T6" t="n">
-        <v>21</v>
-      </c>
       <c r="U6" t="n">
-        <v>1706.1</v>
+        <v>1728.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1314</v>
+        <v>1257</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Louisville</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -901,61 +913,61 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G7" t="n">
-        <v>1917.6</v>
+        <v>1836.9</v>
       </c>
       <c r="H7" t="n">
-        <v>2.3735</v>
+        <v>-2.5958</v>
       </c>
       <c r="I7" t="n">
-        <v>115.09</v>
+        <v>118.9</v>
       </c>
       <c r="J7" t="n">
-        <v>103.39</v>
+        <v>101.88</v>
       </c>
       <c r="K7" t="n">
-        <v>11.71</v>
+        <v>17.02</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2653</v>
+        <v>0.289</v>
       </c>
       <c r="M7" t="n">
-        <v>0.14</v>
+        <v>0.1597</v>
       </c>
       <c r="N7" t="n">
         <v>2.4</v>
       </c>
       <c r="O7" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="P7" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>9</v>
+      </c>
+      <c r="R7" t="n">
         <v>21</v>
       </c>
-      <c r="Q7" t="n">
-        <v>24</v>
-      </c>
-      <c r="R7" t="n">
-        <v>24</v>
-      </c>
       <c r="S7" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="T7" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="U7" t="n">
-        <v>1676</v>
+        <v>1686.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1437</v>
+        <v>1246</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Villanova</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -972,61 +984,61 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G8" t="n">
-        <v>1825.7</v>
+        <v>1897</v>
       </c>
       <c r="H8" t="n">
-        <v>6.1267</v>
+        <v>4.9403</v>
       </c>
       <c r="I8" t="n">
-        <v>115.45</v>
+        <v>116.84</v>
       </c>
       <c r="J8" t="n">
-        <v>104.42</v>
+        <v>106.32</v>
       </c>
       <c r="K8" t="n">
-        <v>11.03</v>
+        <v>10.52</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3111</v>
+        <v>0.312</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1421</v>
+        <v>0.1463</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2</v>
+        <v>1.4</v>
       </c>
       <c r="O8" t="n">
+        <v>27</v>
+      </c>
+      <c r="P8" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>26</v>
+      </c>
+      <c r="R8" t="n">
         <v>32</v>
       </c>
-      <c r="P8" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>35</v>
-      </c>
-      <c r="R8" t="n">
-        <v>26</v>
-      </c>
       <c r="S8" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="T8" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="U8" t="n">
-        <v>1644.1</v>
+        <v>1723.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1274</v>
+        <v>1208</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Miami FL</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1043,61 +1055,61 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G9" t="n">
-        <v>1761</v>
+        <v>1798.1</v>
       </c>
       <c r="H9" t="n">
-        <v>12.4806</v>
+        <v>0.2861</v>
       </c>
       <c r="I9" t="n">
-        <v>118.15</v>
+        <v>119.92</v>
       </c>
       <c r="J9" t="n">
-        <v>101.88</v>
+        <v>106.59</v>
       </c>
       <c r="K9" t="n">
-        <v>16.27</v>
+        <v>13.33</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3077</v>
+        <v>0.3181</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1596</v>
+        <v>0.141</v>
       </c>
       <c r="N9" t="n">
-        <v>6.8</v>
+        <v>4.6</v>
       </c>
       <c r="O9" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="P9" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="Q9" t="n">
+        <v>28</v>
+      </c>
+      <c r="R9" t="n">
         <v>27</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
+        <v>32</v>
+      </c>
+      <c r="T9" t="n">
         <v>31</v>
       </c>
-      <c r="S9" t="n">
-        <v>26</v>
-      </c>
-      <c r="T9" t="n">
-        <v>32</v>
-      </c>
       <c r="U9" t="n">
-        <v>1617.1</v>
+        <v>1643.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1234</v>
+        <v>1395</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Iowa</t>
+          <t>TCU</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1114,61 +1126,61 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G10" t="n">
-        <v>1848.9</v>
+        <v>1836.1</v>
       </c>
       <c r="H10" t="n">
-        <v>3.6941</v>
+        <v>6.9164</v>
       </c>
       <c r="I10" t="n">
-        <v>118.64</v>
+        <v>111.16</v>
       </c>
       <c r="J10" t="n">
-        <v>103.68</v>
+        <v>102.34</v>
       </c>
       <c r="K10" t="n">
-        <v>14.95</v>
+        <v>8.81</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2884</v>
+        <v>0.3231</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1443</v>
+        <v>0.1514</v>
       </c>
       <c r="N10" t="n">
-        <v>2.8</v>
+        <v>5.8</v>
       </c>
       <c r="O10" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="P10" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="Q10" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="R10" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="S10" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="T10" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="U10" t="n">
-        <v>1707.5</v>
+        <v>1691.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1416</v>
+        <v>1365</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UCF</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1185,61 +1197,61 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G11" t="n">
-        <v>1831.1</v>
+        <v>1782.8</v>
       </c>
       <c r="H11" t="n">
-        <v>6.3402</v>
+        <v>0.0374</v>
       </c>
       <c r="I11" t="n">
-        <v>113.8</v>
+        <v>117.62</v>
       </c>
       <c r="J11" t="n">
-        <v>109.32</v>
+        <v>104.11</v>
       </c>
       <c r="K11" t="n">
-        <v>4.47</v>
+        <v>13.51</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3133</v>
+        <v>0.3504</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1536</v>
+        <v>0.1498</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.8</v>
+        <v>0.8</v>
       </c>
       <c r="O11" t="n">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="P11" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>46</v>
+      </c>
+      <c r="R11" t="n">
+        <v>36</v>
+      </c>
+      <c r="S11" t="n">
+        <v>36</v>
+      </c>
+      <c r="T11" t="n">
         <v>42</v>
       </c>
-      <c r="Q11" t="n">
-        <v>57</v>
-      </c>
-      <c r="R11" t="n">
-        <v>46</v>
-      </c>
-      <c r="S11" t="n">
-        <v>37</v>
-      </c>
-      <c r="T11" t="n">
-        <v>51</v>
-      </c>
       <c r="U11" t="n">
-        <v>1689.6</v>
+        <v>1596.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1275</v>
+        <v>1281</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Miami OH</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1249,68 +1261,68 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>11a</t>
         </is>
       </c>
       <c r="E12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="G12" t="n">
-        <v>1775.2</v>
+        <v>1747.8</v>
       </c>
       <c r="H12" t="n">
-        <v>9.651999999999999</v>
+        <v>-1.7576</v>
       </c>
       <c r="I12" t="n">
-        <v>120.89</v>
+        <v>114.92</v>
       </c>
       <c r="J12" t="n">
-        <v>105.23</v>
+        <v>109.48</v>
       </c>
       <c r="K12" t="n">
-        <v>15.66</v>
+        <v>5.45</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2107</v>
+        <v>0.2996</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1402</v>
+        <v>0.1685</v>
       </c>
       <c r="N12" t="n">
-        <v>6</v>
+        <v>0.4</v>
       </c>
       <c r="O12" t="n">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="P12" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="Q12" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="R12" t="n">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="T12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="U12" t="n">
-        <v>1414.6</v>
+        <v>1658.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1320</v>
+        <v>1433</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Northern Iowa</t>
+          <t>VCU</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1320,68 +1332,68 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11b</t>
         </is>
       </c>
       <c r="E13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G13" t="n">
-        <v>1573.9</v>
+        <v>1739.9</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.696</v>
+        <v>2.9764</v>
       </c>
       <c r="I13" t="n">
-        <v>108.74</v>
+        <v>118.46</v>
       </c>
       <c r="J13" t="n">
-        <v>97.5</v>
+        <v>103.76</v>
       </c>
       <c r="K13" t="n">
-        <v>11.25</v>
+        <v>14.7</v>
       </c>
       <c r="L13" t="n">
-        <v>0.225</v>
+        <v>0.2979</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1354</v>
+        <v>0.1497</v>
       </c>
       <c r="N13" t="n">
-        <v>14.4</v>
+        <v>6.2</v>
       </c>
       <c r="O13" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="P13" t="n">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="Q13" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="R13" t="n">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="S13" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="T13" t="n">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="U13" t="n">
-        <v>1515.8</v>
+        <v>1554.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1358</v>
+        <v>1463</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sam Houston St</t>
+          <t>Yale</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1391,68 +1403,68 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E14" t="b">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="G14" t="n">
-        <v>1545</v>
+        <v>1720.2</v>
       </c>
       <c r="H14" t="n">
-        <v>4.4295</v>
+        <v>1.1161</v>
       </c>
       <c r="I14" t="n">
-        <v>112.95</v>
+        <v>120.93</v>
       </c>
       <c r="J14" t="n">
-        <v>106.4</v>
+        <v>107.17</v>
       </c>
       <c r="K14" t="n">
-        <v>6.55</v>
+        <v>13.77</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3122</v>
+        <v>0.2847</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1587</v>
+        <v>0.1362</v>
       </c>
       <c r="N14" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="O14" t="n">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="P14" t="n">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="Q14" t="n">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="R14" t="n">
-        <v>111</v>
+        <v>72</v>
       </c>
       <c r="S14" t="n">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="T14" t="n">
-        <v>104</v>
+        <v>66</v>
       </c>
       <c r="U14" t="n">
-        <v>1499.6</v>
+        <v>1457.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1407</v>
+        <v>1320</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Troy</t>
+          <t>Northern Iowa</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1462,68 +1474,68 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E15" t="b">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G15" t="n">
-        <v>1601</v>
+        <v>1573.9</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1284</v>
+        <v>-3.696</v>
       </c>
       <c r="I15" t="n">
-        <v>112.28</v>
+        <v>108.74</v>
       </c>
       <c r="J15" t="n">
-        <v>106.19</v>
+        <v>97.5</v>
       </c>
       <c r="K15" t="n">
-        <v>6.08</v>
+        <v>11.25</v>
       </c>
       <c r="L15" t="n">
-        <v>0.316</v>
+        <v>0.225</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1667</v>
+        <v>0.1354</v>
       </c>
       <c r="N15" t="n">
-        <v>9.4</v>
+        <v>14.4</v>
       </c>
       <c r="O15" t="n">
-        <v>153</v>
+        <v>70</v>
       </c>
       <c r="P15" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="Q15" t="n">
-        <v>137</v>
+        <v>72</v>
       </c>
       <c r="R15" t="n">
-        <v>137</v>
+        <v>76</v>
       </c>
       <c r="S15" t="n">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="T15" t="n">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="U15" t="n">
-        <v>1466</v>
+        <v>1515.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1474</v>
+        <v>1295</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Queens NC</t>
+          <t>N Dakota St</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1533,7 +1545,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E16" t="b">
@@ -1543,58 +1555,58 @@
         <v>125</v>
       </c>
       <c r="G16" t="n">
-        <v>1427.4</v>
+        <v>1593.8</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0039</v>
+        <v>3.5257</v>
       </c>
       <c r="I16" t="n">
-        <v>119.17</v>
+        <v>114.28</v>
       </c>
       <c r="J16" t="n">
-        <v>116.56</v>
+        <v>102.18</v>
       </c>
       <c r="K16" t="n">
-        <v>2.61</v>
+        <v>12.1</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2859</v>
+        <v>0.3104</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1441</v>
+        <v>0.1506</v>
       </c>
       <c r="N16" t="n">
-        <v>6.4</v>
+        <v>10.8</v>
       </c>
       <c r="O16" t="n">
-        <v>183</v>
+        <v>114</v>
       </c>
       <c r="P16" t="n">
-        <v>192</v>
+        <v>116</v>
       </c>
       <c r="Q16" t="n">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="R16" t="n">
-        <v>177</v>
+        <v>115</v>
       </c>
       <c r="S16" t="n">
-        <v>171</v>
+        <v>98</v>
       </c>
       <c r="T16" t="n">
-        <v>187</v>
+        <v>115</v>
       </c>
       <c r="U16" t="n">
-        <v>1430.9</v>
+        <v>1410.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1373</v>
+        <v>1398</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Siena</t>
+          <t>Tennessee St</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1604,139 +1616,139 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E17" t="b">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G17" t="n">
-        <v>1478</v>
+        <v>1466.9</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9489</v>
+        <v>3.3618</v>
       </c>
       <c r="I17" t="n">
-        <v>109.73</v>
+        <v>109.9</v>
       </c>
       <c r="J17" t="n">
-        <v>101.77</v>
+        <v>103.28</v>
       </c>
       <c r="K17" t="n">
-        <v>7.95</v>
+        <v>6.62</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2799</v>
+        <v>0.328</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1508</v>
+        <v>0.1589</v>
       </c>
       <c r="N17" t="n">
-        <v>6.2</v>
+        <v>19.8</v>
       </c>
       <c r="O17" t="n">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="P17" t="n">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="Q17" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="R17" t="n">
+        <v>168</v>
+      </c>
+      <c r="S17" t="n">
+        <v>153</v>
+      </c>
+      <c r="T17" t="n">
         <v>172</v>
       </c>
-      <c r="S17" t="n">
-        <v>177</v>
-      </c>
-      <c r="T17" t="n">
-        <v>188</v>
-      </c>
       <c r="U17" t="n">
-        <v>1430.3</v>
+        <v>1407.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1196</v>
+        <v>1373</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Siena</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E18" t="b">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G18" t="n">
-        <v>2014.8</v>
+        <v>1478</v>
       </c>
       <c r="H18" t="n">
-        <v>2.8716</v>
+        <v>0.9489</v>
       </c>
       <c r="I18" t="n">
-        <v>120.95</v>
+        <v>109.73</v>
       </c>
       <c r="J18" t="n">
-        <v>99.02</v>
+        <v>101.77</v>
       </c>
       <c r="K18" t="n">
-        <v>21.92</v>
+        <v>7.95</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3329</v>
+        <v>0.2799</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1552</v>
+        <v>0.1508</v>
       </c>
       <c r="N18" t="n">
-        <v>21.4</v>
+        <v>6.2</v>
       </c>
       <c r="O18" t="n">
-        <v>4</v>
+        <v>195</v>
       </c>
       <c r="P18" t="n">
-        <v>4</v>
+        <v>212</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>180</v>
       </c>
       <c r="R18" t="n">
-        <v>4</v>
+        <v>172</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>177</v>
       </c>
       <c r="T18" t="n">
-        <v>4</v>
+        <v>188</v>
       </c>
       <c r="U18" t="n">
-        <v>1709.6</v>
+        <v>1430.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1222</v>
+        <v>1196</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1746,7 +1758,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="E19" t="b">
@@ -1756,58 +1768,58 @@
         <v>124</v>
       </c>
       <c r="G19" t="n">
-        <v>2102.9</v>
+        <v>2014.8</v>
       </c>
       <c r="H19" t="n">
-        <v>1.6401</v>
+        <v>2.8716</v>
       </c>
       <c r="I19" t="n">
-        <v>117.95</v>
+        <v>120.95</v>
       </c>
       <c r="J19" t="n">
-        <v>95.43000000000001</v>
+        <v>99.02</v>
       </c>
       <c r="K19" t="n">
-        <v>22.51</v>
+        <v>21.92</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3379</v>
+        <v>0.3329</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1199</v>
+        <v>0.1552</v>
       </c>
       <c r="N19" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4</v>
+      </c>
+      <c r="P19" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4</v>
+      </c>
+      <c r="R19" t="n">
+        <v>4</v>
+      </c>
+      <c r="S19" t="n">
         <v>8</v>
       </c>
-      <c r="O19" t="n">
-        <v>6</v>
-      </c>
-      <c r="P19" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>7</v>
-      </c>
-      <c r="R19" t="n">
-        <v>5</v>
-      </c>
-      <c r="S19" t="n">
-        <v>6</v>
-      </c>
       <c r="T19" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U19" t="n">
-        <v>1706.6</v>
+        <v>1709.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1304</v>
+        <v>1222</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nebraska</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1817,68 +1829,68 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="E20" t="b">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G20" t="n">
-        <v>1999.6</v>
+        <v>2111.2</v>
       </c>
       <c r="H20" t="n">
-        <v>10.6735</v>
+        <v>1.4261</v>
       </c>
       <c r="I20" t="n">
-        <v>115.4</v>
+        <v>117.41</v>
       </c>
       <c r="J20" t="n">
-        <v>97.95</v>
+        <v>95.28</v>
       </c>
       <c r="K20" t="n">
-        <v>17.45</v>
+        <v>22.14</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2379</v>
+        <v>0.3403</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1402</v>
+        <v>0.1244</v>
       </c>
       <c r="N20" t="n">
-        <v>8</v>
+        <v>10.8</v>
       </c>
       <c r="O20" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="P20" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="Q20" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="R20" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T20" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="U20" t="n">
-        <v>1665.7</v>
+        <v>1716.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1345</v>
+        <v>1304</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Purdue</t>
+          <t>Nebraska</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1888,68 +1900,68 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="E21" t="b">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G21" t="n">
-        <v>1955.6</v>
+        <v>1999.6</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3963</v>
+        <v>10.6735</v>
       </c>
       <c r="I21" t="n">
-        <v>124.64</v>
+        <v>115.4</v>
       </c>
       <c r="J21" t="n">
-        <v>107.6</v>
+        <v>97.95</v>
       </c>
       <c r="K21" t="n">
-        <v>17.04</v>
+        <v>17.45</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3051</v>
+        <v>0.2379</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1348</v>
+        <v>0.1402</v>
       </c>
       <c r="N21" t="n">
-        <v>3.8</v>
+        <v>8</v>
       </c>
       <c r="O21" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P21" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>16</v>
+      </c>
+      <c r="R21" t="n">
+        <v>13</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="n">
         <v>12</v>
       </c>
-      <c r="Q21" t="n">
-        <v>8</v>
-      </c>
-      <c r="R21" t="n">
-        <v>8</v>
-      </c>
-      <c r="S21" t="n">
-        <v>13</v>
-      </c>
-      <c r="T21" t="n">
-        <v>10</v>
-      </c>
       <c r="U21" t="n">
-        <v>1746.9</v>
+        <v>1665.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1385</v>
+        <v>1403</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>St John's</t>
+          <t>Texas Tech</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1959,68 +1971,68 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>04</t>
         </is>
       </c>
       <c r="E22" t="b">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="G22" t="n">
-        <v>1961.4</v>
+        <v>2010.7</v>
       </c>
       <c r="H22" t="n">
-        <v>5.5897</v>
+        <v>9.579599999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>113.79</v>
+        <v>117.2</v>
       </c>
       <c r="J22" t="n">
-        <v>98.7</v>
+        <v>106.7</v>
       </c>
       <c r="K22" t="n">
-        <v>15.09</v>
+        <v>10.5</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3238</v>
+        <v>0.2893</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1418</v>
+        <v>0.155</v>
       </c>
       <c r="N22" t="n">
-        <v>7.8</v>
+        <v>-3</v>
       </c>
       <c r="O22" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="P22" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>19</v>
+      </c>
+      <c r="R22" t="n">
         <v>15</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="S22" t="n">
         <v>17</v>
       </c>
-      <c r="R22" t="n">
-        <v>17</v>
-      </c>
-      <c r="S22" t="n">
-        <v>20</v>
-      </c>
       <c r="T22" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="U22" t="n">
-        <v>1680.5</v>
+        <v>1772.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1140</v>
+        <v>1385</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BYU</t>
+          <t>St John's</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2030,68 +2042,68 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>05</t>
         </is>
       </c>
       <c r="E23" t="b">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G23" t="n">
-        <v>1934.4</v>
+        <v>1964.1</v>
       </c>
       <c r="H23" t="n">
-        <v>0.879</v>
+        <v>5.6344</v>
       </c>
       <c r="I23" t="n">
-        <v>118.42</v>
+        <v>113.75</v>
       </c>
       <c r="J23" t="n">
-        <v>105.83</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>12.58</v>
+        <v>15.21</v>
       </c>
       <c r="L23" t="n">
-        <v>0.3042</v>
+        <v>0.3255</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1509</v>
+        <v>0.1408</v>
       </c>
       <c r="N23" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="O23" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="P23" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="Q23" t="n">
+        <v>17</v>
+      </c>
+      <c r="R23" t="n">
+        <v>17</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="n">
         <v>22</v>
       </c>
-      <c r="R23" t="n">
-        <v>22</v>
-      </c>
-      <c r="S23" t="n">
-        <v>25</v>
-      </c>
-      <c r="T23" t="n">
-        <v>24</v>
-      </c>
       <c r="U23" t="n">
-        <v>1718.9</v>
+        <v>1676.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1388</v>
+        <v>1314</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>St Mary's CA</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2101,68 +2113,68 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>06</t>
         </is>
       </c>
       <c r="E24" t="b">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G24" t="n">
-        <v>1857.8</v>
+        <v>1899.5</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2818</v>
+        <v>2.2848</v>
       </c>
       <c r="I24" t="n">
-        <v>118.73</v>
+        <v>115.28</v>
       </c>
       <c r="J24" t="n">
-        <v>99.88</v>
+        <v>103.72</v>
       </c>
       <c r="K24" t="n">
-        <v>18.85</v>
+        <v>11.56</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2975</v>
+        <v>0.2596</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1525</v>
+        <v>0.1375</v>
       </c>
       <c r="N24" t="n">
-        <v>8.6</v>
+        <v>-0.4</v>
       </c>
       <c r="O24" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="P24" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>24</v>
+      </c>
+      <c r="R24" t="n">
+        <v>24</v>
+      </c>
+      <c r="S24" t="n">
+        <v>18</v>
+      </c>
+      <c r="T24" t="n">
         <v>23</v>
       </c>
-      <c r="Q24" t="n">
-        <v>25</v>
-      </c>
-      <c r="R24" t="n">
-        <v>23</v>
-      </c>
-      <c r="S24" t="n">
-        <v>19</v>
-      </c>
-      <c r="T24" t="n">
-        <v>20</v>
-      </c>
       <c r="U24" t="n">
-        <v>1596.9</v>
+        <v>1677.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1395</v>
+        <v>1388</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TCU</t>
+          <t>St Mary's CA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2172,59 +2184,59 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>07</t>
         </is>
       </c>
       <c r="E25" t="b">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G25" t="n">
-        <v>1845.8</v>
+        <v>1857.8</v>
       </c>
       <c r="H25" t="n">
-        <v>6.897</v>
+        <v>-0.2818</v>
       </c>
       <c r="I25" t="n">
-        <v>111.93</v>
+        <v>118.73</v>
       </c>
       <c r="J25" t="n">
-        <v>102.48</v>
+        <v>99.88</v>
       </c>
       <c r="K25" t="n">
-        <v>9.449999999999999</v>
+        <v>18.85</v>
       </c>
       <c r="L25" t="n">
-        <v>0.3255</v>
+        <v>0.2975</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1494</v>
+        <v>0.1525</v>
       </c>
       <c r="N25" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="O25" t="n">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="P25" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="Q25" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="R25" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="S25" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="T25" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="U25" t="n">
-        <v>1680.3</v>
+        <v>1596.9</v>
       </c>
     </row>
     <row r="26">
@@ -2243,38 +2255,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>08</t>
         </is>
       </c>
       <c r="E26" t="b">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G26" t="n">
-        <v>1799.9</v>
+        <v>1817</v>
       </c>
       <c r="H26" t="n">
-        <v>1.5472</v>
+        <v>1.7194</v>
       </c>
       <c r="I26" t="n">
-        <v>118.74</v>
+        <v>118.68</v>
       </c>
       <c r="J26" t="n">
-        <v>107.91</v>
+        <v>108.16</v>
       </c>
       <c r="K26" t="n">
-        <v>10.83</v>
+        <v>10.52</v>
       </c>
       <c r="L26" t="n">
-        <v>0.2524</v>
+        <v>0.2526</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1503</v>
+        <v>0.1502</v>
       </c>
       <c r="N26" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="O26" t="n">
         <v>26</v>
@@ -2295,16 +2307,16 @@
         <v>30</v>
       </c>
       <c r="U26" t="n">
-        <v>1700.1</v>
+        <v>1705.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1301</v>
+        <v>1155</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NC State</t>
+          <t>Clemson</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2314,68 +2326,68 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>09</t>
         </is>
       </c>
       <c r="E27" t="b">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G27" t="n">
-        <v>1740.7</v>
+        <v>1863.6</v>
       </c>
       <c r="H27" t="n">
-        <v>7.3141</v>
+        <v>2.7155</v>
       </c>
       <c r="I27" t="n">
-        <v>120.03</v>
+        <v>113.29</v>
       </c>
       <c r="J27" t="n">
-        <v>109.14</v>
+        <v>101.28</v>
       </c>
       <c r="K27" t="n">
-        <v>10.89</v>
+        <v>12</v>
       </c>
       <c r="L27" t="n">
-        <v>0.2784</v>
+        <v>0.2541</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1277</v>
+        <v>0.1378</v>
       </c>
       <c r="N27" t="n">
-        <v>-11</v>
+        <v>2.8</v>
       </c>
       <c r="O27" t="n">
+        <v>38</v>
+      </c>
+      <c r="P27" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>32</v>
+      </c>
+      <c r="R27" t="n">
+        <v>35</v>
+      </c>
+      <c r="S27" t="n">
+        <v>34</v>
+      </c>
+      <c r="T27" t="n">
         <v>36</v>
       </c>
-      <c r="P27" t="n">
-        <v>45</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>34</v>
-      </c>
-      <c r="R27" t="n">
-        <v>38</v>
-      </c>
-      <c r="S27" t="n">
-        <v>42</v>
-      </c>
-      <c r="T27" t="n">
-        <v>35</v>
-      </c>
       <c r="U27" t="n">
-        <v>1669.5</v>
+        <v>1655.1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1374</v>
+        <v>1387</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SMU</t>
+          <t>St Louis</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2385,68 +2397,68 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>11a</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="G28" t="n">
-        <v>1733.9</v>
+        <v>1807.8</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2411</v>
+        <v>9.839</v>
       </c>
       <c r="I28" t="n">
-        <v>117.96</v>
+        <v>120.36</v>
       </c>
       <c r="J28" t="n">
-        <v>109.76</v>
+        <v>98.52</v>
       </c>
       <c r="K28" t="n">
-        <v>8.199999999999999</v>
+        <v>21.84</v>
       </c>
       <c r="L28" t="n">
-        <v>0.3098</v>
+        <v>0.2436</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1542</v>
+        <v>0.1686</v>
       </c>
       <c r="N28" t="n">
-        <v>-5.6</v>
+        <v>-0.4</v>
       </c>
       <c r="O28" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="P28" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="Q28" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="R28" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="S28" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="T28" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="U28" t="n">
-        <v>1649.8</v>
+        <v>1512.1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1120</v>
+        <v>1378</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Auburn</t>
+          <t>South Florida</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2456,68 +2468,68 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>11b</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G29" t="n">
-        <v>1837.5</v>
+        <v>1711.8</v>
       </c>
       <c r="H29" t="n">
-        <v>-7.6154</v>
+        <v>9.207800000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>118.87</v>
+        <v>116.06</v>
       </c>
       <c r="J29" t="n">
-        <v>113.5</v>
+        <v>101.73</v>
       </c>
       <c r="K29" t="n">
-        <v>5.37</v>
+        <v>14.32</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3462</v>
+        <v>0.3392</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1435</v>
+        <v>0.1453</v>
       </c>
       <c r="N29" t="n">
-        <v>0.4</v>
+        <v>19.6</v>
       </c>
       <c r="O29" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P29" t="n">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="Q29" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="R29" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="T29" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U29" t="n">
-        <v>1750.3</v>
+        <v>1553.3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1378</v>
+        <v>1270</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>South Florida</t>
+          <t>McNeese St</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2534,61 +2546,61 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G30" t="n">
-        <v>1711.8</v>
+        <v>1726.8</v>
       </c>
       <c r="H30" t="n">
-        <v>9.207800000000001</v>
+        <v>2.6895</v>
       </c>
       <c r="I30" t="n">
-        <v>116.06</v>
+        <v>115.07</v>
       </c>
       <c r="J30" t="n">
-        <v>101.73</v>
+        <v>100.01</v>
       </c>
       <c r="K30" t="n">
-        <v>14.32</v>
+        <v>15.06</v>
       </c>
       <c r="L30" t="n">
-        <v>0.3392</v>
+        <v>0.3483</v>
       </c>
       <c r="M30" t="n">
-        <v>0.1453</v>
+        <v>0.139</v>
       </c>
       <c r="N30" t="n">
-        <v>19.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O30" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="P30" t="n">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="Q30" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="R30" t="n">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="S30" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="T30" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="U30" t="n">
-        <v>1553.3</v>
+        <v>1428.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1220</v>
+        <v>1430</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Hofstra</t>
+          <t>Utah Valley</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2605,52 +2617,52 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G31" t="n">
-        <v>1586.2</v>
+        <v>1637</v>
       </c>
       <c r="H31" t="n">
-        <v>3.3583</v>
+        <v>3.1528</v>
       </c>
       <c r="I31" t="n">
-        <v>113.56</v>
+        <v>111.58</v>
       </c>
       <c r="J31" t="n">
-        <v>102.69</v>
+        <v>100.45</v>
       </c>
       <c r="K31" t="n">
-        <v>10.87</v>
+        <v>11.12</v>
       </c>
       <c r="L31" t="n">
-        <v>0.3081</v>
+        <v>0.3056</v>
       </c>
       <c r="M31" t="n">
-        <v>0.1527</v>
+        <v>0.1962</v>
       </c>
       <c r="N31" t="n">
-        <v>12</v>
+        <v>6.6</v>
       </c>
       <c r="O31" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="P31" t="n">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="Q31" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="R31" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="S31" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="T31" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="U31" t="n">
-        <v>1482.3</v>
+        <v>1455.5</v>
       </c>
     </row>
     <row r="32">
@@ -2818,31 +2830,31 @@
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="G34" t="n">
-        <v>1374.1</v>
+        <v>1375.9</v>
       </c>
       <c r="H34" t="n">
-        <v>-2.5631</v>
+        <v>-2.3939</v>
       </c>
       <c r="I34" t="n">
-        <v>105.51</v>
+        <v>106.4</v>
       </c>
       <c r="J34" t="n">
-        <v>111.44</v>
+        <v>111.97</v>
       </c>
       <c r="K34" t="n">
-        <v>-5.93</v>
+        <v>-5.57</v>
       </c>
       <c r="L34" t="n">
-        <v>0.3235</v>
+        <v>0.322</v>
       </c>
       <c r="M34" t="n">
-        <v>0.1584</v>
+        <v>0.159</v>
       </c>
       <c r="N34" t="n">
-        <v>2</v>
+        <v>-0.2</v>
       </c>
       <c r="O34" t="n">
         <v>275</v>
@@ -2863,7 +2875,7 @@
         <v>277</v>
       </c>
       <c r="U34" t="n">
-        <v>1401.7</v>
+        <v>1396.5</v>
       </c>
     </row>
     <row r="35">
@@ -3031,31 +3043,31 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G37" t="n">
-        <v>2064.2</v>
+        <v>2066.1</v>
       </c>
       <c r="H37" t="n">
-        <v>8.950200000000001</v>
+        <v>8.2806</v>
       </c>
       <c r="I37" t="n">
-        <v>116.34</v>
+        <v>117.74</v>
       </c>
       <c r="J37" t="n">
-        <v>97.40000000000001</v>
+        <v>97.67</v>
       </c>
       <c r="K37" t="n">
-        <v>18.93</v>
+        <v>20.07</v>
       </c>
       <c r="L37" t="n">
-        <v>0.2937</v>
+        <v>0.2928</v>
       </c>
       <c r="M37" t="n">
-        <v>0.1558</v>
+        <v>0.1549</v>
       </c>
       <c r="N37" t="n">
-        <v>6.6</v>
+        <v>13</v>
       </c>
       <c r="O37" t="n">
         <v>11</v>
@@ -3076,16 +3088,16 @@
         <v>9</v>
       </c>
       <c r="U37" t="n">
-        <v>1660.9</v>
+        <v>1659.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1235</v>
+        <v>1104</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Iowa St</t>
+          <t>Alabama</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3102,61 +3114,61 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="G38" t="n">
-        <v>2031.1</v>
+        <v>1975.1</v>
       </c>
       <c r="H38" t="n">
-        <v>2.7523</v>
+        <v>-1.4869</v>
       </c>
       <c r="I38" t="n">
-        <v>118.89</v>
+        <v>122.11</v>
       </c>
       <c r="J38" t="n">
-        <v>94.63</v>
+        <v>110.78</v>
       </c>
       <c r="K38" t="n">
-        <v>24.26</v>
+        <v>11.33</v>
       </c>
       <c r="L38" t="n">
-        <v>0.3199</v>
+        <v>0.2853</v>
       </c>
       <c r="M38" t="n">
-        <v>0.1454</v>
+        <v>0.1289</v>
       </c>
       <c r="N38" t="n">
-        <v>12.2</v>
+        <v>7.2</v>
       </c>
       <c r="O38" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="P38" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q38" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R38" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="S38" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T38" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="U38" t="n">
-        <v>1687.1</v>
+        <v>1772.1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1403</v>
+        <v>1242</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Texas Tech</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3173,61 +3185,61 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G39" t="n">
-        <v>2025.5</v>
+        <v>1983.4</v>
       </c>
       <c r="H39" t="n">
-        <v>10.1327</v>
+        <v>10.797</v>
       </c>
       <c r="I39" t="n">
-        <v>118.86</v>
+        <v>111.09</v>
       </c>
       <c r="J39" t="n">
-        <v>106.69</v>
+        <v>100.73</v>
       </c>
       <c r="K39" t="n">
-        <v>12.16</v>
+        <v>10.36</v>
       </c>
       <c r="L39" t="n">
-        <v>0.2944</v>
+        <v>0.2493</v>
       </c>
       <c r="M39" t="n">
-        <v>0.155</v>
+        <v>0.1516</v>
       </c>
       <c r="N39" t="n">
-        <v>7</v>
+        <v>0.8</v>
       </c>
       <c r="O39" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P39" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>14</v>
+      </c>
+      <c r="R39" t="n">
+        <v>18</v>
+      </c>
+      <c r="S39" t="n">
         <v>16</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="T39" t="n">
         <v>19</v>
       </c>
-      <c r="R39" t="n">
-        <v>15</v>
-      </c>
-      <c r="S39" t="n">
-        <v>17</v>
-      </c>
-      <c r="T39" t="n">
-        <v>15</v>
-      </c>
       <c r="U39" t="n">
-        <v>1762.7</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1435</v>
+        <v>1397</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Vanderbilt</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3244,61 +3256,61 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G40" t="n">
-        <v>1935.7</v>
+        <v>1911</v>
       </c>
       <c r="H40" t="n">
-        <v>2.1989</v>
+        <v>-1.5912</v>
       </c>
       <c r="I40" t="n">
-        <v>121.8</v>
+        <v>117.14</v>
       </c>
       <c r="J40" t="n">
-        <v>105.67</v>
+        <v>101.72</v>
       </c>
       <c r="K40" t="n">
-        <v>16.12</v>
+        <v>15.42</v>
       </c>
       <c r="L40" t="n">
-        <v>0.2802</v>
+        <v>0.3527</v>
       </c>
       <c r="M40" t="n">
-        <v>0.1278</v>
+        <v>0.1643</v>
       </c>
       <c r="N40" t="n">
-        <v>-0.6</v>
+        <v>3.8</v>
       </c>
       <c r="O40" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P40" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Q40" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="R40" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="S40" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="T40" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="U40" t="n">
-        <v>1694.9</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1257</v>
+        <v>1458</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Louisville</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3315,61 +3327,61 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G41" t="n">
-        <v>1855.9</v>
+        <v>1866.2</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.8167</v>
+        <v>1.8886</v>
       </c>
       <c r="I41" t="n">
-        <v>119.15</v>
+        <v>119.65</v>
       </c>
       <c r="J41" t="n">
-        <v>101.26</v>
+        <v>108.66</v>
       </c>
       <c r="K41" t="n">
-        <v>17.89</v>
+        <v>10.99</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2908</v>
+        <v>0.2811</v>
       </c>
       <c r="M41" t="n">
-        <v>0.1584</v>
+        <v>0.123</v>
       </c>
       <c r="N41" t="n">
-        <v>2.8</v>
+        <v>8.6</v>
       </c>
       <c r="O41" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="P41" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="Q41" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="R41" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="S41" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="T41" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="U41" t="n">
-        <v>1683.7</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1208</v>
+        <v>1274</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Miami FL</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3386,52 +3398,52 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G42" t="n">
-        <v>1816.9</v>
+        <v>1780</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2065</v>
+        <v>12.0727</v>
       </c>
       <c r="I42" t="n">
-        <v>121.14</v>
+        <v>117.75</v>
       </c>
       <c r="J42" t="n">
-        <v>107.06</v>
+        <v>101.58</v>
       </c>
       <c r="K42" t="n">
-        <v>14.09</v>
+        <v>16.16</v>
       </c>
       <c r="L42" t="n">
-        <v>0.3227</v>
+        <v>0.3083</v>
       </c>
       <c r="M42" t="n">
-        <v>0.1388</v>
+        <v>0.1583</v>
       </c>
       <c r="N42" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="O42" t="n">
+        <v>29</v>
+      </c>
+      <c r="P42" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>27</v>
+      </c>
+      <c r="R42" t="n">
         <v>31</v>
       </c>
-      <c r="P42" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>28</v>
-      </c>
-      <c r="R42" t="n">
-        <v>27</v>
-      </c>
       <c r="S42" t="n">
+        <v>26</v>
+      </c>
+      <c r="T42" t="n">
         <v>32</v>
       </c>
-      <c r="T42" t="n">
-        <v>31</v>
-      </c>
       <c r="U42" t="n">
-        <v>1643</v>
+        <v>1624.7</v>
       </c>
     </row>
     <row r="43">
@@ -3457,31 +3469,31 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G43" t="n">
-        <v>1869.8</v>
+        <v>1875.9</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2419</v>
+        <v>0.1664</v>
       </c>
       <c r="I43" t="n">
-        <v>120.49</v>
+        <v>120.08</v>
       </c>
       <c r="J43" t="n">
-        <v>105.01</v>
+        <v>104.01</v>
       </c>
       <c r="K43" t="n">
-        <v>15.48</v>
+        <v>16.07</v>
       </c>
       <c r="L43" t="n">
-        <v>0.3065</v>
+        <v>0.305</v>
       </c>
       <c r="M43" t="n">
-        <v>0.1487</v>
+        <v>0.1501</v>
       </c>
       <c r="N43" t="n">
-        <v>-7.6</v>
+        <v>-3</v>
       </c>
       <c r="O43" t="n">
         <v>35</v>
@@ -3502,16 +3514,16 @@
         <v>29</v>
       </c>
       <c r="U43" t="n">
-        <v>1599.2</v>
+        <v>1599.4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1155</v>
+        <v>1234</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Clemson</t>
+          <t>Iowa</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3528,61 +3540,61 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G44" t="n">
-        <v>1845.5</v>
+        <v>1831.8</v>
       </c>
       <c r="H44" t="n">
-        <v>3.0058</v>
+        <v>3.3952</v>
       </c>
       <c r="I44" t="n">
-        <v>113.18</v>
+        <v>118.92</v>
       </c>
       <c r="J44" t="n">
-        <v>100.7</v>
+        <v>104.81</v>
       </c>
       <c r="K44" t="n">
-        <v>12.47</v>
+        <v>14.12</v>
       </c>
       <c r="L44" t="n">
-        <v>0.2545</v>
+        <v>0.2886</v>
       </c>
       <c r="M44" t="n">
-        <v>0.1366</v>
+        <v>0.1455</v>
       </c>
       <c r="N44" t="n">
-        <v>1.6</v>
+        <v>-1.2</v>
       </c>
       <c r="O44" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="P44" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q44" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="R44" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="S44" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="T44" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="U44" t="n">
-        <v>1644.4</v>
+        <v>1712.2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1365</v>
+        <v>1416</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>UCF</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3599,61 +3611,61 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G45" t="n">
-        <v>1782.8</v>
+        <v>1828.6</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0374</v>
+        <v>5.8051</v>
       </c>
       <c r="I45" t="n">
-        <v>117.62</v>
+        <v>113</v>
       </c>
       <c r="J45" t="n">
-        <v>104.11</v>
+        <v>110.03</v>
       </c>
       <c r="K45" t="n">
-        <v>13.51</v>
+        <v>2.97</v>
       </c>
       <c r="L45" t="n">
-        <v>0.3504</v>
+        <v>0.3147</v>
       </c>
       <c r="M45" t="n">
-        <v>0.1498</v>
+        <v>0.1543</v>
       </c>
       <c r="N45" t="n">
-        <v>0.8</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="O45" t="n">
+        <v>53</v>
+      </c>
+      <c r="P45" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>57</v>
+      </c>
+      <c r="R45" t="n">
+        <v>46</v>
+      </c>
+      <c r="S45" t="n">
         <v>37</v>
       </c>
-      <c r="P45" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>46</v>
-      </c>
-      <c r="R45" t="n">
-        <v>36</v>
-      </c>
-      <c r="S45" t="n">
-        <v>36</v>
-      </c>
       <c r="T45" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="U45" t="n">
-        <v>1596.2</v>
+        <v>1712.7</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1281</v>
+        <v>1275</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>Miami OH</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3663,68 +3675,68 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>11a</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G46" t="n">
-        <v>1757.5</v>
+        <v>1758.6</v>
       </c>
       <c r="H46" t="n">
-        <v>-1.923</v>
+        <v>9.362500000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>115.19</v>
+        <v>120.74</v>
       </c>
       <c r="J46" t="n">
-        <v>109.25</v>
+        <v>105.88</v>
       </c>
       <c r="K46" t="n">
-        <v>5.95</v>
+        <v>14.87</v>
       </c>
       <c r="L46" t="n">
-        <v>0.3014</v>
+        <v>0.2186</v>
       </c>
       <c r="M46" t="n">
-        <v>0.1701</v>
+        <v>0.1413</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O46" t="n">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="P46" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="Q46" t="n">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="R46" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="S46" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="T46" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="U46" t="n">
-        <v>1651.9</v>
+        <v>1416.9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1433</v>
+        <v>1103</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>VCU</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3734,68 +3746,68 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>11b</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="G47" t="n">
-        <v>1739.9</v>
+        <v>1696.5</v>
       </c>
       <c r="H47" t="n">
-        <v>2.9764</v>
+        <v>1.818</v>
       </c>
       <c r="I47" t="n">
-        <v>118.46</v>
+        <v>122.16</v>
       </c>
       <c r="J47" t="n">
-        <v>103.76</v>
+        <v>104.24</v>
       </c>
       <c r="K47" t="n">
-        <v>14.7</v>
+        <v>17.92</v>
       </c>
       <c r="L47" t="n">
-        <v>0.2979</v>
+        <v>0.2856</v>
       </c>
       <c r="M47" t="n">
-        <v>0.1497</v>
+        <v>0.1521</v>
       </c>
       <c r="N47" t="n">
-        <v>6.2</v>
+        <v>18.2</v>
       </c>
       <c r="O47" t="n">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="P47" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>49</v>
+      </c>
+      <c r="R47" t="n">
         <v>54</v>
       </c>
-      <c r="Q47" t="n">
-        <v>48</v>
-      </c>
-      <c r="R47" t="n">
-        <v>45</v>
-      </c>
       <c r="S47" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="T47" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="U47" t="n">
-        <v>1554.6</v>
+        <v>1474.6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1219</v>
+        <v>1358</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>High Point</t>
+          <t>Sam Houston St</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3805,68 +3817,68 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E48" t="b">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G48" t="n">
-        <v>1625.5</v>
+        <v>1545</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.8564000000000001</v>
+        <v>4.4295</v>
       </c>
       <c r="I48" t="n">
-        <v>121.16</v>
+        <v>112.95</v>
       </c>
       <c r="J48" t="n">
-        <v>100.19</v>
+        <v>106.4</v>
       </c>
       <c r="K48" t="n">
-        <v>20.97</v>
+        <v>6.55</v>
       </c>
       <c r="L48" t="n">
-        <v>0.3061</v>
+        <v>0.3122</v>
       </c>
       <c r="M48" t="n">
-        <v>0.1276</v>
+        <v>0.1587</v>
       </c>
       <c r="N48" t="n">
-        <v>9.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="O48" t="n">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="P48" t="n">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="Q48" t="n">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="R48" t="n">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="S48" t="n">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="T48" t="n">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="U48" t="n">
-        <v>1382.5</v>
+        <v>1499.6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1430</v>
+        <v>1407</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Utah Valley</t>
+          <t>Troy</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3876,68 +3888,68 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E49" t="b">
         <v>0</v>
       </c>
       <c r="F49" t="n">
+        <v>126</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1601</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1.1284</v>
+      </c>
+      <c r="I49" t="n">
+        <v>112.28</v>
+      </c>
+      <c r="J49" t="n">
+        <v>106.19</v>
+      </c>
+      <c r="K49" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="N49" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="O49" t="n">
+        <v>153</v>
+      </c>
+      <c r="P49" t="n">
+        <v>130</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>137</v>
+      </c>
+      <c r="R49" t="n">
+        <v>137</v>
+      </c>
+      <c r="S49" t="n">
         <v>124</v>
       </c>
-      <c r="G49" t="n">
-        <v>1637</v>
-      </c>
-      <c r="H49" t="n">
-        <v>3.1528</v>
-      </c>
-      <c r="I49" t="n">
-        <v>111.58</v>
-      </c>
-      <c r="J49" t="n">
-        <v>100.45</v>
-      </c>
-      <c r="K49" t="n">
-        <v>11.12</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0.3056</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0.1962</v>
-      </c>
-      <c r="N49" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O49" t="n">
-        <v>90</v>
-      </c>
-      <c r="P49" t="n">
-        <v>98</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>93</v>
-      </c>
-      <c r="R49" t="n">
-        <v>82</v>
-      </c>
-      <c r="S49" t="n">
-        <v>77</v>
-      </c>
       <c r="T49" t="n">
-        <v>85</v>
+        <v>132</v>
       </c>
       <c r="U49" t="n">
-        <v>1455.5</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1295</v>
+        <v>1420</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>N Dakota St</t>
+          <t>UMBC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3947,68 +3959,68 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E50" t="b">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G50" t="n">
-        <v>1593.8</v>
+        <v>1393.7</v>
       </c>
       <c r="H50" t="n">
-        <v>3.5257</v>
+        <v>1.2859</v>
       </c>
       <c r="I50" t="n">
-        <v>114.28</v>
+        <v>113.44</v>
       </c>
       <c r="J50" t="n">
-        <v>102.18</v>
+        <v>102.32</v>
       </c>
       <c r="K50" t="n">
-        <v>12.1</v>
+        <v>11.13</v>
       </c>
       <c r="L50" t="n">
-        <v>0.3104</v>
+        <v>0.2168</v>
       </c>
       <c r="M50" t="n">
-        <v>0.1506</v>
+        <v>0.1344</v>
       </c>
       <c r="N50" t="n">
-        <v>10.8</v>
+        <v>22.4</v>
       </c>
       <c r="O50" t="n">
-        <v>114</v>
+        <v>198</v>
       </c>
       <c r="P50" t="n">
-        <v>116</v>
+        <v>225</v>
       </c>
       <c r="Q50" t="n">
-        <v>163</v>
+        <v>191</v>
       </c>
       <c r="R50" t="n">
-        <v>115</v>
+        <v>194</v>
       </c>
       <c r="S50" t="n">
-        <v>98</v>
+        <v>197</v>
       </c>
       <c r="T50" t="n">
-        <v>115</v>
+        <v>205</v>
       </c>
       <c r="U50" t="n">
-        <v>1410.6</v>
+        <v>1364.8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1420</v>
+        <v>1224</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>UMBC</t>
+          <t>Howard</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4018,68 +4030,68 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16a</t>
         </is>
       </c>
       <c r="E51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="G51" t="n">
-        <v>1393.7</v>
+        <v>1404.4</v>
       </c>
       <c r="H51" t="n">
-        <v>1.2859</v>
+        <v>3.2279</v>
       </c>
       <c r="I51" t="n">
-        <v>113.44</v>
+        <v>109.08</v>
       </c>
       <c r="J51" t="n">
-        <v>102.32</v>
+        <v>98.81</v>
       </c>
       <c r="K51" t="n">
-        <v>11.13</v>
+        <v>10.27</v>
       </c>
       <c r="L51" t="n">
-        <v>0.2168</v>
+        <v>0.3126</v>
       </c>
       <c r="M51" t="n">
-        <v>0.1344</v>
+        <v>0.1855</v>
       </c>
       <c r="N51" t="n">
-        <v>22.4</v>
+        <v>23.6</v>
       </c>
       <c r="O51" t="n">
+        <v>202</v>
+      </c>
+      <c r="P51" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>270</v>
+      </c>
+      <c r="R51" t="n">
         <v>198</v>
       </c>
-      <c r="P51" t="n">
-        <v>225</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>191</v>
-      </c>
-      <c r="R51" t="n">
-        <v>194</v>
-      </c>
       <c r="S51" t="n">
-        <v>197</v>
+        <v>232</v>
       </c>
       <c r="T51" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="U51" t="n">
-        <v>1364.8</v>
+        <v>1380.6</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Howard</t>
+          <t>Idaho</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4089,139 +4101,139 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>16a</t>
+          <t>16b</t>
         </is>
       </c>
       <c r="E52" t="b">
         <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="G52" t="n">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="H52" t="n">
-        <v>3.2279</v>
+        <v>-0.3498</v>
       </c>
       <c r="I52" t="n">
-        <v>109.08</v>
+        <v>110.28</v>
       </c>
       <c r="J52" t="n">
-        <v>98.81</v>
+        <v>106.53</v>
       </c>
       <c r="K52" t="n">
-        <v>10.27</v>
+        <v>3.75</v>
       </c>
       <c r="L52" t="n">
-        <v>0.3126</v>
+        <v>0.2693</v>
       </c>
       <c r="M52" t="n">
-        <v>0.1855</v>
+        <v>0.1475</v>
       </c>
       <c r="N52" t="n">
-        <v>23.6</v>
+        <v>11</v>
       </c>
       <c r="O52" t="n">
-        <v>202</v>
+        <v>165</v>
       </c>
       <c r="P52" t="n">
-        <v>250</v>
+        <v>184</v>
       </c>
       <c r="Q52" t="n">
-        <v>270</v>
+        <v>179</v>
       </c>
       <c r="R52" t="n">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="S52" t="n">
-        <v>232</v>
+        <v>184</v>
       </c>
       <c r="T52" t="n">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="U52" t="n">
-        <v>1380.6</v>
+        <v>1415.2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1225</v>
+        <v>1112</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Idaho</t>
+          <t>Arizona</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>W</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>16b</t>
+          <t>01</t>
         </is>
       </c>
       <c r="E53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G53" t="n">
-        <v>1410</v>
+        <v>2256</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.3498</v>
+        <v>7.4143</v>
       </c>
       <c r="I53" t="n">
-        <v>110.28</v>
+        <v>121.01</v>
       </c>
       <c r="J53" t="n">
-        <v>106.53</v>
+        <v>95.61</v>
       </c>
       <c r="K53" t="n">
-        <v>3.75</v>
+        <v>25.4</v>
       </c>
       <c r="L53" t="n">
-        <v>0.2693</v>
+        <v>0.2928</v>
       </c>
       <c r="M53" t="n">
-        <v>0.1475</v>
+        <v>0.1495</v>
       </c>
       <c r="N53" t="n">
-        <v>11</v>
+        <v>15.6</v>
       </c>
       <c r="O53" t="n">
-        <v>165</v>
+        <v>3</v>
       </c>
       <c r="P53" t="n">
-        <v>184</v>
+        <v>2</v>
       </c>
       <c r="Q53" t="n">
-        <v>179</v>
+        <v>3</v>
       </c>
       <c r="R53" t="n">
-        <v>180</v>
+        <v>3</v>
       </c>
       <c r="S53" t="n">
-        <v>184</v>
+        <v>2</v>
       </c>
       <c r="T53" t="n">
-        <v>161</v>
+        <v>3</v>
       </c>
       <c r="U53" t="n">
-        <v>1415.2</v>
+        <v>1747.3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1112</v>
+        <v>1277</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>Michigan St</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4231,68 +4243,68 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="E54" t="b">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G54" t="n">
-        <v>2253.6</v>
+        <v>2049.8</v>
       </c>
       <c r="H54" t="n">
-        <v>7.7769</v>
+        <v>0.2376</v>
       </c>
       <c r="I54" t="n">
-        <v>121.09</v>
+        <v>117.05</v>
       </c>
       <c r="J54" t="n">
-        <v>96.09999999999999</v>
+        <v>100.92</v>
       </c>
       <c r="K54" t="n">
-        <v>24.99</v>
+        <v>16.13</v>
       </c>
       <c r="L54" t="n">
-        <v>0.291</v>
+        <v>0.2993</v>
       </c>
       <c r="M54" t="n">
-        <v>0.1505</v>
+        <v>0.1615</v>
       </c>
       <c r="N54" t="n">
-        <v>12.6</v>
+        <v>3</v>
       </c>
       <c r="O54" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="P54" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Q54" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="R54" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="S54" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T54" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="U54" t="n">
-        <v>1742.6</v>
+        <v>1729.6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1228</v>
+        <v>1211</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>Gonzaga</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4302,68 +4314,68 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="E55" t="b">
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G55" t="n">
-        <v>2003.3</v>
+        <v>2068.3</v>
       </c>
       <c r="H55" t="n">
-        <v>8.2525</v>
+        <v>5.8188</v>
       </c>
       <c r="I55" t="n">
-        <v>125.48</v>
+        <v>120.75</v>
       </c>
       <c r="J55" t="n">
-        <v>103.07</v>
+        <v>93.89</v>
       </c>
       <c r="K55" t="n">
-        <v>22.41</v>
+        <v>26.86</v>
       </c>
       <c r="L55" t="n">
-        <v>0.3238</v>
+        <v>0.2992</v>
       </c>
       <c r="M55" t="n">
-        <v>0.1295</v>
+        <v>0.1335</v>
       </c>
       <c r="N55" t="n">
-        <v>10.6</v>
+        <v>11.8</v>
       </c>
       <c r="O55" t="n">
+        <v>10</v>
+      </c>
+      <c r="P55" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>15</v>
+      </c>
+      <c r="R55" t="n">
+        <v>11</v>
+      </c>
+      <c r="S55" t="n">
         <v>5</v>
       </c>
-      <c r="P55" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q55" t="n">
+      <c r="T55" t="n">
         <v>5</v>
       </c>
-      <c r="R55" t="n">
-        <v>7</v>
-      </c>
-      <c r="S55" t="n">
-        <v>12</v>
-      </c>
-      <c r="T55" t="n">
-        <v>6</v>
-      </c>
       <c r="U55" t="n">
-        <v>1709.5</v>
+        <v>1601.3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1211</v>
+        <v>1438</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Gonzaga</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4373,68 +4385,68 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="E56" t="b">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G56" t="n">
-        <v>2068.3</v>
+        <v>1963.2</v>
       </c>
       <c r="H56" t="n">
-        <v>5.8188</v>
+        <v>13.0176</v>
       </c>
       <c r="I56" t="n">
-        <v>120.75</v>
+        <v>118.86</v>
       </c>
       <c r="J56" t="n">
-        <v>93.89</v>
+        <v>100.31</v>
       </c>
       <c r="K56" t="n">
-        <v>26.86</v>
+        <v>18.55</v>
       </c>
       <c r="L56" t="n">
-        <v>0.2992</v>
+        <v>0.3146</v>
       </c>
       <c r="M56" t="n">
-        <v>0.1335</v>
+        <v>0.1527</v>
       </c>
       <c r="N56" t="n">
-        <v>11.8</v>
+        <v>3.8</v>
       </c>
       <c r="O56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="P56" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="Q56" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="R56" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T56" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="U56" t="n">
-        <v>1601.3</v>
+        <v>1642.5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1438</v>
+        <v>1435</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>Vanderbilt</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4444,7 +4456,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>05</t>
         </is>
       </c>
       <c r="E57" t="b">
@@ -4454,58 +4466,58 @@
         <v>124</v>
       </c>
       <c r="G57" t="n">
-        <v>1956.5</v>
+        <v>1935.7</v>
       </c>
       <c r="H57" t="n">
-        <v>13.4946</v>
+        <v>2.1989</v>
       </c>
       <c r="I57" t="n">
-        <v>118.84</v>
+        <v>121.8</v>
       </c>
       <c r="J57" t="n">
-        <v>100.06</v>
+        <v>105.67</v>
       </c>
       <c r="K57" t="n">
-        <v>18.77</v>
+        <v>16.12</v>
       </c>
       <c r="L57" t="n">
-        <v>0.3168</v>
+        <v>0.2802</v>
       </c>
       <c r="M57" t="n">
-        <v>0.1532</v>
+        <v>0.1278</v>
       </c>
       <c r="N57" t="n">
-        <v>3</v>
+        <v>-0.6</v>
       </c>
       <c r="O57" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="P57" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q57" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="R57" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="S57" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="T57" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="U57" t="n">
-        <v>1639.2</v>
+        <v>1694.9</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1116</v>
+        <v>1140</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>BYU</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4515,68 +4527,68 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>06</t>
         </is>
       </c>
       <c r="E58" t="b">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G58" t="n">
-        <v>1950</v>
+        <v>1926.2</v>
       </c>
       <c r="H58" t="n">
-        <v>5.5428</v>
+        <v>0.632</v>
       </c>
       <c r="I58" t="n">
-        <v>122.85</v>
+        <v>117.67</v>
       </c>
       <c r="J58" t="n">
-        <v>108.88</v>
+        <v>106.1</v>
       </c>
       <c r="K58" t="n">
-        <v>13.96</v>
+        <v>11.57</v>
       </c>
       <c r="L58" t="n">
-        <v>0.3009</v>
+        <v>0.3038</v>
       </c>
       <c r="M58" t="n">
-        <v>0.1205</v>
+        <v>0.1534</v>
       </c>
       <c r="N58" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="O58" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="P58" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="Q58" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="R58" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="S58" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="T58" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="U58" t="n">
-        <v>1728.7</v>
+        <v>1733.2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1458</v>
+        <v>1437</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Villanova</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4586,68 +4598,68 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>07</t>
         </is>
       </c>
       <c r="E59" t="b">
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G59" t="n">
-        <v>1859.5</v>
+        <v>1806.3</v>
       </c>
       <c r="H59" t="n">
-        <v>1.6302</v>
+        <v>5.8793</v>
       </c>
       <c r="I59" t="n">
-        <v>119.64</v>
+        <v>114.59</v>
       </c>
       <c r="J59" t="n">
-        <v>108.42</v>
+        <v>104.94</v>
       </c>
       <c r="K59" t="n">
-        <v>11.21</v>
+        <v>9.66</v>
       </c>
       <c r="L59" t="n">
-        <v>0.276</v>
+        <v>0.313</v>
       </c>
       <c r="M59" t="n">
-        <v>0.1244</v>
+        <v>0.1447</v>
       </c>
       <c r="N59" t="n">
-        <v>10.6</v>
+        <v>-1</v>
       </c>
       <c r="O59" t="n">
+        <v>32</v>
+      </c>
+      <c r="P59" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>35</v>
+      </c>
+      <c r="R59" t="n">
+        <v>26</v>
+      </c>
+      <c r="S59" t="n">
         <v>23</v>
       </c>
-      <c r="P59" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>23</v>
-      </c>
-      <c r="R59" t="n">
-        <v>25</v>
-      </c>
-      <c r="S59" t="n">
-        <v>29</v>
-      </c>
       <c r="T59" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="U59" t="n">
-        <v>1701.3</v>
+        <v>1641.5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1246</v>
+        <v>1417</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>UCLA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4657,68 +4669,68 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>08</t>
         </is>
       </c>
       <c r="E60" t="b">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G60" t="n">
-        <v>1887.4</v>
+        <v>1863</v>
       </c>
       <c r="H60" t="n">
-        <v>5.1867</v>
+        <v>2.4395</v>
       </c>
       <c r="I60" t="n">
-        <v>117.12</v>
+        <v>116.91</v>
       </c>
       <c r="J60" t="n">
-        <v>106.56</v>
+        <v>106.2</v>
       </c>
       <c r="K60" t="n">
-        <v>10.57</v>
+        <v>10.71</v>
       </c>
       <c r="L60" t="n">
-        <v>0.3122</v>
+        <v>0.2986</v>
       </c>
       <c r="M60" t="n">
-        <v>0.1426</v>
+        <v>0.1298</v>
       </c>
       <c r="N60" t="n">
-        <v>2</v>
+        <v>13.6</v>
       </c>
       <c r="O60" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P60" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q60" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="R60" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="S60" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="T60" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="U60" t="n">
-        <v>1721.6</v>
+        <v>1683.8</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1417</v>
+        <v>1401</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>UCLA</t>
+          <t>Texas A&amp;M</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4728,68 +4740,68 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>09</t>
         </is>
       </c>
       <c r="E61" t="b">
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G61" t="n">
-        <v>1859.1</v>
+        <v>1824</v>
       </c>
       <c r="H61" t="n">
-        <v>2.2498</v>
+        <v>4.3608</v>
       </c>
       <c r="I61" t="n">
-        <v>117.64</v>
+        <v>117.14</v>
       </c>
       <c r="J61" t="n">
-        <v>107.04</v>
+        <v>107.43</v>
       </c>
       <c r="K61" t="n">
-        <v>10.59</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L61" t="n">
-        <v>0.2985</v>
+        <v>0.3098</v>
       </c>
       <c r="M61" t="n">
-        <v>0.1288</v>
+        <v>0.1389</v>
       </c>
       <c r="N61" t="n">
-        <v>11.2</v>
+        <v>-5.4</v>
       </c>
       <c r="O61" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="P61" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q61" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="R61" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="S61" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="T61" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="U61" t="n">
-        <v>1689.3</v>
+        <v>1653.7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1401</v>
+        <v>1301</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Texas A&amp;M</t>
+          <t>NC State</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4799,68 +4811,68 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E62" t="b">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G62" t="n">
-        <v>1843.5</v>
+        <v>1734</v>
       </c>
       <c r="H62" t="n">
-        <v>4.536</v>
+        <v>6.962</v>
       </c>
       <c r="I62" t="n">
-        <v>117.79</v>
+        <v>119.36</v>
       </c>
       <c r="J62" t="n">
-        <v>106.34</v>
+        <v>109.32</v>
       </c>
       <c r="K62" t="n">
-        <v>11.45</v>
+        <v>10.04</v>
       </c>
       <c r="L62" t="n">
-        <v>0.3067</v>
+        <v>0.2802</v>
       </c>
       <c r="M62" t="n">
-        <v>0.1399</v>
+        <v>0.1288</v>
       </c>
       <c r="N62" t="n">
-        <v>-0.6</v>
+        <v>-6.6</v>
       </c>
       <c r="O62" t="n">
+        <v>36</v>
+      </c>
+      <c r="P62" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q62" t="n">
         <v>34</v>
       </c>
-      <c r="P62" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>33</v>
-      </c>
       <c r="R62" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S62" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T62" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="U62" t="n">
-        <v>1651.1</v>
+        <v>1681.7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1387</v>
+        <v>1374</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>St Louis</t>
+          <t>SMU</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4870,59 +4882,59 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11a</t>
         </is>
       </c>
       <c r="E63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G63" t="n">
-        <v>1807.8</v>
+        <v>1733.9</v>
       </c>
       <c r="H63" t="n">
-        <v>9.839</v>
+        <v>0.2411</v>
       </c>
       <c r="I63" t="n">
-        <v>120.36</v>
+        <v>117.96</v>
       </c>
       <c r="J63" t="n">
-        <v>98.52</v>
+        <v>109.76</v>
       </c>
       <c r="K63" t="n">
-        <v>21.84</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>0.2436</v>
+        <v>0.3098</v>
       </c>
       <c r="M63" t="n">
-        <v>0.1686</v>
+        <v>0.1542</v>
       </c>
       <c r="N63" t="n">
-        <v>-0.4</v>
+        <v>-5.6</v>
       </c>
       <c r="O63" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="P63" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Q63" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="R63" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="S63" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="T63" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="U63" t="n">
-        <v>1512.1</v>
+        <v>1649.8</v>
       </c>
     </row>
     <row r="64">
@@ -4941,11 +4953,11 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>11b</t>
         </is>
       </c>
       <c r="E64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>128</v>
@@ -4998,11 +5010,11 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1463</v>
+        <v>1219</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Yale</t>
+          <t>High Point</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5019,61 +5031,61 @@
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G65" t="n">
-        <v>1720.2</v>
+        <v>1625.5</v>
       </c>
       <c r="H65" t="n">
-        <v>1.1161</v>
+        <v>-0.8564000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>120.93</v>
+        <v>121.16</v>
       </c>
       <c r="J65" t="n">
-        <v>107.17</v>
+        <v>100.19</v>
       </c>
       <c r="K65" t="n">
-        <v>13.77</v>
+        <v>20.97</v>
       </c>
       <c r="L65" t="n">
-        <v>0.2847</v>
+        <v>0.3061</v>
       </c>
       <c r="M65" t="n">
-        <v>0.1362</v>
+        <v>0.1276</v>
       </c>
       <c r="N65" t="n">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O65" t="n">
+        <v>93</v>
+      </c>
+      <c r="P65" t="n">
+        <v>93</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>95</v>
+      </c>
+      <c r="R65" t="n">
+        <v>84</v>
+      </c>
+      <c r="S65" t="n">
         <v>78</v>
       </c>
-      <c r="P65" t="n">
-        <v>89</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>96</v>
-      </c>
-      <c r="R65" t="n">
-        <v>72</v>
-      </c>
-      <c r="S65" t="n">
-        <v>62</v>
-      </c>
       <c r="T65" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="U65" t="n">
-        <v>1457.4</v>
+        <v>1382.5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1270</v>
+        <v>1220</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>McNeese St</t>
+          <t>Hofstra</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5090,52 +5102,52 @@
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G66" t="n">
-        <v>1726.8</v>
+        <v>1586.2</v>
       </c>
       <c r="H66" t="n">
-        <v>2.6895</v>
+        <v>3.3583</v>
       </c>
       <c r="I66" t="n">
-        <v>115.07</v>
+        <v>113.56</v>
       </c>
       <c r="J66" t="n">
-        <v>100.01</v>
+        <v>102.69</v>
       </c>
       <c r="K66" t="n">
-        <v>15.06</v>
+        <v>10.87</v>
       </c>
       <c r="L66" t="n">
-        <v>0.3483</v>
+        <v>0.3081</v>
       </c>
       <c r="M66" t="n">
-        <v>0.139</v>
+        <v>0.1527</v>
       </c>
       <c r="N66" t="n">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="O66" t="n">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="P66" t="n">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="Q66" t="n">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="R66" t="n">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="S66" t="n">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="T66" t="n">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="U66" t="n">
-        <v>1428.4</v>
+        <v>1482.3</v>
       </c>
     </row>
     <row r="67">
@@ -5211,11 +5223,11 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1398</v>
+        <v>1474</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tennessee St</t>
+          <t>Queens NC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5232,52 +5244,52 @@
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G68" t="n">
-        <v>1466.9</v>
+        <v>1427.4</v>
       </c>
       <c r="H68" t="n">
-        <v>3.3618</v>
+        <v>1.0039</v>
       </c>
       <c r="I68" t="n">
-        <v>109.9</v>
+        <v>119.17</v>
       </c>
       <c r="J68" t="n">
-        <v>103.28</v>
+        <v>116.56</v>
       </c>
       <c r="K68" t="n">
-        <v>6.62</v>
+        <v>2.61</v>
       </c>
       <c r="L68" t="n">
-        <v>0.328</v>
+        <v>0.2859</v>
       </c>
       <c r="M68" t="n">
-        <v>0.1589</v>
+        <v>0.1441</v>
       </c>
       <c r="N68" t="n">
-        <v>19.8</v>
+        <v>6.4</v>
       </c>
       <c r="O68" t="n">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="P68" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q68" t="n">
+        <v>181</v>
+      </c>
+      <c r="R68" t="n">
+        <v>177</v>
+      </c>
+      <c r="S68" t="n">
+        <v>171</v>
+      </c>
+      <c r="T68" t="n">
         <v>187</v>
       </c>
-      <c r="R68" t="n">
-        <v>168</v>
-      </c>
-      <c r="S68" t="n">
-        <v>153</v>
-      </c>
-      <c r="T68" t="n">
-        <v>172</v>
-      </c>
       <c r="U68" t="n">
-        <v>1407.8</v>
+        <v>1430.9</v>
       </c>
     </row>
     <row r="69">

--- a/team_stats_2026.xlsx
+++ b/team_stats_2026.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,107 +417,107 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Is_FirstFour</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>

--- a/team_stats_2026.xlsx
+++ b/team_stats_2026.xlsx
@@ -546,31 +546,31 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G2" t="n">
-        <v>2185.1</v>
+        <v>2189.2</v>
       </c>
       <c r="H2" t="n">
-        <v>3.7089</v>
+        <v>3.7126</v>
       </c>
       <c r="I2" t="n">
-        <v>123.04</v>
+        <v>122.89</v>
       </c>
       <c r="J2" t="n">
-        <v>94.12</v>
+        <v>94.03</v>
       </c>
       <c r="K2" t="n">
-        <v>28.93</v>
+        <v>28.87</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2948</v>
+        <v>0.2894</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1547</v>
+        <v>0.1548</v>
       </c>
       <c r="N2" t="n">
-        <v>23</v>
+        <v>16.6</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -591,7 +591,7 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>1695.7</v>
+        <v>1703.5</v>
       </c>
     </row>
     <row r="3">
@@ -617,31 +617,31 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G3" t="n">
-        <v>2045.9</v>
+        <v>2039</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4203</v>
+        <v>2.2111</v>
       </c>
       <c r="I3" t="n">
-        <v>118.77</v>
+        <v>118.9</v>
       </c>
       <c r="J3" t="n">
-        <v>94.51000000000001</v>
+        <v>95.73</v>
       </c>
       <c r="K3" t="n">
-        <v>24.26</v>
+        <v>23.17</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3164</v>
+        <v>0.3217</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1462</v>
+        <v>0.1469</v>
       </c>
       <c r="N3" t="n">
-        <v>13.4</v>
+        <v>14.8</v>
       </c>
       <c r="O3" t="n">
         <v>7</v>
@@ -662,7 +662,7 @@
         <v>8</v>
       </c>
       <c r="U3" t="n">
-        <v>1700.1</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="4">
@@ -688,31 +688,31 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="G4" t="n">
-        <v>2003.3</v>
+        <v>1982.7</v>
       </c>
       <c r="H4" t="n">
-        <v>8.2525</v>
+        <v>7.8712</v>
       </c>
       <c r="I4" t="n">
-        <v>125.48</v>
+        <v>125.11</v>
       </c>
       <c r="J4" t="n">
-        <v>103.07</v>
+        <v>103.66</v>
       </c>
       <c r="K4" t="n">
-        <v>22.41</v>
+        <v>21.45</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3238</v>
+        <v>0.3222</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1295</v>
+        <v>0.1281</v>
       </c>
       <c r="N4" t="n">
-        <v>10.6</v>
+        <v>2.8</v>
       </c>
       <c r="O4" t="n">
         <v>5</v>
@@ -733,16 +733,16 @@
         <v>6</v>
       </c>
       <c r="U4" t="n">
-        <v>1709.5</v>
+        <v>1717.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1345</v>
+        <v>1435</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Purdue</t>
+          <t>Vanderbilt</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -759,61 +759,61 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G5" t="n">
-        <v>1959</v>
+        <v>1949.6</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.051</v>
+        <v>1.887</v>
       </c>
       <c r="I5" t="n">
-        <v>124.95</v>
+        <v>121.84</v>
       </c>
       <c r="J5" t="n">
-        <v>107.45</v>
+        <v>105.79</v>
       </c>
       <c r="K5" t="n">
-        <v>17.5</v>
+        <v>16.05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3095</v>
+        <v>0.2851</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1344</v>
+        <v>0.1258</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="O5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="P5" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Q5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="R5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="T5" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="U5" t="n">
-        <v>1740.1</v>
+        <v>1701.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1116</v>
+        <v>1458</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -830,52 +830,52 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="G6" t="n">
-        <v>1950</v>
+        <v>1886.8</v>
       </c>
       <c r="H6" t="n">
-        <v>5.5428</v>
+        <v>2.1287</v>
       </c>
       <c r="I6" t="n">
-        <v>122.85</v>
+        <v>119.67</v>
       </c>
       <c r="J6" t="n">
-        <v>108.88</v>
+        <v>108.89</v>
       </c>
       <c r="K6" t="n">
-        <v>13.96</v>
+        <v>10.78</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3009</v>
+        <v>0.2787</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1205</v>
+        <v>0.1222</v>
       </c>
       <c r="N6" t="n">
-        <v>2.6</v>
+        <v>12</v>
       </c>
       <c r="O6" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="P6" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="Q6" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="R6" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="S6" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="T6" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="U6" t="n">
-        <v>1728.7</v>
+        <v>1709.1</v>
       </c>
     </row>
     <row r="7">
@@ -972,31 +972,31 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G8" t="n">
-        <v>1897</v>
+        <v>1886.9</v>
       </c>
       <c r="H8" t="n">
-        <v>4.9403</v>
+        <v>4.7611</v>
       </c>
       <c r="I8" t="n">
-        <v>116.84</v>
+        <v>115.76</v>
       </c>
       <c r="J8" t="n">
-        <v>106.32</v>
+        <v>106.05</v>
       </c>
       <c r="K8" t="n">
-        <v>10.52</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>0.312</v>
+        <v>0.3106</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1463</v>
+        <v>0.1465</v>
       </c>
       <c r="N8" t="n">
-        <v>1.4</v>
+        <v>-3</v>
       </c>
       <c r="O8" t="n">
         <v>27</v>
@@ -1017,7 +1017,7 @@
         <v>28</v>
       </c>
       <c r="U8" t="n">
-        <v>1723.9</v>
+        <v>1734.8</v>
       </c>
     </row>
     <row r="9">
@@ -1327,31 +1327,31 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="G13" t="n">
-        <v>1739.9</v>
+        <v>1743.5</v>
       </c>
       <c r="H13" t="n">
-        <v>2.9764</v>
+        <v>3.091</v>
       </c>
       <c r="I13" t="n">
-        <v>118.46</v>
+        <v>118.25</v>
       </c>
       <c r="J13" t="n">
-        <v>103.76</v>
+        <v>103.78</v>
       </c>
       <c r="K13" t="n">
-        <v>14.7</v>
+        <v>14.46</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2979</v>
+        <v>0.2985</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1497</v>
+        <v>0.1511</v>
       </c>
       <c r="N13" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="O13" t="n">
         <v>45</v>
@@ -1372,16 +1372,16 @@
         <v>44</v>
       </c>
       <c r="U13" t="n">
-        <v>1554.6</v>
+        <v>1550.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1463</v>
+        <v>1219</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Yale</t>
+          <t>High Point</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1398,61 +1398,61 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G14" t="n">
-        <v>1720.2</v>
+        <v>1625.5</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1161</v>
+        <v>-0.8564000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>120.93</v>
+        <v>121.16</v>
       </c>
       <c r="J14" t="n">
-        <v>107.17</v>
+        <v>100.19</v>
       </c>
       <c r="K14" t="n">
-        <v>13.77</v>
+        <v>20.97</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2847</v>
+        <v>0.3061</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1362</v>
+        <v>0.1276</v>
       </c>
       <c r="N14" t="n">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O14" t="n">
+        <v>93</v>
+      </c>
+      <c r="P14" t="n">
+        <v>93</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>95</v>
+      </c>
+      <c r="R14" t="n">
+        <v>84</v>
+      </c>
+      <c r="S14" t="n">
         <v>78</v>
       </c>
-      <c r="P14" t="n">
-        <v>89</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>96</v>
-      </c>
-      <c r="R14" t="n">
-        <v>72</v>
-      </c>
-      <c r="S14" t="n">
-        <v>62</v>
-      </c>
       <c r="T14" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="U14" t="n">
-        <v>1457.4</v>
+        <v>1382.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1320</v>
+        <v>1295</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Northern Iowa</t>
+          <t>N Dakota St</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1472,58 +1472,58 @@
         <v>125</v>
       </c>
       <c r="G15" t="n">
-        <v>1573.9</v>
+        <v>1593.8</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.696</v>
+        <v>3.5257</v>
       </c>
       <c r="I15" t="n">
-        <v>108.74</v>
+        <v>114.28</v>
       </c>
       <c r="J15" t="n">
-        <v>97.5</v>
+        <v>102.18</v>
       </c>
       <c r="K15" t="n">
-        <v>11.25</v>
+        <v>12.1</v>
       </c>
       <c r="L15" t="n">
-        <v>0.225</v>
+        <v>0.3104</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1354</v>
+        <v>0.1506</v>
       </c>
       <c r="N15" t="n">
-        <v>14.4</v>
+        <v>10.8</v>
       </c>
       <c r="O15" t="n">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="P15" t="n">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="Q15" t="n">
-        <v>72</v>
+        <v>163</v>
       </c>
       <c r="R15" t="n">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="S15" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="T15" t="n">
-        <v>72</v>
+        <v>115</v>
       </c>
       <c r="U15" t="n">
-        <v>1515.8</v>
+        <v>1410.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1295</v>
+        <v>1460</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>N Dakota St</t>
+          <t>Wright St</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1540,61 +1540,61 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
+        <v>127</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1470.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.7419</v>
+      </c>
+      <c r="I16" t="n">
+        <v>115.44</v>
+      </c>
+      <c r="J16" t="n">
+        <v>108.91</v>
+      </c>
+      <c r="K16" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.2971</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.1569</v>
+      </c>
+      <c r="N16" t="n">
+        <v>10</v>
+      </c>
+      <c r="O16" t="n">
+        <v>144</v>
+      </c>
+      <c r="P16" t="n">
+        <v>145</v>
+      </c>
+      <c r="Q16" t="n">
         <v>125</v>
       </c>
-      <c r="G16" t="n">
-        <v>1593.8</v>
-      </c>
-      <c r="H16" t="n">
-        <v>3.5257</v>
-      </c>
-      <c r="I16" t="n">
-        <v>114.28</v>
-      </c>
-      <c r="J16" t="n">
-        <v>102.18</v>
-      </c>
-      <c r="K16" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.3104</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.1506</v>
-      </c>
-      <c r="N16" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="O16" t="n">
-        <v>114</v>
-      </c>
-      <c r="P16" t="n">
-        <v>116</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>163</v>
-      </c>
       <c r="R16" t="n">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="S16" t="n">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="T16" t="n">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="U16" t="n">
-        <v>1410.6</v>
+        <v>1431.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1398</v>
+        <v>1202</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tennessee St</t>
+          <t>Furman</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1611,61 +1611,61 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G17" t="n">
-        <v>1466.9</v>
+        <v>1542.9</v>
       </c>
       <c r="H17" t="n">
-        <v>3.3618</v>
+        <v>0.8197</v>
       </c>
       <c r="I17" t="n">
-        <v>109.9</v>
+        <v>112.01</v>
       </c>
       <c r="J17" t="n">
-        <v>103.28</v>
+        <v>107.28</v>
       </c>
       <c r="K17" t="n">
-        <v>6.62</v>
+        <v>4.73</v>
       </c>
       <c r="L17" t="n">
-        <v>0.328</v>
+        <v>0.2562</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1589</v>
+        <v>0.171</v>
       </c>
       <c r="N17" t="n">
-        <v>19.8</v>
+        <v>5.6</v>
       </c>
       <c r="O17" t="n">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="P17" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="Q17" t="n">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="R17" t="n">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="S17" t="n">
-        <v>153</v>
+        <v>192</v>
       </c>
       <c r="T17" t="n">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="U17" t="n">
-        <v>1407.8</v>
+        <v>1422.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1373</v>
+        <v>1420</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Siena</t>
+          <t>UMBC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1685,49 +1685,49 @@
         <v>127</v>
       </c>
       <c r="G18" t="n">
-        <v>1478</v>
+        <v>1393.7</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9489</v>
+        <v>1.2859</v>
       </c>
       <c r="I18" t="n">
-        <v>109.73</v>
+        <v>113.44</v>
       </c>
       <c r="J18" t="n">
-        <v>101.77</v>
+        <v>102.32</v>
       </c>
       <c r="K18" t="n">
-        <v>7.95</v>
+        <v>11.13</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2799</v>
+        <v>0.2168</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1508</v>
+        <v>0.1344</v>
       </c>
       <c r="N18" t="n">
-        <v>6.2</v>
+        <v>22.4</v>
       </c>
       <c r="O18" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="P18" t="n">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="Q18" t="n">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="R18" t="n">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="S18" t="n">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="T18" t="n">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="U18" t="n">
-        <v>1430.3</v>
+        <v>1364.8</v>
       </c>
     </row>
     <row r="19">
@@ -1753,31 +1753,31 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="G19" t="n">
-        <v>2014.8</v>
+        <v>2024.9</v>
       </c>
       <c r="H19" t="n">
-        <v>2.8716</v>
+        <v>3.1754</v>
       </c>
       <c r="I19" t="n">
-        <v>120.95</v>
+        <v>120.02</v>
       </c>
       <c r="J19" t="n">
-        <v>99.02</v>
+        <v>98.41</v>
       </c>
       <c r="K19" t="n">
-        <v>21.92</v>
+        <v>21.61</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3329</v>
+        <v>0.3339</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1552</v>
+        <v>0.1592</v>
       </c>
       <c r="N19" t="n">
-        <v>21.4</v>
+        <v>19.2</v>
       </c>
       <c r="O19" t="n">
         <v>4</v>
@@ -1798,7 +1798,7 @@
         <v>4</v>
       </c>
       <c r="U19" t="n">
-        <v>1709.6</v>
+        <v>1715.4</v>
       </c>
     </row>
     <row r="20">
@@ -1824,31 +1824,31 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G20" t="n">
-        <v>2111.2</v>
+        <v>2120.9</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4261</v>
+        <v>1.2885</v>
       </c>
       <c r="I20" t="n">
-        <v>117.41</v>
+        <v>117.48</v>
       </c>
       <c r="J20" t="n">
-        <v>95.28</v>
+        <v>94.63</v>
       </c>
       <c r="K20" t="n">
-        <v>22.14</v>
+        <v>22.86</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3403</v>
+        <v>0.3358</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1244</v>
+        <v>0.1237</v>
       </c>
       <c r="N20" t="n">
-        <v>10.8</v>
+        <v>17.8</v>
       </c>
       <c r="O20" t="n">
         <v>6</v>
@@ -1869,16 +1869,16 @@
         <v>7</v>
       </c>
       <c r="U20" t="n">
-        <v>1716.1</v>
+        <v>1724.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1304</v>
+        <v>1345</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nebraska</t>
+          <t>Purdue</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1895,61 +1895,61 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="G21" t="n">
-        <v>1999.6</v>
+        <v>1975.7</v>
       </c>
       <c r="H21" t="n">
-        <v>10.6735</v>
+        <v>-0.3998</v>
       </c>
       <c r="I21" t="n">
-        <v>115.4</v>
+        <v>124.77</v>
       </c>
       <c r="J21" t="n">
-        <v>97.95</v>
+        <v>106.95</v>
       </c>
       <c r="K21" t="n">
-        <v>17.45</v>
+        <v>17.82</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2379</v>
+        <v>0.3094</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1402</v>
+        <v>0.1359</v>
       </c>
       <c r="N21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O21" t="n">
         <v>8</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>12</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
+        <v>8</v>
+      </c>
+      <c r="R21" t="n">
+        <v>8</v>
+      </c>
+      <c r="S21" t="n">
         <v>13</v>
       </c>
-      <c r="Q21" t="n">
-        <v>16</v>
-      </c>
-      <c r="R21" t="n">
-        <v>13</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>10</v>
       </c>
-      <c r="T21" t="n">
-        <v>12</v>
-      </c>
       <c r="U21" t="n">
-        <v>1665.7</v>
+        <v>1751.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1403</v>
+        <v>1438</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Texas Tech</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1966,61 +1966,61 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G22" t="n">
-        <v>2010.7</v>
+        <v>1971</v>
       </c>
       <c r="H22" t="n">
-        <v>9.579599999999999</v>
+        <v>12.5889</v>
       </c>
       <c r="I22" t="n">
-        <v>117.2</v>
+        <v>119.48</v>
       </c>
       <c r="J22" t="n">
-        <v>106.7</v>
+        <v>100.21</v>
       </c>
       <c r="K22" t="n">
-        <v>10.5</v>
+        <v>19.27</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2893</v>
+        <v>0.3151</v>
       </c>
       <c r="M22" t="n">
-        <v>0.155</v>
+        <v>0.153</v>
       </c>
       <c r="N22" t="n">
-        <v>-3</v>
+        <v>2.4</v>
       </c>
       <c r="O22" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="P22" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="Q22" t="n">
+        <v>11</v>
+      </c>
+      <c r="R22" t="n">
         <v>19</v>
       </c>
-      <c r="R22" t="n">
-        <v>15</v>
-      </c>
       <c r="S22" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="T22" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="U22" t="n">
-        <v>1772.3</v>
+        <v>1646.9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1385</v>
+        <v>1403</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>St John's</t>
+          <t>Texas Tech</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2040,58 +2040,58 @@
         <v>129</v>
       </c>
       <c r="G23" t="n">
-        <v>1964.1</v>
+        <v>2010.7</v>
       </c>
       <c r="H23" t="n">
-        <v>5.6344</v>
+        <v>9.579599999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>113.75</v>
+        <v>117.2</v>
       </c>
       <c r="J23" t="n">
-        <v>98.54000000000001</v>
+        <v>106.7</v>
       </c>
       <c r="K23" t="n">
-        <v>15.21</v>
+        <v>10.5</v>
       </c>
       <c r="L23" t="n">
-        <v>0.3255</v>
+        <v>0.2893</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1408</v>
+        <v>0.155</v>
       </c>
       <c r="N23" t="n">
-        <v>4.6</v>
+        <v>-3</v>
       </c>
       <c r="O23" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="P23" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>19</v>
+      </c>
+      <c r="R23" t="n">
         <v>15</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="S23" t="n">
         <v>17</v>
       </c>
-      <c r="R23" t="n">
-        <v>17</v>
-      </c>
-      <c r="S23" t="n">
-        <v>20</v>
-      </c>
       <c r="T23" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="U23" t="n">
-        <v>1676.3</v>
+        <v>1772.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1314</v>
+        <v>1397</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2108,61 +2108,61 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G24" t="n">
-        <v>1899.5</v>
+        <v>1897.1</v>
       </c>
       <c r="H24" t="n">
-        <v>2.2848</v>
+        <v>-1.4465</v>
       </c>
       <c r="I24" t="n">
-        <v>115.28</v>
+        <v>116.86</v>
       </c>
       <c r="J24" t="n">
-        <v>103.72</v>
+        <v>102.57</v>
       </c>
       <c r="K24" t="n">
-        <v>11.56</v>
+        <v>14.29</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2596</v>
+        <v>0.36</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1375</v>
+        <v>0.1643</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4</v>
+        <v>3.2</v>
       </c>
       <c r="O24" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="P24" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>18</v>
+      </c>
+      <c r="R24" t="n">
+        <v>20</v>
+      </c>
+      <c r="S24" t="n">
+        <v>24</v>
+      </c>
+      <c r="T24" t="n">
         <v>21</v>
       </c>
-      <c r="Q24" t="n">
-        <v>24</v>
-      </c>
-      <c r="R24" t="n">
-        <v>24</v>
-      </c>
-      <c r="S24" t="n">
-        <v>18</v>
-      </c>
-      <c r="T24" t="n">
-        <v>23</v>
-      </c>
       <c r="U24" t="n">
-        <v>1677.4</v>
+        <v>1716.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1388</v>
+        <v>1417</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>St Mary's CA</t>
+          <t>UCLA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2179,52 +2179,52 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G25" t="n">
-        <v>1857.8</v>
+        <v>1885.4</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.2818</v>
+        <v>2.6042</v>
       </c>
       <c r="I25" t="n">
-        <v>118.73</v>
+        <v>117.52</v>
       </c>
       <c r="J25" t="n">
-        <v>99.88</v>
+        <v>107.06</v>
       </c>
       <c r="K25" t="n">
-        <v>18.85</v>
+        <v>10.46</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2975</v>
+        <v>0.3052</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1525</v>
+        <v>0.1315</v>
       </c>
       <c r="N25" t="n">
-        <v>8.6</v>
+        <v>10.6</v>
       </c>
       <c r="O25" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="P25" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q25" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="R25" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="S25" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="T25" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="U25" t="n">
-        <v>1596.9</v>
+        <v>1698.9</v>
       </c>
     </row>
     <row r="26">
@@ -2250,31 +2250,31 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G26" t="n">
-        <v>1817</v>
+        <v>1813.9</v>
       </c>
       <c r="H26" t="n">
-        <v>1.7194</v>
+        <v>1.9487</v>
       </c>
       <c r="I26" t="n">
-        <v>118.68</v>
+        <v>118</v>
       </c>
       <c r="J26" t="n">
-        <v>108.16</v>
+        <v>108.07</v>
       </c>
       <c r="K26" t="n">
-        <v>10.52</v>
+        <v>9.93</v>
       </c>
       <c r="L26" t="n">
-        <v>0.2526</v>
+        <v>0.255</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1502</v>
+        <v>0.1503</v>
       </c>
       <c r="N26" t="n">
-        <v>7.8</v>
+        <v>10.4</v>
       </c>
       <c r="O26" t="n">
         <v>26</v>
@@ -2295,16 +2295,16 @@
         <v>30</v>
       </c>
       <c r="U26" t="n">
-        <v>1705.5</v>
+        <v>1722.9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1155</v>
+        <v>1437</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Clemson</t>
+          <t>Villanova</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2324,58 +2324,58 @@
         <v>129</v>
       </c>
       <c r="G27" t="n">
-        <v>1863.6</v>
+        <v>1806.3</v>
       </c>
       <c r="H27" t="n">
-        <v>2.7155</v>
+        <v>5.8793</v>
       </c>
       <c r="I27" t="n">
-        <v>113.29</v>
+        <v>114.59</v>
       </c>
       <c r="J27" t="n">
-        <v>101.28</v>
+        <v>104.94</v>
       </c>
       <c r="K27" t="n">
-        <v>12</v>
+        <v>9.66</v>
       </c>
       <c r="L27" t="n">
-        <v>0.2541</v>
+        <v>0.313</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1378</v>
+        <v>0.1447</v>
       </c>
       <c r="N27" t="n">
-        <v>2.8</v>
+        <v>-1</v>
       </c>
       <c r="O27" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="P27" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="Q27" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="R27" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="S27" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="T27" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="U27" t="n">
-        <v>1655.1</v>
+        <v>1641.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1387</v>
+        <v>1401</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>St Louis</t>
+          <t>Texas A&amp;M</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2392,61 +2392,61 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G28" t="n">
-        <v>1807.8</v>
+        <v>1824</v>
       </c>
       <c r="H28" t="n">
-        <v>9.839</v>
+        <v>4.3608</v>
       </c>
       <c r="I28" t="n">
-        <v>120.36</v>
+        <v>117.14</v>
       </c>
       <c r="J28" t="n">
-        <v>98.52</v>
+        <v>107.43</v>
       </c>
       <c r="K28" t="n">
-        <v>21.84</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>0.2436</v>
+        <v>0.3098</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1686</v>
+        <v>0.1389</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.4</v>
+        <v>-5.4</v>
       </c>
       <c r="O28" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="P28" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="Q28" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="R28" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="S28" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="T28" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="U28" t="n">
-        <v>1512.1</v>
+        <v>1653.7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1378</v>
+        <v>1275</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>South Florida</t>
+          <t>Miami OH</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2463,61 +2463,61 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G29" t="n">
-        <v>1711.8</v>
+        <v>1758.6</v>
       </c>
       <c r="H29" t="n">
-        <v>9.207800000000001</v>
+        <v>9.362500000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>116.06</v>
+        <v>120.74</v>
       </c>
       <c r="J29" t="n">
-        <v>101.73</v>
+        <v>105.88</v>
       </c>
       <c r="K29" t="n">
-        <v>14.32</v>
+        <v>14.87</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3392</v>
+        <v>0.2186</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1453</v>
+        <v>0.1413</v>
       </c>
       <c r="N29" t="n">
-        <v>19.6</v>
+        <v>2.4</v>
       </c>
       <c r="O29" t="n">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="P29" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="Q29" t="n">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="R29" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="S29" t="n">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="T29" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="U29" t="n">
-        <v>1553.3</v>
+        <v>1416.9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1270</v>
+        <v>1463</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>McNeese St</t>
+          <t>Yale</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2534,52 +2534,52 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="G30" t="n">
-        <v>1726.8</v>
+        <v>1720.2</v>
       </c>
       <c r="H30" t="n">
-        <v>2.6895</v>
+        <v>1.1161</v>
       </c>
       <c r="I30" t="n">
-        <v>115.07</v>
+        <v>120.93</v>
       </c>
       <c r="J30" t="n">
-        <v>100.01</v>
+        <v>107.17</v>
       </c>
       <c r="K30" t="n">
-        <v>15.06</v>
+        <v>13.77</v>
       </c>
       <c r="L30" t="n">
-        <v>0.3483</v>
+        <v>0.2847</v>
       </c>
       <c r="M30" t="n">
-        <v>0.139</v>
+        <v>0.1362</v>
       </c>
       <c r="N30" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="O30" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="P30" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="Q30" t="n">
+        <v>96</v>
+      </c>
+      <c r="R30" t="n">
+        <v>72</v>
+      </c>
+      <c r="S30" t="n">
         <v>62</v>
       </c>
-      <c r="R30" t="n">
+      <c r="T30" t="n">
         <v>66</v>
       </c>
-      <c r="S30" t="n">
-        <v>57</v>
-      </c>
-      <c r="T30" t="n">
-        <v>62</v>
-      </c>
       <c r="U30" t="n">
-        <v>1428.4</v>
+        <v>1457.4</v>
       </c>
     </row>
     <row r="31">
@@ -2605,31 +2605,31 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="G31" t="n">
-        <v>1637</v>
+        <v>1641</v>
       </c>
       <c r="H31" t="n">
-        <v>3.1528</v>
+        <v>3.0131</v>
       </c>
       <c r="I31" t="n">
-        <v>111.58</v>
+        <v>111.37</v>
       </c>
       <c r="J31" t="n">
-        <v>100.45</v>
+        <v>100.52</v>
       </c>
       <c r="K31" t="n">
-        <v>11.12</v>
+        <v>10.85</v>
       </c>
       <c r="L31" t="n">
-        <v>0.3056</v>
+        <v>0.304</v>
       </c>
       <c r="M31" t="n">
-        <v>0.1962</v>
+        <v>0.1971</v>
       </c>
       <c r="N31" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="O31" t="n">
         <v>90</v>
@@ -2650,16 +2650,16 @@
         <v>85</v>
       </c>
       <c r="U31" t="n">
-        <v>1455.5</v>
+        <v>1456.2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1460</v>
+        <v>1407</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Wright St</t>
+          <t>Troy</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2676,61 +2676,61 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G32" t="n">
-        <v>1470.5</v>
+        <v>1601</v>
       </c>
       <c r="H32" t="n">
-        <v>2.7419</v>
+        <v>1.1284</v>
       </c>
       <c r="I32" t="n">
-        <v>115.44</v>
+        <v>112.28</v>
       </c>
       <c r="J32" t="n">
-        <v>108.91</v>
+        <v>106.19</v>
       </c>
       <c r="K32" t="n">
-        <v>6.53</v>
+        <v>6.08</v>
       </c>
       <c r="L32" t="n">
-        <v>0.2971</v>
+        <v>0.316</v>
       </c>
       <c r="M32" t="n">
-        <v>0.1569</v>
+        <v>0.1667</v>
       </c>
       <c r="N32" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="O32" t="n">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="P32" t="n">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="Q32" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="R32" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="S32" t="n">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="T32" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="U32" t="n">
-        <v>1431.7</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1202</v>
+        <v>1254</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Furman</t>
+          <t>LIU Brooklyn</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2747,52 +2747,52 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G33" t="n">
-        <v>1542.9</v>
+        <v>1418.2</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8197</v>
+        <v>2.3581</v>
       </c>
       <c r="I33" t="n">
-        <v>112.01</v>
+        <v>109.38</v>
       </c>
       <c r="J33" t="n">
-        <v>107.28</v>
+        <v>104.38</v>
       </c>
       <c r="K33" t="n">
-        <v>4.73</v>
+        <v>5</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2562</v>
+        <v>0.3119</v>
       </c>
       <c r="M33" t="n">
-        <v>0.171</v>
+        <v>0.183</v>
       </c>
       <c r="N33" t="n">
-        <v>5.6</v>
+        <v>10.4</v>
       </c>
       <c r="O33" t="n">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="P33" t="n">
-        <v>170</v>
+        <v>228</v>
       </c>
       <c r="Q33" t="n">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="R33" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="S33" t="n">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="T33" t="n">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="U33" t="n">
-        <v>1422.2</v>
+        <v>1378.8</v>
       </c>
     </row>
     <row r="34">
@@ -2818,31 +2818,31 @@
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G34" t="n">
-        <v>1375.9</v>
+        <v>1377.9</v>
       </c>
       <c r="H34" t="n">
-        <v>-2.3939</v>
+        <v>-2.2287</v>
       </c>
       <c r="I34" t="n">
-        <v>106.4</v>
+        <v>106.09</v>
       </c>
       <c r="J34" t="n">
-        <v>111.97</v>
+        <v>111.35</v>
       </c>
       <c r="K34" t="n">
-        <v>-5.57</v>
+        <v>-5.25</v>
       </c>
       <c r="L34" t="n">
-        <v>0.322</v>
+        <v>0.3165</v>
       </c>
       <c r="M34" t="n">
-        <v>0.159</v>
+        <v>0.1627</v>
       </c>
       <c r="N34" t="n">
-        <v>-0.2</v>
+        <v>2.6</v>
       </c>
       <c r="O34" t="n">
         <v>275</v>
@@ -2863,16 +2863,16 @@
         <v>277</v>
       </c>
       <c r="U34" t="n">
-        <v>1396.5</v>
+        <v>1393.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1250</v>
+        <v>1256</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lehigh</t>
+          <t>Louisiana Tech</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2889,52 +2889,52 @@
         <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G35" t="n">
-        <v>1325.5</v>
+        <v>1515.2</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.465</v>
+        <v>-1.3208</v>
       </c>
       <c r="I35" t="n">
-        <v>105.58</v>
+        <v>104.02</v>
       </c>
       <c r="J35" t="n">
-        <v>108.39</v>
+        <v>103.4</v>
       </c>
       <c r="K35" t="n">
-        <v>-2.8</v>
+        <v>0.62</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2229</v>
+        <v>0.3299</v>
       </c>
       <c r="M35" t="n">
-        <v>0.1707</v>
+        <v>0.1728</v>
       </c>
       <c r="N35" t="n">
-        <v>7.8</v>
+        <v>10.8</v>
       </c>
       <c r="O35" t="n">
-        <v>290</v>
+        <v>208</v>
       </c>
       <c r="P35" t="n">
-        <v>295</v>
+        <v>158</v>
       </c>
       <c r="Q35" t="n">
-        <v>279</v>
+        <v>165</v>
       </c>
       <c r="R35" t="n">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="S35" t="n">
-        <v>268</v>
+        <v>205</v>
       </c>
       <c r="T35" t="n">
-        <v>282</v>
+        <v>213</v>
       </c>
       <c r="U35" t="n">
-        <v>1399</v>
+        <v>1463.6</v>
       </c>
     </row>
     <row r="36">
@@ -2960,31 +2960,31 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="G36" t="n">
-        <v>2189.2</v>
+        <v>2192.4</v>
       </c>
       <c r="H36" t="n">
-        <v>7.2681</v>
+        <v>6.99</v>
       </c>
       <c r="I36" t="n">
-        <v>121.97</v>
+        <v>121.3</v>
       </c>
       <c r="J36" t="n">
-        <v>95.94</v>
+        <v>95.95</v>
       </c>
       <c r="K36" t="n">
-        <v>26.03</v>
+        <v>25.34</v>
       </c>
       <c r="L36" t="n">
-        <v>0.2632</v>
+        <v>0.2601</v>
       </c>
       <c r="M36" t="n">
-        <v>0.1657</v>
+        <v>0.1647</v>
       </c>
       <c r="N36" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
@@ -3005,7 +3005,7 @@
         <v>2</v>
       </c>
       <c r="U36" t="n">
-        <v>1769.7</v>
+        <v>1768.8</v>
       </c>
     </row>
     <row r="37">
@@ -3031,31 +3031,31 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G37" t="n">
-        <v>2066.1</v>
+        <v>2067.9</v>
       </c>
       <c r="H37" t="n">
-        <v>8.2806</v>
+        <v>7.6929</v>
       </c>
       <c r="I37" t="n">
-        <v>117.74</v>
+        <v>117.25</v>
       </c>
       <c r="J37" t="n">
-        <v>97.67</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>20.07</v>
+        <v>20.14</v>
       </c>
       <c r="L37" t="n">
-        <v>0.2928</v>
+        <v>0.2963</v>
       </c>
       <c r="M37" t="n">
-        <v>0.1549</v>
+        <v>0.1567</v>
       </c>
       <c r="N37" t="n">
-        <v>13</v>
+        <v>14.2</v>
       </c>
       <c r="O37" t="n">
         <v>11</v>
@@ -3076,16 +3076,16 @@
         <v>9</v>
       </c>
       <c r="U37" t="n">
-        <v>1659.9</v>
+        <v>1657.6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1104</v>
+        <v>1304</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Alabama</t>
+          <t>Nebraska</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3102,52 +3102,52 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="G38" t="n">
-        <v>1975.1</v>
+        <v>1982.9</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.4869</v>
+        <v>9.932399999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>122.11</v>
+        <v>114.61</v>
       </c>
       <c r="J38" t="n">
-        <v>110.78</v>
+        <v>98.94</v>
       </c>
       <c r="K38" t="n">
-        <v>11.33</v>
+        <v>15.67</v>
       </c>
       <c r="L38" t="n">
-        <v>0.2853</v>
+        <v>0.2433</v>
       </c>
       <c r="M38" t="n">
-        <v>0.1289</v>
+        <v>0.1403</v>
       </c>
       <c r="N38" t="n">
-        <v>7.2</v>
+        <v>0.2</v>
       </c>
       <c r="O38" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="P38" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Q38" t="n">
+        <v>16</v>
+      </c>
+      <c r="R38" t="n">
+        <v>13</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="n">
         <v>12</v>
       </c>
-      <c r="R38" t="n">
-        <v>12</v>
-      </c>
-      <c r="S38" t="n">
-        <v>14</v>
-      </c>
-      <c r="T38" t="n">
-        <v>17</v>
-      </c>
       <c r="U38" t="n">
-        <v>1772.1</v>
+        <v>1675.8</v>
       </c>
     </row>
     <row r="39">
@@ -3173,31 +3173,31 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G39" t="n">
-        <v>1983.4</v>
+        <v>1973.7</v>
       </c>
       <c r="H39" t="n">
-        <v>10.797</v>
+        <v>10.346</v>
       </c>
       <c r="I39" t="n">
-        <v>111.09</v>
+        <v>109.9</v>
       </c>
       <c r="J39" t="n">
-        <v>100.73</v>
+        <v>101.51</v>
       </c>
       <c r="K39" t="n">
-        <v>10.36</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>0.2493</v>
+        <v>0.2556</v>
       </c>
       <c r="M39" t="n">
-        <v>0.1516</v>
+        <v>0.1512</v>
       </c>
       <c r="N39" t="n">
-        <v>0.8</v>
+        <v>-6.2</v>
       </c>
       <c r="O39" t="n">
         <v>19</v>
@@ -3218,16 +3218,16 @@
         <v>19</v>
       </c>
       <c r="U39" t="n">
-        <v>1778</v>
+        <v>1791.1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1397</v>
+        <v>1116</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3244,61 +3244,61 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G40" t="n">
-        <v>1911</v>
+        <v>1956.5</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.5912</v>
+        <v>5.3805</v>
       </c>
       <c r="I40" t="n">
-        <v>117.14</v>
+        <v>122.83</v>
       </c>
       <c r="J40" t="n">
-        <v>101.72</v>
+        <v>109.16</v>
       </c>
       <c r="K40" t="n">
-        <v>15.42</v>
+        <v>13.66</v>
       </c>
       <c r="L40" t="n">
-        <v>0.3527</v>
+        <v>0.3026</v>
       </c>
       <c r="M40" t="n">
-        <v>0.1643</v>
+        <v>0.1196</v>
       </c>
       <c r="N40" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="O40" t="n">
+        <v>18</v>
+      </c>
+      <c r="P40" t="n">
         <v>14</v>
       </c>
-      <c r="P40" t="n">
-        <v>17</v>
-      </c>
       <c r="Q40" t="n">
+        <v>20</v>
+      </c>
+      <c r="R40" t="n">
+        <v>16</v>
+      </c>
+      <c r="S40" t="n">
+        <v>21</v>
+      </c>
+      <c r="T40" t="n">
         <v>18</v>
       </c>
-      <c r="R40" t="n">
-        <v>20</v>
-      </c>
-      <c r="S40" t="n">
-        <v>24</v>
-      </c>
-      <c r="T40" t="n">
-        <v>21</v>
-      </c>
       <c r="U40" t="n">
-        <v>1709</v>
+        <v>1728.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1458</v>
+        <v>1314</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3318,58 +3318,58 @@
         <v>129</v>
       </c>
       <c r="G41" t="n">
-        <v>1866.2</v>
+        <v>1899.5</v>
       </c>
       <c r="H41" t="n">
-        <v>1.8886</v>
+        <v>2.2848</v>
       </c>
       <c r="I41" t="n">
-        <v>119.65</v>
+        <v>115.28</v>
       </c>
       <c r="J41" t="n">
-        <v>108.66</v>
+        <v>103.72</v>
       </c>
       <c r="K41" t="n">
-        <v>10.99</v>
+        <v>11.56</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2811</v>
+        <v>0.2596</v>
       </c>
       <c r="M41" t="n">
-        <v>0.123</v>
+        <v>0.1375</v>
       </c>
       <c r="N41" t="n">
-        <v>8.6</v>
+        <v>-0.4</v>
       </c>
       <c r="O41" t="n">
+        <v>30</v>
+      </c>
+      <c r="P41" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>24</v>
+      </c>
+      <c r="R41" t="n">
+        <v>24</v>
+      </c>
+      <c r="S41" t="n">
+        <v>18</v>
+      </c>
+      <c r="T41" t="n">
         <v>23</v>
       </c>
-      <c r="P41" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>23</v>
-      </c>
-      <c r="R41" t="n">
-        <v>25</v>
-      </c>
-      <c r="S41" t="n">
-        <v>29</v>
-      </c>
-      <c r="T41" t="n">
-        <v>26</v>
-      </c>
       <c r="U41" t="n">
-        <v>1697</v>
+        <v>1677.4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1274</v>
+        <v>1388</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Miami FL</t>
+          <t>St Mary's CA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3386,61 +3386,61 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G42" t="n">
-        <v>1780</v>
+        <v>1857.8</v>
       </c>
       <c r="H42" t="n">
-        <v>12.0727</v>
+        <v>-0.2818</v>
       </c>
       <c r="I42" t="n">
-        <v>117.75</v>
+        <v>118.73</v>
       </c>
       <c r="J42" t="n">
-        <v>101.58</v>
+        <v>99.88</v>
       </c>
       <c r="K42" t="n">
-        <v>16.16</v>
+        <v>18.85</v>
       </c>
       <c r="L42" t="n">
-        <v>0.3083</v>
+        <v>0.2975</v>
       </c>
       <c r="M42" t="n">
-        <v>0.1583</v>
+        <v>0.1525</v>
       </c>
       <c r="N42" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="O42" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="P42" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="Q42" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="R42" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="S42" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="T42" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="U42" t="n">
-        <v>1624.7</v>
+        <v>1596.9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1429</v>
+        <v>1155</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Utah St</t>
+          <t>Clemson</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3457,61 +3457,61 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G43" t="n">
-        <v>1875.9</v>
+        <v>1859.5</v>
       </c>
       <c r="H43" t="n">
-        <v>0.1664</v>
+        <v>2.557</v>
       </c>
       <c r="I43" t="n">
-        <v>120.08</v>
+        <v>112.59</v>
       </c>
       <c r="J43" t="n">
-        <v>104.01</v>
+        <v>101.68</v>
       </c>
       <c r="K43" t="n">
-        <v>16.07</v>
+        <v>10.91</v>
       </c>
       <c r="L43" t="n">
-        <v>0.305</v>
+        <v>0.2554</v>
       </c>
       <c r="M43" t="n">
-        <v>0.1501</v>
+        <v>0.136</v>
       </c>
       <c r="N43" t="n">
-        <v>-3</v>
+        <v>-0.6</v>
       </c>
       <c r="O43" t="n">
+        <v>38</v>
+      </c>
+      <c r="P43" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>32</v>
+      </c>
+      <c r="R43" t="n">
         <v>35</v>
       </c>
-      <c r="P43" t="n">
+      <c r="S43" t="n">
+        <v>34</v>
+      </c>
+      <c r="T43" t="n">
         <v>36</v>
       </c>
-      <c r="Q43" t="n">
-        <v>37</v>
-      </c>
-      <c r="R43" t="n">
-        <v>33</v>
-      </c>
-      <c r="S43" t="n">
-        <v>30</v>
-      </c>
-      <c r="T43" t="n">
-        <v>29</v>
-      </c>
       <c r="U43" t="n">
-        <v>1599.4</v>
+        <v>1672.9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1234</v>
+        <v>1387</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Iowa</t>
+          <t>St Louis</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3528,61 +3528,61 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G44" t="n">
-        <v>1831.8</v>
+        <v>1811.5</v>
       </c>
       <c r="H44" t="n">
-        <v>3.3952</v>
+        <v>9.2125</v>
       </c>
       <c r="I44" t="n">
-        <v>118.92</v>
+        <v>120.63</v>
       </c>
       <c r="J44" t="n">
-        <v>104.81</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>14.12</v>
+        <v>22.12</v>
       </c>
       <c r="L44" t="n">
-        <v>0.2886</v>
+        <v>0.2386</v>
       </c>
       <c r="M44" t="n">
-        <v>0.1455</v>
+        <v>0.1675</v>
       </c>
       <c r="N44" t="n">
-        <v>-1.2</v>
+        <v>-1.6</v>
       </c>
       <c r="O44" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="P44" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="Q44" t="n">
+        <v>36</v>
+      </c>
+      <c r="R44" t="n">
         <v>30</v>
       </c>
-      <c r="R44" t="n">
+      <c r="S44" t="n">
         <v>28</v>
       </c>
-      <c r="S44" t="n">
-        <v>39</v>
-      </c>
       <c r="T44" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="U44" t="n">
-        <v>1712.2</v>
+        <v>1510.4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1416</v>
+        <v>1301</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>UCF</t>
+          <t>NC State</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3602,58 +3602,58 @@
         <v>129</v>
       </c>
       <c r="G45" t="n">
-        <v>1828.6</v>
+        <v>1734</v>
       </c>
       <c r="H45" t="n">
-        <v>5.8051</v>
+        <v>6.962</v>
       </c>
       <c r="I45" t="n">
-        <v>113</v>
+        <v>119.36</v>
       </c>
       <c r="J45" t="n">
-        <v>110.03</v>
+        <v>109.32</v>
       </c>
       <c r="K45" t="n">
-        <v>2.97</v>
+        <v>10.04</v>
       </c>
       <c r="L45" t="n">
-        <v>0.3147</v>
+        <v>0.2802</v>
       </c>
       <c r="M45" t="n">
-        <v>0.1543</v>
+        <v>0.1288</v>
       </c>
       <c r="N45" t="n">
-        <v>-8.800000000000001</v>
+        <v>-6.6</v>
       </c>
       <c r="O45" t="n">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="P45" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>34</v>
+      </c>
+      <c r="R45" t="n">
+        <v>38</v>
+      </c>
+      <c r="S45" t="n">
         <v>42</v>
       </c>
-      <c r="Q45" t="n">
-        <v>57</v>
-      </c>
-      <c r="R45" t="n">
-        <v>46</v>
-      </c>
-      <c r="S45" t="n">
-        <v>37</v>
-      </c>
       <c r="T45" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="U45" t="n">
-        <v>1712.7</v>
+        <v>1681.7</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1275</v>
+        <v>1378</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Miami OH</t>
+          <t>South Florida</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3670,52 +3670,52 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G46" t="n">
-        <v>1758.6</v>
+        <v>1711.8</v>
       </c>
       <c r="H46" t="n">
-        <v>9.362500000000001</v>
+        <v>9.207800000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>120.74</v>
+        <v>116.06</v>
       </c>
       <c r="J46" t="n">
-        <v>105.88</v>
+        <v>101.73</v>
       </c>
       <c r="K46" t="n">
-        <v>14.87</v>
+        <v>14.32</v>
       </c>
       <c r="L46" t="n">
-        <v>0.2186</v>
+        <v>0.3392</v>
       </c>
       <c r="M46" t="n">
-        <v>0.1413</v>
+        <v>0.1453</v>
       </c>
       <c r="N46" t="n">
-        <v>2.4</v>
+        <v>19.6</v>
       </c>
       <c r="O46" t="n">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="P46" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="Q46" t="n">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="R46" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="T46" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="U46" t="n">
-        <v>1416.9</v>
+        <v>1553.3</v>
       </c>
     </row>
     <row r="47">
@@ -3741,31 +3741,31 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G47" t="n">
-        <v>1696.5</v>
+        <v>1704.5</v>
       </c>
       <c r="H47" t="n">
-        <v>1.818</v>
+        <v>1.8839</v>
       </c>
       <c r="I47" t="n">
-        <v>122.16</v>
+        <v>121.82</v>
       </c>
       <c r="J47" t="n">
-        <v>104.24</v>
+        <v>104.08</v>
       </c>
       <c r="K47" t="n">
-        <v>17.92</v>
+        <v>17.74</v>
       </c>
       <c r="L47" t="n">
-        <v>0.2856</v>
+        <v>0.2847</v>
       </c>
       <c r="M47" t="n">
-        <v>0.1521</v>
+        <v>0.1512</v>
       </c>
       <c r="N47" t="n">
-        <v>18.2</v>
+        <v>16.8</v>
       </c>
       <c r="O47" t="n">
         <v>61</v>
@@ -3786,16 +3786,16 @@
         <v>52</v>
       </c>
       <c r="U47" t="n">
-        <v>1474.6</v>
+        <v>1481.1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1358</v>
+        <v>1320</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sam Houston St</t>
+          <t>Northern Iowa</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3812,61 +3812,61 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G48" t="n">
-        <v>1545</v>
+        <v>1573.9</v>
       </c>
       <c r="H48" t="n">
-        <v>4.4295</v>
+        <v>-3.696</v>
       </c>
       <c r="I48" t="n">
-        <v>112.95</v>
+        <v>108.74</v>
       </c>
       <c r="J48" t="n">
-        <v>106.4</v>
+        <v>97.5</v>
       </c>
       <c r="K48" t="n">
-        <v>6.55</v>
+        <v>11.25</v>
       </c>
       <c r="L48" t="n">
-        <v>0.3122</v>
+        <v>0.225</v>
       </c>
       <c r="M48" t="n">
-        <v>0.1587</v>
+        <v>0.1354</v>
       </c>
       <c r="N48" t="n">
-        <v>7.2</v>
+        <v>14.4</v>
       </c>
       <c r="O48" t="n">
-        <v>109</v>
+        <v>70</v>
       </c>
       <c r="P48" t="n">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="Q48" t="n">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="R48" t="n">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="S48" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="T48" t="n">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="U48" t="n">
-        <v>1499.6</v>
+        <v>1515.8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1407</v>
+        <v>1398</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Troy</t>
+          <t>Tennessee St</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3883,61 +3883,61 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G49" t="n">
-        <v>1601</v>
+        <v>1466.9</v>
       </c>
       <c r="H49" t="n">
-        <v>1.1284</v>
+        <v>3.3618</v>
       </c>
       <c r="I49" t="n">
-        <v>112.28</v>
+        <v>109.9</v>
       </c>
       <c r="J49" t="n">
-        <v>106.19</v>
+        <v>103.28</v>
       </c>
       <c r="K49" t="n">
-        <v>6.08</v>
+        <v>6.62</v>
       </c>
       <c r="L49" t="n">
-        <v>0.316</v>
+        <v>0.328</v>
       </c>
       <c r="M49" t="n">
-        <v>0.1667</v>
+        <v>0.1589</v>
       </c>
       <c r="N49" t="n">
-        <v>9.4</v>
+        <v>19.8</v>
       </c>
       <c r="O49" t="n">
+        <v>186</v>
+      </c>
+      <c r="P49" t="n">
+        <v>190</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>187</v>
+      </c>
+      <c r="R49" t="n">
+        <v>168</v>
+      </c>
+      <c r="S49" t="n">
         <v>153</v>
       </c>
-      <c r="P49" t="n">
-        <v>130</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>137</v>
-      </c>
-      <c r="R49" t="n">
-        <v>137</v>
-      </c>
-      <c r="S49" t="n">
-        <v>124</v>
-      </c>
       <c r="T49" t="n">
-        <v>132</v>
+        <v>172</v>
       </c>
       <c r="U49" t="n">
-        <v>1466</v>
+        <v>1407.8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1420</v>
+        <v>1474</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>UMBC</t>
+          <t>Queens NC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3954,61 +3954,61 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G50" t="n">
-        <v>1393.7</v>
+        <v>1427.4</v>
       </c>
       <c r="H50" t="n">
-        <v>1.2859</v>
+        <v>1.0039</v>
       </c>
       <c r="I50" t="n">
-        <v>113.44</v>
+        <v>119.17</v>
       </c>
       <c r="J50" t="n">
-        <v>102.32</v>
+        <v>116.56</v>
       </c>
       <c r="K50" t="n">
-        <v>11.13</v>
+        <v>2.61</v>
       </c>
       <c r="L50" t="n">
-        <v>0.2168</v>
+        <v>0.2859</v>
       </c>
       <c r="M50" t="n">
-        <v>0.1344</v>
+        <v>0.1441</v>
       </c>
       <c r="N50" t="n">
-        <v>22.4</v>
+        <v>6.4</v>
       </c>
       <c r="O50" t="n">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="P50" t="n">
-        <v>225</v>
+        <v>192</v>
       </c>
       <c r="Q50" t="n">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="R50" t="n">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="S50" t="n">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="T50" t="n">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="U50" t="n">
-        <v>1364.8</v>
+        <v>1430.9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1224</v>
+        <v>1250</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Howard</t>
+          <t>Lehigh</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4025,52 +4025,52 @@
         <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="G51" t="n">
-        <v>1404.4</v>
+        <v>1325.5</v>
       </c>
       <c r="H51" t="n">
-        <v>3.2279</v>
+        <v>-0.465</v>
       </c>
       <c r="I51" t="n">
-        <v>109.08</v>
+        <v>105.58</v>
       </c>
       <c r="J51" t="n">
-        <v>98.81</v>
+        <v>108.39</v>
       </c>
       <c r="K51" t="n">
-        <v>10.27</v>
+        <v>-2.8</v>
       </c>
       <c r="L51" t="n">
-        <v>0.3126</v>
+        <v>0.2229</v>
       </c>
       <c r="M51" t="n">
-        <v>0.1855</v>
+        <v>0.1707</v>
       </c>
       <c r="N51" t="n">
-        <v>23.6</v>
+        <v>7.8</v>
       </c>
       <c r="O51" t="n">
-        <v>202</v>
+        <v>290</v>
       </c>
       <c r="P51" t="n">
-        <v>250</v>
+        <v>295</v>
       </c>
       <c r="Q51" t="n">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="R51" t="n">
-        <v>198</v>
+        <v>282</v>
       </c>
       <c r="S51" t="n">
-        <v>232</v>
+        <v>268</v>
       </c>
       <c r="T51" t="n">
-        <v>202</v>
+        <v>282</v>
       </c>
       <c r="U51" t="n">
-        <v>1380.6</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="52">
@@ -4167,31 +4167,31 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G53" t="n">
-        <v>2256</v>
+        <v>2262.9</v>
       </c>
       <c r="H53" t="n">
-        <v>7.4143</v>
+        <v>7.0872</v>
       </c>
       <c r="I53" t="n">
-        <v>121.01</v>
+        <v>121.14</v>
       </c>
       <c r="J53" t="n">
-        <v>95.61</v>
+        <v>96.66</v>
       </c>
       <c r="K53" t="n">
-        <v>25.4</v>
+        <v>24.48</v>
       </c>
       <c r="L53" t="n">
-        <v>0.2928</v>
+        <v>0.2942</v>
       </c>
       <c r="M53" t="n">
-        <v>0.1495</v>
+        <v>0.151</v>
       </c>
       <c r="N53" t="n">
-        <v>15.6</v>
+        <v>14.6</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -4212,7 +4212,7 @@
         <v>3</v>
       </c>
       <c r="U53" t="n">
-        <v>1747.3</v>
+        <v>1758.1</v>
       </c>
     </row>
     <row r="54">
@@ -4238,31 +4238,31 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="G54" t="n">
-        <v>2049.8</v>
+        <v>2027.4</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2376</v>
+        <v>0.218</v>
       </c>
       <c r="I54" t="n">
-        <v>117.05</v>
+        <v>117.66</v>
       </c>
       <c r="J54" t="n">
-        <v>100.92</v>
+        <v>102.12</v>
       </c>
       <c r="K54" t="n">
-        <v>16.13</v>
+        <v>15.54</v>
       </c>
       <c r="L54" t="n">
-        <v>0.2993</v>
+        <v>0.2963</v>
       </c>
       <c r="M54" t="n">
-        <v>0.1615</v>
+        <v>0.1607</v>
       </c>
       <c r="N54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O54" t="n">
         <v>9</v>
@@ -4283,7 +4283,7 @@
         <v>11</v>
       </c>
       <c r="U54" t="n">
-        <v>1729.6</v>
+        <v>1730.1</v>
       </c>
     </row>
     <row r="55">
@@ -4359,11 +4359,11 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1438</v>
+        <v>1104</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>Alabama</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4380,61 +4380,61 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G56" t="n">
-        <v>1963.2</v>
+        <v>1949.3</v>
       </c>
       <c r="H56" t="n">
-        <v>13.0176</v>
+        <v>-1.3255</v>
       </c>
       <c r="I56" t="n">
-        <v>118.86</v>
+        <v>121.37</v>
       </c>
       <c r="J56" t="n">
-        <v>100.31</v>
+        <v>110.6</v>
       </c>
       <c r="K56" t="n">
-        <v>18.55</v>
+        <v>10.77</v>
       </c>
       <c r="L56" t="n">
-        <v>0.3146</v>
+        <v>0.2809</v>
       </c>
       <c r="M56" t="n">
-        <v>0.1527</v>
+        <v>0.1288</v>
       </c>
       <c r="N56" t="n">
-        <v>3.8</v>
+        <v>5.6</v>
       </c>
       <c r="O56" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="P56" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="Q56" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R56" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="S56" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T56" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="U56" t="n">
-        <v>1642.5</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1435</v>
+        <v>1385</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Vanderbilt</t>
+          <t>St John's</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4451,52 +4451,52 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="G57" t="n">
-        <v>1935.7</v>
+        <v>1967.8</v>
       </c>
       <c r="H57" t="n">
-        <v>2.1989</v>
+        <v>5.6546</v>
       </c>
       <c r="I57" t="n">
-        <v>121.8</v>
+        <v>114.06</v>
       </c>
       <c r="J57" t="n">
-        <v>105.67</v>
+        <v>98.84999999999999</v>
       </c>
       <c r="K57" t="n">
-        <v>16.12</v>
+        <v>15.21</v>
       </c>
       <c r="L57" t="n">
-        <v>0.2802</v>
+        <v>0.3244</v>
       </c>
       <c r="M57" t="n">
-        <v>0.1278</v>
+        <v>0.1434</v>
       </c>
       <c r="N57" t="n">
-        <v>-0.6</v>
+        <v>13</v>
       </c>
       <c r="O57" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="P57" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Q57" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="R57" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="S57" t="n">
+        <v>20</v>
+      </c>
+      <c r="T57" t="n">
         <v>22</v>
       </c>
-      <c r="T57" t="n">
-        <v>16</v>
-      </c>
       <c r="U57" t="n">
-        <v>1694.9</v>
+        <v>1677.1</v>
       </c>
     </row>
     <row r="58">
@@ -4572,11 +4572,11 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1437</v>
+        <v>1274</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Villanova</t>
+          <t>Miami FL</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4593,61 +4593,61 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G59" t="n">
-        <v>1806.3</v>
+        <v>1772.3</v>
       </c>
       <c r="H59" t="n">
-        <v>5.8793</v>
+        <v>11.776</v>
       </c>
       <c r="I59" t="n">
-        <v>114.59</v>
+        <v>117.07</v>
       </c>
       <c r="J59" t="n">
-        <v>104.94</v>
+        <v>102.95</v>
       </c>
       <c r="K59" t="n">
-        <v>9.66</v>
+        <v>14.11</v>
       </c>
       <c r="L59" t="n">
-        <v>0.313</v>
+        <v>0.3096</v>
       </c>
       <c r="M59" t="n">
-        <v>0.1447</v>
+        <v>0.1569</v>
       </c>
       <c r="N59" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="O59" t="n">
+        <v>29</v>
+      </c>
+      <c r="P59" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>27</v>
+      </c>
+      <c r="R59" t="n">
+        <v>31</v>
+      </c>
+      <c r="S59" t="n">
+        <v>26</v>
+      </c>
+      <c r="T59" t="n">
         <v>32</v>
       </c>
-      <c r="P59" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>35</v>
-      </c>
-      <c r="R59" t="n">
-        <v>26</v>
-      </c>
-      <c r="S59" t="n">
-        <v>23</v>
-      </c>
-      <c r="T59" t="n">
-        <v>33</v>
-      </c>
       <c r="U59" t="n">
-        <v>1641.5</v>
+        <v>1635.9</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1417</v>
+        <v>1429</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>UCLA</t>
+          <t>Utah St</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4664,61 +4664,61 @@
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G60" t="n">
-        <v>1863</v>
+        <v>1885.6</v>
       </c>
       <c r="H60" t="n">
-        <v>2.4395</v>
+        <v>0.1404</v>
       </c>
       <c r="I60" t="n">
-        <v>116.91</v>
+        <v>119.83</v>
       </c>
       <c r="J60" t="n">
-        <v>106.2</v>
+        <v>103.76</v>
       </c>
       <c r="K60" t="n">
-        <v>10.71</v>
+        <v>16.07</v>
       </c>
       <c r="L60" t="n">
-        <v>0.2986</v>
+        <v>0.3026</v>
       </c>
       <c r="M60" t="n">
-        <v>0.1298</v>
+        <v>0.1501</v>
       </c>
       <c r="N60" t="n">
-        <v>13.6</v>
+        <v>3</v>
       </c>
       <c r="O60" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="P60" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>37</v>
+      </c>
+      <c r="R60" t="n">
+        <v>33</v>
+      </c>
+      <c r="S60" t="n">
+        <v>30</v>
+      </c>
+      <c r="T60" t="n">
         <v>29</v>
       </c>
-      <c r="Q60" t="n">
-        <v>31</v>
-      </c>
-      <c r="R60" t="n">
-        <v>34</v>
-      </c>
-      <c r="S60" t="n">
-        <v>33</v>
-      </c>
-      <c r="T60" t="n">
-        <v>34</v>
-      </c>
       <c r="U60" t="n">
-        <v>1683.8</v>
+        <v>1604.7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1401</v>
+        <v>1234</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Texas A&amp;M</t>
+          <t>Iowa</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4738,58 +4738,58 @@
         <v>129</v>
       </c>
       <c r="G61" t="n">
-        <v>1824</v>
+        <v>1831.8</v>
       </c>
       <c r="H61" t="n">
-        <v>4.3608</v>
+        <v>3.3952</v>
       </c>
       <c r="I61" t="n">
-        <v>117.14</v>
+        <v>118.92</v>
       </c>
       <c r="J61" t="n">
-        <v>107.43</v>
+        <v>104.81</v>
       </c>
       <c r="K61" t="n">
-        <v>9.699999999999999</v>
+        <v>14.12</v>
       </c>
       <c r="L61" t="n">
-        <v>0.3098</v>
+        <v>0.2886</v>
       </c>
       <c r="M61" t="n">
-        <v>0.1389</v>
+        <v>0.1455</v>
       </c>
       <c r="N61" t="n">
-        <v>-5.4</v>
+        <v>-1.2</v>
       </c>
       <c r="O61" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="P61" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q61" t="n">
         <v>30</v>
       </c>
-      <c r="Q61" t="n">
-        <v>33</v>
-      </c>
       <c r="R61" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="S61" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="T61" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="U61" t="n">
-        <v>1653.7</v>
+        <v>1712.2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1301</v>
+        <v>1416</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NC State</t>
+          <t>UCF</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4809,49 +4809,49 @@
         <v>129</v>
       </c>
       <c r="G62" t="n">
-        <v>1734</v>
+        <v>1828.6</v>
       </c>
       <c r="H62" t="n">
-        <v>6.962</v>
+        <v>5.8051</v>
       </c>
       <c r="I62" t="n">
-        <v>119.36</v>
+        <v>113</v>
       </c>
       <c r="J62" t="n">
-        <v>109.32</v>
+        <v>110.03</v>
       </c>
       <c r="K62" t="n">
-        <v>10.04</v>
+        <v>2.97</v>
       </c>
       <c r="L62" t="n">
-        <v>0.2802</v>
+        <v>0.3147</v>
       </c>
       <c r="M62" t="n">
-        <v>0.1288</v>
+        <v>0.1543</v>
       </c>
       <c r="N62" t="n">
-        <v>-6.6</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="O62" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="P62" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Q62" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="R62" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="S62" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="T62" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="U62" t="n">
-        <v>1681.7</v>
+        <v>1712.7</v>
       </c>
     </row>
     <row r="63">
@@ -4998,11 +4998,11 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1219</v>
+        <v>1270</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>High Point</t>
+          <t>McNeese St</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5019,52 +5019,52 @@
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G65" t="n">
-        <v>1625.5</v>
+        <v>1726.8</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.8564000000000001</v>
+        <v>2.6895</v>
       </c>
       <c r="I65" t="n">
-        <v>121.16</v>
+        <v>115.07</v>
       </c>
       <c r="J65" t="n">
-        <v>100.19</v>
+        <v>100.01</v>
       </c>
       <c r="K65" t="n">
-        <v>20.97</v>
+        <v>15.06</v>
       </c>
       <c r="L65" t="n">
-        <v>0.3061</v>
+        <v>0.3483</v>
       </c>
       <c r="M65" t="n">
-        <v>0.1276</v>
+        <v>0.139</v>
       </c>
       <c r="N65" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O65" t="n">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="P65" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="Q65" t="n">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="R65" t="n">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="S65" t="n">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="T65" t="n">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="U65" t="n">
-        <v>1382.5</v>
+        <v>1428.4</v>
       </c>
     </row>
     <row r="66">
@@ -5161,31 +5161,31 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="G67" t="n">
-        <v>1614.5</v>
+        <v>1620.3</v>
       </c>
       <c r="H67" t="n">
-        <v>2.2068</v>
+        <v>2.2032</v>
       </c>
       <c r="I67" t="n">
-        <v>103.59</v>
+        <v>104.72</v>
       </c>
       <c r="J67" t="n">
-        <v>96.37</v>
+        <v>96.98</v>
       </c>
       <c r="K67" t="n">
-        <v>7.22</v>
+        <v>7.74</v>
       </c>
       <c r="L67" t="n">
-        <v>0.2658</v>
+        <v>0.2714</v>
       </c>
       <c r="M67" t="n">
-        <v>0.1712</v>
+        <v>0.1714</v>
       </c>
       <c r="N67" t="n">
-        <v>7</v>
+        <v>10.4</v>
       </c>
       <c r="O67" t="n">
         <v>106</v>
@@ -5206,16 +5206,16 @@
         <v>118</v>
       </c>
       <c r="U67" t="n">
-        <v>1471.2</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1474</v>
+        <v>1373</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Queens NC</t>
+          <t>Siena</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5232,61 +5232,61 @@
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G68" t="n">
-        <v>1427.4</v>
+        <v>1478</v>
       </c>
       <c r="H68" t="n">
-        <v>1.0039</v>
+        <v>0.9489</v>
       </c>
       <c r="I68" t="n">
-        <v>119.17</v>
+        <v>109.73</v>
       </c>
       <c r="J68" t="n">
-        <v>116.56</v>
+        <v>101.77</v>
       </c>
       <c r="K68" t="n">
-        <v>2.61</v>
+        <v>7.95</v>
       </c>
       <c r="L68" t="n">
-        <v>0.2859</v>
+        <v>0.2799</v>
       </c>
       <c r="M68" t="n">
-        <v>0.1441</v>
+        <v>0.1508</v>
       </c>
       <c r="N68" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="O68" t="n">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="P68" t="n">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="Q68" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="R68" t="n">
+        <v>172</v>
+      </c>
+      <c r="S68" t="n">
         <v>177</v>
       </c>
-      <c r="S68" t="n">
-        <v>171</v>
-      </c>
       <c r="T68" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="U68" t="n">
-        <v>1430.9</v>
+        <v>1430.3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1254</v>
+        <v>1224</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>LIU Brooklyn</t>
+          <t>Howard</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5303,52 +5303,52 @@
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G69" t="n">
-        <v>1418.2</v>
+        <v>1406</v>
       </c>
       <c r="H69" t="n">
-        <v>2.3581</v>
+        <v>3.0696</v>
       </c>
       <c r="I69" t="n">
-        <v>109.38</v>
+        <v>108.81</v>
       </c>
       <c r="J69" t="n">
-        <v>104.38</v>
+        <v>97.94</v>
       </c>
       <c r="K69" t="n">
-        <v>5</v>
+        <v>10.87</v>
       </c>
       <c r="L69" t="n">
-        <v>0.3119</v>
+        <v>0.3142</v>
       </c>
       <c r="M69" t="n">
-        <v>0.183</v>
+        <v>0.1871</v>
       </c>
       <c r="N69" t="n">
-        <v>10.4</v>
+        <v>20.6</v>
       </c>
       <c r="O69" t="n">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="P69" t="n">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="Q69" t="n">
-        <v>213</v>
+        <v>270</v>
       </c>
       <c r="R69" t="n">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="S69" t="n">
-        <v>166</v>
+        <v>232</v>
       </c>
       <c r="T69" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="U69" t="n">
-        <v>1378.8</v>
+        <v>1374.8</v>
       </c>
     </row>
   </sheetData>

--- a/team_stats_2026.xlsx
+++ b/team_stats_2026.xlsx
@@ -546,31 +546,31 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G2" t="n">
-        <v>2189.2</v>
+        <v>2195.9</v>
       </c>
       <c r="H2" t="n">
-        <v>3.7126</v>
+        <v>3.7176</v>
       </c>
       <c r="I2" t="n">
-        <v>122.89</v>
+        <v>122.74</v>
       </c>
       <c r="J2" t="n">
-        <v>94.03</v>
+        <v>94.67</v>
       </c>
       <c r="K2" t="n">
-        <v>28.87</v>
+        <v>28.07</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2894</v>
+        <v>0.2982</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1548</v>
+        <v>0.1541</v>
       </c>
       <c r="N2" t="n">
-        <v>16.6</v>
+        <v>12.2</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -591,7 +591,7 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>1703.5</v>
+        <v>1712.3</v>
       </c>
     </row>
     <row r="3">
@@ -759,31 +759,31 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G5" t="n">
-        <v>1949.6</v>
+        <v>1967.8</v>
       </c>
       <c r="H5" t="n">
-        <v>1.887</v>
+        <v>1.6985</v>
       </c>
       <c r="I5" t="n">
-        <v>121.84</v>
+        <v>122.92</v>
       </c>
       <c r="J5" t="n">
-        <v>105.79</v>
+        <v>106.35</v>
       </c>
       <c r="K5" t="n">
-        <v>16.05</v>
+        <v>16.57</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2851</v>
+        <v>0.2937</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1258</v>
+        <v>0.1302</v>
       </c>
       <c r="N5" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="O5" t="n">
         <v>13</v>
@@ -804,16 +804,16 @@
         <v>16</v>
       </c>
       <c r="U5" t="n">
-        <v>1701.5</v>
+        <v>1712.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1458</v>
+        <v>1385</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>St John's</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -830,52 +830,52 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G6" t="n">
-        <v>1886.8</v>
+        <v>1984.9</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1287</v>
+        <v>5.6609</v>
       </c>
       <c r="I6" t="n">
-        <v>119.67</v>
+        <v>113.97</v>
       </c>
       <c r="J6" t="n">
-        <v>108.89</v>
+        <v>98.16</v>
       </c>
       <c r="K6" t="n">
-        <v>10.78</v>
+        <v>15.81</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2787</v>
+        <v>0.3224</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1222</v>
+        <v>0.1422</v>
       </c>
       <c r="N6" t="n">
-        <v>12</v>
+        <v>10.6</v>
       </c>
       <c r="O6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P6" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>17</v>
+      </c>
+      <c r="R6" t="n">
+        <v>17</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="n">
         <v>22</v>
       </c>
-      <c r="Q6" t="n">
-        <v>23</v>
-      </c>
-      <c r="R6" t="n">
-        <v>25</v>
-      </c>
-      <c r="S6" t="n">
-        <v>29</v>
-      </c>
-      <c r="T6" t="n">
-        <v>26</v>
-      </c>
       <c r="U6" t="n">
-        <v>1709.1</v>
+        <v>1691.6</v>
       </c>
     </row>
     <row r="7">
@@ -1022,11 +1022,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1208</v>
+        <v>1326</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Ohio St</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1043,52 +1043,52 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G9" t="n">
-        <v>1798.1</v>
+        <v>1813.9</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2861</v>
+        <v>1.9487</v>
       </c>
       <c r="I9" t="n">
-        <v>119.92</v>
+        <v>118</v>
       </c>
       <c r="J9" t="n">
-        <v>106.59</v>
+        <v>108.07</v>
       </c>
       <c r="K9" t="n">
-        <v>13.33</v>
+        <v>9.93</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3181</v>
+        <v>0.255</v>
       </c>
       <c r="M9" t="n">
-        <v>0.141</v>
+        <v>0.1503</v>
       </c>
       <c r="N9" t="n">
-        <v>4.6</v>
+        <v>10.4</v>
       </c>
       <c r="O9" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P9" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Q9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R9" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="S9" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="T9" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="U9" t="n">
-        <v>1643.1</v>
+        <v>1722.9</v>
       </c>
     </row>
     <row r="10">
@@ -1306,11 +1306,11 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1433</v>
+        <v>1275</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VCU</t>
+          <t>Miami OH</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1327,61 +1327,61 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G13" t="n">
-        <v>1743.5</v>
+        <v>1758.6</v>
       </c>
       <c r="H13" t="n">
-        <v>3.091</v>
+        <v>9.362500000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>118.25</v>
+        <v>120.74</v>
       </c>
       <c r="J13" t="n">
-        <v>103.78</v>
+        <v>105.88</v>
       </c>
       <c r="K13" t="n">
-        <v>14.46</v>
+        <v>14.87</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2985</v>
+        <v>0.2186</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1511</v>
+        <v>0.1413</v>
       </c>
       <c r="N13" t="n">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="O13" t="n">
-        <v>45</v>
+        <v>91</v>
       </c>
       <c r="P13" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="Q13" t="n">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="R13" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="S13" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="T13" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="U13" t="n">
-        <v>1550.6</v>
+        <v>1416.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1219</v>
+        <v>1103</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>High Point</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1398,61 +1398,61 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="G14" t="n">
-        <v>1625.5</v>
+        <v>1707.9</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.8564000000000001</v>
+        <v>1.9745</v>
       </c>
       <c r="I14" t="n">
-        <v>121.16</v>
+        <v>121.64</v>
       </c>
       <c r="J14" t="n">
-        <v>100.19</v>
+        <v>104.36</v>
       </c>
       <c r="K14" t="n">
-        <v>20.97</v>
+        <v>17.27</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3061</v>
+        <v>0.2887</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1276</v>
+        <v>0.15</v>
       </c>
       <c r="N14" t="n">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="O14" t="n">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="P14" t="n">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="Q14" t="n">
-        <v>95</v>
+        <v>49</v>
       </c>
       <c r="R14" t="n">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="S14" t="n">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="T14" t="n">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="U14" t="n">
-        <v>1382.5</v>
+        <v>1479.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1295</v>
+        <v>1320</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>N Dakota St</t>
+          <t>Northern Iowa</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1472,49 +1472,49 @@
         <v>125</v>
       </c>
       <c r="G15" t="n">
-        <v>1593.8</v>
+        <v>1573.9</v>
       </c>
       <c r="H15" t="n">
-        <v>3.5257</v>
+        <v>-3.696</v>
       </c>
       <c r="I15" t="n">
-        <v>114.28</v>
+        <v>108.74</v>
       </c>
       <c r="J15" t="n">
-        <v>102.18</v>
+        <v>97.5</v>
       </c>
       <c r="K15" t="n">
-        <v>12.1</v>
+        <v>11.25</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3104</v>
+        <v>0.225</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1506</v>
+        <v>0.1354</v>
       </c>
       <c r="N15" t="n">
-        <v>10.8</v>
+        <v>14.4</v>
       </c>
       <c r="O15" t="n">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="P15" t="n">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="Q15" t="n">
-        <v>163</v>
+        <v>72</v>
       </c>
       <c r="R15" t="n">
-        <v>115</v>
+        <v>76</v>
       </c>
       <c r="S15" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="T15" t="n">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="U15" t="n">
-        <v>1410.6</v>
+        <v>1515.8</v>
       </c>
     </row>
     <row r="16">
@@ -1661,11 +1661,11 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1420</v>
+        <v>1254</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>UMBC</t>
+          <t>LIU Brooklyn</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1685,49 +1685,49 @@
         <v>127</v>
       </c>
       <c r="G18" t="n">
-        <v>1393.7</v>
+        <v>1418.2</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2859</v>
+        <v>2.3581</v>
       </c>
       <c r="I18" t="n">
-        <v>113.44</v>
+        <v>109.38</v>
       </c>
       <c r="J18" t="n">
-        <v>102.32</v>
+        <v>104.38</v>
       </c>
       <c r="K18" t="n">
-        <v>11.13</v>
+        <v>5</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2168</v>
+        <v>0.3119</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1344</v>
+        <v>0.183</v>
       </c>
       <c r="N18" t="n">
-        <v>22.4</v>
+        <v>10.4</v>
       </c>
       <c r="O18" t="n">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="P18" t="n">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q18" t="n">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="R18" t="n">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="S18" t="n">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="T18" t="n">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="U18" t="n">
-        <v>1364.8</v>
+        <v>1378.8</v>
       </c>
     </row>
     <row r="19">
@@ -1753,31 +1753,31 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G19" t="n">
-        <v>2024.9</v>
+        <v>2006.7</v>
       </c>
       <c r="H19" t="n">
-        <v>3.1754</v>
+        <v>3.4651</v>
       </c>
       <c r="I19" t="n">
-        <v>120.02</v>
+        <v>119.99</v>
       </c>
       <c r="J19" t="n">
-        <v>98.41</v>
+        <v>100.19</v>
       </c>
       <c r="K19" t="n">
-        <v>21.61</v>
+        <v>19.81</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3339</v>
+        <v>0.3342</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1592</v>
+        <v>0.1568</v>
       </c>
       <c r="N19" t="n">
-        <v>19.2</v>
+        <v>13.2</v>
       </c>
       <c r="O19" t="n">
         <v>4</v>
@@ -1798,7 +1798,7 @@
         <v>4</v>
       </c>
       <c r="U19" t="n">
-        <v>1715.4</v>
+        <v>1722.9</v>
       </c>
     </row>
     <row r="20">
@@ -1824,31 +1824,31 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G20" t="n">
-        <v>2120.9</v>
+        <v>2111.7</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2885</v>
+        <v>1.2196</v>
       </c>
       <c r="I20" t="n">
-        <v>117.48</v>
+        <v>117.35</v>
       </c>
       <c r="J20" t="n">
-        <v>94.63</v>
+        <v>95.8</v>
       </c>
       <c r="K20" t="n">
-        <v>22.86</v>
+        <v>21.55</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3358</v>
+        <v>0.3386</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1237</v>
+        <v>0.1236</v>
       </c>
       <c r="N20" t="n">
-        <v>17.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O20" t="n">
         <v>6</v>
@@ -1869,7 +1869,7 @@
         <v>7</v>
       </c>
       <c r="U20" t="n">
-        <v>1724.5</v>
+        <v>1742.7</v>
       </c>
     </row>
     <row r="21">
@@ -1895,31 +1895,31 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G21" t="n">
-        <v>1975.7</v>
+        <v>1986.9</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3998</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>124.77</v>
+        <v>124.76</v>
       </c>
       <c r="J21" t="n">
-        <v>106.95</v>
+        <v>107.25</v>
       </c>
       <c r="K21" t="n">
-        <v>17.82</v>
+        <v>17.51</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3094</v>
+        <v>0.3105</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1359</v>
+        <v>0.1343</v>
       </c>
       <c r="N21" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="O21" t="n">
         <v>8</v>
@@ -1940,16 +1940,16 @@
         <v>10</v>
       </c>
       <c r="U21" t="n">
-        <v>1751.8</v>
+        <v>1754.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1438</v>
+        <v>1211</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>Gonzaga</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1966,52 +1966,52 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="G22" t="n">
-        <v>1971</v>
+        <v>2068.3</v>
       </c>
       <c r="H22" t="n">
-        <v>12.5889</v>
+        <v>5.8188</v>
       </c>
       <c r="I22" t="n">
-        <v>119.48</v>
+        <v>120.75</v>
       </c>
       <c r="J22" t="n">
-        <v>100.21</v>
+        <v>93.89</v>
       </c>
       <c r="K22" t="n">
-        <v>19.27</v>
+        <v>26.86</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3151</v>
+        <v>0.2992</v>
       </c>
       <c r="M22" t="n">
-        <v>0.153</v>
+        <v>0.1335</v>
       </c>
       <c r="N22" t="n">
-        <v>2.4</v>
+        <v>11.8</v>
       </c>
       <c r="O22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="P22" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="Q22" t="n">
+        <v>15</v>
+      </c>
+      <c r="R22" t="n">
         <v>11</v>
       </c>
-      <c r="R22" t="n">
-        <v>19</v>
-      </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T22" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="U22" t="n">
-        <v>1646.9</v>
+        <v>1601.3</v>
       </c>
     </row>
     <row r="23">
@@ -2158,11 +2158,11 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1417</v>
+        <v>1388</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>UCLA</t>
+          <t>St Mary's CA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2179,61 +2179,61 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G25" t="n">
-        <v>1885.4</v>
+        <v>1857.8</v>
       </c>
       <c r="H25" t="n">
-        <v>2.6042</v>
+        <v>-0.2818</v>
       </c>
       <c r="I25" t="n">
-        <v>117.52</v>
+        <v>118.73</v>
       </c>
       <c r="J25" t="n">
-        <v>107.06</v>
+        <v>99.88</v>
       </c>
       <c r="K25" t="n">
-        <v>10.46</v>
+        <v>18.85</v>
       </c>
       <c r="L25" t="n">
-        <v>0.3052</v>
+        <v>0.2975</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1315</v>
+        <v>0.1525</v>
       </c>
       <c r="N25" t="n">
-        <v>10.6</v>
+        <v>8.6</v>
       </c>
       <c r="O25" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="P25" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Q25" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="R25" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="S25" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="T25" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="U25" t="n">
-        <v>1698.9</v>
+        <v>1596.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1326</v>
+        <v>1155</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ohio St</t>
+          <t>Clemson</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2253,49 +2253,49 @@
         <v>130</v>
       </c>
       <c r="G26" t="n">
-        <v>1813.9</v>
+        <v>1859.5</v>
       </c>
       <c r="H26" t="n">
-        <v>1.9487</v>
+        <v>2.557</v>
       </c>
       <c r="I26" t="n">
-        <v>118</v>
+        <v>112.59</v>
       </c>
       <c r="J26" t="n">
-        <v>108.07</v>
+        <v>101.68</v>
       </c>
       <c r="K26" t="n">
-        <v>9.93</v>
+        <v>10.91</v>
       </c>
       <c r="L26" t="n">
-        <v>0.255</v>
+        <v>0.2554</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1503</v>
+        <v>0.136</v>
       </c>
       <c r="N26" t="n">
-        <v>10.4</v>
+        <v>-0.6</v>
       </c>
       <c r="O26" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="P26" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q26" t="n">
         <v>32</v>
       </c>
-      <c r="Q26" t="n">
-        <v>29</v>
-      </c>
       <c r="R26" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="S26" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="T26" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="U26" t="n">
-        <v>1722.9</v>
+        <v>1672.9</v>
       </c>
     </row>
     <row r="27">
@@ -2442,11 +2442,11 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1275</v>
+        <v>1433</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Miami OH</t>
+          <t>VCU</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2463,52 +2463,52 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G29" t="n">
-        <v>1758.6</v>
+        <v>1751</v>
       </c>
       <c r="H29" t="n">
-        <v>9.362500000000001</v>
+        <v>3.1884</v>
       </c>
       <c r="I29" t="n">
-        <v>120.74</v>
+        <v>118.3</v>
       </c>
       <c r="J29" t="n">
-        <v>105.88</v>
+        <v>103.55</v>
       </c>
       <c r="K29" t="n">
-        <v>14.87</v>
+        <v>14.75</v>
       </c>
       <c r="L29" t="n">
-        <v>0.2186</v>
+        <v>0.2988</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1413</v>
+        <v>0.1491</v>
       </c>
       <c r="N29" t="n">
-        <v>2.4</v>
+        <v>9.6</v>
       </c>
       <c r="O29" t="n">
-        <v>91</v>
+        <v>45</v>
       </c>
       <c r="P29" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q29" t="n">
         <v>48</v>
       </c>
-      <c r="Q29" t="n">
-        <v>87</v>
-      </c>
       <c r="R29" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="T29" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="U29" t="n">
-        <v>1416.9</v>
+        <v>1553.9</v>
       </c>
     </row>
     <row r="30">
@@ -2534,31 +2534,31 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="G30" t="n">
-        <v>1720.2</v>
+        <v>1727.4</v>
       </c>
       <c r="H30" t="n">
-        <v>1.1161</v>
+        <v>1.0257</v>
       </c>
       <c r="I30" t="n">
-        <v>120.93</v>
+        <v>122.21</v>
       </c>
       <c r="J30" t="n">
-        <v>107.17</v>
+        <v>108.54</v>
       </c>
       <c r="K30" t="n">
-        <v>13.77</v>
+        <v>13.66</v>
       </c>
       <c r="L30" t="n">
-        <v>0.2847</v>
+        <v>0.2923</v>
       </c>
       <c r="M30" t="n">
-        <v>0.1362</v>
+        <v>0.1356</v>
       </c>
       <c r="N30" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O30" t="n">
         <v>78</v>
@@ -2579,16 +2579,16 @@
         <v>66</v>
       </c>
       <c r="U30" t="n">
-        <v>1457.4</v>
+        <v>1459.8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1430</v>
+        <v>1220</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Utah Valley</t>
+          <t>Hofstra</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2605,52 +2605,52 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="G31" t="n">
-        <v>1641</v>
+        <v>1586.2</v>
       </c>
       <c r="H31" t="n">
-        <v>3.0131</v>
+        <v>3.3583</v>
       </c>
       <c r="I31" t="n">
-        <v>111.37</v>
+        <v>113.56</v>
       </c>
       <c r="J31" t="n">
-        <v>100.52</v>
+        <v>102.69</v>
       </c>
       <c r="K31" t="n">
-        <v>10.85</v>
+        <v>10.87</v>
       </c>
       <c r="L31" t="n">
-        <v>0.304</v>
+        <v>0.3081</v>
       </c>
       <c r="M31" t="n">
-        <v>0.1971</v>
+        <v>0.1527</v>
       </c>
       <c r="N31" t="n">
-        <v>4.6</v>
+        <v>12</v>
       </c>
       <c r="O31" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="P31" t="n">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="Q31" t="n">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="R31" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="S31" t="n">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="T31" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="U31" t="n">
-        <v>1456.2</v>
+        <v>1482.3</v>
       </c>
     </row>
     <row r="32">
@@ -2726,11 +2726,11 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1254</v>
+        <v>1420</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LIU Brooklyn</t>
+          <t>UMBC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2747,61 +2747,61 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G33" t="n">
-        <v>1418.2</v>
+        <v>1397.9</v>
       </c>
       <c r="H33" t="n">
-        <v>2.3581</v>
+        <v>1.3468</v>
       </c>
       <c r="I33" t="n">
-        <v>109.38</v>
+        <v>113.39</v>
       </c>
       <c r="J33" t="n">
-        <v>104.38</v>
+        <v>101.92</v>
       </c>
       <c r="K33" t="n">
-        <v>5</v>
+        <v>11.47</v>
       </c>
       <c r="L33" t="n">
-        <v>0.3119</v>
+        <v>0.2176</v>
       </c>
       <c r="M33" t="n">
-        <v>0.183</v>
+        <v>0.135</v>
       </c>
       <c r="N33" t="n">
-        <v>10.4</v>
+        <v>23</v>
       </c>
       <c r="O33" t="n">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="P33" t="n">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="Q33" t="n">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="R33" t="n">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="S33" t="n">
-        <v>166</v>
+        <v>197</v>
       </c>
       <c r="T33" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="U33" t="n">
-        <v>1378.8</v>
+        <v>1369.1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1380</v>
+        <v>1244</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Southern Univ</t>
+          <t>Kennesaw</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2818,61 +2818,61 @@
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G34" t="n">
-        <v>1377.9</v>
+        <v>1521.3</v>
       </c>
       <c r="H34" t="n">
-        <v>-2.2287</v>
+        <v>-0.1615</v>
       </c>
       <c r="I34" t="n">
-        <v>106.09</v>
+        <v>111.12</v>
       </c>
       <c r="J34" t="n">
-        <v>111.35</v>
+        <v>108.1</v>
       </c>
       <c r="K34" t="n">
-        <v>-5.25</v>
+        <v>3.02</v>
       </c>
       <c r="L34" t="n">
-        <v>0.3165</v>
+        <v>0.345</v>
       </c>
       <c r="M34" t="n">
-        <v>0.1627</v>
+        <v>0.165</v>
       </c>
       <c r="N34" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="O34" t="n">
-        <v>275</v>
+        <v>178</v>
       </c>
       <c r="P34" t="n">
-        <v>280</v>
+        <v>159</v>
       </c>
       <c r="Q34" t="n">
-        <v>256</v>
+        <v>149</v>
       </c>
       <c r="R34" t="n">
-        <v>259</v>
+        <v>184</v>
       </c>
       <c r="S34" t="n">
-        <v>272</v>
+        <v>170</v>
       </c>
       <c r="T34" t="n">
-        <v>277</v>
+        <v>170</v>
       </c>
       <c r="U34" t="n">
-        <v>1393.5</v>
+        <v>1474.6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1256</v>
+        <v>1341</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Louisiana Tech</t>
+          <t>Prairie View</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2889,52 +2889,52 @@
         <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G35" t="n">
-        <v>1515.2</v>
+        <v>1266.7</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.3208</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>104.02</v>
+        <v>104.38</v>
       </c>
       <c r="J35" t="n">
-        <v>103.4</v>
+        <v>107.11</v>
       </c>
       <c r="K35" t="n">
-        <v>0.62</v>
+        <v>-2.73</v>
       </c>
       <c r="L35" t="n">
-        <v>0.3299</v>
+        <v>0.2878</v>
       </c>
       <c r="M35" t="n">
-        <v>0.1728</v>
+        <v>0.1551</v>
       </c>
       <c r="N35" t="n">
-        <v>10.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O35" t="n">
-        <v>208</v>
+        <v>312</v>
       </c>
       <c r="P35" t="n">
-        <v>158</v>
+        <v>330</v>
       </c>
       <c r="Q35" t="n">
-        <v>165</v>
+        <v>303</v>
       </c>
       <c r="R35" t="n">
-        <v>212</v>
+        <v>306</v>
       </c>
       <c r="S35" t="n">
-        <v>205</v>
+        <v>325</v>
       </c>
       <c r="T35" t="n">
-        <v>213</v>
+        <v>316</v>
       </c>
       <c r="U35" t="n">
-        <v>1463.6</v>
+        <v>1383.4</v>
       </c>
     </row>
     <row r="36">
@@ -2960,31 +2960,31 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G36" t="n">
-        <v>2192.4</v>
+        <v>2196.8</v>
       </c>
       <c r="H36" t="n">
-        <v>6.99</v>
+        <v>6.739</v>
       </c>
       <c r="I36" t="n">
-        <v>121.3</v>
+        <v>120.64</v>
       </c>
       <c r="J36" t="n">
-        <v>95.95</v>
+        <v>95.94</v>
       </c>
       <c r="K36" t="n">
-        <v>25.34</v>
+        <v>24.71</v>
       </c>
       <c r="L36" t="n">
-        <v>0.2601</v>
+        <v>0.2604</v>
       </c>
       <c r="M36" t="n">
-        <v>0.1647</v>
+        <v>0.1666</v>
       </c>
       <c r="N36" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="O36" t="n">
         <v>2</v>
@@ -3005,7 +3005,7 @@
         <v>2</v>
       </c>
       <c r="U36" t="n">
-        <v>1768.8</v>
+        <v>1772.9</v>
       </c>
     </row>
     <row r="37">
@@ -3031,31 +3031,31 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G37" t="n">
-        <v>2067.9</v>
+        <v>2050.7</v>
       </c>
       <c r="H37" t="n">
-        <v>7.6929</v>
+        <v>7.1741</v>
       </c>
       <c r="I37" t="n">
-        <v>117.25</v>
+        <v>116.06</v>
       </c>
       <c r="J37" t="n">
-        <v>97.09999999999999</v>
+        <v>98.01000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>20.14</v>
+        <v>18.05</v>
       </c>
       <c r="L37" t="n">
-        <v>0.2963</v>
+        <v>0.3013</v>
       </c>
       <c r="M37" t="n">
-        <v>0.1567</v>
+        <v>0.1603</v>
       </c>
       <c r="N37" t="n">
-        <v>14.2</v>
+        <v>3.8</v>
       </c>
       <c r="O37" t="n">
         <v>11</v>
@@ -3076,7 +3076,7 @@
         <v>9</v>
       </c>
       <c r="U37" t="n">
-        <v>1657.6</v>
+        <v>1670.2</v>
       </c>
     </row>
     <row r="38">
@@ -3244,31 +3244,31 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G40" t="n">
-        <v>1956.5</v>
+        <v>1961.7</v>
       </c>
       <c r="H40" t="n">
-        <v>5.3805</v>
+        <v>5.2535</v>
       </c>
       <c r="I40" t="n">
-        <v>122.83</v>
+        <v>122.84</v>
       </c>
       <c r="J40" t="n">
-        <v>109.16</v>
+        <v>109.47</v>
       </c>
       <c r="K40" t="n">
-        <v>13.66</v>
+        <v>13.37</v>
       </c>
       <c r="L40" t="n">
-        <v>0.3026</v>
+        <v>0.3045</v>
       </c>
       <c r="M40" t="n">
-        <v>0.1196</v>
+        <v>0.1197</v>
       </c>
       <c r="N40" t="n">
-        <v>1.6</v>
+        <v>-0.8</v>
       </c>
       <c r="O40" t="n">
         <v>18</v>
@@ -3289,7 +3289,7 @@
         <v>18</v>
       </c>
       <c r="U40" t="n">
-        <v>1728.4</v>
+        <v>1726.7</v>
       </c>
     </row>
     <row r="41">
@@ -3365,11 +3365,11 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1388</v>
+        <v>1417</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>St Mary's CA</t>
+          <t>UCLA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3386,61 +3386,61 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G42" t="n">
-        <v>1857.8</v>
+        <v>1874.2</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.2818</v>
+        <v>2.8463</v>
       </c>
       <c r="I42" t="n">
-        <v>118.73</v>
+        <v>117.18</v>
       </c>
       <c r="J42" t="n">
-        <v>99.88</v>
+        <v>107.51</v>
       </c>
       <c r="K42" t="n">
-        <v>18.85</v>
+        <v>9.67</v>
       </c>
       <c r="L42" t="n">
-        <v>0.2975</v>
+        <v>0.3055</v>
       </c>
       <c r="M42" t="n">
-        <v>0.1525</v>
+        <v>0.1325</v>
       </c>
       <c r="N42" t="n">
-        <v>8.6</v>
+        <v>10.2</v>
       </c>
       <c r="O42" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="P42" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q42" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="R42" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="S42" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="T42" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="U42" t="n">
-        <v>1596.9</v>
+        <v>1706.3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1155</v>
+        <v>1208</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Clemson</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3457,52 +3457,52 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G43" t="n">
-        <v>1859.5</v>
+        <v>1798.1</v>
       </c>
       <c r="H43" t="n">
-        <v>2.557</v>
+        <v>0.2861</v>
       </c>
       <c r="I43" t="n">
-        <v>112.59</v>
+        <v>119.92</v>
       </c>
       <c r="J43" t="n">
-        <v>101.68</v>
+        <v>106.59</v>
       </c>
       <c r="K43" t="n">
-        <v>10.91</v>
+        <v>13.33</v>
       </c>
       <c r="L43" t="n">
-        <v>0.2554</v>
+        <v>0.3181</v>
       </c>
       <c r="M43" t="n">
-        <v>0.136</v>
+        <v>0.141</v>
       </c>
       <c r="N43" t="n">
-        <v>-0.6</v>
+        <v>4.6</v>
       </c>
       <c r="O43" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="P43" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q43" t="n">
+        <v>28</v>
+      </c>
+      <c r="R43" t="n">
+        <v>27</v>
+      </c>
+      <c r="S43" t="n">
         <v>32</v>
       </c>
-      <c r="R43" t="n">
-        <v>35</v>
-      </c>
-      <c r="S43" t="n">
-        <v>34</v>
-      </c>
       <c r="T43" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="U43" t="n">
-        <v>1672.9</v>
+        <v>1643.1</v>
       </c>
     </row>
     <row r="44">
@@ -3528,31 +3528,31 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G44" t="n">
-        <v>1811.5</v>
+        <v>1793.2</v>
       </c>
       <c r="H44" t="n">
-        <v>9.2125</v>
+        <v>8.666399999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>120.63</v>
+        <v>120</v>
       </c>
       <c r="J44" t="n">
-        <v>98.51000000000001</v>
+        <v>98.73</v>
       </c>
       <c r="K44" t="n">
-        <v>22.12</v>
+        <v>21.28</v>
       </c>
       <c r="L44" t="n">
-        <v>0.2386</v>
+        <v>0.2418</v>
       </c>
       <c r="M44" t="n">
-        <v>0.1675</v>
+        <v>0.1658</v>
       </c>
       <c r="N44" t="n">
-        <v>-1.6</v>
+        <v>1.2</v>
       </c>
       <c r="O44" t="n">
         <v>40</v>
@@ -3573,7 +3573,7 @@
         <v>27</v>
       </c>
       <c r="U44" t="n">
-        <v>1510.4</v>
+        <v>1516.9</v>
       </c>
     </row>
     <row r="45">
@@ -3670,31 +3670,31 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="G46" t="n">
-        <v>1711.8</v>
+        <v>1714.9</v>
       </c>
       <c r="H46" t="n">
-        <v>9.207800000000001</v>
+        <v>9.035</v>
       </c>
       <c r="I46" t="n">
-        <v>116.06</v>
+        <v>116.33</v>
       </c>
       <c r="J46" t="n">
-        <v>101.73</v>
+        <v>101.48</v>
       </c>
       <c r="K46" t="n">
-        <v>14.32</v>
+        <v>14.84</v>
       </c>
       <c r="L46" t="n">
-        <v>0.3392</v>
+        <v>0.3412</v>
       </c>
       <c r="M46" t="n">
-        <v>0.1453</v>
+        <v>0.1466</v>
       </c>
       <c r="N46" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="O46" t="n">
         <v>51</v>
@@ -3715,16 +3715,16 @@
         <v>49</v>
       </c>
       <c r="U46" t="n">
-        <v>1553.3</v>
+        <v>1550.3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1103</v>
+        <v>1270</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>McNeese St</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3741,61 +3741,61 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G47" t="n">
-        <v>1704.5</v>
+        <v>1726.8</v>
       </c>
       <c r="H47" t="n">
-        <v>1.8839</v>
+        <v>2.6895</v>
       </c>
       <c r="I47" t="n">
-        <v>121.82</v>
+        <v>115.07</v>
       </c>
       <c r="J47" t="n">
-        <v>104.08</v>
+        <v>100.01</v>
       </c>
       <c r="K47" t="n">
-        <v>17.74</v>
+        <v>15.06</v>
       </c>
       <c r="L47" t="n">
-        <v>0.2847</v>
+        <v>0.3483</v>
       </c>
       <c r="M47" t="n">
-        <v>0.1512</v>
+        <v>0.139</v>
       </c>
       <c r="N47" t="n">
-        <v>16.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O47" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="P47" t="n">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="Q47" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="R47" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="S47" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="T47" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="U47" t="n">
-        <v>1481.1</v>
+        <v>1428.4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1320</v>
+        <v>1465</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Northern Iowa</t>
+          <t>Cal Baptist</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3812,61 +3812,61 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="G48" t="n">
-        <v>1573.9</v>
+        <v>1607.9</v>
       </c>
       <c r="H48" t="n">
-        <v>-3.696</v>
+        <v>1.5554</v>
       </c>
       <c r="I48" t="n">
-        <v>108.74</v>
+        <v>107.22</v>
       </c>
       <c r="J48" t="n">
-        <v>97.5</v>
+        <v>99.23999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>11.25</v>
+        <v>7.97</v>
       </c>
       <c r="L48" t="n">
-        <v>0.225</v>
+        <v>0.3287</v>
       </c>
       <c r="M48" t="n">
-        <v>0.1354</v>
+        <v>0.1735</v>
       </c>
       <c r="N48" t="n">
-        <v>14.4</v>
+        <v>15.4</v>
       </c>
       <c r="O48" t="n">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="P48" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="Q48" t="n">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="R48" t="n">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="S48" t="n">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="T48" t="n">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="U48" t="n">
-        <v>1515.8</v>
+        <v>1462.4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1398</v>
+        <v>1218</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tennessee St</t>
+          <t>Hawaii</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3883,52 +3883,52 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="G49" t="n">
-        <v>1466.9</v>
+        <v>1549.1</v>
       </c>
       <c r="H49" t="n">
-        <v>3.3618</v>
+        <v>2.9832</v>
       </c>
       <c r="I49" t="n">
-        <v>109.9</v>
+        <v>108.14</v>
       </c>
       <c r="J49" t="n">
-        <v>103.28</v>
+        <v>96.69</v>
       </c>
       <c r="K49" t="n">
-        <v>6.62</v>
+        <v>11.45</v>
       </c>
       <c r="L49" t="n">
-        <v>0.328</v>
+        <v>0.2583</v>
       </c>
       <c r="M49" t="n">
-        <v>0.1589</v>
+        <v>0.1851</v>
       </c>
       <c r="N49" t="n">
-        <v>19.8</v>
+        <v>6.8</v>
       </c>
       <c r="O49" t="n">
-        <v>186</v>
+        <v>115</v>
       </c>
       <c r="P49" t="n">
-        <v>190</v>
+        <v>127</v>
       </c>
       <c r="Q49" t="n">
-        <v>187</v>
+        <v>148</v>
       </c>
       <c r="R49" t="n">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="S49" t="n">
-        <v>153</v>
+        <v>101</v>
       </c>
       <c r="T49" t="n">
-        <v>172</v>
+        <v>112</v>
       </c>
       <c r="U49" t="n">
-        <v>1407.8</v>
+        <v>1452.3</v>
       </c>
     </row>
     <row r="50">
@@ -4167,31 +4167,31 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G53" t="n">
-        <v>2262.9</v>
+        <v>2272.1</v>
       </c>
       <c r="H53" t="n">
-        <v>7.0872</v>
+        <v>6.8151</v>
       </c>
       <c r="I53" t="n">
         <v>121.14</v>
       </c>
       <c r="J53" t="n">
-        <v>96.66</v>
+        <v>97.11</v>
       </c>
       <c r="K53" t="n">
-        <v>24.48</v>
+        <v>24.03</v>
       </c>
       <c r="L53" t="n">
-        <v>0.2942</v>
+        <v>0.2925</v>
       </c>
       <c r="M53" t="n">
-        <v>0.151</v>
+        <v>0.1497</v>
       </c>
       <c r="N53" t="n">
-        <v>14.6</v>
+        <v>11</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -4212,7 +4212,7 @@
         <v>3</v>
       </c>
       <c r="U53" t="n">
-        <v>1758.1</v>
+        <v>1769.2</v>
       </c>
     </row>
     <row r="54">
@@ -4288,11 +4288,11 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1211</v>
+        <v>1438</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Gonzaga</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4309,52 +4309,52 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G55" t="n">
-        <v>2068.3</v>
+        <v>1964.3</v>
       </c>
       <c r="H55" t="n">
-        <v>5.8188</v>
+        <v>12.2076</v>
       </c>
       <c r="I55" t="n">
-        <v>120.75</v>
+        <v>119.04</v>
       </c>
       <c r="J55" t="n">
-        <v>93.89</v>
+        <v>100.85</v>
       </c>
       <c r="K55" t="n">
-        <v>26.86</v>
+        <v>18.19</v>
       </c>
       <c r="L55" t="n">
-        <v>0.2992</v>
+        <v>0.3154</v>
       </c>
       <c r="M55" t="n">
-        <v>0.1335</v>
+        <v>0.1544</v>
       </c>
       <c r="N55" t="n">
-        <v>11.8</v>
+        <v>6.8</v>
       </c>
       <c r="O55" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="P55" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="Q55" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="R55" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T55" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="U55" t="n">
-        <v>1601.3</v>
+        <v>1665.9</v>
       </c>
     </row>
     <row r="56">
@@ -4430,11 +4430,11 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1385</v>
+        <v>1458</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>St John's</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4451,52 +4451,52 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G57" t="n">
-        <v>1967.8</v>
+        <v>1882.4</v>
       </c>
       <c r="H57" t="n">
-        <v>5.6546</v>
+        <v>2.4266</v>
       </c>
       <c r="I57" t="n">
-        <v>114.06</v>
+        <v>118.8</v>
       </c>
       <c r="J57" t="n">
-        <v>98.84999999999999</v>
+        <v>108.53</v>
       </c>
       <c r="K57" t="n">
-        <v>15.21</v>
+        <v>10.27</v>
       </c>
       <c r="L57" t="n">
-        <v>0.3244</v>
+        <v>0.2776</v>
       </c>
       <c r="M57" t="n">
-        <v>0.1434</v>
+        <v>0.124</v>
       </c>
       <c r="N57" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="O57" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P57" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q57" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="R57" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="T57" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="U57" t="n">
-        <v>1677.1</v>
+        <v>1724.6</v>
       </c>
     </row>
     <row r="58">
@@ -4664,31 +4664,31 @@
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G60" t="n">
-        <v>1885.6</v>
+        <v>1897.5</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1404</v>
+        <v>0.1736</v>
       </c>
       <c r="I60" t="n">
-        <v>119.83</v>
+        <v>119.56</v>
       </c>
       <c r="J60" t="n">
-        <v>103.76</v>
+        <v>103.49</v>
       </c>
       <c r="K60" t="n">
-        <v>16.07</v>
+        <v>16.08</v>
       </c>
       <c r="L60" t="n">
-        <v>0.3026</v>
+        <v>0.3032</v>
       </c>
       <c r="M60" t="n">
-        <v>0.1501</v>
+        <v>0.1479</v>
       </c>
       <c r="N60" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="O60" t="n">
         <v>35</v>
@@ -4709,7 +4709,7 @@
         <v>29</v>
       </c>
       <c r="U60" t="n">
-        <v>1604.7</v>
+        <v>1611.4</v>
       </c>
     </row>
     <row r="61">
@@ -4998,11 +4998,11 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1270</v>
+        <v>1219</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>McNeese St</t>
+          <t>High Point</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5019,61 +5019,61 @@
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G65" t="n">
-        <v>1726.8</v>
+        <v>1625.5</v>
       </c>
       <c r="H65" t="n">
-        <v>2.6895</v>
+        <v>-0.8564000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>115.07</v>
+        <v>121.16</v>
       </c>
       <c r="J65" t="n">
-        <v>100.01</v>
+        <v>100.19</v>
       </c>
       <c r="K65" t="n">
-        <v>15.06</v>
+        <v>20.97</v>
       </c>
       <c r="L65" t="n">
-        <v>0.3483</v>
+        <v>0.3061</v>
       </c>
       <c r="M65" t="n">
-        <v>0.139</v>
+        <v>0.1276</v>
       </c>
       <c r="N65" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O65" t="n">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="P65" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="Q65" t="n">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="R65" t="n">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="S65" t="n">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="T65" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="U65" t="n">
-        <v>1428.4</v>
+        <v>1382.5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1220</v>
+        <v>1295</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Hofstra</t>
+          <t>N Dakota St</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5090,61 +5090,61 @@
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G66" t="n">
-        <v>1586.2</v>
+        <v>1593.8</v>
       </c>
       <c r="H66" t="n">
-        <v>3.3583</v>
+        <v>3.5257</v>
       </c>
       <c r="I66" t="n">
-        <v>113.56</v>
+        <v>114.28</v>
       </c>
       <c r="J66" t="n">
-        <v>102.69</v>
+        <v>102.18</v>
       </c>
       <c r="K66" t="n">
-        <v>10.87</v>
+        <v>12.1</v>
       </c>
       <c r="L66" t="n">
-        <v>0.3081</v>
+        <v>0.3104</v>
       </c>
       <c r="M66" t="n">
-        <v>0.1527</v>
+        <v>0.1506</v>
       </c>
       <c r="N66" t="n">
-        <v>12</v>
+        <v>10.8</v>
       </c>
       <c r="O66" t="n">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="P66" t="n">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="Q66" t="n">
-        <v>84</v>
+        <v>163</v>
       </c>
       <c r="R66" t="n">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="S66" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="T66" t="n">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="U66" t="n">
-        <v>1482.3</v>
+        <v>1410.6</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1414</v>
+        <v>1398</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>UC Irvine</t>
+          <t>Tennessee St</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5161,52 +5161,52 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="G67" t="n">
-        <v>1620.3</v>
+        <v>1466.9</v>
       </c>
       <c r="H67" t="n">
-        <v>2.2032</v>
+        <v>3.3618</v>
       </c>
       <c r="I67" t="n">
-        <v>104.72</v>
+        <v>109.9</v>
       </c>
       <c r="J67" t="n">
-        <v>96.98</v>
+        <v>103.28</v>
       </c>
       <c r="K67" t="n">
-        <v>7.74</v>
+        <v>6.62</v>
       </c>
       <c r="L67" t="n">
-        <v>0.2714</v>
+        <v>0.328</v>
       </c>
       <c r="M67" t="n">
-        <v>0.1714</v>
+        <v>0.1589</v>
       </c>
       <c r="N67" t="n">
-        <v>10.4</v>
+        <v>19.8</v>
       </c>
       <c r="O67" t="n">
-        <v>106</v>
+        <v>186</v>
       </c>
       <c r="P67" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="Q67" t="n">
-        <v>105</v>
+        <v>187</v>
       </c>
       <c r="R67" t="n">
-        <v>110</v>
+        <v>168</v>
       </c>
       <c r="S67" t="n">
-        <v>107</v>
+        <v>153</v>
       </c>
       <c r="T67" t="n">
-        <v>118</v>
+        <v>172</v>
       </c>
       <c r="U67" t="n">
-        <v>1473</v>
+        <v>1407.8</v>
       </c>
     </row>
     <row r="68">
@@ -5303,31 +5303,31 @@
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G69" t="n">
-        <v>1406</v>
+        <v>1407.8</v>
       </c>
       <c r="H69" t="n">
-        <v>3.0696</v>
+        <v>2.9318</v>
       </c>
       <c r="I69" t="n">
-        <v>108.81</v>
+        <v>109.06</v>
       </c>
       <c r="J69" t="n">
-        <v>97.94</v>
+        <v>98.31999999999999</v>
       </c>
       <c r="K69" t="n">
-        <v>10.87</v>
+        <v>10.75</v>
       </c>
       <c r="L69" t="n">
-        <v>0.3142</v>
+        <v>0.3191</v>
       </c>
       <c r="M69" t="n">
-        <v>0.1871</v>
+        <v>0.1856</v>
       </c>
       <c r="N69" t="n">
-        <v>20.6</v>
+        <v>15.4</v>
       </c>
       <c r="O69" t="n">
         <v>202</v>
@@ -5348,7 +5348,7 @@
         <v>202</v>
       </c>
       <c r="U69" t="n">
-        <v>1374.8</v>
+        <v>1372.4</v>
       </c>
     </row>
   </sheetData>

--- a/team_stats_2026.xlsx
+++ b/team_stats_2026.xlsx
@@ -596,11 +596,11 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1235</v>
+        <v>1163</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Iowa St</t>
+          <t>Connecticut</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,61 +617,61 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G3" t="n">
-        <v>2039</v>
+        <v>2050.7</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2111</v>
+        <v>7.1741</v>
       </c>
       <c r="I3" t="n">
-        <v>118.9</v>
+        <v>116.06</v>
       </c>
       <c r="J3" t="n">
-        <v>95.73</v>
+        <v>98.01000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>23.17</v>
+        <v>18.05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3217</v>
+        <v>0.3013</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1469</v>
+        <v>0.1603</v>
       </c>
       <c r="N3" t="n">
-        <v>14.8</v>
+        <v>3.8</v>
       </c>
       <c r="O3" t="n">
+        <v>11</v>
+      </c>
+      <c r="P3" t="n">
         <v>7</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
+        <v>21</v>
+      </c>
+      <c r="R3" t="n">
         <v>10</v>
       </c>
-      <c r="Q3" t="n">
-        <v>6</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6</v>
-      </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U3" t="n">
-        <v>1718</v>
+        <v>1670.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1228</v>
+        <v>1277</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>Michigan St</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,58 +691,58 @@
         <v>130</v>
       </c>
       <c r="G4" t="n">
-        <v>1982.7</v>
+        <v>2027.4</v>
       </c>
       <c r="H4" t="n">
-        <v>7.8712</v>
+        <v>0.218</v>
       </c>
       <c r="I4" t="n">
-        <v>125.11</v>
+        <v>117.66</v>
       </c>
       <c r="J4" t="n">
-        <v>103.66</v>
+        <v>102.12</v>
       </c>
       <c r="K4" t="n">
-        <v>21.45</v>
+        <v>15.54</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3222</v>
+        <v>0.2963</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1281</v>
+        <v>0.1607</v>
       </c>
       <c r="N4" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>10</v>
+      </c>
+      <c r="R4" t="n">
         <v>9</v>
       </c>
-      <c r="Q4" t="n">
-        <v>5</v>
-      </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>7</v>
       </c>
-      <c r="S4" t="n">
-        <v>12</v>
-      </c>
       <c r="T4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="U4" t="n">
-        <v>1717.2</v>
+        <v>1730.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1435</v>
+        <v>1242</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Vanderbilt</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -759,52 +759,52 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G5" t="n">
-        <v>1967.8</v>
+        <v>1973.7</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6985</v>
+        <v>10.346</v>
       </c>
       <c r="I5" t="n">
-        <v>122.92</v>
+        <v>109.9</v>
       </c>
       <c r="J5" t="n">
-        <v>106.35</v>
+        <v>101.51</v>
       </c>
       <c r="K5" t="n">
-        <v>16.57</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2937</v>
+        <v>0.2556</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1302</v>
+        <v>0.1512</v>
       </c>
       <c r="N5" t="n">
-        <v>3.4</v>
+        <v>-6.2</v>
       </c>
       <c r="O5" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="P5" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>14</v>
+      </c>
+      <c r="R5" t="n">
+        <v>18</v>
+      </c>
+      <c r="S5" t="n">
+        <v>16</v>
+      </c>
+      <c r="T5" t="n">
         <v>19</v>
       </c>
-      <c r="Q5" t="n">
-        <v>13</v>
-      </c>
-      <c r="R5" t="n">
-        <v>14</v>
-      </c>
-      <c r="S5" t="n">
-        <v>22</v>
-      </c>
-      <c r="T5" t="n">
-        <v>16</v>
-      </c>
       <c r="U5" t="n">
-        <v>1712.2</v>
+        <v>1791.1</v>
       </c>
     </row>
     <row r="6">
@@ -951,11 +951,11 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1246</v>
+        <v>1417</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>UCLA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -972,52 +972,52 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G8" t="n">
-        <v>1886.9</v>
+        <v>1874.2</v>
       </c>
       <c r="H8" t="n">
-        <v>4.7611</v>
+        <v>2.8463</v>
       </c>
       <c r="I8" t="n">
-        <v>115.76</v>
+        <v>117.18</v>
       </c>
       <c r="J8" t="n">
-        <v>106.05</v>
+        <v>107.51</v>
       </c>
       <c r="K8" t="n">
-        <v>9.710000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3106</v>
+        <v>0.3055</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1465</v>
+        <v>0.1325</v>
       </c>
       <c r="N8" t="n">
-        <v>-3</v>
+        <v>10.2</v>
       </c>
       <c r="O8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P8" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q8" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="R8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="S8" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="T8" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="U8" t="n">
-        <v>1734.8</v>
+        <v>1706.3</v>
       </c>
     </row>
     <row r="9">
@@ -1164,11 +1164,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1365</v>
+        <v>1416</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>UCF</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1185,61 +1185,61 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G11" t="n">
-        <v>1782.8</v>
+        <v>1828.6</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0374</v>
+        <v>5.8051</v>
       </c>
       <c r="I11" t="n">
-        <v>117.62</v>
+        <v>113</v>
       </c>
       <c r="J11" t="n">
-        <v>104.11</v>
+        <v>110.03</v>
       </c>
       <c r="K11" t="n">
-        <v>13.51</v>
+        <v>2.97</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3504</v>
+        <v>0.3147</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1498</v>
+        <v>0.1543</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="O11" t="n">
+        <v>53</v>
+      </c>
+      <c r="P11" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>57</v>
+      </c>
+      <c r="R11" t="n">
+        <v>46</v>
+      </c>
+      <c r="S11" t="n">
         <v>37</v>
       </c>
-      <c r="P11" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>46</v>
-      </c>
-      <c r="R11" t="n">
-        <v>36</v>
-      </c>
-      <c r="S11" t="n">
-        <v>36</v>
-      </c>
       <c r="T11" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="U11" t="n">
-        <v>1596.2</v>
+        <v>1712.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1281</v>
+        <v>1378</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>South Florida</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1249,68 +1249,68 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>11a</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G12" t="n">
-        <v>1747.8</v>
+        <v>1714.9</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.7576</v>
+        <v>9.035</v>
       </c>
       <c r="I12" t="n">
-        <v>114.92</v>
+        <v>116.33</v>
       </c>
       <c r="J12" t="n">
-        <v>109.48</v>
+        <v>101.48</v>
       </c>
       <c r="K12" t="n">
-        <v>5.45</v>
+        <v>14.84</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2996</v>
+        <v>0.3412</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1685</v>
+        <v>0.1466</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4</v>
+        <v>19.8</v>
       </c>
       <c r="O12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P12" t="n">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="Q12" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R12" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="S12" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="T12" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="U12" t="n">
-        <v>1658.3</v>
+        <v>1550.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1275</v>
+        <v>1320</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Miami OH</t>
+          <t>Northern Iowa</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1320,68 +1320,68 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>11b</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G13" t="n">
-        <v>1758.6</v>
+        <v>1573.9</v>
       </c>
       <c r="H13" t="n">
-        <v>9.362500000000001</v>
+        <v>-3.696</v>
       </c>
       <c r="I13" t="n">
-        <v>120.74</v>
+        <v>108.74</v>
       </c>
       <c r="J13" t="n">
-        <v>105.88</v>
+        <v>97.5</v>
       </c>
       <c r="K13" t="n">
-        <v>14.87</v>
+        <v>11.25</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2186</v>
+        <v>0.225</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1413</v>
+        <v>0.1354</v>
       </c>
       <c r="N13" t="n">
-        <v>2.4</v>
+        <v>14.4</v>
       </c>
       <c r="O13" t="n">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="P13" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="Q13" t="n">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="R13" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>95</v>
       </c>
       <c r="T13" t="n">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="U13" t="n">
-        <v>1416.9</v>
+        <v>1515.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1103</v>
+        <v>1465</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Cal Baptist</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E14" t="b">
@@ -1401,58 +1401,58 @@
         <v>131</v>
       </c>
       <c r="G14" t="n">
-        <v>1707.9</v>
+        <v>1607.9</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9745</v>
+        <v>1.5554</v>
       </c>
       <c r="I14" t="n">
-        <v>121.64</v>
+        <v>107.22</v>
       </c>
       <c r="J14" t="n">
-        <v>104.36</v>
+        <v>99.23999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>17.27</v>
+        <v>7.97</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2887</v>
+        <v>0.3287</v>
       </c>
       <c r="M14" t="n">
-        <v>0.15</v>
+        <v>0.1735</v>
       </c>
       <c r="N14" t="n">
-        <v>13</v>
+        <v>15.4</v>
       </c>
       <c r="O14" t="n">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="P14" t="n">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="Q14" t="n">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="R14" t="n">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="S14" t="n">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="T14" t="n">
-        <v>52</v>
+        <v>103</v>
       </c>
       <c r="U14" t="n">
-        <v>1479.2</v>
+        <v>1462.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1320</v>
+        <v>1295</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Northern Iowa</t>
+          <t>N Dakota St</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E15" t="b">
@@ -1472,58 +1472,58 @@
         <v>125</v>
       </c>
       <c r="G15" t="n">
-        <v>1573.9</v>
+        <v>1593.8</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.696</v>
+        <v>3.5257</v>
       </c>
       <c r="I15" t="n">
-        <v>108.74</v>
+        <v>114.28</v>
       </c>
       <c r="J15" t="n">
-        <v>97.5</v>
+        <v>102.18</v>
       </c>
       <c r="K15" t="n">
-        <v>11.25</v>
+        <v>12.1</v>
       </c>
       <c r="L15" t="n">
-        <v>0.225</v>
+        <v>0.3104</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1354</v>
+        <v>0.1506</v>
       </c>
       <c r="N15" t="n">
-        <v>14.4</v>
+        <v>10.8</v>
       </c>
       <c r="O15" t="n">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="P15" t="n">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="Q15" t="n">
-        <v>72</v>
+        <v>163</v>
       </c>
       <c r="R15" t="n">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="S15" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="T15" t="n">
-        <v>72</v>
+        <v>115</v>
       </c>
       <c r="U15" t="n">
-        <v>1515.8</v>
+        <v>1410.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1460</v>
+        <v>1202</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wright St</t>
+          <t>Furman</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1533,68 +1533,68 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E16" t="b">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G16" t="n">
-        <v>1470.5</v>
+        <v>1542.9</v>
       </c>
       <c r="H16" t="n">
-        <v>2.7419</v>
+        <v>0.8197</v>
       </c>
       <c r="I16" t="n">
-        <v>115.44</v>
+        <v>112.01</v>
       </c>
       <c r="J16" t="n">
-        <v>108.91</v>
+        <v>107.28</v>
       </c>
       <c r="K16" t="n">
-        <v>6.53</v>
+        <v>4.73</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2971</v>
+        <v>0.2562</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1569</v>
+        <v>0.171</v>
       </c>
       <c r="N16" t="n">
-        <v>10</v>
+        <v>5.6</v>
       </c>
       <c r="O16" t="n">
-        <v>144</v>
+        <v>199</v>
       </c>
       <c r="P16" t="n">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="Q16" t="n">
-        <v>125</v>
+        <v>193</v>
       </c>
       <c r="R16" t="n">
-        <v>136</v>
+        <v>189</v>
       </c>
       <c r="S16" t="n">
-        <v>138</v>
+        <v>192</v>
       </c>
       <c r="T16" t="n">
-        <v>133</v>
+        <v>194</v>
       </c>
       <c r="U16" t="n">
-        <v>1431.7</v>
+        <v>1422.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1202</v>
+        <v>1373</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Furman</t>
+          <t>Siena</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1604,139 +1604,139 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E17" t="b">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G17" t="n">
-        <v>1542.9</v>
+        <v>1478</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8197</v>
+        <v>0.9489</v>
       </c>
       <c r="I17" t="n">
-        <v>112.01</v>
+        <v>109.73</v>
       </c>
       <c r="J17" t="n">
-        <v>107.28</v>
+        <v>101.77</v>
       </c>
       <c r="K17" t="n">
-        <v>4.73</v>
+        <v>7.95</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2562</v>
+        <v>0.2799</v>
       </c>
       <c r="M17" t="n">
-        <v>0.171</v>
+        <v>0.1508</v>
       </c>
       <c r="N17" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="O17" t="n">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="P17" t="n">
-        <v>170</v>
+        <v>212</v>
       </c>
       <c r="Q17" t="n">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="R17" t="n">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="S17" t="n">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="T17" t="n">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="U17" t="n">
-        <v>1422.2</v>
+        <v>1430.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1254</v>
+        <v>1196</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LIU Brooklyn</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>01</t>
         </is>
       </c>
       <c r="E18" t="b">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G18" t="n">
-        <v>1418.2</v>
+        <v>2006.7</v>
       </c>
       <c r="H18" t="n">
-        <v>2.3581</v>
+        <v>3.4651</v>
       </c>
       <c r="I18" t="n">
-        <v>109.38</v>
+        <v>119.99</v>
       </c>
       <c r="J18" t="n">
-        <v>104.38</v>
+        <v>100.19</v>
       </c>
       <c r="K18" t="n">
-        <v>5</v>
+        <v>19.81</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3119</v>
+        <v>0.3342</v>
       </c>
       <c r="M18" t="n">
-        <v>0.183</v>
+        <v>0.1568</v>
       </c>
       <c r="N18" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="O18" t="n">
-        <v>217</v>
+        <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>228</v>
+        <v>4</v>
       </c>
       <c r="Q18" t="n">
-        <v>213</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>188</v>
+        <v>4</v>
       </c>
       <c r="S18" t="n">
-        <v>166</v>
+        <v>8</v>
       </c>
       <c r="T18" t="n">
-        <v>200</v>
+        <v>4</v>
       </c>
       <c r="U18" t="n">
-        <v>1378.8</v>
+        <v>1722.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1196</v>
+        <v>1222</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="E19" t="b">
@@ -1756,58 +1756,58 @@
         <v>131</v>
       </c>
       <c r="G19" t="n">
-        <v>2006.7</v>
+        <v>2111.7</v>
       </c>
       <c r="H19" t="n">
-        <v>3.4651</v>
+        <v>1.2196</v>
       </c>
       <c r="I19" t="n">
-        <v>119.99</v>
+        <v>117.35</v>
       </c>
       <c r="J19" t="n">
-        <v>100.19</v>
+        <v>95.8</v>
       </c>
       <c r="K19" t="n">
-        <v>19.81</v>
+        <v>21.55</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3342</v>
+        <v>0.3386</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1568</v>
+        <v>0.1236</v>
       </c>
       <c r="N19" t="n">
-        <v>13.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T19" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U19" t="n">
-        <v>1722.9</v>
+        <v>1742.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1222</v>
+        <v>1228</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1817,68 +1817,68 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="E20" t="b">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G20" t="n">
-        <v>2111.7</v>
+        <v>1982.7</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2196</v>
+        <v>7.8712</v>
       </c>
       <c r="I20" t="n">
-        <v>117.35</v>
+        <v>125.11</v>
       </c>
       <c r="J20" t="n">
-        <v>95.8</v>
+        <v>103.66</v>
       </c>
       <c r="K20" t="n">
-        <v>21.55</v>
+        <v>21.45</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3386</v>
+        <v>0.3222</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1236</v>
+        <v>0.1281</v>
       </c>
       <c r="N20" t="n">
-        <v>8.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="O20" t="n">
+        <v>5</v>
+      </c>
+      <c r="P20" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>5</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7</v>
+      </c>
+      <c r="S20" t="n">
+        <v>12</v>
+      </c>
+      <c r="T20" t="n">
         <v>6</v>
       </c>
-      <c r="P20" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>7</v>
-      </c>
-      <c r="R20" t="n">
-        <v>5</v>
-      </c>
-      <c r="S20" t="n">
-        <v>6</v>
-      </c>
-      <c r="T20" t="n">
-        <v>7</v>
-      </c>
       <c r="U20" t="n">
-        <v>1742.7</v>
+        <v>1717.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1345</v>
+        <v>1304</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Purdue</t>
+          <t>Nebraska</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1888,68 +1888,68 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="E21" t="b">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G21" t="n">
-        <v>1986.9</v>
+        <v>1982.9</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5973000000000001</v>
+        <v>9.932399999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>124.76</v>
+        <v>114.61</v>
       </c>
       <c r="J21" t="n">
-        <v>107.25</v>
+        <v>98.94</v>
       </c>
       <c r="K21" t="n">
-        <v>17.51</v>
+        <v>15.67</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3105</v>
+        <v>0.2433</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1343</v>
+        <v>0.1403</v>
       </c>
       <c r="N21" t="n">
-        <v>7.2</v>
+        <v>0.2</v>
       </c>
       <c r="O21" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P21" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>16</v>
+      </c>
+      <c r="R21" t="n">
+        <v>13</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="n">
         <v>12</v>
       </c>
-      <c r="Q21" t="n">
-        <v>8</v>
-      </c>
-      <c r="R21" t="n">
-        <v>8</v>
-      </c>
-      <c r="S21" t="n">
-        <v>13</v>
-      </c>
-      <c r="T21" t="n">
-        <v>10</v>
-      </c>
       <c r="U21" t="n">
-        <v>1754.6</v>
+        <v>1675.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1211</v>
+        <v>1435</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Gonzaga</t>
+          <t>Vanderbilt</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1959,68 +1959,68 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>05</t>
         </is>
       </c>
       <c r="E22" t="b">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G22" t="n">
-        <v>2068.3</v>
+        <v>1967.8</v>
       </c>
       <c r="H22" t="n">
-        <v>5.8188</v>
+        <v>1.6985</v>
       </c>
       <c r="I22" t="n">
-        <v>120.75</v>
+        <v>122.92</v>
       </c>
       <c r="J22" t="n">
-        <v>93.89</v>
+        <v>106.35</v>
       </c>
       <c r="K22" t="n">
-        <v>26.86</v>
+        <v>16.57</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2992</v>
+        <v>0.2937</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1335</v>
+        <v>0.1302</v>
       </c>
       <c r="N22" t="n">
-        <v>11.8</v>
+        <v>3.4</v>
       </c>
       <c r="O22" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="P22" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="Q22" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R22" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="T22" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="U22" t="n">
-        <v>1601.3</v>
+        <v>1712.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1403</v>
+        <v>1314</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Texas Tech</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>06</t>
         </is>
       </c>
       <c r="E23" t="b">
@@ -2040,58 +2040,58 @@
         <v>129</v>
       </c>
       <c r="G23" t="n">
-        <v>2010.7</v>
+        <v>1899.5</v>
       </c>
       <c r="H23" t="n">
-        <v>9.579599999999999</v>
+        <v>2.2848</v>
       </c>
       <c r="I23" t="n">
-        <v>117.2</v>
+        <v>115.28</v>
       </c>
       <c r="J23" t="n">
-        <v>106.7</v>
+        <v>103.72</v>
       </c>
       <c r="K23" t="n">
-        <v>10.5</v>
+        <v>11.56</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2893</v>
+        <v>0.2596</v>
       </c>
       <c r="M23" t="n">
-        <v>0.155</v>
+        <v>0.1375</v>
       </c>
       <c r="N23" t="n">
-        <v>-3</v>
+        <v>-0.4</v>
       </c>
       <c r="O23" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="P23" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="Q23" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="R23" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="S23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T23" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="U23" t="n">
-        <v>1772.3</v>
+        <v>1677.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1397</v>
+        <v>1388</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>St Mary's CA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2101,68 +2101,68 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>07</t>
         </is>
       </c>
       <c r="E24" t="b">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G24" t="n">
-        <v>1897.1</v>
+        <v>1857.8</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.4465</v>
+        <v>-0.2818</v>
       </c>
       <c r="I24" t="n">
-        <v>116.86</v>
+        <v>118.73</v>
       </c>
       <c r="J24" t="n">
-        <v>102.57</v>
+        <v>99.88</v>
       </c>
       <c r="K24" t="n">
-        <v>14.29</v>
+        <v>18.85</v>
       </c>
       <c r="L24" t="n">
-        <v>0.36</v>
+        <v>0.2975</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1643</v>
+        <v>0.1525</v>
       </c>
       <c r="N24" t="n">
-        <v>3.2</v>
+        <v>8.6</v>
       </c>
       <c r="O24" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="P24" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="Q24" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="R24" t="n">
+        <v>23</v>
+      </c>
+      <c r="S24" t="n">
+        <v>19</v>
+      </c>
+      <c r="T24" t="n">
         <v>20</v>
       </c>
-      <c r="S24" t="n">
-        <v>24</v>
-      </c>
-      <c r="T24" t="n">
-        <v>21</v>
-      </c>
       <c r="U24" t="n">
-        <v>1716.9</v>
+        <v>1596.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1388</v>
+        <v>1155</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>St Mary's CA</t>
+          <t>Clemson</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2172,68 +2172,68 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>08</t>
         </is>
       </c>
       <c r="E25" t="b">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G25" t="n">
-        <v>1857.8</v>
+        <v>1859.5</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.2818</v>
+        <v>2.557</v>
       </c>
       <c r="I25" t="n">
-        <v>118.73</v>
+        <v>112.59</v>
       </c>
       <c r="J25" t="n">
-        <v>99.88</v>
+        <v>101.68</v>
       </c>
       <c r="K25" t="n">
-        <v>18.85</v>
+        <v>10.91</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2975</v>
+        <v>0.2554</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1525</v>
+        <v>0.136</v>
       </c>
       <c r="N25" t="n">
-        <v>8.6</v>
+        <v>-0.6</v>
       </c>
       <c r="O25" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="P25" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="Q25" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="R25" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="S25" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="T25" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="U25" t="n">
-        <v>1596.9</v>
+        <v>1672.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1155</v>
+        <v>1234</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Clemson</t>
+          <t>Iowa</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2243,68 +2243,68 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>09</t>
         </is>
       </c>
       <c r="E26" t="b">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G26" t="n">
-        <v>1859.5</v>
+        <v>1831.8</v>
       </c>
       <c r="H26" t="n">
-        <v>2.557</v>
+        <v>3.3952</v>
       </c>
       <c r="I26" t="n">
-        <v>112.59</v>
+        <v>118.92</v>
       </c>
       <c r="J26" t="n">
-        <v>101.68</v>
+        <v>104.81</v>
       </c>
       <c r="K26" t="n">
-        <v>10.91</v>
+        <v>14.12</v>
       </c>
       <c r="L26" t="n">
-        <v>0.2554</v>
+        <v>0.2886</v>
       </c>
       <c r="M26" t="n">
-        <v>0.136</v>
+        <v>0.1455</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.6</v>
+        <v>-1.2</v>
       </c>
       <c r="O26" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="P26" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q26" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="R26" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="S26" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="T26" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="U26" t="n">
-        <v>1672.9</v>
+        <v>1712.2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1437</v>
+        <v>1401</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Villanova</t>
+          <t>Texas A&amp;M</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E27" t="b">
@@ -2324,58 +2324,58 @@
         <v>129</v>
       </c>
       <c r="G27" t="n">
-        <v>1806.3</v>
+        <v>1824</v>
       </c>
       <c r="H27" t="n">
-        <v>5.8793</v>
+        <v>4.3608</v>
       </c>
       <c r="I27" t="n">
-        <v>114.59</v>
+        <v>117.14</v>
       </c>
       <c r="J27" t="n">
-        <v>104.94</v>
+        <v>107.43</v>
       </c>
       <c r="K27" t="n">
-        <v>9.66</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>0.313</v>
+        <v>0.3098</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1447</v>
+        <v>0.1389</v>
       </c>
       <c r="N27" t="n">
-        <v>-1</v>
+        <v>-5.4</v>
       </c>
       <c r="O27" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P27" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="Q27" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="R27" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="S27" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="T27" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="U27" t="n">
-        <v>1641.5</v>
+        <v>1653.7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1401</v>
+        <v>1433</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Texas A&amp;M</t>
+          <t>VCU</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2385,68 +2385,68 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E28" t="b">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G28" t="n">
-        <v>1824</v>
+        <v>1751</v>
       </c>
       <c r="H28" t="n">
-        <v>4.3608</v>
+        <v>3.1884</v>
       </c>
       <c r="I28" t="n">
-        <v>117.14</v>
+        <v>118.3</v>
       </c>
       <c r="J28" t="n">
-        <v>107.43</v>
+        <v>103.55</v>
       </c>
       <c r="K28" t="n">
-        <v>9.699999999999999</v>
+        <v>14.75</v>
       </c>
       <c r="L28" t="n">
-        <v>0.3098</v>
+        <v>0.2988</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1389</v>
+        <v>0.1491</v>
       </c>
       <c r="N28" t="n">
-        <v>-5.4</v>
+        <v>9.6</v>
       </c>
       <c r="O28" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="P28" t="n">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="Q28" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="R28" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="S28" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T28" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="U28" t="n">
-        <v>1653.7</v>
+        <v>1553.9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1433</v>
+        <v>1270</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VCU</t>
+          <t>McNeese St</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2456,68 +2456,68 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E29" t="b">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G29" t="n">
-        <v>1751</v>
+        <v>1726.8</v>
       </c>
       <c r="H29" t="n">
-        <v>3.1884</v>
+        <v>2.6895</v>
       </c>
       <c r="I29" t="n">
-        <v>118.3</v>
+        <v>115.07</v>
       </c>
       <c r="J29" t="n">
-        <v>103.55</v>
+        <v>100.01</v>
       </c>
       <c r="K29" t="n">
-        <v>14.75</v>
+        <v>15.06</v>
       </c>
       <c r="L29" t="n">
-        <v>0.2988</v>
+        <v>0.3483</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1491</v>
+        <v>0.139</v>
       </c>
       <c r="N29" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O29" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="P29" t="n">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="Q29" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="R29" t="n">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="S29" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="T29" t="n">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="U29" t="n">
-        <v>1553.9</v>
+        <v>1428.4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1463</v>
+        <v>1407</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Yale</t>
+          <t>Troy</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2527,68 +2527,68 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E30" t="b">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="G30" t="n">
-        <v>1727.4</v>
+        <v>1601</v>
       </c>
       <c r="H30" t="n">
-        <v>1.0257</v>
+        <v>1.1284</v>
       </c>
       <c r="I30" t="n">
-        <v>122.21</v>
+        <v>112.28</v>
       </c>
       <c r="J30" t="n">
-        <v>108.54</v>
+        <v>106.19</v>
       </c>
       <c r="K30" t="n">
-        <v>13.66</v>
+        <v>6.08</v>
       </c>
       <c r="L30" t="n">
-        <v>0.2923</v>
+        <v>0.316</v>
       </c>
       <c r="M30" t="n">
-        <v>0.1356</v>
+        <v>0.1667</v>
       </c>
       <c r="N30" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="O30" t="n">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="P30" t="n">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="Q30" t="n">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="R30" t="n">
-        <v>72</v>
+        <v>137</v>
       </c>
       <c r="S30" t="n">
-        <v>62</v>
+        <v>124</v>
       </c>
       <c r="T30" t="n">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="U30" t="n">
-        <v>1459.8</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1220</v>
+        <v>1335</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Hofstra</t>
+          <t>Penn</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2598,68 +2598,68 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E31" t="b">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G31" t="n">
-        <v>1586.2</v>
+        <v>1431.7</v>
       </c>
       <c r="H31" t="n">
-        <v>3.3583</v>
+        <v>1.1135</v>
       </c>
       <c r="I31" t="n">
-        <v>113.56</v>
+        <v>107.49</v>
       </c>
       <c r="J31" t="n">
-        <v>102.69</v>
+        <v>105.83</v>
       </c>
       <c r="K31" t="n">
-        <v>10.87</v>
+        <v>1.66</v>
       </c>
       <c r="L31" t="n">
-        <v>0.3081</v>
+        <v>0.3084</v>
       </c>
       <c r="M31" t="n">
-        <v>0.1527</v>
+        <v>0.1543</v>
       </c>
       <c r="N31" t="n">
-        <v>12</v>
+        <v>6.2</v>
       </c>
       <c r="O31" t="n">
-        <v>84</v>
+        <v>163</v>
       </c>
       <c r="P31" t="n">
-        <v>125</v>
+        <v>167</v>
       </c>
       <c r="Q31" t="n">
-        <v>84</v>
+        <v>147</v>
       </c>
       <c r="R31" t="n">
-        <v>88</v>
+        <v>147</v>
       </c>
       <c r="S31" t="n">
-        <v>92</v>
+        <v>141</v>
       </c>
       <c r="T31" t="n">
-        <v>88</v>
+        <v>148</v>
       </c>
       <c r="U31" t="n">
-        <v>1482.3</v>
+        <v>1482.7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1407</v>
+        <v>1225</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Troy</t>
+          <t>Idaho</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2669,68 +2669,68 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E32" t="b">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G32" t="n">
-        <v>1601</v>
+        <v>1410</v>
       </c>
       <c r="H32" t="n">
-        <v>1.1284</v>
+        <v>-0.3498</v>
       </c>
       <c r="I32" t="n">
-        <v>112.28</v>
+        <v>110.28</v>
       </c>
       <c r="J32" t="n">
-        <v>106.19</v>
+        <v>106.53</v>
       </c>
       <c r="K32" t="n">
-        <v>6.08</v>
+        <v>3.75</v>
       </c>
       <c r="L32" t="n">
-        <v>0.316</v>
+        <v>0.2693</v>
       </c>
       <c r="M32" t="n">
-        <v>0.1667</v>
+        <v>0.1475</v>
       </c>
       <c r="N32" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="O32" t="n">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="P32" t="n">
-        <v>130</v>
+        <v>184</v>
       </c>
       <c r="Q32" t="n">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c r="R32" t="n">
-        <v>137</v>
+        <v>180</v>
       </c>
       <c r="S32" t="n">
-        <v>124</v>
+        <v>184</v>
       </c>
       <c r="T32" t="n">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="U32" t="n">
-        <v>1466</v>
+        <v>1415.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1420</v>
+        <v>1341</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>UMBC</t>
+          <t>Prairie View</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2740,68 +2740,68 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16a</t>
         </is>
       </c>
       <c r="E33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
         <v>131</v>
       </c>
       <c r="G33" t="n">
-        <v>1397.9</v>
+        <v>1266.7</v>
       </c>
       <c r="H33" t="n">
-        <v>1.3468</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>113.39</v>
+        <v>104.38</v>
       </c>
       <c r="J33" t="n">
-        <v>101.92</v>
+        <v>107.11</v>
       </c>
       <c r="K33" t="n">
-        <v>11.47</v>
+        <v>-2.73</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2176</v>
+        <v>0.2878</v>
       </c>
       <c r="M33" t="n">
-        <v>0.135</v>
+        <v>0.1551</v>
       </c>
       <c r="N33" t="n">
-        <v>23</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O33" t="n">
-        <v>198</v>
+        <v>312</v>
       </c>
       <c r="P33" t="n">
-        <v>225</v>
+        <v>330</v>
       </c>
       <c r="Q33" t="n">
-        <v>191</v>
+        <v>303</v>
       </c>
       <c r="R33" t="n">
-        <v>194</v>
+        <v>306</v>
       </c>
       <c r="S33" t="n">
-        <v>197</v>
+        <v>325</v>
       </c>
       <c r="T33" t="n">
-        <v>205</v>
+        <v>316</v>
       </c>
       <c r="U33" t="n">
-        <v>1369.1</v>
+        <v>1383.4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1244</v>
+        <v>1250</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kennesaw</t>
+          <t>Lehigh</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2811,139 +2811,139 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>16a</t>
+          <t>16b</t>
         </is>
       </c>
       <c r="E34" t="b">
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G34" t="n">
-        <v>1521.3</v>
+        <v>1325.5</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.1615</v>
+        <v>-0.465</v>
       </c>
       <c r="I34" t="n">
-        <v>111.12</v>
+        <v>105.58</v>
       </c>
       <c r="J34" t="n">
-        <v>108.1</v>
+        <v>108.39</v>
       </c>
       <c r="K34" t="n">
-        <v>3.02</v>
+        <v>-2.8</v>
       </c>
       <c r="L34" t="n">
-        <v>0.345</v>
+        <v>0.2229</v>
       </c>
       <c r="M34" t="n">
-        <v>0.165</v>
+        <v>0.1707</v>
       </c>
       <c r="N34" t="n">
-        <v>3.2</v>
+        <v>7.8</v>
       </c>
       <c r="O34" t="n">
-        <v>178</v>
+        <v>290</v>
       </c>
       <c r="P34" t="n">
-        <v>159</v>
+        <v>295</v>
       </c>
       <c r="Q34" t="n">
-        <v>149</v>
+        <v>279</v>
       </c>
       <c r="R34" t="n">
-        <v>184</v>
+        <v>282</v>
       </c>
       <c r="S34" t="n">
-        <v>170</v>
+        <v>268</v>
       </c>
       <c r="T34" t="n">
-        <v>170</v>
+        <v>282</v>
       </c>
       <c r="U34" t="n">
-        <v>1474.6</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1341</v>
+        <v>1276</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Prairie View</t>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>MW</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>16b</t>
+          <t>01</t>
         </is>
       </c>
       <c r="E35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
         <v>131</v>
       </c>
       <c r="G35" t="n">
-        <v>1266.7</v>
+        <v>2196.8</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.5639999999999999</v>
+        <v>6.739</v>
       </c>
       <c r="I35" t="n">
-        <v>104.38</v>
+        <v>120.64</v>
       </c>
       <c r="J35" t="n">
-        <v>107.11</v>
+        <v>95.94</v>
       </c>
       <c r="K35" t="n">
-        <v>-2.73</v>
+        <v>24.71</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2878</v>
+        <v>0.2604</v>
       </c>
       <c r="M35" t="n">
-        <v>0.1551</v>
+        <v>0.1666</v>
       </c>
       <c r="N35" t="n">
-        <v>9.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="O35" t="n">
-        <v>312</v>
+        <v>2</v>
       </c>
       <c r="P35" t="n">
-        <v>330</v>
+        <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>303</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>306</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
-        <v>325</v>
+        <v>3</v>
       </c>
       <c r="T35" t="n">
-        <v>316</v>
+        <v>2</v>
       </c>
       <c r="U35" t="n">
-        <v>1383.4</v>
+        <v>1772.9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1276</v>
+        <v>1235</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Iowa St</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2953,68 +2953,68 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="E36" t="b">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G36" t="n">
-        <v>2196.8</v>
+        <v>2039</v>
       </c>
       <c r="H36" t="n">
-        <v>6.739</v>
+        <v>2.2111</v>
       </c>
       <c r="I36" t="n">
-        <v>120.64</v>
+        <v>118.9</v>
       </c>
       <c r="J36" t="n">
-        <v>95.94</v>
+        <v>95.73</v>
       </c>
       <c r="K36" t="n">
-        <v>24.71</v>
+        <v>23.17</v>
       </c>
       <c r="L36" t="n">
-        <v>0.2604</v>
+        <v>0.3217</v>
       </c>
       <c r="M36" t="n">
-        <v>0.1666</v>
+        <v>0.1469</v>
       </c>
       <c r="N36" t="n">
-        <v>6.8</v>
+        <v>14.8</v>
       </c>
       <c r="O36" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="P36" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R36" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T36" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U36" t="n">
-        <v>1772.9</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1163</v>
+        <v>1438</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Connecticut</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="E37" t="b">
@@ -3034,58 +3034,58 @@
         <v>131</v>
       </c>
       <c r="G37" t="n">
-        <v>2050.7</v>
+        <v>1964.3</v>
       </c>
       <c r="H37" t="n">
-        <v>7.1741</v>
+        <v>12.2076</v>
       </c>
       <c r="I37" t="n">
-        <v>116.06</v>
+        <v>119.04</v>
       </c>
       <c r="J37" t="n">
-        <v>98.01000000000001</v>
+        <v>100.85</v>
       </c>
       <c r="K37" t="n">
-        <v>18.05</v>
+        <v>18.19</v>
       </c>
       <c r="L37" t="n">
-        <v>0.3013</v>
+        <v>0.3154</v>
       </c>
       <c r="M37" t="n">
-        <v>0.1603</v>
+        <v>0.1544</v>
       </c>
       <c r="N37" t="n">
-        <v>3.8</v>
+        <v>6.8</v>
       </c>
       <c r="O37" t="n">
+        <v>20</v>
+      </c>
+      <c r="P37" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q37" t="n">
         <v>11</v>
       </c>
-      <c r="P37" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>21</v>
-      </c>
       <c r="R37" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T37" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="U37" t="n">
-        <v>1670.2</v>
+        <v>1665.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1304</v>
+        <v>1104</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nebraska</t>
+          <t>Alabama</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="E38" t="b">
@@ -3105,58 +3105,58 @@
         <v>130</v>
       </c>
       <c r="G38" t="n">
-        <v>1982.9</v>
+        <v>1949.3</v>
       </c>
       <c r="H38" t="n">
-        <v>9.932399999999999</v>
+        <v>-1.3255</v>
       </c>
       <c r="I38" t="n">
-        <v>114.61</v>
+        <v>121.37</v>
       </c>
       <c r="J38" t="n">
-        <v>98.94</v>
+        <v>110.6</v>
       </c>
       <c r="K38" t="n">
-        <v>15.67</v>
+        <v>10.77</v>
       </c>
       <c r="L38" t="n">
-        <v>0.2433</v>
+        <v>0.2809</v>
       </c>
       <c r="M38" t="n">
-        <v>0.1403</v>
+        <v>0.1288</v>
       </c>
       <c r="N38" t="n">
-        <v>0.2</v>
+        <v>5.6</v>
       </c>
       <c r="O38" t="n">
+        <v>15</v>
+      </c>
+      <c r="P38" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q38" t="n">
         <v>12</v>
       </c>
-      <c r="P38" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>16</v>
-      </c>
       <c r="R38" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T38" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="U38" t="n">
-        <v>1675.8</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1242</v>
+        <v>1403</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Texas Tech</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3166,68 +3166,68 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>05</t>
         </is>
       </c>
       <c r="E39" t="b">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G39" t="n">
-        <v>1973.7</v>
+        <v>2010.7</v>
       </c>
       <c r="H39" t="n">
-        <v>10.346</v>
+        <v>9.579599999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>109.9</v>
+        <v>117.2</v>
       </c>
       <c r="J39" t="n">
-        <v>101.51</v>
+        <v>106.7</v>
       </c>
       <c r="K39" t="n">
-        <v>8.390000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="L39" t="n">
-        <v>0.2556</v>
+        <v>0.2893</v>
       </c>
       <c r="M39" t="n">
-        <v>0.1512</v>
+        <v>0.155</v>
       </c>
       <c r="N39" t="n">
-        <v>-6.2</v>
+        <v>-3</v>
       </c>
       <c r="O39" t="n">
+        <v>17</v>
+      </c>
+      <c r="P39" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q39" t="n">
         <v>19</v>
       </c>
-      <c r="P39" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>14</v>
-      </c>
       <c r="R39" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="S39" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T39" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="U39" t="n">
-        <v>1791.1</v>
+        <v>1772.3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1116</v>
+        <v>1397</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3237,68 +3237,68 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>06</t>
         </is>
       </c>
       <c r="E40" t="b">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G40" t="n">
-        <v>1961.7</v>
+        <v>1897.1</v>
       </c>
       <c r="H40" t="n">
-        <v>5.2535</v>
+        <v>-1.4465</v>
       </c>
       <c r="I40" t="n">
-        <v>122.84</v>
+        <v>116.86</v>
       </c>
       <c r="J40" t="n">
-        <v>109.47</v>
+        <v>102.57</v>
       </c>
       <c r="K40" t="n">
-        <v>13.37</v>
+        <v>14.29</v>
       </c>
       <c r="L40" t="n">
-        <v>0.3045</v>
+        <v>0.36</v>
       </c>
       <c r="M40" t="n">
-        <v>0.1197</v>
+        <v>0.1643</v>
       </c>
       <c r="N40" t="n">
-        <v>-0.8</v>
+        <v>3.2</v>
       </c>
       <c r="O40" t="n">
+        <v>14</v>
+      </c>
+      <c r="P40" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q40" t="n">
         <v>18</v>
       </c>
-      <c r="P40" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
         <v>20</v>
       </c>
-      <c r="R40" t="n">
-        <v>16</v>
-      </c>
       <c r="S40" t="n">
+        <v>24</v>
+      </c>
+      <c r="T40" t="n">
         <v>21</v>
       </c>
-      <c r="T40" t="n">
-        <v>18</v>
-      </c>
       <c r="U40" t="n">
-        <v>1726.7</v>
+        <v>1716.9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1314</v>
+        <v>1246</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3308,68 +3308,68 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>07</t>
         </is>
       </c>
       <c r="E41" t="b">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G41" t="n">
-        <v>1899.5</v>
+        <v>1886.9</v>
       </c>
       <c r="H41" t="n">
-        <v>2.2848</v>
+        <v>4.7611</v>
       </c>
       <c r="I41" t="n">
-        <v>115.28</v>
+        <v>115.76</v>
       </c>
       <c r="J41" t="n">
-        <v>103.72</v>
+        <v>106.05</v>
       </c>
       <c r="K41" t="n">
-        <v>11.56</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2596</v>
+        <v>0.3106</v>
       </c>
       <c r="M41" t="n">
-        <v>0.1375</v>
+        <v>0.1465</v>
       </c>
       <c r="N41" t="n">
-        <v>-0.4</v>
+        <v>-3</v>
       </c>
       <c r="O41" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P41" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q41" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="R41" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="S41" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="T41" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="U41" t="n">
-        <v>1677.4</v>
+        <v>1734.8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1417</v>
+        <v>1208</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>UCLA</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3379,68 +3379,68 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>08</t>
         </is>
       </c>
       <c r="E42" t="b">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G42" t="n">
-        <v>1874.2</v>
+        <v>1798.1</v>
       </c>
       <c r="H42" t="n">
-        <v>2.8463</v>
+        <v>0.2861</v>
       </c>
       <c r="I42" t="n">
-        <v>117.18</v>
+        <v>119.92</v>
       </c>
       <c r="J42" t="n">
-        <v>107.51</v>
+        <v>106.59</v>
       </c>
       <c r="K42" t="n">
-        <v>9.67</v>
+        <v>13.33</v>
       </c>
       <c r="L42" t="n">
-        <v>0.3055</v>
+        <v>0.3181</v>
       </c>
       <c r="M42" t="n">
-        <v>0.1325</v>
+        <v>0.141</v>
       </c>
       <c r="N42" t="n">
-        <v>10.2</v>
+        <v>4.6</v>
       </c>
       <c r="O42" t="n">
+        <v>31</v>
+      </c>
+      <c r="P42" t="n">
         <v>28</v>
       </c>
-      <c r="P42" t="n">
-        <v>29</v>
-      </c>
       <c r="Q42" t="n">
+        <v>28</v>
+      </c>
+      <c r="R42" t="n">
+        <v>27</v>
+      </c>
+      <c r="S42" t="n">
+        <v>32</v>
+      </c>
+      <c r="T42" t="n">
         <v>31</v>
       </c>
-      <c r="R42" t="n">
-        <v>34</v>
-      </c>
-      <c r="S42" t="n">
-        <v>33</v>
-      </c>
-      <c r="T42" t="n">
-        <v>34</v>
-      </c>
       <c r="U42" t="n">
-        <v>1706.3</v>
+        <v>1643.1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1208</v>
+        <v>1387</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>St Louis</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3450,68 +3450,68 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>09</t>
         </is>
       </c>
       <c r="E43" t="b">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G43" t="n">
-        <v>1798.1</v>
+        <v>1793.2</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2861</v>
+        <v>8.666399999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>119.92</v>
+        <v>120</v>
       </c>
       <c r="J43" t="n">
-        <v>106.59</v>
+        <v>98.73</v>
       </c>
       <c r="K43" t="n">
-        <v>13.33</v>
+        <v>21.28</v>
       </c>
       <c r="L43" t="n">
-        <v>0.3181</v>
+        <v>0.2418</v>
       </c>
       <c r="M43" t="n">
-        <v>0.141</v>
+        <v>0.1658</v>
       </c>
       <c r="N43" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="O43" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="P43" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>36</v>
+      </c>
+      <c r="R43" t="n">
+        <v>30</v>
+      </c>
+      <c r="S43" t="n">
         <v>28</v>
       </c>
-      <c r="Q43" t="n">
-        <v>28</v>
-      </c>
-      <c r="R43" t="n">
+      <c r="T43" t="n">
         <v>27</v>
       </c>
-      <c r="S43" t="n">
-        <v>32</v>
-      </c>
-      <c r="T43" t="n">
-        <v>31</v>
-      </c>
       <c r="U43" t="n">
-        <v>1643.1</v>
+        <v>1516.9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1387</v>
+        <v>1365</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>St Louis</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3521,68 +3521,68 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E44" t="b">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="G44" t="n">
-        <v>1793.2</v>
+        <v>1782.8</v>
       </c>
       <c r="H44" t="n">
-        <v>8.666399999999999</v>
+        <v>0.0374</v>
       </c>
       <c r="I44" t="n">
-        <v>120</v>
+        <v>117.62</v>
       </c>
       <c r="J44" t="n">
-        <v>98.73</v>
+        <v>104.11</v>
       </c>
       <c r="K44" t="n">
-        <v>21.28</v>
+        <v>13.51</v>
       </c>
       <c r="L44" t="n">
-        <v>0.2418</v>
+        <v>0.3504</v>
       </c>
       <c r="M44" t="n">
-        <v>0.1658</v>
+        <v>0.1498</v>
       </c>
       <c r="N44" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="O44" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="P44" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q44" t="n">
         <v>46</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>36</v>
       </c>
-      <c r="R44" t="n">
-        <v>30</v>
-      </c>
       <c r="S44" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="T44" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="U44" t="n">
-        <v>1516.9</v>
+        <v>1596.2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1301</v>
+        <v>1275</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NC State</t>
+          <t>Miami OH</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3592,68 +3592,68 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11a</t>
         </is>
       </c>
       <c r="E45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
         <v>129</v>
       </c>
       <c r="G45" t="n">
-        <v>1734</v>
+        <v>1758.6</v>
       </c>
       <c r="H45" t="n">
-        <v>6.962</v>
+        <v>9.362500000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>119.36</v>
+        <v>120.74</v>
       </c>
       <c r="J45" t="n">
-        <v>109.32</v>
+        <v>105.88</v>
       </c>
       <c r="K45" t="n">
-        <v>10.04</v>
+        <v>14.87</v>
       </c>
       <c r="L45" t="n">
-        <v>0.2802</v>
+        <v>0.2186</v>
       </c>
       <c r="M45" t="n">
-        <v>0.1288</v>
+        <v>0.1413</v>
       </c>
       <c r="N45" t="n">
-        <v>-6.6</v>
+        <v>2.4</v>
       </c>
       <c r="O45" t="n">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="P45" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q45" t="n">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="R45" t="n">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="S45" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="T45" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="U45" t="n">
-        <v>1681.7</v>
+        <v>1416.9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1378</v>
+        <v>1374</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>South Florida</t>
+          <t>SMU</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3663,68 +3663,68 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>11b</t>
         </is>
       </c>
       <c r="E46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G46" t="n">
-        <v>1714.9</v>
+        <v>1733.9</v>
       </c>
       <c r="H46" t="n">
-        <v>9.035</v>
+        <v>0.2411</v>
       </c>
       <c r="I46" t="n">
-        <v>116.33</v>
+        <v>117.96</v>
       </c>
       <c r="J46" t="n">
-        <v>101.48</v>
+        <v>109.76</v>
       </c>
       <c r="K46" t="n">
-        <v>14.84</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>0.3412</v>
+        <v>0.3098</v>
       </c>
       <c r="M46" t="n">
-        <v>0.1466</v>
+        <v>0.1542</v>
       </c>
       <c r="N46" t="n">
-        <v>19.8</v>
+        <v>-5.6</v>
       </c>
       <c r="O46" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="P46" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="Q46" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="R46" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="S46" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="T46" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="U46" t="n">
-        <v>1550.3</v>
+        <v>1649.8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1270</v>
+        <v>1103</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>McNeese St</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3741,61 +3741,61 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G47" t="n">
-        <v>1726.8</v>
+        <v>1707.9</v>
       </c>
       <c r="H47" t="n">
-        <v>2.6895</v>
+        <v>1.9745</v>
       </c>
       <c r="I47" t="n">
-        <v>115.07</v>
+        <v>121.64</v>
       </c>
       <c r="J47" t="n">
-        <v>100.01</v>
+        <v>104.36</v>
       </c>
       <c r="K47" t="n">
-        <v>15.06</v>
+        <v>17.27</v>
       </c>
       <c r="L47" t="n">
-        <v>0.3483</v>
+        <v>0.2887</v>
       </c>
       <c r="M47" t="n">
-        <v>0.139</v>
+        <v>0.15</v>
       </c>
       <c r="N47" t="n">
-        <v>8.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="O47" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="P47" t="n">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="Q47" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="R47" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="S47" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="T47" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="U47" t="n">
-        <v>1428.4</v>
+        <v>1479.2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1465</v>
+        <v>1220</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cal Baptist</t>
+          <t>Hofstra</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3812,61 +3812,61 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="G48" t="n">
-        <v>1607.9</v>
+        <v>1586.2</v>
       </c>
       <c r="H48" t="n">
-        <v>1.5554</v>
+        <v>3.3583</v>
       </c>
       <c r="I48" t="n">
-        <v>107.22</v>
+        <v>113.56</v>
       </c>
       <c r="J48" t="n">
-        <v>99.23999999999999</v>
+        <v>102.69</v>
       </c>
       <c r="K48" t="n">
-        <v>7.97</v>
+        <v>10.87</v>
       </c>
       <c r="L48" t="n">
-        <v>0.3287</v>
+        <v>0.3081</v>
       </c>
       <c r="M48" t="n">
-        <v>0.1735</v>
+        <v>0.1527</v>
       </c>
       <c r="N48" t="n">
-        <v>15.4</v>
+        <v>12</v>
       </c>
       <c r="O48" t="n">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="P48" t="n">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="Q48" t="n">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="R48" t="n">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="S48" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="T48" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="U48" t="n">
-        <v>1462.4</v>
+        <v>1482.3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1218</v>
+        <v>1460</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Hawaii</t>
+          <t>Wright St</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3883,61 +3883,61 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="G49" t="n">
-        <v>1549.1</v>
+        <v>1470.5</v>
       </c>
       <c r="H49" t="n">
-        <v>2.9832</v>
+        <v>2.7419</v>
       </c>
       <c r="I49" t="n">
-        <v>108.14</v>
+        <v>115.44</v>
       </c>
       <c r="J49" t="n">
-        <v>96.69</v>
+        <v>108.91</v>
       </c>
       <c r="K49" t="n">
-        <v>11.45</v>
+        <v>6.53</v>
       </c>
       <c r="L49" t="n">
-        <v>0.2583</v>
+        <v>0.2971</v>
       </c>
       <c r="M49" t="n">
-        <v>0.1851</v>
+        <v>0.1569</v>
       </c>
       <c r="N49" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="O49" t="n">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="P49" t="n">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="Q49" t="n">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="R49" t="n">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="S49" t="n">
-        <v>101</v>
+        <v>138</v>
       </c>
       <c r="T49" t="n">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="U49" t="n">
-        <v>1452.3</v>
+        <v>1431.7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1474</v>
+        <v>1398</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Queens NC</t>
+          <t>Tennessee St</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3954,61 +3954,61 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G50" t="n">
-        <v>1427.4</v>
+        <v>1466.9</v>
       </c>
       <c r="H50" t="n">
-        <v>1.0039</v>
+        <v>3.3618</v>
       </c>
       <c r="I50" t="n">
-        <v>119.17</v>
+        <v>109.9</v>
       </c>
       <c r="J50" t="n">
-        <v>116.56</v>
+        <v>103.28</v>
       </c>
       <c r="K50" t="n">
-        <v>2.61</v>
+        <v>6.62</v>
       </c>
       <c r="L50" t="n">
-        <v>0.2859</v>
+        <v>0.328</v>
       </c>
       <c r="M50" t="n">
-        <v>0.1441</v>
+        <v>0.1589</v>
       </c>
       <c r="N50" t="n">
-        <v>6.4</v>
+        <v>19.8</v>
       </c>
       <c r="O50" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="P50" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="Q50" t="n">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="R50" t="n">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="S50" t="n">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="T50" t="n">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="U50" t="n">
-        <v>1430.9</v>
+        <v>1407.8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1250</v>
+        <v>1420</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Lehigh</t>
+          <t>UMBC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4025,61 +4025,61 @@
         <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G51" t="n">
-        <v>1325.5</v>
+        <v>1397.9</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.465</v>
+        <v>1.3468</v>
       </c>
       <c r="I51" t="n">
-        <v>105.58</v>
+        <v>113.39</v>
       </c>
       <c r="J51" t="n">
-        <v>108.39</v>
+        <v>101.92</v>
       </c>
       <c r="K51" t="n">
-        <v>-2.8</v>
+        <v>11.47</v>
       </c>
       <c r="L51" t="n">
-        <v>0.2229</v>
+        <v>0.2176</v>
       </c>
       <c r="M51" t="n">
-        <v>0.1707</v>
+        <v>0.135</v>
       </c>
       <c r="N51" t="n">
-        <v>7.8</v>
+        <v>23</v>
       </c>
       <c r="O51" t="n">
-        <v>290</v>
+        <v>198</v>
       </c>
       <c r="P51" t="n">
-        <v>295</v>
+        <v>225</v>
       </c>
       <c r="Q51" t="n">
-        <v>279</v>
+        <v>191</v>
       </c>
       <c r="R51" t="n">
-        <v>282</v>
+        <v>194</v>
       </c>
       <c r="S51" t="n">
-        <v>268</v>
+        <v>197</v>
       </c>
       <c r="T51" t="n">
-        <v>282</v>
+        <v>205</v>
       </c>
       <c r="U51" t="n">
-        <v>1399</v>
+        <v>1369.1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Idaho</t>
+          <t>Howard</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4096,52 +4096,52 @@
         <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G52" t="n">
-        <v>1410</v>
+        <v>1407.8</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.3498</v>
+        <v>2.9318</v>
       </c>
       <c r="I52" t="n">
-        <v>110.28</v>
+        <v>109.06</v>
       </c>
       <c r="J52" t="n">
-        <v>106.53</v>
+        <v>98.31999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>3.75</v>
+        <v>10.75</v>
       </c>
       <c r="L52" t="n">
-        <v>0.2693</v>
+        <v>0.3191</v>
       </c>
       <c r="M52" t="n">
-        <v>0.1475</v>
+        <v>0.1856</v>
       </c>
       <c r="N52" t="n">
-        <v>11</v>
+        <v>15.4</v>
       </c>
       <c r="O52" t="n">
-        <v>165</v>
+        <v>202</v>
       </c>
       <c r="P52" t="n">
-        <v>184</v>
+        <v>250</v>
       </c>
       <c r="Q52" t="n">
-        <v>179</v>
+        <v>270</v>
       </c>
       <c r="R52" t="n">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="S52" t="n">
-        <v>184</v>
+        <v>232</v>
       </c>
       <c r="T52" t="n">
-        <v>161</v>
+        <v>202</v>
       </c>
       <c r="U52" t="n">
-        <v>1415.2</v>
+        <v>1372.4</v>
       </c>
     </row>
     <row r="53">
@@ -4217,11 +4217,11 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1277</v>
+        <v>1345</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Michigan St</t>
+          <t>Purdue</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4238,61 +4238,61 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G54" t="n">
-        <v>2027.4</v>
+        <v>1986.9</v>
       </c>
       <c r="H54" t="n">
-        <v>0.218</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>117.66</v>
+        <v>124.76</v>
       </c>
       <c r="J54" t="n">
-        <v>102.12</v>
+        <v>107.25</v>
       </c>
       <c r="K54" t="n">
-        <v>15.54</v>
+        <v>17.51</v>
       </c>
       <c r="L54" t="n">
-        <v>0.2963</v>
+        <v>0.3105</v>
       </c>
       <c r="M54" t="n">
-        <v>0.1607</v>
+        <v>0.1343</v>
       </c>
       <c r="N54" t="n">
-        <v>1</v>
+        <v>7.2</v>
       </c>
       <c r="O54" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P54" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q54" t="n">
+        <v>8</v>
+      </c>
+      <c r="R54" t="n">
+        <v>8</v>
+      </c>
+      <c r="S54" t="n">
+        <v>13</v>
+      </c>
+      <c r="T54" t="n">
         <v>10</v>
       </c>
-      <c r="R54" t="n">
-        <v>9</v>
-      </c>
-      <c r="S54" t="n">
-        <v>7</v>
-      </c>
-      <c r="T54" t="n">
-        <v>11</v>
-      </c>
       <c r="U54" t="n">
-        <v>1730.1</v>
+        <v>1754.6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1438</v>
+        <v>1211</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>Gonzaga</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4309,61 +4309,61 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="G55" t="n">
-        <v>1964.3</v>
+        <v>2068.3</v>
       </c>
       <c r="H55" t="n">
-        <v>12.2076</v>
+        <v>5.8188</v>
       </c>
       <c r="I55" t="n">
-        <v>119.04</v>
+        <v>120.75</v>
       </c>
       <c r="J55" t="n">
-        <v>100.85</v>
+        <v>93.89</v>
       </c>
       <c r="K55" t="n">
-        <v>18.19</v>
+        <v>26.86</v>
       </c>
       <c r="L55" t="n">
-        <v>0.3154</v>
+        <v>0.2992</v>
       </c>
       <c r="M55" t="n">
-        <v>0.1544</v>
+        <v>0.1335</v>
       </c>
       <c r="N55" t="n">
-        <v>6.8</v>
+        <v>11.8</v>
       </c>
       <c r="O55" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="P55" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="Q55" t="n">
+        <v>15</v>
+      </c>
+      <c r="R55" t="n">
         <v>11</v>
       </c>
-      <c r="R55" t="n">
-        <v>19</v>
-      </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T55" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="U55" t="n">
-        <v>1665.9</v>
+        <v>1601.3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1104</v>
+        <v>1116</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Alabama</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4380,52 +4380,52 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G56" t="n">
-        <v>1949.3</v>
+        <v>1961.7</v>
       </c>
       <c r="H56" t="n">
-        <v>-1.3255</v>
+        <v>5.2535</v>
       </c>
       <c r="I56" t="n">
-        <v>121.37</v>
+        <v>122.84</v>
       </c>
       <c r="J56" t="n">
-        <v>110.6</v>
+        <v>109.47</v>
       </c>
       <c r="K56" t="n">
-        <v>10.77</v>
+        <v>13.37</v>
       </c>
       <c r="L56" t="n">
-        <v>0.2809</v>
+        <v>0.3045</v>
       </c>
       <c r="M56" t="n">
-        <v>0.1288</v>
+        <v>0.1197</v>
       </c>
       <c r="N56" t="n">
-        <v>5.6</v>
+        <v>-0.8</v>
       </c>
       <c r="O56" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P56" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Q56" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="R56" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="S56" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="T56" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U56" t="n">
-        <v>1767</v>
+        <v>1726.7</v>
       </c>
     </row>
     <row r="57">
@@ -4643,11 +4643,11 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1429</v>
+        <v>1437</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Utah St</t>
+          <t>Villanova</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4664,61 +4664,61 @@
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G60" t="n">
-        <v>1897.5</v>
+        <v>1806.3</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1736</v>
+        <v>5.8793</v>
       </c>
       <c r="I60" t="n">
-        <v>119.56</v>
+        <v>114.59</v>
       </c>
       <c r="J60" t="n">
-        <v>103.49</v>
+        <v>104.94</v>
       </c>
       <c r="K60" t="n">
-        <v>16.08</v>
+        <v>9.66</v>
       </c>
       <c r="L60" t="n">
-        <v>0.3032</v>
+        <v>0.313</v>
       </c>
       <c r="M60" t="n">
-        <v>0.1479</v>
+        <v>0.1447</v>
       </c>
       <c r="N60" t="n">
-        <v>4.2</v>
+        <v>-1</v>
       </c>
       <c r="O60" t="n">
+        <v>32</v>
+      </c>
+      <c r="P60" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q60" t="n">
         <v>35</v>
       </c>
-      <c r="P60" t="n">
-        <v>36</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>37</v>
-      </c>
       <c r="R60" t="n">
+        <v>26</v>
+      </c>
+      <c r="S60" t="n">
+        <v>23</v>
+      </c>
+      <c r="T60" t="n">
         <v>33</v>
       </c>
-      <c r="S60" t="n">
-        <v>30</v>
-      </c>
-      <c r="T60" t="n">
-        <v>29</v>
-      </c>
       <c r="U60" t="n">
-        <v>1611.4</v>
+        <v>1641.5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1234</v>
+        <v>1429</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Iowa</t>
+          <t>Utah St</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4735,61 +4735,61 @@
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G61" t="n">
-        <v>1831.8</v>
+        <v>1897.5</v>
       </c>
       <c r="H61" t="n">
-        <v>3.3952</v>
+        <v>0.1736</v>
       </c>
       <c r="I61" t="n">
-        <v>118.92</v>
+        <v>119.56</v>
       </c>
       <c r="J61" t="n">
-        <v>104.81</v>
+        <v>103.49</v>
       </c>
       <c r="K61" t="n">
-        <v>14.12</v>
+        <v>16.08</v>
       </c>
       <c r="L61" t="n">
-        <v>0.2886</v>
+        <v>0.3032</v>
       </c>
       <c r="M61" t="n">
-        <v>0.1455</v>
+        <v>0.1479</v>
       </c>
       <c r="N61" t="n">
-        <v>-1.2</v>
+        <v>4.2</v>
       </c>
       <c r="O61" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="P61" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>37</v>
+      </c>
+      <c r="R61" t="n">
         <v>33</v>
       </c>
-      <c r="Q61" t="n">
+      <c r="S61" t="n">
         <v>30</v>
       </c>
-      <c r="R61" t="n">
-        <v>28</v>
-      </c>
-      <c r="S61" t="n">
-        <v>39</v>
-      </c>
       <c r="T61" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="U61" t="n">
-        <v>1712.2</v>
+        <v>1611.4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1416</v>
+        <v>1281</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>UCF</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4809,58 +4809,58 @@
         <v>129</v>
       </c>
       <c r="G62" t="n">
-        <v>1828.6</v>
+        <v>1747.8</v>
       </c>
       <c r="H62" t="n">
-        <v>5.8051</v>
+        <v>-1.7576</v>
       </c>
       <c r="I62" t="n">
-        <v>113</v>
+        <v>114.92</v>
       </c>
       <c r="J62" t="n">
-        <v>110.03</v>
+        <v>109.48</v>
       </c>
       <c r="K62" t="n">
-        <v>2.97</v>
+        <v>5.45</v>
       </c>
       <c r="L62" t="n">
-        <v>0.3147</v>
+        <v>0.2996</v>
       </c>
       <c r="M62" t="n">
-        <v>0.1543</v>
+        <v>0.1685</v>
       </c>
       <c r="N62" t="n">
-        <v>-8.800000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="O62" t="n">
+        <v>50</v>
+      </c>
+      <c r="P62" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q62" t="n">
         <v>53</v>
       </c>
-      <c r="P62" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>57</v>
-      </c>
       <c r="R62" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="S62" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="T62" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="U62" t="n">
-        <v>1712.7</v>
+        <v>1658.3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1374</v>
+        <v>1301</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SMU</t>
+          <t>NC State</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4877,52 +4877,52 @@
         <v>1</v>
       </c>
       <c r="F63" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G63" t="n">
-        <v>1733.9</v>
+        <v>1734</v>
       </c>
       <c r="H63" t="n">
-        <v>0.2411</v>
+        <v>6.962</v>
       </c>
       <c r="I63" t="n">
-        <v>117.96</v>
+        <v>119.36</v>
       </c>
       <c r="J63" t="n">
-        <v>109.76</v>
+        <v>109.32</v>
       </c>
       <c r="K63" t="n">
-        <v>8.199999999999999</v>
+        <v>10.04</v>
       </c>
       <c r="L63" t="n">
-        <v>0.3098</v>
+        <v>0.2802</v>
       </c>
       <c r="M63" t="n">
-        <v>0.1542</v>
+        <v>0.1288</v>
       </c>
       <c r="N63" t="n">
-        <v>-5.6</v>
+        <v>-6.6</v>
       </c>
       <c r="O63" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="P63" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="Q63" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R63" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S63" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="T63" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="U63" t="n">
-        <v>1649.8</v>
+        <v>1681.7</v>
       </c>
     </row>
     <row r="64">
@@ -5069,11 +5069,11 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1295</v>
+        <v>1218</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>N Dakota St</t>
+          <t>Hawaii</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5090,61 +5090,61 @@
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="G66" t="n">
-        <v>1593.8</v>
+        <v>1549.1</v>
       </c>
       <c r="H66" t="n">
-        <v>3.5257</v>
+        <v>2.9832</v>
       </c>
       <c r="I66" t="n">
-        <v>114.28</v>
+        <v>108.14</v>
       </c>
       <c r="J66" t="n">
-        <v>102.18</v>
+        <v>96.69</v>
       </c>
       <c r="K66" t="n">
-        <v>12.1</v>
+        <v>11.45</v>
       </c>
       <c r="L66" t="n">
-        <v>0.3104</v>
+        <v>0.2583</v>
       </c>
       <c r="M66" t="n">
-        <v>0.1506</v>
+        <v>0.1851</v>
       </c>
       <c r="N66" t="n">
-        <v>10.8</v>
+        <v>6.8</v>
       </c>
       <c r="O66" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P66" t="n">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="Q66" t="n">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="R66" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="S66" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="T66" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="U66" t="n">
-        <v>1410.6</v>
+        <v>1452.3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1398</v>
+        <v>1244</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tennessee St</t>
+          <t>Kennesaw</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5161,61 +5161,61 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="G67" t="n">
-        <v>1466.9</v>
+        <v>1521.3</v>
       </c>
       <c r="H67" t="n">
-        <v>3.3618</v>
+        <v>-0.1615</v>
       </c>
       <c r="I67" t="n">
-        <v>109.9</v>
+        <v>111.12</v>
       </c>
       <c r="J67" t="n">
-        <v>103.28</v>
+        <v>108.1</v>
       </c>
       <c r="K67" t="n">
-        <v>6.62</v>
+        <v>3.02</v>
       </c>
       <c r="L67" t="n">
-        <v>0.328</v>
+        <v>0.345</v>
       </c>
       <c r="M67" t="n">
-        <v>0.1589</v>
+        <v>0.165</v>
       </c>
       <c r="N67" t="n">
-        <v>19.8</v>
+        <v>3.2</v>
       </c>
       <c r="O67" t="n">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="P67" t="n">
-        <v>190</v>
+        <v>159</v>
       </c>
       <c r="Q67" t="n">
-        <v>187</v>
+        <v>149</v>
       </c>
       <c r="R67" t="n">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="S67" t="n">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="T67" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="U67" t="n">
-        <v>1407.8</v>
+        <v>1474.6</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1373</v>
+        <v>1474</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Siena</t>
+          <t>Queens NC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5232,61 +5232,61 @@
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G68" t="n">
-        <v>1478</v>
+        <v>1427.4</v>
       </c>
       <c r="H68" t="n">
-        <v>0.9489</v>
+        <v>1.0039</v>
       </c>
       <c r="I68" t="n">
-        <v>109.73</v>
+        <v>119.17</v>
       </c>
       <c r="J68" t="n">
-        <v>101.77</v>
+        <v>116.56</v>
       </c>
       <c r="K68" t="n">
-        <v>7.95</v>
+        <v>2.61</v>
       </c>
       <c r="L68" t="n">
-        <v>0.2799</v>
+        <v>0.2859</v>
       </c>
       <c r="M68" t="n">
-        <v>0.1508</v>
+        <v>0.1441</v>
       </c>
       <c r="N68" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O68" t="n">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="P68" t="n">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="Q68" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="R68" t="n">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="S68" t="n">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="T68" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="U68" t="n">
-        <v>1430.3</v>
+        <v>1430.9</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1224</v>
+        <v>1254</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Howard</t>
+          <t>LIU Brooklyn</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5303,52 +5303,52 @@
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="G69" t="n">
-        <v>1407.8</v>
+        <v>1418.2</v>
       </c>
       <c r="H69" t="n">
-        <v>2.9318</v>
+        <v>2.3581</v>
       </c>
       <c r="I69" t="n">
-        <v>109.06</v>
+        <v>109.38</v>
       </c>
       <c r="J69" t="n">
-        <v>98.31999999999999</v>
+        <v>104.38</v>
       </c>
       <c r="K69" t="n">
-        <v>10.75</v>
+        <v>5</v>
       </c>
       <c r="L69" t="n">
-        <v>0.3191</v>
+        <v>0.3119</v>
       </c>
       <c r="M69" t="n">
-        <v>0.1856</v>
+        <v>0.183</v>
       </c>
       <c r="N69" t="n">
-        <v>15.4</v>
+        <v>10.4</v>
       </c>
       <c r="O69" t="n">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="P69" t="n">
-        <v>250</v>
+        <v>228</v>
       </c>
       <c r="Q69" t="n">
-        <v>270</v>
+        <v>213</v>
       </c>
       <c r="R69" t="n">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="S69" t="n">
-        <v>232</v>
+        <v>166</v>
       </c>
       <c r="T69" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="U69" t="n">
-        <v>1372.4</v>
+        <v>1378.8</v>
       </c>
     </row>
   </sheetData>

--- a/team_stats_2026.xlsx
+++ b/team_stats_2026.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,107 +429,107 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Is_FirstFour</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -576,16 +588,16 @@
         <v>1</v>
       </c>
       <c r="P2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q2" t="n">
         <v>1</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2</v>
       </c>
       <c r="R2" t="n">
         <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -647,13 +659,13 @@
         <v>11</v>
       </c>
       <c r="P3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="R3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -718,16 +730,16 @@
         <v>9</v>
       </c>
       <c r="P4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q4" t="n">
+        <v>12</v>
+      </c>
+      <c r="R4" t="n">
         <v>10</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>9</v>
-      </c>
-      <c r="S4" t="n">
-        <v>7</v>
       </c>
       <c r="T4" t="n">
         <v>11</v>
@@ -786,19 +798,19 @@
         <v>-6.2</v>
       </c>
       <c r="O5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P5" t="n">
         <v>18</v>
       </c>
       <c r="Q5" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="R5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="S5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T5" t="n">
         <v>19</v>
@@ -857,19 +869,19 @@
         <v>10.6</v>
       </c>
       <c r="O6" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="P6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Q6" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="R6" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="T6" t="n">
         <v>22</v>
@@ -928,19 +940,19 @@
         <v>2.4</v>
       </c>
       <c r="O7" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="P7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q7" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="R7" t="n">
         <v>21</v>
       </c>
       <c r="S7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T7" t="n">
         <v>14</v>
@@ -999,16 +1011,16 @@
         <v>10.2</v>
       </c>
       <c r="O8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P8" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="Q8" t="n">
+        <v>32</v>
+      </c>
+      <c r="R8" t="n">
         <v>31</v>
-      </c>
-      <c r="R8" t="n">
-        <v>34</v>
       </c>
       <c r="S8" t="n">
         <v>33</v>
@@ -1073,13 +1085,13 @@
         <v>26</v>
       </c>
       <c r="P9" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="Q9" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="R9" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="S9" t="n">
         <v>38</v>
@@ -1141,16 +1153,16 @@
         <v>5.8</v>
       </c>
       <c r="O10" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q10" t="n">
         <v>43</v>
       </c>
       <c r="R10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="S10" t="n">
         <v>35</v>
@@ -1212,19 +1224,19 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P11" t="n">
         <v>42</v>
       </c>
       <c r="Q11" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="R11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S11" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T11" t="n">
         <v>51</v>
@@ -1256,52 +1268,50 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G12" t="n">
-        <v>1714.9</v>
+        <v>1723.5</v>
       </c>
       <c r="H12" t="n">
-        <v>9.035</v>
+        <v>8.857799999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>116.33</v>
+        <v>115.66</v>
       </c>
       <c r="J12" t="n">
-        <v>101.48</v>
+        <v>100.71</v>
       </c>
       <c r="K12" t="n">
-        <v>14.84</v>
+        <v>14.95</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3412</v>
+        <v>0.3398</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1466</v>
+        <v>0.1464</v>
       </c>
       <c r="N12" t="n">
-        <v>19.8</v>
+        <v>19</v>
       </c>
       <c r="O12" t="n">
+        <v>47</v>
+      </c>
+      <c r="P12" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>49</v>
+      </c>
+      <c r="R12" t="n">
+        <v>45</v>
+      </c>
+      <c r="S12" t="n">
         <v>51</v>
       </c>
-      <c r="P12" t="n">
-        <v>64</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>51</v>
-      </c>
-      <c r="R12" t="n">
-        <v>49</v>
-      </c>
-      <c r="S12" t="n">
-        <v>54</v>
-      </c>
-      <c r="T12" t="n">
-        <v>49</v>
-      </c>
+      <c r="T12" t="inlineStr"/>
       <c r="U12" t="n">
-        <v>1550.3</v>
+        <v>1554.8</v>
       </c>
     </row>
     <row r="13">
@@ -1354,19 +1364,19 @@
         <v>14.4</v>
       </c>
       <c r="O13" t="n">
+        <v>72</v>
+      </c>
+      <c r="P13" t="n">
+        <v>93</v>
+      </c>
+      <c r="Q13" t="n">
         <v>70</v>
       </c>
-      <c r="P13" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>72</v>
-      </c>
       <c r="R13" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="S13" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="T13" t="n">
         <v>72</v>
@@ -1425,19 +1435,19 @@
         <v>15.4</v>
       </c>
       <c r="O14" t="n">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="P14" t="n">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="Q14" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="R14" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="S14" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T14" t="n">
         <v>103</v>
@@ -1496,16 +1506,16 @@
         <v>10.8</v>
       </c>
       <c r="O15" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P15" t="n">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="Q15" t="n">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="R15" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="S15" t="n">
         <v>98</v>
@@ -1567,19 +1577,19 @@
         <v>5.6</v>
       </c>
       <c r="O16" t="n">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="P16" t="n">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="Q16" t="n">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="R16" t="n">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="S16" t="n">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="T16" t="n">
         <v>194</v>
@@ -1638,19 +1648,19 @@
         <v>6.2</v>
       </c>
       <c r="O17" t="n">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="P17" t="n">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="Q17" t="n">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="R17" t="n">
+        <v>170</v>
+      </c>
+      <c r="S17" t="n">
         <v>172</v>
-      </c>
-      <c r="S17" t="n">
-        <v>177</v>
       </c>
       <c r="T17" t="n">
         <v>188</v>
@@ -1712,7 +1722,7 @@
         <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q18" t="n">
         <v>4</v>
@@ -1721,7 +1731,7 @@
         <v>4</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T18" t="n">
         <v>4</v>
@@ -1780,16 +1790,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="O19" t="n">
+        <v>5</v>
+      </c>
+      <c r="P19" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q19" t="n">
         <v>6</v>
       </c>
-      <c r="P19" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>7</v>
-      </c>
       <c r="R19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S19" t="n">
         <v>6</v>
@@ -1851,19 +1861,19 @@
         <v>2.8</v>
       </c>
       <c r="O20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P20" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Q20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T20" t="n">
         <v>6</v>
@@ -1922,19 +1932,19 @@
         <v>0.2</v>
       </c>
       <c r="O21" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P21" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Q21" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R21" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T21" t="n">
         <v>12</v>
@@ -1966,52 +1976,50 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G22" t="n">
-        <v>1967.8</v>
+        <v>1952.6</v>
       </c>
       <c r="H22" t="n">
-        <v>1.6985</v>
+        <v>1.6305</v>
       </c>
       <c r="I22" t="n">
-        <v>122.92</v>
+        <v>122.08</v>
       </c>
       <c r="J22" t="n">
-        <v>106.35</v>
+        <v>106.87</v>
       </c>
       <c r="K22" t="n">
-        <v>16.57</v>
+        <v>15.21</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2937</v>
+        <v>0.2915</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1302</v>
+        <v>0.1281</v>
       </c>
       <c r="N22" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="O22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P22" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Q22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R22" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="S22" t="n">
-        <v>22</v>
-      </c>
-      <c r="T22" t="n">
-        <v>16</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="T22" t="inlineStr"/>
       <c r="U22" t="n">
-        <v>1712.2</v>
+        <v>1718.8</v>
       </c>
     </row>
     <row r="23">
@@ -2064,19 +2072,19 @@
         <v>-0.4</v>
       </c>
       <c r="O23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P23" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q23" t="n">
         <v>24</v>
       </c>
       <c r="R23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T23" t="n">
         <v>23</v>
@@ -2135,19 +2143,19 @@
         <v>8.6</v>
       </c>
       <c r="O24" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P24" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="Q24" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="R24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S24" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="T24" t="n">
         <v>20</v>
@@ -2206,19 +2214,19 @@
         <v>-0.6</v>
       </c>
       <c r="O25" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="P25" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q25" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="R25" t="n">
         <v>35</v>
       </c>
       <c r="S25" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="T25" t="n">
         <v>36</v>
@@ -2277,13 +2285,13 @@
         <v>-1.2</v>
       </c>
       <c r="O26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P26" t="n">
         <v>33</v>
       </c>
       <c r="Q26" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R26" t="n">
         <v>28</v>
@@ -2348,19 +2356,19 @@
         <v>-5.4</v>
       </c>
       <c r="O27" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P27" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="Q27" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="R27" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="S27" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T27" t="n">
         <v>43</v>
@@ -2392,52 +2400,50 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G28" t="n">
-        <v>1751</v>
+        <v>1761.3</v>
       </c>
       <c r="H28" t="n">
-        <v>3.1884</v>
+        <v>3.2921</v>
       </c>
       <c r="I28" t="n">
-        <v>118.3</v>
+        <v>117.94</v>
       </c>
       <c r="J28" t="n">
-        <v>103.55</v>
+        <v>103.32</v>
       </c>
       <c r="K28" t="n">
-        <v>14.75</v>
+        <v>14.61</v>
       </c>
       <c r="L28" t="n">
-        <v>0.2988</v>
+        <v>0.2941</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1491</v>
+        <v>0.1467</v>
       </c>
       <c r="N28" t="n">
-        <v>9.6</v>
+        <v>7.4</v>
       </c>
       <c r="O28" t="n">
         <v>45</v>
       </c>
       <c r="P28" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="Q28" t="n">
         <v>48</v>
       </c>
       <c r="R28" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="S28" t="n">
         <v>40</v>
       </c>
-      <c r="T28" t="n">
-        <v>44</v>
-      </c>
+      <c r="T28" t="inlineStr"/>
       <c r="U28" t="n">
-        <v>1553.9</v>
+        <v>1558.4</v>
       </c>
     </row>
     <row r="29">
@@ -2496,13 +2502,13 @@
         <v>87</v>
       </c>
       <c r="Q29" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="R29" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="S29" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="T29" t="n">
         <v>62</v>
@@ -2561,19 +2567,19 @@
         <v>9.4</v>
       </c>
       <c r="O30" t="n">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="P30" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q30" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="R30" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="S30" t="n">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="T30" t="n">
         <v>132</v>
@@ -2605,52 +2611,50 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G31" t="n">
-        <v>1431.7</v>
+        <v>1458.4</v>
       </c>
       <c r="H31" t="n">
-        <v>1.1135</v>
+        <v>1.2024</v>
       </c>
       <c r="I31" t="n">
-        <v>107.49</v>
+        <v>108.54</v>
       </c>
       <c r="J31" t="n">
-        <v>105.83</v>
+        <v>106.7</v>
       </c>
       <c r="K31" t="n">
-        <v>1.66</v>
+        <v>1.84</v>
       </c>
       <c r="L31" t="n">
-        <v>0.3084</v>
+        <v>0.3143</v>
       </c>
       <c r="M31" t="n">
-        <v>0.1543</v>
+        <v>0.1519</v>
       </c>
       <c r="N31" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="O31" t="n">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="P31" t="n">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="Q31" t="n">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="R31" t="n">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="S31" t="n">
-        <v>141</v>
-      </c>
-      <c r="T31" t="n">
-        <v>148</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="T31" t="inlineStr"/>
       <c r="U31" t="n">
-        <v>1482.7</v>
+        <v>1493.7</v>
       </c>
     </row>
     <row r="32">
@@ -2703,19 +2707,19 @@
         <v>11</v>
       </c>
       <c r="O32" t="n">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="P32" t="n">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="Q32" t="n">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="R32" t="n">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="S32" t="n">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="T32" t="n">
         <v>161</v>
@@ -2774,19 +2778,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="O33" t="n">
-        <v>312</v>
+        <v>288</v>
       </c>
       <c r="P33" t="n">
-        <v>330</v>
+        <v>309</v>
       </c>
       <c r="Q33" t="n">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="R33" t="n">
+        <v>281</v>
+      </c>
+      <c r="S33" t="n">
         <v>306</v>
-      </c>
-      <c r="S33" t="n">
-        <v>325</v>
       </c>
       <c r="T33" t="n">
         <v>316</v>
@@ -2845,19 +2849,19 @@
         <v>7.8</v>
       </c>
       <c r="O34" t="n">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="P34" t="n">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="Q34" t="n">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="R34" t="n">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="S34" t="n">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="T34" t="n">
         <v>282</v>
@@ -2889,52 +2893,50 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G35" t="n">
-        <v>2196.8</v>
+        <v>2173.7</v>
       </c>
       <c r="H35" t="n">
-        <v>6.739</v>
+        <v>6.5185</v>
       </c>
       <c r="I35" t="n">
-        <v>120.64</v>
+        <v>120.66</v>
       </c>
       <c r="J35" t="n">
-        <v>95.94</v>
+        <v>97.18000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>24.71</v>
+        <v>23.48</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2604</v>
+        <v>0.2598</v>
       </c>
       <c r="M35" t="n">
-        <v>0.1666</v>
+        <v>0.1613</v>
       </c>
       <c r="N35" t="n">
-        <v>6.8</v>
+        <v>2.4</v>
       </c>
       <c r="O35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P35" t="n">
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
       </c>
-      <c r="T35" t="n">
-        <v>2</v>
-      </c>
+      <c r="T35" t="inlineStr"/>
       <c r="U35" t="n">
-        <v>1772.9</v>
+        <v>1779.9</v>
       </c>
     </row>
     <row r="36">
@@ -2987,19 +2989,19 @@
         <v>14.8</v>
       </c>
       <c r="O36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P36" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>5</v>
+      </c>
+      <c r="R36" t="n">
+        <v>5</v>
+      </c>
+      <c r="S36" t="n">
         <v>10</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>6</v>
-      </c>
-      <c r="R36" t="n">
-        <v>6</v>
-      </c>
-      <c r="S36" t="n">
-        <v>11</v>
       </c>
       <c r="T36" t="n">
         <v>8</v>
@@ -3058,19 +3060,19 @@
         <v>6.8</v>
       </c>
       <c r="O37" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="P37" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q37" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="R37" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T37" t="n">
         <v>13</v>
@@ -3129,16 +3131,16 @@
         <v>5.6</v>
       </c>
       <c r="O38" t="n">
+        <v>18</v>
+      </c>
+      <c r="P38" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>16</v>
+      </c>
+      <c r="R38" t="n">
         <v>15</v>
-      </c>
-      <c r="P38" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>12</v>
-      </c>
-      <c r="R38" t="n">
-        <v>12</v>
       </c>
       <c r="S38" t="n">
         <v>14</v>
@@ -3200,16 +3202,16 @@
         <v>-3</v>
       </c>
       <c r="O39" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="P39" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="Q39" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="R39" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="S39" t="n">
         <v>17</v>
@@ -3271,19 +3273,19 @@
         <v>3.2</v>
       </c>
       <c r="O40" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="P40" t="n">
         <v>17</v>
       </c>
       <c r="Q40" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R40" t="n">
         <v>20</v>
       </c>
       <c r="S40" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T40" t="n">
         <v>21</v>
@@ -3342,16 +3344,16 @@
         <v>-3</v>
       </c>
       <c r="O41" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P41" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q41" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R41" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S41" t="n">
         <v>31</v>
@@ -3413,19 +3415,19 @@
         <v>4.6</v>
       </c>
       <c r="O42" t="n">
+        <v>32</v>
+      </c>
+      <c r="P42" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q42" t="n">
         <v>31</v>
       </c>
-      <c r="P42" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>28</v>
-      </c>
       <c r="R42" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="S42" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="T42" t="n">
         <v>31</v>
@@ -3484,19 +3486,19 @@
         <v>1.2</v>
       </c>
       <c r="O43" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P43" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="Q43" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="R43" t="n">
+        <v>34</v>
+      </c>
+      <c r="S43" t="n">
         <v>30</v>
-      </c>
-      <c r="S43" t="n">
-        <v>28</v>
       </c>
       <c r="T43" t="n">
         <v>27</v>
@@ -3555,19 +3557,19 @@
         <v>0.8</v>
       </c>
       <c r="O44" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="P44" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q44" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R44" t="n">
         <v>36</v>
       </c>
       <c r="S44" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="T44" t="n">
         <v>42</v>
@@ -3626,19 +3628,19 @@
         <v>2.4</v>
       </c>
       <c r="O45" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="P45" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="Q45" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="R45" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="T45" t="n">
         <v>55</v>
@@ -3697,16 +3699,16 @@
         <v>-5.6</v>
       </c>
       <c r="O46" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P46" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q46" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="R46" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S46" t="n">
         <v>44</v>
@@ -3768,19 +3770,19 @@
         <v>13</v>
       </c>
       <c r="O47" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="P47" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="Q47" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="R47" t="n">
         <v>54</v>
       </c>
       <c r="S47" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="T47" t="n">
         <v>52</v>
@@ -3839,16 +3841,16 @@
         <v>12</v>
       </c>
       <c r="O48" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="P48" t="n">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="Q48" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="R48" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="S48" t="n">
         <v>92</v>
@@ -3910,19 +3912,19 @@
         <v>10</v>
       </c>
       <c r="O49" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="P49" t="n">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="Q49" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="R49" t="n">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="S49" t="n">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="T49" t="n">
         <v>133</v>
@@ -3981,10 +3983,10 @@
         <v>19.8</v>
       </c>
       <c r="O50" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P50" t="n">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="Q50" t="n">
         <v>187</v>
@@ -3993,10 +3995,10 @@
         <v>168</v>
       </c>
       <c r="S50" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="T50" t="n">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="U50" t="n">
         <v>1407.8</v>
@@ -4052,19 +4054,19 @@
         <v>23</v>
       </c>
       <c r="O51" t="n">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="P51" t="n">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="Q51" t="n">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="R51" t="n">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="S51" t="n">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="T51" t="n">
         <v>205</v>
@@ -4123,19 +4125,19 @@
         <v>15.4</v>
       </c>
       <c r="O52" t="n">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="P52" t="n">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="Q52" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R52" t="n">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="S52" t="n">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="T52" t="n">
         <v>202</v>
@@ -4194,19 +4196,19 @@
         <v>11</v>
       </c>
       <c r="O53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q53" t="n">
         <v>3</v>
       </c>
       <c r="R53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T53" t="n">
         <v>3</v>
@@ -4238,52 +4240,50 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G54" t="n">
-        <v>1986.9</v>
+        <v>2010</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.5973000000000001</v>
+        <v>-0.7024</v>
       </c>
       <c r="I54" t="n">
-        <v>124.76</v>
+        <v>124.87</v>
       </c>
       <c r="J54" t="n">
-        <v>107.25</v>
+        <v>107.49</v>
       </c>
       <c r="K54" t="n">
-        <v>17.51</v>
+        <v>17.39</v>
       </c>
       <c r="L54" t="n">
-        <v>0.3105</v>
+        <v>0.311</v>
       </c>
       <c r="M54" t="n">
-        <v>0.1343</v>
+        <v>0.1337</v>
       </c>
       <c r="N54" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="O54" t="n">
         <v>8</v>
       </c>
       <c r="P54" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>7</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7</v>
+      </c>
+      <c r="S54" t="n">
         <v>12</v>
       </c>
-      <c r="Q54" t="n">
-        <v>8</v>
-      </c>
-      <c r="R54" t="n">
-        <v>8</v>
-      </c>
-      <c r="S54" t="n">
-        <v>13</v>
-      </c>
-      <c r="T54" t="n">
-        <v>10</v>
-      </c>
+      <c r="T54" t="inlineStr"/>
       <c r="U54" t="n">
-        <v>1754.6</v>
+        <v>1769.7</v>
       </c>
     </row>
     <row r="55">
@@ -4339,10 +4339,10 @@
         <v>10</v>
       </c>
       <c r="P55" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q55" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="R55" t="n">
         <v>11</v>
@@ -4380,52 +4380,50 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G56" t="n">
-        <v>1961.7</v>
+        <v>1977</v>
       </c>
       <c r="H56" t="n">
-        <v>5.2535</v>
+        <v>5.1479</v>
       </c>
       <c r="I56" t="n">
-        <v>122.84</v>
+        <v>122.87</v>
       </c>
       <c r="J56" t="n">
-        <v>109.47</v>
+        <v>109.33</v>
       </c>
       <c r="K56" t="n">
-        <v>13.37</v>
+        <v>13.54</v>
       </c>
       <c r="L56" t="n">
-        <v>0.3045</v>
+        <v>0.2979</v>
       </c>
       <c r="M56" t="n">
-        <v>0.1197</v>
+        <v>0.1206</v>
       </c>
       <c r="N56" t="n">
-        <v>-0.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O56" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P56" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>15</v>
+      </c>
+      <c r="R56" t="n">
         <v>14</v>
       </c>
-      <c r="Q56" t="n">
+      <c r="S56" t="n">
         <v>20</v>
       </c>
-      <c r="R56" t="n">
-        <v>16</v>
-      </c>
-      <c r="S56" t="n">
-        <v>21</v>
-      </c>
-      <c r="T56" t="n">
-        <v>18</v>
-      </c>
+      <c r="T56" t="inlineStr"/>
       <c r="U56" t="n">
-        <v>1726.7</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="57">
@@ -4478,19 +4476,19 @@
         <v>8</v>
       </c>
       <c r="O57" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P57" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q57" t="n">
         <v>23</v>
       </c>
       <c r="R57" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S57" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="T57" t="n">
         <v>26</v>
@@ -4549,10 +4547,10 @@
         <v>2.2</v>
       </c>
       <c r="O58" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P58" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Q58" t="n">
         <v>22</v>
@@ -4561,7 +4559,7 @@
         <v>22</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="T58" t="n">
         <v>24</v>
@@ -4620,16 +4618,16 @@
         <v>2</v>
       </c>
       <c r="O59" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="P59" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q59" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R59" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S59" t="n">
         <v>26</v>
@@ -4691,19 +4689,19 @@
         <v>-1</v>
       </c>
       <c r="O60" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P60" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="Q60" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="R60" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S60" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T60" t="n">
         <v>33</v>
@@ -4762,19 +4760,19 @@
         <v>4.2</v>
       </c>
       <c r="O61" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="P61" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="Q61" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="R61" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="S61" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T61" t="n">
         <v>29</v>
@@ -4833,16 +4831,16 @@
         <v>0.4</v>
       </c>
       <c r="O62" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="P62" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="Q62" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R62" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="S62" t="n">
         <v>43</v>
@@ -4904,19 +4902,19 @@
         <v>-6.6</v>
       </c>
       <c r="O63" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="P63" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q63" t="n">
         <v>34</v>
       </c>
       <c r="R63" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S63" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T63" t="n">
         <v>35</v>
@@ -4975,19 +4973,19 @@
         <v>-8</v>
       </c>
       <c r="O64" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="P64" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Q64" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="R64" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S64" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T64" t="n">
         <v>41</v>
@@ -5046,19 +5044,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="O65" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P65" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="Q65" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="R65" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="S65" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="T65" t="n">
         <v>76</v>
@@ -5117,19 +5115,19 @@
         <v>6.8</v>
       </c>
       <c r="O66" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="P66" t="n">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="Q66" t="n">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="R66" t="n">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="S66" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="T66" t="n">
         <v>112</v>
@@ -5188,19 +5186,19 @@
         <v>3.2</v>
       </c>
       <c r="O67" t="n">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="P67" t="n">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="Q67" t="n">
+        <v>132</v>
+      </c>
+      <c r="R67" t="n">
+        <v>165</v>
+      </c>
+      <c r="S67" t="n">
         <v>149</v>
-      </c>
-      <c r="R67" t="n">
-        <v>184</v>
-      </c>
-      <c r="S67" t="n">
-        <v>170</v>
       </c>
       <c r="T67" t="n">
         <v>170</v>
@@ -5259,16 +5257,16 @@
         <v>6.4</v>
       </c>
       <c r="O68" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="P68" t="n">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="Q68" t="n">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="R68" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="S68" t="n">
         <v>171</v>
@@ -5330,19 +5328,19 @@
         <v>10.4</v>
       </c>
       <c r="O69" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P69" t="n">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="Q69" t="n">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="R69" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="S69" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="T69" t="n">
         <v>200</v>

--- a/team_stats_2026.xlsx
+++ b/team_stats_2026.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,107 +417,107 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Is_FirstFour</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -588,16 +576,16 @@
         <v>1</v>
       </c>
       <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
         <v>2</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -659,13 +647,13 @@
         <v>11</v>
       </c>
       <c r="P3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="R3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -730,16 +718,16 @@
         <v>9</v>
       </c>
       <c r="P4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Q4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T4" t="n">
         <v>11</v>
@@ -798,19 +786,19 @@
         <v>-6.2</v>
       </c>
       <c r="O5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P5" t="n">
         <v>18</v>
       </c>
       <c r="Q5" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="R5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T5" t="n">
         <v>19</v>
@@ -869,19 +857,19 @@
         <v>10.6</v>
       </c>
       <c r="O6" t="n">
+        <v>21</v>
+      </c>
+      <c r="P6" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q6" t="n">
         <v>17</v>
       </c>
-      <c r="P6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>10</v>
-      </c>
       <c r="R6" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="S6" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="T6" t="n">
         <v>22</v>
@@ -940,19 +928,19 @@
         <v>2.4</v>
       </c>
       <c r="O7" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="P7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q7" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="R7" t="n">
         <v>21</v>
       </c>
       <c r="S7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="T7" t="n">
         <v>14</v>
@@ -1011,16 +999,16 @@
         <v>10.2</v>
       </c>
       <c r="O8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P8" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="Q8" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R8" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="S8" t="n">
         <v>33</v>
@@ -1085,13 +1073,13 @@
         <v>26</v>
       </c>
       <c r="P9" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="Q9" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="R9" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="S9" t="n">
         <v>38</v>
@@ -1153,16 +1141,16 @@
         <v>5.8</v>
       </c>
       <c r="O10" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q10" t="n">
         <v>43</v>
       </c>
       <c r="R10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="S10" t="n">
         <v>35</v>
@@ -1224,19 +1212,19 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="P11" t="n">
         <v>42</v>
       </c>
       <c r="Q11" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="R11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S11" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T11" t="n">
         <v>51</v>
@@ -1268,50 +1256,52 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G12" t="n">
-        <v>1723.5</v>
+        <v>1714.9</v>
       </c>
       <c r="H12" t="n">
-        <v>8.857799999999999</v>
+        <v>9.035</v>
       </c>
       <c r="I12" t="n">
-        <v>115.66</v>
+        <v>116.33</v>
       </c>
       <c r="J12" t="n">
-        <v>100.71</v>
+        <v>101.48</v>
       </c>
       <c r="K12" t="n">
-        <v>14.95</v>
+        <v>14.84</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3398</v>
+        <v>0.3412</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1464</v>
+        <v>0.1466</v>
       </c>
       <c r="N12" t="n">
-        <v>19</v>
+        <v>19.8</v>
       </c>
       <c r="O12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="P12" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="Q12" t="n">
+        <v>51</v>
+      </c>
+      <c r="R12" t="n">
         <v>49</v>
       </c>
-      <c r="R12" t="n">
-        <v>45</v>
-      </c>
       <c r="S12" t="n">
-        <v>51</v>
-      </c>
-      <c r="T12" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="T12" t="n">
+        <v>49</v>
+      </c>
       <c r="U12" t="n">
-        <v>1554.8</v>
+        <v>1550.3</v>
       </c>
     </row>
     <row r="13">
@@ -1364,19 +1354,19 @@
         <v>14.4</v>
       </c>
       <c r="O13" t="n">
+        <v>70</v>
+      </c>
+      <c r="P13" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q13" t="n">
         <v>72</v>
       </c>
-      <c r="P13" t="n">
-        <v>93</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>70</v>
-      </c>
       <c r="R13" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="S13" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T13" t="n">
         <v>72</v>
@@ -1435,19 +1425,19 @@
         <v>15.4</v>
       </c>
       <c r="O14" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="P14" t="n">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="Q14" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="R14" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="S14" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T14" t="n">
         <v>103</v>
@@ -1506,16 +1496,16 @@
         <v>10.8</v>
       </c>
       <c r="O15" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P15" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="Q15" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="R15" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="S15" t="n">
         <v>98</v>
@@ -1577,19 +1567,19 @@
         <v>5.6</v>
       </c>
       <c r="O16" t="n">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="P16" t="n">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="Q16" t="n">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="R16" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="S16" t="n">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="T16" t="n">
         <v>194</v>
@@ -1648,19 +1638,19 @@
         <v>6.2</v>
       </c>
       <c r="O17" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="P17" t="n">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="Q17" t="n">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="R17" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="S17" t="n">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="T17" t="n">
         <v>188</v>
@@ -1722,7 +1712,7 @@
         <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q18" t="n">
         <v>4</v>
@@ -1731,7 +1721,7 @@
         <v>4</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T18" t="n">
         <v>4</v>
@@ -1790,16 +1780,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="O19" t="n">
+        <v>6</v>
+      </c>
+      <c r="P19" t="n">
         <v>5</v>
       </c>
-      <c r="P19" t="n">
-        <v>4</v>
-      </c>
       <c r="Q19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S19" t="n">
         <v>6</v>
@@ -1861,19 +1851,19 @@
         <v>2.8</v>
       </c>
       <c r="O20" t="n">
+        <v>5</v>
+      </c>
+      <c r="P20" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>5</v>
+      </c>
+      <c r="R20" t="n">
         <v>7</v>
       </c>
-      <c r="P20" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>8</v>
-      </c>
-      <c r="R20" t="n">
-        <v>8</v>
-      </c>
       <c r="S20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T20" t="n">
         <v>6</v>
@@ -1932,19 +1922,19 @@
         <v>0.2</v>
       </c>
       <c r="O21" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P21" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q21" t="n">
         <v>16</v>
       </c>
-      <c r="Q21" t="n">
-        <v>18</v>
-      </c>
       <c r="R21" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="S21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T21" t="n">
         <v>12</v>
@@ -1976,50 +1966,52 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G22" t="n">
-        <v>1952.6</v>
+        <v>1967.8</v>
       </c>
       <c r="H22" t="n">
-        <v>1.6305</v>
+        <v>1.6985</v>
       </c>
       <c r="I22" t="n">
-        <v>122.08</v>
+        <v>122.92</v>
       </c>
       <c r="J22" t="n">
-        <v>106.87</v>
+        <v>106.35</v>
       </c>
       <c r="K22" t="n">
-        <v>15.21</v>
+        <v>16.57</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2915</v>
+        <v>0.2937</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1281</v>
+        <v>0.1302</v>
       </c>
       <c r="N22" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="O22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P22" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Q22" t="n">
+        <v>13</v>
+      </c>
+      <c r="R22" t="n">
         <v>14</v>
       </c>
-      <c r="R22" t="n">
-        <v>12</v>
-      </c>
       <c r="S22" t="n">
-        <v>18</v>
-      </c>
-      <c r="T22" t="inlineStr"/>
+        <v>22</v>
+      </c>
+      <c r="T22" t="n">
+        <v>16</v>
+      </c>
       <c r="U22" t="n">
-        <v>1718.8</v>
+        <v>1712.2</v>
       </c>
     </row>
     <row r="23">
@@ -2072,19 +2064,19 @@
         <v>-0.4</v>
       </c>
       <c r="O23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P23" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q23" t="n">
         <v>24</v>
       </c>
       <c r="R23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="S23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="T23" t="n">
         <v>23</v>
@@ -2143,19 +2135,19 @@
         <v>8.6</v>
       </c>
       <c r="O24" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="P24" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="Q24" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="R24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S24" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="T24" t="n">
         <v>20</v>
@@ -2214,19 +2206,19 @@
         <v>-0.6</v>
       </c>
       <c r="O25" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P25" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q25" t="n">
         <v>32</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>30</v>
       </c>
       <c r="R25" t="n">
         <v>35</v>
       </c>
       <c r="S25" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T25" t="n">
         <v>36</v>
@@ -2285,13 +2277,13 @@
         <v>-1.2</v>
       </c>
       <c r="O26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P26" t="n">
         <v>33</v>
       </c>
       <c r="Q26" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="R26" t="n">
         <v>28</v>
@@ -2356,19 +2348,19 @@
         <v>-5.4</v>
       </c>
       <c r="O27" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P27" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="Q27" t="n">
+        <v>33</v>
+      </c>
+      <c r="R27" t="n">
         <v>37</v>
       </c>
-      <c r="R27" t="n">
-        <v>40</v>
-      </c>
       <c r="S27" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T27" t="n">
         <v>43</v>
@@ -2400,50 +2392,52 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G28" t="n">
-        <v>1761.3</v>
+        <v>1751</v>
       </c>
       <c r="H28" t="n">
-        <v>3.2921</v>
+        <v>3.1884</v>
       </c>
       <c r="I28" t="n">
-        <v>117.94</v>
+        <v>118.3</v>
       </c>
       <c r="J28" t="n">
-        <v>103.32</v>
+        <v>103.55</v>
       </c>
       <c r="K28" t="n">
-        <v>14.61</v>
+        <v>14.75</v>
       </c>
       <c r="L28" t="n">
-        <v>0.2941</v>
+        <v>0.2988</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1467</v>
+        <v>0.1491</v>
       </c>
       <c r="N28" t="n">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="O28" t="n">
         <v>45</v>
       </c>
       <c r="P28" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="Q28" t="n">
         <v>48</v>
       </c>
       <c r="R28" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="S28" t="n">
         <v>40</v>
       </c>
-      <c r="T28" t="inlineStr"/>
+      <c r="T28" t="n">
+        <v>44</v>
+      </c>
       <c r="U28" t="n">
-        <v>1558.4</v>
+        <v>1553.9</v>
       </c>
     </row>
     <row r="29">
@@ -2502,13 +2496,13 @@
         <v>87</v>
       </c>
       <c r="Q29" t="n">
+        <v>62</v>
+      </c>
+      <c r="R29" t="n">
+        <v>66</v>
+      </c>
+      <c r="S29" t="n">
         <v>57</v>
-      </c>
-      <c r="R29" t="n">
-        <v>63</v>
-      </c>
-      <c r="S29" t="n">
-        <v>49</v>
       </c>
       <c r="T29" t="n">
         <v>62</v>
@@ -2567,19 +2561,19 @@
         <v>9.4</v>
       </c>
       <c r="O30" t="n">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="P30" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q30" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="R30" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="S30" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="T30" t="n">
         <v>132</v>
@@ -2611,50 +2605,52 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G31" t="n">
-        <v>1458.4</v>
+        <v>1431.7</v>
       </c>
       <c r="H31" t="n">
-        <v>1.2024</v>
+        <v>1.1135</v>
       </c>
       <c r="I31" t="n">
-        <v>108.54</v>
+        <v>107.49</v>
       </c>
       <c r="J31" t="n">
-        <v>106.7</v>
+        <v>105.83</v>
       </c>
       <c r="K31" t="n">
-        <v>1.84</v>
+        <v>1.66</v>
       </c>
       <c r="L31" t="n">
-        <v>0.3143</v>
+        <v>0.3084</v>
       </c>
       <c r="M31" t="n">
-        <v>0.1519</v>
+        <v>0.1543</v>
       </c>
       <c r="N31" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="O31" t="n">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="P31" t="n">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="Q31" t="n">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="R31" t="n">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="S31" t="n">
-        <v>138</v>
-      </c>
-      <c r="T31" t="inlineStr"/>
+        <v>141</v>
+      </c>
+      <c r="T31" t="n">
+        <v>148</v>
+      </c>
       <c r="U31" t="n">
-        <v>1493.7</v>
+        <v>1482.7</v>
       </c>
     </row>
     <row r="32">
@@ -2707,19 +2703,19 @@
         <v>11</v>
       </c>
       <c r="O32" t="n">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="P32" t="n">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="Q32" t="n">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="R32" t="n">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="S32" t="n">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="T32" t="n">
         <v>161</v>
@@ -2778,19 +2774,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="O33" t="n">
-        <v>288</v>
+        <v>312</v>
       </c>
       <c r="P33" t="n">
-        <v>309</v>
+        <v>330</v>
       </c>
       <c r="Q33" t="n">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="R33" t="n">
-        <v>281</v>
+        <v>306</v>
       </c>
       <c r="S33" t="n">
-        <v>306</v>
+        <v>325</v>
       </c>
       <c r="T33" t="n">
         <v>316</v>
@@ -2849,19 +2845,19 @@
         <v>7.8</v>
       </c>
       <c r="O34" t="n">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="P34" t="n">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="Q34" t="n">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="R34" t="n">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="S34" t="n">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="T34" t="n">
         <v>282</v>
@@ -2893,50 +2889,52 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G35" t="n">
-        <v>2173.7</v>
+        <v>2196.8</v>
       </c>
       <c r="H35" t="n">
-        <v>6.5185</v>
+        <v>6.739</v>
       </c>
       <c r="I35" t="n">
-        <v>120.66</v>
+        <v>120.64</v>
       </c>
       <c r="J35" t="n">
-        <v>97.18000000000001</v>
+        <v>95.94</v>
       </c>
       <c r="K35" t="n">
-        <v>23.48</v>
+        <v>24.71</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2598</v>
+        <v>0.2604</v>
       </c>
       <c r="M35" t="n">
-        <v>0.1613</v>
+        <v>0.1666</v>
       </c>
       <c r="N35" t="n">
-        <v>2.4</v>
+        <v>6.8</v>
       </c>
       <c r="O35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P35" t="n">
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
       </c>
-      <c r="T35" t="inlineStr"/>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
       <c r="U35" t="n">
-        <v>1779.9</v>
+        <v>1772.9</v>
       </c>
     </row>
     <row r="36">
@@ -2989,19 +2987,19 @@
         <v>14.8</v>
       </c>
       <c r="O36" t="n">
+        <v>7</v>
+      </c>
+      <c r="P36" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q36" t="n">
         <v>6</v>
       </c>
-      <c r="P36" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>5</v>
-      </c>
       <c r="R36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T36" t="n">
         <v>8</v>
@@ -3060,19 +3058,19 @@
         <v>6.8</v>
       </c>
       <c r="O37" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="P37" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>11</v>
+      </c>
+      <c r="R37" t="n">
         <v>19</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="S37" t="n">
         <v>9</v>
-      </c>
-      <c r="R37" t="n">
-        <v>16</v>
-      </c>
-      <c r="S37" t="n">
-        <v>8</v>
       </c>
       <c r="T37" t="n">
         <v>13</v>
@@ -3131,16 +3129,16 @@
         <v>5.6</v>
       </c>
       <c r="O38" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P38" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Q38" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="R38" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="S38" t="n">
         <v>14</v>
@@ -3202,16 +3200,16 @@
         <v>-3</v>
       </c>
       <c r="O39" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="P39" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="Q39" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="R39" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="S39" t="n">
         <v>17</v>
@@ -3273,19 +3271,19 @@
         <v>3.2</v>
       </c>
       <c r="O40" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P40" t="n">
         <v>17</v>
       </c>
       <c r="Q40" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R40" t="n">
         <v>20</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T40" t="n">
         <v>21</v>
@@ -3344,16 +3342,16 @@
         <v>-3</v>
       </c>
       <c r="O41" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P41" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q41" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R41" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S41" t="n">
         <v>31</v>
@@ -3415,19 +3413,19 @@
         <v>4.6</v>
       </c>
       <c r="O42" t="n">
+        <v>31</v>
+      </c>
+      <c r="P42" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>28</v>
+      </c>
+      <c r="R42" t="n">
+        <v>27</v>
+      </c>
+      <c r="S42" t="n">
         <v>32</v>
-      </c>
-      <c r="P42" t="n">
-        <v>34</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>31</v>
-      </c>
-      <c r="R42" t="n">
-        <v>32</v>
-      </c>
-      <c r="S42" t="n">
-        <v>37</v>
       </c>
       <c r="T42" t="n">
         <v>31</v>
@@ -3486,19 +3484,19 @@
         <v>1.2</v>
       </c>
       <c r="O43" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P43" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="Q43" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R43" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="S43" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="T43" t="n">
         <v>27</v>
@@ -3557,19 +3555,19 @@
         <v>0.8</v>
       </c>
       <c r="O44" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="P44" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q44" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R44" t="n">
         <v>36</v>
       </c>
       <c r="S44" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T44" t="n">
         <v>42</v>
@@ -3628,19 +3626,19 @@
         <v>2.4</v>
       </c>
       <c r="O45" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P45" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="Q45" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="R45" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="S45" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="T45" t="n">
         <v>55</v>
@@ -3699,16 +3697,16 @@
         <v>-5.6</v>
       </c>
       <c r="O46" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P46" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q46" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="R46" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="S46" t="n">
         <v>44</v>
@@ -3770,19 +3768,19 @@
         <v>13</v>
       </c>
       <c r="O47" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="P47" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="Q47" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="R47" t="n">
         <v>54</v>
       </c>
       <c r="S47" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="T47" t="n">
         <v>52</v>
@@ -3841,16 +3839,16 @@
         <v>12</v>
       </c>
       <c r="O48" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P48" t="n">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="Q48" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="R48" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S48" t="n">
         <v>92</v>
@@ -3912,19 +3910,19 @@
         <v>10</v>
       </c>
       <c r="O49" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="P49" t="n">
+        <v>145</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>125</v>
+      </c>
+      <c r="R49" t="n">
         <v>136</v>
       </c>
-      <c r="Q49" t="n">
-        <v>124</v>
-      </c>
-      <c r="R49" t="n">
-        <v>130</v>
-      </c>
       <c r="S49" t="n">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="T49" t="n">
         <v>133</v>
@@ -3983,10 +3981,10 @@
         <v>19.8</v>
       </c>
       <c r="O50" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P50" t="n">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="Q50" t="n">
         <v>187</v>
@@ -3995,10 +3993,10 @@
         <v>168</v>
       </c>
       <c r="S50" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="T50" t="n">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="U50" t="n">
         <v>1407.8</v>
@@ -4054,19 +4052,19 @@
         <v>23</v>
       </c>
       <c r="O51" t="n">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="P51" t="n">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="Q51" t="n">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="R51" t="n">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="S51" t="n">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="T51" t="n">
         <v>205</v>
@@ -4125,19 +4123,19 @@
         <v>15.4</v>
       </c>
       <c r="O52" t="n">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="P52" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="Q52" t="n">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R52" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="S52" t="n">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="T52" t="n">
         <v>202</v>
@@ -4196,19 +4194,19 @@
         <v>11</v>
       </c>
       <c r="O53" t="n">
+        <v>3</v>
+      </c>
+      <c r="P53" t="n">
         <v>2</v>
-      </c>
-      <c r="P53" t="n">
-        <v>1</v>
       </c>
       <c r="Q53" t="n">
         <v>3</v>
       </c>
       <c r="R53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T53" t="n">
         <v>3</v>
@@ -4240,50 +4238,52 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G54" t="n">
-        <v>2010</v>
+        <v>1986.9</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.7024</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>124.87</v>
+        <v>124.76</v>
       </c>
       <c r="J54" t="n">
-        <v>107.49</v>
+        <v>107.25</v>
       </c>
       <c r="K54" t="n">
-        <v>17.39</v>
+        <v>17.51</v>
       </c>
       <c r="L54" t="n">
-        <v>0.311</v>
+        <v>0.3105</v>
       </c>
       <c r="M54" t="n">
-        <v>0.1337</v>
+        <v>0.1343</v>
       </c>
       <c r="N54" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="O54" t="n">
         <v>8</v>
       </c>
       <c r="P54" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Q54" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R54" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S54" t="n">
-        <v>12</v>
-      </c>
-      <c r="T54" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="T54" t="n">
+        <v>10</v>
+      </c>
       <c r="U54" t="n">
-        <v>1769.7</v>
+        <v>1754.6</v>
       </c>
     </row>
     <row r="55">
@@ -4339,10 +4339,10 @@
         <v>10</v>
       </c>
       <c r="P55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q55" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="R55" t="n">
         <v>11</v>
@@ -4380,50 +4380,52 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G56" t="n">
-        <v>1977</v>
+        <v>1961.7</v>
       </c>
       <c r="H56" t="n">
-        <v>5.1479</v>
+        <v>5.2535</v>
       </c>
       <c r="I56" t="n">
-        <v>122.87</v>
+        <v>122.84</v>
       </c>
       <c r="J56" t="n">
-        <v>109.33</v>
+        <v>109.47</v>
       </c>
       <c r="K56" t="n">
-        <v>13.54</v>
+        <v>13.37</v>
       </c>
       <c r="L56" t="n">
-        <v>0.2979</v>
+        <v>0.3045</v>
       </c>
       <c r="M56" t="n">
-        <v>0.1206</v>
+        <v>0.1197</v>
       </c>
       <c r="N56" t="n">
-        <v>8.199999999999999</v>
+        <v>-0.8</v>
       </c>
       <c r="O56" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P56" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q56" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R56" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
-      </c>
-      <c r="T56" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="T56" t="n">
+        <v>18</v>
+      </c>
       <c r="U56" t="n">
-        <v>1736</v>
+        <v>1726.7</v>
       </c>
     </row>
     <row r="57">
@@ -4476,19 +4478,19 @@
         <v>8</v>
       </c>
       <c r="O57" t="n">
+        <v>23</v>
+      </c>
+      <c r="P57" t="n">
         <v>22</v>
-      </c>
-      <c r="P57" t="n">
-        <v>21</v>
       </c>
       <c r="Q57" t="n">
         <v>23</v>
       </c>
       <c r="R57" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="S57" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="T57" t="n">
         <v>26</v>
@@ -4547,10 +4549,10 @@
         <v>2.2</v>
       </c>
       <c r="O58" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="P58" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Q58" t="n">
         <v>22</v>
@@ -4559,7 +4561,7 @@
         <v>22</v>
       </c>
       <c r="S58" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="T58" t="n">
         <v>24</v>
@@ -4618,16 +4620,16 @@
         <v>2</v>
       </c>
       <c r="O59" t="n">
+        <v>29</v>
+      </c>
+      <c r="P59" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>27</v>
+      </c>
+      <c r="R59" t="n">
         <v>31</v>
-      </c>
-      <c r="P59" t="n">
-        <v>37</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>28</v>
-      </c>
-      <c r="R59" t="n">
-        <v>33</v>
       </c>
       <c r="S59" t="n">
         <v>26</v>
@@ -4689,19 +4691,19 @@
         <v>-1</v>
       </c>
       <c r="O60" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P60" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="Q60" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="R60" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S60" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="T60" t="n">
         <v>33</v>
@@ -4760,19 +4762,19 @@
         <v>4.2</v>
       </c>
       <c r="O61" t="n">
+        <v>35</v>
+      </c>
+      <c r="P61" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>37</v>
+      </c>
+      <c r="R61" t="n">
+        <v>33</v>
+      </c>
+      <c r="S61" t="n">
         <v>30</v>
-      </c>
-      <c r="P61" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>33</v>
-      </c>
-      <c r="R61" t="n">
-        <v>26</v>
-      </c>
-      <c r="S61" t="n">
-        <v>29</v>
       </c>
       <c r="T61" t="n">
         <v>29</v>
@@ -4831,16 +4833,16 @@
         <v>0.4</v>
       </c>
       <c r="O62" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="P62" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q62" t="n">
+        <v>53</v>
+      </c>
+      <c r="R62" t="n">
         <v>51</v>
-      </c>
-      <c r="R62" t="n">
-        <v>52</v>
       </c>
       <c r="S62" t="n">
         <v>43</v>
@@ -4902,19 +4904,19 @@
         <v>-6.6</v>
       </c>
       <c r="O63" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P63" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="Q63" t="n">
         <v>34</v>
       </c>
       <c r="R63" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S63" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T63" t="n">
         <v>35</v>
@@ -4973,19 +4975,19 @@
         <v>-8</v>
       </c>
       <c r="O64" t="n">
+        <v>33</v>
+      </c>
+      <c r="P64" t="n">
         <v>37</v>
       </c>
-      <c r="P64" t="n">
-        <v>39</v>
-      </c>
       <c r="Q64" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="R64" t="n">
+        <v>42</v>
+      </c>
+      <c r="S64" t="n">
         <v>46</v>
-      </c>
-      <c r="S64" t="n">
-        <v>47</v>
       </c>
       <c r="T64" t="n">
         <v>41</v>
@@ -5044,19 +5046,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="O65" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P65" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="Q65" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="R65" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="S65" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="T65" t="n">
         <v>76</v>
@@ -5115,19 +5117,19 @@
         <v>6.8</v>
       </c>
       <c r="O66" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="P66" t="n">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="Q66" t="n">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="R66" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="S66" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="T66" t="n">
         <v>112</v>
@@ -5186,19 +5188,19 @@
         <v>3.2</v>
       </c>
       <c r="O67" t="n">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="P67" t="n">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="Q67" t="n">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="R67" t="n">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="S67" t="n">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="T67" t="n">
         <v>170</v>
@@ -5257,16 +5259,16 @@
         <v>6.4</v>
       </c>
       <c r="O68" t="n">
+        <v>183</v>
+      </c>
+      <c r="P68" t="n">
+        <v>192</v>
+      </c>
+      <c r="Q68" t="n">
         <v>181</v>
       </c>
-      <c r="P68" t="n">
-        <v>184</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>178</v>
-      </c>
       <c r="R68" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S68" t="n">
         <v>171</v>
@@ -5328,19 +5330,19 @@
         <v>10.4</v>
       </c>
       <c r="O69" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P69" t="n">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q69" t="n">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="R69" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="S69" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="T69" t="n">
         <v>200</v>

--- a/team_stats_2026.xlsx
+++ b/team_stats_2026.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,107 +417,107 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>TeamID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Is_FirstFour</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Last_DayNum</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>elo_last</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>elo_trend</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>avg_off_rtg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>avg_def_rtg</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>avg_net_rtg</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>avg_oreb_pct</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>avg_tov_pct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>last5_Margin</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rank_POM</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rank_MAS</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rank_MOR</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rank_WLK</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>rank_BIH</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>rank_NET</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>elo_sos</t>
         </is>
@@ -671,7 +659,7 @@
         <v>4</v>
       </c>
       <c r="T3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U3" t="n">
         <v>1670.2</v>
@@ -813,7 +801,7 @@
         <v>15</v>
       </c>
       <c r="T5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="U5" t="n">
         <v>1791.1</v>
@@ -884,7 +872,7 @@
         <v>16</v>
       </c>
       <c r="T6" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="U6" t="n">
         <v>1691.6</v>
@@ -955,7 +943,7 @@
         <v>28</v>
       </c>
       <c r="T7" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="U7" t="n">
         <v>1686.1</v>
@@ -1026,7 +1014,7 @@
         <v>33</v>
       </c>
       <c r="T8" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="U8" t="n">
         <v>1706.3</v>
@@ -1097,7 +1085,7 @@
         <v>38</v>
       </c>
       <c r="T9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U9" t="n">
         <v>1722.9</v>
@@ -1168,7 +1156,7 @@
         <v>35</v>
       </c>
       <c r="T10" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="U10" t="n">
         <v>1691.3</v>
@@ -1307,9 +1295,11 @@
         <v>45</v>
       </c>
       <c r="S12" t="n">
-        <v>51</v>
-      </c>
-      <c r="T12" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="T12" t="n">
+        <v>45</v>
+      </c>
       <c r="U12" t="n">
         <v>1554.8</v>
       </c>
@@ -1450,7 +1440,7 @@
         <v>81</v>
       </c>
       <c r="T14" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="U14" t="n">
         <v>1462.4</v>
@@ -1521,7 +1511,7 @@
         <v>98</v>
       </c>
       <c r="T15" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="U15" t="n">
         <v>1410.6</v>
@@ -1592,7 +1582,7 @@
         <v>183</v>
       </c>
       <c r="T16" t="n">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="U16" t="n">
         <v>1422.2</v>
@@ -1663,7 +1653,7 @@
         <v>172</v>
       </c>
       <c r="T17" t="n">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="U17" t="n">
         <v>1430.3</v>
@@ -1802,10 +1792,10 @@
         <v>6</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U19" t="n">
         <v>1742.7</v>
@@ -1876,7 +1866,7 @@
         <v>13</v>
       </c>
       <c r="T20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U20" t="n">
         <v>1717.2</v>
@@ -1947,7 +1937,7 @@
         <v>11</v>
       </c>
       <c r="T21" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="U21" t="n">
         <v>1675.8</v>
@@ -2015,9 +2005,11 @@
         <v>12</v>
       </c>
       <c r="S22" t="n">
-        <v>18</v>
-      </c>
-      <c r="T22" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="T22" t="n">
+        <v>13</v>
+      </c>
       <c r="U22" t="n">
         <v>1718.8</v>
       </c>
@@ -2087,7 +2079,7 @@
         <v>19</v>
       </c>
       <c r="T23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U23" t="n">
         <v>1677.4</v>
@@ -2158,7 +2150,7 @@
         <v>21</v>
       </c>
       <c r="T24" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="U24" t="n">
         <v>1596.9</v>
@@ -2229,7 +2221,7 @@
         <v>32</v>
       </c>
       <c r="T25" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="U25" t="n">
         <v>1672.9</v>
@@ -2297,10 +2289,10 @@
         <v>28</v>
       </c>
       <c r="S26" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="T26" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="U26" t="n">
         <v>1712.2</v>
@@ -2371,7 +2363,7 @@
         <v>42</v>
       </c>
       <c r="T27" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="U27" t="n">
         <v>1653.7</v>
@@ -2439,9 +2431,11 @@
         <v>41</v>
       </c>
       <c r="S28" t="n">
-        <v>40</v>
-      </c>
-      <c r="T28" t="inlineStr"/>
+        <v>39</v>
+      </c>
+      <c r="T28" t="n">
+        <v>43</v>
+      </c>
       <c r="U28" t="n">
         <v>1558.4</v>
       </c>
@@ -2508,10 +2502,10 @@
         <v>63</v>
       </c>
       <c r="S29" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T29" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="U29" t="n">
         <v>1428.4</v>
@@ -2582,7 +2576,7 @@
         <v>120</v>
       </c>
       <c r="T30" t="n">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="U30" t="n">
         <v>1466</v>
@@ -2650,9 +2644,11 @@
         <v>139</v>
       </c>
       <c r="S31" t="n">
-        <v>138</v>
-      </c>
-      <c r="T31" t="inlineStr"/>
+        <v>128</v>
+      </c>
+      <c r="T31" t="n">
+        <v>139</v>
+      </c>
       <c r="U31" t="n">
         <v>1493.7</v>
       </c>
@@ -2722,7 +2718,7 @@
         <v>174</v>
       </c>
       <c r="T32" t="n">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="U32" t="n">
         <v>1415.2</v>
@@ -2793,7 +2789,7 @@
         <v>306</v>
       </c>
       <c r="T33" t="n">
-        <v>316</v>
+        <v>300</v>
       </c>
       <c r="U33" t="n">
         <v>1383.4</v>
@@ -2864,7 +2860,7 @@
         <v>263</v>
       </c>
       <c r="T34" t="n">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="U34" t="n">
         <v>1399</v>
@@ -2934,7 +2930,9 @@
       <c r="S35" t="n">
         <v>3</v>
       </c>
-      <c r="T35" t="inlineStr"/>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
       <c r="U35" t="n">
         <v>1779.9</v>
       </c>
@@ -3004,7 +3002,7 @@
         <v>10</v>
       </c>
       <c r="T36" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U36" t="n">
         <v>1718</v>
@@ -3075,7 +3073,7 @@
         <v>8</v>
       </c>
       <c r="T37" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U37" t="n">
         <v>1665.9</v>
@@ -3146,7 +3144,7 @@
         <v>14</v>
       </c>
       <c r="T38" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U38" t="n">
         <v>1767</v>
@@ -3217,7 +3215,7 @@
         <v>17</v>
       </c>
       <c r="T39" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="U39" t="n">
         <v>1772.3</v>
@@ -3285,10 +3283,10 @@
         <v>20</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T40" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U40" t="n">
         <v>1716.9</v>
@@ -3430,7 +3428,7 @@
         <v>37</v>
       </c>
       <c r="T42" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="U42" t="n">
         <v>1643.1</v>
@@ -3501,7 +3499,7 @@
         <v>30</v>
       </c>
       <c r="T43" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="U43" t="n">
         <v>1516.9</v>
@@ -3572,7 +3570,7 @@
         <v>34</v>
       </c>
       <c r="T44" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="U44" t="n">
         <v>1596.2</v>
@@ -3643,7 +3641,7 @@
         <v>22</v>
       </c>
       <c r="T45" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="U45" t="n">
         <v>1416.9</v>
@@ -3714,7 +3712,7 @@
         <v>44</v>
       </c>
       <c r="T46" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="U46" t="n">
         <v>1649.8</v>
@@ -3782,10 +3780,10 @@
         <v>54</v>
       </c>
       <c r="S47" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="T47" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="U47" t="n">
         <v>1479.2</v>
@@ -3927,7 +3925,7 @@
         <v>124</v>
       </c>
       <c r="T49" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="U49" t="n">
         <v>1431.7</v>
@@ -3998,7 +3996,7 @@
         <v>152</v>
       </c>
       <c r="T50" t="n">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="U50" t="n">
         <v>1407.8</v>
@@ -4069,7 +4067,7 @@
         <v>189</v>
       </c>
       <c r="T51" t="n">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="U51" t="n">
         <v>1369.1</v>
@@ -4137,10 +4135,10 @@
         <v>196</v>
       </c>
       <c r="S52" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="T52" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="U52" t="n">
         <v>1372.4</v>
@@ -4281,7 +4279,9 @@
       <c r="S54" t="n">
         <v>12</v>
       </c>
-      <c r="T54" t="inlineStr"/>
+      <c r="T54" t="n">
+        <v>9</v>
+      </c>
       <c r="U54" t="n">
         <v>1769.7</v>
       </c>
@@ -4348,10 +4348,10 @@
         <v>11</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T55" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U55" t="n">
         <v>1601.3</v>
@@ -4419,9 +4419,11 @@
         <v>14</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
-      </c>
-      <c r="T56" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="T56" t="n">
+        <v>15</v>
+      </c>
       <c r="U56" t="n">
         <v>1736</v>
       </c>
@@ -4491,7 +4493,7 @@
         <v>27</v>
       </c>
       <c r="T57" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="U57" t="n">
         <v>1724.6</v>
@@ -4562,7 +4564,7 @@
         <v>23</v>
       </c>
       <c r="T58" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="U58" t="n">
         <v>1733.2</v>
@@ -4630,7 +4632,7 @@
         <v>33</v>
       </c>
       <c r="S59" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T59" t="n">
         <v>32</v>
@@ -4704,7 +4706,7 @@
         <v>24</v>
       </c>
       <c r="T60" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="U60" t="n">
         <v>1641.5</v>
@@ -4775,7 +4777,7 @@
         <v>29</v>
       </c>
       <c r="T61" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U61" t="n">
         <v>1611.4</v>
@@ -4846,7 +4848,7 @@
         <v>43</v>
       </c>
       <c r="T62" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="U62" t="n">
         <v>1658.3</v>
@@ -4917,7 +4919,7 @@
         <v>41</v>
       </c>
       <c r="T63" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="U63" t="n">
         <v>1681.7</v>
@@ -4988,7 +4990,7 @@
         <v>47</v>
       </c>
       <c r="T64" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="U64" t="n">
         <v>1696.4</v>
@@ -5059,7 +5061,7 @@
         <v>75</v>
       </c>
       <c r="T65" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="U65" t="n">
         <v>1382.5</v>
@@ -5130,7 +5132,7 @@
         <v>93</v>
       </c>
       <c r="T66" t="n">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="U66" t="n">
         <v>1452.3</v>
@@ -5201,7 +5203,7 @@
         <v>149</v>
       </c>
       <c r="T67" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="U67" t="n">
         <v>1474.6</v>
@@ -5272,7 +5274,7 @@
         <v>171</v>
       </c>
       <c r="T68" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="U68" t="n">
         <v>1430.9</v>
@@ -5343,7 +5345,7 @@
         <v>165</v>
       </c>
       <c r="T69" t="n">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="U69" t="n">
         <v>1378.8</v>

--- a/team_stats_2026.xlsx
+++ b/team_stats_2026.xlsx
@@ -2608,7 +2608,7 @@
         <v>132</v>
       </c>
       <c r="G31" t="n">
-        <v>1458.4</v>
+        <v>1435.4</v>
       </c>
       <c r="H31" t="n">
         <v>1.2024</v>
@@ -4025,31 +4025,31 @@
         <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G51" t="n">
-        <v>1397.9</v>
+        <v>1392.7</v>
       </c>
       <c r="H51" t="n">
-        <v>1.3468</v>
+        <v>1.415</v>
       </c>
       <c r="I51" t="n">
-        <v>113.39</v>
+        <v>113.6</v>
       </c>
       <c r="J51" t="n">
-        <v>101.92</v>
+        <v>102.82</v>
       </c>
       <c r="K51" t="n">
-        <v>11.47</v>
+        <v>10.78</v>
       </c>
       <c r="L51" t="n">
-        <v>0.2176</v>
+        <v>0.2162</v>
       </c>
       <c r="M51" t="n">
-        <v>0.135</v>
+        <v>0.1348</v>
       </c>
       <c r="N51" t="n">
-        <v>23</v>
+        <v>17.6</v>
       </c>
       <c r="O51" t="n">
         <v>185</v>
@@ -4070,7 +4070,7 @@
         <v>196</v>
       </c>
       <c r="U51" t="n">
-        <v>1369.1</v>
+        <v>1369.9</v>
       </c>
     </row>
     <row r="52">
@@ -4096,31 +4096,31 @@
         <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G52" t="n">
-        <v>1407.8</v>
+        <v>1413</v>
       </c>
       <c r="H52" t="n">
-        <v>2.9318</v>
+        <v>2.8128</v>
       </c>
       <c r="I52" t="n">
-        <v>109.06</v>
+        <v>109.77</v>
       </c>
       <c r="J52" t="n">
-        <v>98.31999999999999</v>
+        <v>99.3</v>
       </c>
       <c r="K52" t="n">
-        <v>10.75</v>
+        <v>10.47</v>
       </c>
       <c r="L52" t="n">
-        <v>0.3191</v>
+        <v>0.3178</v>
       </c>
       <c r="M52" t="n">
-        <v>0.1856</v>
+        <v>0.1829</v>
       </c>
       <c r="N52" t="n">
-        <v>15.4</v>
+        <v>11</v>
       </c>
       <c r="O52" t="n">
         <v>207</v>
@@ -4141,7 +4141,7 @@
         <v>203</v>
       </c>
       <c r="U52" t="n">
-        <v>1372.4</v>
+        <v>1374.4</v>
       </c>
     </row>
     <row r="53">
@@ -4877,31 +4877,31 @@
         <v>1</v>
       </c>
       <c r="F63" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="G63" t="n">
-        <v>1734</v>
+        <v>1711.5</v>
       </c>
       <c r="H63" t="n">
-        <v>6.962</v>
+        <v>6.597</v>
       </c>
       <c r="I63" t="n">
-        <v>119.36</v>
+        <v>118.68</v>
       </c>
       <c r="J63" t="n">
-        <v>109.32</v>
+        <v>108.95</v>
       </c>
       <c r="K63" t="n">
-        <v>10.04</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="L63" t="n">
-        <v>0.2802</v>
+        <v>0.282</v>
       </c>
       <c r="M63" t="n">
-        <v>0.1288</v>
+        <v>0.1305</v>
       </c>
       <c r="N63" t="n">
-        <v>-6.6</v>
+        <v>-5.8</v>
       </c>
       <c r="O63" t="n">
         <v>34</v>
@@ -4948,31 +4948,31 @@
         <v>1</v>
       </c>
       <c r="F64" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="G64" t="n">
-        <v>1741.7</v>
+        <v>1764.2</v>
       </c>
       <c r="H64" t="n">
-        <v>2.8164</v>
+        <v>2.6628</v>
       </c>
       <c r="I64" t="n">
-        <v>119.5</v>
+        <v>119</v>
       </c>
       <c r="J64" t="n">
-        <v>111.34</v>
+        <v>110.83</v>
       </c>
       <c r="K64" t="n">
-        <v>8.16</v>
+        <v>8.17</v>
       </c>
       <c r="L64" t="n">
-        <v>0.3072</v>
+        <v>0.3041</v>
       </c>
       <c r="M64" t="n">
-        <v>0.145</v>
+        <v>0.1443</v>
       </c>
       <c r="N64" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="O64" t="n">
         <v>37</v>
@@ -4993,7 +4993,7 @@
         <v>42</v>
       </c>
       <c r="U64" t="n">
-        <v>1696.4</v>
+        <v>1698.6</v>
       </c>
     </row>
     <row r="65">

--- a/team_stats_2026.xlsx
+++ b/team_stats_2026.xlsx
@@ -2747,31 +2747,31 @@
         <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G33" t="n">
-        <v>1266.7</v>
+        <v>1272.1</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5639999999999999</v>
+        <v>-0.4587</v>
       </c>
       <c r="I33" t="n">
-        <v>104.38</v>
+        <v>104.27</v>
       </c>
       <c r="J33" t="n">
-        <v>107.11</v>
+        <v>106.28</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.73</v>
+        <v>-2.01</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2878</v>
+        <v>0.2897</v>
       </c>
       <c r="M33" t="n">
-        <v>0.1551</v>
+        <v>0.1584</v>
       </c>
       <c r="N33" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="O33" t="n">
         <v>288</v>
@@ -2792,7 +2792,7 @@
         <v>300</v>
       </c>
       <c r="U33" t="n">
-        <v>1383.4</v>
+        <v>1381.2</v>
       </c>
     </row>
     <row r="34">
@@ -2818,31 +2818,31 @@
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="G34" t="n">
-        <v>1325.5</v>
+        <v>1320.2</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.465</v>
+        <v>-0.3498</v>
       </c>
       <c r="I34" t="n">
-        <v>105.58</v>
+        <v>104.5</v>
       </c>
       <c r="J34" t="n">
-        <v>108.39</v>
+        <v>108.29</v>
       </c>
       <c r="K34" t="n">
-        <v>-2.8</v>
+        <v>-3.79</v>
       </c>
       <c r="L34" t="n">
-        <v>0.2229</v>
+        <v>0.2201</v>
       </c>
       <c r="M34" t="n">
-        <v>0.1707</v>
+        <v>0.1701</v>
       </c>
       <c r="N34" t="n">
-        <v>7.8</v>
+        <v>4.4</v>
       </c>
       <c r="O34" t="n">
         <v>284</v>
@@ -2863,7 +2863,7 @@
         <v>275</v>
       </c>
       <c r="U34" t="n">
-        <v>1399</v>
+        <v>1394.1</v>
       </c>
     </row>
     <row r="35">
@@ -3599,28 +3599,28 @@
         <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="G45" t="n">
-        <v>1758.6</v>
+        <v>1780.4</v>
       </c>
       <c r="H45" t="n">
-        <v>9.362500000000001</v>
+        <v>8.9497</v>
       </c>
       <c r="I45" t="n">
-        <v>120.74</v>
+        <v>121.34</v>
       </c>
       <c r="J45" t="n">
-        <v>105.88</v>
+        <v>106.31</v>
       </c>
       <c r="K45" t="n">
-        <v>14.87</v>
+        <v>15.03</v>
       </c>
       <c r="L45" t="n">
-        <v>0.2186</v>
+        <v>0.2222</v>
       </c>
       <c r="M45" t="n">
-        <v>0.1413</v>
+        <v>0.1392</v>
       </c>
       <c r="N45" t="n">
         <v>2.4</v>
@@ -3644,7 +3644,7 @@
         <v>64</v>
       </c>
       <c r="U45" t="n">
-        <v>1416.9</v>
+        <v>1429.2</v>
       </c>
     </row>
     <row r="46">
@@ -3670,31 +3670,31 @@
         <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="G46" t="n">
-        <v>1733.9</v>
+        <v>1712.1</v>
       </c>
       <c r="H46" t="n">
-        <v>0.2411</v>
+        <v>-0.0531</v>
       </c>
       <c r="I46" t="n">
-        <v>117.96</v>
+        <v>118.26</v>
       </c>
       <c r="J46" t="n">
-        <v>109.76</v>
+        <v>110.82</v>
       </c>
       <c r="K46" t="n">
-        <v>8.199999999999999</v>
+        <v>7.44</v>
       </c>
       <c r="L46" t="n">
-        <v>0.3098</v>
+        <v>0.3109</v>
       </c>
       <c r="M46" t="n">
-        <v>0.1542</v>
+        <v>0.1499</v>
       </c>
       <c r="N46" t="n">
-        <v>-5.6</v>
+        <v>-3.6</v>
       </c>
       <c r="O46" t="n">
         <v>42</v>
@@ -3715,7 +3715,7 @@
         <v>37</v>
       </c>
       <c r="U46" t="n">
-        <v>1649.8</v>
+        <v>1652.1</v>
       </c>
     </row>
     <row r="47">

--- a/team_stats_2026.xlsx
+++ b/team_stats_2026.xlsx
@@ -546,31 +546,31 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="G2" t="n">
-        <v>2195.9</v>
+        <v>2196.7</v>
       </c>
       <c r="H2" t="n">
-        <v>3.7176</v>
+        <v>3.7365</v>
       </c>
       <c r="I2" t="n">
-        <v>122.74</v>
+        <v>122.61</v>
       </c>
       <c r="J2" t="n">
-        <v>94.67</v>
+        <v>95</v>
       </c>
       <c r="K2" t="n">
-        <v>28.07</v>
+        <v>27.61</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2982</v>
+        <v>0.299</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1541</v>
+        <v>0.1534</v>
       </c>
       <c r="N2" t="n">
-        <v>12.2</v>
+        <v>7.6</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -591,7 +591,7 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>1712.3</v>
+        <v>1700.6</v>
       </c>
     </row>
     <row r="3">
@@ -688,31 +688,31 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="G4" t="n">
-        <v>2027.4</v>
+        <v>2031.4</v>
       </c>
       <c r="H4" t="n">
-        <v>0.218</v>
+        <v>0.0735</v>
       </c>
       <c r="I4" t="n">
-        <v>117.66</v>
+        <v>117.93</v>
       </c>
       <c r="J4" t="n">
-        <v>102.12</v>
+        <v>101.4</v>
       </c>
       <c r="K4" t="n">
-        <v>15.54</v>
+        <v>16.54</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2963</v>
+        <v>0.2897</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1607</v>
+        <v>0.1613</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>5.6</v>
       </c>
       <c r="O4" t="n">
         <v>9</v>
@@ -733,7 +733,7 @@
         <v>11</v>
       </c>
       <c r="U4" t="n">
-        <v>1730.1</v>
+        <v>1723.2</v>
       </c>
     </row>
     <row r="5">
@@ -901,31 +901,31 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="G7" t="n">
-        <v>1836.9</v>
+        <v>1854.1</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.5958</v>
+        <v>-2.5004</v>
       </c>
       <c r="I7" t="n">
-        <v>118.9</v>
+        <v>118.73</v>
       </c>
       <c r="J7" t="n">
-        <v>101.88</v>
+        <v>101.94</v>
       </c>
       <c r="K7" t="n">
-        <v>17.02</v>
+        <v>16.79</v>
       </c>
       <c r="L7" t="n">
-        <v>0.289</v>
+        <v>0.2886</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1597</v>
+        <v>0.1645</v>
       </c>
       <c r="N7" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="O7" t="n">
         <v>19</v>
@@ -946,7 +946,7 @@
         <v>17</v>
       </c>
       <c r="U7" t="n">
-        <v>1686.1</v>
+        <v>1686.9</v>
       </c>
     </row>
     <row r="8">
@@ -1043,31 +1043,31 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="G9" t="n">
-        <v>1813.9</v>
+        <v>1789.3</v>
       </c>
       <c r="H9" t="n">
-        <v>1.9487</v>
+        <v>2.1115</v>
       </c>
       <c r="I9" t="n">
-        <v>118</v>
+        <v>117.64</v>
       </c>
       <c r="J9" t="n">
         <v>108.07</v>
       </c>
       <c r="K9" t="n">
-        <v>9.93</v>
+        <v>9.57</v>
       </c>
       <c r="L9" t="n">
-        <v>0.255</v>
+        <v>0.2568</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1503</v>
+        <v>0.1489</v>
       </c>
       <c r="N9" t="n">
-        <v>10.4</v>
+        <v>8.4</v>
       </c>
       <c r="O9" t="n">
         <v>26</v>
@@ -1088,7 +1088,7 @@
         <v>29</v>
       </c>
       <c r="U9" t="n">
-        <v>1722.9</v>
+        <v>1723.3</v>
       </c>
     </row>
     <row r="10">
@@ -1114,31 +1114,31 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="G10" t="n">
-        <v>1836.1</v>
+        <v>1860.6</v>
       </c>
       <c r="H10" t="n">
-        <v>6.9164</v>
+        <v>6.8435</v>
       </c>
       <c r="I10" t="n">
-        <v>111.16</v>
+        <v>111.03</v>
       </c>
       <c r="J10" t="n">
-        <v>102.34</v>
+        <v>102.3</v>
       </c>
       <c r="K10" t="n">
-        <v>8.81</v>
+        <v>8.73</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3231</v>
+        <v>0.3183</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1514</v>
+        <v>0.1496</v>
       </c>
       <c r="N10" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="O10" t="n">
         <v>43</v>
@@ -1159,7 +1159,7 @@
         <v>39</v>
       </c>
       <c r="U10" t="n">
-        <v>1691.3</v>
+        <v>1693.5</v>
       </c>
     </row>
     <row r="11">
@@ -1256,31 +1256,31 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G12" t="n">
-        <v>1723.5</v>
+        <v>1706.2</v>
       </c>
       <c r="H12" t="n">
-        <v>8.857799999999999</v>
+        <v>8.7103</v>
       </c>
       <c r="I12" t="n">
-        <v>115.66</v>
+        <v>115.38</v>
       </c>
       <c r="J12" t="n">
-        <v>100.71</v>
+        <v>101.32</v>
       </c>
       <c r="K12" t="n">
-        <v>14.95</v>
+        <v>14.06</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3398</v>
+        <v>0.3458</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1464</v>
+        <v>0.1454</v>
       </c>
       <c r="N12" t="n">
-        <v>19</v>
+        <v>12.6</v>
       </c>
       <c r="O12" t="n">
         <v>47</v>
@@ -1301,7 +1301,7 @@
         <v>45</v>
       </c>
       <c r="U12" t="n">
-        <v>1554.8</v>
+        <v>1565.3</v>
       </c>
     </row>
     <row r="13">
@@ -1469,31 +1469,31 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="G15" t="n">
-        <v>1593.8</v>
+        <v>1589.8</v>
       </c>
       <c r="H15" t="n">
-        <v>3.5257</v>
+        <v>3.408</v>
       </c>
       <c r="I15" t="n">
-        <v>114.28</v>
+        <v>113.47</v>
       </c>
       <c r="J15" t="n">
-        <v>102.18</v>
+        <v>103.17</v>
       </c>
       <c r="K15" t="n">
-        <v>12.1</v>
+        <v>10.3</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3104</v>
+        <v>0.3053</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1506</v>
+        <v>0.151</v>
       </c>
       <c r="N15" t="n">
-        <v>10.8</v>
+        <v>10.2</v>
       </c>
       <c r="O15" t="n">
         <v>113</v>
@@ -1514,7 +1514,7 @@
         <v>114</v>
       </c>
       <c r="U15" t="n">
-        <v>1410.6</v>
+        <v>1434.7</v>
       </c>
     </row>
     <row r="16">
@@ -1611,31 +1611,31 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="G17" t="n">
-        <v>1478</v>
+        <v>1477.2</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9489</v>
+        <v>0.9855</v>
       </c>
       <c r="I17" t="n">
-        <v>109.73</v>
+        <v>109.58</v>
       </c>
       <c r="J17" t="n">
-        <v>101.77</v>
+        <v>102.38</v>
       </c>
       <c r="K17" t="n">
-        <v>7.95</v>
+        <v>7.2</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2799</v>
+        <v>0.2829</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1508</v>
+        <v>0.1493</v>
       </c>
       <c r="N17" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="O17" t="n">
         <v>192</v>
@@ -1656,7 +1656,7 @@
         <v>183</v>
       </c>
       <c r="U17" t="n">
-        <v>1430.3</v>
+        <v>1458.8</v>
       </c>
     </row>
     <row r="18">
@@ -1753,31 +1753,31 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="G19" t="n">
-        <v>2111.7</v>
+        <v>2112.6</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2196</v>
+        <v>1.1096</v>
       </c>
       <c r="I19" t="n">
-        <v>117.35</v>
+        <v>117.42</v>
       </c>
       <c r="J19" t="n">
-        <v>95.8</v>
+        <v>94.67</v>
       </c>
       <c r="K19" t="n">
-        <v>21.55</v>
+        <v>22.76</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3386</v>
+        <v>0.3319</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1236</v>
+        <v>0.1229</v>
       </c>
       <c r="N19" t="n">
-        <v>8.800000000000001</v>
+        <v>12.4</v>
       </c>
       <c r="O19" t="n">
         <v>5</v>
@@ -1798,7 +1798,7 @@
         <v>5</v>
       </c>
       <c r="U19" t="n">
-        <v>1742.7</v>
+        <v>1725.6</v>
       </c>
     </row>
     <row r="20">
@@ -1824,31 +1824,31 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="G20" t="n">
-        <v>1982.7</v>
+        <v>1984.4</v>
       </c>
       <c r="H20" t="n">
-        <v>7.8712</v>
+        <v>7.3951</v>
       </c>
       <c r="I20" t="n">
-        <v>125.11</v>
+        <v>126.53</v>
       </c>
       <c r="J20" t="n">
-        <v>103.66</v>
+        <v>103.56</v>
       </c>
       <c r="K20" t="n">
-        <v>21.45</v>
+        <v>22.97</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3222</v>
+        <v>0.3263</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1281</v>
+        <v>0.1252</v>
       </c>
       <c r="N20" t="n">
-        <v>2.8</v>
+        <v>10</v>
       </c>
       <c r="O20" t="n">
         <v>7</v>
@@ -1869,7 +1869,7 @@
         <v>8</v>
       </c>
       <c r="U20" t="n">
-        <v>1717.2</v>
+        <v>1704.4</v>
       </c>
     </row>
     <row r="21">
@@ -1895,31 +1895,31 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="G21" t="n">
-        <v>1982.9</v>
+        <v>1988</v>
       </c>
       <c r="H21" t="n">
-        <v>9.932399999999999</v>
+        <v>9.170199999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>114.61</v>
+        <v>115.23</v>
       </c>
       <c r="J21" t="n">
-        <v>98.94</v>
+        <v>97.83</v>
       </c>
       <c r="K21" t="n">
-        <v>15.67</v>
+        <v>17.4</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2433</v>
+        <v>0.2465</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1403</v>
+        <v>0.1386</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2</v>
+        <v>3.4</v>
       </c>
       <c r="O21" t="n">
         <v>14</v>
@@ -1940,7 +1940,7 @@
         <v>14</v>
       </c>
       <c r="U21" t="n">
-        <v>1675.8</v>
+        <v>1669.8</v>
       </c>
     </row>
     <row r="22">
@@ -1966,31 +1966,31 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G22" t="n">
-        <v>1952.6</v>
+        <v>1963.8</v>
       </c>
       <c r="H22" t="n">
-        <v>1.6305</v>
+        <v>1.4886</v>
       </c>
       <c r="I22" t="n">
-        <v>122.08</v>
+        <v>122.22</v>
       </c>
       <c r="J22" t="n">
-        <v>106.87</v>
+        <v>106.71</v>
       </c>
       <c r="K22" t="n">
-        <v>15.21</v>
+        <v>15.51</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2915</v>
+        <v>0.2897</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1281</v>
+        <v>0.1312</v>
       </c>
       <c r="N22" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="O22" t="n">
         <v>12</v>
@@ -2011,7 +2011,7 @@
         <v>13</v>
       </c>
       <c r="U22" t="n">
-        <v>1718.8</v>
+        <v>1716.9</v>
       </c>
     </row>
     <row r="23">
@@ -2037,31 +2037,31 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="G23" t="n">
-        <v>1899.5</v>
+        <v>1863.3</v>
       </c>
       <c r="H23" t="n">
-        <v>2.2848</v>
+        <v>2.0961</v>
       </c>
       <c r="I23" t="n">
-        <v>115.28</v>
+        <v>114.78</v>
       </c>
       <c r="J23" t="n">
-        <v>103.72</v>
+        <v>103.76</v>
       </c>
       <c r="K23" t="n">
-        <v>11.56</v>
+        <v>11.02</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2596</v>
+        <v>0.258</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1375</v>
+        <v>0.1376</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4</v>
+        <v>-1.8</v>
       </c>
       <c r="O23" t="n">
         <v>29</v>
@@ -2082,7 +2082,7 @@
         <v>24</v>
       </c>
       <c r="U23" t="n">
-        <v>1677.4</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="24">
@@ -2108,31 +2108,31 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="G24" t="n">
-        <v>1857.8</v>
+        <v>1829</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2818</v>
+        <v>-0.1963</v>
       </c>
       <c r="I24" t="n">
-        <v>118.73</v>
+        <v>117.39</v>
       </c>
       <c r="J24" t="n">
-        <v>99.88</v>
+        <v>99.94</v>
       </c>
       <c r="K24" t="n">
-        <v>18.85</v>
+        <v>17.45</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2975</v>
+        <v>0.2968</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1525</v>
+        <v>0.1542</v>
       </c>
       <c r="N24" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="O24" t="n">
         <v>24</v>
@@ -2153,7 +2153,7 @@
         <v>22</v>
       </c>
       <c r="U24" t="n">
-        <v>1596.9</v>
+        <v>1604.4</v>
       </c>
     </row>
     <row r="25">
@@ -2321,31 +2321,31 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="G27" t="n">
-        <v>1824</v>
+        <v>1852.8</v>
       </c>
       <c r="H27" t="n">
-        <v>4.3608</v>
+        <v>4.0806</v>
       </c>
       <c r="I27" t="n">
-        <v>117.14</v>
+        <v>116.94</v>
       </c>
       <c r="J27" t="n">
-        <v>107.43</v>
+        <v>106.22</v>
       </c>
       <c r="K27" t="n">
-        <v>9.699999999999999</v>
+        <v>10.72</v>
       </c>
       <c r="L27" t="n">
-        <v>0.3098</v>
+        <v>0.3101</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1389</v>
+        <v>0.1462</v>
       </c>
       <c r="N27" t="n">
-        <v>-5.4</v>
+        <v>0.2</v>
       </c>
       <c r="O27" t="n">
         <v>39</v>
@@ -2366,7 +2366,7 @@
         <v>44</v>
       </c>
       <c r="U27" t="n">
-        <v>1653.7</v>
+        <v>1661.5</v>
       </c>
     </row>
     <row r="28">
@@ -2392,31 +2392,31 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G28" t="n">
-        <v>1761.3</v>
+        <v>1797.5</v>
       </c>
       <c r="H28" t="n">
-        <v>3.2921</v>
+        <v>3.4141</v>
       </c>
       <c r="I28" t="n">
-        <v>117.94</v>
+        <v>117.66</v>
       </c>
       <c r="J28" t="n">
-        <v>103.32</v>
+        <v>103.37</v>
       </c>
       <c r="K28" t="n">
-        <v>14.61</v>
+        <v>14.29</v>
       </c>
       <c r="L28" t="n">
-        <v>0.2941</v>
+        <v>0.2935</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1467</v>
+        <v>0.1459</v>
       </c>
       <c r="N28" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="O28" t="n">
         <v>45</v>
@@ -2437,7 +2437,7 @@
         <v>43</v>
       </c>
       <c r="U28" t="n">
-        <v>1558.4</v>
+        <v>1569.9</v>
       </c>
     </row>
     <row r="29">
@@ -2463,31 +2463,31 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="G29" t="n">
-        <v>1726.8</v>
+        <v>1715.6</v>
       </c>
       <c r="H29" t="n">
-        <v>2.6895</v>
+        <v>2.6075</v>
       </c>
       <c r="I29" t="n">
-        <v>115.07</v>
+        <v>114.78</v>
       </c>
       <c r="J29" t="n">
-        <v>100.01</v>
+        <v>100.99</v>
       </c>
       <c r="K29" t="n">
-        <v>15.06</v>
+        <v>13.79</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3483</v>
+        <v>0.3535</v>
       </c>
       <c r="M29" t="n">
-        <v>0.139</v>
+        <v>0.137</v>
       </c>
       <c r="N29" t="n">
-        <v>8.199999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="O29" t="n">
         <v>68</v>
@@ -2508,7 +2508,7 @@
         <v>56</v>
       </c>
       <c r="U29" t="n">
-        <v>1428.4</v>
+        <v>1447.5</v>
       </c>
     </row>
     <row r="30">
@@ -2534,31 +2534,31 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="G30" t="n">
-        <v>1601</v>
+        <v>1595.8</v>
       </c>
       <c r="H30" t="n">
-        <v>1.1284</v>
+        <v>1.0762</v>
       </c>
       <c r="I30" t="n">
-        <v>112.28</v>
+        <v>110.67</v>
       </c>
       <c r="J30" t="n">
-        <v>106.19</v>
+        <v>107.2</v>
       </c>
       <c r="K30" t="n">
-        <v>6.08</v>
+        <v>3.47</v>
       </c>
       <c r="L30" t="n">
-        <v>0.316</v>
+        <v>0.3141</v>
       </c>
       <c r="M30" t="n">
-        <v>0.1667</v>
+        <v>0.1706</v>
       </c>
       <c r="N30" t="n">
-        <v>9.4</v>
+        <v>5.8</v>
       </c>
       <c r="O30" t="n">
         <v>143</v>
@@ -2579,7 +2579,7 @@
         <v>125</v>
       </c>
       <c r="U30" t="n">
-        <v>1466</v>
+        <v>1488.7</v>
       </c>
     </row>
     <row r="31">
@@ -2605,31 +2605,31 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G31" t="n">
-        <v>1435.4</v>
+        <v>1433.6</v>
       </c>
       <c r="H31" t="n">
-        <v>1.2024</v>
+        <v>1.3668</v>
       </c>
       <c r="I31" t="n">
-        <v>108.54</v>
+        <v>108.03</v>
       </c>
       <c r="J31" t="n">
-        <v>106.7</v>
+        <v>108.64</v>
       </c>
       <c r="K31" t="n">
-        <v>1.84</v>
+        <v>-0.6</v>
       </c>
       <c r="L31" t="n">
-        <v>0.3143</v>
+        <v>0.3115</v>
       </c>
       <c r="M31" t="n">
-        <v>0.1519</v>
+        <v>0.1505</v>
       </c>
       <c r="N31" t="n">
-        <v>7.8</v>
+        <v>-1</v>
       </c>
       <c r="O31" t="n">
         <v>150</v>
@@ -2650,7 +2650,7 @@
         <v>139</v>
       </c>
       <c r="U31" t="n">
-        <v>1493.7</v>
+        <v>1513.2</v>
       </c>
     </row>
     <row r="32">
@@ -2676,31 +2676,31 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="G32" t="n">
-        <v>1410</v>
+        <v>1409.1</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.3498</v>
+        <v>-0.2978</v>
       </c>
       <c r="I32" t="n">
-        <v>110.28</v>
+        <v>108.98</v>
       </c>
       <c r="J32" t="n">
-        <v>106.53</v>
+        <v>107.14</v>
       </c>
       <c r="K32" t="n">
-        <v>3.75</v>
+        <v>1.84</v>
       </c>
       <c r="L32" t="n">
-        <v>0.2693</v>
+        <v>0.2685</v>
       </c>
       <c r="M32" t="n">
-        <v>0.1475</v>
+        <v>0.147</v>
       </c>
       <c r="N32" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="O32" t="n">
         <v>145</v>
@@ -2721,7 +2721,7 @@
         <v>145</v>
       </c>
       <c r="U32" t="n">
-        <v>1415.2</v>
+        <v>1439.8</v>
       </c>
     </row>
     <row r="33">
@@ -2889,31 +2889,31 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G35" t="n">
-        <v>2173.7</v>
+        <v>2174.3</v>
       </c>
       <c r="H35" t="n">
-        <v>6.5185</v>
+        <v>6.1854</v>
       </c>
       <c r="I35" t="n">
-        <v>120.66</v>
+        <v>121.55</v>
       </c>
       <c r="J35" t="n">
-        <v>97.18000000000001</v>
+        <v>97.56</v>
       </c>
       <c r="K35" t="n">
-        <v>23.48</v>
+        <v>23.99</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2598</v>
+        <v>0.2548</v>
       </c>
       <c r="M35" t="n">
-        <v>0.1613</v>
+        <v>0.1616</v>
       </c>
       <c r="N35" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
@@ -2934,7 +2934,7 @@
         <v>2</v>
       </c>
       <c r="U35" t="n">
-        <v>1779.9</v>
+        <v>1765.3</v>
       </c>
     </row>
     <row r="36">
@@ -3386,31 +3386,31 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="G42" t="n">
-        <v>1798.1</v>
+        <v>1771.7</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2861</v>
+        <v>0.2428</v>
       </c>
       <c r="I42" t="n">
-        <v>119.92</v>
+        <v>119.28</v>
       </c>
       <c r="J42" t="n">
-        <v>106.59</v>
+        <v>107.6</v>
       </c>
       <c r="K42" t="n">
-        <v>13.33</v>
+        <v>11.68</v>
       </c>
       <c r="L42" t="n">
-        <v>0.3181</v>
+        <v>0.3159</v>
       </c>
       <c r="M42" t="n">
-        <v>0.141</v>
+        <v>0.1413</v>
       </c>
       <c r="N42" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="O42" t="n">
         <v>32</v>
@@ -3431,7 +3431,7 @@
         <v>33</v>
       </c>
       <c r="U42" t="n">
-        <v>1643.1</v>
+        <v>1649.4</v>
       </c>
     </row>
     <row r="43">
@@ -3457,31 +3457,31 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="G43" t="n">
-        <v>1793.2</v>
+        <v>1819.6</v>
       </c>
       <c r="H43" t="n">
-        <v>8.666399999999999</v>
+        <v>8.063000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>120</v>
+        <v>120.5</v>
       </c>
       <c r="J43" t="n">
-        <v>98.73</v>
+        <v>98.58</v>
       </c>
       <c r="K43" t="n">
-        <v>21.28</v>
+        <v>21.92</v>
       </c>
       <c r="L43" t="n">
-        <v>0.2418</v>
+        <v>0.2482</v>
       </c>
       <c r="M43" t="n">
-        <v>0.1658</v>
+        <v>0.1652</v>
       </c>
       <c r="N43" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="O43" t="n">
         <v>41</v>
@@ -3502,7 +3502,7 @@
         <v>31</v>
       </c>
       <c r="U43" t="n">
-        <v>1516.9</v>
+        <v>1526.5</v>
       </c>
     </row>
     <row r="44">
@@ -4096,31 +4096,31 @@
         <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G52" t="n">
-        <v>1413</v>
+        <v>1412.4</v>
       </c>
       <c r="H52" t="n">
-        <v>2.8128</v>
+        <v>2.7318</v>
       </c>
       <c r="I52" t="n">
-        <v>109.77</v>
+        <v>109.69</v>
       </c>
       <c r="J52" t="n">
-        <v>99.3</v>
+        <v>100.82</v>
       </c>
       <c r="K52" t="n">
-        <v>10.47</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="L52" t="n">
-        <v>0.3178</v>
+        <v>0.3172</v>
       </c>
       <c r="M52" t="n">
-        <v>0.1829</v>
+        <v>0.1806</v>
       </c>
       <c r="N52" t="n">
-        <v>11</v>
+        <v>2.8</v>
       </c>
       <c r="O52" t="n">
         <v>207</v>
@@ -4141,7 +4141,7 @@
         <v>203</v>
       </c>
       <c r="U52" t="n">
-        <v>1374.4</v>
+        <v>1406.7</v>
       </c>
     </row>
     <row r="53">
@@ -4309,28 +4309,28 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="G55" t="n">
-        <v>2068.3</v>
+        <v>2070.4</v>
       </c>
       <c r="H55" t="n">
-        <v>5.8188</v>
+        <v>5.4527</v>
       </c>
       <c r="I55" t="n">
-        <v>120.75</v>
+        <v>120.17</v>
       </c>
       <c r="J55" t="n">
-        <v>93.89</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="K55" t="n">
-        <v>26.86</v>
+        <v>26.42</v>
       </c>
       <c r="L55" t="n">
-        <v>0.2992</v>
+        <v>0.3009</v>
       </c>
       <c r="M55" t="n">
-        <v>0.1335</v>
+        <v>0.1341</v>
       </c>
       <c r="N55" t="n">
         <v>11.8</v>
@@ -4354,7 +4354,7 @@
         <v>7</v>
       </c>
       <c r="U55" t="n">
-        <v>1601.3</v>
+        <v>1596.4</v>
       </c>
     </row>
     <row r="56">
@@ -4380,31 +4380,31 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G56" t="n">
-        <v>1977</v>
+        <v>1980.8</v>
       </c>
       <c r="H56" t="n">
-        <v>5.1479</v>
+        <v>5.1109</v>
       </c>
       <c r="I56" t="n">
-        <v>122.87</v>
+        <v>122.95</v>
       </c>
       <c r="J56" t="n">
-        <v>109.33</v>
+        <v>109.03</v>
       </c>
       <c r="K56" t="n">
-        <v>13.54</v>
+        <v>13.91</v>
       </c>
       <c r="L56" t="n">
-        <v>0.2979</v>
+        <v>0.2989</v>
       </c>
       <c r="M56" t="n">
-        <v>0.1206</v>
+        <v>0.1207</v>
       </c>
       <c r="N56" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="O56" t="n">
         <v>15</v>
@@ -4425,7 +4425,7 @@
         <v>15</v>
       </c>
       <c r="U56" t="n">
-        <v>1736</v>
+        <v>1727.5</v>
       </c>
     </row>
     <row r="57">
@@ -4451,31 +4451,31 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="G57" t="n">
-        <v>1882.4</v>
+        <v>1843.6</v>
       </c>
       <c r="H57" t="n">
-        <v>2.4266</v>
+        <v>2.6405</v>
       </c>
       <c r="I57" t="n">
-        <v>118.8</v>
+        <v>118.85</v>
       </c>
       <c r="J57" t="n">
-        <v>108.53</v>
+        <v>108.89</v>
       </c>
       <c r="K57" t="n">
-        <v>10.27</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="L57" t="n">
-        <v>0.2776</v>
+        <v>0.2796</v>
       </c>
       <c r="M57" t="n">
-        <v>0.124</v>
+        <v>0.1222</v>
       </c>
       <c r="N57" t="n">
-        <v>8</v>
+        <v>1.2</v>
       </c>
       <c r="O57" t="n">
         <v>22</v>
@@ -4496,7 +4496,7 @@
         <v>25</v>
       </c>
       <c r="U57" t="n">
-        <v>1724.6</v>
+        <v>1717.5</v>
       </c>
     </row>
     <row r="58">
@@ -4522,31 +4522,31 @@
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="G58" t="n">
-        <v>1926.2</v>
+        <v>1888.5</v>
       </c>
       <c r="H58" t="n">
-        <v>0.632</v>
+        <v>0.3813</v>
       </c>
       <c r="I58" t="n">
-        <v>117.67</v>
+        <v>117.42</v>
       </c>
       <c r="J58" t="n">
-        <v>106.1</v>
+        <v>106.52</v>
       </c>
       <c r="K58" t="n">
-        <v>11.57</v>
+        <v>10.9</v>
       </c>
       <c r="L58" t="n">
-        <v>0.3038</v>
+        <v>0.3073</v>
       </c>
       <c r="M58" t="n">
-        <v>0.1534</v>
+        <v>0.1519</v>
       </c>
       <c r="N58" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="O58" t="n">
         <v>23</v>
@@ -4567,7 +4567,7 @@
         <v>23</v>
       </c>
       <c r="U58" t="n">
-        <v>1733.2</v>
+        <v>1731.5</v>
       </c>
     </row>
     <row r="59">
@@ -4948,31 +4948,31 @@
         <v>1</v>
       </c>
       <c r="F64" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G64" t="n">
-        <v>1764.2</v>
+        <v>1801.8</v>
       </c>
       <c r="H64" t="n">
-        <v>2.6628</v>
+        <v>2.6488</v>
       </c>
       <c r="I64" t="n">
-        <v>119</v>
+        <v>119.21</v>
       </c>
       <c r="J64" t="n">
         <v>110.83</v>
       </c>
       <c r="K64" t="n">
-        <v>8.17</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>0.3041</v>
+        <v>0.3031</v>
       </c>
       <c r="M64" t="n">
-        <v>0.1443</v>
+        <v>0.1432</v>
       </c>
       <c r="N64" t="n">
-        <v>-5</v>
+        <v>-4.6</v>
       </c>
       <c r="O64" t="n">
         <v>37</v>
@@ -4993,7 +4993,7 @@
         <v>42</v>
       </c>
       <c r="U64" t="n">
-        <v>1698.6</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="65">
@@ -5019,31 +5019,31 @@
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="G65" t="n">
-        <v>1625.5</v>
+        <v>1664.3</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.8564000000000001</v>
+        <v>-0.6842</v>
       </c>
       <c r="I65" t="n">
-        <v>121.16</v>
+        <v>120.78</v>
       </c>
       <c r="J65" t="n">
-        <v>100.19</v>
+        <v>100.59</v>
       </c>
       <c r="K65" t="n">
-        <v>20.97</v>
+        <v>20.2</v>
       </c>
       <c r="L65" t="n">
-        <v>0.3061</v>
+        <v>0.3016</v>
       </c>
       <c r="M65" t="n">
-        <v>0.1276</v>
+        <v>0.128</v>
       </c>
       <c r="N65" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="O65" t="n">
         <v>92</v>
@@ -5064,7 +5064,7 @@
         <v>75</v>
       </c>
       <c r="U65" t="n">
-        <v>1382.5</v>
+        <v>1401.4</v>
       </c>
     </row>
     <row r="66">
@@ -5090,31 +5090,31 @@
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="G66" t="n">
-        <v>1549.1</v>
+        <v>1545.3</v>
       </c>
       <c r="H66" t="n">
-        <v>2.9832</v>
+        <v>2.9403</v>
       </c>
       <c r="I66" t="n">
-        <v>108.14</v>
+        <v>108.06</v>
       </c>
       <c r="J66" t="n">
-        <v>96.69</v>
+        <v>98.12</v>
       </c>
       <c r="K66" t="n">
-        <v>11.45</v>
+        <v>9.93</v>
       </c>
       <c r="L66" t="n">
-        <v>0.2583</v>
+        <v>0.2616</v>
       </c>
       <c r="M66" t="n">
-        <v>0.1851</v>
+        <v>0.1837</v>
       </c>
       <c r="N66" t="n">
-        <v>6.8</v>
+        <v>2.6</v>
       </c>
       <c r="O66" t="n">
         <v>108</v>
@@ -5135,7 +5135,7 @@
         <v>101</v>
       </c>
       <c r="U66" t="n">
-        <v>1452.3</v>
+        <v>1472.5</v>
       </c>
     </row>
     <row r="67">
@@ -5161,31 +5161,31 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="G67" t="n">
-        <v>1521.3</v>
+        <v>1519.2</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.1615</v>
+        <v>-0.0429</v>
       </c>
       <c r="I67" t="n">
-        <v>111.12</v>
+        <v>110.41</v>
       </c>
       <c r="J67" t="n">
-        <v>108.1</v>
+        <v>108.11</v>
       </c>
       <c r="K67" t="n">
-        <v>3.02</v>
+        <v>2.3</v>
       </c>
       <c r="L67" t="n">
-        <v>0.345</v>
+        <v>0.3429</v>
       </c>
       <c r="M67" t="n">
-        <v>0.165</v>
+        <v>0.1651</v>
       </c>
       <c r="N67" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="O67" t="n">
         <v>163</v>
@@ -5206,7 +5206,7 @@
         <v>155</v>
       </c>
       <c r="U67" t="n">
-        <v>1474.6</v>
+        <v>1497.2</v>
       </c>
     </row>
     <row r="68">

--- a/team_stats_2026.xlsx
+++ b/team_stats_2026.xlsx
@@ -617,31 +617,31 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="G3" t="n">
-        <v>2050.7</v>
+        <v>2053.4</v>
       </c>
       <c r="H3" t="n">
-        <v>7.1741</v>
+        <v>6.6189</v>
       </c>
       <c r="I3" t="n">
-        <v>116.06</v>
+        <v>116.79</v>
       </c>
       <c r="J3" t="n">
-        <v>98.01000000000001</v>
+        <v>98.31999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>18.05</v>
+        <v>18.48</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3013</v>
+        <v>0.3039</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1603</v>
+        <v>0.1587</v>
       </c>
       <c r="N3" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="O3" t="n">
         <v>11</v>
@@ -662,7 +662,7 @@
         <v>10</v>
       </c>
       <c r="U3" t="n">
-        <v>1670.2</v>
+        <v>1662.8</v>
       </c>
     </row>
     <row r="4">
@@ -759,31 +759,31 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="G5" t="n">
-        <v>1973.7</v>
+        <v>1979.2</v>
       </c>
       <c r="H5" t="n">
-        <v>10.346</v>
+        <v>9.864800000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>109.9</v>
+        <v>109.77</v>
       </c>
       <c r="J5" t="n">
-        <v>101.51</v>
+        <v>100.72</v>
       </c>
       <c r="K5" t="n">
-        <v>8.390000000000001</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2556</v>
+        <v>0.2534</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1512</v>
+        <v>0.15</v>
       </c>
       <c r="N5" t="n">
-        <v>-6.2</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>21</v>
@@ -804,7 +804,7 @@
         <v>21</v>
       </c>
       <c r="U5" t="n">
-        <v>1791.1</v>
+        <v>1780.1</v>
       </c>
     </row>
     <row r="6">
@@ -830,31 +830,31 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="G6" t="n">
-        <v>1984.9</v>
+        <v>1989.2</v>
       </c>
       <c r="H6" t="n">
-        <v>5.6609</v>
+        <v>5.7241</v>
       </c>
       <c r="I6" t="n">
-        <v>113.97</v>
+        <v>114.41</v>
       </c>
       <c r="J6" t="n">
-        <v>98.16</v>
+        <v>97.8</v>
       </c>
       <c r="K6" t="n">
-        <v>15.81</v>
+        <v>16.61</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3224</v>
+        <v>0.3208</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1422</v>
+        <v>0.1418</v>
       </c>
       <c r="N6" t="n">
-        <v>10.6</v>
+        <v>15.2</v>
       </c>
       <c r="O6" t="n">
         <v>17</v>
@@ -875,7 +875,7 @@
         <v>16</v>
       </c>
       <c r="U6" t="n">
-        <v>1691.6</v>
+        <v>1684.5</v>
       </c>
     </row>
     <row r="7">
@@ -972,31 +972,31 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="G8" t="n">
-        <v>1874.2</v>
+        <v>1897.1</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8463</v>
+        <v>2.9774</v>
       </c>
       <c r="I8" t="n">
-        <v>117.18</v>
+        <v>116.93</v>
       </c>
       <c r="J8" t="n">
-        <v>107.51</v>
+        <v>107.23</v>
       </c>
       <c r="K8" t="n">
-        <v>9.67</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3055</v>
+        <v>0.3073</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1325</v>
+        <v>0.1316</v>
       </c>
       <c r="N8" t="n">
-        <v>10.2</v>
+        <v>7</v>
       </c>
       <c r="O8" t="n">
         <v>27</v>
@@ -1017,7 +1017,7 @@
         <v>30</v>
       </c>
       <c r="U8" t="n">
-        <v>1706.3</v>
+        <v>1708.6</v>
       </c>
     </row>
     <row r="9">
@@ -1185,31 +1185,31 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="G11" t="n">
-        <v>1828.6</v>
+        <v>1805.8</v>
       </c>
       <c r="H11" t="n">
-        <v>5.8051</v>
+        <v>5.3176</v>
       </c>
       <c r="I11" t="n">
-        <v>113</v>
+        <v>112.74</v>
       </c>
       <c r="J11" t="n">
-        <v>110.03</v>
+        <v>109.75</v>
       </c>
       <c r="K11" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3147</v>
+        <v>0.3205</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1543</v>
+        <v>0.1576</v>
       </c>
       <c r="N11" t="n">
-        <v>-8.800000000000001</v>
+        <v>-9.4</v>
       </c>
       <c r="O11" t="n">
         <v>54</v>
@@ -1230,7 +1230,7 @@
         <v>51</v>
       </c>
       <c r="U11" t="n">
-        <v>1712.7</v>
+        <v>1713.5</v>
       </c>
     </row>
     <row r="12">
@@ -1327,31 +1327,31 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="G13" t="n">
-        <v>1573.9</v>
+        <v>1569.6</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.696</v>
+        <v>-3.4213</v>
       </c>
       <c r="I13" t="n">
-        <v>108.74</v>
+        <v>107.64</v>
       </c>
       <c r="J13" t="n">
-        <v>97.5</v>
+        <v>98.39</v>
       </c>
       <c r="K13" t="n">
-        <v>11.25</v>
+        <v>9.24</v>
       </c>
       <c r="L13" t="n">
-        <v>0.225</v>
+        <v>0.2219</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1354</v>
+        <v>0.1344</v>
       </c>
       <c r="N13" t="n">
-        <v>14.4</v>
+        <v>4.8</v>
       </c>
       <c r="O13" t="n">
         <v>72</v>
@@ -1372,7 +1372,7 @@
         <v>72</v>
       </c>
       <c r="U13" t="n">
-        <v>1515.8</v>
+        <v>1532.4</v>
       </c>
     </row>
     <row r="14">
@@ -1398,31 +1398,31 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="G14" t="n">
-        <v>1607.9</v>
+        <v>1602.3</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5554</v>
+        <v>1.6245</v>
       </c>
       <c r="I14" t="n">
-        <v>107.22</v>
+        <v>106.58</v>
       </c>
       <c r="J14" t="n">
-        <v>99.23999999999999</v>
+        <v>99.31</v>
       </c>
       <c r="K14" t="n">
-        <v>7.97</v>
+        <v>7.26</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3287</v>
+        <v>0.3276</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1735</v>
+        <v>0.1709</v>
       </c>
       <c r="N14" t="n">
-        <v>15.4</v>
+        <v>10.8</v>
       </c>
       <c r="O14" t="n">
         <v>106</v>
@@ -1443,7 +1443,7 @@
         <v>98</v>
       </c>
       <c r="U14" t="n">
-        <v>1462.4</v>
+        <v>1480.3</v>
       </c>
     </row>
     <row r="15">
@@ -1540,31 +1540,31 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="G16" t="n">
-        <v>1542.9</v>
+        <v>1540.2</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8197</v>
+        <v>0.788</v>
       </c>
       <c r="I16" t="n">
-        <v>112.01</v>
+        <v>111.79</v>
       </c>
       <c r="J16" t="n">
-        <v>107.28</v>
+        <v>108.04</v>
       </c>
       <c r="K16" t="n">
-        <v>4.73</v>
+        <v>3.75</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2562</v>
+        <v>0.253</v>
       </c>
       <c r="M16" t="n">
         <v>0.171</v>
       </c>
       <c r="N16" t="n">
-        <v>5.6</v>
+        <v>-0.8</v>
       </c>
       <c r="O16" t="n">
         <v>191</v>
@@ -1585,7 +1585,7 @@
         <v>186</v>
       </c>
       <c r="U16" t="n">
-        <v>1422.2</v>
+        <v>1445.6</v>
       </c>
     </row>
     <row r="17">
@@ -1682,31 +1682,31 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="G18" t="n">
-        <v>2006.7</v>
+        <v>2007.2</v>
       </c>
       <c r="H18" t="n">
-        <v>3.4651</v>
+        <v>3.5894</v>
       </c>
       <c r="I18" t="n">
-        <v>119.99</v>
+        <v>121.8</v>
       </c>
       <c r="J18" t="n">
-        <v>100.19</v>
+        <v>99.02</v>
       </c>
       <c r="K18" t="n">
-        <v>19.81</v>
+        <v>22.78</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3342</v>
+        <v>0.3326</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1568</v>
+        <v>0.155</v>
       </c>
       <c r="N18" t="n">
-        <v>13.2</v>
+        <v>18.2</v>
       </c>
       <c r="O18" t="n">
         <v>4</v>
@@ -1727,7 +1727,7 @@
         <v>4</v>
       </c>
       <c r="U18" t="n">
-        <v>1722.9</v>
+        <v>1703.3</v>
       </c>
     </row>
     <row r="19">
@@ -2179,31 +2179,31 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="G25" t="n">
-        <v>1859.5</v>
+        <v>1831.1</v>
       </c>
       <c r="H25" t="n">
-        <v>2.557</v>
+        <v>2.3914</v>
       </c>
       <c r="I25" t="n">
-        <v>112.59</v>
+        <v>112.78</v>
       </c>
       <c r="J25" t="n">
-        <v>101.68</v>
+        <v>102.42</v>
       </c>
       <c r="K25" t="n">
-        <v>10.91</v>
+        <v>10.36</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2554</v>
+        <v>0.2595</v>
       </c>
       <c r="M25" t="n">
-        <v>0.136</v>
+        <v>0.1369</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
       <c r="O25" t="n">
         <v>36</v>
@@ -2224,7 +2224,7 @@
         <v>34</v>
       </c>
       <c r="U25" t="n">
-        <v>1672.9</v>
+        <v>1674.2</v>
       </c>
     </row>
     <row r="26">
@@ -2250,31 +2250,31 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="G26" t="n">
-        <v>1831.8</v>
+        <v>1860.1</v>
       </c>
       <c r="H26" t="n">
-        <v>3.3952</v>
+        <v>3.0379</v>
       </c>
       <c r="I26" t="n">
-        <v>118.92</v>
+        <v>119.22</v>
       </c>
       <c r="J26" t="n">
-        <v>104.81</v>
+        <v>105.02</v>
       </c>
       <c r="K26" t="n">
-        <v>14.12</v>
+        <v>14.21</v>
       </c>
       <c r="L26" t="n">
-        <v>0.2886</v>
+        <v>0.2918</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1455</v>
+        <v>0.1418</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.2</v>
+        <v>0.4</v>
       </c>
       <c r="O26" t="n">
         <v>25</v>
@@ -2295,7 +2295,7 @@
         <v>27</v>
       </c>
       <c r="U26" t="n">
-        <v>1712.2</v>
+        <v>1717.1</v>
       </c>
     </row>
     <row r="27">
@@ -2747,31 +2747,31 @@
         <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G33" t="n">
-        <v>1272.1</v>
+        <v>1271.6</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.4587</v>
+        <v>-0.3388</v>
       </c>
       <c r="I33" t="n">
-        <v>104.27</v>
+        <v>103.39</v>
       </c>
       <c r="J33" t="n">
-        <v>106.28</v>
+        <v>108.67</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.01</v>
+        <v>-5.28</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2897</v>
+        <v>0.2951</v>
       </c>
       <c r="M33" t="n">
-        <v>0.1584</v>
+        <v>0.1557</v>
       </c>
       <c r="N33" t="n">
-        <v>10</v>
+        <v>-3.6</v>
       </c>
       <c r="O33" t="n">
         <v>288</v>
@@ -2792,7 +2792,7 @@
         <v>300</v>
       </c>
       <c r="U33" t="n">
-        <v>1381.2</v>
+        <v>1406.5</v>
       </c>
     </row>
     <row r="34">
@@ -2960,31 +2960,31 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="G36" t="n">
-        <v>2039</v>
+        <v>2040.7</v>
       </c>
       <c r="H36" t="n">
-        <v>2.2111</v>
+        <v>1.9908</v>
       </c>
       <c r="I36" t="n">
-        <v>118.9</v>
+        <v>119.65</v>
       </c>
       <c r="J36" t="n">
-        <v>95.73</v>
+        <v>95.53</v>
       </c>
       <c r="K36" t="n">
-        <v>23.17</v>
+        <v>24.12</v>
       </c>
       <c r="L36" t="n">
-        <v>0.3217</v>
+        <v>0.3242</v>
       </c>
       <c r="M36" t="n">
-        <v>0.1469</v>
+        <v>0.1466</v>
       </c>
       <c r="N36" t="n">
-        <v>14.8</v>
+        <v>24.8</v>
       </c>
       <c r="O36" t="n">
         <v>6</v>
@@ -3005,7 +3005,7 @@
         <v>6</v>
       </c>
       <c r="U36" t="n">
-        <v>1718</v>
+        <v>1704.9</v>
       </c>
     </row>
     <row r="37">
@@ -3031,31 +3031,31 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="G37" t="n">
-        <v>1964.3</v>
+        <v>1966.7</v>
       </c>
       <c r="H37" t="n">
-        <v>12.2076</v>
+        <v>11.7947</v>
       </c>
       <c r="I37" t="n">
-        <v>119.04</v>
+        <v>119.42</v>
       </c>
       <c r="J37" t="n">
-        <v>100.85</v>
+        <v>101.19</v>
       </c>
       <c r="K37" t="n">
-        <v>18.19</v>
+        <v>18.23</v>
       </c>
       <c r="L37" t="n">
-        <v>0.3154</v>
+        <v>0.3132</v>
       </c>
       <c r="M37" t="n">
-        <v>0.1544</v>
+        <v>0.1564</v>
       </c>
       <c r="N37" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="O37" t="n">
         <v>13</v>
@@ -3076,7 +3076,7 @@
         <v>12</v>
       </c>
       <c r="U37" t="n">
-        <v>1665.9</v>
+        <v>1654.9</v>
       </c>
     </row>
     <row r="38">
@@ -3102,31 +3102,31 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="G38" t="n">
-        <v>1949.3</v>
+        <v>1954.7</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.3255</v>
+        <v>-1.3316</v>
       </c>
       <c r="I38" t="n">
-        <v>121.37</v>
+        <v>121.89</v>
       </c>
       <c r="J38" t="n">
-        <v>110.6</v>
+        <v>110.31</v>
       </c>
       <c r="K38" t="n">
-        <v>10.77</v>
+        <v>11.59</v>
       </c>
       <c r="L38" t="n">
-        <v>0.2809</v>
+        <v>0.2849</v>
       </c>
       <c r="M38" t="n">
-        <v>0.1288</v>
+        <v>0.1295</v>
       </c>
       <c r="N38" t="n">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="O38" t="n">
         <v>18</v>
@@ -3147,7 +3147,7 @@
         <v>18</v>
       </c>
       <c r="U38" t="n">
-        <v>1767</v>
+        <v>1760.9</v>
       </c>
     </row>
     <row r="39">
@@ -3173,31 +3173,31 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="G39" t="n">
-        <v>2010.7</v>
+        <v>2018.6</v>
       </c>
       <c r="H39" t="n">
-        <v>9.579599999999999</v>
+        <v>8.9857</v>
       </c>
       <c r="I39" t="n">
-        <v>117.2</v>
+        <v>118.54</v>
       </c>
       <c r="J39" t="n">
-        <v>106.7</v>
+        <v>106.75</v>
       </c>
       <c r="K39" t="n">
-        <v>10.5</v>
+        <v>11.79</v>
       </c>
       <c r="L39" t="n">
-        <v>0.2893</v>
+        <v>0.2876</v>
       </c>
       <c r="M39" t="n">
         <v>0.155</v>
       </c>
       <c r="N39" t="n">
-        <v>-3</v>
+        <v>-1.4</v>
       </c>
       <c r="O39" t="n">
         <v>20</v>
@@ -3218,7 +3218,7 @@
         <v>19</v>
       </c>
       <c r="U39" t="n">
-        <v>1772.3</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="40">
@@ -3244,31 +3244,31 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="G40" t="n">
-        <v>1897.1</v>
+        <v>1914.8</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.4465</v>
+        <v>-1.3934</v>
       </c>
       <c r="I40" t="n">
-        <v>116.86</v>
+        <v>116.95</v>
       </c>
       <c r="J40" t="n">
-        <v>102.57</v>
+        <v>101.62</v>
       </c>
       <c r="K40" t="n">
-        <v>14.29</v>
+        <v>15.34</v>
       </c>
       <c r="L40" t="n">
-        <v>0.36</v>
+        <v>0.3564</v>
       </c>
       <c r="M40" t="n">
-        <v>0.1643</v>
+        <v>0.1676</v>
       </c>
       <c r="N40" t="n">
-        <v>3.2</v>
+        <v>8</v>
       </c>
       <c r="O40" t="n">
         <v>16</v>
@@ -3315,31 +3315,31 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="G41" t="n">
-        <v>1886.9</v>
+        <v>1905.5</v>
       </c>
       <c r="H41" t="n">
-        <v>4.7611</v>
+        <v>4.5369</v>
       </c>
       <c r="I41" t="n">
-        <v>115.76</v>
+        <v>116.17</v>
       </c>
       <c r="J41" t="n">
-        <v>106.05</v>
+        <v>106.38</v>
       </c>
       <c r="K41" t="n">
-        <v>9.710000000000001</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>0.3106</v>
+        <v>0.3078</v>
       </c>
       <c r="M41" t="n">
-        <v>0.1465</v>
+        <v>0.1463</v>
       </c>
       <c r="N41" t="n">
-        <v>-3</v>
+        <v>0.2</v>
       </c>
       <c r="O41" t="n">
         <v>28</v>
@@ -3360,7 +3360,7 @@
         <v>28</v>
       </c>
       <c r="U41" t="n">
-        <v>1734.8</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="42">
@@ -3528,31 +3528,31 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="G44" t="n">
-        <v>1782.8</v>
+        <v>1764.2</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0374</v>
+        <v>0.252</v>
       </c>
       <c r="I44" t="n">
-        <v>117.62</v>
+        <v>117.53</v>
       </c>
       <c r="J44" t="n">
-        <v>104.11</v>
+        <v>104.51</v>
       </c>
       <c r="K44" t="n">
-        <v>13.51</v>
+        <v>13.02</v>
       </c>
       <c r="L44" t="n">
-        <v>0.3504</v>
+        <v>0.348</v>
       </c>
       <c r="M44" t="n">
-        <v>0.1498</v>
+        <v>0.1478</v>
       </c>
       <c r="N44" t="n">
-        <v>0.8</v>
+        <v>3.6</v>
       </c>
       <c r="O44" t="n">
         <v>35</v>
@@ -3573,7 +3573,7 @@
         <v>40</v>
       </c>
       <c r="U44" t="n">
-        <v>1596.2</v>
+        <v>1603.2</v>
       </c>
     </row>
     <row r="45">
@@ -3599,31 +3599,31 @@
         <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G45" t="n">
-        <v>1780.4</v>
+        <v>1762.6</v>
       </c>
       <c r="H45" t="n">
-        <v>8.9497</v>
+        <v>8.696899999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>121.34</v>
+        <v>119.94</v>
       </c>
       <c r="J45" t="n">
-        <v>106.31</v>
+        <v>106.8</v>
       </c>
       <c r="K45" t="n">
-        <v>15.03</v>
+        <v>13.13</v>
       </c>
       <c r="L45" t="n">
-        <v>0.2222</v>
+        <v>0.2251</v>
       </c>
       <c r="M45" t="n">
-        <v>0.1392</v>
+        <v>0.1414</v>
       </c>
       <c r="N45" t="n">
-        <v>2.4</v>
+        <v>-2.4</v>
       </c>
       <c r="O45" t="n">
         <v>93</v>
@@ -3644,7 +3644,7 @@
         <v>64</v>
       </c>
       <c r="U45" t="n">
-        <v>1429.2</v>
+        <v>1434.9</v>
       </c>
     </row>
     <row r="46">
@@ -3741,31 +3741,31 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="G47" t="n">
-        <v>1707.9</v>
+        <v>1700.1</v>
       </c>
       <c r="H47" t="n">
-        <v>1.9745</v>
+        <v>2.0575</v>
       </c>
       <c r="I47" t="n">
-        <v>121.64</v>
+        <v>121.23</v>
       </c>
       <c r="J47" t="n">
-        <v>104.36</v>
+        <v>105.7</v>
       </c>
       <c r="K47" t="n">
-        <v>17.27</v>
+        <v>15.54</v>
       </c>
       <c r="L47" t="n">
-        <v>0.2887</v>
+        <v>0.2937</v>
       </c>
       <c r="M47" t="n">
-        <v>0.15</v>
+        <v>0.1498</v>
       </c>
       <c r="N47" t="n">
-        <v>13</v>
+        <v>6.4</v>
       </c>
       <c r="O47" t="n">
         <v>64</v>
@@ -3786,7 +3786,7 @@
         <v>54</v>
       </c>
       <c r="U47" t="n">
-        <v>1479.2</v>
+        <v>1499.8</v>
       </c>
     </row>
     <row r="48">
@@ -3812,31 +3812,31 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="G48" t="n">
-        <v>1586.2</v>
+        <v>1580.8</v>
       </c>
       <c r="H48" t="n">
-        <v>3.3583</v>
+        <v>3.2408</v>
       </c>
       <c r="I48" t="n">
-        <v>113.56</v>
+        <v>113.03</v>
       </c>
       <c r="J48" t="n">
-        <v>102.69</v>
+        <v>103.66</v>
       </c>
       <c r="K48" t="n">
-        <v>10.87</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>0.3081</v>
+        <v>0.3106</v>
       </c>
       <c r="M48" t="n">
-        <v>0.1527</v>
+        <v>0.1533</v>
       </c>
       <c r="N48" t="n">
-        <v>12</v>
+        <v>6.2</v>
       </c>
       <c r="O48" t="n">
         <v>87</v>
@@ -3857,7 +3857,7 @@
         <v>88</v>
       </c>
       <c r="U48" t="n">
-        <v>1482.3</v>
+        <v>1500.6</v>
       </c>
     </row>
     <row r="49">
@@ -3883,31 +3883,31 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="G49" t="n">
-        <v>1470.5</v>
+        <v>1468.1</v>
       </c>
       <c r="H49" t="n">
-        <v>2.7419</v>
+        <v>2.7298</v>
       </c>
       <c r="I49" t="n">
-        <v>115.44</v>
+        <v>115.45</v>
       </c>
       <c r="J49" t="n">
-        <v>108.91</v>
+        <v>109.66</v>
       </c>
       <c r="K49" t="n">
-        <v>6.53</v>
+        <v>5.79</v>
       </c>
       <c r="L49" t="n">
-        <v>0.2971</v>
+        <v>0.2983</v>
       </c>
       <c r="M49" t="n">
-        <v>0.1569</v>
+        <v>0.1551</v>
       </c>
       <c r="N49" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="O49" t="n">
         <v>140</v>
@@ -3928,7 +3928,7 @@
         <v>127</v>
       </c>
       <c r="U49" t="n">
-        <v>1431.7</v>
+        <v>1452.2</v>
       </c>
     </row>
     <row r="50">
@@ -3954,31 +3954,31 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="G50" t="n">
-        <v>1466.9</v>
+        <v>1465.2</v>
       </c>
       <c r="H50" t="n">
-        <v>3.3618</v>
+        <v>3.2842</v>
       </c>
       <c r="I50" t="n">
-        <v>109.9</v>
+        <v>109.1</v>
       </c>
       <c r="J50" t="n">
-        <v>103.28</v>
+        <v>104.71</v>
       </c>
       <c r="K50" t="n">
-        <v>6.62</v>
+        <v>4.4</v>
       </c>
       <c r="L50" t="n">
-        <v>0.328</v>
+        <v>0.3301</v>
       </c>
       <c r="M50" t="n">
-        <v>0.1589</v>
+        <v>0.1608</v>
       </c>
       <c r="N50" t="n">
-        <v>19.8</v>
+        <v>7.6</v>
       </c>
       <c r="O50" t="n">
         <v>187</v>
@@ -3999,7 +3999,7 @@
         <v>172</v>
       </c>
       <c r="U50" t="n">
-        <v>1407.8</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="51">
@@ -4167,31 +4167,31 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="G53" t="n">
-        <v>2272.1</v>
+        <v>2272.5</v>
       </c>
       <c r="H53" t="n">
-        <v>6.8151</v>
+        <v>6.6001</v>
       </c>
       <c r="I53" t="n">
-        <v>121.14</v>
+        <v>121.6</v>
       </c>
       <c r="J53" t="n">
-        <v>97.11</v>
+        <v>96.53</v>
       </c>
       <c r="K53" t="n">
-        <v>24.03</v>
+        <v>25.07</v>
       </c>
       <c r="L53" t="n">
-        <v>0.2925</v>
+        <v>0.2933</v>
       </c>
       <c r="M53" t="n">
-        <v>0.1497</v>
+        <v>0.1498</v>
       </c>
       <c r="N53" t="n">
-        <v>11</v>
+        <v>14.6</v>
       </c>
       <c r="O53" t="n">
         <v>2</v>
@@ -4212,7 +4212,7 @@
         <v>3</v>
       </c>
       <c r="U53" t="n">
-        <v>1769.2</v>
+        <v>1753.9</v>
       </c>
     </row>
     <row r="54">
@@ -4238,31 +4238,31 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G54" t="n">
-        <v>2010</v>
+        <v>2011.5</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.7024</v>
+        <v>-0.6772</v>
       </c>
       <c r="I54" t="n">
-        <v>124.87</v>
+        <v>125.91</v>
       </c>
       <c r="J54" t="n">
-        <v>107.49</v>
+        <v>107.36</v>
       </c>
       <c r="K54" t="n">
-        <v>17.39</v>
+        <v>18.55</v>
       </c>
       <c r="L54" t="n">
-        <v>0.311</v>
+        <v>0.3128</v>
       </c>
       <c r="M54" t="n">
-        <v>0.1337</v>
+        <v>0.1355</v>
       </c>
       <c r="N54" t="n">
-        <v>8</v>
+        <v>15.4</v>
       </c>
       <c r="O54" t="n">
         <v>8</v>
@@ -4283,7 +4283,7 @@
         <v>9</v>
       </c>
       <c r="U54" t="n">
-        <v>1769.7</v>
+        <v>1753.9</v>
       </c>
     </row>
     <row r="55">
@@ -4593,31 +4593,31 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="G59" t="n">
-        <v>1772.3</v>
+        <v>1794.7</v>
       </c>
       <c r="H59" t="n">
-        <v>11.776</v>
+        <v>11.4257</v>
       </c>
       <c r="I59" t="n">
-        <v>117.07</v>
+        <v>117.44</v>
       </c>
       <c r="J59" t="n">
-        <v>102.95</v>
+        <v>102.47</v>
       </c>
       <c r="K59" t="n">
-        <v>14.11</v>
+        <v>14.97</v>
       </c>
       <c r="L59" t="n">
-        <v>0.3096</v>
+        <v>0.3107</v>
       </c>
       <c r="M59" t="n">
-        <v>0.1569</v>
+        <v>0.1566</v>
       </c>
       <c r="N59" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="O59" t="n">
         <v>31</v>
@@ -4638,7 +4638,7 @@
         <v>32</v>
       </c>
       <c r="U59" t="n">
-        <v>1635.9</v>
+        <v>1636.7</v>
       </c>
     </row>
     <row r="60">
@@ -4664,31 +4664,31 @@
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="G60" t="n">
-        <v>1806.3</v>
+        <v>1786.8</v>
       </c>
       <c r="H60" t="n">
-        <v>5.8793</v>
+        <v>5.5318</v>
       </c>
       <c r="I60" t="n">
-        <v>114.59</v>
+        <v>114.71</v>
       </c>
       <c r="J60" t="n">
-        <v>104.94</v>
+        <v>105.72</v>
       </c>
       <c r="K60" t="n">
-        <v>9.66</v>
+        <v>8.98</v>
       </c>
       <c r="L60" t="n">
-        <v>0.313</v>
+        <v>0.3101</v>
       </c>
       <c r="M60" t="n">
-        <v>0.1447</v>
+        <v>0.1437</v>
       </c>
       <c r="N60" t="n">
-        <v>-1</v>
+        <v>-4.8</v>
       </c>
       <c r="O60" t="n">
         <v>33</v>
@@ -4709,7 +4709,7 @@
         <v>35</v>
       </c>
       <c r="U60" t="n">
-        <v>1641.5</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="61">
@@ -4735,31 +4735,31 @@
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="G61" t="n">
-        <v>1897.5</v>
+        <v>1917</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1736</v>
+        <v>0.2638</v>
       </c>
       <c r="I61" t="n">
-        <v>119.56</v>
+        <v>119.89</v>
       </c>
       <c r="J61" t="n">
-        <v>103.49</v>
+        <v>103.86</v>
       </c>
       <c r="K61" t="n">
-        <v>16.08</v>
+        <v>16.03</v>
       </c>
       <c r="L61" t="n">
-        <v>0.3032</v>
+        <v>0.3056</v>
       </c>
       <c r="M61" t="n">
-        <v>0.1479</v>
+        <v>0.1477</v>
       </c>
       <c r="N61" t="n">
-        <v>4.2</v>
+        <v>11.6</v>
       </c>
       <c r="O61" t="n">
         <v>30</v>
@@ -4780,7 +4780,7 @@
         <v>26</v>
       </c>
       <c r="U61" t="n">
-        <v>1611.4</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="62">
@@ -4806,31 +4806,31 @@
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="G62" t="n">
-        <v>1747.8</v>
+        <v>1725.4</v>
       </c>
       <c r="H62" t="n">
-        <v>-1.7576</v>
+        <v>-1.6662</v>
       </c>
       <c r="I62" t="n">
-        <v>114.92</v>
+        <v>114.34</v>
       </c>
       <c r="J62" t="n">
-        <v>109.48</v>
+        <v>109.81</v>
       </c>
       <c r="K62" t="n">
-        <v>5.45</v>
+        <v>4.52</v>
       </c>
       <c r="L62" t="n">
-        <v>0.2996</v>
+        <v>0.2974</v>
       </c>
       <c r="M62" t="n">
-        <v>0.1685</v>
+        <v>0.1675</v>
       </c>
       <c r="N62" t="n">
-        <v>0.4</v>
+        <v>-3.2</v>
       </c>
       <c r="O62" t="n">
         <v>52</v>
@@ -4851,7 +4851,7 @@
         <v>58</v>
       </c>
       <c r="U62" t="n">
-        <v>1658.3</v>
+        <v>1660.3</v>
       </c>
     </row>
     <row r="63">
@@ -5232,31 +5232,31 @@
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="G68" t="n">
-        <v>1427.4</v>
+        <v>1425.9</v>
       </c>
       <c r="H68" t="n">
-        <v>1.0039</v>
+        <v>1.0261</v>
       </c>
       <c r="I68" t="n">
-        <v>119.17</v>
+        <v>118.64</v>
       </c>
       <c r="J68" t="n">
-        <v>116.56</v>
+        <v>117.98</v>
       </c>
       <c r="K68" t="n">
-        <v>2.61</v>
+        <v>0.67</v>
       </c>
       <c r="L68" t="n">
-        <v>0.2859</v>
+        <v>0.2897</v>
       </c>
       <c r="M68" t="n">
-        <v>0.1441</v>
+        <v>0.1432</v>
       </c>
       <c r="N68" t="n">
-        <v>6.4</v>
+        <v>-3.6</v>
       </c>
       <c r="O68" t="n">
         <v>181</v>
@@ -5277,7 +5277,7 @@
         <v>189</v>
       </c>
       <c r="U68" t="n">
-        <v>1430.9</v>
+        <v>1452.8</v>
       </c>
     </row>
     <row r="69">
@@ -5303,31 +5303,31 @@
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="G69" t="n">
-        <v>1418.2</v>
+        <v>1417.8</v>
       </c>
       <c r="H69" t="n">
-        <v>2.3581</v>
+        <v>2.3176</v>
       </c>
       <c r="I69" t="n">
-        <v>109.38</v>
+        <v>108.23</v>
       </c>
       <c r="J69" t="n">
-        <v>104.38</v>
+        <v>105.25</v>
       </c>
       <c r="K69" t="n">
-        <v>5</v>
+        <v>2.97</v>
       </c>
       <c r="L69" t="n">
-        <v>0.3119</v>
+        <v>0.3159</v>
       </c>
       <c r="M69" t="n">
-        <v>0.183</v>
+        <v>0.1828</v>
       </c>
       <c r="N69" t="n">
-        <v>10.4</v>
+        <v>0.2</v>
       </c>
       <c r="O69" t="n">
         <v>216</v>
@@ -5348,7 +5348,7 @@
         <v>198</v>
       </c>
       <c r="U69" t="n">
-        <v>1378.8</v>
+        <v>1411.9</v>
       </c>
     </row>
   </sheetData>

--- a/team_stats_2026.xlsx
+++ b/team_stats_2026.xlsx
@@ -546,31 +546,31 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G2" t="n">
-        <v>2196.7</v>
+        <v>2203.3</v>
       </c>
       <c r="H2" t="n">
-        <v>3.7365</v>
+        <v>3.7385</v>
       </c>
       <c r="I2" t="n">
-        <v>122.61</v>
+        <v>122.58</v>
       </c>
       <c r="J2" t="n">
-        <v>95</v>
+        <v>94.55</v>
       </c>
       <c r="K2" t="n">
-        <v>27.61</v>
+        <v>28.03</v>
       </c>
       <c r="L2" t="n">
-        <v>0.299</v>
+        <v>0.2951</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1534</v>
+        <v>0.1573</v>
       </c>
       <c r="N2" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -591,7 +591,7 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>1700.6</v>
+        <v>1715.1</v>
       </c>
     </row>
     <row r="3">
@@ -688,31 +688,31 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G4" t="n">
-        <v>2031.4</v>
+        <v>2045.3</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0735</v>
+        <v>-0.0252</v>
       </c>
       <c r="I4" t="n">
-        <v>117.93</v>
+        <v>117.7</v>
       </c>
       <c r="J4" t="n">
-        <v>101.4</v>
+        <v>101.52</v>
       </c>
       <c r="K4" t="n">
-        <v>16.54</v>
+        <v>16.18</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2897</v>
+        <v>0.2911</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1613</v>
+        <v>0.1636</v>
       </c>
       <c r="N4" t="n">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="O4" t="n">
         <v>9</v>
@@ -733,7 +733,7 @@
         <v>11</v>
       </c>
       <c r="U4" t="n">
-        <v>1723.2</v>
+        <v>1733.5</v>
       </c>
     </row>
     <row r="5">
@@ -901,31 +901,31 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G7" t="n">
-        <v>1854.1</v>
+        <v>1840.2</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.5004</v>
+        <v>-2.3212</v>
       </c>
       <c r="I7" t="n">
-        <v>118.73</v>
+        <v>118.3</v>
       </c>
       <c r="J7" t="n">
-        <v>101.94</v>
+        <v>102.46</v>
       </c>
       <c r="K7" t="n">
-        <v>16.79</v>
+        <v>15.84</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2886</v>
+        <v>0.2907</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1645</v>
+        <v>0.1636</v>
       </c>
       <c r="N7" t="n">
-        <v>4.2</v>
+        <v>-0.4</v>
       </c>
       <c r="O7" t="n">
         <v>19</v>
@@ -946,7 +946,7 @@
         <v>17</v>
       </c>
       <c r="U7" t="n">
-        <v>1686.9</v>
+        <v>1697.9</v>
       </c>
     </row>
     <row r="8">
@@ -1114,31 +1114,31 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G10" t="n">
-        <v>1860.6</v>
+        <v>1854</v>
       </c>
       <c r="H10" t="n">
-        <v>6.8435</v>
+        <v>6.8722</v>
       </c>
       <c r="I10" t="n">
-        <v>111.03</v>
+        <v>110.06</v>
       </c>
       <c r="J10" t="n">
-        <v>102.3</v>
+        <v>102.76</v>
       </c>
       <c r="K10" t="n">
-        <v>8.73</v>
+        <v>7.29</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3183</v>
+        <v>0.3236</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1496</v>
+        <v>0.1486</v>
       </c>
       <c r="N10" t="n">
-        <v>4.4</v>
+        <v>-1.8</v>
       </c>
       <c r="O10" t="n">
         <v>43</v>
@@ -1159,7 +1159,7 @@
         <v>39</v>
       </c>
       <c r="U10" t="n">
-        <v>1693.5</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="11">
@@ -1753,31 +1753,31 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G19" t="n">
-        <v>2112.6</v>
+        <v>2122.2</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1096</v>
+        <v>1.0162</v>
       </c>
       <c r="I19" t="n">
-        <v>117.42</v>
+        <v>117.91</v>
       </c>
       <c r="J19" t="n">
-        <v>94.67</v>
+        <v>94.52</v>
       </c>
       <c r="K19" t="n">
-        <v>22.76</v>
+        <v>23.39</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3319</v>
+        <v>0.3362</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1229</v>
+        <v>0.1224</v>
       </c>
       <c r="N19" t="n">
-        <v>12.4</v>
+        <v>17.2</v>
       </c>
       <c r="O19" t="n">
         <v>5</v>
@@ -1798,7 +1798,7 @@
         <v>5</v>
       </c>
       <c r="U19" t="n">
-        <v>1725.6</v>
+        <v>1741.9</v>
       </c>
     </row>
     <row r="20">
@@ -1824,31 +1824,31 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G20" t="n">
-        <v>1984.4</v>
+        <v>1997.8</v>
       </c>
       <c r="H20" t="n">
-        <v>7.3951</v>
+        <v>6.9704</v>
       </c>
       <c r="I20" t="n">
-        <v>126.53</v>
+        <v>125.89</v>
       </c>
       <c r="J20" t="n">
-        <v>103.56</v>
+        <v>102.84</v>
       </c>
       <c r="K20" t="n">
-        <v>22.97</v>
+        <v>23.05</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3263</v>
+        <v>0.3231</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1252</v>
+        <v>0.1277</v>
       </c>
       <c r="N20" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="O20" t="n">
         <v>7</v>
@@ -1869,7 +1869,7 @@
         <v>8</v>
       </c>
       <c r="U20" t="n">
-        <v>1704.4</v>
+        <v>1718.8</v>
       </c>
     </row>
     <row r="21">
@@ -1895,31 +1895,31 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G21" t="n">
-        <v>1988</v>
+        <v>2012.5</v>
       </c>
       <c r="H21" t="n">
-        <v>9.170199999999999</v>
+        <v>8.516999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>115.23</v>
+        <v>115.19</v>
       </c>
       <c r="J21" t="n">
-        <v>97.83</v>
+        <v>98.64</v>
       </c>
       <c r="K21" t="n">
-        <v>17.4</v>
+        <v>16.56</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2465</v>
+        <v>0.2422</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1386</v>
+        <v>0.1409</v>
       </c>
       <c r="N21" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="O21" t="n">
         <v>14</v>
@@ -1940,7 +1940,7 @@
         <v>14</v>
       </c>
       <c r="U21" t="n">
-        <v>1669.8</v>
+        <v>1683.9</v>
       </c>
     </row>
     <row r="22">
@@ -1966,31 +1966,31 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G22" t="n">
-        <v>1963.8</v>
+        <v>1939.4</v>
       </c>
       <c r="H22" t="n">
-        <v>1.4886</v>
+        <v>1.4161</v>
       </c>
       <c r="I22" t="n">
-        <v>122.22</v>
+        <v>121.91</v>
       </c>
       <c r="J22" t="n">
-        <v>106.71</v>
+        <v>107.07</v>
       </c>
       <c r="K22" t="n">
-        <v>15.51</v>
+        <v>14.84</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2897</v>
+        <v>0.2928</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1312</v>
+        <v>0.1304</v>
       </c>
       <c r="N22" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="O22" t="n">
         <v>12</v>
@@ -2011,7 +2011,7 @@
         <v>13</v>
       </c>
       <c r="U22" t="n">
-        <v>1716.9</v>
+        <v>1726.2</v>
       </c>
     </row>
     <row r="23">
@@ -2321,31 +2321,31 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G27" t="n">
-        <v>1852.8</v>
+        <v>1843.1</v>
       </c>
       <c r="H27" t="n">
-        <v>4.0806</v>
+        <v>3.9805</v>
       </c>
       <c r="I27" t="n">
-        <v>116.94</v>
+        <v>116.03</v>
       </c>
       <c r="J27" t="n">
-        <v>106.22</v>
+        <v>107.86</v>
       </c>
       <c r="K27" t="n">
-        <v>10.72</v>
+        <v>8.18</v>
       </c>
       <c r="L27" t="n">
-        <v>0.3101</v>
+        <v>0.3098</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1462</v>
+        <v>0.1456</v>
       </c>
       <c r="N27" t="n">
-        <v>0.2</v>
+        <v>-4.8</v>
       </c>
       <c r="O27" t="n">
         <v>39</v>
@@ -2366,7 +2366,7 @@
         <v>44</v>
       </c>
       <c r="U27" t="n">
-        <v>1661.5</v>
+        <v>1671.3</v>
       </c>
     </row>
     <row r="28">
@@ -2392,31 +2392,31 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G28" t="n">
-        <v>1797.5</v>
+        <v>1784.2</v>
       </c>
       <c r="H28" t="n">
-        <v>3.4141</v>
+        <v>3.6722</v>
       </c>
       <c r="I28" t="n">
-        <v>117.66</v>
+        <v>116.48</v>
       </c>
       <c r="J28" t="n">
-        <v>103.37</v>
+        <v>103.76</v>
       </c>
       <c r="K28" t="n">
-        <v>14.29</v>
+        <v>12.73</v>
       </c>
       <c r="L28" t="n">
-        <v>0.2935</v>
+        <v>0.2982</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1459</v>
+        <v>0.1464</v>
       </c>
       <c r="N28" t="n">
-        <v>7.2</v>
+        <v>1.8</v>
       </c>
       <c r="O28" t="n">
         <v>45</v>
@@ -2437,7 +2437,7 @@
         <v>43</v>
       </c>
       <c r="U28" t="n">
-        <v>1569.9</v>
+        <v>1572.5</v>
       </c>
     </row>
     <row r="29">
@@ -2889,31 +2889,31 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G35" t="n">
-        <v>2174.3</v>
+        <v>2180.4</v>
       </c>
       <c r="H35" t="n">
-        <v>6.1854</v>
+        <v>5.8798</v>
       </c>
       <c r="I35" t="n">
-        <v>121.55</v>
+        <v>121.93</v>
       </c>
       <c r="J35" t="n">
-        <v>97.56</v>
+        <v>97.66</v>
       </c>
       <c r="K35" t="n">
-        <v>23.99</v>
+        <v>24.27</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2548</v>
+        <v>0.256</v>
       </c>
       <c r="M35" t="n">
-        <v>0.1616</v>
+        <v>0.1607</v>
       </c>
       <c r="N35" t="n">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
@@ -2934,7 +2934,7 @@
         <v>2</v>
       </c>
       <c r="U35" t="n">
-        <v>1765.3</v>
+        <v>1779.7</v>
       </c>
     </row>
     <row r="36">
@@ -3457,31 +3457,31 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G43" t="n">
-        <v>1819.6</v>
+        <v>1813.6</v>
       </c>
       <c r="H43" t="n">
-        <v>8.063000000000001</v>
+        <v>7.6609</v>
       </c>
       <c r="I43" t="n">
-        <v>120.5</v>
+        <v>119.71</v>
       </c>
       <c r="J43" t="n">
-        <v>98.58</v>
+        <v>99.98</v>
       </c>
       <c r="K43" t="n">
-        <v>21.92</v>
+        <v>19.73</v>
       </c>
       <c r="L43" t="n">
-        <v>0.2482</v>
+        <v>0.2441</v>
       </c>
       <c r="M43" t="n">
-        <v>0.1652</v>
+        <v>0.1634</v>
       </c>
       <c r="N43" t="n">
-        <v>3.2</v>
+        <v>-4.2</v>
       </c>
       <c r="O43" t="n">
         <v>41</v>
@@ -3502,7 +3502,7 @@
         <v>31</v>
       </c>
       <c r="U43" t="n">
-        <v>1526.5</v>
+        <v>1540.5</v>
       </c>
     </row>
     <row r="44">
@@ -4309,31 +4309,31 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G55" t="n">
-        <v>2070.4</v>
+        <v>2027.1</v>
       </c>
       <c r="H55" t="n">
-        <v>5.4527</v>
+        <v>5.1307</v>
       </c>
       <c r="I55" t="n">
-        <v>120.17</v>
+        <v>119.76</v>
       </c>
       <c r="J55" t="n">
-        <v>93.73999999999999</v>
+        <v>94.54000000000001</v>
       </c>
       <c r="K55" t="n">
-        <v>26.42</v>
+        <v>25.22</v>
       </c>
       <c r="L55" t="n">
-        <v>0.3009</v>
+        <v>0.2957</v>
       </c>
       <c r="M55" t="n">
-        <v>0.1341</v>
+        <v>0.1318</v>
       </c>
       <c r="N55" t="n">
-        <v>11.8</v>
+        <v>2.4</v>
       </c>
       <c r="O55" t="n">
         <v>10</v>
@@ -4354,7 +4354,7 @@
         <v>7</v>
       </c>
       <c r="U55" t="n">
-        <v>1596.4</v>
+        <v>1606.9</v>
       </c>
     </row>
     <row r="56">
@@ -4380,31 +4380,31 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G56" t="n">
-        <v>1980.8</v>
+        <v>1988.1</v>
       </c>
       <c r="H56" t="n">
-        <v>5.1109</v>
+        <v>5.0738</v>
       </c>
       <c r="I56" t="n">
-        <v>122.95</v>
+        <v>122.97</v>
       </c>
       <c r="J56" t="n">
-        <v>109.03</v>
+        <v>109.34</v>
       </c>
       <c r="K56" t="n">
-        <v>13.91</v>
+        <v>13.63</v>
       </c>
       <c r="L56" t="n">
-        <v>0.2989</v>
+        <v>0.2961</v>
       </c>
       <c r="M56" t="n">
-        <v>0.1207</v>
+        <v>0.1197</v>
       </c>
       <c r="N56" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="O56" t="n">
         <v>15</v>
@@ -4425,7 +4425,7 @@
         <v>15</v>
       </c>
       <c r="U56" t="n">
-        <v>1727.5</v>
+        <v>1731.7</v>
       </c>
     </row>
     <row r="57">
@@ -4948,31 +4948,31 @@
         <v>1</v>
       </c>
       <c r="F64" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G64" t="n">
-        <v>1801.8</v>
+        <v>1845.1</v>
       </c>
       <c r="H64" t="n">
-        <v>2.6488</v>
+        <v>2.8244</v>
       </c>
       <c r="I64" t="n">
-        <v>119.21</v>
+        <v>119.11</v>
       </c>
       <c r="J64" t="n">
-        <v>110.83</v>
+        <v>110.73</v>
       </c>
       <c r="K64" t="n">
-        <v>8.369999999999999</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="L64" t="n">
-        <v>0.3031</v>
+        <v>0.3021</v>
       </c>
       <c r="M64" t="n">
-        <v>0.1432</v>
+        <v>0.1423</v>
       </c>
       <c r="N64" t="n">
-        <v>-4.6</v>
+        <v>0.6</v>
       </c>
       <c r="O64" t="n">
         <v>37</v>
@@ -4993,7 +4993,7 @@
         <v>42</v>
       </c>
       <c r="U64" t="n">
-        <v>1706</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="65">
@@ -5019,31 +5019,31 @@
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G65" t="n">
-        <v>1664.3</v>
+        <v>1657</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.6842</v>
+        <v>-0.3178</v>
       </c>
       <c r="I65" t="n">
-        <v>120.78</v>
+        <v>120.56</v>
       </c>
       <c r="J65" t="n">
-        <v>100.59</v>
+        <v>101.28</v>
       </c>
       <c r="K65" t="n">
-        <v>20.2</v>
+        <v>19.29</v>
       </c>
       <c r="L65" t="n">
-        <v>0.3016</v>
+        <v>0.303</v>
       </c>
       <c r="M65" t="n">
-        <v>0.128</v>
+        <v>0.1274</v>
       </c>
       <c r="N65" t="n">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="O65" t="n">
         <v>92</v>
@@ -5064,7 +5064,7 @@
         <v>75</v>
       </c>
       <c r="U65" t="n">
-        <v>1401.4</v>
+        <v>1404.4</v>
       </c>
     </row>
     <row r="66">

--- a/team_stats_2026.xlsx
+++ b/team_stats_2026.xlsx
@@ -617,31 +617,31 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G3" t="n">
-        <v>2053.4</v>
+        <v>2068.6</v>
       </c>
       <c r="H3" t="n">
-        <v>6.6189</v>
+        <v>6.1349</v>
       </c>
       <c r="I3" t="n">
-        <v>116.79</v>
+        <v>116.64</v>
       </c>
       <c r="J3" t="n">
-        <v>98.31999999999999</v>
+        <v>97.92</v>
       </c>
       <c r="K3" t="n">
-        <v>18.48</v>
+        <v>18.73</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3039</v>
+        <v>0.3031</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1587</v>
+        <v>0.1622</v>
       </c>
       <c r="N3" t="n">
-        <v>5.2</v>
+        <v>9.6</v>
       </c>
       <c r="O3" t="n">
         <v>11</v>
@@ -662,7 +662,7 @@
         <v>10</v>
       </c>
       <c r="U3" t="n">
-        <v>1662.8</v>
+        <v>1675.6</v>
       </c>
     </row>
     <row r="4">
@@ -759,31 +759,31 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G5" t="n">
-        <v>1979.2</v>
+        <v>1953.8</v>
       </c>
       <c r="H5" t="n">
-        <v>9.864800000000001</v>
+        <v>9.4422</v>
       </c>
       <c r="I5" t="n">
-        <v>109.77</v>
+        <v>109.19</v>
       </c>
       <c r="J5" t="n">
-        <v>100.72</v>
+        <v>100.64</v>
       </c>
       <c r="K5" t="n">
-        <v>9.039999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2534</v>
+        <v>0.2555</v>
       </c>
       <c r="M5" t="n">
-        <v>0.15</v>
+        <v>0.1489</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O5" t="n">
         <v>21</v>
@@ -804,7 +804,7 @@
         <v>21</v>
       </c>
       <c r="U5" t="n">
-        <v>1780.1</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="6">
@@ -830,31 +830,31 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G6" t="n">
-        <v>1989.2</v>
+        <v>2014.7</v>
       </c>
       <c r="H6" t="n">
-        <v>5.7241</v>
+        <v>5.7703</v>
       </c>
       <c r="I6" t="n">
-        <v>114.41</v>
+        <v>113.75</v>
       </c>
       <c r="J6" t="n">
         <v>97.8</v>
       </c>
       <c r="K6" t="n">
-        <v>16.61</v>
+        <v>15.96</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3208</v>
+        <v>0.3172</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1418</v>
+        <v>0.1451</v>
       </c>
       <c r="N6" t="n">
-        <v>15.2</v>
+        <v>14.2</v>
       </c>
       <c r="O6" t="n">
         <v>17</v>
@@ -875,7 +875,7 @@
         <v>16</v>
       </c>
       <c r="U6" t="n">
-        <v>1684.5</v>
+        <v>1698.7</v>
       </c>
     </row>
     <row r="7">
@@ -972,31 +972,31 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G8" t="n">
-        <v>1897.1</v>
+        <v>1881.9</v>
       </c>
       <c r="H8" t="n">
-        <v>2.9774</v>
+        <v>3.1818</v>
       </c>
       <c r="I8" t="n">
-        <v>116.93</v>
+        <v>116.16</v>
       </c>
       <c r="J8" t="n">
-        <v>107.23</v>
+        <v>107.67</v>
       </c>
       <c r="K8" t="n">
-        <v>9.699999999999999</v>
+        <v>8.49</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3073</v>
+        <v>0.3078</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1316</v>
+        <v>0.1334</v>
       </c>
       <c r="N8" t="n">
-        <v>7</v>
+        <v>-0.4</v>
       </c>
       <c r="O8" t="n">
         <v>27</v>
@@ -1017,7 +1017,7 @@
         <v>30</v>
       </c>
       <c r="U8" t="n">
-        <v>1708.6</v>
+        <v>1716.2</v>
       </c>
     </row>
     <row r="9">
@@ -1682,31 +1682,31 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G18" t="n">
-        <v>2007.2</v>
+        <v>1970.4</v>
       </c>
       <c r="H18" t="n">
-        <v>3.5894</v>
+        <v>3.6774</v>
       </c>
       <c r="I18" t="n">
-        <v>121.8</v>
+        <v>121.29</v>
       </c>
       <c r="J18" t="n">
-        <v>99.02</v>
+        <v>99.98</v>
       </c>
       <c r="K18" t="n">
-        <v>22.78</v>
+        <v>21.31</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3326</v>
+        <v>0.3343</v>
       </c>
       <c r="M18" t="n">
-        <v>0.155</v>
+        <v>0.1559</v>
       </c>
       <c r="N18" t="n">
-        <v>18.2</v>
+        <v>11.2</v>
       </c>
       <c r="O18" t="n">
         <v>4</v>
@@ -1727,7 +1727,7 @@
         <v>4</v>
       </c>
       <c r="U18" t="n">
-        <v>1703.3</v>
+        <v>1725.7</v>
       </c>
     </row>
     <row r="19">
@@ -2250,31 +2250,31 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G26" t="n">
-        <v>1860.1</v>
+        <v>1896.9</v>
       </c>
       <c r="H26" t="n">
-        <v>3.0379</v>
+        <v>2.8676</v>
       </c>
       <c r="I26" t="n">
-        <v>119.22</v>
+        <v>119.24</v>
       </c>
       <c r="J26" t="n">
-        <v>105.02</v>
+        <v>105.48</v>
       </c>
       <c r="K26" t="n">
-        <v>14.21</v>
+        <v>13.77</v>
       </c>
       <c r="L26" t="n">
-        <v>0.2918</v>
+        <v>0.2926</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1418</v>
+        <v>0.1441</v>
       </c>
       <c r="N26" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="O26" t="n">
         <v>25</v>
@@ -2295,7 +2295,7 @@
         <v>27</v>
       </c>
       <c r="U26" t="n">
-        <v>1717.1</v>
+        <v>1722.3</v>
       </c>
     </row>
     <row r="27">
@@ -2960,31 +2960,31 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G36" t="n">
-        <v>2040.7</v>
+        <v>2057.2</v>
       </c>
       <c r="H36" t="n">
-        <v>1.9908</v>
+        <v>1.8048</v>
       </c>
       <c r="I36" t="n">
-        <v>119.65</v>
+        <v>119.44</v>
       </c>
       <c r="J36" t="n">
-        <v>95.53</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>24.12</v>
+        <v>24.09</v>
       </c>
       <c r="L36" t="n">
-        <v>0.3242</v>
+        <v>0.3224</v>
       </c>
       <c r="M36" t="n">
-        <v>0.1466</v>
+        <v>0.145</v>
       </c>
       <c r="N36" t="n">
-        <v>24.8</v>
+        <v>24.4</v>
       </c>
       <c r="O36" t="n">
         <v>6</v>
@@ -3005,7 +3005,7 @@
         <v>6</v>
       </c>
       <c r="U36" t="n">
-        <v>1704.9</v>
+        <v>1720.3</v>
       </c>
     </row>
     <row r="37">
@@ -3031,31 +3031,31 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G37" t="n">
-        <v>1966.7</v>
+        <v>1936.6</v>
       </c>
       <c r="H37" t="n">
-        <v>11.7947</v>
+        <v>11.404</v>
       </c>
       <c r="I37" t="n">
-        <v>119.42</v>
+        <v>119.06</v>
       </c>
       <c r="J37" t="n">
-        <v>101.19</v>
+        <v>101.8</v>
       </c>
       <c r="K37" t="n">
-        <v>18.23</v>
+        <v>17.26</v>
       </c>
       <c r="L37" t="n">
-        <v>0.3132</v>
+        <v>0.3125</v>
       </c>
       <c r="M37" t="n">
-        <v>0.1564</v>
+        <v>0.1558</v>
       </c>
       <c r="N37" t="n">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="O37" t="n">
         <v>13</v>
@@ -3076,7 +3076,7 @@
         <v>12</v>
       </c>
       <c r="U37" t="n">
-        <v>1654.9</v>
+        <v>1670.5</v>
       </c>
     </row>
     <row r="38">
@@ -3102,31 +3102,31 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G38" t="n">
-        <v>1954.7</v>
+        <v>1985.7</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.3316</v>
+        <v>-1.3006</v>
       </c>
       <c r="I38" t="n">
-        <v>121.89</v>
+        <v>122.08</v>
       </c>
       <c r="J38" t="n">
-        <v>110.31</v>
+        <v>109.74</v>
       </c>
       <c r="K38" t="n">
-        <v>11.59</v>
+        <v>12.34</v>
       </c>
       <c r="L38" t="n">
-        <v>0.2849</v>
+        <v>0.2878</v>
       </c>
       <c r="M38" t="n">
-        <v>0.1295</v>
+        <v>0.1315</v>
       </c>
       <c r="N38" t="n">
-        <v>4.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O38" t="n">
         <v>18</v>
@@ -3147,7 +3147,7 @@
         <v>18</v>
       </c>
       <c r="U38" t="n">
-        <v>1760.9</v>
+        <v>1777.2</v>
       </c>
     </row>
     <row r="39">
@@ -3173,31 +3173,31 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G39" t="n">
-        <v>2018.6</v>
+        <v>1987.5</v>
       </c>
       <c r="H39" t="n">
-        <v>8.9857</v>
+        <v>8.4871</v>
       </c>
       <c r="I39" t="n">
-        <v>118.54</v>
+        <v>117.46</v>
       </c>
       <c r="J39" t="n">
-        <v>106.75</v>
+        <v>107.74</v>
       </c>
       <c r="K39" t="n">
-        <v>11.79</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>0.2876</v>
+        <v>0.2926</v>
       </c>
       <c r="M39" t="n">
-        <v>0.155</v>
+        <v>0.1548</v>
       </c>
       <c r="N39" t="n">
-        <v>-1.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="O39" t="n">
         <v>20</v>
@@ -3218,7 +3218,7 @@
         <v>19</v>
       </c>
       <c r="U39" t="n">
-        <v>1767</v>
+        <v>1776.6</v>
       </c>
     </row>
     <row r="40">
@@ -3244,31 +3244,31 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G40" t="n">
-        <v>1914.8</v>
+        <v>1945</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.3934</v>
+        <v>-1.2526</v>
       </c>
       <c r="I40" t="n">
-        <v>116.95</v>
+        <v>117.14</v>
       </c>
       <c r="J40" t="n">
-        <v>101.62</v>
+        <v>102.16</v>
       </c>
       <c r="K40" t="n">
-        <v>15.34</v>
+        <v>14.97</v>
       </c>
       <c r="L40" t="n">
-        <v>0.3564</v>
+        <v>0.3608</v>
       </c>
       <c r="M40" t="n">
-        <v>0.1676</v>
+        <v>0.1645</v>
       </c>
       <c r="N40" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="O40" t="n">
         <v>16</v>
@@ -3289,7 +3289,7 @@
         <v>20</v>
       </c>
       <c r="U40" t="n">
-        <v>1716.9</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="41">
@@ -3315,31 +3315,31 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G41" t="n">
-        <v>1905.5</v>
+        <v>1889</v>
       </c>
       <c r="H41" t="n">
-        <v>4.5369</v>
+        <v>4.416</v>
       </c>
       <c r="I41" t="n">
-        <v>116.17</v>
+        <v>115.32</v>
       </c>
       <c r="J41" t="n">
-        <v>106.38</v>
+        <v>106.86</v>
       </c>
       <c r="K41" t="n">
-        <v>9.789999999999999</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>0.3078</v>
+        <v>0.3034</v>
       </c>
       <c r="M41" t="n">
-        <v>0.1463</v>
+        <v>0.1517</v>
       </c>
       <c r="N41" t="n">
-        <v>0.2</v>
+        <v>-2.2</v>
       </c>
       <c r="O41" t="n">
         <v>28</v>
@@ -3360,7 +3360,7 @@
         <v>28</v>
       </c>
       <c r="U41" t="n">
-        <v>1734</v>
+        <v>1743.2</v>
       </c>
     </row>
     <row r="42">
@@ -4167,31 +4167,31 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G53" t="n">
-        <v>2272.5</v>
+        <v>2278.5</v>
       </c>
       <c r="H53" t="n">
-        <v>6.6001</v>
+        <v>6.3904</v>
       </c>
       <c r="I53" t="n">
-        <v>121.6</v>
+        <v>121.65</v>
       </c>
       <c r="J53" t="n">
-        <v>96.53</v>
+        <v>96.95</v>
       </c>
       <c r="K53" t="n">
-        <v>25.07</v>
+        <v>24.69</v>
       </c>
       <c r="L53" t="n">
-        <v>0.2933</v>
+        <v>0.2971</v>
       </c>
       <c r="M53" t="n">
-        <v>0.1498</v>
+        <v>0.1507</v>
       </c>
       <c r="N53" t="n">
-        <v>14.6</v>
+        <v>15</v>
       </c>
       <c r="O53" t="n">
         <v>2</v>
@@ -4212,7 +4212,7 @@
         <v>3</v>
       </c>
       <c r="U53" t="n">
-        <v>1753.9</v>
+        <v>1771.6</v>
       </c>
     </row>
     <row r="54">
@@ -4238,31 +4238,31 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G54" t="n">
-        <v>2011.5</v>
+        <v>2023.2</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.6772</v>
+        <v>-0.6463</v>
       </c>
       <c r="I54" t="n">
-        <v>125.91</v>
+        <v>125.55</v>
       </c>
       <c r="J54" t="n">
-        <v>107.36</v>
+        <v>107.35</v>
       </c>
       <c r="K54" t="n">
-        <v>18.55</v>
+        <v>18.21</v>
       </c>
       <c r="L54" t="n">
-        <v>0.3128</v>
+        <v>0.3071</v>
       </c>
       <c r="M54" t="n">
-        <v>0.1355</v>
+        <v>0.1369</v>
       </c>
       <c r="N54" t="n">
-        <v>15.4</v>
+        <v>14.8</v>
       </c>
       <c r="O54" t="n">
         <v>8</v>
@@ -4283,7 +4283,7 @@
         <v>9</v>
       </c>
       <c r="U54" t="n">
-        <v>1753.9</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="55">
@@ -4593,31 +4593,31 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G59" t="n">
-        <v>1794.7</v>
+        <v>1783</v>
       </c>
       <c r="H59" t="n">
-        <v>11.4257</v>
+        <v>11.1893</v>
       </c>
       <c r="I59" t="n">
-        <v>117.44</v>
+        <v>116.93</v>
       </c>
       <c r="J59" t="n">
-        <v>102.47</v>
+        <v>103.2</v>
       </c>
       <c r="K59" t="n">
-        <v>14.97</v>
+        <v>13.73</v>
       </c>
       <c r="L59" t="n">
-        <v>0.3107</v>
+        <v>0.3146</v>
       </c>
       <c r="M59" t="n">
-        <v>0.1566</v>
+        <v>0.1579</v>
       </c>
       <c r="N59" t="n">
-        <v>0.4</v>
+        <v>-3.2</v>
       </c>
       <c r="O59" t="n">
         <v>31</v>
@@ -4638,7 +4638,7 @@
         <v>32</v>
       </c>
       <c r="U59" t="n">
-        <v>1636.7</v>
+        <v>1646.6</v>
       </c>
     </row>
     <row r="60">
@@ -4735,31 +4735,31 @@
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G61" t="n">
-        <v>1917</v>
+        <v>1911</v>
       </c>
       <c r="H61" t="n">
-        <v>0.2638</v>
+        <v>0.436</v>
       </c>
       <c r="I61" t="n">
-        <v>119.89</v>
+        <v>119.22</v>
       </c>
       <c r="J61" t="n">
-        <v>103.86</v>
+        <v>104.38</v>
       </c>
       <c r="K61" t="n">
-        <v>16.03</v>
+        <v>14.84</v>
       </c>
       <c r="L61" t="n">
-        <v>0.3056</v>
+        <v>0.3052</v>
       </c>
       <c r="M61" t="n">
-        <v>0.1477</v>
+        <v>0.1448</v>
       </c>
       <c r="N61" t="n">
-        <v>11.6</v>
+        <v>8.4</v>
       </c>
       <c r="O61" t="n">
         <v>30</v>
@@ -4780,7 +4780,7 @@
         <v>26</v>
       </c>
       <c r="U61" t="n">
-        <v>1617</v>
+        <v>1632.8</v>
       </c>
     </row>
     <row r="62">

--- a/team_stats_2026.xlsx
+++ b/team_stats_2026.xlsx
@@ -1753,31 +1753,31 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="G19" t="n">
-        <v>2122.2</v>
+        <v>2086.9</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0162</v>
+        <v>0.9762</v>
       </c>
       <c r="I19" t="n">
-        <v>117.91</v>
+        <v>117.05</v>
       </c>
       <c r="J19" t="n">
-        <v>94.52</v>
+        <v>95.25</v>
       </c>
       <c r="K19" t="n">
-        <v>23.39</v>
+        <v>21.8</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3362</v>
+        <v>0.3336</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1224</v>
+        <v>0.1237</v>
       </c>
       <c r="N19" t="n">
-        <v>17.2</v>
+        <v>13.8</v>
       </c>
       <c r="O19" t="n">
         <v>5</v>
@@ -1798,7 +1798,7 @@
         <v>5</v>
       </c>
       <c r="U19" t="n">
-        <v>1741.9</v>
+        <v>1746.8</v>
       </c>
     </row>
     <row r="20">
@@ -1824,31 +1824,31 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="G20" t="n">
-        <v>1997.8</v>
+        <v>2033.1</v>
       </c>
       <c r="H20" t="n">
-        <v>6.9704</v>
+        <v>6.6485</v>
       </c>
       <c r="I20" t="n">
-        <v>125.89</v>
+        <v>125.39</v>
       </c>
       <c r="J20" t="n">
-        <v>102.84</v>
+        <v>102.65</v>
       </c>
       <c r="K20" t="n">
-        <v>23.05</v>
+        <v>22.74</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3231</v>
+        <v>0.3236</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1277</v>
+        <v>0.1257</v>
       </c>
       <c r="N20" t="n">
-        <v>17</v>
+        <v>13.8</v>
       </c>
       <c r="O20" t="n">
         <v>7</v>
@@ -1869,7 +1869,7 @@
         <v>8</v>
       </c>
       <c r="U20" t="n">
-        <v>1718.8</v>
+        <v>1730.7</v>
       </c>
     </row>
     <row r="21">
@@ -1895,31 +1895,31 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="G21" t="n">
-        <v>2012.5</v>
+        <v>1992.7</v>
       </c>
       <c r="H21" t="n">
-        <v>8.516999999999999</v>
+        <v>8.0527</v>
       </c>
       <c r="I21" t="n">
-        <v>115.19</v>
+        <v>115.35</v>
       </c>
       <c r="J21" t="n">
-        <v>98.64</v>
+        <v>99.66</v>
       </c>
       <c r="K21" t="n">
-        <v>16.56</v>
+        <v>15.69</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2422</v>
+        <v>0.2383</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1409</v>
+        <v>0.1384</v>
       </c>
       <c r="N21" t="n">
-        <v>0.8</v>
+        <v>3.6</v>
       </c>
       <c r="O21" t="n">
         <v>14</v>
@@ -1940,7 +1940,7 @@
         <v>14</v>
       </c>
       <c r="U21" t="n">
-        <v>1683.9</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="22">
@@ -2250,31 +2250,31 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G26" t="n">
-        <v>1896.9</v>
+        <v>1916.7</v>
       </c>
       <c r="H26" t="n">
-        <v>2.8676</v>
+        <v>2.8861</v>
       </c>
       <c r="I26" t="n">
-        <v>119.24</v>
+        <v>119.48</v>
       </c>
       <c r="J26" t="n">
-        <v>105.48</v>
+        <v>105.75</v>
       </c>
       <c r="K26" t="n">
-        <v>13.77</v>
+        <v>13.73</v>
       </c>
       <c r="L26" t="n">
-        <v>0.2926</v>
+        <v>0.294</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1441</v>
+        <v>0.1445</v>
       </c>
       <c r="N26" t="n">
-        <v>1.2</v>
+        <v>4.2</v>
       </c>
       <c r="O26" t="n">
         <v>25</v>
@@ -2295,7 +2295,7 @@
         <v>27</v>
       </c>
       <c r="U26" t="n">
-        <v>1722.3</v>
+        <v>1722.1</v>
       </c>
     </row>
     <row r="27">
@@ -4167,31 +4167,31 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G53" t="n">
-        <v>2278.5</v>
+        <v>2286.8</v>
       </c>
       <c r="H53" t="n">
-        <v>6.3904</v>
+        <v>6.212</v>
       </c>
       <c r="I53" t="n">
-        <v>121.65</v>
+        <v>122.04</v>
       </c>
       <c r="J53" t="n">
-        <v>96.95</v>
+        <v>97.27</v>
       </c>
       <c r="K53" t="n">
-        <v>24.69</v>
+        <v>24.77</v>
       </c>
       <c r="L53" t="n">
-        <v>0.2971</v>
+        <v>0.2931</v>
       </c>
       <c r="M53" t="n">
-        <v>0.1507</v>
+        <v>0.1505</v>
       </c>
       <c r="N53" t="n">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="O53" t="n">
         <v>2</v>
@@ -4212,7 +4212,7 @@
         <v>3</v>
       </c>
       <c r="U53" t="n">
-        <v>1771.6</v>
+        <v>1773.8</v>
       </c>
     </row>
     <row r="54">
@@ -4238,31 +4238,31 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G54" t="n">
-        <v>2023.2</v>
+        <v>2037.1</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.6463</v>
+        <v>-0.5673</v>
       </c>
       <c r="I54" t="n">
-        <v>125.55</v>
+        <v>125.58</v>
       </c>
       <c r="J54" t="n">
-        <v>107.35</v>
+        <v>107.86</v>
       </c>
       <c r="K54" t="n">
-        <v>18.21</v>
+        <v>17.73</v>
       </c>
       <c r="L54" t="n">
-        <v>0.3071</v>
+        <v>0.3105</v>
       </c>
       <c r="M54" t="n">
-        <v>0.1369</v>
+        <v>0.1341</v>
       </c>
       <c r="N54" t="n">
-        <v>14.8</v>
+        <v>12</v>
       </c>
       <c r="O54" t="n">
         <v>8</v>
@@ -4283,7 +4283,7 @@
         <v>9</v>
       </c>
       <c r="U54" t="n">
-        <v>1767</v>
+        <v>1768.6</v>
       </c>
     </row>
     <row r="55">
@@ -4380,31 +4380,31 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="G56" t="n">
-        <v>1988.1</v>
+        <v>1979.8</v>
       </c>
       <c r="H56" t="n">
-        <v>5.0738</v>
+        <v>5.0525</v>
       </c>
       <c r="I56" t="n">
-        <v>122.97</v>
+        <v>122.7</v>
       </c>
       <c r="J56" t="n">
-        <v>109.34</v>
+        <v>110.4</v>
       </c>
       <c r="K56" t="n">
-        <v>13.63</v>
+        <v>12.3</v>
       </c>
       <c r="L56" t="n">
-        <v>0.2961</v>
+        <v>0.2975</v>
       </c>
       <c r="M56" t="n">
-        <v>0.1197</v>
+        <v>0.1198</v>
       </c>
       <c r="N56" t="n">
-        <v>8.4</v>
+        <v>3.6</v>
       </c>
       <c r="O56" t="n">
         <v>15</v>
@@ -4425,7 +4425,7 @@
         <v>15</v>
       </c>
       <c r="U56" t="n">
-        <v>1731.7</v>
+        <v>1752.3</v>
       </c>
     </row>
     <row r="57">
@@ -4948,31 +4948,31 @@
         <v>1</v>
       </c>
       <c r="F64" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="G64" t="n">
-        <v>1845.1</v>
+        <v>1831.3</v>
       </c>
       <c r="H64" t="n">
-        <v>2.8244</v>
+        <v>3.1749</v>
       </c>
       <c r="I64" t="n">
-        <v>119.11</v>
+        <v>119.65</v>
       </c>
       <c r="J64" t="n">
-        <v>110.73</v>
+        <v>111.7</v>
       </c>
       <c r="K64" t="n">
-        <v>8.380000000000001</v>
+        <v>7.95</v>
       </c>
       <c r="L64" t="n">
-        <v>0.3021</v>
+        <v>0.3054</v>
       </c>
       <c r="M64" t="n">
-        <v>0.1423</v>
+        <v>0.1418</v>
       </c>
       <c r="N64" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="O64" t="n">
         <v>37</v>
@@ -4993,7 +4993,7 @@
         <v>42</v>
       </c>
       <c r="U64" t="n">
-        <v>1711</v>
+        <v>1708.8</v>
       </c>
     </row>
     <row r="65">

--- a/team_stats_2026.xlsx
+++ b/team_stats_2026.xlsx
@@ -546,31 +546,31 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="G2" t="n">
-        <v>2203.3</v>
+        <v>2216.6</v>
       </c>
       <c r="H2" t="n">
-        <v>3.7385</v>
+        <v>3.7533</v>
       </c>
       <c r="I2" t="n">
-        <v>122.58</v>
+        <v>122.72</v>
       </c>
       <c r="J2" t="n">
-        <v>94.55</v>
+        <v>95.47</v>
       </c>
       <c r="K2" t="n">
-        <v>28.03</v>
+        <v>27.25</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2951</v>
+        <v>0.296</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1573</v>
+        <v>0.1558</v>
       </c>
       <c r="N2" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -591,7 +591,7 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>1715.1</v>
+        <v>1720.4</v>
       </c>
     </row>
     <row r="3">
@@ -617,31 +617,31 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="G3" t="n">
-        <v>2068.6</v>
+        <v>2093.1</v>
       </c>
       <c r="H3" t="n">
-        <v>6.1349</v>
+        <v>5.7678</v>
       </c>
       <c r="I3" t="n">
-        <v>116.64</v>
+        <v>116.3</v>
       </c>
       <c r="J3" t="n">
-        <v>97.92</v>
+        <v>98.05</v>
       </c>
       <c r="K3" t="n">
-        <v>18.73</v>
+        <v>18.25</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3031</v>
+        <v>0.2995</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1622</v>
+        <v>0.1613</v>
       </c>
       <c r="N3" t="n">
-        <v>9.6</v>
+        <v>5.4</v>
       </c>
       <c r="O3" t="n">
         <v>11</v>
@@ -662,7 +662,7 @@
         <v>10</v>
       </c>
       <c r="U3" t="n">
-        <v>1675.6</v>
+        <v>1680.4</v>
       </c>
     </row>
     <row r="4">
@@ -688,31 +688,31 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="G4" t="n">
-        <v>2045.3</v>
+        <v>2020.8</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0252</v>
+        <v>-0.0373</v>
       </c>
       <c r="I4" t="n">
-        <v>117.7</v>
+        <v>117.08</v>
       </c>
       <c r="J4" t="n">
-        <v>101.52</v>
+        <v>101.69</v>
       </c>
       <c r="K4" t="n">
-        <v>16.18</v>
+        <v>15.38</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2911</v>
+        <v>0.2927</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1636</v>
+        <v>0.1629</v>
       </c>
       <c r="N4" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
         <v>9</v>
@@ -733,7 +733,7 @@
         <v>11</v>
       </c>
       <c r="U4" t="n">
-        <v>1733.5</v>
+        <v>1741.2</v>
       </c>
     </row>
     <row r="5">
@@ -830,31 +830,31 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="G6" t="n">
-        <v>2014.7</v>
+        <v>2001.5</v>
       </c>
       <c r="H6" t="n">
-        <v>5.7703</v>
+        <v>5.8981</v>
       </c>
       <c r="I6" t="n">
-        <v>113.75</v>
+        <v>114</v>
       </c>
       <c r="J6" t="n">
-        <v>97.8</v>
+        <v>98.75</v>
       </c>
       <c r="K6" t="n">
-        <v>15.96</v>
+        <v>15.25</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3172</v>
+        <v>0.3197</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1451</v>
+        <v>0.1428</v>
       </c>
       <c r="N6" t="n">
-        <v>14.2</v>
+        <v>10.6</v>
       </c>
       <c r="O6" t="n">
         <v>17</v>
@@ -875,7 +875,7 @@
         <v>16</v>
       </c>
       <c r="U6" t="n">
-        <v>1698.7</v>
+        <v>1705.8</v>
       </c>
     </row>
     <row r="7">
@@ -2889,31 +2889,31 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="G35" t="n">
-        <v>2180.4</v>
+        <v>2193.3</v>
       </c>
       <c r="H35" t="n">
-        <v>5.8798</v>
+        <v>5.6231</v>
       </c>
       <c r="I35" t="n">
-        <v>121.93</v>
+        <v>122.06</v>
       </c>
       <c r="J35" t="n">
-        <v>97.66</v>
+        <v>98.04000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>24.27</v>
+        <v>24.02</v>
       </c>
       <c r="L35" t="n">
-        <v>0.256</v>
+        <v>0.2569</v>
       </c>
       <c r="M35" t="n">
-        <v>0.1607</v>
+        <v>0.1594</v>
       </c>
       <c r="N35" t="n">
-        <v>8.6</v>
+        <v>10.4</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
@@ -2934,7 +2934,7 @@
         <v>2</v>
       </c>
       <c r="U35" t="n">
-        <v>1779.7</v>
+        <v>1785.2</v>
       </c>
     </row>
     <row r="36">
@@ -2960,31 +2960,31 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="G36" t="n">
-        <v>2057.2</v>
+        <v>2022.8</v>
       </c>
       <c r="H36" t="n">
-        <v>1.8048</v>
+        <v>1.7144</v>
       </c>
       <c r="I36" t="n">
-        <v>119.44</v>
+        <v>118.57</v>
       </c>
       <c r="J36" t="n">
-        <v>95.34999999999999</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>24.09</v>
+        <v>22.56</v>
       </c>
       <c r="L36" t="n">
-        <v>0.3224</v>
+        <v>0.3242</v>
       </c>
       <c r="M36" t="n">
-        <v>0.145</v>
+        <v>0.149</v>
       </c>
       <c r="N36" t="n">
-        <v>24.4</v>
+        <v>11.8</v>
       </c>
       <c r="O36" t="n">
         <v>6</v>
@@ -3005,7 +3005,7 @@
         <v>6</v>
       </c>
       <c r="U36" t="n">
-        <v>1720.3</v>
+        <v>1721.4</v>
       </c>
     </row>
     <row r="37">
@@ -3102,31 +3102,31 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="G38" t="n">
-        <v>1985.7</v>
+        <v>1972.8</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.3006</v>
+        <v>-1.1118</v>
       </c>
       <c r="I38" t="n">
-        <v>122.08</v>
+        <v>121.53</v>
       </c>
       <c r="J38" t="n">
-        <v>109.74</v>
+        <v>110.47</v>
       </c>
       <c r="K38" t="n">
-        <v>12.34</v>
+        <v>11.07</v>
       </c>
       <c r="L38" t="n">
-        <v>0.2878</v>
+        <v>0.2891</v>
       </c>
       <c r="M38" t="n">
-        <v>0.1315</v>
+        <v>0.1299</v>
       </c>
       <c r="N38" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="O38" t="n">
         <v>18</v>
@@ -3147,7 +3147,7 @@
         <v>18</v>
       </c>
       <c r="U38" t="n">
-        <v>1777.2</v>
+        <v>1782.7</v>
       </c>
     </row>
     <row r="39">
@@ -3244,31 +3244,31 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="G40" t="n">
-        <v>1945</v>
+        <v>1979.4</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.2526</v>
+        <v>-0.9851</v>
       </c>
       <c r="I40" t="n">
-        <v>117.14</v>
+        <v>116.89</v>
       </c>
       <c r="J40" t="n">
-        <v>102.16</v>
+        <v>101.67</v>
       </c>
       <c r="K40" t="n">
-        <v>14.97</v>
+        <v>15.22</v>
       </c>
       <c r="L40" t="n">
-        <v>0.3608</v>
+        <v>0.3599</v>
       </c>
       <c r="M40" t="n">
-        <v>0.1645</v>
+        <v>0.165</v>
       </c>
       <c r="N40" t="n">
-        <v>5.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O40" t="n">
         <v>16</v>
@@ -3289,7 +3289,7 @@
         <v>20</v>
       </c>
       <c r="U40" t="n">
-        <v>1724</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="41">

--- a/team_stats_2026.xlsx
+++ b/team_stats_2026.xlsx
@@ -1824,31 +1824,31 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G20" t="n">
-        <v>2033.1</v>
+        <v>2043.2</v>
       </c>
       <c r="H20" t="n">
-        <v>6.6485</v>
+        <v>6.515</v>
       </c>
       <c r="I20" t="n">
-        <v>125.39</v>
+        <v>125.71</v>
       </c>
       <c r="J20" t="n">
-        <v>102.65</v>
+        <v>102.95</v>
       </c>
       <c r="K20" t="n">
-        <v>22.74</v>
+        <v>22.77</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3236</v>
+        <v>0.3271</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1257</v>
+        <v>0.1268</v>
       </c>
       <c r="N20" t="n">
-        <v>13.8</v>
+        <v>15</v>
       </c>
       <c r="O20" t="n">
         <v>7</v>
@@ -1869,7 +1869,7 @@
         <v>8</v>
       </c>
       <c r="U20" t="n">
-        <v>1730.7</v>
+        <v>1722.8</v>
       </c>
     </row>
     <row r="21">
@@ -2250,31 +2250,31 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G26" t="n">
-        <v>1916.7</v>
+        <v>1906.5</v>
       </c>
       <c r="H26" t="n">
-        <v>2.8861</v>
+        <v>2.978</v>
       </c>
       <c r="I26" t="n">
-        <v>119.48</v>
+        <v>119.06</v>
       </c>
       <c r="J26" t="n">
-        <v>105.75</v>
+        <v>106.54</v>
       </c>
       <c r="K26" t="n">
-        <v>13.73</v>
+        <v>12.52</v>
       </c>
       <c r="L26" t="n">
-        <v>0.294</v>
+        <v>0.2966</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1445</v>
+        <v>0.1451</v>
       </c>
       <c r="N26" t="n">
-        <v>4.2</v>
+        <v>-0.4</v>
       </c>
       <c r="O26" t="n">
         <v>25</v>
@@ -2295,7 +2295,7 @@
         <v>27</v>
       </c>
       <c r="U26" t="n">
-        <v>1722.1</v>
+        <v>1722.5</v>
       </c>
     </row>
     <row r="27">
@@ -4167,31 +4167,31 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G53" t="n">
-        <v>2286.8</v>
+        <v>2296.9</v>
       </c>
       <c r="H53" t="n">
-        <v>6.212</v>
+        <v>6.07</v>
       </c>
       <c r="I53" t="n">
-        <v>122.04</v>
+        <v>122.03</v>
       </c>
       <c r="J53" t="n">
-        <v>97.27</v>
+        <v>97.31</v>
       </c>
       <c r="K53" t="n">
-        <v>24.77</v>
+        <v>24.72</v>
       </c>
       <c r="L53" t="n">
-        <v>0.2931</v>
+        <v>0.293</v>
       </c>
       <c r="M53" t="n">
-        <v>0.1505</v>
+        <v>0.1487</v>
       </c>
       <c r="N53" t="n">
-        <v>14.8</v>
+        <v>17.4</v>
       </c>
       <c r="O53" t="n">
         <v>2</v>
@@ -4212,7 +4212,7 @@
         <v>3</v>
       </c>
       <c r="U53" t="n">
-        <v>1773.8</v>
+        <v>1775.1</v>
       </c>
     </row>
     <row r="54">
@@ -4238,31 +4238,31 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G54" t="n">
-        <v>2037.1</v>
+        <v>2027</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.5673</v>
+        <v>-0.4418</v>
       </c>
       <c r="I54" t="n">
-        <v>125.58</v>
+        <v>124.67</v>
       </c>
       <c r="J54" t="n">
-        <v>107.86</v>
+        <v>108.15</v>
       </c>
       <c r="K54" t="n">
-        <v>17.73</v>
+        <v>16.52</v>
       </c>
       <c r="L54" t="n">
-        <v>0.3105</v>
+        <v>0.3125</v>
       </c>
       <c r="M54" t="n">
-        <v>0.1341</v>
+        <v>0.1356</v>
       </c>
       <c r="N54" t="n">
-        <v>12</v>
+        <v>7.6</v>
       </c>
       <c r="O54" t="n">
         <v>8</v>
@@ -4283,7 +4283,7 @@
         <v>9</v>
       </c>
       <c r="U54" t="n">
-        <v>1768.6</v>
+        <v>1782.8</v>
       </c>
     </row>
     <row r="55">

--- a/team_stats_2026.xlsx
+++ b/team_stats_2026.xlsx
@@ -546,31 +546,31 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G2" t="n">
-        <v>2216.6</v>
+        <v>2181.4</v>
       </c>
       <c r="H2" t="n">
-        <v>3.7533</v>
+        <v>3.8063</v>
       </c>
       <c r="I2" t="n">
-        <v>122.72</v>
+        <v>122.37</v>
       </c>
       <c r="J2" t="n">
-        <v>95.47</v>
+        <v>95.94</v>
       </c>
       <c r="K2" t="n">
-        <v>27.25</v>
+        <v>26.43</v>
       </c>
       <c r="L2" t="n">
-        <v>0.296</v>
+        <v>0.3018</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1558</v>
+        <v>0.1533</v>
       </c>
       <c r="N2" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -591,7 +591,7 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>1720.4</v>
+        <v>1722.7</v>
       </c>
     </row>
     <row r="3">
@@ -617,31 +617,31 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G3" t="n">
-        <v>2093.1</v>
+        <v>2128.3</v>
       </c>
       <c r="H3" t="n">
-        <v>5.7678</v>
+        <v>5.5371</v>
       </c>
       <c r="I3" t="n">
-        <v>116.3</v>
+        <v>116.5</v>
       </c>
       <c r="J3" t="n">
-        <v>98.05</v>
+        <v>98.72</v>
       </c>
       <c r="K3" t="n">
-        <v>18.25</v>
+        <v>17.79</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2995</v>
+        <v>0.3001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1613</v>
+        <v>0.1631</v>
       </c>
       <c r="N3" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="O3" t="n">
         <v>11</v>
@@ -662,7 +662,7 @@
         <v>10</v>
       </c>
       <c r="U3" t="n">
-        <v>1680.4</v>
+        <v>1685.7</v>
       </c>
     </row>
     <row r="4">
@@ -2889,31 +2889,31 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G35" t="n">
-        <v>2193.3</v>
+        <v>2205.2</v>
       </c>
       <c r="H35" t="n">
-        <v>5.6231</v>
+        <v>5.4369</v>
       </c>
       <c r="I35" t="n">
-        <v>122.06</v>
+        <v>122.15</v>
       </c>
       <c r="J35" t="n">
-        <v>98.04000000000001</v>
+        <v>97.45999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>24.02</v>
+        <v>24.69</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2569</v>
+        <v>0.2545</v>
       </c>
       <c r="M35" t="n">
-        <v>0.1594</v>
+        <v>0.1592</v>
       </c>
       <c r="N35" t="n">
-        <v>10.4</v>
+        <v>16.4</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
@@ -2934,7 +2934,7 @@
         <v>2</v>
       </c>
       <c r="U35" t="n">
-        <v>1785.2</v>
+        <v>1784.8</v>
       </c>
     </row>
     <row r="36">
@@ -3244,31 +3244,31 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G40" t="n">
-        <v>1979.4</v>
+        <v>1967.6</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.9851</v>
+        <v>-0.6001</v>
       </c>
       <c r="I40" t="n">
-        <v>116.89</v>
+        <v>115.78</v>
       </c>
       <c r="J40" t="n">
-        <v>101.67</v>
+        <v>102.75</v>
       </c>
       <c r="K40" t="n">
-        <v>15.22</v>
+        <v>13.03</v>
       </c>
       <c r="L40" t="n">
-        <v>0.3599</v>
+        <v>0.3632</v>
       </c>
       <c r="M40" t="n">
-        <v>0.165</v>
+        <v>0.1635</v>
       </c>
       <c r="N40" t="n">
-        <v>9.199999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="O40" t="n">
         <v>16</v>
@@ -3289,7 +3289,7 @@
         <v>20</v>
       </c>
       <c r="U40" t="n">
-        <v>1727</v>
+        <v>1731.4</v>
       </c>
     </row>
     <row r="41">

--- a/team_stats_2026.xlsx
+++ b/team_stats_2026.xlsx
@@ -617,31 +617,31 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="G3" t="n">
-        <v>2128.3</v>
+        <v>2148.2</v>
       </c>
       <c r="H3" t="n">
-        <v>5.5371</v>
+        <v>5.461</v>
       </c>
       <c r="I3" t="n">
-        <v>116.5</v>
+        <v>116.33</v>
       </c>
       <c r="J3" t="n">
-        <v>98.72</v>
+        <v>98.55</v>
       </c>
       <c r="K3" t="n">
-        <v>17.79</v>
+        <v>17.78</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3001</v>
+        <v>0.2992</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1631</v>
+        <v>0.1595</v>
       </c>
       <c r="N3" t="n">
-        <v>2.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O3" t="n">
         <v>11</v>
@@ -662,7 +662,7 @@
         <v>10</v>
       </c>
       <c r="U3" t="n">
-        <v>1685.7</v>
+        <v>1679.5</v>
       </c>
     </row>
     <row r="4">
@@ -1824,31 +1824,31 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="G20" t="n">
-        <v>2043.2</v>
+        <v>2023.3</v>
       </c>
       <c r="H20" t="n">
-        <v>6.515</v>
+        <v>6.4189</v>
       </c>
       <c r="I20" t="n">
-        <v>125.71</v>
+        <v>124.78</v>
       </c>
       <c r="J20" t="n">
-        <v>102.95</v>
+        <v>103.29</v>
       </c>
       <c r="K20" t="n">
-        <v>22.77</v>
+        <v>21.49</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3271</v>
+        <v>0.3245</v>
       </c>
       <c r="M20" t="n">
         <v>0.1268</v>
       </c>
       <c r="N20" t="n">
-        <v>15</v>
+        <v>13.8</v>
       </c>
       <c r="O20" t="n">
         <v>7</v>
@@ -1869,7 +1869,7 @@
         <v>8</v>
       </c>
       <c r="U20" t="n">
-        <v>1722.8</v>
+        <v>1729.9</v>
       </c>
     </row>
     <row r="21">
@@ -2889,31 +2889,31 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="G35" t="n">
-        <v>2205.2</v>
+        <v>2238.2</v>
       </c>
       <c r="H35" t="n">
-        <v>5.4369</v>
+        <v>5.3046</v>
       </c>
       <c r="I35" t="n">
-        <v>122.15</v>
+        <v>122.02</v>
       </c>
       <c r="J35" t="n">
-        <v>97.45999999999999</v>
+        <v>97.48</v>
       </c>
       <c r="K35" t="n">
-        <v>24.69</v>
+        <v>24.54</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2545</v>
+        <v>0.2598</v>
       </c>
       <c r="M35" t="n">
-        <v>0.1592</v>
+        <v>0.16</v>
       </c>
       <c r="N35" t="n">
-        <v>16.4</v>
+        <v>21.6</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
@@ -2934,7 +2934,7 @@
         <v>2</v>
       </c>
       <c r="U35" t="n">
-        <v>1784.8</v>
+        <v>1794.5</v>
       </c>
     </row>
     <row r="36">
@@ -4167,31 +4167,31 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="G53" t="n">
-        <v>2296.9</v>
+        <v>2263.9</v>
       </c>
       <c r="H53" t="n">
-        <v>6.07</v>
+        <v>5.9654</v>
       </c>
       <c r="I53" t="n">
-        <v>122.03</v>
+        <v>121.13</v>
       </c>
       <c r="J53" t="n">
-        <v>97.31</v>
+        <v>97.89</v>
       </c>
       <c r="K53" t="n">
-        <v>24.72</v>
+        <v>23.24</v>
       </c>
       <c r="L53" t="n">
-        <v>0.293</v>
+        <v>0.2925</v>
       </c>
       <c r="M53" t="n">
-        <v>0.1487</v>
+        <v>0.1495</v>
       </c>
       <c r="N53" t="n">
-        <v>17.4</v>
+        <v>12.8</v>
       </c>
       <c r="O53" t="n">
         <v>2</v>
@@ -4212,7 +4212,7 @@
         <v>3</v>
       </c>
       <c r="U53" t="n">
-        <v>1775.1</v>
+        <v>1780.1</v>
       </c>
     </row>
     <row r="54">
